--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="129">
   <si>
     <t>id</t>
   </si>
@@ -528,6 +528,9 @@
   </si>
   <si>
     <t>糖果派对</t>
+  </si>
+  <si>
+    <t>伽罗宝石</t>
   </si>
   <si>
     <t>1980000_500000</t>
@@ -784,26 +787,19 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -817,13 +813,20 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1358,7 +1361,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1499,6 +1502,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1517,9 +1529,6 @@
     <xf numFmtId="176" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1527,9 +1536,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1544,14 +1550,8 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
@@ -1899,7 +1899,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T199"/>
+  <dimension ref="A1:T205"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -6577,619 +6577,619 @@
       <c r="T94" s="40"/>
     </row>
     <row r="95" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A95" s="50">
-        <v>10010010</v>
-      </c>
-      <c r="B95" s="51">
-        <v>100100</v>
-      </c>
-      <c r="C95" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="D95" s="53">
-        <v>100100026</v>
-      </c>
-      <c r="E95" s="54">
-        <v>10</v>
-      </c>
-      <c r="F95" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="G95" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="H95" s="55">
-        <v>0</v>
-      </c>
-      <c r="I95" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J95" s="57">
-        <v>0</v>
-      </c>
-      <c r="K95" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L95" s="58">
-        <v>0</v>
+      <c r="A95" s="34">
+        <v>1055001</v>
+      </c>
+      <c r="B95" s="35">
+        <v>105500</v>
+      </c>
+      <c r="C95" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D95" s="37">
+        <v>105500001</v>
+      </c>
+      <c r="E95" s="36">
+        <v>1</v>
+      </c>
+      <c r="F95" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="G95" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="H95" s="30">
+        <v>10000000</v>
+      </c>
+      <c r="I95" s="27">
+        <v>9500</v>
+      </c>
+      <c r="J95" s="25">
+        <v>5000000</v>
+      </c>
+      <c r="K95" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L95" s="38">
+        <v>100</v>
       </c>
       <c r="M95" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N95" s="59" t="s">
+      <c r="N95" s="39">
+        <v>0</v>
+      </c>
+      <c r="O95" s="51"/>
+      <c r="P95" s="51"/>
+      <c r="Q95" s="51"/>
+      <c r="R95" s="51"/>
+      <c r="S95" s="52"/>
+      <c r="T95" s="52"/>
+    </row>
+    <row r="96" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A96" s="34">
+        <v>1055002</v>
+      </c>
+      <c r="B96" s="35">
+        <v>105500</v>
+      </c>
+      <c r="C96" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="O95" s="60"/>
-      <c r="P95" s="60"/>
-      <c r="Q95" s="60"/>
-      <c r="R95" s="60"/>
-      <c r="S95" s="56"/>
-      <c r="T95" s="56"/>
-    </row>
-    <row r="96" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A96" s="50">
-        <v>10010011</v>
-      </c>
-      <c r="B96" s="51">
-        <v>100100</v>
-      </c>
-      <c r="C96" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="D96" s="53">
-        <v>100100026</v>
-      </c>
-      <c r="E96" s="54">
-        <v>11</v>
-      </c>
-      <c r="F96" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="G96" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="H96" s="55">
-        <v>0</v>
-      </c>
-      <c r="I96" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J96" s="57">
-        <v>0</v>
-      </c>
-      <c r="K96" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L96" s="58">
-        <v>0</v>
+      <c r="D96" s="37">
+        <v>105500001</v>
+      </c>
+      <c r="E96" s="36">
+        <v>2</v>
+      </c>
+      <c r="F96" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G96" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="H96" s="30">
+        <v>100000000</v>
+      </c>
+      <c r="I96" s="27">
+        <v>9500</v>
+      </c>
+      <c r="J96" s="25">
+        <v>50000000</v>
+      </c>
+      <c r="K96" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L96" s="38">
+        <v>100</v>
       </c>
       <c r="M96" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N96" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O96" s="60"/>
-      <c r="P96" s="60"/>
-      <c r="Q96" s="60"/>
-      <c r="R96" s="60"/>
-      <c r="S96" s="56"/>
-      <c r="T96" s="56"/>
+      <c r="N96" s="39">
+        <v>0</v>
+      </c>
+      <c r="O96" s="51"/>
+      <c r="P96" s="51"/>
+      <c r="Q96" s="51"/>
+      <c r="R96" s="51"/>
+      <c r="S96" s="52"/>
+      <c r="T96" s="52"/>
     </row>
     <row r="97" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A97" s="50">
-        <v>10010012</v>
-      </c>
-      <c r="B97" s="51">
-        <v>100100</v>
-      </c>
-      <c r="C97" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="D97" s="53">
-        <v>100100026</v>
-      </c>
-      <c r="E97" s="54">
-        <v>12</v>
-      </c>
-      <c r="F97" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="G97" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H97" s="61">
-        <v>0</v>
-      </c>
-      <c r="I97" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J97" s="57">
-        <v>0</v>
-      </c>
-      <c r="K97" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L97" s="58">
-        <v>0</v>
+      <c r="A97" s="34">
+        <v>1055003</v>
+      </c>
+      <c r="B97" s="35">
+        <v>105500</v>
+      </c>
+      <c r="C97" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D97" s="37">
+        <v>105500001</v>
+      </c>
+      <c r="E97" s="36">
+        <v>3</v>
+      </c>
+      <c r="F97" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="G97" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="H97" s="30">
+        <v>1000000000</v>
+      </c>
+      <c r="I97" s="27">
+        <v>9500</v>
+      </c>
+      <c r="J97" s="25">
+        <v>500000000</v>
+      </c>
+      <c r="K97" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L97" s="38">
+        <v>100</v>
       </c>
       <c r="M97" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N97" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O97" s="60"/>
-      <c r="P97" s="60"/>
-      <c r="Q97" s="60"/>
-      <c r="R97" s="60"/>
-      <c r="S97" s="56"/>
-      <c r="T97" s="56"/>
+      <c r="N97" s="39">
+        <v>0</v>
+      </c>
+      <c r="O97" s="51"/>
+      <c r="P97" s="51"/>
+      <c r="Q97" s="51"/>
+      <c r="R97" s="51"/>
+      <c r="S97" s="52"/>
+      <c r="T97" s="52"/>
     </row>
     <row r="98" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A98" s="50">
-        <v>10030010</v>
-      </c>
-      <c r="B98" s="51">
-        <v>100300</v>
-      </c>
-      <c r="C98" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="D98" s="53">
+      <c r="A98" s="53">
+        <v>10010010</v>
+      </c>
+      <c r="B98" s="54">
+        <v>100100</v>
+      </c>
+      <c r="C98" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="D98" s="56">
         <v>100100026</v>
       </c>
-      <c r="E98" s="54">
+      <c r="E98" s="57">
         <v>10</v>
       </c>
       <c r="F98" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G98" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H98" s="55">
-        <v>0</v>
-      </c>
-      <c r="I98" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J98" s="57">
-        <v>0</v>
-      </c>
-      <c r="K98" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L98" s="62">
+        <v>35</v>
+      </c>
+      <c r="H98" s="58">
+        <v>0</v>
+      </c>
+      <c r="I98" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J98" s="59">
+        <v>0</v>
+      </c>
+      <c r="K98" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L98" s="60">
         <v>0</v>
       </c>
       <c r="M98" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N98" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O98" s="60"/>
-      <c r="P98" s="60"/>
-      <c r="Q98" s="60"/>
-      <c r="R98" s="60"/>
-      <c r="S98" s="56"/>
-      <c r="T98" s="56"/>
+      <c r="N98" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O98" s="51"/>
+      <c r="P98" s="51"/>
+      <c r="Q98" s="51"/>
+      <c r="R98" s="51"/>
+      <c r="S98" s="52"/>
+      <c r="T98" s="52"/>
     </row>
     <row r="99" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A99" s="50">
-        <v>10030011</v>
-      </c>
-      <c r="B99" s="51">
-        <v>100300</v>
-      </c>
-      <c r="C99" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="D99" s="53">
+      <c r="A99" s="53">
+        <v>10010011</v>
+      </c>
+      <c r="B99" s="54">
+        <v>100100</v>
+      </c>
+      <c r="C99" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="D99" s="56">
         <v>100100026</v>
       </c>
-      <c r="E99" s="54">
+      <c r="E99" s="57">
         <v>11</v>
       </c>
       <c r="F99" s="23" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G99" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="H99" s="55">
-        <v>0</v>
-      </c>
-      <c r="I99" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J99" s="57">
-        <v>0</v>
-      </c>
-      <c r="K99" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L99" s="62">
+        <v>39</v>
+      </c>
+      <c r="H99" s="58">
+        <v>0</v>
+      </c>
+      <c r="I99" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J99" s="59">
+        <v>0</v>
+      </c>
+      <c r="K99" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L99" s="60">
         <v>0</v>
       </c>
       <c r="M99" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N99" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O99" s="60"/>
-      <c r="P99" s="60"/>
-      <c r="Q99" s="60"/>
-      <c r="R99" s="60"/>
-      <c r="S99" s="56"/>
-      <c r="T99" s="56"/>
+      <c r="N99" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O99" s="51"/>
+      <c r="P99" s="51"/>
+      <c r="Q99" s="51"/>
+      <c r="R99" s="51"/>
+      <c r="S99" s="52"/>
+      <c r="T99" s="52"/>
     </row>
     <row r="100" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A100" s="50">
-        <v>10030012</v>
-      </c>
-      <c r="B100" s="51">
-        <v>100300</v>
-      </c>
-      <c r="C100" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="D100" s="53">
+      <c r="A100" s="53">
+        <v>10010012</v>
+      </c>
+      <c r="B100" s="54">
+        <v>100100</v>
+      </c>
+      <c r="C100" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" s="56">
         <v>100100026</v>
       </c>
-      <c r="E100" s="54">
+      <c r="E100" s="57">
         <v>12</v>
       </c>
       <c r="F100" s="23" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G100" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H100" s="61">
-        <v>0</v>
-      </c>
-      <c r="I100" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J100" s="57">
-        <v>0</v>
-      </c>
-      <c r="K100" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L100" s="62">
+        <v>42</v>
+      </c>
+      <c r="H100" s="62">
+        <v>0</v>
+      </c>
+      <c r="I100" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J100" s="59">
+        <v>0</v>
+      </c>
+      <c r="K100" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L100" s="60">
         <v>0</v>
       </c>
       <c r="M100" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N100" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O100" s="60"/>
-      <c r="P100" s="60"/>
-      <c r="Q100" s="60"/>
-      <c r="R100" s="60"/>
-      <c r="S100" s="56"/>
-      <c r="T100" s="56"/>
+      <c r="N100" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O100" s="51"/>
+      <c r="P100" s="51"/>
+      <c r="Q100" s="51"/>
+      <c r="R100" s="51"/>
+      <c r="S100" s="52"/>
+      <c r="T100" s="52"/>
     </row>
     <row r="101" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A101" s="50">
-        <v>10070010</v>
-      </c>
-      <c r="B101" s="51">
-        <v>100700</v>
-      </c>
-      <c r="C101" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="D101" s="53">
+      <c r="A101" s="53">
+        <v>10030010</v>
+      </c>
+      <c r="B101" s="54">
+        <v>100300</v>
+      </c>
+      <c r="C101" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="D101" s="56">
         <v>100100026</v>
       </c>
-      <c r="E101" s="54">
+      <c r="E101" s="57">
         <v>10</v>
       </c>
       <c r="F101" s="23" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G101" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H101" s="55">
-        <v>0</v>
-      </c>
-      <c r="I101" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J101" s="57">
-        <v>0</v>
-      </c>
-      <c r="K101" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L101" s="58">
+        <v>42</v>
+      </c>
+      <c r="H101" s="58">
+        <v>0</v>
+      </c>
+      <c r="I101" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J101" s="59">
+        <v>0</v>
+      </c>
+      <c r="K101" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L101" s="63">
         <v>0</v>
       </c>
       <c r="M101" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N101" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O101" s="60"/>
-      <c r="P101" s="60"/>
-      <c r="Q101" s="60"/>
-      <c r="R101" s="60"/>
-      <c r="S101" s="56"/>
-      <c r="T101" s="56"/>
+      <c r="N101" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O101" s="51"/>
+      <c r="P101" s="51"/>
+      <c r="Q101" s="51"/>
+      <c r="R101" s="51"/>
+      <c r="S101" s="52"/>
+      <c r="T101" s="52"/>
     </row>
     <row r="102" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A102" s="50">
-        <v>10070011</v>
-      </c>
-      <c r="B102" s="51">
-        <v>100700</v>
-      </c>
-      <c r="C102" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="D102" s="53">
+      <c r="A102" s="53">
+        <v>10030011</v>
+      </c>
+      <c r="B102" s="54">
+        <v>100300</v>
+      </c>
+      <c r="C102" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="D102" s="56">
         <v>100100026</v>
       </c>
-      <c r="E102" s="54">
+      <c r="E102" s="57">
         <v>11</v>
       </c>
       <c r="F102" s="23" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G102" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H102" s="55">
-        <v>0</v>
-      </c>
-      <c r="I102" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J102" s="57">
-        <v>0</v>
-      </c>
-      <c r="K102" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L102" s="58">
+        <v>46</v>
+      </c>
+      <c r="H102" s="58">
+        <v>0</v>
+      </c>
+      <c r="I102" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J102" s="59">
+        <v>0</v>
+      </c>
+      <c r="K102" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L102" s="63">
         <v>0</v>
       </c>
       <c r="M102" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N102" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O102" s="60"/>
-      <c r="P102" s="60"/>
-      <c r="Q102" s="60"/>
-      <c r="R102" s="60"/>
-      <c r="S102" s="56"/>
-      <c r="T102" s="56"/>
+      <c r="N102" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O102" s="51"/>
+      <c r="P102" s="51"/>
+      <c r="Q102" s="51"/>
+      <c r="R102" s="51"/>
+      <c r="S102" s="52"/>
+      <c r="T102" s="52"/>
     </row>
     <row r="103" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A103" s="50">
-        <v>10070012</v>
-      </c>
-      <c r="B103" s="51">
-        <v>100700</v>
-      </c>
-      <c r="C103" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="D103" s="53">
+      <c r="A103" s="53">
+        <v>10030012</v>
+      </c>
+      <c r="B103" s="54">
+        <v>100300</v>
+      </c>
+      <c r="C103" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="D103" s="56">
         <v>100100026</v>
       </c>
-      <c r="E103" s="54">
+      <c r="E103" s="57">
         <v>12</v>
       </c>
       <c r="F103" s="23" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G103" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="H103" s="61">
-        <v>0</v>
-      </c>
-      <c r="I103" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J103" s="57">
-        <v>0</v>
-      </c>
-      <c r="K103" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L103" s="58">
+        <v>48</v>
+      </c>
+      <c r="H103" s="62">
+        <v>0</v>
+      </c>
+      <c r="I103" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J103" s="59">
+        <v>0</v>
+      </c>
+      <c r="K103" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L103" s="63">
         <v>0</v>
       </c>
       <c r="M103" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N103" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O103" s="60"/>
-      <c r="P103" s="60"/>
-      <c r="Q103" s="60"/>
-      <c r="R103" s="60"/>
-      <c r="S103" s="56"/>
-      <c r="T103" s="56"/>
-    </row>
-    <row r="104" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A104" s="50">
-        <v>10120010</v>
-      </c>
-      <c r="B104" s="63">
-        <v>101200</v>
-      </c>
-      <c r="C104" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="D104" s="64">
-        <v>101200026</v>
-      </c>
-      <c r="E104" s="54">
+      <c r="N103" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O103" s="51"/>
+      <c r="P103" s="51"/>
+      <c r="Q103" s="51"/>
+      <c r="R103" s="51"/>
+      <c r="S103" s="52"/>
+      <c r="T103" s="52"/>
+    </row>
+    <row r="104" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A104" s="53">
+        <v>10070010</v>
+      </c>
+      <c r="B104" s="54">
+        <v>100700</v>
+      </c>
+      <c r="C104" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="D104" s="56">
+        <v>100100026</v>
+      </c>
+      <c r="E104" s="57">
         <v>10</v>
       </c>
       <c r="F104" s="23" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G104" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="H104" s="55">
-        <v>0</v>
-      </c>
-      <c r="I104" s="57">
-        <v>9500</v>
-      </c>
-      <c r="J104" s="57">
-        <v>0</v>
-      </c>
-      <c r="K104" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="L104" s="62">
+        <v>51</v>
+      </c>
+      <c r="H104" s="58">
+        <v>0</v>
+      </c>
+      <c r="I104" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J104" s="59">
+        <v>0</v>
+      </c>
+      <c r="K104" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L104" s="60">
         <v>0</v>
       </c>
       <c r="M104" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N104" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O104" s="59"/>
-      <c r="P104" s="59"/>
-      <c r="Q104" s="59"/>
-      <c r="R104" s="59"/>
-      <c r="S104" s="57"/>
-      <c r="T104" s="57"/>
-    </row>
-    <row r="105" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A105" s="50">
-        <v>10120011</v>
-      </c>
-      <c r="B105" s="63">
-        <v>101200</v>
-      </c>
-      <c r="C105" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="D105" s="64">
-        <v>101200026</v>
-      </c>
-      <c r="E105" s="54">
+      <c r="N104" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O104" s="51"/>
+      <c r="P104" s="51"/>
+      <c r="Q104" s="51"/>
+      <c r="R104" s="51"/>
+      <c r="S104" s="52"/>
+      <c r="T104" s="52"/>
+    </row>
+    <row r="105" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A105" s="53">
+        <v>10070011</v>
+      </c>
+      <c r="B105" s="54">
+        <v>100700</v>
+      </c>
+      <c r="C105" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="D105" s="56">
+        <v>100100026</v>
+      </c>
+      <c r="E105" s="57">
         <v>11</v>
       </c>
       <c r="F105" s="23" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G105" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H105" s="55">
-        <v>0</v>
-      </c>
-      <c r="I105" s="57">
-        <v>9500</v>
-      </c>
-      <c r="J105" s="57">
-        <v>0</v>
-      </c>
-      <c r="K105" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="L105" s="62">
+        <v>53</v>
+      </c>
+      <c r="H105" s="58">
+        <v>0</v>
+      </c>
+      <c r="I105" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J105" s="59">
+        <v>0</v>
+      </c>
+      <c r="K105" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L105" s="60">
         <v>0</v>
       </c>
       <c r="M105" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N105" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O105" s="59"/>
-      <c r="P105" s="59"/>
-      <c r="Q105" s="59"/>
-      <c r="R105" s="59"/>
-      <c r="S105" s="57"/>
-      <c r="T105" s="57"/>
-    </row>
-    <row r="106" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A106" s="50">
-        <v>10120012</v>
-      </c>
-      <c r="B106" s="63">
-        <v>101200</v>
-      </c>
-      <c r="C106" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="D106" s="64">
-        <v>101200026</v>
-      </c>
-      <c r="E106" s="54">
+      <c r="N105" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O105" s="51"/>
+      <c r="P105" s="51"/>
+      <c r="Q105" s="51"/>
+      <c r="R105" s="51"/>
+      <c r="S105" s="52"/>
+      <c r="T105" s="52"/>
+    </row>
+    <row r="106" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A106" s="53">
+        <v>10070012</v>
+      </c>
+      <c r="B106" s="54">
+        <v>100700</v>
+      </c>
+      <c r="C106" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="D106" s="56">
+        <v>100100026</v>
+      </c>
+      <c r="E106" s="57">
         <v>12</v>
       </c>
       <c r="F106" s="23" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G106" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="H106" s="61">
-        <v>0</v>
-      </c>
-      <c r="I106" s="57">
-        <v>9500</v>
-      </c>
-      <c r="J106" s="57">
-        <v>0</v>
-      </c>
-      <c r="K106" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="L106" s="62">
+        <v>55</v>
+      </c>
+      <c r="H106" s="62">
+        <v>0</v>
+      </c>
+      <c r="I106" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J106" s="59">
+        <v>0</v>
+      </c>
+      <c r="K106" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L106" s="60">
         <v>0</v>
       </c>
       <c r="M106" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N106" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O106" s="59"/>
-      <c r="P106" s="59"/>
-      <c r="Q106" s="59"/>
-      <c r="R106" s="59"/>
-      <c r="S106" s="57"/>
-      <c r="T106" s="57"/>
-    </row>
-    <row r="107" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A107" s="50">
-        <v>10140010</v>
-      </c>
-      <c r="B107" s="51">
-        <v>101400</v>
-      </c>
-      <c r="C107" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="D107" s="53">
-        <v>100100026</v>
-      </c>
-      <c r="E107" s="54">
+      <c r="N106" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O106" s="51"/>
+      <c r="P106" s="51"/>
+      <c r="Q106" s="51"/>
+      <c r="R106" s="51"/>
+      <c r="S106" s="52"/>
+      <c r="T106" s="52"/>
+    </row>
+    <row r="107" s="6" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A107" s="53">
+        <v>10120010</v>
+      </c>
+      <c r="B107" s="64">
+        <v>101200</v>
+      </c>
+      <c r="C107" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="D107" s="65">
+        <v>101200026</v>
+      </c>
+      <c r="E107" s="57">
         <v>10</v>
       </c>
       <c r="F107" s="23" t="s">
@@ -7198,48 +7198,48 @@
       <c r="G107" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H107" s="55">
-        <v>0</v>
-      </c>
-      <c r="I107" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J107" s="57">
-        <v>0</v>
-      </c>
-      <c r="K107" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L107" s="58">
+      <c r="H107" s="58">
+        <v>0</v>
+      </c>
+      <c r="I107" s="59">
+        <v>9500</v>
+      </c>
+      <c r="J107" s="59">
+        <v>0</v>
+      </c>
+      <c r="K107" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="L107" s="63">
         <v>0</v>
       </c>
       <c r="M107" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N107" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O107" s="60"/>
-      <c r="P107" s="60"/>
-      <c r="Q107" s="60"/>
-      <c r="R107" s="60"/>
-      <c r="S107" s="56"/>
-      <c r="T107" s="56"/>
-    </row>
-    <row r="108" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A108" s="50">
-        <v>10140011</v>
-      </c>
-      <c r="B108" s="51">
-        <v>101400</v>
-      </c>
-      <c r="C108" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="D108" s="53">
-        <v>100100026</v>
-      </c>
-      <c r="E108" s="54">
+      <c r="N107" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O107" s="61"/>
+      <c r="P107" s="61"/>
+      <c r="Q107" s="61"/>
+      <c r="R107" s="61"/>
+      <c r="S107" s="59"/>
+      <c r="T107" s="59"/>
+    </row>
+    <row r="108" s="6" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A108" s="53">
+        <v>10120011</v>
+      </c>
+      <c r="B108" s="64">
+        <v>101200</v>
+      </c>
+      <c r="C108" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="D108" s="65">
+        <v>101200026</v>
+      </c>
+      <c r="E108" s="57">
         <v>11</v>
       </c>
       <c r="F108" s="23" t="s">
@@ -7248,48 +7248,48 @@
       <c r="G108" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="H108" s="55">
-        <v>0</v>
-      </c>
-      <c r="I108" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J108" s="57">
-        <v>0</v>
-      </c>
-      <c r="K108" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L108" s="58">
+      <c r="H108" s="58">
+        <v>0</v>
+      </c>
+      <c r="I108" s="59">
+        <v>9500</v>
+      </c>
+      <c r="J108" s="59">
+        <v>0</v>
+      </c>
+      <c r="K108" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="L108" s="63">
         <v>0</v>
       </c>
       <c r="M108" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N108" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O108" s="60"/>
-      <c r="P108" s="60"/>
-      <c r="Q108" s="60"/>
-      <c r="R108" s="60"/>
-      <c r="S108" s="56"/>
-      <c r="T108" s="56"/>
-    </row>
-    <row r="109" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A109" s="50">
-        <v>10140012</v>
-      </c>
-      <c r="B109" s="51">
-        <v>101400</v>
-      </c>
-      <c r="C109" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="D109" s="53">
-        <v>100100026</v>
-      </c>
-      <c r="E109" s="54">
+      <c r="N108" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O108" s="61"/>
+      <c r="P108" s="61"/>
+      <c r="Q108" s="61"/>
+      <c r="R108" s="61"/>
+      <c r="S108" s="59"/>
+      <c r="T108" s="59"/>
+    </row>
+    <row r="109" s="6" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A109" s="53">
+        <v>10120012</v>
+      </c>
+      <c r="B109" s="64">
+        <v>101200</v>
+      </c>
+      <c r="C109" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="D109" s="65">
+        <v>101200026</v>
+      </c>
+      <c r="E109" s="57">
         <v>12</v>
       </c>
       <c r="F109" s="23" t="s">
@@ -7298,198 +7298,198 @@
       <c r="G109" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="H109" s="61">
-        <v>0</v>
-      </c>
-      <c r="I109" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J109" s="57">
-        <v>0</v>
-      </c>
-      <c r="K109" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L109" s="58">
+      <c r="H109" s="62">
+        <v>0</v>
+      </c>
+      <c r="I109" s="59">
+        <v>9500</v>
+      </c>
+      <c r="J109" s="59">
+        <v>0</v>
+      </c>
+      <c r="K109" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="L109" s="63">
         <v>0</v>
       </c>
       <c r="M109" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N109" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O109" s="60"/>
-      <c r="P109" s="60"/>
-      <c r="Q109" s="60"/>
-      <c r="R109" s="60"/>
-      <c r="S109" s="56"/>
-      <c r="T109" s="56"/>
+      <c r="N109" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O109" s="61"/>
+      <c r="P109" s="61"/>
+      <c r="Q109" s="61"/>
+      <c r="R109" s="61"/>
+      <c r="S109" s="59"/>
+      <c r="T109" s="59"/>
     </row>
     <row r="110" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A110" s="50">
-        <v>10170010</v>
-      </c>
-      <c r="B110" s="51">
-        <v>101700</v>
-      </c>
-      <c r="C110" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="D110" s="53">
-        <v>101700001</v>
-      </c>
-      <c r="E110" s="54">
+      <c r="A110" s="53">
+        <v>10140010</v>
+      </c>
+      <c r="B110" s="54">
+        <v>101400</v>
+      </c>
+      <c r="C110" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="D110" s="56">
+        <v>100100026</v>
+      </c>
+      <c r="E110" s="57">
         <v>10</v>
       </c>
       <c r="F110" s="23" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G110" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H110" s="55">
-        <v>0</v>
-      </c>
-      <c r="I110" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J110" s="57">
-        <v>0</v>
-      </c>
-      <c r="K110" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L110" s="58">
+        <v>39</v>
+      </c>
+      <c r="H110" s="58">
+        <v>0</v>
+      </c>
+      <c r="I110" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J110" s="59">
+        <v>0</v>
+      </c>
+      <c r="K110" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L110" s="60">
         <v>0</v>
       </c>
       <c r="M110" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N110" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O110" s="60"/>
-      <c r="P110" s="60"/>
-      <c r="Q110" s="60"/>
-      <c r="R110" s="60"/>
-      <c r="S110" s="56"/>
-      <c r="T110" s="56"/>
+      <c r="N110" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O110" s="51"/>
+      <c r="P110" s="51"/>
+      <c r="Q110" s="51"/>
+      <c r="R110" s="51"/>
+      <c r="S110" s="52"/>
+      <c r="T110" s="52"/>
     </row>
     <row r="111" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A111" s="50">
-        <v>10170011</v>
-      </c>
-      <c r="B111" s="51">
-        <v>101700</v>
-      </c>
-      <c r="C111" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="D111" s="53">
-        <v>101700001</v>
-      </c>
-      <c r="E111" s="54">
+      <c r="A111" s="53">
+        <v>10140011</v>
+      </c>
+      <c r="B111" s="54">
+        <v>101400</v>
+      </c>
+      <c r="C111" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="D111" s="56">
+        <v>100100026</v>
+      </c>
+      <c r="E111" s="57">
         <v>11</v>
       </c>
       <c r="F111" s="23" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G111" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H111" s="55">
-        <v>0</v>
-      </c>
-      <c r="I111" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J111" s="57">
-        <v>0</v>
-      </c>
-      <c r="K111" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L111" s="58">
+        <v>42</v>
+      </c>
+      <c r="H111" s="58">
+        <v>0</v>
+      </c>
+      <c r="I111" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J111" s="59">
+        <v>0</v>
+      </c>
+      <c r="K111" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L111" s="60">
         <v>0</v>
       </c>
       <c r="M111" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N111" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O111" s="60"/>
-      <c r="P111" s="60"/>
-      <c r="Q111" s="60"/>
-      <c r="R111" s="60"/>
-      <c r="S111" s="56"/>
-      <c r="T111" s="56"/>
+      <c r="N111" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O111" s="51"/>
+      <c r="P111" s="51"/>
+      <c r="Q111" s="51"/>
+      <c r="R111" s="51"/>
+      <c r="S111" s="52"/>
+      <c r="T111" s="52"/>
     </row>
     <row r="112" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A112" s="50">
-        <v>10170012</v>
-      </c>
-      <c r="B112" s="51">
-        <v>101700</v>
-      </c>
-      <c r="C112" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="D112" s="53">
-        <v>101700001</v>
-      </c>
-      <c r="E112" s="54">
+      <c r="A112" s="53">
+        <v>10140012</v>
+      </c>
+      <c r="B112" s="54">
+        <v>101400</v>
+      </c>
+      <c r="C112" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="D112" s="56">
+        <v>100100026</v>
+      </c>
+      <c r="E112" s="57">
         <v>12</v>
       </c>
       <c r="F112" s="23" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G112" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="H112" s="61">
-        <v>0</v>
-      </c>
-      <c r="I112" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J112" s="57">
-        <v>0</v>
-      </c>
-      <c r="K112" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L112" s="58">
+        <v>46</v>
+      </c>
+      <c r="H112" s="62">
+        <v>0</v>
+      </c>
+      <c r="I112" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J112" s="59">
+        <v>0</v>
+      </c>
+      <c r="K112" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L112" s="60">
         <v>0</v>
       </c>
       <c r="M112" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N112" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O112" s="60"/>
-      <c r="P112" s="60"/>
-      <c r="Q112" s="60"/>
-      <c r="R112" s="60"/>
-      <c r="S112" s="56"/>
-      <c r="T112" s="56"/>
+      <c r="N112" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O112" s="51"/>
+      <c r="P112" s="51"/>
+      <c r="Q112" s="51"/>
+      <c r="R112" s="51"/>
+      <c r="S112" s="52"/>
+      <c r="T112" s="52"/>
     </row>
     <row r="113" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A113" s="50">
-        <v>10210010</v>
-      </c>
-      <c r="B113" s="51">
-        <v>102100</v>
-      </c>
-      <c r="C113" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="D113" s="53">
-        <v>102100001</v>
-      </c>
-      <c r="E113" s="54">
+      <c r="A113" s="53">
+        <v>10170010</v>
+      </c>
+      <c r="B113" s="54">
+        <v>101700</v>
+      </c>
+      <c r="C113" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="D113" s="56">
+        <v>101700001</v>
+      </c>
+      <c r="E113" s="57">
         <v>10</v>
       </c>
       <c r="F113" s="23" t="s">
@@ -7498,48 +7498,48 @@
       <c r="G113" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H113" s="55">
-        <v>0</v>
-      </c>
-      <c r="I113" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J113" s="57">
-        <v>0</v>
-      </c>
-      <c r="K113" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L113" s="62">
+      <c r="H113" s="58">
+        <v>0</v>
+      </c>
+      <c r="I113" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J113" s="59">
+        <v>0</v>
+      </c>
+      <c r="K113" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L113" s="60">
         <v>0</v>
       </c>
       <c r="M113" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N113" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O113" s="60"/>
-      <c r="P113" s="60"/>
-      <c r="Q113" s="60"/>
-      <c r="R113" s="60"/>
-      <c r="S113" s="56"/>
-      <c r="T113" s="56"/>
+      <c r="N113" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O113" s="51"/>
+      <c r="P113" s="51"/>
+      <c r="Q113" s="51"/>
+      <c r="R113" s="51"/>
+      <c r="S113" s="52"/>
+      <c r="T113" s="52"/>
     </row>
     <row r="114" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A114" s="50">
-        <v>10210011</v>
-      </c>
-      <c r="B114" s="51">
-        <v>102100</v>
-      </c>
-      <c r="C114" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="D114" s="53">
-        <v>102100001</v>
-      </c>
-      <c r="E114" s="54">
+      <c r="A114" s="53">
+        <v>10170011</v>
+      </c>
+      <c r="B114" s="54">
+        <v>101700</v>
+      </c>
+      <c r="C114" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="D114" s="56">
+        <v>101700001</v>
+      </c>
+      <c r="E114" s="57">
         <v>11</v>
       </c>
       <c r="F114" s="23" t="s">
@@ -7548,48 +7548,48 @@
       <c r="G114" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H114" s="55">
-        <v>0</v>
-      </c>
-      <c r="I114" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J114" s="57">
-        <v>0</v>
-      </c>
-      <c r="K114" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L114" s="62">
+      <c r="H114" s="58">
+        <v>0</v>
+      </c>
+      <c r="I114" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J114" s="59">
+        <v>0</v>
+      </c>
+      <c r="K114" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L114" s="60">
         <v>0</v>
       </c>
       <c r="M114" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N114" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O114" s="60"/>
-      <c r="P114" s="60"/>
-      <c r="Q114" s="60"/>
-      <c r="R114" s="60"/>
-      <c r="S114" s="56"/>
-      <c r="T114" s="56"/>
+      <c r="N114" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O114" s="51"/>
+      <c r="P114" s="51"/>
+      <c r="Q114" s="51"/>
+      <c r="R114" s="51"/>
+      <c r="S114" s="52"/>
+      <c r="T114" s="52"/>
     </row>
     <row r="115" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A115" s="50">
-        <v>10210012</v>
-      </c>
-      <c r="B115" s="51">
-        <v>102100</v>
-      </c>
-      <c r="C115" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="D115" s="53">
-        <v>102100001</v>
-      </c>
-      <c r="E115" s="54">
+      <c r="A115" s="53">
+        <v>10170012</v>
+      </c>
+      <c r="B115" s="54">
+        <v>101700</v>
+      </c>
+      <c r="C115" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="D115" s="56">
+        <v>101700001</v>
+      </c>
+      <c r="E115" s="57">
         <v>12</v>
       </c>
       <c r="F115" s="23" t="s">
@@ -7598,48 +7598,48 @@
       <c r="G115" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="H115" s="61">
-        <v>0</v>
-      </c>
-      <c r="I115" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J115" s="57">
-        <v>0</v>
-      </c>
-      <c r="K115" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L115" s="62">
+      <c r="H115" s="62">
+        <v>0</v>
+      </c>
+      <c r="I115" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J115" s="59">
+        <v>0</v>
+      </c>
+      <c r="K115" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L115" s="60">
         <v>0</v>
       </c>
       <c r="M115" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N115" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O115" s="60"/>
-      <c r="P115" s="60"/>
-      <c r="Q115" s="60"/>
-      <c r="R115" s="60"/>
-      <c r="S115" s="56"/>
-      <c r="T115" s="56"/>
+      <c r="N115" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O115" s="51"/>
+      <c r="P115" s="51"/>
+      <c r="Q115" s="51"/>
+      <c r="R115" s="51"/>
+      <c r="S115" s="52"/>
+      <c r="T115" s="52"/>
     </row>
     <row r="116" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A116" s="50">
-        <v>10220010</v>
-      </c>
-      <c r="B116" s="51">
-        <v>102200</v>
-      </c>
-      <c r="C116" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="D116" s="53">
-        <v>102200001</v>
-      </c>
-      <c r="E116" s="54">
+      <c r="A116" s="53">
+        <v>10210010</v>
+      </c>
+      <c r="B116" s="54">
+        <v>102100</v>
+      </c>
+      <c r="C116" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="D116" s="56">
+        <v>102100001</v>
+      </c>
+      <c r="E116" s="57">
         <v>10</v>
       </c>
       <c r="F116" s="23" t="s">
@@ -7648,48 +7648,48 @@
       <c r="G116" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H116" s="55">
-        <v>0</v>
-      </c>
-      <c r="I116" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J116" s="57">
-        <v>0</v>
-      </c>
-      <c r="K116" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L116" s="62">
+      <c r="H116" s="58">
+        <v>0</v>
+      </c>
+      <c r="I116" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J116" s="59">
+        <v>0</v>
+      </c>
+      <c r="K116" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L116" s="63">
         <v>0</v>
       </c>
       <c r="M116" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N116" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O116" s="60"/>
-      <c r="P116" s="60"/>
-      <c r="Q116" s="60"/>
-      <c r="R116" s="60"/>
-      <c r="S116" s="56"/>
-      <c r="T116" s="56"/>
+      <c r="N116" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O116" s="51"/>
+      <c r="P116" s="51"/>
+      <c r="Q116" s="51"/>
+      <c r="R116" s="51"/>
+      <c r="S116" s="52"/>
+      <c r="T116" s="52"/>
     </row>
     <row r="117" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A117" s="50">
-        <v>10220011</v>
-      </c>
-      <c r="B117" s="51">
-        <v>102200</v>
-      </c>
-      <c r="C117" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="D117" s="53">
-        <v>102200001</v>
-      </c>
-      <c r="E117" s="54">
+      <c r="A117" s="53">
+        <v>10210011</v>
+      </c>
+      <c r="B117" s="54">
+        <v>102100</v>
+      </c>
+      <c r="C117" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="D117" s="56">
+        <v>102100001</v>
+      </c>
+      <c r="E117" s="57">
         <v>11</v>
       </c>
       <c r="F117" s="23" t="s">
@@ -7698,48 +7698,48 @@
       <c r="G117" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H117" s="55">
-        <v>0</v>
-      </c>
-      <c r="I117" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J117" s="57">
-        <v>0</v>
-      </c>
-      <c r="K117" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L117" s="62">
+      <c r="H117" s="58">
+        <v>0</v>
+      </c>
+      <c r="I117" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J117" s="59">
+        <v>0</v>
+      </c>
+      <c r="K117" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L117" s="63">
         <v>0</v>
       </c>
       <c r="M117" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N117" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O117" s="60"/>
-      <c r="P117" s="60"/>
-      <c r="Q117" s="60"/>
-      <c r="R117" s="60"/>
-      <c r="S117" s="56"/>
-      <c r="T117" s="56"/>
+      <c r="N117" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O117" s="51"/>
+      <c r="P117" s="51"/>
+      <c r="Q117" s="51"/>
+      <c r="R117" s="51"/>
+      <c r="S117" s="52"/>
+      <c r="T117" s="52"/>
     </row>
     <row r="118" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A118" s="50">
-        <v>10220012</v>
-      </c>
-      <c r="B118" s="51">
-        <v>102200</v>
-      </c>
-      <c r="C118" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="D118" s="53">
-        <v>102200001</v>
-      </c>
-      <c r="E118" s="54">
+      <c r="A118" s="53">
+        <v>10210012</v>
+      </c>
+      <c r="B118" s="54">
+        <v>102100</v>
+      </c>
+      <c r="C118" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="D118" s="56">
+        <v>102100001</v>
+      </c>
+      <c r="E118" s="57">
         <v>12</v>
       </c>
       <c r="F118" s="23" t="s">
@@ -7748,948 +7748,948 @@
       <c r="G118" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="H118" s="61">
-        <v>0</v>
-      </c>
-      <c r="I118" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J118" s="57">
-        <v>0</v>
-      </c>
-      <c r="K118" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L118" s="62">
+      <c r="H118" s="62">
+        <v>0</v>
+      </c>
+      <c r="I118" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J118" s="59">
+        <v>0</v>
+      </c>
+      <c r="K118" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L118" s="63">
         <v>0</v>
       </c>
       <c r="M118" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N118" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O118" s="60"/>
-      <c r="P118" s="60"/>
-      <c r="Q118" s="60"/>
-      <c r="R118" s="60"/>
-      <c r="S118" s="56"/>
-      <c r="T118" s="56"/>
+      <c r="N118" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O118" s="51"/>
+      <c r="P118" s="51"/>
+      <c r="Q118" s="51"/>
+      <c r="R118" s="51"/>
+      <c r="S118" s="52"/>
+      <c r="T118" s="52"/>
     </row>
     <row r="119" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A119" s="50">
-        <v>10240010</v>
-      </c>
-      <c r="B119" s="51">
-        <v>102400</v>
-      </c>
-      <c r="C119" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="D119" s="53">
-        <v>102400026</v>
-      </c>
-      <c r="E119" s="54">
+      <c r="A119" s="53">
+        <v>10220010</v>
+      </c>
+      <c r="B119" s="54">
+        <v>102200</v>
+      </c>
+      <c r="C119" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D119" s="56">
+        <v>102200001</v>
+      </c>
+      <c r="E119" s="57">
         <v>10</v>
       </c>
       <c r="F119" s="23" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G119" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="H119" s="55">
-        <v>0</v>
-      </c>
-      <c r="I119" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J119" s="57">
-        <v>0</v>
-      </c>
-      <c r="K119" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L119" s="62">
+        <v>51</v>
+      </c>
+      <c r="H119" s="58">
+        <v>0</v>
+      </c>
+      <c r="I119" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J119" s="59">
+        <v>0</v>
+      </c>
+      <c r="K119" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L119" s="63">
         <v>0</v>
       </c>
       <c r="M119" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N119" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O119" s="60"/>
-      <c r="P119" s="60"/>
-      <c r="Q119" s="60"/>
-      <c r="R119" s="60"/>
-      <c r="S119" s="56"/>
-      <c r="T119" s="56"/>
+      <c r="N119" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O119" s="51"/>
+      <c r="P119" s="51"/>
+      <c r="Q119" s="51"/>
+      <c r="R119" s="51"/>
+      <c r="S119" s="52"/>
+      <c r="T119" s="52"/>
     </row>
     <row r="120" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A120" s="50">
-        <v>10240011</v>
-      </c>
-      <c r="B120" s="51">
-        <v>102400</v>
-      </c>
-      <c r="C120" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="D120" s="53">
-        <v>102400026</v>
-      </c>
-      <c r="E120" s="54">
+      <c r="A120" s="53">
+        <v>10220011</v>
+      </c>
+      <c r="B120" s="54">
+        <v>102200</v>
+      </c>
+      <c r="C120" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D120" s="56">
+        <v>102200001</v>
+      </c>
+      <c r="E120" s="57">
         <v>11</v>
       </c>
       <c r="F120" s="23" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G120" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="H120" s="55">
-        <v>0</v>
-      </c>
-      <c r="I120" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J120" s="57">
-        <v>0</v>
-      </c>
-      <c r="K120" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L120" s="62">
+        <v>53</v>
+      </c>
+      <c r="H120" s="58">
+        <v>0</v>
+      </c>
+      <c r="I120" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J120" s="59">
+        <v>0</v>
+      </c>
+      <c r="K120" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L120" s="63">
         <v>0</v>
       </c>
       <c r="M120" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N120" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O120" s="60"/>
-      <c r="P120" s="60"/>
-      <c r="Q120" s="60"/>
-      <c r="R120" s="60"/>
-      <c r="S120" s="56"/>
-      <c r="T120" s="56"/>
+      <c r="N120" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O120" s="51"/>
+      <c r="P120" s="51"/>
+      <c r="Q120" s="51"/>
+      <c r="R120" s="51"/>
+      <c r="S120" s="52"/>
+      <c r="T120" s="52"/>
     </row>
     <row r="121" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A121" s="50">
-        <v>10240012</v>
-      </c>
-      <c r="B121" s="51">
-        <v>102400</v>
-      </c>
-      <c r="C121" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="D121" s="53">
-        <v>102400026</v>
-      </c>
-      <c r="E121" s="54">
+      <c r="A121" s="53">
+        <v>10220012</v>
+      </c>
+      <c r="B121" s="54">
+        <v>102200</v>
+      </c>
+      <c r="C121" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D121" s="56">
+        <v>102200001</v>
+      </c>
+      <c r="E121" s="57">
         <v>12</v>
       </c>
       <c r="F121" s="23" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G121" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H121" s="61">
-        <v>0</v>
-      </c>
-      <c r="I121" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J121" s="57">
-        <v>0</v>
-      </c>
-      <c r="K121" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L121" s="62">
+        <v>55</v>
+      </c>
+      <c r="H121" s="62">
+        <v>0</v>
+      </c>
+      <c r="I121" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J121" s="59">
+        <v>0</v>
+      </c>
+      <c r="K121" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L121" s="63">
         <v>0</v>
       </c>
       <c r="M121" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N121" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O121" s="60"/>
-      <c r="P121" s="60"/>
-      <c r="Q121" s="60"/>
-      <c r="R121" s="60"/>
-      <c r="S121" s="56"/>
-      <c r="T121" s="56"/>
+      <c r="N121" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O121" s="51"/>
+      <c r="P121" s="51"/>
+      <c r="Q121" s="51"/>
+      <c r="R121" s="51"/>
+      <c r="S121" s="52"/>
+      <c r="T121" s="52"/>
     </row>
     <row r="122" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A122" s="50">
-        <v>10180010</v>
-      </c>
-      <c r="B122" s="51">
-        <v>101800</v>
-      </c>
-      <c r="C122" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="D122" s="53">
-        <v>101800001</v>
-      </c>
-      <c r="E122" s="54">
+      <c r="A122" s="53">
+        <v>10240010</v>
+      </c>
+      <c r="B122" s="54">
+        <v>102400</v>
+      </c>
+      <c r="C122" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="D122" s="56">
+        <v>102400026</v>
+      </c>
+      <c r="E122" s="57">
         <v>10</v>
       </c>
       <c r="F122" s="23" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G122" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H122" s="61">
-        <v>0</v>
-      </c>
-      <c r="I122" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J122" s="57">
-        <v>0</v>
-      </c>
-      <c r="K122" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L122" s="62">
+        <v>35</v>
+      </c>
+      <c r="H122" s="58">
+        <v>0</v>
+      </c>
+      <c r="I122" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J122" s="59">
+        <v>0</v>
+      </c>
+      <c r="K122" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L122" s="63">
         <v>0</v>
       </c>
       <c r="M122" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N122" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O122" s="60"/>
-      <c r="P122" s="60"/>
-      <c r="Q122" s="60"/>
-      <c r="R122" s="60"/>
-      <c r="S122" s="56"/>
-      <c r="T122" s="56"/>
+      <c r="N122" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O122" s="51"/>
+      <c r="P122" s="51"/>
+      <c r="Q122" s="51"/>
+      <c r="R122" s="51"/>
+      <c r="S122" s="52"/>
+      <c r="T122" s="52"/>
     </row>
     <row r="123" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A123" s="50">
-        <v>10180011</v>
-      </c>
-      <c r="B123" s="51">
-        <v>101800</v>
-      </c>
-      <c r="C123" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="D123" s="53">
-        <v>101800001</v>
-      </c>
-      <c r="E123" s="54">
+      <c r="A123" s="53">
+        <v>10240011</v>
+      </c>
+      <c r="B123" s="54">
+        <v>102400</v>
+      </c>
+      <c r="C123" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="D123" s="56">
+        <v>102400026</v>
+      </c>
+      <c r="E123" s="57">
         <v>11</v>
       </c>
       <c r="F123" s="23" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G123" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H123" s="61">
-        <v>0</v>
-      </c>
-      <c r="I123" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J123" s="57">
-        <v>0</v>
-      </c>
-      <c r="K123" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L123" s="62">
+        <v>39</v>
+      </c>
+      <c r="H123" s="58">
+        <v>0</v>
+      </c>
+      <c r="I123" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J123" s="59">
+        <v>0</v>
+      </c>
+      <c r="K123" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L123" s="63">
         <v>0</v>
       </c>
       <c r="M123" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N123" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O123" s="60"/>
-      <c r="P123" s="60"/>
-      <c r="Q123" s="60"/>
-      <c r="R123" s="60"/>
-      <c r="S123" s="56"/>
-      <c r="T123" s="56"/>
+      <c r="N123" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O123" s="51"/>
+      <c r="P123" s="51"/>
+      <c r="Q123" s="51"/>
+      <c r="R123" s="51"/>
+      <c r="S123" s="52"/>
+      <c r="T123" s="52"/>
     </row>
     <row r="124" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A124" s="50">
-        <v>10180012</v>
-      </c>
-      <c r="B124" s="51">
-        <v>101800</v>
-      </c>
-      <c r="C124" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="D124" s="53">
-        <v>101800001</v>
-      </c>
-      <c r="E124" s="54">
+      <c r="A124" s="53">
+        <v>10240012</v>
+      </c>
+      <c r="B124" s="54">
+        <v>102400</v>
+      </c>
+      <c r="C124" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="D124" s="56">
+        <v>102400026</v>
+      </c>
+      <c r="E124" s="57">
         <v>12</v>
       </c>
       <c r="F124" s="23" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G124" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="H124" s="61">
-        <v>0</v>
-      </c>
-      <c r="I124" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J124" s="57">
-        <v>0</v>
-      </c>
-      <c r="K124" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L124" s="62">
+        <v>42</v>
+      </c>
+      <c r="H124" s="62">
+        <v>0</v>
+      </c>
+      <c r="I124" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J124" s="59">
+        <v>0</v>
+      </c>
+      <c r="K124" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L124" s="63">
         <v>0</v>
       </c>
       <c r="M124" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N124" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O124" s="60"/>
-      <c r="P124" s="60"/>
-      <c r="Q124" s="60"/>
-      <c r="R124" s="60"/>
-      <c r="S124" s="56"/>
-      <c r="T124" s="56"/>
+      <c r="N124" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O124" s="51"/>
+      <c r="P124" s="51"/>
+      <c r="Q124" s="51"/>
+      <c r="R124" s="51"/>
+      <c r="S124" s="52"/>
+      <c r="T124" s="52"/>
     </row>
     <row r="125" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A125" s="50">
-        <v>10250010</v>
-      </c>
-      <c r="B125" s="51">
-        <v>102500</v>
-      </c>
-      <c r="C125" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="D125" s="53">
-        <v>102500001</v>
-      </c>
-      <c r="E125" s="54">
+      <c r="A125" s="53">
+        <v>10180010</v>
+      </c>
+      <c r="B125" s="54">
+        <v>101800</v>
+      </c>
+      <c r="C125" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="D125" s="56">
+        <v>101800001</v>
+      </c>
+      <c r="E125" s="57">
         <v>10</v>
       </c>
       <c r="F125" s="23" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G125" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="H125" s="61">
-        <v>0</v>
-      </c>
-      <c r="I125" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J125" s="57">
-        <v>0</v>
-      </c>
-      <c r="K125" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L125" s="62">
+        <v>51</v>
+      </c>
+      <c r="H125" s="62">
+        <v>0</v>
+      </c>
+      <c r="I125" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J125" s="59">
+        <v>0</v>
+      </c>
+      <c r="K125" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L125" s="63">
         <v>0</v>
       </c>
       <c r="M125" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N125" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O125" s="60"/>
-      <c r="P125" s="60"/>
-      <c r="Q125" s="60"/>
-      <c r="R125" s="60"/>
-      <c r="S125" s="56"/>
-      <c r="T125" s="56"/>
+      <c r="N125" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O125" s="51"/>
+      <c r="P125" s="51"/>
+      <c r="Q125" s="51"/>
+      <c r="R125" s="51"/>
+      <c r="S125" s="52"/>
+      <c r="T125" s="52"/>
     </row>
     <row r="126" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A126" s="50">
-        <v>10250011</v>
-      </c>
-      <c r="B126" s="51">
-        <v>102500</v>
-      </c>
-      <c r="C126" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="D126" s="53">
-        <v>102500001</v>
-      </c>
-      <c r="E126" s="54">
+      <c r="A126" s="53">
+        <v>10180011</v>
+      </c>
+      <c r="B126" s="54">
+        <v>101800</v>
+      </c>
+      <c r="C126" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="D126" s="56">
+        <v>101800001</v>
+      </c>
+      <c r="E126" s="57">
         <v>11</v>
       </c>
       <c r="F126" s="23" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G126" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H126" s="61">
-        <v>0</v>
-      </c>
-      <c r="I126" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J126" s="57">
-        <v>0</v>
-      </c>
-      <c r="K126" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L126" s="62">
+        <v>53</v>
+      </c>
+      <c r="H126" s="62">
+        <v>0</v>
+      </c>
+      <c r="I126" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J126" s="59">
+        <v>0</v>
+      </c>
+      <c r="K126" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L126" s="63">
         <v>0</v>
       </c>
       <c r="M126" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N126" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O126" s="60"/>
-      <c r="P126" s="60"/>
-      <c r="Q126" s="60"/>
-      <c r="R126" s="60"/>
-      <c r="S126" s="56"/>
-      <c r="T126" s="56"/>
+      <c r="N126" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O126" s="51"/>
+      <c r="P126" s="51"/>
+      <c r="Q126" s="51"/>
+      <c r="R126" s="51"/>
+      <c r="S126" s="52"/>
+      <c r="T126" s="52"/>
     </row>
     <row r="127" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A127" s="50">
-        <v>10250012</v>
-      </c>
-      <c r="B127" s="51">
-        <v>102500</v>
-      </c>
-      <c r="C127" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="D127" s="53">
-        <v>102500001</v>
-      </c>
-      <c r="E127" s="54">
+      <c r="A127" s="53">
+        <v>10180012</v>
+      </c>
+      <c r="B127" s="54">
+        <v>101800</v>
+      </c>
+      <c r="C127" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="D127" s="56">
+        <v>101800001</v>
+      </c>
+      <c r="E127" s="57">
         <v>12</v>
       </c>
       <c r="F127" s="23" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G127" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="H127" s="61">
-        <v>0</v>
-      </c>
-      <c r="I127" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J127" s="57">
-        <v>0</v>
-      </c>
-      <c r="K127" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L127" s="62">
+        <v>55</v>
+      </c>
+      <c r="H127" s="62">
+        <v>0</v>
+      </c>
+      <c r="I127" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J127" s="59">
+        <v>0</v>
+      </c>
+      <c r="K127" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L127" s="63">
         <v>0</v>
       </c>
       <c r="M127" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N127" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O127" s="60"/>
-      <c r="P127" s="60"/>
-      <c r="Q127" s="60"/>
-      <c r="R127" s="60"/>
-      <c r="S127" s="56"/>
-      <c r="T127" s="56"/>
+      <c r="N127" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O127" s="51"/>
+      <c r="P127" s="51"/>
+      <c r="Q127" s="51"/>
+      <c r="R127" s="51"/>
+      <c r="S127" s="52"/>
+      <c r="T127" s="52"/>
     </row>
     <row r="128" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A128" s="50">
-        <v>10230010</v>
-      </c>
-      <c r="B128" s="51">
-        <v>102300</v>
-      </c>
-      <c r="C128" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="D128" s="53">
-        <v>102300001</v>
-      </c>
-      <c r="E128" s="54">
+      <c r="A128" s="53">
+        <v>10250010</v>
+      </c>
+      <c r="B128" s="54">
+        <v>102500</v>
+      </c>
+      <c r="C128" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="D128" s="56">
+        <v>102500001</v>
+      </c>
+      <c r="E128" s="57">
         <v>10</v>
       </c>
       <c r="F128" s="23" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G128" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H128" s="61">
-        <v>0</v>
-      </c>
-      <c r="I128" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J128" s="57">
-        <v>0</v>
-      </c>
-      <c r="K128" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L128" s="62">
+        <v>69</v>
+      </c>
+      <c r="H128" s="62">
+        <v>0</v>
+      </c>
+      <c r="I128" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J128" s="59">
+        <v>0</v>
+      </c>
+      <c r="K128" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L128" s="63">
         <v>0</v>
       </c>
       <c r="M128" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N128" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O128" s="60"/>
-      <c r="P128" s="60"/>
-      <c r="Q128" s="60"/>
-      <c r="R128" s="60"/>
-      <c r="S128" s="56"/>
-      <c r="T128" s="56"/>
+      <c r="N128" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O128" s="51"/>
+      <c r="P128" s="51"/>
+      <c r="Q128" s="51"/>
+      <c r="R128" s="51"/>
+      <c r="S128" s="52"/>
+      <c r="T128" s="52"/>
     </row>
     <row r="129" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A129" s="50">
-        <v>10230011</v>
-      </c>
-      <c r="B129" s="51">
-        <v>102300</v>
-      </c>
-      <c r="C129" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="D129" s="53">
-        <v>102300001</v>
-      </c>
-      <c r="E129" s="54">
+      <c r="A129" s="53">
+        <v>10250011</v>
+      </c>
+      <c r="B129" s="54">
+        <v>102500</v>
+      </c>
+      <c r="C129" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="D129" s="56">
+        <v>102500001</v>
+      </c>
+      <c r="E129" s="57">
         <v>11</v>
       </c>
       <c r="F129" s="23" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G129" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H129" s="61">
-        <v>0</v>
-      </c>
-      <c r="I129" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J129" s="57">
-        <v>0</v>
-      </c>
-      <c r="K129" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L129" s="62">
+        <v>71</v>
+      </c>
+      <c r="H129" s="62">
+        <v>0</v>
+      </c>
+      <c r="I129" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J129" s="59">
+        <v>0</v>
+      </c>
+      <c r="K129" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L129" s="63">
         <v>0</v>
       </c>
       <c r="M129" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N129" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O129" s="60"/>
-      <c r="P129" s="60"/>
-      <c r="Q129" s="60"/>
-      <c r="R129" s="60"/>
-      <c r="S129" s="56"/>
-      <c r="T129" s="56"/>
+      <c r="N129" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O129" s="51"/>
+      <c r="P129" s="51"/>
+      <c r="Q129" s="51"/>
+      <c r="R129" s="51"/>
+      <c r="S129" s="52"/>
+      <c r="T129" s="52"/>
     </row>
     <row r="130" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A130" s="50">
-        <v>10230012</v>
-      </c>
-      <c r="B130" s="51">
-        <v>102300</v>
-      </c>
-      <c r="C130" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="D130" s="53">
-        <v>102300001</v>
-      </c>
-      <c r="E130" s="54">
+      <c r="A130" s="53">
+        <v>10250012</v>
+      </c>
+      <c r="B130" s="54">
+        <v>102500</v>
+      </c>
+      <c r="C130" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="D130" s="56">
+        <v>102500001</v>
+      </c>
+      <c r="E130" s="57">
         <v>12</v>
       </c>
       <c r="F130" s="23" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G130" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="H130" s="61">
-        <v>0</v>
-      </c>
-      <c r="I130" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J130" s="57">
-        <v>0</v>
-      </c>
-      <c r="K130" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L130" s="62">
+        <v>73</v>
+      </c>
+      <c r="H130" s="62">
+        <v>0</v>
+      </c>
+      <c r="I130" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J130" s="59">
+        <v>0</v>
+      </c>
+      <c r="K130" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L130" s="63">
         <v>0</v>
       </c>
       <c r="M130" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N130" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O130" s="60"/>
-      <c r="P130" s="60"/>
-      <c r="Q130" s="60"/>
-      <c r="R130" s="60"/>
-      <c r="S130" s="56"/>
-      <c r="T130" s="56"/>
+      <c r="N130" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O130" s="51"/>
+      <c r="P130" s="51"/>
+      <c r="Q130" s="51"/>
+      <c r="R130" s="51"/>
+      <c r="S130" s="52"/>
+      <c r="T130" s="52"/>
     </row>
     <row r="131" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A131" s="50">
-        <v>10340010</v>
-      </c>
-      <c r="B131" s="51">
-        <v>103400</v>
-      </c>
-      <c r="C131" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="D131" s="53">
-        <v>103000001</v>
-      </c>
-      <c r="E131" s="54">
+      <c r="A131" s="53">
+        <v>10230010</v>
+      </c>
+      <c r="B131" s="54">
+        <v>102300</v>
+      </c>
+      <c r="C131" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="D131" s="56">
+        <v>102300001</v>
+      </c>
+      <c r="E131" s="57">
         <v>10</v>
       </c>
       <c r="F131" s="23" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G131" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H131" s="61">
-        <v>0</v>
-      </c>
-      <c r="I131" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J131" s="57">
-        <v>0</v>
-      </c>
-      <c r="K131" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L131" s="62">
+        <v>51</v>
+      </c>
+      <c r="H131" s="62">
+        <v>0</v>
+      </c>
+      <c r="I131" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J131" s="59">
+        <v>0</v>
+      </c>
+      <c r="K131" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L131" s="63">
         <v>0</v>
       </c>
       <c r="M131" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N131" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O131" s="60"/>
-      <c r="P131" s="60"/>
-      <c r="Q131" s="60"/>
-      <c r="R131" s="60"/>
-      <c r="S131" s="56"/>
-      <c r="T131" s="56"/>
+      <c r="N131" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O131" s="51"/>
+      <c r="P131" s="51"/>
+      <c r="Q131" s="51"/>
+      <c r="R131" s="51"/>
+      <c r="S131" s="52"/>
+      <c r="T131" s="52"/>
     </row>
     <row r="132" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A132" s="50">
-        <v>10340011</v>
-      </c>
-      <c r="B132" s="51">
-        <v>103400</v>
-      </c>
-      <c r="C132" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="D132" s="53">
-        <v>103000001</v>
-      </c>
-      <c r="E132" s="54">
+      <c r="A132" s="53">
+        <v>10230011</v>
+      </c>
+      <c r="B132" s="54">
+        <v>102300</v>
+      </c>
+      <c r="C132" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="D132" s="56">
+        <v>102300001</v>
+      </c>
+      <c r="E132" s="57">
         <v>11</v>
       </c>
       <c r="F132" s="23" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G132" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="H132" s="61">
-        <v>0</v>
-      </c>
-      <c r="I132" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J132" s="57">
-        <v>0</v>
-      </c>
-      <c r="K132" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L132" s="62">
+        <v>53</v>
+      </c>
+      <c r="H132" s="62">
+        <v>0</v>
+      </c>
+      <c r="I132" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J132" s="59">
+        <v>0</v>
+      </c>
+      <c r="K132" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L132" s="63">
         <v>0</v>
       </c>
       <c r="M132" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N132" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O132" s="60"/>
-      <c r="P132" s="60"/>
-      <c r="Q132" s="60"/>
-      <c r="R132" s="60"/>
-      <c r="S132" s="56"/>
-      <c r="T132" s="56"/>
+      <c r="N132" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O132" s="51"/>
+      <c r="P132" s="51"/>
+      <c r="Q132" s="51"/>
+      <c r="R132" s="51"/>
+      <c r="S132" s="52"/>
+      <c r="T132" s="52"/>
     </row>
     <row r="133" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A133" s="50">
-        <v>10340012</v>
-      </c>
-      <c r="B133" s="51">
-        <v>103400</v>
-      </c>
-      <c r="C133" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="D133" s="53">
-        <v>103000001</v>
-      </c>
-      <c r="E133" s="54">
+      <c r="A133" s="53">
+        <v>10230012</v>
+      </c>
+      <c r="B133" s="54">
+        <v>102300</v>
+      </c>
+      <c r="C133" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="D133" s="56">
+        <v>102300001</v>
+      </c>
+      <c r="E133" s="57">
         <v>12</v>
       </c>
       <c r="F133" s="23" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="G133" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="H133" s="61">
-        <v>0</v>
-      </c>
-      <c r="I133" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J133" s="57">
-        <v>0</v>
-      </c>
-      <c r="K133" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L133" s="62">
+        <v>55</v>
+      </c>
+      <c r="H133" s="62">
+        <v>0</v>
+      </c>
+      <c r="I133" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J133" s="59">
+        <v>0</v>
+      </c>
+      <c r="K133" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L133" s="63">
         <v>0</v>
       </c>
       <c r="M133" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N133" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O133" s="60"/>
-      <c r="P133" s="60"/>
-      <c r="Q133" s="60"/>
-      <c r="R133" s="60"/>
-      <c r="S133" s="56"/>
-      <c r="T133" s="56"/>
+      <c r="N133" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O133" s="51"/>
+      <c r="P133" s="51"/>
+      <c r="Q133" s="51"/>
+      <c r="R133" s="51"/>
+      <c r="S133" s="52"/>
+      <c r="T133" s="52"/>
     </row>
     <row r="134" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A134" s="50">
-        <v>10350010</v>
-      </c>
-      <c r="B134" s="51">
-        <v>103500</v>
-      </c>
-      <c r="C134" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="D134" s="53">
-        <v>102900001</v>
-      </c>
-      <c r="E134" s="54">
+      <c r="A134" s="53">
+        <v>10340010</v>
+      </c>
+      <c r="B134" s="54">
+        <v>103400</v>
+      </c>
+      <c r="C134" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="D134" s="56">
+        <v>103000001</v>
+      </c>
+      <c r="E134" s="57">
         <v>10</v>
       </c>
       <c r="F134" s="23" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G134" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="H134" s="61">
-        <v>0</v>
-      </c>
-      <c r="I134" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J134" s="57">
-        <v>0</v>
-      </c>
-      <c r="K134" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L134" s="62">
+        <v>71</v>
+      </c>
+      <c r="H134" s="62">
+        <v>0</v>
+      </c>
+      <c r="I134" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J134" s="59">
+        <v>0</v>
+      </c>
+      <c r="K134" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L134" s="63">
         <v>0</v>
       </c>
       <c r="M134" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N134" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O134" s="60"/>
-      <c r="P134" s="60"/>
-      <c r="Q134" s="60"/>
-      <c r="R134" s="60"/>
-      <c r="S134" s="56"/>
-      <c r="T134" s="56"/>
+      <c r="N134" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O134" s="51"/>
+      <c r="P134" s="51"/>
+      <c r="Q134" s="51"/>
+      <c r="R134" s="51"/>
+      <c r="S134" s="52"/>
+      <c r="T134" s="52"/>
     </row>
     <row r="135" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A135" s="50">
-        <v>10350011</v>
-      </c>
-      <c r="B135" s="51">
-        <v>103500</v>
-      </c>
-      <c r="C135" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="D135" s="53">
-        <v>102900001</v>
-      </c>
-      <c r="E135" s="54">
+      <c r="A135" s="53">
+        <v>10340011</v>
+      </c>
+      <c r="B135" s="54">
+        <v>103400</v>
+      </c>
+      <c r="C135" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="D135" s="56">
+        <v>103000001</v>
+      </c>
+      <c r="E135" s="57">
         <v>11</v>
       </c>
       <c r="F135" s="23" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G135" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H135" s="61">
-        <v>0</v>
-      </c>
-      <c r="I135" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J135" s="57">
-        <v>0</v>
-      </c>
-      <c r="K135" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L135" s="62">
+        <v>73</v>
+      </c>
+      <c r="H135" s="62">
+        <v>0</v>
+      </c>
+      <c r="I135" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J135" s="59">
+        <v>0</v>
+      </c>
+      <c r="K135" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L135" s="63">
         <v>0</v>
       </c>
       <c r="M135" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N135" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O135" s="60"/>
-      <c r="P135" s="60"/>
-      <c r="Q135" s="60"/>
-      <c r="R135" s="60"/>
-      <c r="S135" s="56"/>
-      <c r="T135" s="56"/>
+      <c r="N135" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O135" s="51"/>
+      <c r="P135" s="51"/>
+      <c r="Q135" s="51"/>
+      <c r="R135" s="51"/>
+      <c r="S135" s="52"/>
+      <c r="T135" s="52"/>
     </row>
     <row r="136" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A136" s="50">
-        <v>10350012</v>
-      </c>
-      <c r="B136" s="51">
-        <v>103500</v>
-      </c>
-      <c r="C136" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="D136" s="53">
-        <v>102900001</v>
-      </c>
-      <c r="E136" s="54">
+      <c r="A136" s="53">
+        <v>10340012</v>
+      </c>
+      <c r="B136" s="54">
+        <v>103400</v>
+      </c>
+      <c r="C136" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="D136" s="56">
+        <v>103000001</v>
+      </c>
+      <c r="E136" s="57">
         <v>12</v>
       </c>
       <c r="F136" s="23" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G136" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="H136" s="61">
-        <v>0</v>
-      </c>
-      <c r="I136" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J136" s="57">
-        <v>0</v>
-      </c>
-      <c r="K136" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L136" s="62">
+        <v>78</v>
+      </c>
+      <c r="H136" s="62">
+        <v>0</v>
+      </c>
+      <c r="I136" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J136" s="59">
+        <v>0</v>
+      </c>
+      <c r="K136" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L136" s="63">
         <v>0</v>
       </c>
       <c r="M136" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N136" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O136" s="60"/>
-      <c r="P136" s="60"/>
-      <c r="Q136" s="60"/>
-      <c r="R136" s="60"/>
-      <c r="S136" s="56"/>
-      <c r="T136" s="56"/>
+      <c r="N136" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O136" s="51"/>
+      <c r="P136" s="51"/>
+      <c r="Q136" s="51"/>
+      <c r="R136" s="51"/>
+      <c r="S136" s="52"/>
+      <c r="T136" s="52"/>
     </row>
     <row r="137" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A137" s="50">
-        <v>10350110</v>
-      </c>
-      <c r="B137" s="51">
-        <v>103501</v>
-      </c>
-      <c r="C137" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="D137" s="53">
-        <v>103501001</v>
-      </c>
-      <c r="E137" s="54">
+      <c r="A137" s="53">
+        <v>10350010</v>
+      </c>
+      <c r="B137" s="54">
+        <v>103500</v>
+      </c>
+      <c r="C137" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="D137" s="56">
+        <v>102900001</v>
+      </c>
+      <c r="E137" s="57">
         <v>10</v>
       </c>
       <c r="F137" s="23" t="s">
@@ -8698,48 +8698,48 @@
       <c r="G137" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H137" s="61">
-        <v>0</v>
-      </c>
-      <c r="I137" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J137" s="57">
-        <v>0</v>
-      </c>
-      <c r="K137" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L137" s="62">
+      <c r="H137" s="62">
+        <v>0</v>
+      </c>
+      <c r="I137" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J137" s="59">
+        <v>0</v>
+      </c>
+      <c r="K137" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L137" s="63">
         <v>0</v>
       </c>
       <c r="M137" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N137" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O137" s="60"/>
-      <c r="P137" s="60"/>
-      <c r="Q137" s="60"/>
-      <c r="R137" s="60"/>
-      <c r="S137" s="56"/>
-      <c r="T137" s="56"/>
+      <c r="N137" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O137" s="51"/>
+      <c r="P137" s="51"/>
+      <c r="Q137" s="51"/>
+      <c r="R137" s="51"/>
+      <c r="S137" s="52"/>
+      <c r="T137" s="52"/>
     </row>
     <row r="138" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A138" s="50">
-        <v>10350111</v>
-      </c>
-      <c r="B138" s="51">
-        <v>103501</v>
-      </c>
-      <c r="C138" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="D138" s="53">
-        <v>103501001</v>
-      </c>
-      <c r="E138" s="54">
+      <c r="A138" s="53">
+        <v>10350011</v>
+      </c>
+      <c r="B138" s="54">
+        <v>103500</v>
+      </c>
+      <c r="C138" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="D138" s="56">
+        <v>102900001</v>
+      </c>
+      <c r="E138" s="57">
         <v>11</v>
       </c>
       <c r="F138" s="23" t="s">
@@ -8748,48 +8748,48 @@
       <c r="G138" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="H138" s="61">
-        <v>0</v>
-      </c>
-      <c r="I138" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J138" s="57">
-        <v>0</v>
-      </c>
-      <c r="K138" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L138" s="62">
+      <c r="H138" s="62">
+        <v>0</v>
+      </c>
+      <c r="I138" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J138" s="59">
+        <v>0</v>
+      </c>
+      <c r="K138" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L138" s="63">
         <v>0</v>
       </c>
       <c r="M138" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N138" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O138" s="60"/>
-      <c r="P138" s="60"/>
-      <c r="Q138" s="60"/>
-      <c r="R138" s="60"/>
-      <c r="S138" s="56"/>
-      <c r="T138" s="56"/>
+      <c r="N138" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O138" s="51"/>
+      <c r="P138" s="51"/>
+      <c r="Q138" s="51"/>
+      <c r="R138" s="51"/>
+      <c r="S138" s="52"/>
+      <c r="T138" s="52"/>
     </row>
     <row r="139" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A139" s="50">
-        <v>10350112</v>
-      </c>
-      <c r="B139" s="51">
-        <v>103501</v>
-      </c>
-      <c r="C139" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="D139" s="53">
-        <v>103501001</v>
-      </c>
-      <c r="E139" s="54">
+      <c r="A139" s="53">
+        <v>10350012</v>
+      </c>
+      <c r="B139" s="54">
+        <v>103500</v>
+      </c>
+      <c r="C139" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="D139" s="56">
+        <v>102900001</v>
+      </c>
+      <c r="E139" s="57">
         <v>12</v>
       </c>
       <c r="F139" s="23" t="s">
@@ -8798,1698 +8798,1698 @@
       <c r="G139" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="H139" s="61">
-        <v>0</v>
-      </c>
-      <c r="I139" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J139" s="57">
-        <v>0</v>
-      </c>
-      <c r="K139" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L139" s="62">
+      <c r="H139" s="62">
+        <v>0</v>
+      </c>
+      <c r="I139" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J139" s="59">
+        <v>0</v>
+      </c>
+      <c r="K139" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L139" s="63">
         <v>0</v>
       </c>
       <c r="M139" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N139" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O139" s="60"/>
-      <c r="P139" s="60"/>
-      <c r="Q139" s="60"/>
-      <c r="R139" s="60"/>
-      <c r="S139" s="56"/>
-      <c r="T139" s="56"/>
+      <c r="N139" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O139" s="51"/>
+      <c r="P139" s="51"/>
+      <c r="Q139" s="51"/>
+      <c r="R139" s="51"/>
+      <c r="S139" s="52"/>
+      <c r="T139" s="52"/>
     </row>
     <row r="140" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A140" s="50">
-        <v>10360010</v>
-      </c>
-      <c r="B140" s="51">
-        <v>103600</v>
-      </c>
-      <c r="C140" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="D140" s="53">
-        <v>103600001</v>
-      </c>
-      <c r="E140" s="54">
+      <c r="A140" s="53">
+        <v>10350110</v>
+      </c>
+      <c r="B140" s="54">
+        <v>103501</v>
+      </c>
+      <c r="C140" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="D140" s="56">
+        <v>103501001</v>
+      </c>
+      <c r="E140" s="57">
         <v>10</v>
       </c>
       <c r="F140" s="23" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="G140" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H140" s="55">
-        <v>0</v>
-      </c>
-      <c r="I140" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J140" s="57">
-        <v>0</v>
-      </c>
-      <c r="K140" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L140" s="62">
+        <v>39</v>
+      </c>
+      <c r="H140" s="62">
+        <v>0</v>
+      </c>
+      <c r="I140" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J140" s="59">
+        <v>0</v>
+      </c>
+      <c r="K140" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L140" s="63">
         <v>0</v>
       </c>
       <c r="M140" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N140" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O140" s="60"/>
-      <c r="P140" s="60"/>
-      <c r="Q140" s="60"/>
-      <c r="R140" s="60"/>
-      <c r="S140" s="56"/>
-      <c r="T140" s="56"/>
+      <c r="N140" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O140" s="51"/>
+      <c r="P140" s="51"/>
+      <c r="Q140" s="51"/>
+      <c r="R140" s="51"/>
+      <c r="S140" s="52"/>
+      <c r="T140" s="52"/>
     </row>
     <row r="141" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A141" s="50">
-        <v>10360011</v>
-      </c>
-      <c r="B141" s="51">
-        <v>103600</v>
-      </c>
-      <c r="C141" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="D141" s="53">
-        <v>103600001</v>
-      </c>
-      <c r="E141" s="54">
+      <c r="A141" s="53">
+        <v>10350111</v>
+      </c>
+      <c r="B141" s="54">
+        <v>103501</v>
+      </c>
+      <c r="C141" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="D141" s="56">
+        <v>103501001</v>
+      </c>
+      <c r="E141" s="57">
         <v>11</v>
       </c>
       <c r="F141" s="23" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G141" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="H141" s="55">
-        <v>0</v>
-      </c>
-      <c r="I141" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J141" s="57">
-        <v>0</v>
-      </c>
-      <c r="K141" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L141" s="62">
+        <v>42</v>
+      </c>
+      <c r="H141" s="62">
+        <v>0</v>
+      </c>
+      <c r="I141" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J141" s="59">
+        <v>0</v>
+      </c>
+      <c r="K141" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L141" s="63">
         <v>0</v>
       </c>
       <c r="M141" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N141" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O141" s="60"/>
-      <c r="P141" s="60"/>
-      <c r="Q141" s="60"/>
-      <c r="R141" s="60"/>
-      <c r="S141" s="56"/>
-      <c r="T141" s="56"/>
+      <c r="N141" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O141" s="51"/>
+      <c r="P141" s="51"/>
+      <c r="Q141" s="51"/>
+      <c r="R141" s="51"/>
+      <c r="S141" s="52"/>
+      <c r="T141" s="52"/>
     </row>
     <row r="142" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A142" s="50">
-        <v>10360012</v>
-      </c>
-      <c r="B142" s="51">
-        <v>103600</v>
-      </c>
-      <c r="C142" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="D142" s="53">
-        <v>103600001</v>
-      </c>
-      <c r="E142" s="54">
+      <c r="A142" s="53">
+        <v>10350112</v>
+      </c>
+      <c r="B142" s="54">
+        <v>103501</v>
+      </c>
+      <c r="C142" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="D142" s="56">
+        <v>103501001</v>
+      </c>
+      <c r="E142" s="57">
         <v>12</v>
       </c>
       <c r="F142" s="23" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="G142" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="H142" s="61">
-        <v>0</v>
-      </c>
-      <c r="I142" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J142" s="57">
-        <v>0</v>
-      </c>
-      <c r="K142" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L142" s="62">
+        <v>46</v>
+      </c>
+      <c r="H142" s="62">
+        <v>0</v>
+      </c>
+      <c r="I142" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J142" s="59">
+        <v>0</v>
+      </c>
+      <c r="K142" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L142" s="63">
         <v>0</v>
       </c>
       <c r="M142" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N142" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O142" s="60"/>
-      <c r="P142" s="60"/>
-      <c r="Q142" s="60"/>
-      <c r="R142" s="60"/>
-      <c r="S142" s="56"/>
-      <c r="T142" s="56"/>
+      <c r="N142" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O142" s="51"/>
+      <c r="P142" s="51"/>
+      <c r="Q142" s="51"/>
+      <c r="R142" s="51"/>
+      <c r="S142" s="52"/>
+      <c r="T142" s="52"/>
     </row>
     <row r="143" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A143" s="50">
-        <v>10280010</v>
-      </c>
-      <c r="B143" s="51">
-        <v>102800</v>
-      </c>
-      <c r="C143" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="D143" s="53">
-        <v>102800001</v>
-      </c>
-      <c r="E143" s="54">
+      <c r="A143" s="53">
+        <v>10360010</v>
+      </c>
+      <c r="B143" s="54">
+        <v>103600</v>
+      </c>
+      <c r="C143" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="D143" s="56">
+        <v>103600001</v>
+      </c>
+      <c r="E143" s="57">
         <v>10</v>
       </c>
       <c r="F143" s="23" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G143" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H143" s="61">
-        <v>0</v>
-      </c>
-      <c r="I143" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J143" s="57">
-        <v>0</v>
-      </c>
-      <c r="K143" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L143" s="62">
+        <v>71</v>
+      </c>
+      <c r="H143" s="58">
+        <v>0</v>
+      </c>
+      <c r="I143" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J143" s="59">
+        <v>0</v>
+      </c>
+      <c r="K143" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L143" s="63">
         <v>0</v>
       </c>
       <c r="M143" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N143" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O143" s="60"/>
-      <c r="P143" s="60"/>
-      <c r="Q143" s="60"/>
-      <c r="R143" s="60"/>
-      <c r="S143" s="56"/>
-      <c r="T143" s="56"/>
+      <c r="N143" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O143" s="51"/>
+      <c r="P143" s="51"/>
+      <c r="Q143" s="51"/>
+      <c r="R143" s="51"/>
+      <c r="S143" s="52"/>
+      <c r="T143" s="52"/>
     </row>
     <row r="144" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A144" s="50">
-        <v>10280011</v>
-      </c>
-      <c r="B144" s="51">
-        <v>102800</v>
-      </c>
-      <c r="C144" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="D144" s="53">
-        <v>102800001</v>
-      </c>
-      <c r="E144" s="54">
+      <c r="A144" s="53">
+        <v>10360011</v>
+      </c>
+      <c r="B144" s="54">
+        <v>103600</v>
+      </c>
+      <c r="C144" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="D144" s="56">
+        <v>103600001</v>
+      </c>
+      <c r="E144" s="57">
         <v>11</v>
       </c>
       <c r="F144" s="23" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G144" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H144" s="61">
-        <v>0</v>
-      </c>
-      <c r="I144" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J144" s="57">
-        <v>0</v>
-      </c>
-      <c r="K144" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L144" s="62">
+        <v>73</v>
+      </c>
+      <c r="H144" s="58">
+        <v>0</v>
+      </c>
+      <c r="I144" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J144" s="59">
+        <v>0</v>
+      </c>
+      <c r="K144" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L144" s="63">
         <v>0</v>
       </c>
       <c r="M144" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N144" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O144" s="60"/>
-      <c r="P144" s="60"/>
-      <c r="Q144" s="60"/>
-      <c r="R144" s="60"/>
-      <c r="S144" s="56"/>
-      <c r="T144" s="56"/>
+      <c r="N144" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O144" s="51"/>
+      <c r="P144" s="51"/>
+      <c r="Q144" s="51"/>
+      <c r="R144" s="51"/>
+      <c r="S144" s="52"/>
+      <c r="T144" s="52"/>
     </row>
     <row r="145" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A145" s="50">
-        <v>10280012</v>
-      </c>
-      <c r="B145" s="51">
-        <v>102800</v>
-      </c>
-      <c r="C145" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="D145" s="53">
-        <v>102800001</v>
-      </c>
-      <c r="E145" s="54">
+      <c r="A145" s="53">
+        <v>10360012</v>
+      </c>
+      <c r="B145" s="54">
+        <v>103600</v>
+      </c>
+      <c r="C145" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="D145" s="56">
+        <v>103600001</v>
+      </c>
+      <c r="E145" s="57">
         <v>12</v>
       </c>
       <c r="F145" s="23" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="G145" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="H145" s="61">
-        <v>0</v>
-      </c>
-      <c r="I145" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J145" s="57">
-        <v>0</v>
-      </c>
-      <c r="K145" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L145" s="62">
+        <v>78</v>
+      </c>
+      <c r="H145" s="62">
+        <v>0</v>
+      </c>
+      <c r="I145" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J145" s="59">
+        <v>0</v>
+      </c>
+      <c r="K145" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L145" s="63">
         <v>0</v>
       </c>
       <c r="M145" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N145" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O145" s="60"/>
-      <c r="P145" s="60"/>
-      <c r="Q145" s="60"/>
-      <c r="R145" s="60"/>
-      <c r="S145" s="56"/>
-      <c r="T145" s="56"/>
+      <c r="N145" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O145" s="51"/>
+      <c r="P145" s="51"/>
+      <c r="Q145" s="51"/>
+      <c r="R145" s="51"/>
+      <c r="S145" s="52"/>
+      <c r="T145" s="52"/>
     </row>
     <row r="146" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A146" s="50">
-        <v>10200010</v>
-      </c>
-      <c r="B146" s="51">
-        <v>102000</v>
-      </c>
-      <c r="C146" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="D146" s="53">
-        <v>102000001</v>
-      </c>
-      <c r="E146" s="54">
+      <c r="A146" s="53">
+        <v>10280010</v>
+      </c>
+      <c r="B146" s="54">
+        <v>102800</v>
+      </c>
+      <c r="C146" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="D146" s="56">
+        <v>102800001</v>
+      </c>
+      <c r="E146" s="57">
         <v>10</v>
       </c>
       <c r="F146" s="23" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G146" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="H146" s="61">
-        <v>0</v>
-      </c>
-      <c r="I146" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J146" s="57">
-        <v>0</v>
-      </c>
-      <c r="K146" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L146" s="62">
+        <v>51</v>
+      </c>
+      <c r="H146" s="62">
+        <v>0</v>
+      </c>
+      <c r="I146" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J146" s="59">
+        <v>0</v>
+      </c>
+      <c r="K146" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L146" s="63">
         <v>0</v>
       </c>
       <c r="M146" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N146" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O146" s="60"/>
-      <c r="P146" s="60"/>
-      <c r="Q146" s="60"/>
-      <c r="R146" s="60"/>
-      <c r="S146" s="56"/>
-      <c r="T146" s="56"/>
+      <c r="N146" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O146" s="51"/>
+      <c r="P146" s="51"/>
+      <c r="Q146" s="51"/>
+      <c r="R146" s="51"/>
+      <c r="S146" s="52"/>
+      <c r="T146" s="52"/>
     </row>
     <row r="147" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A147" s="50">
-        <v>10200011</v>
-      </c>
-      <c r="B147" s="51">
-        <v>102000</v>
-      </c>
-      <c r="C147" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="D147" s="53">
-        <v>102000001</v>
-      </c>
-      <c r="E147" s="54">
+      <c r="A147" s="53">
+        <v>10280011</v>
+      </c>
+      <c r="B147" s="54">
+        <v>102800</v>
+      </c>
+      <c r="C147" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="D147" s="56">
+        <v>102800001</v>
+      </c>
+      <c r="E147" s="57">
         <v>11</v>
       </c>
       <c r="F147" s="23" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="G147" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="H147" s="61">
-        <v>0</v>
-      </c>
-      <c r="I147" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J147" s="57">
-        <v>0</v>
-      </c>
-      <c r="K147" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L147" s="62">
+        <v>53</v>
+      </c>
+      <c r="H147" s="62">
+        <v>0</v>
+      </c>
+      <c r="I147" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J147" s="59">
+        <v>0</v>
+      </c>
+      <c r="K147" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L147" s="63">
         <v>0</v>
       </c>
       <c r="M147" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N147" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O147" s="60"/>
-      <c r="P147" s="60"/>
-      <c r="Q147" s="60"/>
-      <c r="R147" s="60"/>
-      <c r="S147" s="56"/>
-      <c r="T147" s="56"/>
+      <c r="N147" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O147" s="51"/>
+      <c r="P147" s="51"/>
+      <c r="Q147" s="51"/>
+      <c r="R147" s="51"/>
+      <c r="S147" s="52"/>
+      <c r="T147" s="52"/>
     </row>
     <row r="148" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A148" s="50">
-        <v>10200012</v>
-      </c>
-      <c r="B148" s="51">
-        <v>102000</v>
-      </c>
-      <c r="C148" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="D148" s="53">
-        <v>102000001</v>
-      </c>
-      <c r="E148" s="54">
+      <c r="A148" s="53">
+        <v>10280012</v>
+      </c>
+      <c r="B148" s="54">
+        <v>102800</v>
+      </c>
+      <c r="C148" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="D148" s="56">
+        <v>102800001</v>
+      </c>
+      <c r="E148" s="57">
         <v>12</v>
       </c>
       <c r="F148" s="23" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="G148" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H148" s="61">
-        <v>0</v>
-      </c>
-      <c r="I148" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J148" s="57">
-        <v>0</v>
-      </c>
-      <c r="K148" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L148" s="62">
+        <v>55</v>
+      </c>
+      <c r="H148" s="62">
+        <v>0</v>
+      </c>
+      <c r="I148" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J148" s="59">
+        <v>0</v>
+      </c>
+      <c r="K148" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L148" s="63">
         <v>0</v>
       </c>
       <c r="M148" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N148" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O148" s="60"/>
-      <c r="P148" s="60"/>
-      <c r="Q148" s="60"/>
-      <c r="R148" s="60"/>
-      <c r="S148" s="56"/>
-      <c r="T148" s="56"/>
+      <c r="N148" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O148" s="51"/>
+      <c r="P148" s="51"/>
+      <c r="Q148" s="51"/>
+      <c r="R148" s="51"/>
+      <c r="S148" s="52"/>
+      <c r="T148" s="52"/>
     </row>
     <row r="149" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A149" s="50">
-        <v>10340110</v>
-      </c>
-      <c r="B149" s="51">
-        <v>103401</v>
-      </c>
-      <c r="C149" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="D149" s="53">
-        <v>103400001</v>
-      </c>
-      <c r="E149" s="54">
+      <c r="A149" s="53">
+        <v>10200010</v>
+      </c>
+      <c r="B149" s="54">
+        <v>102000</v>
+      </c>
+      <c r="C149" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="D149" s="56">
+        <v>102000001</v>
+      </c>
+      <c r="E149" s="57">
         <v>10</v>
       </c>
       <c r="F149" s="23" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G149" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H149" s="61">
-        <v>0</v>
-      </c>
-      <c r="I149" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J149" s="57">
-        <v>0</v>
-      </c>
-      <c r="K149" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L149" s="62">
+        <v>85</v>
+      </c>
+      <c r="H149" s="62">
+        <v>0</v>
+      </c>
+      <c r="I149" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J149" s="59">
+        <v>0</v>
+      </c>
+      <c r="K149" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L149" s="63">
         <v>0</v>
       </c>
       <c r="M149" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N149" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O149" s="60"/>
-      <c r="P149" s="60"/>
-      <c r="Q149" s="60"/>
-      <c r="R149" s="60"/>
-      <c r="S149" s="56"/>
-      <c r="T149" s="56"/>
+      <c r="N149" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O149" s="51"/>
+      <c r="P149" s="51"/>
+      <c r="Q149" s="51"/>
+      <c r="R149" s="51"/>
+      <c r="S149" s="52"/>
+      <c r="T149" s="52"/>
     </row>
     <row r="150" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A150" s="50">
-        <v>10340111</v>
-      </c>
-      <c r="B150" s="51">
-        <v>103401</v>
-      </c>
-      <c r="C150" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="D150" s="53">
-        <v>103400001</v>
-      </c>
-      <c r="E150" s="54">
+      <c r="A150" s="53">
+        <v>10200011</v>
+      </c>
+      <c r="B150" s="54">
+        <v>102000</v>
+      </c>
+      <c r="C150" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="D150" s="56">
+        <v>102000001</v>
+      </c>
+      <c r="E150" s="57">
         <v>11</v>
       </c>
       <c r="F150" s="23" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G150" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="H150" s="61">
-        <v>0</v>
-      </c>
-      <c r="I150" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J150" s="57">
-        <v>0</v>
-      </c>
-      <c r="K150" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L150" s="62">
+        <v>87</v>
+      </c>
+      <c r="H150" s="62">
+        <v>0</v>
+      </c>
+      <c r="I150" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J150" s="59">
+        <v>0</v>
+      </c>
+      <c r="K150" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L150" s="63">
         <v>0</v>
       </c>
       <c r="M150" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N150" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O150" s="60"/>
-      <c r="P150" s="60"/>
-      <c r="Q150" s="60"/>
-      <c r="R150" s="60"/>
-      <c r="S150" s="56"/>
-      <c r="T150" s="56"/>
+      <c r="N150" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O150" s="51"/>
+      <c r="P150" s="51"/>
+      <c r="Q150" s="51"/>
+      <c r="R150" s="51"/>
+      <c r="S150" s="52"/>
+      <c r="T150" s="52"/>
     </row>
     <row r="151" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A151" s="50">
-        <v>10340112</v>
-      </c>
-      <c r="B151" s="51">
-        <v>103401</v>
-      </c>
-      <c r="C151" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="D151" s="53">
-        <v>103400001</v>
-      </c>
-      <c r="E151" s="54">
+      <c r="A151" s="53">
+        <v>10200012</v>
+      </c>
+      <c r="B151" s="54">
+        <v>102000</v>
+      </c>
+      <c r="C151" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="D151" s="56">
+        <v>102000001</v>
+      </c>
+      <c r="E151" s="57">
         <v>12</v>
       </c>
       <c r="F151" s="23" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G151" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="H151" s="61">
-        <v>0</v>
-      </c>
-      <c r="I151" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J151" s="57">
-        <v>0</v>
-      </c>
-      <c r="K151" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L151" s="62">
+        <v>89</v>
+      </c>
+      <c r="H151" s="62">
+        <v>0</v>
+      </c>
+      <c r="I151" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J151" s="59">
+        <v>0</v>
+      </c>
+      <c r="K151" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L151" s="63">
         <v>0</v>
       </c>
       <c r="M151" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N151" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O151" s="60"/>
-      <c r="P151" s="60"/>
-      <c r="Q151" s="60"/>
-      <c r="R151" s="60"/>
-      <c r="S151" s="56"/>
-      <c r="T151" s="56"/>
+      <c r="N151" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O151" s="51"/>
+      <c r="P151" s="51"/>
+      <c r="Q151" s="51"/>
+      <c r="R151" s="51"/>
+      <c r="S151" s="52"/>
+      <c r="T151" s="52"/>
     </row>
     <row r="152" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A152" s="50">
-        <v>10380010</v>
-      </c>
-      <c r="B152" s="51">
-        <v>103800</v>
-      </c>
-      <c r="C152" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="D152" s="53">
-        <v>103800001</v>
-      </c>
-      <c r="E152" s="54">
-        <v>11</v>
+      <c r="A152" s="53">
+        <v>10340110</v>
+      </c>
+      <c r="B152" s="54">
+        <v>103401</v>
+      </c>
+      <c r="C152" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="D152" s="56">
+        <v>103400001</v>
+      </c>
+      <c r="E152" s="57">
+        <v>10</v>
       </c>
       <c r="F152" s="23" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G152" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="H152" s="61">
-        <v>0</v>
-      </c>
-      <c r="I152" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J152" s="57">
-        <v>0</v>
-      </c>
-      <c r="K152" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L152" s="62">
+        <v>71</v>
+      </c>
+      <c r="H152" s="62">
+        <v>0</v>
+      </c>
+      <c r="I152" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J152" s="59">
+        <v>0</v>
+      </c>
+      <c r="K152" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L152" s="63">
         <v>0</v>
       </c>
       <c r="M152" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N152" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O152" s="60"/>
-      <c r="P152" s="60"/>
-      <c r="Q152" s="60"/>
-      <c r="R152" s="60"/>
-      <c r="S152" s="56"/>
-      <c r="T152" s="56"/>
+      <c r="N152" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O152" s="51"/>
+      <c r="P152" s="51"/>
+      <c r="Q152" s="51"/>
+      <c r="R152" s="51"/>
+      <c r="S152" s="52"/>
+      <c r="T152" s="52"/>
     </row>
     <row r="153" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A153" s="50">
-        <v>10380011</v>
-      </c>
-      <c r="B153" s="51">
-        <v>103800</v>
-      </c>
-      <c r="C153" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="D153" s="53">
-        <v>103800001</v>
-      </c>
-      <c r="E153" s="54">
-        <v>12</v>
+      <c r="A153" s="53">
+        <v>10340111</v>
+      </c>
+      <c r="B153" s="54">
+        <v>103401</v>
+      </c>
+      <c r="C153" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="D153" s="56">
+        <v>103400001</v>
+      </c>
+      <c r="E153" s="57">
+        <v>11</v>
       </c>
       <c r="F153" s="23" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="G153" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="H153" s="61">
-        <v>0</v>
-      </c>
-      <c r="I153" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J153" s="57">
-        <v>0</v>
-      </c>
-      <c r="K153" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L153" s="62">
+        <v>73</v>
+      </c>
+      <c r="H153" s="62">
+        <v>0</v>
+      </c>
+      <c r="I153" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J153" s="59">
+        <v>0</v>
+      </c>
+      <c r="K153" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L153" s="63">
         <v>0</v>
       </c>
       <c r="M153" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N153" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O153" s="60"/>
-      <c r="P153" s="60"/>
-      <c r="Q153" s="60"/>
-      <c r="R153" s="60"/>
-      <c r="S153" s="56"/>
-      <c r="T153" s="56"/>
+      <c r="N153" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O153" s="51"/>
+      <c r="P153" s="51"/>
+      <c r="Q153" s="51"/>
+      <c r="R153" s="51"/>
+      <c r="S153" s="52"/>
+      <c r="T153" s="52"/>
     </row>
     <row r="154" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A154" s="50">
-        <v>10380012</v>
-      </c>
-      <c r="B154" s="51">
-        <v>103800</v>
-      </c>
-      <c r="C154" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="D154" s="53">
-        <v>103800001</v>
-      </c>
-      <c r="E154" s="54">
-        <v>13</v>
+      <c r="A154" s="53">
+        <v>10340112</v>
+      </c>
+      <c r="B154" s="54">
+        <v>103401</v>
+      </c>
+      <c r="C154" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="D154" s="56">
+        <v>103400001</v>
+      </c>
+      <c r="E154" s="57">
+        <v>12</v>
       </c>
       <c r="F154" s="23" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G154" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="H154" s="61">
-        <v>0</v>
-      </c>
-      <c r="I154" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J154" s="57">
-        <v>0</v>
-      </c>
-      <c r="K154" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L154" s="62">
+        <v>78</v>
+      </c>
+      <c r="H154" s="62">
+        <v>0</v>
+      </c>
+      <c r="I154" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J154" s="59">
+        <v>0</v>
+      </c>
+      <c r="K154" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L154" s="63">
         <v>0</v>
       </c>
       <c r="M154" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N154" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O154" s="60"/>
-      <c r="P154" s="60"/>
-      <c r="Q154" s="60"/>
-      <c r="R154" s="60"/>
-      <c r="S154" s="56"/>
-      <c r="T154" s="56"/>
+      <c r="N154" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O154" s="51"/>
+      <c r="P154" s="51"/>
+      <c r="Q154" s="51"/>
+      <c r="R154" s="51"/>
+      <c r="S154" s="52"/>
+      <c r="T154" s="52"/>
     </row>
     <row r="155" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A155" s="50">
-        <v>10270010</v>
-      </c>
-      <c r="B155" s="51">
-        <v>102700</v>
-      </c>
-      <c r="C155" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="D155" s="53">
-        <v>102700001</v>
-      </c>
-      <c r="E155" s="54">
+      <c r="A155" s="53">
+        <v>10380010</v>
+      </c>
+      <c r="B155" s="54">
+        <v>103800</v>
+      </c>
+      <c r="C155" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="D155" s="56">
+        <v>103800001</v>
+      </c>
+      <c r="E155" s="57">
         <v>11</v>
       </c>
       <c r="F155" s="23" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G155" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H155" s="61">
-        <v>0</v>
-      </c>
-      <c r="I155" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J155" s="57">
-        <v>0</v>
-      </c>
-      <c r="K155" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L155" s="62">
+        <v>93</v>
+      </c>
+      <c r="H155" s="62">
+        <v>0</v>
+      </c>
+      <c r="I155" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J155" s="59">
+        <v>0</v>
+      </c>
+      <c r="K155" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L155" s="63">
         <v>0</v>
       </c>
       <c r="M155" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N155" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O155" s="60"/>
-      <c r="P155" s="60"/>
-      <c r="Q155" s="60"/>
-      <c r="R155" s="60"/>
-      <c r="S155" s="56"/>
-      <c r="T155" s="56"/>
+      <c r="N155" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O155" s="51"/>
+      <c r="P155" s="51"/>
+      <c r="Q155" s="51"/>
+      <c r="R155" s="51"/>
+      <c r="S155" s="52"/>
+      <c r="T155" s="52"/>
     </row>
     <row r="156" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A156" s="50">
-        <v>10270011</v>
-      </c>
-      <c r="B156" s="51">
-        <v>102700</v>
-      </c>
-      <c r="C156" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="D156" s="53">
-        <v>102700001</v>
-      </c>
-      <c r="E156" s="54">
+      <c r="A156" s="53">
+        <v>10380011</v>
+      </c>
+      <c r="B156" s="54">
+        <v>103800</v>
+      </c>
+      <c r="C156" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="D156" s="56">
+        <v>103800001</v>
+      </c>
+      <c r="E156" s="57">
         <v>12</v>
       </c>
       <c r="F156" s="23" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="G156" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H156" s="61">
-        <v>0</v>
-      </c>
-      <c r="I156" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J156" s="57">
-        <v>0</v>
-      </c>
-      <c r="K156" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L156" s="62">
+        <v>95</v>
+      </c>
+      <c r="H156" s="62">
+        <v>0</v>
+      </c>
+      <c r="I156" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J156" s="59">
+        <v>0</v>
+      </c>
+      <c r="K156" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L156" s="63">
         <v>0</v>
       </c>
       <c r="M156" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N156" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O156" s="60"/>
-      <c r="P156" s="60"/>
-      <c r="Q156" s="60"/>
-      <c r="R156" s="60"/>
-      <c r="S156" s="56"/>
-      <c r="T156" s="56"/>
+      <c r="N156" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O156" s="51"/>
+      <c r="P156" s="51"/>
+      <c r="Q156" s="51"/>
+      <c r="R156" s="51"/>
+      <c r="S156" s="52"/>
+      <c r="T156" s="52"/>
     </row>
     <row r="157" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A157" s="50">
-        <v>10270012</v>
-      </c>
-      <c r="B157" s="51">
-        <v>102700</v>
-      </c>
-      <c r="C157" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="D157" s="53">
-        <v>102700001</v>
-      </c>
-      <c r="E157" s="54">
+      <c r="A157" s="53">
+        <v>10380012</v>
+      </c>
+      <c r="B157" s="54">
+        <v>103800</v>
+      </c>
+      <c r="C157" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="D157" s="56">
+        <v>103800001</v>
+      </c>
+      <c r="E157" s="57">
         <v>13</v>
       </c>
       <c r="F157" s="23" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="G157" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="H157" s="61">
-        <v>0</v>
-      </c>
-      <c r="I157" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J157" s="57">
-        <v>0</v>
-      </c>
-      <c r="K157" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L157" s="62">
+        <v>97</v>
+      </c>
+      <c r="H157" s="62">
+        <v>0</v>
+      </c>
+      <c r="I157" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J157" s="59">
+        <v>0</v>
+      </c>
+      <c r="K157" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L157" s="63">
         <v>0</v>
       </c>
       <c r="M157" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N157" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O157" s="60"/>
-      <c r="P157" s="60"/>
-      <c r="Q157" s="60"/>
-      <c r="R157" s="60"/>
-      <c r="S157" s="56"/>
-      <c r="T157" s="56"/>
+      <c r="N157" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O157" s="51"/>
+      <c r="P157" s="51"/>
+      <c r="Q157" s="51"/>
+      <c r="R157" s="51"/>
+      <c r="S157" s="52"/>
+      <c r="T157" s="52"/>
     </row>
     <row r="158" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A158" s="50">
-        <v>10370010</v>
-      </c>
-      <c r="B158" s="51">
-        <v>103700</v>
-      </c>
-      <c r="C158" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="D158" s="53">
-        <v>103700001</v>
-      </c>
-      <c r="E158" s="54">
+      <c r="A158" s="53">
+        <v>10270010</v>
+      </c>
+      <c r="B158" s="54">
+        <v>102700</v>
+      </c>
+      <c r="C158" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D158" s="56">
+        <v>102700001</v>
+      </c>
+      <c r="E158" s="57">
         <v>11</v>
       </c>
       <c r="F158" s="23" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G158" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="H158" s="61">
-        <v>0</v>
-      </c>
-      <c r="I158" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J158" s="57">
-        <v>0</v>
-      </c>
-      <c r="K158" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L158" s="62">
+        <v>51</v>
+      </c>
+      <c r="H158" s="62">
+        <v>0</v>
+      </c>
+      <c r="I158" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J158" s="59">
+        <v>0</v>
+      </c>
+      <c r="K158" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L158" s="63">
         <v>0</v>
       </c>
       <c r="M158" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N158" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O158" s="60"/>
-      <c r="P158" s="60"/>
-      <c r="Q158" s="60"/>
-      <c r="R158" s="60"/>
-      <c r="S158" s="56"/>
-      <c r="T158" s="56"/>
+      <c r="N158" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O158" s="51"/>
+      <c r="P158" s="51"/>
+      <c r="Q158" s="51"/>
+      <c r="R158" s="51"/>
+      <c r="S158" s="52"/>
+      <c r="T158" s="52"/>
     </row>
     <row r="159" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A159" s="50">
-        <v>10370011</v>
-      </c>
-      <c r="B159" s="51">
-        <v>103700</v>
-      </c>
-      <c r="C159" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="D159" s="53">
-        <v>103700001</v>
-      </c>
-      <c r="E159" s="54">
+      <c r="A159" s="53">
+        <v>10270011</v>
+      </c>
+      <c r="B159" s="54">
+        <v>102700</v>
+      </c>
+      <c r="C159" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D159" s="56">
+        <v>102700001</v>
+      </c>
+      <c r="E159" s="57">
         <v>12</v>
       </c>
       <c r="F159" s="23" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G159" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H159" s="61">
-        <v>0</v>
-      </c>
-      <c r="I159" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J159" s="57">
-        <v>0</v>
-      </c>
-      <c r="K159" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L159" s="62">
+        <v>53</v>
+      </c>
+      <c r="H159" s="62">
+        <v>0</v>
+      </c>
+      <c r="I159" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J159" s="59">
+        <v>0</v>
+      </c>
+      <c r="K159" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L159" s="63">
         <v>0</v>
       </c>
       <c r="M159" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N159" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O159" s="60"/>
-      <c r="P159" s="60"/>
-      <c r="Q159" s="60"/>
-      <c r="R159" s="60"/>
-      <c r="S159" s="56"/>
-      <c r="T159" s="56"/>
+      <c r="N159" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O159" s="51"/>
+      <c r="P159" s="51"/>
+      <c r="Q159" s="51"/>
+      <c r="R159" s="51"/>
+      <c r="S159" s="52"/>
+      <c r="T159" s="52"/>
     </row>
     <row r="160" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A160" s="50">
-        <v>10370012</v>
-      </c>
-      <c r="B160" s="51">
-        <v>103700</v>
-      </c>
-      <c r="C160" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="D160" s="53">
-        <v>103100001</v>
-      </c>
-      <c r="E160" s="54">
+      <c r="A160" s="53">
+        <v>10270012</v>
+      </c>
+      <c r="B160" s="54">
+        <v>102700</v>
+      </c>
+      <c r="C160" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D160" s="56">
+        <v>102700001</v>
+      </c>
+      <c r="E160" s="57">
         <v>13</v>
       </c>
       <c r="F160" s="23" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G160" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="H160" s="61">
-        <v>0</v>
-      </c>
-      <c r="I160" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J160" s="57">
-        <v>0</v>
-      </c>
-      <c r="K160" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L160" s="62">
+        <v>55</v>
+      </c>
+      <c r="H160" s="62">
+        <v>0</v>
+      </c>
+      <c r="I160" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J160" s="59">
+        <v>0</v>
+      </c>
+      <c r="K160" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L160" s="63">
         <v>0</v>
       </c>
       <c r="M160" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N160" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O160" s="60"/>
-      <c r="P160" s="60"/>
-      <c r="Q160" s="60"/>
-      <c r="R160" s="60"/>
-      <c r="S160" s="56"/>
-      <c r="T160" s="56"/>
+      <c r="N160" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O160" s="51"/>
+      <c r="P160" s="51"/>
+      <c r="Q160" s="51"/>
+      <c r="R160" s="51"/>
+      <c r="S160" s="52"/>
+      <c r="T160" s="52"/>
     </row>
     <row r="161" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A161" s="50">
-        <v>10310010</v>
-      </c>
-      <c r="B161" s="51">
-        <v>103100</v>
-      </c>
-      <c r="C161" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="D161" s="53">
-        <v>103100001</v>
-      </c>
-      <c r="E161" s="54">
+      <c r="A161" s="53">
+        <v>10370010</v>
+      </c>
+      <c r="B161" s="54">
+        <v>103700</v>
+      </c>
+      <c r="C161" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="D161" s="56">
+        <v>103700001</v>
+      </c>
+      <c r="E161" s="57">
         <v>11</v>
       </c>
       <c r="F161" s="23" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="G161" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="H161" s="55">
-        <v>0</v>
-      </c>
-      <c r="I161" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J161" s="57">
-        <v>0</v>
-      </c>
-      <c r="K161" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L161" s="62">
+        <v>39</v>
+      </c>
+      <c r="H161" s="62">
+        <v>0</v>
+      </c>
+      <c r="I161" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J161" s="59">
+        <v>0</v>
+      </c>
+      <c r="K161" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L161" s="63">
         <v>0</v>
       </c>
       <c r="M161" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N161" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O161" s="60"/>
-      <c r="P161" s="60"/>
-      <c r="Q161" s="60"/>
-      <c r="R161" s="60"/>
-      <c r="S161" s="56"/>
-      <c r="T161" s="56"/>
+      <c r="N161" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O161" s="51"/>
+      <c r="P161" s="51"/>
+      <c r="Q161" s="51"/>
+      <c r="R161" s="51"/>
+      <c r="S161" s="52"/>
+      <c r="T161" s="52"/>
     </row>
     <row r="162" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A162" s="50">
-        <v>10310011</v>
-      </c>
-      <c r="B162" s="51">
-        <v>103100</v>
-      </c>
-      <c r="C162" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="D162" s="53">
-        <v>103100001</v>
-      </c>
-      <c r="E162" s="54">
+      <c r="A162" s="53">
+        <v>10370011</v>
+      </c>
+      <c r="B162" s="54">
+        <v>103700</v>
+      </c>
+      <c r="C162" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="D162" s="56">
+        <v>103700001</v>
+      </c>
+      <c r="E162" s="57">
         <v>12</v>
       </c>
       <c r="F162" s="23" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="G162" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="H162" s="55">
-        <v>0</v>
-      </c>
-      <c r="I162" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J162" s="57">
-        <v>0</v>
-      </c>
-      <c r="K162" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L162" s="62">
+        <v>42</v>
+      </c>
+      <c r="H162" s="62">
+        <v>0</v>
+      </c>
+      <c r="I162" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J162" s="59">
+        <v>0</v>
+      </c>
+      <c r="K162" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L162" s="63">
         <v>0</v>
       </c>
       <c r="M162" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N162" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O162" s="60"/>
-      <c r="P162" s="60"/>
-      <c r="Q162" s="60"/>
-      <c r="R162" s="60"/>
-      <c r="S162" s="56"/>
-      <c r="T162" s="56"/>
+      <c r="N162" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O162" s="51"/>
+      <c r="P162" s="51"/>
+      <c r="Q162" s="51"/>
+      <c r="R162" s="51"/>
+      <c r="S162" s="52"/>
+      <c r="T162" s="52"/>
     </row>
     <row r="163" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A163" s="50">
-        <v>10310012</v>
-      </c>
-      <c r="B163" s="51">
-        <v>103100</v>
-      </c>
-      <c r="C163" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="D163" s="53">
+      <c r="A163" s="53">
+        <v>10370012</v>
+      </c>
+      <c r="B163" s="54">
+        <v>103700</v>
+      </c>
+      <c r="C163" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="D163" s="56">
         <v>103100001</v>
       </c>
-      <c r="E163" s="54">
+      <c r="E163" s="57">
         <v>13</v>
       </c>
       <c r="F163" s="23" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="G163" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="H163" s="61">
-        <v>0</v>
-      </c>
-      <c r="I163" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J163" s="57">
-        <v>0</v>
-      </c>
-      <c r="K163" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L163" s="62">
+        <v>46</v>
+      </c>
+      <c r="H163" s="62">
+        <v>0</v>
+      </c>
+      <c r="I163" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J163" s="59">
+        <v>0</v>
+      </c>
+      <c r="K163" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L163" s="63">
         <v>0</v>
       </c>
       <c r="M163" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N163" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O163" s="60"/>
-      <c r="P163" s="60"/>
-      <c r="Q163" s="60"/>
-      <c r="R163" s="60"/>
-      <c r="S163" s="56"/>
-      <c r="T163" s="56"/>
+      <c r="N163" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O163" s="51"/>
+      <c r="P163" s="51"/>
+      <c r="Q163" s="51"/>
+      <c r="R163" s="51"/>
+      <c r="S163" s="52"/>
+      <c r="T163" s="52"/>
     </row>
     <row r="164" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A164" s="50">
-        <v>10400010</v>
-      </c>
-      <c r="B164" s="51">
-        <v>104000</v>
-      </c>
-      <c r="C164" s="52" t="s">
-        <v>107</v>
-      </c>
-      <c r="D164" s="53">
-        <v>104000001</v>
-      </c>
-      <c r="E164" s="54">
+      <c r="A164" s="53">
+        <v>10310010</v>
+      </c>
+      <c r="B164" s="54">
+        <v>103100</v>
+      </c>
+      <c r="C164" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="D164" s="56">
+        <v>103100001</v>
+      </c>
+      <c r="E164" s="57">
         <v>11</v>
       </c>
       <c r="F164" s="23" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G164" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="H164" s="61">
-        <v>0</v>
-      </c>
-      <c r="I164" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J164" s="57">
-        <v>0</v>
-      </c>
-      <c r="K164" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L164" s="62">
+        <v>102</v>
+      </c>
+      <c r="H164" s="58">
+        <v>0</v>
+      </c>
+      <c r="I164" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J164" s="59">
+        <v>0</v>
+      </c>
+      <c r="K164" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L164" s="63">
         <v>0</v>
       </c>
       <c r="M164" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N164" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O164" s="60"/>
-      <c r="P164" s="60"/>
-      <c r="Q164" s="60"/>
-      <c r="R164" s="60"/>
-      <c r="S164" s="56"/>
-      <c r="T164" s="56"/>
+      <c r="N164" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O164" s="51"/>
+      <c r="P164" s="51"/>
+      <c r="Q164" s="51"/>
+      <c r="R164" s="51"/>
+      <c r="S164" s="52"/>
+      <c r="T164" s="52"/>
     </row>
     <row r="165" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A165" s="50">
-        <v>10400011</v>
-      </c>
-      <c r="B165" s="51">
-        <v>104000</v>
-      </c>
-      <c r="C165" s="52" t="s">
-        <v>107</v>
-      </c>
-      <c r="D165" s="53">
-        <v>104000001</v>
-      </c>
-      <c r="E165" s="54">
+      <c r="A165" s="53">
+        <v>10310011</v>
+      </c>
+      <c r="B165" s="54">
+        <v>103100</v>
+      </c>
+      <c r="C165" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="D165" s="56">
+        <v>103100001</v>
+      </c>
+      <c r="E165" s="57">
         <v>12</v>
       </c>
       <c r="F165" s="23" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G165" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="H165" s="61">
-        <v>0</v>
-      </c>
-      <c r="I165" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J165" s="57">
-        <v>0</v>
-      </c>
-      <c r="K165" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L165" s="62">
+        <v>104</v>
+      </c>
+      <c r="H165" s="58">
+        <v>0</v>
+      </c>
+      <c r="I165" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J165" s="59">
+        <v>0</v>
+      </c>
+      <c r="K165" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L165" s="63">
         <v>0</v>
       </c>
       <c r="M165" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N165" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O165" s="60"/>
-      <c r="P165" s="60"/>
-      <c r="Q165" s="60"/>
-      <c r="R165" s="60"/>
-      <c r="S165" s="56"/>
-      <c r="T165" s="56"/>
+      <c r="N165" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O165" s="51"/>
+      <c r="P165" s="51"/>
+      <c r="Q165" s="51"/>
+      <c r="R165" s="51"/>
+      <c r="S165" s="52"/>
+      <c r="T165" s="52"/>
     </row>
     <row r="166" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A166" s="50">
-        <v>10400012</v>
-      </c>
-      <c r="B166" s="51">
-        <v>104000</v>
-      </c>
-      <c r="C166" s="52" t="s">
-        <v>107</v>
-      </c>
-      <c r="D166" s="53">
-        <v>104000001</v>
-      </c>
-      <c r="E166" s="54">
+      <c r="A166" s="53">
+        <v>10310012</v>
+      </c>
+      <c r="B166" s="54">
+        <v>103100</v>
+      </c>
+      <c r="C166" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="D166" s="56">
+        <v>103100001</v>
+      </c>
+      <c r="E166" s="57">
         <v>13</v>
       </c>
       <c r="F166" s="23" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G166" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="H166" s="61">
-        <v>0</v>
-      </c>
-      <c r="I166" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J166" s="57">
-        <v>0</v>
-      </c>
-      <c r="K166" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L166" s="62">
+        <v>106</v>
+      </c>
+      <c r="H166" s="62">
+        <v>0</v>
+      </c>
+      <c r="I166" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J166" s="59">
+        <v>0</v>
+      </c>
+      <c r="K166" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L166" s="63">
         <v>0</v>
       </c>
       <c r="M166" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N166" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O166" s="60"/>
-      <c r="P166" s="60"/>
-      <c r="Q166" s="60"/>
-      <c r="R166" s="60"/>
-      <c r="S166" s="56"/>
-      <c r="T166" s="56"/>
+      <c r="N166" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O166" s="51"/>
+      <c r="P166" s="51"/>
+      <c r="Q166" s="51"/>
+      <c r="R166" s="51"/>
+      <c r="S166" s="52"/>
+      <c r="T166" s="52"/>
     </row>
     <row r="167" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A167" s="50">
-        <v>10390010</v>
-      </c>
-      <c r="B167" s="51">
-        <v>103900</v>
-      </c>
-      <c r="C167" s="52" t="s">
-        <v>108</v>
-      </c>
-      <c r="D167" s="53">
-        <v>103900001</v>
-      </c>
-      <c r="E167" s="54">
+      <c r="A167" s="53">
+        <v>10400010</v>
+      </c>
+      <c r="B167" s="54">
+        <v>104000</v>
+      </c>
+      <c r="C167" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="D167" s="56">
+        <v>104000001</v>
+      </c>
+      <c r="E167" s="57">
         <v>11</v>
       </c>
       <c r="F167" s="23" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G167" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="H167" s="61">
-        <v>0</v>
-      </c>
-      <c r="I167" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J167" s="57">
-        <v>0</v>
-      </c>
-      <c r="K167" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L167" s="62">
+        <v>93</v>
+      </c>
+      <c r="H167" s="62">
+        <v>0</v>
+      </c>
+      <c r="I167" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J167" s="59">
+        <v>0</v>
+      </c>
+      <c r="K167" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L167" s="63">
         <v>0</v>
       </c>
       <c r="M167" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N167" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O167" s="60"/>
-      <c r="P167" s="60"/>
-      <c r="Q167" s="60"/>
-      <c r="R167" s="60"/>
-      <c r="S167" s="56"/>
-      <c r="T167" s="56"/>
+      <c r="N167" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O167" s="51"/>
+      <c r="P167" s="51"/>
+      <c r="Q167" s="51"/>
+      <c r="R167" s="51"/>
+      <c r="S167" s="52"/>
+      <c r="T167" s="52"/>
     </row>
     <row r="168" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A168" s="50">
-        <v>10390011</v>
-      </c>
-      <c r="B168" s="51">
-        <v>103900</v>
-      </c>
-      <c r="C168" s="52" t="s">
-        <v>108</v>
-      </c>
-      <c r="D168" s="53">
-        <v>103900001</v>
-      </c>
-      <c r="E168" s="54">
+      <c r="A168" s="53">
+        <v>10400011</v>
+      </c>
+      <c r="B168" s="54">
+        <v>104000</v>
+      </c>
+      <c r="C168" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="D168" s="56">
+        <v>104000001</v>
+      </c>
+      <c r="E168" s="57">
         <v>12</v>
       </c>
       <c r="F168" s="23" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G168" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="H168" s="61">
-        <v>0</v>
-      </c>
-      <c r="I168" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J168" s="57">
-        <v>0</v>
-      </c>
-      <c r="K168" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L168" s="62">
+        <v>95</v>
+      </c>
+      <c r="H168" s="62">
+        <v>0</v>
+      </c>
+      <c r="I168" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J168" s="59">
+        <v>0</v>
+      </c>
+      <c r="K168" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L168" s="63">
         <v>0</v>
       </c>
       <c r="M168" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N168" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O168" s="60"/>
-      <c r="P168" s="60"/>
-      <c r="Q168" s="60"/>
-      <c r="R168" s="60"/>
-      <c r="S168" s="56"/>
-      <c r="T168" s="56"/>
+      <c r="N168" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O168" s="51"/>
+      <c r="P168" s="51"/>
+      <c r="Q168" s="51"/>
+      <c r="R168" s="51"/>
+      <c r="S168" s="52"/>
+      <c r="T168" s="52"/>
     </row>
     <row r="169" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A169" s="50">
-        <v>10390012</v>
-      </c>
-      <c r="B169" s="51">
-        <v>103900</v>
-      </c>
-      <c r="C169" s="52" t="s">
-        <v>108</v>
-      </c>
-      <c r="D169" s="53">
-        <v>103900001</v>
-      </c>
-      <c r="E169" s="54">
+      <c r="A169" s="53">
+        <v>10400012</v>
+      </c>
+      <c r="B169" s="54">
+        <v>104000</v>
+      </c>
+      <c r="C169" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="D169" s="56">
+        <v>104000001</v>
+      </c>
+      <c r="E169" s="57">
         <v>13</v>
       </c>
       <c r="F169" s="23" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G169" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="H169" s="61">
-        <v>0</v>
-      </c>
-      <c r="I169" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J169" s="57">
-        <v>0</v>
-      </c>
-      <c r="K169" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L169" s="62">
+        <v>97</v>
+      </c>
+      <c r="H169" s="62">
+        <v>0</v>
+      </c>
+      <c r="I169" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J169" s="59">
+        <v>0</v>
+      </c>
+      <c r="K169" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L169" s="63">
         <v>0</v>
       </c>
       <c r="M169" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N169" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O169" s="60"/>
-      <c r="P169" s="60"/>
-      <c r="Q169" s="60"/>
-      <c r="R169" s="60"/>
-      <c r="S169" s="56"/>
-      <c r="T169" s="56"/>
+      <c r="N169" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O169" s="51"/>
+      <c r="P169" s="51"/>
+      <c r="Q169" s="51"/>
+      <c r="R169" s="51"/>
+      <c r="S169" s="52"/>
+      <c r="T169" s="52"/>
     </row>
     <row r="170" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A170" s="50">
-        <v>10160010</v>
-      </c>
-      <c r="B170" s="51">
-        <v>101600</v>
-      </c>
-      <c r="C170" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="D170" s="53">
-        <v>101600001</v>
-      </c>
-      <c r="E170" s="54">
+      <c r="A170" s="53">
+        <v>10390010</v>
+      </c>
+      <c r="B170" s="54">
+        <v>103900</v>
+      </c>
+      <c r="C170" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="D170" s="56">
+        <v>103900001</v>
+      </c>
+      <c r="E170" s="57">
         <v>11</v>
       </c>
       <c r="F170" s="23" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="G170" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H170" s="61">
-        <v>0</v>
-      </c>
-      <c r="I170" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J170" s="57">
-        <v>0</v>
-      </c>
-      <c r="K170" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L170" s="62">
+        <v>102</v>
+      </c>
+      <c r="H170" s="62">
+        <v>0</v>
+      </c>
+      <c r="I170" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J170" s="59">
+        <v>0</v>
+      </c>
+      <c r="K170" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L170" s="63">
         <v>0</v>
       </c>
       <c r="M170" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N170" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O170" s="60"/>
-      <c r="P170" s="60"/>
-      <c r="Q170" s="60"/>
-      <c r="R170" s="60"/>
-      <c r="S170" s="56"/>
-      <c r="T170" s="56"/>
+      <c r="N170" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O170" s="51"/>
+      <c r="P170" s="51"/>
+      <c r="Q170" s="51"/>
+      <c r="R170" s="51"/>
+      <c r="S170" s="52"/>
+      <c r="T170" s="52"/>
     </row>
     <row r="171" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A171" s="50">
-        <v>10160011</v>
-      </c>
-      <c r="B171" s="51">
-        <v>101600</v>
-      </c>
-      <c r="C171" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="D171" s="53">
-        <v>101600001</v>
-      </c>
-      <c r="E171" s="54">
+      <c r="A171" s="53">
+        <v>10390011</v>
+      </c>
+      <c r="B171" s="54">
+        <v>103900</v>
+      </c>
+      <c r="C171" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="D171" s="56">
+        <v>103900001</v>
+      </c>
+      <c r="E171" s="57">
         <v>12</v>
       </c>
       <c r="F171" s="23" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="G171" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H171" s="61">
-        <v>0</v>
-      </c>
-      <c r="I171" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J171" s="57">
-        <v>0</v>
-      </c>
-      <c r="K171" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L171" s="62">
+        <v>104</v>
+      </c>
+      <c r="H171" s="62">
+        <v>0</v>
+      </c>
+      <c r="I171" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J171" s="59">
+        <v>0</v>
+      </c>
+      <c r="K171" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L171" s="63">
         <v>0</v>
       </c>
       <c r="M171" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N171" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O171" s="60"/>
-      <c r="P171" s="60"/>
-      <c r="Q171" s="60"/>
-      <c r="R171" s="60"/>
-      <c r="S171" s="56"/>
-      <c r="T171" s="56"/>
+      <c r="N171" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O171" s="51"/>
+      <c r="P171" s="51"/>
+      <c r="Q171" s="51"/>
+      <c r="R171" s="51"/>
+      <c r="S171" s="52"/>
+      <c r="T171" s="52"/>
     </row>
     <row r="172" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A172" s="50">
-        <v>10160012</v>
-      </c>
-      <c r="B172" s="51">
-        <v>101600</v>
-      </c>
-      <c r="C172" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="D172" s="53">
-        <v>101600001</v>
-      </c>
-      <c r="E172" s="54">
+      <c r="A172" s="53">
+        <v>10390012</v>
+      </c>
+      <c r="B172" s="54">
+        <v>103900</v>
+      </c>
+      <c r="C172" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="D172" s="56">
+        <v>103900001</v>
+      </c>
+      <c r="E172" s="57">
         <v>13</v>
       </c>
       <c r="F172" s="23" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="G172" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="H172" s="61">
-        <v>0</v>
-      </c>
-      <c r="I172" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J172" s="57">
-        <v>0</v>
-      </c>
-      <c r="K172" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L172" s="62">
+        <v>106</v>
+      </c>
+      <c r="H172" s="62">
+        <v>0</v>
+      </c>
+      <c r="I172" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J172" s="59">
+        <v>0</v>
+      </c>
+      <c r="K172" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L172" s="63">
         <v>0</v>
       </c>
       <c r="M172" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N172" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O172" s="60"/>
-      <c r="P172" s="60"/>
-      <c r="Q172" s="60"/>
-      <c r="R172" s="60"/>
-      <c r="S172" s="56"/>
-      <c r="T172" s="56"/>
+      <c r="N172" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O172" s="51"/>
+      <c r="P172" s="51"/>
+      <c r="Q172" s="51"/>
+      <c r="R172" s="51"/>
+      <c r="S172" s="52"/>
+      <c r="T172" s="52"/>
     </row>
     <row r="173" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A173" s="50">
-        <v>10150010</v>
-      </c>
-      <c r="B173" s="51">
-        <v>101500</v>
-      </c>
-      <c r="C173" s="52" t="s">
-        <v>110</v>
-      </c>
-      <c r="D173" s="53">
-        <v>101500001</v>
-      </c>
-      <c r="E173" s="54">
+      <c r="A173" s="53">
+        <v>10160010</v>
+      </c>
+      <c r="B173" s="54">
+        <v>101600</v>
+      </c>
+      <c r="C173" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="D173" s="56">
+        <v>101600001</v>
+      </c>
+      <c r="E173" s="57">
         <v>11</v>
       </c>
       <c r="F173" s="23" t="s">
@@ -10498,48 +10498,48 @@
       <c r="G173" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H173" s="61">
-        <v>0</v>
-      </c>
-      <c r="I173" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J173" s="57">
-        <v>0</v>
-      </c>
-      <c r="K173" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L173" s="62">
+      <c r="H173" s="62">
+        <v>0</v>
+      </c>
+      <c r="I173" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J173" s="59">
+        <v>0</v>
+      </c>
+      <c r="K173" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L173" s="63">
         <v>0</v>
       </c>
       <c r="M173" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N173" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O173" s="60"/>
-      <c r="P173" s="60"/>
-      <c r="Q173" s="60"/>
-      <c r="R173" s="60"/>
-      <c r="S173" s="56"/>
-      <c r="T173" s="56"/>
+      <c r="N173" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O173" s="51"/>
+      <c r="P173" s="51"/>
+      <c r="Q173" s="51"/>
+      <c r="R173" s="51"/>
+      <c r="S173" s="52"/>
+      <c r="T173" s="52"/>
     </row>
     <row r="174" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A174" s="50">
-        <v>10150011</v>
-      </c>
-      <c r="B174" s="51">
-        <v>101500</v>
-      </c>
-      <c r="C174" s="52" t="s">
-        <v>110</v>
-      </c>
-      <c r="D174" s="53">
-        <v>101500001</v>
-      </c>
-      <c r="E174" s="54">
+      <c r="A174" s="53">
+        <v>10160011</v>
+      </c>
+      <c r="B174" s="54">
+        <v>101600</v>
+      </c>
+      <c r="C174" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="D174" s="56">
+        <v>101600001</v>
+      </c>
+      <c r="E174" s="57">
         <v>12</v>
       </c>
       <c r="F174" s="23" t="s">
@@ -10548,48 +10548,48 @@
       <c r="G174" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H174" s="61">
-        <v>0</v>
-      </c>
-      <c r="I174" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J174" s="57">
-        <v>0</v>
-      </c>
-      <c r="K174" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L174" s="62">
+      <c r="H174" s="62">
+        <v>0</v>
+      </c>
+      <c r="I174" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J174" s="59">
+        <v>0</v>
+      </c>
+      <c r="K174" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L174" s="63">
         <v>0</v>
       </c>
       <c r="M174" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N174" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O174" s="60"/>
-      <c r="P174" s="60"/>
-      <c r="Q174" s="60"/>
-      <c r="R174" s="60"/>
-      <c r="S174" s="56"/>
-      <c r="T174" s="56"/>
+      <c r="N174" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O174" s="51"/>
+      <c r="P174" s="51"/>
+      <c r="Q174" s="51"/>
+      <c r="R174" s="51"/>
+      <c r="S174" s="52"/>
+      <c r="T174" s="52"/>
     </row>
     <row r="175" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A175" s="50">
-        <v>10150012</v>
-      </c>
-      <c r="B175" s="51">
-        <v>101500</v>
-      </c>
-      <c r="C175" s="52" t="s">
-        <v>110</v>
-      </c>
-      <c r="D175" s="53">
-        <v>101500001</v>
-      </c>
-      <c r="E175" s="54">
+      <c r="A175" s="53">
+        <v>10160012</v>
+      </c>
+      <c r="B175" s="54">
+        <v>101600</v>
+      </c>
+      <c r="C175" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="D175" s="56">
+        <v>101600001</v>
+      </c>
+      <c r="E175" s="57">
         <v>13</v>
       </c>
       <c r="F175" s="23" t="s">
@@ -10598,48 +10598,48 @@
       <c r="G175" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="H175" s="61">
-        <v>0</v>
-      </c>
-      <c r="I175" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J175" s="57">
-        <v>0</v>
-      </c>
-      <c r="K175" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L175" s="62">
+      <c r="H175" s="62">
+        <v>0</v>
+      </c>
+      <c r="I175" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J175" s="59">
+        <v>0</v>
+      </c>
+      <c r="K175" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L175" s="63">
         <v>0</v>
       </c>
       <c r="M175" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N175" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O175" s="60"/>
-      <c r="P175" s="60"/>
-      <c r="Q175" s="60"/>
-      <c r="R175" s="60"/>
-      <c r="S175" s="56"/>
-      <c r="T175" s="56"/>
+      <c r="N175" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O175" s="51"/>
+      <c r="P175" s="51"/>
+      <c r="Q175" s="51"/>
+      <c r="R175" s="51"/>
+      <c r="S175" s="52"/>
+      <c r="T175" s="52"/>
     </row>
     <row r="176" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A176" s="50">
-        <v>10260010</v>
-      </c>
-      <c r="B176" s="51">
-        <v>102600</v>
-      </c>
-      <c r="C176" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="D176" s="53">
-        <v>102600001</v>
-      </c>
-      <c r="E176" s="54">
+      <c r="A176" s="53">
+        <v>10150010</v>
+      </c>
+      <c r="B176" s="54">
+        <v>101500</v>
+      </c>
+      <c r="C176" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D176" s="56">
+        <v>101500001</v>
+      </c>
+      <c r="E176" s="57">
         <v>11</v>
       </c>
       <c r="F176" s="23" t="s">
@@ -10648,48 +10648,48 @@
       <c r="G176" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H176" s="61">
-        <v>0</v>
-      </c>
-      <c r="I176" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J176" s="57">
-        <v>0</v>
-      </c>
-      <c r="K176" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L176" s="62">
+      <c r="H176" s="62">
+        <v>0</v>
+      </c>
+      <c r="I176" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J176" s="59">
+        <v>0</v>
+      </c>
+      <c r="K176" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L176" s="63">
         <v>0</v>
       </c>
       <c r="M176" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N176" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O176" s="60"/>
-      <c r="P176" s="60"/>
-      <c r="Q176" s="60"/>
-      <c r="R176" s="60"/>
-      <c r="S176" s="56"/>
-      <c r="T176" s="56"/>
+      <c r="N176" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O176" s="51"/>
+      <c r="P176" s="51"/>
+      <c r="Q176" s="51"/>
+      <c r="R176" s="51"/>
+      <c r="S176" s="52"/>
+      <c r="T176" s="52"/>
     </row>
     <row r="177" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A177" s="50">
-        <v>10260011</v>
-      </c>
-      <c r="B177" s="51">
-        <v>102600</v>
-      </c>
-      <c r="C177" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="D177" s="53">
-        <v>102600001</v>
-      </c>
-      <c r="E177" s="54">
+      <c r="A177" s="53">
+        <v>10150011</v>
+      </c>
+      <c r="B177" s="54">
+        <v>101500</v>
+      </c>
+      <c r="C177" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D177" s="56">
+        <v>101500001</v>
+      </c>
+      <c r="E177" s="57">
         <v>12</v>
       </c>
       <c r="F177" s="23" t="s">
@@ -10698,48 +10698,48 @@
       <c r="G177" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H177" s="61">
-        <v>0</v>
-      </c>
-      <c r="I177" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J177" s="57">
-        <v>0</v>
-      </c>
-      <c r="K177" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L177" s="62">
+      <c r="H177" s="62">
+        <v>0</v>
+      </c>
+      <c r="I177" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J177" s="59">
+        <v>0</v>
+      </c>
+      <c r="K177" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L177" s="63">
         <v>0</v>
       </c>
       <c r="M177" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N177" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O177" s="60"/>
-      <c r="P177" s="60"/>
-      <c r="Q177" s="60"/>
-      <c r="R177" s="60"/>
-      <c r="S177" s="56"/>
-      <c r="T177" s="56"/>
+      <c r="N177" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O177" s="51"/>
+      <c r="P177" s="51"/>
+      <c r="Q177" s="51"/>
+      <c r="R177" s="51"/>
+      <c r="S177" s="52"/>
+      <c r="T177" s="52"/>
     </row>
     <row r="178" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A178" s="50">
-        <v>10260012</v>
-      </c>
-      <c r="B178" s="51">
-        <v>102600</v>
-      </c>
-      <c r="C178" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="D178" s="53">
-        <v>102600001</v>
-      </c>
-      <c r="E178" s="54">
+      <c r="A178" s="53">
+        <v>10150012</v>
+      </c>
+      <c r="B178" s="54">
+        <v>101500</v>
+      </c>
+      <c r="C178" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D178" s="56">
+        <v>101500001</v>
+      </c>
+      <c r="E178" s="57">
         <v>13</v>
       </c>
       <c r="F178" s="23" t="s">
@@ -10748,48 +10748,48 @@
       <c r="G178" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="H178" s="61">
-        <v>0</v>
-      </c>
-      <c r="I178" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J178" s="57">
-        <v>0</v>
-      </c>
-      <c r="K178" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L178" s="62">
+      <c r="H178" s="62">
+        <v>0</v>
+      </c>
+      <c r="I178" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J178" s="59">
+        <v>0</v>
+      </c>
+      <c r="K178" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L178" s="63">
         <v>0</v>
       </c>
       <c r="M178" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N178" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O178" s="60"/>
-      <c r="P178" s="60"/>
-      <c r="Q178" s="60"/>
-      <c r="R178" s="60"/>
-      <c r="S178" s="56"/>
-      <c r="T178" s="56"/>
+      <c r="N178" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O178" s="51"/>
+      <c r="P178" s="51"/>
+      <c r="Q178" s="51"/>
+      <c r="R178" s="51"/>
+      <c r="S178" s="52"/>
+      <c r="T178" s="52"/>
     </row>
     <row r="179" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A179" s="50">
-        <v>10500010</v>
-      </c>
-      <c r="B179" s="51">
-        <v>105000</v>
-      </c>
-      <c r="C179" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="D179" s="53">
-        <v>105000001</v>
-      </c>
-      <c r="E179" s="54">
+      <c r="A179" s="53">
+        <v>10260010</v>
+      </c>
+      <c r="B179" s="54">
+        <v>102600</v>
+      </c>
+      <c r="C179" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="D179" s="56">
+        <v>102600001</v>
+      </c>
+      <c r="E179" s="57">
         <v>11</v>
       </c>
       <c r="F179" s="23" t="s">
@@ -10798,48 +10798,48 @@
       <c r="G179" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H179" s="61">
-        <v>0</v>
-      </c>
-      <c r="I179" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J179" s="57">
-        <v>0</v>
-      </c>
-      <c r="K179" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L179" s="62">
+      <c r="H179" s="62">
+        <v>0</v>
+      </c>
+      <c r="I179" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J179" s="59">
+        <v>0</v>
+      </c>
+      <c r="K179" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L179" s="63">
         <v>0</v>
       </c>
       <c r="M179" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N179" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O179" s="60"/>
-      <c r="P179" s="60"/>
-      <c r="Q179" s="60"/>
-      <c r="R179" s="60"/>
-      <c r="S179" s="56"/>
-      <c r="T179" s="56"/>
+      <c r="N179" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O179" s="51"/>
+      <c r="P179" s="51"/>
+      <c r="Q179" s="51"/>
+      <c r="R179" s="51"/>
+      <c r="S179" s="52"/>
+      <c r="T179" s="52"/>
     </row>
     <row r="180" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A180" s="50">
-        <v>10500011</v>
-      </c>
-      <c r="B180" s="51">
-        <v>105000</v>
-      </c>
-      <c r="C180" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="D180" s="53">
-        <v>105000001</v>
-      </c>
-      <c r="E180" s="54">
+      <c r="A180" s="53">
+        <v>10260011</v>
+      </c>
+      <c r="B180" s="54">
+        <v>102600</v>
+      </c>
+      <c r="C180" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="D180" s="56">
+        <v>102600001</v>
+      </c>
+      <c r="E180" s="57">
         <v>12</v>
       </c>
       <c r="F180" s="23" t="s">
@@ -10848,48 +10848,48 @@
       <c r="G180" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H180" s="61">
-        <v>0</v>
-      </c>
-      <c r="I180" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J180" s="57">
-        <v>0</v>
-      </c>
-      <c r="K180" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L180" s="62">
+      <c r="H180" s="62">
+        <v>0</v>
+      </c>
+      <c r="I180" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J180" s="59">
+        <v>0</v>
+      </c>
+      <c r="K180" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L180" s="63">
         <v>0</v>
       </c>
       <c r="M180" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N180" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O180" s="60"/>
-      <c r="P180" s="60"/>
-      <c r="Q180" s="60"/>
-      <c r="R180" s="60"/>
-      <c r="S180" s="56"/>
-      <c r="T180" s="56"/>
+      <c r="N180" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O180" s="51"/>
+      <c r="P180" s="51"/>
+      <c r="Q180" s="51"/>
+      <c r="R180" s="51"/>
+      <c r="S180" s="52"/>
+      <c r="T180" s="52"/>
     </row>
     <row r="181" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A181" s="50">
-        <v>10500012</v>
-      </c>
-      <c r="B181" s="51">
-        <v>105000</v>
-      </c>
-      <c r="C181" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="D181" s="53">
-        <v>105000001</v>
-      </c>
-      <c r="E181" s="54">
+      <c r="A181" s="53">
+        <v>10260012</v>
+      </c>
+      <c r="B181" s="54">
+        <v>102600</v>
+      </c>
+      <c r="C181" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="D181" s="56">
+        <v>102600001</v>
+      </c>
+      <c r="E181" s="57">
         <v>13</v>
       </c>
       <c r="F181" s="23" t="s">
@@ -10898,489 +10898,507 @@
       <c r="G181" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="H181" s="61">
-        <v>0</v>
-      </c>
-      <c r="I181" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J181" s="57">
-        <v>0</v>
-      </c>
-      <c r="K181" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L181" s="62">
+      <c r="H181" s="62">
+        <v>0</v>
+      </c>
+      <c r="I181" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J181" s="59">
+        <v>0</v>
+      </c>
+      <c r="K181" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L181" s="63">
         <v>0</v>
       </c>
       <c r="M181" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N181" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O181" s="60"/>
-      <c r="P181" s="60"/>
-      <c r="Q181" s="60"/>
-      <c r="R181" s="60"/>
-      <c r="S181" s="56"/>
-      <c r="T181" s="56"/>
+      <c r="N181" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O181" s="51"/>
+      <c r="P181" s="51"/>
+      <c r="Q181" s="51"/>
+      <c r="R181" s="51"/>
+      <c r="S181" s="52"/>
+      <c r="T181" s="52"/>
     </row>
     <row r="182" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A182" s="50">
-        <v>10510010</v>
-      </c>
-      <c r="B182" s="51">
-        <v>105100</v>
-      </c>
-      <c r="C182" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="D182" s="53">
-        <v>105100001</v>
-      </c>
-      <c r="E182" s="54">
+      <c r="A182" s="53">
+        <v>10500010</v>
+      </c>
+      <c r="B182" s="54">
+        <v>105000</v>
+      </c>
+      <c r="C182" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D182" s="56">
+        <v>105000001</v>
+      </c>
+      <c r="E182" s="57">
         <v>11</v>
       </c>
       <c r="F182" s="23" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G182" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="H182" s="55">
-        <v>0</v>
-      </c>
-      <c r="I182" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J182" s="57">
-        <v>0</v>
-      </c>
-      <c r="K182" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L182" s="62">
+        <v>51</v>
+      </c>
+      <c r="H182" s="62">
+        <v>0</v>
+      </c>
+      <c r="I182" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J182" s="59">
+        <v>0</v>
+      </c>
+      <c r="K182" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L182" s="63">
         <v>0</v>
       </c>
       <c r="M182" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N182" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O182" s="60"/>
-      <c r="P182" s="60"/>
-      <c r="Q182" s="60"/>
-      <c r="R182" s="60"/>
-      <c r="S182" s="56"/>
-      <c r="T182" s="56"/>
+      <c r="N182" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O182" s="51"/>
+      <c r="P182" s="51"/>
+      <c r="Q182" s="51"/>
+      <c r="R182" s="51"/>
+      <c r="S182" s="52"/>
+      <c r="T182" s="52"/>
     </row>
     <row r="183" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A183" s="50">
-        <v>10510011</v>
-      </c>
-      <c r="B183" s="51">
-        <v>105100</v>
-      </c>
-      <c r="C183" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="D183" s="53">
-        <v>105100001</v>
-      </c>
-      <c r="E183" s="54">
+      <c r="A183" s="53">
+        <v>10500011</v>
+      </c>
+      <c r="B183" s="54">
+        <v>105000</v>
+      </c>
+      <c r="C183" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D183" s="56">
+        <v>105000001</v>
+      </c>
+      <c r="E183" s="57">
         <v>12</v>
       </c>
       <c r="F183" s="23" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G183" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H183" s="55">
-        <v>0</v>
-      </c>
-      <c r="I183" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J183" s="57">
-        <v>0</v>
-      </c>
-      <c r="K183" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L183" s="62">
+        <v>53</v>
+      </c>
+      <c r="H183" s="62">
+        <v>0</v>
+      </c>
+      <c r="I183" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J183" s="59">
+        <v>0</v>
+      </c>
+      <c r="K183" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L183" s="63">
         <v>0</v>
       </c>
       <c r="M183" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="N183" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O183" s="60"/>
-      <c r="P183" s="60"/>
-      <c r="Q183" s="60"/>
-      <c r="R183" s="60"/>
-      <c r="S183" s="56"/>
-      <c r="T183" s="56"/>
+      <c r="N183" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O183" s="51"/>
+      <c r="P183" s="51"/>
+      <c r="Q183" s="51"/>
+      <c r="R183" s="51"/>
+      <c r="S183" s="52"/>
+      <c r="T183" s="52"/>
     </row>
     <row r="184" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A184" s="50">
-        <v>10510012</v>
-      </c>
-      <c r="B184" s="51">
-        <v>105100</v>
-      </c>
-      <c r="C184" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="D184" s="53">
-        <v>105100001</v>
-      </c>
-      <c r="E184" s="54">
+      <c r="A184" s="53">
+        <v>10500012</v>
+      </c>
+      <c r="B184" s="54">
+        <v>105000</v>
+      </c>
+      <c r="C184" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D184" s="56">
+        <v>105000001</v>
+      </c>
+      <c r="E184" s="57">
         <v>13</v>
       </c>
       <c r="F184" s="23" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G184" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="H184" s="61">
-        <v>0</v>
-      </c>
-      <c r="I184" s="56">
-        <v>9500</v>
-      </c>
-      <c r="J184" s="57">
-        <v>0</v>
-      </c>
-      <c r="K184" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L184" s="62">
+        <v>55</v>
+      </c>
+      <c r="H184" s="62">
+        <v>0</v>
+      </c>
+      <c r="I184" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J184" s="59">
+        <v>0</v>
+      </c>
+      <c r="K184" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L184" s="63">
         <v>0</v>
       </c>
       <c r="M184" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="N184" s="59" t="s">
+      <c r="N184" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O184" s="51"/>
+      <c r="P184" s="51"/>
+      <c r="Q184" s="51"/>
+      <c r="R184" s="51"/>
+      <c r="S184" s="52"/>
+      <c r="T184" s="52"/>
+    </row>
+    <row r="185" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A185" s="53">
+        <v>10510010</v>
+      </c>
+      <c r="B185" s="54">
+        <v>105100</v>
+      </c>
+      <c r="C185" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="D185" s="56">
+        <v>105100001</v>
+      </c>
+      <c r="E185" s="57">
+        <v>11</v>
+      </c>
+      <c r="F185" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="G185" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H185" s="58">
+        <v>0</v>
+      </c>
+      <c r="I185" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J185" s="59">
+        <v>0</v>
+      </c>
+      <c r="K185" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L185" s="63">
+        <v>0</v>
+      </c>
+      <c r="M185" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N185" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O185" s="51"/>
+      <c r="P185" s="51"/>
+      <c r="Q185" s="51"/>
+      <c r="R185" s="51"/>
+      <c r="S185" s="52"/>
+      <c r="T185" s="52"/>
+    </row>
+    <row r="186" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A186" s="53">
+        <v>10510011</v>
+      </c>
+      <c r="B186" s="54">
+        <v>105100</v>
+      </c>
+      <c r="C186" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="D186" s="56">
+        <v>105100001</v>
+      </c>
+      <c r="E186" s="57">
+        <v>12</v>
+      </c>
+      <c r="F186" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G186" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="H186" s="58">
+        <v>0</v>
+      </c>
+      <c r="I186" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J186" s="59">
+        <v>0</v>
+      </c>
+      <c r="K186" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L186" s="63">
+        <v>0</v>
+      </c>
+      <c r="M186" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="N186" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="O184" s="60"/>
-      <c r="P184" s="60"/>
-      <c r="Q184" s="60"/>
-      <c r="R184" s="60"/>
-      <c r="S184" s="56"/>
-      <c r="T184" s="56"/>
-    </row>
-    <row r="185" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A185" s="50">
+      <c r="O186" s="51"/>
+      <c r="P186" s="51"/>
+      <c r="Q186" s="51"/>
+      <c r="R186" s="51"/>
+      <c r="S186" s="52"/>
+      <c r="T186" s="52"/>
+    </row>
+    <row r="187" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A187" s="53">
+        <v>10510012</v>
+      </c>
+      <c r="B187" s="54">
+        <v>105100</v>
+      </c>
+      <c r="C187" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="D187" s="56">
+        <v>105100001</v>
+      </c>
+      <c r="E187" s="57">
+        <v>13</v>
+      </c>
+      <c r="F187" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="G187" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="H187" s="62">
+        <v>0</v>
+      </c>
+      <c r="I187" s="52">
+        <v>9500</v>
+      </c>
+      <c r="J187" s="59">
+        <v>0</v>
+      </c>
+      <c r="K187" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L187" s="63">
+        <v>0</v>
+      </c>
+      <c r="M187" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="N187" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="O187" s="51"/>
+      <c r="P187" s="51"/>
+      <c r="Q187" s="51"/>
+      <c r="R187" s="51"/>
+      <c r="S187" s="52"/>
+      <c r="T187" s="52"/>
+    </row>
+    <row r="188" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A188" s="53">
         <v>10540011</v>
       </c>
-      <c r="B185" s="51">
+      <c r="B188" s="54">
         <v>105400</v>
       </c>
-      <c r="C185" s="52" t="s">
+      <c r="C188" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D188" s="56">
+        <v>105400001</v>
+      </c>
+      <c r="E188" s="57">
+        <v>11</v>
+      </c>
+      <c r="F188" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G188" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="H188" s="62">
+        <v>0</v>
+      </c>
+      <c r="I188" s="52">
+        <v>9600</v>
+      </c>
+      <c r="J188" s="59">
+        <v>0</v>
+      </c>
+      <c r="K188" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L188" s="63">
+        <v>0</v>
+      </c>
+      <c r="M188" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="N188" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="O188" s="51"/>
+      <c r="P188" s="51"/>
+      <c r="Q188" s="51"/>
+      <c r="R188" s="51"/>
+      <c r="S188" s="52"/>
+      <c r="T188" s="52"/>
+    </row>
+    <row r="189" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A189" s="53">
+        <v>10540012</v>
+      </c>
+      <c r="B189" s="54">
+        <v>105400</v>
+      </c>
+      <c r="C189" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D189" s="56">
+        <v>105400001</v>
+      </c>
+      <c r="E189" s="57">
+        <v>12</v>
+      </c>
+      <c r="F189" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="G189" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="H189" s="62">
+        <v>0</v>
+      </c>
+      <c r="I189" s="52">
+        <v>9600</v>
+      </c>
+      <c r="J189" s="59">
+        <v>0</v>
+      </c>
+      <c r="K189" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L189" s="63">
+        <v>0</v>
+      </c>
+      <c r="M189" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="N189" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="O189" s="51"/>
+      <c r="P189" s="51"/>
+      <c r="Q189" s="51"/>
+      <c r="R189" s="51"/>
+      <c r="S189" s="52"/>
+      <c r="T189" s="52"/>
+    </row>
+    <row r="190" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A190" s="53">
+        <v>10540013</v>
+      </c>
+      <c r="B190" s="54">
+        <v>105400</v>
+      </c>
+      <c r="C190" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D190" s="56">
+        <v>105400001</v>
+      </c>
+      <c r="E190" s="57">
+        <v>13</v>
+      </c>
+      <c r="F190" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="G190" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="H190" s="62">
+        <v>0</v>
+      </c>
+      <c r="I190" s="52">
+        <v>9600</v>
+      </c>
+      <c r="J190" s="59">
+        <v>0</v>
+      </c>
+      <c r="K190" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L190" s="63">
+        <v>0</v>
+      </c>
+      <c r="M190" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="N190" s="61" t="s">
         <v>117</v>
       </c>
-      <c r="D185" s="53">
-        <v>105400001</v>
-      </c>
-      <c r="E185" s="54">
-        <v>11</v>
-      </c>
-      <c r="F185" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="G185" s="65" t="s">
-        <v>51</v>
-      </c>
-      <c r="H185" s="61">
-        <v>0</v>
-      </c>
-      <c r="I185" s="56">
-        <v>9600</v>
-      </c>
-      <c r="J185" s="57">
-        <v>0</v>
-      </c>
-      <c r="K185" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L185" s="62">
-        <v>0</v>
-      </c>
-      <c r="M185" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="N185" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="O185" s="60"/>
-      <c r="P185" s="60"/>
-      <c r="Q185" s="60"/>
-      <c r="R185" s="60"/>
-      <c r="S185" s="56"/>
-      <c r="T185" s="56"/>
-    </row>
-    <row r="186" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A186" s="50">
-        <v>10540012</v>
-      </c>
-      <c r="B186" s="51">
-        <v>105400</v>
-      </c>
-      <c r="C186" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="D186" s="53">
-        <v>105400001</v>
-      </c>
-      <c r="E186" s="54">
-        <v>12</v>
-      </c>
-      <c r="F186" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="G186" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="H186" s="61">
-        <v>0</v>
-      </c>
-      <c r="I186" s="56">
-        <v>9600</v>
-      </c>
-      <c r="J186" s="57">
-        <v>0</v>
-      </c>
-      <c r="K186" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L186" s="62">
-        <v>0</v>
-      </c>
-      <c r="M186" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N186" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="O186" s="60"/>
-      <c r="P186" s="60"/>
-      <c r="Q186" s="60"/>
-      <c r="R186" s="60"/>
-      <c r="S186" s="56"/>
-      <c r="T186" s="56"/>
-    </row>
-    <row r="187" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A187" s="50">
-        <v>10540013</v>
-      </c>
-      <c r="B187" s="51">
-        <v>105400</v>
-      </c>
-      <c r="C187" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="D187" s="53">
-        <v>105400001</v>
-      </c>
-      <c r="E187" s="54">
-        <v>13</v>
-      </c>
-      <c r="F187" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="G187" s="65" t="s">
-        <v>55</v>
-      </c>
-      <c r="H187" s="61">
-        <v>0</v>
-      </c>
-      <c r="I187" s="56">
-        <v>9600</v>
-      </c>
-      <c r="J187" s="57">
-        <v>0</v>
-      </c>
-      <c r="K187" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L187" s="62">
-        <v>0</v>
-      </c>
-      <c r="M187" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="N187" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="O187" s="60"/>
-      <c r="P187" s="60"/>
-      <c r="Q187" s="60"/>
-      <c r="R187" s="60"/>
-      <c r="S187" s="56"/>
-      <c r="T187" s="56"/>
-    </row>
-    <row r="188" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A188" s="66">
+      <c r="O190" s="51"/>
+      <c r="P190" s="51"/>
+      <c r="Q190" s="51"/>
+      <c r="R190" s="51"/>
+      <c r="S190" s="52"/>
+      <c r="T190" s="52"/>
+    </row>
+    <row r="191" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A191" s="66">
         <v>10080010</v>
       </c>
-      <c r="B188" s="66">
+      <c r="B191" s="66">
         <v>100800</v>
       </c>
-      <c r="C188" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D188" s="67">
+      <c r="C191" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D191" s="37">
         <v>100800001</v>
-      </c>
-      <c r="E188" s="12">
-        <v>11</v>
-      </c>
-      <c r="F188" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="G188" s="65" t="s">
-        <v>51</v>
-      </c>
-      <c r="H188" s="68">
-        <v>0</v>
-      </c>
-      <c r="I188" s="40">
-        <v>9600</v>
-      </c>
-      <c r="J188" s="40">
-        <v>0</v>
-      </c>
-      <c r="K188" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L188" s="38">
-        <v>0</v>
-      </c>
-      <c r="M188" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="N188" s="39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="189" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A189" s="66">
-        <v>10080011</v>
-      </c>
-      <c r="B189" s="66">
-        <v>100800</v>
-      </c>
-      <c r="C189" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D189" s="67">
-        <v>100800001</v>
-      </c>
-      <c r="E189" s="12">
-        <v>12</v>
-      </c>
-      <c r="F189" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="G189" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="H189" s="68">
-        <v>0</v>
-      </c>
-      <c r="I189" s="40">
-        <v>9600</v>
-      </c>
-      <c r="J189" s="40">
-        <v>0</v>
-      </c>
-      <c r="K189" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L189" s="38">
-        <v>0</v>
-      </c>
-      <c r="M189" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N189" s="39" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="190" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A190" s="66">
-        <v>10080012</v>
-      </c>
-      <c r="B190" s="66">
-        <v>100800</v>
-      </c>
-      <c r="C190" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D190" s="67">
-        <v>100800001</v>
-      </c>
-      <c r="E190" s="12">
-        <v>13</v>
-      </c>
-      <c r="F190" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="G190" s="65" t="s">
-        <v>55</v>
-      </c>
-      <c r="H190" s="68">
-        <v>0</v>
-      </c>
-      <c r="I190" s="40">
-        <v>9600</v>
-      </c>
-      <c r="J190" s="40">
-        <v>0</v>
-      </c>
-      <c r="K190" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L190" s="38">
-        <v>0</v>
-      </c>
-      <c r="M190" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="N190" s="39" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="191" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A191" s="34">
-        <v>10530010</v>
-      </c>
-      <c r="B191" s="35">
-        <v>105300</v>
-      </c>
-      <c r="C191" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="D191" s="67">
-        <v>105300001</v>
       </c>
       <c r="E191" s="12">
         <v>11</v>
       </c>
       <c r="F191" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="G191" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="G191" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="H191" s="68">
+      <c r="H191" s="67">
         <v>0</v>
       </c>
       <c r="I191" s="40">
@@ -11396,35 +11414,35 @@
         <v>0</v>
       </c>
       <c r="M191" s="40" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N191" s="39" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="192" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A192" s="34">
-        <v>10530011</v>
-      </c>
-      <c r="B192" s="35">
-        <v>105300</v>
-      </c>
-      <c r="C192" s="36" t="s">
+      <c r="A192" s="66">
+        <v>10080011</v>
+      </c>
+      <c r="B192" s="66">
+        <v>100800</v>
+      </c>
+      <c r="C192" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="D192" s="67">
-        <v>105300001</v>
+      <c r="D192" s="37">
+        <v>100800001</v>
       </c>
       <c r="E192" s="12">
         <v>12</v>
       </c>
       <c r="F192" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="G192" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="G192" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="H192" s="68">
+      <c r="H192" s="67">
         <v>0</v>
       </c>
       <c r="I192" s="40">
@@ -11440,35 +11458,35 @@
         <v>0</v>
       </c>
       <c r="M192" s="40" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N192" s="39" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="193" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A193" s="34">
-        <v>10530012</v>
-      </c>
-      <c r="B193" s="35">
-        <v>105300</v>
-      </c>
-      <c r="C193" s="36" t="s">
+      <c r="A193" s="66">
+        <v>10080012</v>
+      </c>
+      <c r="B193" s="66">
+        <v>100800</v>
+      </c>
+      <c r="C193" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="D193" s="67">
-        <v>105300001</v>
+      <c r="D193" s="37">
+        <v>100800001</v>
       </c>
       <c r="E193" s="12">
         <v>13</v>
       </c>
       <c r="F193" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="G193" s="65" t="s">
+        <v>123</v>
+      </c>
+      <c r="G193" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="H193" s="68">
+      <c r="H193" s="67">
         <v>0</v>
       </c>
       <c r="I193" s="40">
@@ -11484,35 +11502,35 @@
         <v>0</v>
       </c>
       <c r="M193" s="40" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N193" s="39" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="194" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A194" s="66">
-        <v>10570010</v>
-      </c>
-      <c r="B194" s="66">
-        <v>105700</v>
-      </c>
-      <c r="C194" t="s">
+      <c r="A194" s="34">
+        <v>10530010</v>
+      </c>
+      <c r="B194" s="35">
+        <v>105300</v>
+      </c>
+      <c r="C194" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="D194" s="67">
-        <v>105700001</v>
+      <c r="D194" s="37">
+        <v>105300001</v>
       </c>
       <c r="E194" s="12">
         <v>11</v>
       </c>
       <c r="F194" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="G194" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="G194" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="H194" s="68">
+      <c r="H194" s="67">
         <v>0</v>
       </c>
       <c r="I194" s="40">
@@ -11528,35 +11546,35 @@
         <v>0</v>
       </c>
       <c r="M194" s="40" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N194" s="39" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="195" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A195" s="66">
-        <v>10570011</v>
-      </c>
-      <c r="B195" s="66">
-        <v>105700</v>
-      </c>
-      <c r="C195" t="s">
+      <c r="A195" s="34">
+        <v>10530011</v>
+      </c>
+      <c r="B195" s="35">
+        <v>105300</v>
+      </c>
+      <c r="C195" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="D195" s="67">
-        <v>105700001</v>
+      <c r="D195" s="37">
+        <v>105300001</v>
       </c>
       <c r="E195" s="12">
         <v>12</v>
       </c>
       <c r="F195" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="G195" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="G195" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="H195" s="68">
+      <c r="H195" s="67">
         <v>0</v>
       </c>
       <c r="I195" s="40">
@@ -11572,35 +11590,35 @@
         <v>0</v>
       </c>
       <c r="M195" s="40" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N195" s="39" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="196" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A196" s="66">
-        <v>10570012</v>
-      </c>
-      <c r="B196" s="66">
-        <v>105700</v>
-      </c>
-      <c r="C196" t="s">
+      <c r="A196" s="34">
+        <v>10530012</v>
+      </c>
+      <c r="B196" s="35">
+        <v>105300</v>
+      </c>
+      <c r="C196" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="D196" s="67">
-        <v>105700001</v>
+      <c r="D196" s="37">
+        <v>105300001</v>
       </c>
       <c r="E196" s="12">
         <v>13</v>
       </c>
       <c r="F196" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="G196" s="65" t="s">
+        <v>123</v>
+      </c>
+      <c r="G196" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="H196" s="68">
+      <c r="H196" s="67">
         <v>0</v>
       </c>
       <c r="I196" s="40">
@@ -11616,35 +11634,35 @@
         <v>0</v>
       </c>
       <c r="M196" s="40" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N196" s="39" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="197" s="7" customFormat="1" ht="16.5" spans="1:14">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="197" customFormat="1" ht="16.5" spans="1:14">
       <c r="A197" s="66">
-        <v>10580010</v>
+        <v>10570010</v>
       </c>
       <c r="B197" s="66">
-        <v>105800</v>
-      </c>
-      <c r="C197" s="7" t="s">
+        <v>105700</v>
+      </c>
+      <c r="C197" t="s">
         <v>127</v>
       </c>
-      <c r="D197" s="69">
-        <v>105800001</v>
+      <c r="D197" s="37">
+        <v>105700001</v>
       </c>
       <c r="E197" s="12">
         <v>11</v>
       </c>
       <c r="F197" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="G197" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="G197" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="H197" s="68">
+      <c r="H197" s="67">
         <v>0</v>
       </c>
       <c r="I197" s="40">
@@ -11660,35 +11678,35 @@
         <v>0</v>
       </c>
       <c r="M197" s="40" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N197" s="39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="198" s="7" customFormat="1" ht="16.5" spans="1:14">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="198" customFormat="1" ht="16.5" spans="1:14">
       <c r="A198" s="66">
-        <v>10580011</v>
+        <v>10570011</v>
       </c>
       <c r="B198" s="66">
-        <v>105800</v>
-      </c>
-      <c r="C198" s="7" t="s">
+        <v>105700</v>
+      </c>
+      <c r="C198" t="s">
         <v>127</v>
       </c>
-      <c r="D198" s="69">
-        <v>105800001</v>
+      <c r="D198" s="37">
+        <v>105700001</v>
       </c>
       <c r="E198" s="12">
         <v>12</v>
       </c>
       <c r="F198" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="G198" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="G198" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="H198" s="68">
+      <c r="H198" s="67">
         <v>0</v>
       </c>
       <c r="I198" s="40">
@@ -11704,35 +11722,35 @@
         <v>0</v>
       </c>
       <c r="M198" s="40" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N198" s="39" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="199" s="7" customFormat="1" ht="16.5" spans="1:14">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="199" customFormat="1" ht="16.5" spans="1:14">
       <c r="A199" s="66">
-        <v>10580012</v>
+        <v>10570012</v>
       </c>
       <c r="B199" s="66">
-        <v>105800</v>
-      </c>
-      <c r="C199" s="7" t="s">
+        <v>105700</v>
+      </c>
+      <c r="C199" t="s">
         <v>127</v>
       </c>
-      <c r="D199" s="69">
-        <v>105800001</v>
+      <c r="D199" s="37">
+        <v>105700001</v>
       </c>
       <c r="E199" s="12">
         <v>13</v>
       </c>
       <c r="F199" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="G199" s="65" t="s">
+        <v>123</v>
+      </c>
+      <c r="G199" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="H199" s="68">
+      <c r="H199" s="67">
         <v>0</v>
       </c>
       <c r="I199" s="40">
@@ -11748,10 +11766,274 @@
         <v>0</v>
       </c>
       <c r="M199" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="N199" s="39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="200" s="7" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A200" s="66">
+        <v>10580010</v>
+      </c>
+      <c r="B200" s="66">
+        <v>105800</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D200" s="68">
+        <v>105800001</v>
+      </c>
+      <c r="E200" s="12">
+        <v>11</v>
+      </c>
+      <c r="F200" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G200" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="H200" s="67">
+        <v>0</v>
+      </c>
+      <c r="I200" s="40">
+        <v>9600</v>
+      </c>
+      <c r="J200" s="40">
+        <v>0</v>
+      </c>
+      <c r="K200" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L200" s="38">
+        <v>0</v>
+      </c>
+      <c r="M200" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="N200" s="39" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="201" s="7" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A201" s="66">
+        <v>10580011</v>
+      </c>
+      <c r="B201" s="66">
+        <v>105800</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D201" s="68">
+        <v>105800001</v>
+      </c>
+      <c r="E201" s="12">
+        <v>12</v>
+      </c>
+      <c r="F201" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="G201" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="H201" s="67">
+        <v>0</v>
+      </c>
+      <c r="I201" s="40">
+        <v>9600</v>
+      </c>
+      <c r="J201" s="40">
+        <v>0</v>
+      </c>
+      <c r="K201" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L201" s="38">
+        <v>0</v>
+      </c>
+      <c r="M201" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="N201" s="39" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="202" s="7" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A202" s="66">
+        <v>10580012</v>
+      </c>
+      <c r="B202" s="66">
+        <v>105800</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D202" s="68">
+        <v>105800001</v>
+      </c>
+      <c r="E202" s="12">
+        <v>13</v>
+      </c>
+      <c r="F202" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="N199" s="39" t="s">
+      <c r="G202" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="H202" s="67">
+        <v>0</v>
+      </c>
+      <c r="I202" s="40">
+        <v>9600</v>
+      </c>
+      <c r="J202" s="40">
+        <v>0</v>
+      </c>
+      <c r="K202" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L202" s="38">
+        <v>0</v>
+      </c>
+      <c r="M202" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="N202" s="39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="203" s="7" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A203" s="66">
+        <v>10550010</v>
+      </c>
+      <c r="B203" s="66">
+        <v>105500</v>
+      </c>
+      <c r="C203" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="D203" s="68">
+        <v>105500001</v>
+      </c>
+      <c r="E203" s="12">
+        <v>11</v>
+      </c>
+      <c r="F203" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="G203" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="H203" s="67">
+        <v>0</v>
+      </c>
+      <c r="I203" s="40">
+        <v>9600</v>
+      </c>
+      <c r="J203" s="40">
+        <v>0</v>
+      </c>
+      <c r="K203" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L203" s="38">
+        <v>0</v>
+      </c>
+      <c r="M203" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="N203" s="39" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="204" s="7" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A204" s="66">
+        <v>10550011</v>
+      </c>
+      <c r="B204" s="66">
+        <v>105500</v>
+      </c>
+      <c r="C204" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="D204" s="68">
+        <v>105500001</v>
+      </c>
+      <c r="E204" s="12">
+        <v>12</v>
+      </c>
+      <c r="F204" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G204" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="H204" s="67">
+        <v>0</v>
+      </c>
+      <c r="I204" s="40">
+        <v>9600</v>
+      </c>
+      <c r="J204" s="40">
+        <v>0</v>
+      </c>
+      <c r="K204" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L204" s="38">
+        <v>0</v>
+      </c>
+      <c r="M204" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="N204" s="39" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="205" s="7" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A205" s="66">
+        <v>10550012</v>
+      </c>
+      <c r="B205" s="66">
+        <v>105500</v>
+      </c>
+      <c r="C205" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="D205" s="68">
+        <v>105500001</v>
+      </c>
+      <c r="E205" s="12">
+        <v>13</v>
+      </c>
+      <c r="F205" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="G205" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="H205" s="67">
+        <v>0</v>
+      </c>
+      <c r="I205" s="40">
+        <v>9600</v>
+      </c>
+      <c r="J205" s="40">
+        <v>0</v>
+      </c>
+      <c r="K205" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L205" s="38">
+        <v>0</v>
+      </c>
+      <c r="M205" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="N205" s="39" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_19D513439AD080CD3C5919954F9597FF7FCF347B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5A9B0B-24E1-4110-B04F-AB96CD7DD361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -603,8 +603,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -856,7 +856,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -874,10 +874,10 @@
     <xf numFmtId="49" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -886,7 +886,7 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -919,7 +919,7 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -949,7 +949,7 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -976,7 +976,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -988,7 +988,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1643,7 +1643,7 @@
         <v>44</v>
       </c>
       <c r="D8" s="25">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="E8" s="21">
         <v>1</v>
@@ -1693,7 +1693,7 @@
         <v>44</v>
       </c>
       <c r="D9" s="25">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="E9" s="21">
         <v>2</v>
@@ -1743,7 +1743,7 @@
         <v>44</v>
       </c>
       <c r="D10" s="25">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="E10" s="21">
         <v>3</v>
@@ -1793,7 +1793,7 @@
         <v>49</v>
       </c>
       <c r="D11" s="25">
-        <v>100100026</v>
+        <v>100700001</v>
       </c>
       <c r="E11" s="21">
         <v>1</v>
@@ -1843,7 +1843,7 @@
         <v>49</v>
       </c>
       <c r="D12" s="25">
-        <v>100100026</v>
+        <v>100700001</v>
       </c>
       <c r="E12" s="21">
         <v>2</v>
@@ -1893,7 +1893,7 @@
         <v>49</v>
       </c>
       <c r="D13" s="25">
-        <v>100100026</v>
+        <v>100700001</v>
       </c>
       <c r="E13" s="21">
         <v>3</v>
@@ -1943,7 +1943,7 @@
         <v>56</v>
       </c>
       <c r="D14" s="25">
-        <v>100100026</v>
+        <v>101200001</v>
       </c>
       <c r="E14" s="21">
         <v>1</v>
@@ -1993,7 +1993,7 @@
         <v>56</v>
       </c>
       <c r="D15" s="25">
-        <v>100100026</v>
+        <v>101200001</v>
       </c>
       <c r="E15" s="21">
         <v>2</v>
@@ -2043,7 +2043,7 @@
         <v>56</v>
       </c>
       <c r="D16" s="25">
-        <v>100100026</v>
+        <v>101200001</v>
       </c>
       <c r="E16" s="21">
         <v>3</v>
@@ -2093,7 +2093,7 @@
         <v>59</v>
       </c>
       <c r="D17" s="25">
-        <v>100100026</v>
+        <v>101400001</v>
       </c>
       <c r="E17" s="21">
         <v>1</v>
@@ -2143,7 +2143,7 @@
         <v>59</v>
       </c>
       <c r="D18" s="25">
-        <v>100100026</v>
+        <v>101400001</v>
       </c>
       <c r="E18" s="21">
         <v>2</v>
@@ -2193,7 +2193,7 @@
         <v>59</v>
       </c>
       <c r="D19" s="25">
-        <v>100100026</v>
+        <v>101400001</v>
       </c>
       <c r="E19" s="21">
         <v>3</v>
@@ -6593,7 +6593,7 @@
         <v>44</v>
       </c>
       <c r="D107" s="46">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="E107" s="47">
         <v>10</v>
@@ -6643,7 +6643,7 @@
         <v>44</v>
       </c>
       <c r="D108" s="46">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="E108" s="47">
         <v>11</v>
@@ -6693,7 +6693,7 @@
         <v>44</v>
       </c>
       <c r="D109" s="46">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="E109" s="47">
         <v>12</v>
@@ -6743,7 +6743,7 @@
         <v>49</v>
       </c>
       <c r="D110" s="46">
-        <v>100100026</v>
+        <v>100700001</v>
       </c>
       <c r="E110" s="47">
         <v>10</v>
@@ -6793,7 +6793,7 @@
         <v>49</v>
       </c>
       <c r="D111" s="46">
-        <v>100100026</v>
+        <v>100700001</v>
       </c>
       <c r="E111" s="47">
         <v>11</v>
@@ -6843,7 +6843,7 @@
         <v>49</v>
       </c>
       <c r="D112" s="46">
-        <v>100100026</v>
+        <v>100700001</v>
       </c>
       <c r="E112" s="47">
         <v>12</v>
@@ -6893,7 +6893,7 @@
         <v>56</v>
       </c>
       <c r="D113" s="55">
-        <v>101200026</v>
+        <v>101200001</v>
       </c>
       <c r="E113" s="47">
         <v>10</v>
@@ -6943,7 +6943,7 @@
         <v>56</v>
       </c>
       <c r="D114" s="55">
-        <v>101200026</v>
+        <v>101200001</v>
       </c>
       <c r="E114" s="47">
         <v>11</v>
@@ -6993,7 +6993,7 @@
         <v>56</v>
       </c>
       <c r="D115" s="55">
-        <v>101200026</v>
+        <v>101200001</v>
       </c>
       <c r="E115" s="47">
         <v>12</v>
@@ -7043,7 +7043,7 @@
         <v>59</v>
       </c>
       <c r="D116" s="46">
-        <v>100100026</v>
+        <v>101400001</v>
       </c>
       <c r="E116" s="47">
         <v>10</v>
@@ -7093,7 +7093,7 @@
         <v>59</v>
       </c>
       <c r="D117" s="46">
-        <v>100100026</v>
+        <v>101400001</v>
       </c>
       <c r="E117" s="47">
         <v>11</v>
@@ -7143,7 +7143,7 @@
         <v>59</v>
       </c>
       <c r="D118" s="46">
-        <v>100100026</v>
+        <v>101400001</v>
       </c>
       <c r="E118" s="47">
         <v>12</v>
@@ -11742,7 +11742,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="212" spans="1:14" customFormat="1" ht="16.5">
+    <row r="212" spans="1:14" ht="16.5">
       <c r="A212" s="56">
         <v>10480010</v>
       </c>
@@ -11786,7 +11786,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="213" spans="1:14" customFormat="1" ht="16.5">
+    <row r="213" spans="1:14" ht="16.5">
       <c r="A213" s="56">
         <v>10480011</v>
       </c>
@@ -11830,7 +11830,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="214" spans="1:14" customFormat="1" ht="16.5">
+    <row r="214" spans="1:14" ht="16.5">
       <c r="A214" s="56">
         <v>10480012</v>
       </c>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5A9B0B-24E1-4110-B04F-AB96CD7DD361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3067768C-9021-458C-A295-FD4761FB8694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1590" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -203,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="133">
   <si>
     <t>id</t>
   </si>
@@ -596,6 +596,13 @@
   </si>
   <si>
     <t>极速糖果1000</t>
+  </si>
+  <si>
+    <t>伽罗宝石2</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>伽罗宝石2</t>
   </si>
 </sst>
 </file>
@@ -606,7 +613,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -716,6 +723,41 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="13">
@@ -839,7 +881,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1008,6 +1050,48 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1305,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T217"/>
+  <dimension ref="A1:T223"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -6433,176 +6517,176 @@
       <c r="T103" s="43"/>
     </row>
     <row r="104" spans="1:20" s="4" customFormat="1" ht="16.5">
-      <c r="A104" s="44">
-        <v>10010010</v>
-      </c>
-      <c r="B104" s="44">
-        <v>100100</v>
-      </c>
-      <c r="C104" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="D104" s="46">
-        <v>100100026</v>
-      </c>
-      <c r="E104" s="47">
-        <v>10</v>
-      </c>
-      <c r="F104" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G104" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="H104" s="48">
-        <v>0</v>
-      </c>
-      <c r="I104" s="43">
-        <v>9500</v>
-      </c>
-      <c r="J104" s="49">
-        <v>0</v>
-      </c>
-      <c r="K104" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="L104" s="50">
-        <v>0</v>
-      </c>
-      <c r="M104" s="24" t="s">
+      <c r="A104" s="67">
+        <v>1055021</v>
+      </c>
+      <c r="B104" s="67">
+        <v>105502</v>
+      </c>
+      <c r="C104" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="D104" s="69">
+        <v>105502001</v>
+      </c>
+      <c r="E104" s="68">
+        <v>1</v>
+      </c>
+      <c r="F104" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="G104" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="H104" s="64">
+        <v>10000000</v>
+      </c>
+      <c r="I104" s="70">
+        <v>9500</v>
+      </c>
+      <c r="J104" s="65">
+        <v>5000000</v>
+      </c>
+      <c r="K104" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L104" s="66">
+        <v>100</v>
+      </c>
+      <c r="M104" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="N104" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="O104" s="42"/>
-      <c r="P104" s="42"/>
-      <c r="Q104" s="42"/>
-      <c r="R104" s="42"/>
-      <c r="S104" s="43"/>
-      <c r="T104" s="43"/>
+      <c r="N104" s="62">
+        <v>0</v>
+      </c>
+      <c r="O104" s="71"/>
+      <c r="P104" s="71"/>
+      <c r="Q104" s="71"/>
+      <c r="R104" s="71"/>
+      <c r="S104" s="72"/>
+      <c r="T104" s="72"/>
     </row>
     <row r="105" spans="1:20" s="4" customFormat="1" ht="16.5">
-      <c r="A105" s="44">
-        <v>10010011</v>
-      </c>
-      <c r="B105" s="44">
-        <v>100100</v>
-      </c>
-      <c r="C105" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="D105" s="46">
-        <v>100100026</v>
-      </c>
-      <c r="E105" s="47">
-        <v>11</v>
-      </c>
-      <c r="F105" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G105" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="H105" s="48">
-        <v>0</v>
-      </c>
-      <c r="I105" s="43">
-        <v>9500</v>
-      </c>
-      <c r="J105" s="49">
-        <v>0</v>
-      </c>
-      <c r="K105" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="L105" s="50">
-        <v>0</v>
-      </c>
-      <c r="M105" s="24" t="s">
+      <c r="A105" s="67">
+        <v>1055022</v>
+      </c>
+      <c r="B105" s="67">
+        <v>105502</v>
+      </c>
+      <c r="C105" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="D105" s="69">
+        <v>105502001</v>
+      </c>
+      <c r="E105" s="68">
+        <v>2</v>
+      </c>
+      <c r="F105" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="G105" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="H105" s="64">
+        <v>100000000</v>
+      </c>
+      <c r="I105" s="70">
+        <v>9500</v>
+      </c>
+      <c r="J105" s="65">
+        <v>50000000</v>
+      </c>
+      <c r="K105" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L105" s="66">
+        <v>100</v>
+      </c>
+      <c r="M105" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="N105" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="O105" s="42"/>
-      <c r="P105" s="42"/>
-      <c r="Q105" s="42"/>
-      <c r="R105" s="42"/>
-      <c r="S105" s="43"/>
-      <c r="T105" s="43"/>
+      <c r="N105" s="62">
+        <v>0</v>
+      </c>
+      <c r="O105" s="71"/>
+      <c r="P105" s="71"/>
+      <c r="Q105" s="71"/>
+      <c r="R105" s="71"/>
+      <c r="S105" s="72"/>
+      <c r="T105" s="72"/>
     </row>
     <row r="106" spans="1:20" s="4" customFormat="1" ht="16.5">
-      <c r="A106" s="44">
-        <v>10010012</v>
-      </c>
-      <c r="B106" s="44">
-        <v>100100</v>
-      </c>
-      <c r="C106" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="D106" s="46">
-        <v>100100026</v>
-      </c>
-      <c r="E106" s="47">
-        <v>12</v>
-      </c>
-      <c r="F106" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G106" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="H106" s="52">
-        <v>0</v>
-      </c>
-      <c r="I106" s="43">
-        <v>9500</v>
-      </c>
-      <c r="J106" s="49">
-        <v>0</v>
-      </c>
-      <c r="K106" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="L106" s="50">
-        <v>0</v>
-      </c>
-      <c r="M106" s="24" t="s">
+      <c r="A106" s="67">
+        <v>1055023</v>
+      </c>
+      <c r="B106" s="67">
+        <v>105502</v>
+      </c>
+      <c r="C106" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="D106" s="69">
+        <v>105502001</v>
+      </c>
+      <c r="E106" s="68">
+        <v>3</v>
+      </c>
+      <c r="F106" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="G106" s="63" t="s">
+        <v>78</v>
+      </c>
+      <c r="H106" s="64">
+        <v>1000000000</v>
+      </c>
+      <c r="I106" s="70">
+        <v>9500</v>
+      </c>
+      <c r="J106" s="65">
+        <v>500000000</v>
+      </c>
+      <c r="K106" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L106" s="66">
+        <v>100</v>
+      </c>
+      <c r="M106" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="N106" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="O106" s="42"/>
-      <c r="P106" s="42"/>
-      <c r="Q106" s="42"/>
-      <c r="R106" s="42"/>
-      <c r="S106" s="43"/>
-      <c r="T106" s="43"/>
+      <c r="N106" s="62">
+        <v>0</v>
+      </c>
+      <c r="O106" s="71"/>
+      <c r="P106" s="71"/>
+      <c r="Q106" s="71"/>
+      <c r="R106" s="71"/>
+      <c r="S106" s="72"/>
+      <c r="T106" s="72"/>
     </row>
     <row r="107" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A107" s="44">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B107" s="44">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C107" s="45" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D107" s="46">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E107" s="47">
         <v>10</v>
       </c>
       <c r="F107" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G107" s="23" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H107" s="48">
         <v>0</v>
@@ -6616,7 +6700,7 @@
       <c r="K107" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="L107" s="53">
+      <c r="L107" s="50">
         <v>0</v>
       </c>
       <c r="M107" s="24" t="s">
@@ -6634,25 +6718,25 @@
     </row>
     <row r="108" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A108" s="44">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B108" s="44">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C108" s="45" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D108" s="46">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E108" s="47">
         <v>11</v>
       </c>
       <c r="F108" s="22" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G108" s="23" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H108" s="48">
         <v>0</v>
@@ -6666,7 +6750,7 @@
       <c r="K108" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="L108" s="53">
+      <c r="L108" s="50">
         <v>0</v>
       </c>
       <c r="M108" s="24" t="s">
@@ -6684,25 +6768,25 @@
     </row>
     <row r="109" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A109" s="44">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B109" s="44">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C109" s="45" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D109" s="46">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E109" s="47">
         <v>12</v>
       </c>
       <c r="F109" s="22" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G109" s="23" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H109" s="52">
         <v>0</v>
@@ -6716,7 +6800,7 @@
       <c r="K109" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="L109" s="53">
+      <c r="L109" s="50">
         <v>0</v>
       </c>
       <c r="M109" s="24" t="s">
@@ -6734,25 +6818,25 @@
     </row>
     <row r="110" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A110" s="44">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B110" s="44">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C110" s="45" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D110" s="46">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E110" s="47">
         <v>10</v>
       </c>
       <c r="F110" s="22" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G110" s="23" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H110" s="48">
         <v>0</v>
@@ -6766,7 +6850,7 @@
       <c r="K110" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="L110" s="50">
+      <c r="L110" s="53">
         <v>0</v>
       </c>
       <c r="M110" s="24" t="s">
@@ -6784,25 +6868,25 @@
     </row>
     <row r="111" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A111" s="44">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B111" s="44">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C111" s="45" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D111" s="46">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E111" s="47">
         <v>11</v>
       </c>
       <c r="F111" s="22" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G111" s="23" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H111" s="48">
         <v>0</v>
@@ -6816,7 +6900,7 @@
       <c r="K111" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="L111" s="50">
+      <c r="L111" s="53">
         <v>0</v>
       </c>
       <c r="M111" s="24" t="s">
@@ -6834,25 +6918,25 @@
     </row>
     <row r="112" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A112" s="44">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B112" s="44">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C112" s="45" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D112" s="46">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E112" s="47">
         <v>12</v>
       </c>
       <c r="F112" s="22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G112" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H112" s="52">
         <v>0</v>
@@ -6866,7 +6950,7 @@
       <c r="K112" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="L112" s="50">
+      <c r="L112" s="53">
         <v>0</v>
       </c>
       <c r="M112" s="24" t="s">
@@ -6882,41 +6966,41 @@
       <c r="S112" s="43"/>
       <c r="T112" s="43"/>
     </row>
-    <row r="113" spans="1:20" s="5" customFormat="1" ht="16.5">
+    <row r="113" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A113" s="44">
-        <v>10120010</v>
-      </c>
-      <c r="B113" s="54">
-        <v>101200</v>
-      </c>
-      <c r="C113" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D113" s="55">
-        <v>101200001</v>
+        <v>10070010</v>
+      </c>
+      <c r="B113" s="44">
+        <v>100700</v>
+      </c>
+      <c r="C113" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="D113" s="46">
+        <v>100700001</v>
       </c>
       <c r="E113" s="47">
         <v>10</v>
       </c>
       <c r="F113" s="22" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G113" s="23" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H113" s="48">
         <v>0</v>
       </c>
-      <c r="I113" s="49">
+      <c r="I113" s="43">
         <v>9500</v>
       </c>
       <c r="J113" s="49">
         <v>0</v>
       </c>
-      <c r="K113" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="L113" s="53">
+      <c r="K113" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="L113" s="50">
         <v>0</v>
       </c>
       <c r="M113" s="24" t="s">
@@ -6925,48 +7009,48 @@
       <c r="N113" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="O113" s="51"/>
-      <c r="P113" s="51"/>
-      <c r="Q113" s="51"/>
-      <c r="R113" s="51"/>
-      <c r="S113" s="49"/>
-      <c r="T113" s="49"/>
-    </row>
-    <row r="114" spans="1:20" s="5" customFormat="1" ht="16.5">
+      <c r="O113" s="42"/>
+      <c r="P113" s="42"/>
+      <c r="Q113" s="42"/>
+      <c r="R113" s="42"/>
+      <c r="S113" s="43"/>
+      <c r="T113" s="43"/>
+    </row>
+    <row r="114" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A114" s="44">
-        <v>10120011</v>
-      </c>
-      <c r="B114" s="54">
-        <v>101200</v>
-      </c>
-      <c r="C114" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D114" s="55">
-        <v>101200001</v>
+        <v>10070011</v>
+      </c>
+      <c r="B114" s="44">
+        <v>100700</v>
+      </c>
+      <c r="C114" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="D114" s="46">
+        <v>100700001</v>
       </c>
       <c r="E114" s="47">
         <v>11</v>
       </c>
       <c r="F114" s="22" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G114" s="23" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H114" s="48">
         <v>0</v>
       </c>
-      <c r="I114" s="49">
+      <c r="I114" s="43">
         <v>9500</v>
       </c>
       <c r="J114" s="49">
         <v>0</v>
       </c>
-      <c r="K114" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="L114" s="53">
+      <c r="K114" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="L114" s="50">
         <v>0</v>
       </c>
       <c r="M114" s="24" t="s">
@@ -6975,48 +7059,48 @@
       <c r="N114" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="O114" s="51"/>
-      <c r="P114" s="51"/>
-      <c r="Q114" s="51"/>
-      <c r="R114" s="51"/>
-      <c r="S114" s="49"/>
-      <c r="T114" s="49"/>
-    </row>
-    <row r="115" spans="1:20" s="5" customFormat="1" ht="16.5">
+      <c r="O114" s="42"/>
+      <c r="P114" s="42"/>
+      <c r="Q114" s="42"/>
+      <c r="R114" s="42"/>
+      <c r="S114" s="43"/>
+      <c r="T114" s="43"/>
+    </row>
+    <row r="115" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A115" s="44">
-        <v>10120012</v>
-      </c>
-      <c r="B115" s="54">
-        <v>101200</v>
-      </c>
-      <c r="C115" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D115" s="55">
-        <v>101200001</v>
+        <v>10070012</v>
+      </c>
+      <c r="B115" s="44">
+        <v>100700</v>
+      </c>
+      <c r="C115" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="D115" s="46">
+        <v>100700001</v>
       </c>
       <c r="E115" s="47">
         <v>12</v>
       </c>
       <c r="F115" s="22" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G115" s="23" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H115" s="52">
         <v>0</v>
       </c>
-      <c r="I115" s="49">
+      <c r="I115" s="43">
         <v>9500</v>
       </c>
       <c r="J115" s="49">
         <v>0</v>
       </c>
-      <c r="K115" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="L115" s="53">
+      <c r="K115" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="L115" s="50">
         <v>0</v>
       </c>
       <c r="M115" s="24" t="s">
@@ -7025,25 +7109,25 @@
       <c r="N115" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="O115" s="51"/>
-      <c r="P115" s="51"/>
-      <c r="Q115" s="51"/>
-      <c r="R115" s="51"/>
-      <c r="S115" s="49"/>
-      <c r="T115" s="49"/>
-    </row>
-    <row r="116" spans="1:20" s="4" customFormat="1" ht="16.5">
+      <c r="O115" s="42"/>
+      <c r="P115" s="42"/>
+      <c r="Q115" s="42"/>
+      <c r="R115" s="42"/>
+      <c r="S115" s="43"/>
+      <c r="T115" s="43"/>
+    </row>
+    <row r="116" spans="1:20" s="5" customFormat="1" ht="16.5">
       <c r="A116" s="44">
-        <v>10140010</v>
-      </c>
-      <c r="B116" s="44">
-        <v>101400</v>
-      </c>
-      <c r="C116" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="D116" s="46">
-        <v>101400001</v>
+        <v>10120010</v>
+      </c>
+      <c r="B116" s="54">
+        <v>101200</v>
+      </c>
+      <c r="C116" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="D116" s="55">
+        <v>101200001</v>
       </c>
       <c r="E116" s="47">
         <v>10</v>
@@ -7057,16 +7141,16 @@
       <c r="H116" s="48">
         <v>0</v>
       </c>
-      <c r="I116" s="43">
+      <c r="I116" s="49">
         <v>9500</v>
       </c>
       <c r="J116" s="49">
         <v>0</v>
       </c>
-      <c r="K116" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="L116" s="50">
+      <c r="K116" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="L116" s="53">
         <v>0</v>
       </c>
       <c r="M116" s="24" t="s">
@@ -7075,25 +7159,25 @@
       <c r="N116" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="O116" s="42"/>
-      <c r="P116" s="42"/>
-      <c r="Q116" s="42"/>
-      <c r="R116" s="42"/>
-      <c r="S116" s="43"/>
-      <c r="T116" s="43"/>
-    </row>
-    <row r="117" spans="1:20" s="4" customFormat="1" ht="16.5">
+      <c r="O116" s="51"/>
+      <c r="P116" s="51"/>
+      <c r="Q116" s="51"/>
+      <c r="R116" s="51"/>
+      <c r="S116" s="49"/>
+      <c r="T116" s="49"/>
+    </row>
+    <row r="117" spans="1:20" s="5" customFormat="1" ht="16.5">
       <c r="A117" s="44">
-        <v>10140011</v>
-      </c>
-      <c r="B117" s="44">
-        <v>101400</v>
-      </c>
-      <c r="C117" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="D117" s="46">
-        <v>101400001</v>
+        <v>10120011</v>
+      </c>
+      <c r="B117" s="54">
+        <v>101200</v>
+      </c>
+      <c r="C117" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="D117" s="55">
+        <v>101200001</v>
       </c>
       <c r="E117" s="47">
         <v>11</v>
@@ -7107,16 +7191,16 @@
       <c r="H117" s="48">
         <v>0</v>
       </c>
-      <c r="I117" s="43">
+      <c r="I117" s="49">
         <v>9500</v>
       </c>
       <c r="J117" s="49">
         <v>0</v>
       </c>
-      <c r="K117" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="L117" s="50">
+      <c r="K117" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="L117" s="53">
         <v>0</v>
       </c>
       <c r="M117" s="24" t="s">
@@ -7125,25 +7209,25 @@
       <c r="N117" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="O117" s="42"/>
-      <c r="P117" s="42"/>
-      <c r="Q117" s="42"/>
-      <c r="R117" s="42"/>
-      <c r="S117" s="43"/>
-      <c r="T117" s="43"/>
-    </row>
-    <row r="118" spans="1:20" s="4" customFormat="1" ht="16.5">
+      <c r="O117" s="51"/>
+      <c r="P117" s="51"/>
+      <c r="Q117" s="51"/>
+      <c r="R117" s="51"/>
+      <c r="S117" s="49"/>
+      <c r="T117" s="49"/>
+    </row>
+    <row r="118" spans="1:20" s="5" customFormat="1" ht="16.5">
       <c r="A118" s="44">
-        <v>10140012</v>
-      </c>
-      <c r="B118" s="44">
-        <v>101400</v>
-      </c>
-      <c r="C118" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="D118" s="46">
-        <v>101400001</v>
+        <v>10120012</v>
+      </c>
+      <c r="B118" s="54">
+        <v>101200</v>
+      </c>
+      <c r="C118" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="D118" s="55">
+        <v>101200001</v>
       </c>
       <c r="E118" s="47">
         <v>12</v>
@@ -7157,16 +7241,16 @@
       <c r="H118" s="52">
         <v>0</v>
       </c>
-      <c r="I118" s="43">
+      <c r="I118" s="49">
         <v>9500</v>
       </c>
       <c r="J118" s="49">
         <v>0</v>
       </c>
-      <c r="K118" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="L118" s="50">
+      <c r="K118" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="L118" s="53">
         <v>0</v>
       </c>
       <c r="M118" s="24" t="s">
@@ -7175,34 +7259,34 @@
       <c r="N118" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="O118" s="42"/>
-      <c r="P118" s="42"/>
-      <c r="Q118" s="42"/>
-      <c r="R118" s="42"/>
-      <c r="S118" s="43"/>
-      <c r="T118" s="43"/>
+      <c r="O118" s="51"/>
+      <c r="P118" s="51"/>
+      <c r="Q118" s="51"/>
+      <c r="R118" s="51"/>
+      <c r="S118" s="49"/>
+      <c r="T118" s="49"/>
     </row>
     <row r="119" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A119" s="44">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B119" s="44">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C119" s="45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D119" s="46">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E119" s="47">
         <v>10</v>
       </c>
       <c r="F119" s="22" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G119" s="23" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H119" s="48">
         <v>0</v>
@@ -7234,25 +7318,25 @@
     </row>
     <row r="120" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A120" s="44">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B120" s="44">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C120" s="45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D120" s="46">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E120" s="47">
         <v>11</v>
       </c>
       <c r="F120" s="22" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G120" s="23" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H120" s="48">
         <v>0</v>
@@ -7284,25 +7368,25 @@
     </row>
     <row r="121" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A121" s="44">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B121" s="44">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C121" s="45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D121" s="46">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E121" s="47">
         <v>12</v>
       </c>
       <c r="F121" s="22" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G121" s="23" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H121" s="52">
         <v>0</v>
@@ -7334,16 +7418,16 @@
     </row>
     <row r="122" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A122" s="44">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B122" s="44">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C122" s="45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D122" s="46">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E122" s="47">
         <v>10</v>
@@ -7366,7 +7450,7 @@
       <c r="K122" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="L122" s="53">
+      <c r="L122" s="50">
         <v>0</v>
       </c>
       <c r="M122" s="24" t="s">
@@ -7384,16 +7468,16 @@
     </row>
     <row r="123" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A123" s="44">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B123" s="44">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C123" s="45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D123" s="46">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E123" s="47">
         <v>11</v>
@@ -7416,7 +7500,7 @@
       <c r="K123" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="L123" s="53">
+      <c r="L123" s="50">
         <v>0</v>
       </c>
       <c r="M123" s="24" t="s">
@@ -7434,16 +7518,16 @@
     </row>
     <row r="124" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A124" s="44">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B124" s="44">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C124" s="45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D124" s="46">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E124" s="47">
         <v>12</v>
@@ -7466,7 +7550,7 @@
       <c r="K124" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="L124" s="53">
+      <c r="L124" s="50">
         <v>0</v>
       </c>
       <c r="M124" s="24" t="s">
@@ -7484,16 +7568,16 @@
     </row>
     <row r="125" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A125" s="44">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B125" s="44">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C125" s="45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D125" s="46">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E125" s="47">
         <v>10</v>
@@ -7534,16 +7618,16 @@
     </row>
     <row r="126" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A126" s="44">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B126" s="44">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C126" s="45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D126" s="46">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E126" s="47">
         <v>11</v>
@@ -7584,16 +7668,16 @@
     </row>
     <row r="127" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A127" s="44">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B127" s="44">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C127" s="45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D127" s="46">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E127" s="47">
         <v>12</v>
@@ -7634,25 +7718,25 @@
     </row>
     <row r="128" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A128" s="44">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B128" s="44">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C128" s="45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D128" s="46">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E128" s="47">
         <v>10</v>
       </c>
       <c r="F128" s="22" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G128" s="23" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H128" s="48">
         <v>0</v>
@@ -7684,25 +7768,25 @@
     </row>
     <row r="129" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A129" s="44">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B129" s="44">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C129" s="45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D129" s="46">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E129" s="47">
         <v>11</v>
       </c>
       <c r="F129" s="22" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G129" s="23" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H129" s="48">
         <v>0</v>
@@ -7734,25 +7818,25 @@
     </row>
     <row r="130" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A130" s="44">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B130" s="44">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C130" s="45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D130" s="46">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E130" s="47">
         <v>12</v>
       </c>
       <c r="F130" s="22" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G130" s="23" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H130" s="52">
         <v>0</v>
@@ -7784,27 +7868,27 @@
     </row>
     <row r="131" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A131" s="44">
-        <v>10180010</v>
+        <v>10240010</v>
       </c>
       <c r="B131" s="44">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C131" s="45" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D131" s="46">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E131" s="47">
         <v>10</v>
       </c>
       <c r="F131" s="22" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G131" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H131" s="52">
+        <v>35</v>
+      </c>
+      <c r="H131" s="48">
         <v>0</v>
       </c>
       <c r="I131" s="43">
@@ -7834,27 +7918,27 @@
     </row>
     <row r="132" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A132" s="44">
-        <v>10180011</v>
+        <v>10240011</v>
       </c>
       <c r="B132" s="44">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C132" s="45" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D132" s="46">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E132" s="47">
         <v>11</v>
       </c>
       <c r="F132" s="22" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G132" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="H132" s="52">
+        <v>39</v>
+      </c>
+      <c r="H132" s="48">
         <v>0</v>
       </c>
       <c r="I132" s="43">
@@ -7884,25 +7968,25 @@
     </row>
     <row r="133" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A133" s="44">
-        <v>10180012</v>
+        <v>10240012</v>
       </c>
       <c r="B133" s="44">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C133" s="45" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D133" s="46">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E133" s="47">
         <v>12</v>
       </c>
       <c r="F133" s="22" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G133" s="23" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H133" s="52">
         <v>0</v>
@@ -7934,25 +8018,25 @@
     </row>
     <row r="134" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A134" s="44">
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B134" s="44">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C134" s="45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D134" s="46">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E134" s="47">
         <v>10</v>
       </c>
       <c r="F134" s="22" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G134" s="23" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H134" s="52">
         <v>0</v>
@@ -7984,25 +8068,25 @@
     </row>
     <row r="135" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A135" s="44">
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B135" s="44">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C135" s="45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D135" s="46">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E135" s="47">
         <v>11</v>
       </c>
       <c r="F135" s="22" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G135" s="23" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="H135" s="52">
         <v>0</v>
@@ -8034,25 +8118,25 @@
     </row>
     <row r="136" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A136" s="44">
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B136" s="44">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C136" s="45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D136" s="46">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E136" s="47">
         <v>12</v>
       </c>
       <c r="F136" s="22" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G136" s="23" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H136" s="52">
         <v>0</v>
@@ -8084,25 +8168,25 @@
     </row>
     <row r="137" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A137" s="44">
-        <v>10230010</v>
+        <v>10250010</v>
       </c>
       <c r="B137" s="44">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C137" s="45" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D137" s="46">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E137" s="47">
         <v>10</v>
       </c>
       <c r="F137" s="22" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G137" s="23" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H137" s="52">
         <v>0</v>
@@ -8134,25 +8218,25 @@
     </row>
     <row r="138" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A138" s="44">
-        <v>10230011</v>
+        <v>10250011</v>
       </c>
       <c r="B138" s="44">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C138" s="45" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D138" s="46">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E138" s="47">
         <v>11</v>
       </c>
       <c r="F138" s="22" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G138" s="23" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H138" s="52">
         <v>0</v>
@@ -8184,25 +8268,25 @@
     </row>
     <row r="139" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A139" s="44">
-        <v>10230012</v>
+        <v>10250012</v>
       </c>
       <c r="B139" s="44">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C139" s="45" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D139" s="46">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E139" s="47">
         <v>12</v>
       </c>
       <c r="F139" s="22" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G139" s="23" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="H139" s="52">
         <v>0</v>
@@ -8234,25 +8318,25 @@
     </row>
     <row r="140" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A140" s="44">
-        <v>10340010</v>
+        <v>10230010</v>
       </c>
       <c r="B140" s="44">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C140" s="45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D140" s="46">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E140" s="47">
         <v>10</v>
       </c>
       <c r="F140" s="22" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G140" s="23" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H140" s="52">
         <v>0</v>
@@ -8284,25 +8368,25 @@
     </row>
     <row r="141" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A141" s="44">
-        <v>10340011</v>
+        <v>10230011</v>
       </c>
       <c r="B141" s="44">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C141" s="45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D141" s="46">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E141" s="47">
         <v>11</v>
       </c>
       <c r="F141" s="22" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G141" s="23" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H141" s="52">
         <v>0</v>
@@ -8334,25 +8418,25 @@
     </row>
     <row r="142" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A142" s="44">
-        <v>10340012</v>
+        <v>10230012</v>
       </c>
       <c r="B142" s="44">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C142" s="45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D142" s="46">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E142" s="47">
         <v>12</v>
       </c>
       <c r="F142" s="22" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="G142" s="23" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H142" s="52">
         <v>0</v>
@@ -8384,25 +8468,25 @@
     </row>
     <row r="143" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A143" s="44">
-        <v>10350010</v>
+        <v>10340010</v>
       </c>
       <c r="B143" s="44">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C143" s="45" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D143" s="46">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E143" s="47">
         <v>10</v>
       </c>
       <c r="F143" s="22" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G143" s="23" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="H143" s="52">
         <v>0</v>
@@ -8434,25 +8518,25 @@
     </row>
     <row r="144" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A144" s="44">
-        <v>10350011</v>
+        <v>10340011</v>
       </c>
       <c r="B144" s="44">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C144" s="45" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D144" s="46">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E144" s="47">
         <v>11</v>
       </c>
       <c r="F144" s="22" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G144" s="23" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H144" s="52">
         <v>0</v>
@@ -8484,25 +8568,25 @@
     </row>
     <row r="145" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A145" s="44">
-        <v>10350012</v>
+        <v>10340012</v>
       </c>
       <c r="B145" s="44">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C145" s="45" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D145" s="46">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E145" s="47">
         <v>12</v>
       </c>
       <c r="F145" s="22" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G145" s="23" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="H145" s="52">
         <v>0</v>
@@ -8534,16 +8618,16 @@
     </row>
     <row r="146" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A146" s="44">
-        <v>10350110</v>
+        <v>10350010</v>
       </c>
       <c r="B146" s="44">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C146" s="45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D146" s="46">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E146" s="47">
         <v>10</v>
@@ -8584,16 +8668,16 @@
     </row>
     <row r="147" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A147" s="44">
-        <v>10350111</v>
+        <v>10350011</v>
       </c>
       <c r="B147" s="44">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C147" s="45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D147" s="46">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E147" s="47">
         <v>11</v>
@@ -8634,16 +8718,16 @@
     </row>
     <row r="148" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A148" s="44">
-        <v>10350112</v>
+        <v>10350012</v>
       </c>
       <c r="B148" s="44">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C148" s="45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D148" s="46">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E148" s="47">
         <v>12</v>
@@ -8684,27 +8768,27 @@
     </row>
     <row r="149" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A149" s="44">
-        <v>10360010</v>
+        <v>10350110</v>
       </c>
       <c r="B149" s="44">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C149" s="45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D149" s="46">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E149" s="47">
         <v>10</v>
       </c>
       <c r="F149" s="22" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="G149" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="H149" s="48">
+        <v>39</v>
+      </c>
+      <c r="H149" s="52">
         <v>0</v>
       </c>
       <c r="I149" s="43">
@@ -8734,27 +8818,27 @@
     </row>
     <row r="150" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A150" s="44">
-        <v>10360011</v>
+        <v>10350111</v>
       </c>
       <c r="B150" s="44">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C150" s="45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D150" s="46">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E150" s="47">
         <v>11</v>
       </c>
       <c r="F150" s="22" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G150" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="H150" s="48">
+        <v>42</v>
+      </c>
+      <c r="H150" s="52">
         <v>0</v>
       </c>
       <c r="I150" s="43">
@@ -8784,25 +8868,25 @@
     </row>
     <row r="151" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A151" s="44">
-        <v>10360012</v>
+        <v>10350112</v>
       </c>
       <c r="B151" s="44">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C151" s="45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D151" s="46">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E151" s="47">
         <v>12</v>
       </c>
       <c r="F151" s="22" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="G151" s="23" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H151" s="52">
         <v>0</v>
@@ -8834,27 +8918,27 @@
     </row>
     <row r="152" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A152" s="44">
-        <v>10280010</v>
+        <v>10360010</v>
       </c>
       <c r="B152" s="44">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C152" s="45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D152" s="46">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E152" s="47">
         <v>10</v>
       </c>
       <c r="F152" s="22" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G152" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H152" s="52">
+        <v>71</v>
+      </c>
+      <c r="H152" s="48">
         <v>0</v>
       </c>
       <c r="I152" s="43">
@@ -8884,27 +8968,27 @@
     </row>
     <row r="153" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A153" s="44">
-        <v>10280011</v>
+        <v>10360011</v>
       </c>
       <c r="B153" s="44">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C153" s="45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D153" s="46">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E153" s="47">
         <v>11</v>
       </c>
       <c r="F153" s="22" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G153" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="H153" s="52">
+        <v>73</v>
+      </c>
+      <c r="H153" s="48">
         <v>0</v>
       </c>
       <c r="I153" s="43">
@@ -8934,25 +9018,25 @@
     </row>
     <row r="154" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A154" s="44">
-        <v>10280012</v>
+        <v>10360012</v>
       </c>
       <c r="B154" s="44">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C154" s="45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D154" s="46">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E154" s="47">
         <v>12</v>
       </c>
       <c r="F154" s="22" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="G154" s="23" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="H154" s="52">
         <v>0</v>
@@ -8984,25 +9068,25 @@
     </row>
     <row r="155" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A155" s="44">
-        <v>10200010</v>
+        <v>10280010</v>
       </c>
       <c r="B155" s="44">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C155" s="45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D155" s="46">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E155" s="47">
         <v>10</v>
       </c>
       <c r="F155" s="22" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G155" s="23" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="H155" s="52">
         <v>0</v>
@@ -9034,25 +9118,25 @@
     </row>
     <row r="156" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A156" s="44">
-        <v>10200011</v>
+        <v>10280011</v>
       </c>
       <c r="B156" s="44">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C156" s="45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D156" s="46">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E156" s="47">
         <v>11</v>
       </c>
       <c r="F156" s="22" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="G156" s="23" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="H156" s="52">
         <v>0</v>
@@ -9084,25 +9168,25 @@
     </row>
     <row r="157" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A157" s="44">
-        <v>10200012</v>
+        <v>10280012</v>
       </c>
       <c r="B157" s="44">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C157" s="45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D157" s="46">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E157" s="47">
         <v>12</v>
       </c>
       <c r="F157" s="22" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="G157" s="23" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="H157" s="52">
         <v>0</v>
@@ -9134,25 +9218,25 @@
     </row>
     <row r="158" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A158" s="44">
-        <v>10340110</v>
+        <v>10200010</v>
       </c>
       <c r="B158" s="44">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C158" s="45" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D158" s="46">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E158" s="47">
         <v>10</v>
       </c>
       <c r="F158" s="22" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G158" s="23" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H158" s="52">
         <v>0</v>
@@ -9184,25 +9268,25 @@
     </row>
     <row r="159" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A159" s="44">
-        <v>10340111</v>
+        <v>10200011</v>
       </c>
       <c r="B159" s="44">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C159" s="45" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D159" s="46">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E159" s="47">
         <v>11</v>
       </c>
       <c r="F159" s="22" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G159" s="23" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="H159" s="52">
         <v>0</v>
@@ -9234,25 +9318,25 @@
     </row>
     <row r="160" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A160" s="44">
-        <v>10340112</v>
+        <v>10200012</v>
       </c>
       <c r="B160" s="44">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C160" s="45" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D160" s="46">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E160" s="47">
         <v>12</v>
       </c>
       <c r="F160" s="22" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G160" s="23" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H160" s="52">
         <v>0</v>
@@ -9284,25 +9368,25 @@
     </row>
     <row r="161" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A161" s="44">
-        <v>10380010</v>
+        <v>10340110</v>
       </c>
       <c r="B161" s="44">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C161" s="45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D161" s="46">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E161" s="47">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F161" s="22" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G161" s="23" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="H161" s="52">
         <v>0</v>
@@ -9334,25 +9418,25 @@
     </row>
     <row r="162" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A162" s="44">
-        <v>10380011</v>
+        <v>10340111</v>
       </c>
       <c r="B162" s="44">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C162" s="45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D162" s="46">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E162" s="47">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F162" s="22" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="G162" s="23" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H162" s="52">
         <v>0</v>
@@ -9384,25 +9468,25 @@
     </row>
     <row r="163" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A163" s="44">
-        <v>10380012</v>
+        <v>10340112</v>
       </c>
       <c r="B163" s="44">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C163" s="45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D163" s="46">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E163" s="47">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F163" s="22" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G163" s="23" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="H163" s="52">
         <v>0</v>
@@ -9434,25 +9518,25 @@
     </row>
     <row r="164" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A164" s="44">
-        <v>10270010</v>
+        <v>10380010</v>
       </c>
       <c r="B164" s="44">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C164" s="45" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D164" s="46">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E164" s="47">
         <v>11</v>
       </c>
       <c r="F164" s="22" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G164" s="23" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="H164" s="52">
         <v>0</v>
@@ -9484,25 +9568,25 @@
     </row>
     <row r="165" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A165" s="44">
-        <v>10270011</v>
+        <v>10380011</v>
       </c>
       <c r="B165" s="44">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C165" s="45" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D165" s="46">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E165" s="47">
         <v>12</v>
       </c>
       <c r="F165" s="22" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="G165" s="23" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="H165" s="52">
         <v>0</v>
@@ -9534,25 +9618,25 @@
     </row>
     <row r="166" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A166" s="44">
-        <v>10270012</v>
+        <v>10380012</v>
       </c>
       <c r="B166" s="44">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C166" s="45" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D166" s="46">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E166" s="47">
         <v>13</v>
       </c>
       <c r="F166" s="22" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="G166" s="23" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="H166" s="52">
         <v>0</v>
@@ -9584,25 +9668,25 @@
     </row>
     <row r="167" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A167" s="44">
-        <v>10370010</v>
+        <v>10270010</v>
       </c>
       <c r="B167" s="44">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C167" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D167" s="46">
-        <v>103700001</v>
+        <v>102700001</v>
       </c>
       <c r="E167" s="47">
         <v>11</v>
       </c>
       <c r="F167" s="22" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G167" s="23" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H167" s="52">
         <v>0</v>
@@ -9634,25 +9718,25 @@
     </row>
     <row r="168" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A168" s="44">
-        <v>10370011</v>
+        <v>10270011</v>
       </c>
       <c r="B168" s="44">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C168" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D168" s="46">
-        <v>103700001</v>
+        <v>102700001</v>
       </c>
       <c r="E168" s="47">
         <v>12</v>
       </c>
       <c r="F168" s="22" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G168" s="23" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H168" s="52">
         <v>0</v>
@@ -9684,25 +9768,25 @@
     </row>
     <row r="169" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A169" s="44">
-        <v>10370012</v>
+        <v>10270012</v>
       </c>
       <c r="B169" s="44">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C169" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D169" s="46">
-        <v>103100001</v>
+        <v>102700001</v>
       </c>
       <c r="E169" s="47">
         <v>13</v>
       </c>
       <c r="F169" s="22" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G169" s="23" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H169" s="52">
         <v>0</v>
@@ -9734,27 +9818,27 @@
     </row>
     <row r="170" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A170" s="44">
-        <v>10310010</v>
+        <v>10370010</v>
       </c>
       <c r="B170" s="44">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C170" s="45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D170" s="46">
-        <v>103100001</v>
+        <v>103700001</v>
       </c>
       <c r="E170" s="47">
         <v>11</v>
       </c>
       <c r="F170" s="22" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="G170" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="H170" s="48">
+        <v>39</v>
+      </c>
+      <c r="H170" s="52">
         <v>0</v>
       </c>
       <c r="I170" s="43">
@@ -9784,27 +9868,27 @@
     </row>
     <row r="171" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A171" s="44">
-        <v>10310011</v>
+        <v>10370011</v>
       </c>
       <c r="B171" s="44">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C171" s="45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D171" s="46">
-        <v>103100001</v>
+        <v>103700001</v>
       </c>
       <c r="E171" s="47">
         <v>12</v>
       </c>
       <c r="F171" s="22" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="G171" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="H171" s="48">
+        <v>42</v>
+      </c>
+      <c r="H171" s="52">
         <v>0</v>
       </c>
       <c r="I171" s="43">
@@ -9834,13 +9918,13 @@
     </row>
     <row r="172" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A172" s="44">
-        <v>10310012</v>
+        <v>10370012</v>
       </c>
       <c r="B172" s="44">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C172" s="45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D172" s="46">
         <v>103100001</v>
@@ -9849,10 +9933,10 @@
         <v>13</v>
       </c>
       <c r="F172" s="22" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="G172" s="23" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="H172" s="52">
         <v>0</v>
@@ -9884,27 +9968,27 @@
     </row>
     <row r="173" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A173" s="44">
-        <v>10400010</v>
+        <v>10310010</v>
       </c>
       <c r="B173" s="44">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C173" s="45" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D173" s="46">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E173" s="47">
         <v>11</v>
       </c>
       <c r="F173" s="22" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G173" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="H173" s="52">
+        <v>102</v>
+      </c>
+      <c r="H173" s="48">
         <v>0</v>
       </c>
       <c r="I173" s="43">
@@ -9934,27 +10018,27 @@
     </row>
     <row r="174" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A174" s="44">
-        <v>10400011</v>
+        <v>10310011</v>
       </c>
       <c r="B174" s="44">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C174" s="45" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D174" s="46">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E174" s="47">
         <v>12</v>
       </c>
       <c r="F174" s="22" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G174" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="H174" s="52">
+        <v>104</v>
+      </c>
+      <c r="H174" s="48">
         <v>0</v>
       </c>
       <c r="I174" s="43">
@@ -9984,25 +10068,25 @@
     </row>
     <row r="175" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A175" s="44">
-        <v>10400012</v>
+        <v>10310012</v>
       </c>
       <c r="B175" s="44">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C175" s="45" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D175" s="46">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E175" s="47">
         <v>13</v>
       </c>
       <c r="F175" s="22" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G175" s="23" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H175" s="52">
         <v>0</v>
@@ -10034,25 +10118,25 @@
     </row>
     <row r="176" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A176" s="44">
-        <v>10390010</v>
+        <v>10400010</v>
       </c>
       <c r="B176" s="44">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C176" s="45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D176" s="46">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E176" s="47">
         <v>11</v>
       </c>
       <c r="F176" s="22" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G176" s="23" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="H176" s="52">
         <v>0</v>
@@ -10084,25 +10168,25 @@
     </row>
     <row r="177" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A177" s="44">
-        <v>10390011</v>
+        <v>10400011</v>
       </c>
       <c r="B177" s="44">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C177" s="45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D177" s="46">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E177" s="47">
         <v>12</v>
       </c>
       <c r="F177" s="22" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G177" s="23" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="H177" s="52">
         <v>0</v>
@@ -10134,25 +10218,25 @@
     </row>
     <row r="178" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A178" s="44">
-        <v>10390012</v>
+        <v>10400012</v>
       </c>
       <c r="B178" s="44">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C178" s="45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D178" s="46">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E178" s="47">
         <v>13</v>
       </c>
       <c r="F178" s="22" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G178" s="23" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="H178" s="52">
         <v>0</v>
@@ -10184,25 +10268,25 @@
     </row>
     <row r="179" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A179" s="44">
-        <v>10160010</v>
+        <v>10390010</v>
       </c>
       <c r="B179" s="44">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C179" s="45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D179" s="46">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E179" s="47">
         <v>11</v>
       </c>
       <c r="F179" s="22" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="G179" s="23" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="H179" s="52">
         <v>0</v>
@@ -10234,25 +10318,25 @@
     </row>
     <row r="180" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A180" s="44">
-        <v>10160011</v>
+        <v>10390011</v>
       </c>
       <c r="B180" s="44">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C180" s="45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D180" s="46">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E180" s="47">
         <v>12</v>
       </c>
       <c r="F180" s="22" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="G180" s="23" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="H180" s="52">
         <v>0</v>
@@ -10284,25 +10368,25 @@
     </row>
     <row r="181" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A181" s="44">
-        <v>10160012</v>
+        <v>10390012</v>
       </c>
       <c r="B181" s="44">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C181" s="45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D181" s="46">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E181" s="47">
         <v>13</v>
       </c>
       <c r="F181" s="22" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="G181" s="23" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="H181" s="52">
         <v>0</v>
@@ -10334,16 +10418,16 @@
     </row>
     <row r="182" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A182" s="44">
-        <v>10150010</v>
+        <v>10160010</v>
       </c>
       <c r="B182" s="44">
-        <v>101500</v>
+        <v>101600</v>
       </c>
       <c r="C182" s="45" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D182" s="46">
-        <v>101500001</v>
+        <v>101600001</v>
       </c>
       <c r="E182" s="47">
         <v>11</v>
@@ -10384,16 +10468,16 @@
     </row>
     <row r="183" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A183" s="44">
-        <v>10150011</v>
+        <v>10160011</v>
       </c>
       <c r="B183" s="44">
-        <v>101500</v>
+        <v>101600</v>
       </c>
       <c r="C183" s="45" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D183" s="46">
-        <v>101500001</v>
+        <v>101600001</v>
       </c>
       <c r="E183" s="47">
         <v>12</v>
@@ -10434,16 +10518,16 @@
     </row>
     <row r="184" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A184" s="44">
-        <v>10150012</v>
+        <v>10160012</v>
       </c>
       <c r="B184" s="44">
-        <v>101500</v>
+        <v>101600</v>
       </c>
       <c r="C184" s="45" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D184" s="46">
-        <v>101500001</v>
+        <v>101600001</v>
       </c>
       <c r="E184" s="47">
         <v>13</v>
@@ -10484,16 +10568,16 @@
     </row>
     <row r="185" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A185" s="44">
-        <v>10260010</v>
+        <v>10150010</v>
       </c>
       <c r="B185" s="44">
-        <v>102600</v>
+        <v>101500</v>
       </c>
       <c r="C185" s="45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D185" s="46">
-        <v>102600001</v>
+        <v>101500001</v>
       </c>
       <c r="E185" s="47">
         <v>11</v>
@@ -10534,16 +10618,16 @@
     </row>
     <row r="186" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A186" s="44">
-        <v>10260011</v>
+        <v>10150011</v>
       </c>
       <c r="B186" s="44">
-        <v>102600</v>
+        <v>101500</v>
       </c>
       <c r="C186" s="45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D186" s="46">
-        <v>102600001</v>
+        <v>101500001</v>
       </c>
       <c r="E186" s="47">
         <v>12</v>
@@ -10584,16 +10668,16 @@
     </row>
     <row r="187" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A187" s="44">
-        <v>10260012</v>
+        <v>10150012</v>
       </c>
       <c r="B187" s="44">
-        <v>102600</v>
+        <v>101500</v>
       </c>
       <c r="C187" s="45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D187" s="46">
-        <v>102600001</v>
+        <v>101500001</v>
       </c>
       <c r="E187" s="47">
         <v>13</v>
@@ -10634,16 +10718,16 @@
     </row>
     <row r="188" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A188" s="44">
-        <v>10500010</v>
+        <v>10260010</v>
       </c>
       <c r="B188" s="44">
-        <v>105000</v>
+        <v>102600</v>
       </c>
       <c r="C188" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D188" s="46">
-        <v>105000001</v>
+        <v>102600001</v>
       </c>
       <c r="E188" s="47">
         <v>11</v>
@@ -10684,16 +10768,16 @@
     </row>
     <row r="189" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A189" s="44">
-        <v>10500011</v>
+        <v>10260011</v>
       </c>
       <c r="B189" s="44">
-        <v>105000</v>
+        <v>102600</v>
       </c>
       <c r="C189" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D189" s="46">
-        <v>105000001</v>
+        <v>102600001</v>
       </c>
       <c r="E189" s="47">
         <v>12</v>
@@ -10734,16 +10818,16 @@
     </row>
     <row r="190" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A190" s="44">
-        <v>10500012</v>
+        <v>10260012</v>
       </c>
       <c r="B190" s="44">
-        <v>105000</v>
+        <v>102600</v>
       </c>
       <c r="C190" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D190" s="46">
-        <v>105000001</v>
+        <v>102600001</v>
       </c>
       <c r="E190" s="47">
         <v>13</v>
@@ -10784,27 +10868,27 @@
     </row>
     <row r="191" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A191" s="44">
-        <v>10510010</v>
+        <v>10500010</v>
       </c>
       <c r="B191" s="44">
-        <v>105100</v>
+        <v>105000</v>
       </c>
       <c r="C191" s="45" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D191" s="46">
-        <v>105100001</v>
+        <v>105000001</v>
       </c>
       <c r="E191" s="47">
         <v>11</v>
       </c>
       <c r="F191" s="22" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G191" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="H191" s="48">
+        <v>51</v>
+      </c>
+      <c r="H191" s="52">
         <v>0</v>
       </c>
       <c r="I191" s="43">
@@ -10834,27 +10918,27 @@
     </row>
     <row r="192" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A192" s="44">
-        <v>10510011</v>
+        <v>10500011</v>
       </c>
       <c r="B192" s="44">
-        <v>105100</v>
+        <v>105000</v>
       </c>
       <c r="C192" s="45" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D192" s="46">
-        <v>105100001</v>
+        <v>105000001</v>
       </c>
       <c r="E192" s="47">
         <v>12</v>
       </c>
       <c r="F192" s="22" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G192" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="H192" s="48">
+        <v>53</v>
+      </c>
+      <c r="H192" s="52">
         <v>0</v>
       </c>
       <c r="I192" s="43">
@@ -10884,25 +10968,25 @@
     </row>
     <row r="193" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A193" s="44">
-        <v>10510012</v>
+        <v>10500012</v>
       </c>
       <c r="B193" s="44">
-        <v>105100</v>
+        <v>105000</v>
       </c>
       <c r="C193" s="45" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D193" s="46">
-        <v>105100001</v>
+        <v>105000001</v>
       </c>
       <c r="E193" s="47">
         <v>13</v>
       </c>
       <c r="F193" s="22" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G193" s="23" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H193" s="52">
         <v>0</v>
@@ -10934,31 +11018,31 @@
     </row>
     <row r="194" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A194" s="44">
-        <v>10540011</v>
+        <v>10510010</v>
       </c>
       <c r="B194" s="44">
-        <v>105400</v>
+        <v>105100</v>
       </c>
       <c r="C194" s="45" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="D194" s="46">
-        <v>105400001</v>
+        <v>105100001</v>
       </c>
       <c r="E194" s="47">
         <v>11</v>
       </c>
       <c r="F194" s="22" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="G194" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H194" s="52">
+        <v>39</v>
+      </c>
+      <c r="H194" s="48">
         <v>0</v>
       </c>
       <c r="I194" s="43">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J194" s="49">
         <v>0</v>
@@ -10970,7 +11054,7 @@
         <v>0</v>
       </c>
       <c r="M194" s="24" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="N194" s="51" t="s">
         <v>123</v>
@@ -10984,31 +11068,31 @@
     </row>
     <row r="195" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A195" s="44">
-        <v>10540012</v>
+        <v>10510011</v>
       </c>
       <c r="B195" s="44">
-        <v>105400</v>
+        <v>105100</v>
       </c>
       <c r="C195" s="45" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="D195" s="46">
-        <v>105400001</v>
+        <v>105100001</v>
       </c>
       <c r="E195" s="47">
         <v>12</v>
       </c>
       <c r="F195" s="22" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="G195" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="H195" s="52">
+        <v>42</v>
+      </c>
+      <c r="H195" s="48">
         <v>0</v>
       </c>
       <c r="I195" s="43">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J195" s="49">
         <v>0</v>
@@ -11020,7 +11104,7 @@
         <v>0</v>
       </c>
       <c r="M195" s="24" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="N195" s="51" t="s">
         <v>124</v>
@@ -11034,31 +11118,31 @@
     </row>
     <row r="196" spans="1:20" s="4" customFormat="1" ht="16.5">
       <c r="A196" s="44">
-        <v>10540013</v>
+        <v>10510012</v>
       </c>
       <c r="B196" s="44">
-        <v>105400</v>
+        <v>105100</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="D196" s="46">
-        <v>105400001</v>
+        <v>105100001</v>
       </c>
       <c r="E196" s="47">
         <v>13</v>
       </c>
       <c r="F196" s="22" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="G196" s="23" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H196" s="52">
         <v>0</v>
       </c>
       <c r="I196" s="43">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J196" s="49">
         <v>0</v>
@@ -11070,7 +11154,7 @@
         <v>0</v>
       </c>
       <c r="M196" s="24" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="N196" s="51" t="s">
         <v>125</v>
@@ -11082,20 +11166,20 @@
       <c r="S196" s="43"/>
       <c r="T196" s="43"/>
     </row>
-    <row r="197" spans="1:20" ht="16.5">
-      <c r="A197" s="56">
-        <v>10080010</v>
-      </c>
-      <c r="B197" s="56">
-        <v>100800</v>
-      </c>
-      <c r="C197" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="D197" s="33">
-        <v>100800001</v>
-      </c>
-      <c r="E197" s="11">
+    <row r="197" spans="1:20" s="4" customFormat="1" ht="16.5">
+      <c r="A197" s="44">
+        <v>10540011</v>
+      </c>
+      <c r="B197" s="44">
+        <v>105400</v>
+      </c>
+      <c r="C197" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="D197" s="46">
+        <v>105400001</v>
+      </c>
+      <c r="E197" s="47">
         <v>11</v>
       </c>
       <c r="F197" s="22" t="s">
@@ -11104,42 +11188,48 @@
       <c r="G197" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="H197" s="29">
-        <v>0</v>
-      </c>
-      <c r="I197" s="24">
+      <c r="H197" s="52">
+        <v>0</v>
+      </c>
+      <c r="I197" s="43">
         <v>9600</v>
       </c>
-      <c r="J197" s="24">
-        <v>0</v>
-      </c>
-      <c r="K197" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="L197" s="27">
+      <c r="J197" s="49">
+        <v>0</v>
+      </c>
+      <c r="K197" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="L197" s="53">
         <v>0</v>
       </c>
       <c r="M197" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="N197" s="22" t="s">
+      <c r="N197" s="51" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="198" spans="1:20" ht="16.5">
-      <c r="A198" s="56">
-        <v>10080011</v>
-      </c>
-      <c r="B198" s="56">
-        <v>100800</v>
-      </c>
-      <c r="C198" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="D198" s="33">
-        <v>100800001</v>
-      </c>
-      <c r="E198" s="11">
+      <c r="O197" s="42"/>
+      <c r="P197" s="42"/>
+      <c r="Q197" s="42"/>
+      <c r="R197" s="42"/>
+      <c r="S197" s="43"/>
+      <c r="T197" s="43"/>
+    </row>
+    <row r="198" spans="1:20" s="4" customFormat="1" ht="16.5">
+      <c r="A198" s="44">
+        <v>10540012</v>
+      </c>
+      <c r="B198" s="44">
+        <v>105400</v>
+      </c>
+      <c r="C198" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="D198" s="46">
+        <v>105400001</v>
+      </c>
+      <c r="E198" s="47">
         <v>12</v>
       </c>
       <c r="F198" s="22" t="s">
@@ -11148,42 +11238,48 @@
       <c r="G198" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H198" s="29">
-        <v>0</v>
-      </c>
-      <c r="I198" s="24">
+      <c r="H198" s="52">
+        <v>0</v>
+      </c>
+      <c r="I198" s="43">
         <v>9600</v>
       </c>
-      <c r="J198" s="24">
-        <v>0</v>
-      </c>
-      <c r="K198" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="L198" s="27">
+      <c r="J198" s="49">
+        <v>0</v>
+      </c>
+      <c r="K198" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="L198" s="53">
         <v>0</v>
       </c>
       <c r="M198" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="N198" s="22" t="s">
+      <c r="N198" s="51" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="199" spans="1:20" ht="16.5">
-      <c r="A199" s="56">
-        <v>10080012</v>
-      </c>
-      <c r="B199" s="56">
-        <v>100800</v>
-      </c>
-      <c r="C199" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="D199" s="33">
-        <v>100800001</v>
-      </c>
-      <c r="E199" s="11">
+      <c r="O198" s="42"/>
+      <c r="P198" s="42"/>
+      <c r="Q198" s="42"/>
+      <c r="R198" s="42"/>
+      <c r="S198" s="43"/>
+      <c r="T198" s="43"/>
+    </row>
+    <row r="199" spans="1:20" s="4" customFormat="1" ht="16.5">
+      <c r="A199" s="44">
+        <v>10540013</v>
+      </c>
+      <c r="B199" s="44">
+        <v>105400</v>
+      </c>
+      <c r="C199" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="D199" s="46">
+        <v>105400001</v>
+      </c>
+      <c r="E199" s="47">
         <v>13</v>
       </c>
       <c r="F199" s="22" t="s">
@@ -11192,40 +11288,46 @@
       <c r="G199" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="H199" s="29">
-        <v>0</v>
-      </c>
-      <c r="I199" s="24">
+      <c r="H199" s="52">
+        <v>0</v>
+      </c>
+      <c r="I199" s="43">
         <v>9600</v>
       </c>
-      <c r="J199" s="24">
-        <v>0</v>
-      </c>
-      <c r="K199" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="L199" s="27">
+      <c r="J199" s="49">
+        <v>0</v>
+      </c>
+      <c r="K199" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="L199" s="53">
         <v>0</v>
       </c>
       <c r="M199" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="N199" s="22" t="s">
+      <c r="N199" s="51" t="s">
         <v>125</v>
       </c>
+      <c r="O199" s="42"/>
+      <c r="P199" s="42"/>
+      <c r="Q199" s="42"/>
+      <c r="R199" s="42"/>
+      <c r="S199" s="43"/>
+      <c r="T199" s="43"/>
     </row>
     <row r="200" spans="1:20" ht="16.5">
-      <c r="A200" s="20">
-        <v>10530010</v>
-      </c>
-      <c r="B200" s="20">
-        <v>105300</v>
-      </c>
-      <c r="C200" s="21" t="s">
-        <v>128</v>
+      <c r="A200" s="56">
+        <v>10080010</v>
+      </c>
+      <c r="B200" s="56">
+        <v>100800</v>
+      </c>
+      <c r="C200" s="11" t="s">
+        <v>127</v>
       </c>
       <c r="D200" s="33">
-        <v>105300001</v>
+        <v>100800001</v>
       </c>
       <c r="E200" s="11">
         <v>11</v>
@@ -11259,17 +11361,17 @@
       </c>
     </row>
     <row r="201" spans="1:20" ht="16.5">
-      <c r="A201" s="20">
-        <v>10530011</v>
-      </c>
-      <c r="B201" s="20">
-        <v>105300</v>
-      </c>
-      <c r="C201" s="21" t="s">
-        <v>128</v>
+      <c r="A201" s="56">
+        <v>10080011</v>
+      </c>
+      <c r="B201" s="56">
+        <v>100800</v>
+      </c>
+      <c r="C201" s="11" t="s">
+        <v>127</v>
       </c>
       <c r="D201" s="33">
-        <v>105300001</v>
+        <v>100800001</v>
       </c>
       <c r="E201" s="11">
         <v>12</v>
@@ -11303,17 +11405,17 @@
       </c>
     </row>
     <row r="202" spans="1:20" ht="16.5">
-      <c r="A202" s="20">
-        <v>10530012</v>
-      </c>
-      <c r="B202" s="20">
-        <v>105300</v>
-      </c>
-      <c r="C202" s="21" t="s">
-        <v>128</v>
+      <c r="A202" s="56">
+        <v>10080012</v>
+      </c>
+      <c r="B202" s="56">
+        <v>100800</v>
+      </c>
+      <c r="C202" s="11" t="s">
+        <v>127</v>
       </c>
       <c r="D202" s="33">
-        <v>105300001</v>
+        <v>100800001</v>
       </c>
       <c r="E202" s="11">
         <v>13</v>
@@ -11347,17 +11449,17 @@
       </c>
     </row>
     <row r="203" spans="1:20" ht="16.5">
-      <c r="A203" s="56">
-        <v>10570010</v>
-      </c>
-      <c r="B203" s="56">
-        <v>105700</v>
-      </c>
-      <c r="C203" t="s">
-        <v>129</v>
+      <c r="A203" s="20">
+        <v>10530010</v>
+      </c>
+      <c r="B203" s="20">
+        <v>105300</v>
+      </c>
+      <c r="C203" s="21" t="s">
+        <v>128</v>
       </c>
       <c r="D203" s="33">
-        <v>105700001</v>
+        <v>105300001</v>
       </c>
       <c r="E203" s="11">
         <v>11</v>
@@ -11391,17 +11493,17 @@
       </c>
     </row>
     <row r="204" spans="1:20" ht="16.5">
-      <c r="A204" s="56">
-        <v>10570011</v>
-      </c>
-      <c r="B204" s="56">
-        <v>105700</v>
-      </c>
-      <c r="C204" t="s">
-        <v>129</v>
+      <c r="A204" s="20">
+        <v>10530011</v>
+      </c>
+      <c r="B204" s="20">
+        <v>105300</v>
+      </c>
+      <c r="C204" s="21" t="s">
+        <v>128</v>
       </c>
       <c r="D204" s="33">
-        <v>105700001</v>
+        <v>105300001</v>
       </c>
       <c r="E204" s="11">
         <v>12</v>
@@ -11435,17 +11537,17 @@
       </c>
     </row>
     <row r="205" spans="1:20" ht="16.5">
-      <c r="A205" s="56">
-        <v>10570012</v>
-      </c>
-      <c r="B205" s="56">
-        <v>105700</v>
-      </c>
-      <c r="C205" t="s">
-        <v>129</v>
+      <c r="A205" s="20">
+        <v>10530012</v>
+      </c>
+      <c r="B205" s="20">
+        <v>105300</v>
+      </c>
+      <c r="C205" s="21" t="s">
+        <v>128</v>
       </c>
       <c r="D205" s="33">
-        <v>105700001</v>
+        <v>105300001</v>
       </c>
       <c r="E205" s="11">
         <v>13</v>
@@ -11478,18 +11580,18 @@
         <v>125</v>
       </c>
     </row>
-    <row r="206" spans="1:20" s="6" customFormat="1" ht="16.5">
+    <row r="206" spans="1:20" ht="16.5">
       <c r="A206" s="56">
-        <v>10580010</v>
+        <v>10570010</v>
       </c>
       <c r="B206" s="56">
-        <v>105800</v>
-      </c>
-      <c r="C206" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D206" s="57">
-        <v>105800001</v>
+        <v>105700</v>
+      </c>
+      <c r="C206" t="s">
+        <v>129</v>
+      </c>
+      <c r="D206" s="33">
+        <v>105700001</v>
       </c>
       <c r="E206" s="11">
         <v>11</v>
@@ -11522,18 +11624,18 @@
         <v>123</v>
       </c>
     </row>
-    <row r="207" spans="1:20" s="6" customFormat="1" ht="16.5">
+    <row r="207" spans="1:20" ht="16.5">
       <c r="A207" s="56">
-        <v>10580011</v>
+        <v>10570011</v>
       </c>
       <c r="B207" s="56">
-        <v>105800</v>
-      </c>
-      <c r="C207" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D207" s="57">
-        <v>105800001</v>
+        <v>105700</v>
+      </c>
+      <c r="C207" t="s">
+        <v>129</v>
+      </c>
+      <c r="D207" s="33">
+        <v>105700001</v>
       </c>
       <c r="E207" s="11">
         <v>12</v>
@@ -11566,18 +11668,18 @@
         <v>124</v>
       </c>
     </row>
-    <row r="208" spans="1:20" s="6" customFormat="1" ht="16.5">
+    <row r="208" spans="1:20" ht="16.5">
       <c r="A208" s="56">
-        <v>10580012</v>
+        <v>10570012</v>
       </c>
       <c r="B208" s="56">
-        <v>105800</v>
-      </c>
-      <c r="C208" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D208" s="57">
-        <v>105800001</v>
+        <v>105700</v>
+      </c>
+      <c r="C208" t="s">
+        <v>129</v>
+      </c>
+      <c r="D208" s="33">
+        <v>105700001</v>
       </c>
       <c r="E208" s="11">
         <v>13</v>
@@ -11612,25 +11714,25 @@
     </row>
     <row r="209" spans="1:14" s="6" customFormat="1" ht="16.5">
       <c r="A209" s="56">
-        <v>10550010</v>
+        <v>10580010</v>
       </c>
       <c r="B209" s="56">
-        <v>105500</v>
-      </c>
-      <c r="C209" s="56" t="s">
-        <v>114</v>
+        <v>105800</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="D209" s="57">
-        <v>105500001</v>
+        <v>105800001</v>
       </c>
       <c r="E209" s="11">
         <v>11</v>
       </c>
       <c r="F209" s="22" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="G209" s="23" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H209" s="29">
         <v>0</v>
@@ -11656,25 +11758,25 @@
     </row>
     <row r="210" spans="1:14" s="6" customFormat="1" ht="16.5">
       <c r="A210" s="56">
-        <v>10550011</v>
+        <v>10580011</v>
       </c>
       <c r="B210" s="56">
-        <v>105500</v>
-      </c>
-      <c r="C210" s="56" t="s">
-        <v>114</v>
+        <v>105800</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="D210" s="57">
-        <v>105500001</v>
+        <v>105800001</v>
       </c>
       <c r="E210" s="11">
         <v>12</v>
       </c>
       <c r="F210" s="22" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="G210" s="23" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H210" s="29">
         <v>0</v>
@@ -11700,25 +11802,25 @@
     </row>
     <row r="211" spans="1:14" s="6" customFormat="1" ht="16.5">
       <c r="A211" s="56">
-        <v>10550012</v>
+        <v>10580012</v>
       </c>
       <c r="B211" s="56">
-        <v>105500</v>
-      </c>
-      <c r="C211" s="56" t="s">
-        <v>114</v>
+        <v>105800</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="D211" s="57">
-        <v>105500001</v>
+        <v>105800001</v>
       </c>
       <c r="E211" s="11">
         <v>13</v>
       </c>
       <c r="F211" s="22" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="G211" s="23" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H211" s="29">
         <v>0</v>
@@ -11742,27 +11844,27 @@
         <v>125</v>
       </c>
     </row>
-    <row r="212" spans="1:14" ht="16.5">
+    <row r="212" spans="1:14" s="6" customFormat="1" ht="16.5">
       <c r="A212" s="56">
-        <v>10480010</v>
+        <v>10550010</v>
       </c>
       <c r="B212" s="56">
-        <v>104800</v>
-      </c>
-      <c r="C212" t="s">
-        <v>115</v>
-      </c>
-      <c r="D212" s="25">
-        <v>104800001</v>
+        <v>105500</v>
+      </c>
+      <c r="C212" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="D212" s="57">
+        <v>105500001</v>
       </c>
       <c r="E212" s="11">
         <v>11</v>
       </c>
       <c r="F212" s="22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="G212" s="23" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="H212" s="29">
         <v>0</v>
@@ -11786,27 +11888,27 @@
         <v>123</v>
       </c>
     </row>
-    <row r="213" spans="1:14" ht="16.5">
+    <row r="213" spans="1:14" s="6" customFormat="1" ht="16.5">
       <c r="A213" s="56">
-        <v>10480011</v>
+        <v>10550011</v>
       </c>
       <c r="B213" s="56">
-        <v>104800</v>
-      </c>
-      <c r="C213" t="s">
-        <v>115</v>
-      </c>
-      <c r="D213" s="25">
-        <v>104800001</v>
+        <v>105500</v>
+      </c>
+      <c r="C213" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="D213" s="57">
+        <v>105500001</v>
       </c>
       <c r="E213" s="11">
         <v>12</v>
       </c>
       <c r="F213" s="22" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="G213" s="23" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="H213" s="29">
         <v>0</v>
@@ -11830,27 +11932,27 @@
         <v>124</v>
       </c>
     </row>
-    <row r="214" spans="1:14" ht="16.5">
+    <row r="214" spans="1:14" s="6" customFormat="1" ht="16.5">
       <c r="A214" s="56">
-        <v>10480012</v>
+        <v>10550012</v>
       </c>
       <c r="B214" s="56">
-        <v>104800</v>
-      </c>
-      <c r="C214" t="s">
-        <v>115</v>
-      </c>
-      <c r="D214" s="25">
-        <v>104800001</v>
+        <v>105500</v>
+      </c>
+      <c r="C214" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="D214" s="57">
+        <v>105500001</v>
       </c>
       <c r="E214" s="11">
         <v>13</v>
       </c>
       <c r="F214" s="22" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="G214" s="23" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="H214" s="29">
         <v>0</v>
@@ -11874,27 +11976,27 @@
         <v>125</v>
       </c>
     </row>
-    <row r="215" spans="1:14" s="56" customFormat="1" ht="16.5">
+    <row r="215" spans="1:14" ht="16.5">
       <c r="A215" s="56">
-        <v>10550110</v>
+        <v>10480010</v>
       </c>
       <c r="B215" s="56">
-        <v>105501</v>
-      </c>
-      <c r="C215" s="56" t="s">
-        <v>122</v>
-      </c>
-      <c r="D215" s="57">
-        <v>105501001</v>
-      </c>
-      <c r="E215" s="58">
+        <v>104800</v>
+      </c>
+      <c r="C215" t="s">
+        <v>115</v>
+      </c>
+      <c r="D215" s="25">
+        <v>104800001</v>
+      </c>
+      <c r="E215" s="11">
         <v>11</v>
       </c>
       <c r="F215" s="22" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="G215" s="23" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H215" s="29">
         <v>0</v>
@@ -11918,27 +12020,27 @@
         <v>123</v>
       </c>
     </row>
-    <row r="216" spans="1:14" s="56" customFormat="1" ht="16.5">
+    <row r="216" spans="1:14" ht="16.5">
       <c r="A216" s="56">
-        <v>10550111</v>
+        <v>10480011</v>
       </c>
       <c r="B216" s="56">
-        <v>105501</v>
-      </c>
-      <c r="C216" s="56" t="s">
-        <v>122</v>
-      </c>
-      <c r="D216" s="57">
-        <v>105501001</v>
-      </c>
-      <c r="E216" s="58">
+        <v>104800</v>
+      </c>
+      <c r="C216" t="s">
+        <v>115</v>
+      </c>
+      <c r="D216" s="25">
+        <v>104800001</v>
+      </c>
+      <c r="E216" s="11">
         <v>12</v>
       </c>
       <c r="F216" s="22" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="G216" s="23" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H216" s="29">
         <v>0</v>
@@ -11962,27 +12064,27 @@
         <v>124</v>
       </c>
     </row>
-    <row r="217" spans="1:14" s="56" customFormat="1" ht="16.5">
+    <row r="217" spans="1:14" ht="16.5">
       <c r="A217" s="56">
-        <v>10550112</v>
+        <v>10480012</v>
       </c>
       <c r="B217" s="56">
-        <v>105501</v>
-      </c>
-      <c r="C217" s="56" t="s">
-        <v>122</v>
-      </c>
-      <c r="D217" s="57">
-        <v>105501001</v>
-      </c>
-      <c r="E217" s="58">
+        <v>104800</v>
+      </c>
+      <c r="C217" t="s">
+        <v>115</v>
+      </c>
+      <c r="D217" s="25">
+        <v>104800001</v>
+      </c>
+      <c r="E217" s="11">
         <v>13</v>
       </c>
       <c r="F217" s="22" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="G217" s="23" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H217" s="29">
         <v>0</v>
@@ -12003,6 +12105,270 @@
         <v>121</v>
       </c>
       <c r="N217" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" s="56" customFormat="1" ht="16.5">
+      <c r="A218" s="56">
+        <v>10550110</v>
+      </c>
+      <c r="B218" s="56">
+        <v>105501</v>
+      </c>
+      <c r="C218" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="D218" s="57">
+        <v>105501001</v>
+      </c>
+      <c r="E218" s="58">
+        <v>11</v>
+      </c>
+      <c r="F218" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G218" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="H218" s="29">
+        <v>0</v>
+      </c>
+      <c r="I218" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J218" s="24">
+        <v>0</v>
+      </c>
+      <c r="K218" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L218" s="27">
+        <v>0</v>
+      </c>
+      <c r="M218" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="N218" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" s="56" customFormat="1" ht="16.5">
+      <c r="A219" s="56">
+        <v>10550111</v>
+      </c>
+      <c r="B219" s="56">
+        <v>105501</v>
+      </c>
+      <c r="C219" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="D219" s="57">
+        <v>105501001</v>
+      </c>
+      <c r="E219" s="58">
+        <v>12</v>
+      </c>
+      <c r="F219" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="G219" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H219" s="29">
+        <v>0</v>
+      </c>
+      <c r="I219" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J219" s="24">
+        <v>0</v>
+      </c>
+      <c r="K219" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L219" s="27">
+        <v>0</v>
+      </c>
+      <c r="M219" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="N219" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" s="56" customFormat="1" ht="16.5">
+      <c r="A220" s="56">
+        <v>10550112</v>
+      </c>
+      <c r="B220" s="56">
+        <v>105501</v>
+      </c>
+      <c r="C220" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="D220" s="57">
+        <v>105501001</v>
+      </c>
+      <c r="E220" s="58">
+        <v>13</v>
+      </c>
+      <c r="F220" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G220" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="H220" s="29">
+        <v>0</v>
+      </c>
+      <c r="I220" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J220" s="24">
+        <v>0</v>
+      </c>
+      <c r="K220" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L220" s="27">
+        <v>0</v>
+      </c>
+      <c r="M220" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="N220" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" s="59" customFormat="1" ht="16.5">
+      <c r="A221" s="59">
+        <v>10550210</v>
+      </c>
+      <c r="B221" s="59">
+        <v>105502</v>
+      </c>
+      <c r="C221" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="D221" s="60">
+        <v>105502001</v>
+      </c>
+      <c r="E221" s="61">
+        <v>11</v>
+      </c>
+      <c r="F221" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="G221" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="H221" s="64">
+        <v>0</v>
+      </c>
+      <c r="I221" s="65">
+        <v>9600</v>
+      </c>
+      <c r="J221" s="65">
+        <v>0</v>
+      </c>
+      <c r="K221" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L221" s="66">
+        <v>0</v>
+      </c>
+      <c r="M221" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="N221" s="62" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" s="59" customFormat="1" ht="16.5">
+      <c r="A222" s="59">
+        <v>10550211</v>
+      </c>
+      <c r="B222" s="59">
+        <v>105502</v>
+      </c>
+      <c r="C222" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="D222" s="60">
+        <v>105502001</v>
+      </c>
+      <c r="E222" s="61">
+        <v>12</v>
+      </c>
+      <c r="F222" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="G222" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="H222" s="64">
+        <v>0</v>
+      </c>
+      <c r="I222" s="65">
+        <v>9600</v>
+      </c>
+      <c r="J222" s="65">
+        <v>0</v>
+      </c>
+      <c r="K222" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L222" s="66">
+        <v>0</v>
+      </c>
+      <c r="M222" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="N222" s="62" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" s="59" customFormat="1" ht="16.5">
+      <c r="A223" s="59">
+        <v>10550212</v>
+      </c>
+      <c r="B223" s="59">
+        <v>105502</v>
+      </c>
+      <c r="C223" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="D223" s="60">
+        <v>105502001</v>
+      </c>
+      <c r="E223" s="61">
+        <v>13</v>
+      </c>
+      <c r="F223" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="G223" s="63" t="s">
+        <v>78</v>
+      </c>
+      <c r="H223" s="64">
+        <v>0</v>
+      </c>
+      <c r="I223" s="65">
+        <v>9600</v>
+      </c>
+      <c r="J223" s="65">
+        <v>0</v>
+      </c>
+      <c r="K223" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L223" s="66">
+        <v>0</v>
+      </c>
+      <c r="M223" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="N223" s="62" t="s">
         <v>125</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="136">
   <si>
     <t>id</t>
   </si>
@@ -566,6 +566,9 @@
     <t>德古拉黑暗财富</t>
   </si>
   <si>
+    <t>赏金大对决</t>
+  </si>
+  <si>
     <t>1980000_500000</t>
   </si>
   <si>
@@ -579,9 +582,6 @@
   </si>
   <si>
     <t>招财猫</t>
-  </si>
-  <si>
-    <t>赏金大对决</t>
   </si>
   <si>
     <t>极速糖果1000</t>
@@ -808,7 +808,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -821,14 +820,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -838,16 +838,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1911,7 +1911,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T295"/>
+  <dimension ref="A1:T298"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -7488,177 +7488,177 @@
       <c r="S112" s="48"/>
       <c r="T112" s="48"/>
     </row>
-    <row r="113" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A113" s="49">
-        <v>10010010</v>
-      </c>
-      <c r="B113" s="49">
-        <v>100100</v>
-      </c>
-      <c r="C113" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D113" s="51">
-        <v>100100026</v>
-      </c>
-      <c r="E113" s="52">
-        <v>10</v>
+    <row r="113" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A113" s="46">
+        <v>1057001</v>
+      </c>
+      <c r="B113" s="46">
+        <v>105700</v>
+      </c>
+      <c r="C113" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D113" s="35">
+        <v>105700001</v>
+      </c>
+      <c r="E113" s="13">
+        <v>1</v>
       </c>
       <c r="F113" s="24" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="G113" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="H113" s="53">
-        <v>0</v>
-      </c>
-      <c r="I113" s="45">
-        <v>9500</v>
-      </c>
-      <c r="J113" s="54">
-        <v>0</v>
-      </c>
-      <c r="K113" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L113" s="55">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="H113" s="31">
+        <v>10000000</v>
+      </c>
+      <c r="I113" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J113" s="26">
+        <v>5000000</v>
+      </c>
+      <c r="K113" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L113" s="29">
+        <v>100</v>
       </c>
       <c r="M113" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N113" s="56" t="s">
+      <c r="N113" s="24">
+        <v>0</v>
+      </c>
+      <c r="O113" s="47"/>
+      <c r="P113" s="47"/>
+      <c r="Q113" s="47"/>
+      <c r="R113" s="47"/>
+      <c r="S113" s="48"/>
+      <c r="T113" s="48"/>
+    </row>
+    <row r="114" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A114" s="46">
+        <v>1057002</v>
+      </c>
+      <c r="B114" s="46">
+        <v>105700</v>
+      </c>
+      <c r="C114" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="O113" s="44"/>
-      <c r="P113" s="44"/>
-      <c r="Q113" s="44"/>
-      <c r="R113" s="44"/>
-      <c r="S113" s="45"/>
-      <c r="T113" s="45"/>
-    </row>
-    <row r="114" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A114" s="49">
-        <v>10010011</v>
-      </c>
-      <c r="B114" s="49">
-        <v>100100</v>
-      </c>
-      <c r="C114" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D114" s="51">
-        <v>100100026</v>
-      </c>
-      <c r="E114" s="52">
-        <v>11</v>
+      <c r="D114" s="35">
+        <v>105700001</v>
+      </c>
+      <c r="E114" s="13">
+        <v>2</v>
       </c>
       <c r="F114" s="24" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="G114" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="H114" s="53">
-        <v>0</v>
-      </c>
-      <c r="I114" s="45">
-        <v>9500</v>
-      </c>
-      <c r="J114" s="54">
-        <v>0</v>
-      </c>
-      <c r="K114" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L114" s="55">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="H114" s="31">
+        <v>100000000</v>
+      </c>
+      <c r="I114" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J114" s="26">
+        <v>50000000</v>
+      </c>
+      <c r="K114" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L114" s="29">
+        <v>100</v>
       </c>
       <c r="M114" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="N114" s="56" t="s">
-        <v>127</v>
-      </c>
-      <c r="O114" s="44"/>
-      <c r="P114" s="44"/>
-      <c r="Q114" s="44"/>
-      <c r="R114" s="44"/>
-      <c r="S114" s="45"/>
-      <c r="T114" s="45"/>
-    </row>
-    <row r="115" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A115" s="49">
-        <v>10010012</v>
-      </c>
-      <c r="B115" s="49">
-        <v>100100</v>
-      </c>
-      <c r="C115" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D115" s="51">
-        <v>100100026</v>
-      </c>
-      <c r="E115" s="52">
-        <v>12</v>
+      <c r="N114" s="24">
+        <v>0</v>
+      </c>
+      <c r="O114" s="47"/>
+      <c r="P114" s="47"/>
+      <c r="Q114" s="47"/>
+      <c r="R114" s="47"/>
+      <c r="S114" s="48"/>
+      <c r="T114" s="48"/>
+    </row>
+    <row r="115" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A115" s="46">
+        <v>1057003</v>
+      </c>
+      <c r="B115" s="46">
+        <v>105700</v>
+      </c>
+      <c r="C115" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D115" s="35">
+        <v>105700001</v>
+      </c>
+      <c r="E115" s="13">
+        <v>3</v>
       </c>
       <c r="F115" s="24" t="s">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="G115" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="H115" s="57">
-        <v>0</v>
-      </c>
-      <c r="I115" s="45">
-        <v>9500</v>
-      </c>
-      <c r="J115" s="54">
-        <v>0</v>
-      </c>
-      <c r="K115" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L115" s="55">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="H115" s="31">
+        <v>1000000000</v>
+      </c>
+      <c r="I115" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J115" s="26">
+        <v>500000000</v>
+      </c>
+      <c r="K115" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L115" s="29">
+        <v>100</v>
       </c>
       <c r="M115" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="N115" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="O115" s="44"/>
-      <c r="P115" s="44"/>
-      <c r="Q115" s="44"/>
-      <c r="R115" s="44"/>
-      <c r="S115" s="45"/>
-      <c r="T115" s="45"/>
+      <c r="N115" s="24">
+        <v>0</v>
+      </c>
+      <c r="O115" s="47"/>
+      <c r="P115" s="47"/>
+      <c r="Q115" s="47"/>
+      <c r="R115" s="47"/>
+      <c r="S115" s="48"/>
+      <c r="T115" s="48"/>
     </row>
     <row r="116" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A116" s="49">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B116" s="49">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C116" s="50" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D116" s="51">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E116" s="52">
         <v>10</v>
       </c>
       <c r="F116" s="24" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G116" s="25" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H116" s="53">
         <v>0</v>
@@ -7672,14 +7672,14 @@
       <c r="K116" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L116" s="58">
+      <c r="L116" s="55">
         <v>0</v>
       </c>
       <c r="M116" s="26" t="s">
         <v>37</v>
       </c>
       <c r="N116" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O116" s="44"/>
       <c r="P116" s="44"/>
@@ -7690,25 +7690,25 @@
     </row>
     <row r="117" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A117" s="49">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B117" s="49">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C117" s="50" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D117" s="51">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E117" s="52">
         <v>11</v>
       </c>
       <c r="F117" s="24" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G117" s="25" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H117" s="53">
         <v>0</v>
@@ -7722,14 +7722,14 @@
       <c r="K117" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L117" s="58">
+      <c r="L117" s="55">
         <v>0</v>
       </c>
       <c r="M117" s="26" t="s">
         <v>40</v>
       </c>
       <c r="N117" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O117" s="44"/>
       <c r="P117" s="44"/>
@@ -7740,25 +7740,25 @@
     </row>
     <row r="118" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A118" s="49">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B118" s="49">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C118" s="50" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D118" s="51">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E118" s="52">
         <v>12</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G118" s="25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H118" s="57">
         <v>0</v>
@@ -7772,14 +7772,14 @@
       <c r="K118" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L118" s="58">
+      <c r="L118" s="55">
         <v>0</v>
       </c>
       <c r="M118" s="26" t="s">
         <v>43</v>
       </c>
       <c r="N118" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O118" s="44"/>
       <c r="P118" s="44"/>
@@ -7790,25 +7790,25 @@
     </row>
     <row r="119" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A119" s="49">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B119" s="49">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C119" s="50" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D119" s="51">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E119" s="52">
         <v>10</v>
       </c>
       <c r="F119" s="24" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G119" s="25" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H119" s="53">
         <v>0</v>
@@ -7822,14 +7822,14 @@
       <c r="K119" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L119" s="55">
+      <c r="L119" s="58">
         <v>0</v>
       </c>
       <c r="M119" s="26" t="s">
         <v>37</v>
       </c>
       <c r="N119" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O119" s="44"/>
       <c r="P119" s="44"/>
@@ -7840,25 +7840,25 @@
     </row>
     <row r="120" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A120" s="49">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B120" s="49">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C120" s="50" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D120" s="51">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E120" s="52">
         <v>11</v>
       </c>
       <c r="F120" s="24" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G120" s="25" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H120" s="53">
         <v>0</v>
@@ -7872,14 +7872,14 @@
       <c r="K120" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L120" s="55">
+      <c r="L120" s="58">
         <v>0</v>
       </c>
       <c r="M120" s="26" t="s">
         <v>40</v>
       </c>
       <c r="N120" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O120" s="44"/>
       <c r="P120" s="44"/>
@@ -7890,25 +7890,25 @@
     </row>
     <row r="121" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A121" s="49">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B121" s="49">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C121" s="50" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D121" s="51">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E121" s="52">
         <v>12</v>
       </c>
       <c r="F121" s="24" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G121" s="25" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H121" s="57">
         <v>0</v>
@@ -7922,14 +7922,14 @@
       <c r="K121" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L121" s="55">
+      <c r="L121" s="58">
         <v>0</v>
       </c>
       <c r="M121" s="26" t="s">
         <v>43</v>
       </c>
       <c r="N121" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O121" s="44"/>
       <c r="P121" s="44"/>
@@ -7938,168 +7938,168 @@
       <c r="S121" s="45"/>
       <c r="T121" s="45"/>
     </row>
-    <row r="122" s="6" customFormat="1" ht="16.5" spans="1:20">
+    <row r="122" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A122" s="49">
-        <v>10120010</v>
-      </c>
-      <c r="B122" s="59">
-        <v>101200</v>
-      </c>
-      <c r="C122" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="D122" s="60">
-        <v>101200001</v>
+        <v>10070010</v>
+      </c>
+      <c r="B122" s="49">
+        <v>100700</v>
+      </c>
+      <c r="C122" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D122" s="51">
+        <v>100700001</v>
       </c>
       <c r="E122" s="52">
         <v>10</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G122" s="25" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H122" s="53">
         <v>0</v>
       </c>
-      <c r="I122" s="54">
+      <c r="I122" s="45">
         <v>9500</v>
       </c>
       <c r="J122" s="54">
         <v>0</v>
       </c>
-      <c r="K122" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L122" s="58">
+      <c r="K122" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L122" s="55">
         <v>0</v>
       </c>
       <c r="M122" s="26" t="s">
         <v>37</v>
       </c>
       <c r="N122" s="56" t="s">
-        <v>126</v>
-      </c>
-      <c r="O122" s="56"/>
-      <c r="P122" s="56"/>
-      <c r="Q122" s="56"/>
-      <c r="R122" s="56"/>
-      <c r="S122" s="54"/>
-      <c r="T122" s="54"/>
-    </row>
-    <row r="123" s="6" customFormat="1" ht="16.5" spans="1:20">
+        <v>127</v>
+      </c>
+      <c r="O122" s="44"/>
+      <c r="P122" s="44"/>
+      <c r="Q122" s="44"/>
+      <c r="R122" s="44"/>
+      <c r="S122" s="45"/>
+      <c r="T122" s="45"/>
+    </row>
+    <row r="123" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A123" s="49">
-        <v>10120011</v>
-      </c>
-      <c r="B123" s="59">
-        <v>101200</v>
-      </c>
-      <c r="C123" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="D123" s="60">
-        <v>101200001</v>
+        <v>10070011</v>
+      </c>
+      <c r="B123" s="49">
+        <v>100700</v>
+      </c>
+      <c r="C123" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D123" s="51">
+        <v>100700001</v>
       </c>
       <c r="E123" s="52">
         <v>11</v>
       </c>
       <c r="F123" s="24" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G123" s="25" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H123" s="53">
         <v>0</v>
       </c>
-      <c r="I123" s="54">
+      <c r="I123" s="45">
         <v>9500</v>
       </c>
       <c r="J123" s="54">
         <v>0</v>
       </c>
-      <c r="K123" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L123" s="58">
+      <c r="K123" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L123" s="55">
         <v>0</v>
       </c>
       <c r="M123" s="26" t="s">
         <v>40</v>
       </c>
       <c r="N123" s="56" t="s">
-        <v>127</v>
-      </c>
-      <c r="O123" s="56"/>
-      <c r="P123" s="56"/>
-      <c r="Q123" s="56"/>
-      <c r="R123" s="56"/>
-      <c r="S123" s="54"/>
-      <c r="T123" s="54"/>
-    </row>
-    <row r="124" s="6" customFormat="1" ht="16.5" spans="1:20">
+        <v>128</v>
+      </c>
+      <c r="O123" s="44"/>
+      <c r="P123" s="44"/>
+      <c r="Q123" s="44"/>
+      <c r="R123" s="44"/>
+      <c r="S123" s="45"/>
+      <c r="T123" s="45"/>
+    </row>
+    <row r="124" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A124" s="49">
-        <v>10120012</v>
-      </c>
-      <c r="B124" s="59">
-        <v>101200</v>
-      </c>
-      <c r="C124" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="D124" s="60">
-        <v>101200001</v>
+        <v>10070012</v>
+      </c>
+      <c r="B124" s="49">
+        <v>100700</v>
+      </c>
+      <c r="C124" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D124" s="51">
+        <v>100700001</v>
       </c>
       <c r="E124" s="52">
         <v>12</v>
       </c>
       <c r="F124" s="24" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G124" s="25" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H124" s="57">
         <v>0</v>
       </c>
-      <c r="I124" s="54">
+      <c r="I124" s="45">
         <v>9500</v>
       </c>
       <c r="J124" s="54">
         <v>0</v>
       </c>
-      <c r="K124" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L124" s="58">
+      <c r="K124" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L124" s="55">
         <v>0</v>
       </c>
       <c r="M124" s="26" t="s">
         <v>43</v>
       </c>
       <c r="N124" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="O124" s="56"/>
-      <c r="P124" s="56"/>
-      <c r="Q124" s="56"/>
-      <c r="R124" s="56"/>
-      <c r="S124" s="54"/>
-      <c r="T124" s="54"/>
-    </row>
-    <row r="125" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>129</v>
+      </c>
+      <c r="O124" s="44"/>
+      <c r="P124" s="44"/>
+      <c r="Q124" s="44"/>
+      <c r="R124" s="44"/>
+      <c r="S124" s="45"/>
+      <c r="T124" s="45"/>
+    </row>
+    <row r="125" s="6" customFormat="1" ht="16.5" spans="1:20">
       <c r="A125" s="49">
-        <v>10140010</v>
-      </c>
-      <c r="B125" s="49">
-        <v>101400</v>
-      </c>
-      <c r="C125" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="D125" s="51">
-        <v>101400001</v>
+        <v>10120010</v>
+      </c>
+      <c r="B125" s="59">
+        <v>101200</v>
+      </c>
+      <c r="C125" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D125" s="60">
+        <v>101200001</v>
       </c>
       <c r="E125" s="52">
         <v>10</v>
@@ -8113,43 +8113,43 @@
       <c r="H125" s="53">
         <v>0</v>
       </c>
-      <c r="I125" s="45">
+      <c r="I125" s="54">
         <v>9500</v>
       </c>
       <c r="J125" s="54">
         <v>0</v>
       </c>
-      <c r="K125" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L125" s="55">
+      <c r="K125" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="L125" s="58">
         <v>0</v>
       </c>
       <c r="M125" s="26" t="s">
         <v>37</v>
       </c>
       <c r="N125" s="56" t="s">
-        <v>126</v>
-      </c>
-      <c r="O125" s="44"/>
-      <c r="P125" s="44"/>
-      <c r="Q125" s="44"/>
-      <c r="R125" s="44"/>
-      <c r="S125" s="45"/>
-      <c r="T125" s="45"/>
-    </row>
-    <row r="126" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>127</v>
+      </c>
+      <c r="O125" s="56"/>
+      <c r="P125" s="56"/>
+      <c r="Q125" s="56"/>
+      <c r="R125" s="56"/>
+      <c r="S125" s="54"/>
+      <c r="T125" s="54"/>
+    </row>
+    <row r="126" s="6" customFormat="1" ht="16.5" spans="1:20">
       <c r="A126" s="49">
-        <v>10140011</v>
-      </c>
-      <c r="B126" s="49">
-        <v>101400</v>
-      </c>
-      <c r="C126" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="D126" s="51">
-        <v>101400001</v>
+        <v>10120011</v>
+      </c>
+      <c r="B126" s="59">
+        <v>101200</v>
+      </c>
+      <c r="C126" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D126" s="60">
+        <v>101200001</v>
       </c>
       <c r="E126" s="52">
         <v>11</v>
@@ -8163,43 +8163,43 @@
       <c r="H126" s="53">
         <v>0</v>
       </c>
-      <c r="I126" s="45">
+      <c r="I126" s="54">
         <v>9500</v>
       </c>
       <c r="J126" s="54">
         <v>0</v>
       </c>
-      <c r="K126" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L126" s="55">
+      <c r="K126" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="L126" s="58">
         <v>0</v>
       </c>
       <c r="M126" s="26" t="s">
         <v>40</v>
       </c>
       <c r="N126" s="56" t="s">
-        <v>127</v>
-      </c>
-      <c r="O126" s="44"/>
-      <c r="P126" s="44"/>
-      <c r="Q126" s="44"/>
-      <c r="R126" s="44"/>
-      <c r="S126" s="45"/>
-      <c r="T126" s="45"/>
-    </row>
-    <row r="127" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>128</v>
+      </c>
+      <c r="O126" s="56"/>
+      <c r="P126" s="56"/>
+      <c r="Q126" s="56"/>
+      <c r="R126" s="56"/>
+      <c r="S126" s="54"/>
+      <c r="T126" s="54"/>
+    </row>
+    <row r="127" s="6" customFormat="1" ht="16.5" spans="1:20">
       <c r="A127" s="49">
-        <v>10140012</v>
-      </c>
-      <c r="B127" s="49">
-        <v>101400</v>
-      </c>
-      <c r="C127" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="D127" s="51">
-        <v>101400001</v>
+        <v>10120012</v>
+      </c>
+      <c r="B127" s="59">
+        <v>101200</v>
+      </c>
+      <c r="C127" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D127" s="60">
+        <v>101200001</v>
       </c>
       <c r="E127" s="52">
         <v>12</v>
@@ -8213,52 +8213,52 @@
       <c r="H127" s="57">
         <v>0</v>
       </c>
-      <c r="I127" s="45">
+      <c r="I127" s="54">
         <v>9500</v>
       </c>
       <c r="J127" s="54">
         <v>0</v>
       </c>
-      <c r="K127" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L127" s="55">
+      <c r="K127" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="L127" s="58">
         <v>0</v>
       </c>
       <c r="M127" s="26" t="s">
         <v>43</v>
       </c>
       <c r="N127" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="O127" s="44"/>
-      <c r="P127" s="44"/>
-      <c r="Q127" s="44"/>
-      <c r="R127" s="44"/>
-      <c r="S127" s="45"/>
-      <c r="T127" s="45"/>
+        <v>129</v>
+      </c>
+      <c r="O127" s="56"/>
+      <c r="P127" s="56"/>
+      <c r="Q127" s="56"/>
+      <c r="R127" s="56"/>
+      <c r="S127" s="54"/>
+      <c r="T127" s="54"/>
     </row>
     <row r="128" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A128" s="49">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B128" s="49">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D128" s="51">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E128" s="52">
         <v>10</v>
       </c>
       <c r="F128" s="24" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G128" s="25" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H128" s="53">
         <v>0</v>
@@ -8279,7 +8279,7 @@
         <v>37</v>
       </c>
       <c r="N128" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O128" s="44"/>
       <c r="P128" s="44"/>
@@ -8290,25 +8290,25 @@
     </row>
     <row r="129" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A129" s="49">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B129" s="49">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D129" s="51">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E129" s="52">
         <v>11</v>
       </c>
       <c r="F129" s="24" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G129" s="25" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H129" s="53">
         <v>0</v>
@@ -8329,7 +8329,7 @@
         <v>40</v>
       </c>
       <c r="N129" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O129" s="44"/>
       <c r="P129" s="44"/>
@@ -8340,25 +8340,25 @@
     </row>
     <row r="130" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A130" s="49">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B130" s="49">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C130" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D130" s="51">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E130" s="52">
         <v>12</v>
       </c>
       <c r="F130" s="24" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G130" s="25" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H130" s="57">
         <v>0</v>
@@ -8379,7 +8379,7 @@
         <v>43</v>
       </c>
       <c r="N130" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O130" s="44"/>
       <c r="P130" s="44"/>
@@ -8390,16 +8390,16 @@
     </row>
     <row r="131" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A131" s="49">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B131" s="49">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D131" s="51">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E131" s="52">
         <v>10</v>
@@ -8422,14 +8422,14 @@
       <c r="K131" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L131" s="58">
+      <c r="L131" s="55">
         <v>0</v>
       </c>
       <c r="M131" s="26" t="s">
         <v>37</v>
       </c>
       <c r="N131" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O131" s="44"/>
       <c r="P131" s="44"/>
@@ -8440,16 +8440,16 @@
     </row>
     <row r="132" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A132" s="49">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B132" s="49">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D132" s="51">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E132" s="52">
         <v>11</v>
@@ -8472,14 +8472,14 @@
       <c r="K132" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L132" s="58">
+      <c r="L132" s="55">
         <v>0</v>
       </c>
       <c r="M132" s="26" t="s">
         <v>40</v>
       </c>
       <c r="N132" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O132" s="44"/>
       <c r="P132" s="44"/>
@@ -8490,16 +8490,16 @@
     </row>
     <row r="133" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A133" s="49">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B133" s="49">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D133" s="51">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E133" s="52">
         <v>12</v>
@@ -8522,14 +8522,14 @@
       <c r="K133" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L133" s="58">
+      <c r="L133" s="55">
         <v>0</v>
       </c>
       <c r="M133" s="26" t="s">
         <v>43</v>
       </c>
       <c r="N133" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O133" s="44"/>
       <c r="P133" s="44"/>
@@ -8540,16 +8540,16 @@
     </row>
     <row r="134" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A134" s="49">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B134" s="49">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D134" s="51">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E134" s="52">
         <v>10</v>
@@ -8579,7 +8579,7 @@
         <v>37</v>
       </c>
       <c r="N134" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O134" s="44"/>
       <c r="P134" s="44"/>
@@ -8590,16 +8590,16 @@
     </row>
     <row r="135" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A135" s="49">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B135" s="49">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D135" s="51">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E135" s="52">
         <v>11</v>
@@ -8629,7 +8629,7 @@
         <v>40</v>
       </c>
       <c r="N135" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O135" s="44"/>
       <c r="P135" s="44"/>
@@ -8640,16 +8640,16 @@
     </row>
     <row r="136" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A136" s="49">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B136" s="49">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D136" s="51">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E136" s="52">
         <v>12</v>
@@ -8679,7 +8679,7 @@
         <v>43</v>
       </c>
       <c r="N136" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O136" s="44"/>
       <c r="P136" s="44"/>
@@ -8690,25 +8690,25 @@
     </row>
     <row r="137" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A137" s="49">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B137" s="49">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D137" s="51">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E137" s="52">
         <v>10</v>
       </c>
       <c r="F137" s="24" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G137" s="25" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H137" s="53">
         <v>0</v>
@@ -8729,7 +8729,7 @@
         <v>37</v>
       </c>
       <c r="N137" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O137" s="44"/>
       <c r="P137" s="44"/>
@@ -8740,25 +8740,25 @@
     </row>
     <row r="138" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A138" s="49">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B138" s="49">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D138" s="51">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E138" s="52">
         <v>11</v>
       </c>
       <c r="F138" s="24" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G138" s="25" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H138" s="53">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>40</v>
       </c>
       <c r="N138" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O138" s="44"/>
       <c r="P138" s="44"/>
@@ -8790,25 +8790,25 @@
     </row>
     <row r="139" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A139" s="49">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B139" s="49">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D139" s="51">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E139" s="52">
         <v>12</v>
       </c>
       <c r="F139" s="24" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G139" s="25" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H139" s="57">
         <v>0</v>
@@ -8829,7 +8829,7 @@
         <v>43</v>
       </c>
       <c r="N139" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O139" s="44"/>
       <c r="P139" s="44"/>
@@ -8840,27 +8840,27 @@
     </row>
     <row r="140" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A140" s="49">
-        <v>10180010</v>
+        <v>10240010</v>
       </c>
       <c r="B140" s="49">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C140" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D140" s="51">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E140" s="52">
         <v>10</v>
       </c>
       <c r="F140" s="24" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G140" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H140" s="57">
+        <v>35</v>
+      </c>
+      <c r="H140" s="53">
         <v>0</v>
       </c>
       <c r="I140" s="45">
@@ -8879,7 +8879,7 @@
         <v>37</v>
       </c>
       <c r="N140" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O140" s="44"/>
       <c r="P140" s="44"/>
@@ -8890,27 +8890,27 @@
     </row>
     <row r="141" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A141" s="49">
-        <v>10180011</v>
+        <v>10240011</v>
       </c>
       <c r="B141" s="49">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D141" s="51">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E141" s="52">
         <v>11</v>
       </c>
       <c r="F141" s="24" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G141" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="H141" s="57">
+        <v>39</v>
+      </c>
+      <c r="H141" s="53">
         <v>0</v>
       </c>
       <c r="I141" s="45">
@@ -8929,7 +8929,7 @@
         <v>40</v>
       </c>
       <c r="N141" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O141" s="44"/>
       <c r="P141" s="44"/>
@@ -8940,25 +8940,25 @@
     </row>
     <row r="142" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A142" s="49">
-        <v>10180012</v>
+        <v>10240012</v>
       </c>
       <c r="B142" s="49">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D142" s="51">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E142" s="52">
         <v>12</v>
       </c>
       <c r="F142" s="24" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G142" s="25" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H142" s="57">
         <v>0</v>
@@ -8979,7 +8979,7 @@
         <v>43</v>
       </c>
       <c r="N142" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O142" s="44"/>
       <c r="P142" s="44"/>
@@ -8990,25 +8990,25 @@
     </row>
     <row r="143" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A143" s="49">
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B143" s="49">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D143" s="51">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E143" s="52">
         <v>10</v>
       </c>
       <c r="F143" s="24" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G143" s="25" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H143" s="57">
         <v>0</v>
@@ -9029,7 +9029,7 @@
         <v>37</v>
       </c>
       <c r="N143" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O143" s="44"/>
       <c r="P143" s="44"/>
@@ -9040,25 +9040,25 @@
     </row>
     <row r="144" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A144" s="49">
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B144" s="49">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D144" s="51">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E144" s="52">
         <v>11</v>
       </c>
       <c r="F144" s="24" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G144" s="25" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="H144" s="57">
         <v>0</v>
@@ -9079,7 +9079,7 @@
         <v>40</v>
       </c>
       <c r="N144" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O144" s="44"/>
       <c r="P144" s="44"/>
@@ -9090,25 +9090,25 @@
     </row>
     <row r="145" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A145" s="49">
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B145" s="49">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D145" s="51">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E145" s="52">
         <v>12</v>
       </c>
       <c r="F145" s="24" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G145" s="25" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H145" s="57">
         <v>0</v>
@@ -9129,7 +9129,7 @@
         <v>43</v>
       </c>
       <c r="N145" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O145" s="44"/>
       <c r="P145" s="44"/>
@@ -9140,25 +9140,25 @@
     </row>
     <row r="146" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A146" s="49">
-        <v>10230010</v>
+        <v>10250010</v>
       </c>
       <c r="B146" s="49">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D146" s="51">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E146" s="52">
         <v>10</v>
       </c>
       <c r="F146" s="24" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G146" s="25" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H146" s="57">
         <v>0</v>
@@ -9179,7 +9179,7 @@
         <v>37</v>
       </c>
       <c r="N146" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O146" s="44"/>
       <c r="P146" s="44"/>
@@ -9190,25 +9190,25 @@
     </row>
     <row r="147" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A147" s="49">
-        <v>10230011</v>
+        <v>10250011</v>
       </c>
       <c r="B147" s="49">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D147" s="51">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E147" s="52">
         <v>11</v>
       </c>
       <c r="F147" s="24" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G147" s="25" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H147" s="57">
         <v>0</v>
@@ -9229,7 +9229,7 @@
         <v>40</v>
       </c>
       <c r="N147" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O147" s="44"/>
       <c r="P147" s="44"/>
@@ -9240,25 +9240,25 @@
     </row>
     <row r="148" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A148" s="49">
-        <v>10230012</v>
+        <v>10250012</v>
       </c>
       <c r="B148" s="49">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C148" s="50" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D148" s="51">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E148" s="52">
         <v>12</v>
       </c>
       <c r="F148" s="24" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G148" s="25" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="H148" s="57">
         <v>0</v>
@@ -9279,7 +9279,7 @@
         <v>43</v>
       </c>
       <c r="N148" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O148" s="44"/>
       <c r="P148" s="44"/>
@@ -9290,25 +9290,25 @@
     </row>
     <row r="149" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A149" s="49">
-        <v>10340010</v>
+        <v>10230010</v>
       </c>
       <c r="B149" s="49">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D149" s="51">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E149" s="52">
         <v>10</v>
       </c>
       <c r="F149" s="24" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G149" s="25" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H149" s="57">
         <v>0</v>
@@ -9329,7 +9329,7 @@
         <v>37</v>
       </c>
       <c r="N149" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O149" s="44"/>
       <c r="P149" s="44"/>
@@ -9340,25 +9340,25 @@
     </row>
     <row r="150" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A150" s="49">
-        <v>10340011</v>
+        <v>10230011</v>
       </c>
       <c r="B150" s="49">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D150" s="51">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E150" s="52">
         <v>11</v>
       </c>
       <c r="F150" s="24" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G150" s="25" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H150" s="57">
         <v>0</v>
@@ -9379,7 +9379,7 @@
         <v>40</v>
       </c>
       <c r="N150" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O150" s="44"/>
       <c r="P150" s="44"/>
@@ -9390,25 +9390,25 @@
     </row>
     <row r="151" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A151" s="49">
-        <v>10340012</v>
+        <v>10230012</v>
       </c>
       <c r="B151" s="49">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C151" s="50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D151" s="51">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E151" s="52">
         <v>12</v>
       </c>
       <c r="F151" s="24" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="G151" s="25" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H151" s="57">
         <v>0</v>
@@ -9429,7 +9429,7 @@
         <v>43</v>
       </c>
       <c r="N151" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O151" s="44"/>
       <c r="P151" s="44"/>
@@ -9440,25 +9440,25 @@
     </row>
     <row r="152" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A152" s="49">
-        <v>10350010</v>
+        <v>10340010</v>
       </c>
       <c r="B152" s="49">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C152" s="50" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D152" s="51">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E152" s="52">
         <v>10</v>
       </c>
       <c r="F152" s="24" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G152" s="25" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="H152" s="57">
         <v>0</v>
@@ -9479,7 +9479,7 @@
         <v>37</v>
       </c>
       <c r="N152" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O152" s="44"/>
       <c r="P152" s="44"/>
@@ -9490,25 +9490,25 @@
     </row>
     <row r="153" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A153" s="49">
-        <v>10350011</v>
+        <v>10340011</v>
       </c>
       <c r="B153" s="49">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D153" s="51">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E153" s="52">
         <v>11</v>
       </c>
       <c r="F153" s="24" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G153" s="25" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H153" s="57">
         <v>0</v>
@@ -9529,7 +9529,7 @@
         <v>40</v>
       </c>
       <c r="N153" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O153" s="44"/>
       <c r="P153" s="44"/>
@@ -9540,25 +9540,25 @@
     </row>
     <row r="154" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A154" s="49">
-        <v>10350012</v>
+        <v>10340012</v>
       </c>
       <c r="B154" s="49">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D154" s="51">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E154" s="52">
         <v>12</v>
       </c>
       <c r="F154" s="24" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G154" s="25" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="H154" s="57">
         <v>0</v>
@@ -9579,7 +9579,7 @@
         <v>43</v>
       </c>
       <c r="N154" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O154" s="44"/>
       <c r="P154" s="44"/>
@@ -9590,16 +9590,16 @@
     </row>
     <row r="155" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A155" s="49">
-        <v>10350110</v>
+        <v>10350010</v>
       </c>
       <c r="B155" s="49">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D155" s="51">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E155" s="52">
         <v>10</v>
@@ -9629,7 +9629,7 @@
         <v>37</v>
       </c>
       <c r="N155" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O155" s="44"/>
       <c r="P155" s="44"/>
@@ -9640,16 +9640,16 @@
     </row>
     <row r="156" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A156" s="49">
-        <v>10350111</v>
+        <v>10350011</v>
       </c>
       <c r="B156" s="49">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D156" s="51">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E156" s="52">
         <v>11</v>
@@ -9679,7 +9679,7 @@
         <v>40</v>
       </c>
       <c r="N156" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O156" s="44"/>
       <c r="P156" s="44"/>
@@ -9690,16 +9690,16 @@
     </row>
     <row r="157" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A157" s="49">
-        <v>10350112</v>
+        <v>10350012</v>
       </c>
       <c r="B157" s="49">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C157" s="50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D157" s="51">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E157" s="52">
         <v>12</v>
@@ -9729,7 +9729,7 @@
         <v>43</v>
       </c>
       <c r="N157" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O157" s="44"/>
       <c r="P157" s="44"/>
@@ -9740,27 +9740,27 @@
     </row>
     <row r="158" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A158" s="49">
-        <v>10360010</v>
+        <v>10350110</v>
       </c>
       <c r="B158" s="49">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C158" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D158" s="51">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E158" s="52">
         <v>10</v>
       </c>
       <c r="F158" s="24" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="G158" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H158" s="53">
+        <v>39</v>
+      </c>
+      <c r="H158" s="57">
         <v>0</v>
       </c>
       <c r="I158" s="45">
@@ -9779,7 +9779,7 @@
         <v>37</v>
       </c>
       <c r="N158" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O158" s="44"/>
       <c r="P158" s="44"/>
@@ -9790,27 +9790,27 @@
     </row>
     <row r="159" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A159" s="49">
-        <v>10360011</v>
+        <v>10350111</v>
       </c>
       <c r="B159" s="49">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C159" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D159" s="51">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E159" s="52">
         <v>11</v>
       </c>
       <c r="F159" s="24" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G159" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="H159" s="53">
+        <v>42</v>
+      </c>
+      <c r="H159" s="57">
         <v>0</v>
       </c>
       <c r="I159" s="45">
@@ -9829,7 +9829,7 @@
         <v>40</v>
       </c>
       <c r="N159" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O159" s="44"/>
       <c r="P159" s="44"/>
@@ -9840,25 +9840,25 @@
     </row>
     <row r="160" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A160" s="49">
-        <v>10360012</v>
+        <v>10350112</v>
       </c>
       <c r="B160" s="49">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C160" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D160" s="51">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E160" s="52">
         <v>12</v>
       </c>
       <c r="F160" s="24" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="G160" s="25" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H160" s="57">
         <v>0</v>
@@ -9879,7 +9879,7 @@
         <v>43</v>
       </c>
       <c r="N160" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O160" s="44"/>
       <c r="P160" s="44"/>
@@ -9890,27 +9890,27 @@
     </row>
     <row r="161" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A161" s="49">
-        <v>10280010</v>
+        <v>10360010</v>
       </c>
       <c r="B161" s="49">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C161" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D161" s="51">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E161" s="52">
         <v>10</v>
       </c>
       <c r="F161" s="24" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G161" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H161" s="57">
+        <v>71</v>
+      </c>
+      <c r="H161" s="53">
         <v>0</v>
       </c>
       <c r="I161" s="45">
@@ -9929,7 +9929,7 @@
         <v>37</v>
       </c>
       <c r="N161" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O161" s="44"/>
       <c r="P161" s="44"/>
@@ -9940,27 +9940,27 @@
     </row>
     <row r="162" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A162" s="49">
-        <v>10280011</v>
+        <v>10360011</v>
       </c>
       <c r="B162" s="49">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C162" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D162" s="51">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E162" s="52">
         <v>11</v>
       </c>
       <c r="F162" s="24" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G162" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="H162" s="57">
+        <v>73</v>
+      </c>
+      <c r="H162" s="53">
         <v>0</v>
       </c>
       <c r="I162" s="45">
@@ -9979,7 +9979,7 @@
         <v>40</v>
       </c>
       <c r="N162" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O162" s="44"/>
       <c r="P162" s="44"/>
@@ -9990,25 +9990,25 @@
     </row>
     <row r="163" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A163" s="49">
-        <v>10280012</v>
+        <v>10360012</v>
       </c>
       <c r="B163" s="49">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C163" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D163" s="51">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E163" s="52">
         <v>12</v>
       </c>
       <c r="F163" s="24" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="G163" s="25" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="H163" s="57">
         <v>0</v>
@@ -10029,7 +10029,7 @@
         <v>43</v>
       </c>
       <c r="N163" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O163" s="44"/>
       <c r="P163" s="44"/>
@@ -10040,25 +10040,25 @@
     </row>
     <row r="164" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A164" s="49">
-        <v>10200010</v>
+        <v>10280010</v>
       </c>
       <c r="B164" s="49">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C164" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D164" s="51">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E164" s="52">
         <v>10</v>
       </c>
       <c r="F164" s="24" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G164" s="25" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="H164" s="57">
         <v>0</v>
@@ -10079,7 +10079,7 @@
         <v>37</v>
       </c>
       <c r="N164" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O164" s="44"/>
       <c r="P164" s="44"/>
@@ -10090,25 +10090,25 @@
     </row>
     <row r="165" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A165" s="49">
-        <v>10200011</v>
+        <v>10280011</v>
       </c>
       <c r="B165" s="49">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C165" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D165" s="51">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E165" s="52">
         <v>11</v>
       </c>
       <c r="F165" s="24" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="G165" s="25" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="H165" s="57">
         <v>0</v>
@@ -10129,7 +10129,7 @@
         <v>40</v>
       </c>
       <c r="N165" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O165" s="44"/>
       <c r="P165" s="44"/>
@@ -10140,25 +10140,25 @@
     </row>
     <row r="166" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A166" s="49">
-        <v>10200012</v>
+        <v>10280012</v>
       </c>
       <c r="B166" s="49">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C166" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D166" s="51">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E166" s="52">
         <v>12</v>
       </c>
       <c r="F166" s="24" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="G166" s="25" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="H166" s="57">
         <v>0</v>
@@ -10179,7 +10179,7 @@
         <v>43</v>
       </c>
       <c r="N166" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O166" s="44"/>
       <c r="P166" s="44"/>
@@ -10190,25 +10190,25 @@
     </row>
     <row r="167" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A167" s="49">
-        <v>10340110</v>
+        <v>10200010</v>
       </c>
       <c r="B167" s="49">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C167" s="50" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D167" s="51">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E167" s="52">
         <v>10</v>
       </c>
       <c r="F167" s="24" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G167" s="25" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H167" s="57">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>37</v>
       </c>
       <c r="N167" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O167" s="44"/>
       <c r="P167" s="44"/>
@@ -10240,25 +10240,25 @@
     </row>
     <row r="168" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A168" s="49">
-        <v>10340111</v>
+        <v>10200011</v>
       </c>
       <c r="B168" s="49">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C168" s="50" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D168" s="51">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E168" s="52">
         <v>11</v>
       </c>
       <c r="F168" s="24" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G168" s="25" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="H168" s="57">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>40</v>
       </c>
       <c r="N168" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O168" s="44"/>
       <c r="P168" s="44"/>
@@ -10290,25 +10290,25 @@
     </row>
     <row r="169" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A169" s="49">
-        <v>10340112</v>
+        <v>10200012</v>
       </c>
       <c r="B169" s="49">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C169" s="50" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D169" s="51">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E169" s="52">
         <v>12</v>
       </c>
       <c r="F169" s="24" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G169" s="25" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H169" s="57">
         <v>0</v>
@@ -10329,7 +10329,7 @@
         <v>43</v>
       </c>
       <c r="N169" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O169" s="44"/>
       <c r="P169" s="44"/>
@@ -10340,25 +10340,25 @@
     </row>
     <row r="170" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A170" s="49">
-        <v>10380010</v>
+        <v>10340110</v>
       </c>
       <c r="B170" s="49">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C170" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D170" s="51">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E170" s="52">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F170" s="24" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G170" s="25" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="H170" s="57">
         <v>0</v>
@@ -10379,7 +10379,7 @@
         <v>37</v>
       </c>
       <c r="N170" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O170" s="44"/>
       <c r="P170" s="44"/>
@@ -10390,25 +10390,25 @@
     </row>
     <row r="171" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A171" s="49">
-        <v>10380011</v>
+        <v>10340111</v>
       </c>
       <c r="B171" s="49">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C171" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D171" s="51">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E171" s="52">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F171" s="24" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="G171" s="25" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H171" s="57">
         <v>0</v>
@@ -10429,7 +10429,7 @@
         <v>40</v>
       </c>
       <c r="N171" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O171" s="44"/>
       <c r="P171" s="44"/>
@@ -10440,25 +10440,25 @@
     </row>
     <row r="172" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A172" s="49">
-        <v>10380012</v>
+        <v>10340112</v>
       </c>
       <c r="B172" s="49">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C172" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D172" s="51">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E172" s="52">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F172" s="24" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G172" s="25" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="H172" s="57">
         <v>0</v>
@@ -10479,7 +10479,7 @@
         <v>43</v>
       </c>
       <c r="N172" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O172" s="44"/>
       <c r="P172" s="44"/>
@@ -10490,25 +10490,25 @@
     </row>
     <row r="173" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A173" s="49">
-        <v>10270010</v>
+        <v>10380010</v>
       </c>
       <c r="B173" s="49">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C173" s="50" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D173" s="51">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E173" s="52">
         <v>11</v>
       </c>
       <c r="F173" s="24" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G173" s="25" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="H173" s="57">
         <v>0</v>
@@ -10529,7 +10529,7 @@
         <v>37</v>
       </c>
       <c r="N173" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O173" s="44"/>
       <c r="P173" s="44"/>
@@ -10540,25 +10540,25 @@
     </row>
     <row r="174" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A174" s="49">
-        <v>10270011</v>
+        <v>10380011</v>
       </c>
       <c r="B174" s="49">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C174" s="50" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D174" s="51">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E174" s="52">
         <v>12</v>
       </c>
       <c r="F174" s="24" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="G174" s="25" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="H174" s="57">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>40</v>
       </c>
       <c r="N174" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O174" s="44"/>
       <c r="P174" s="44"/>
@@ -10590,25 +10590,25 @@
     </row>
     <row r="175" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A175" s="49">
-        <v>10270012</v>
+        <v>10380012</v>
       </c>
       <c r="B175" s="49">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C175" s="50" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D175" s="51">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E175" s="52">
         <v>13</v>
       </c>
       <c r="F175" s="24" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="G175" s="25" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="H175" s="57">
         <v>0</v>
@@ -10629,7 +10629,7 @@
         <v>43</v>
       </c>
       <c r="N175" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O175" s="44"/>
       <c r="P175" s="44"/>
@@ -10640,25 +10640,25 @@
     </row>
     <row r="176" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A176" s="49">
-        <v>10370010</v>
+        <v>10270010</v>
       </c>
       <c r="B176" s="49">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C176" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D176" s="51">
-        <v>103700001</v>
+        <v>102700001</v>
       </c>
       <c r="E176" s="52">
         <v>11</v>
       </c>
       <c r="F176" s="24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G176" s="25" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H176" s="57">
         <v>0</v>
@@ -10679,7 +10679,7 @@
         <v>37</v>
       </c>
       <c r="N176" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O176" s="44"/>
       <c r="P176" s="44"/>
@@ -10690,25 +10690,25 @@
     </row>
     <row r="177" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A177" s="49">
-        <v>10370011</v>
+        <v>10270011</v>
       </c>
       <c r="B177" s="49">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C177" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D177" s="51">
-        <v>103700001</v>
+        <v>102700001</v>
       </c>
       <c r="E177" s="52">
         <v>12</v>
       </c>
       <c r="F177" s="24" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G177" s="25" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H177" s="57">
         <v>0</v>
@@ -10729,7 +10729,7 @@
         <v>40</v>
       </c>
       <c r="N177" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O177" s="44"/>
       <c r="P177" s="44"/>
@@ -10740,25 +10740,25 @@
     </row>
     <row r="178" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A178" s="49">
-        <v>10370012</v>
+        <v>10270012</v>
       </c>
       <c r="B178" s="49">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C178" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D178" s="51">
-        <v>103100001</v>
+        <v>102700001</v>
       </c>
       <c r="E178" s="52">
         <v>13</v>
       </c>
       <c r="F178" s="24" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G178" s="25" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H178" s="57">
         <v>0</v>
@@ -10779,7 +10779,7 @@
         <v>43</v>
       </c>
       <c r="N178" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O178" s="44"/>
       <c r="P178" s="44"/>
@@ -10790,27 +10790,27 @@
     </row>
     <row r="179" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A179" s="49">
-        <v>10310010</v>
+        <v>10370010</v>
       </c>
       <c r="B179" s="49">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C179" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D179" s="51">
-        <v>103100001</v>
+        <v>103700001</v>
       </c>
       <c r="E179" s="52">
         <v>11</v>
       </c>
       <c r="F179" s="24" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="G179" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="H179" s="53">
+        <v>39</v>
+      </c>
+      <c r="H179" s="57">
         <v>0</v>
       </c>
       <c r="I179" s="45">
@@ -10829,7 +10829,7 @@
         <v>37</v>
       </c>
       <c r="N179" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O179" s="44"/>
       <c r="P179" s="44"/>
@@ -10840,27 +10840,27 @@
     </row>
     <row r="180" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A180" s="49">
-        <v>10310011</v>
+        <v>10370011</v>
       </c>
       <c r="B180" s="49">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C180" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D180" s="51">
-        <v>103100001</v>
+        <v>103700001</v>
       </c>
       <c r="E180" s="52">
         <v>12</v>
       </c>
       <c r="F180" s="24" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="G180" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="H180" s="53">
+        <v>42</v>
+      </c>
+      <c r="H180" s="57">
         <v>0</v>
       </c>
       <c r="I180" s="45">
@@ -10879,7 +10879,7 @@
         <v>40</v>
       </c>
       <c r="N180" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O180" s="44"/>
       <c r="P180" s="44"/>
@@ -10890,13 +10890,13 @@
     </row>
     <row r="181" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A181" s="49">
-        <v>10310012</v>
+        <v>10370012</v>
       </c>
       <c r="B181" s="49">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C181" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D181" s="51">
         <v>103100001</v>
@@ -10905,10 +10905,10 @@
         <v>13</v>
       </c>
       <c r="F181" s="24" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="G181" s="25" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="H181" s="57">
         <v>0</v>
@@ -10929,7 +10929,7 @@
         <v>43</v>
       </c>
       <c r="N181" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O181" s="44"/>
       <c r="P181" s="44"/>
@@ -10940,27 +10940,27 @@
     </row>
     <row r="182" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A182" s="49">
-        <v>10400010</v>
+        <v>10310010</v>
       </c>
       <c r="B182" s="49">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C182" s="50" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D182" s="51">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E182" s="52">
         <v>11</v>
       </c>
       <c r="F182" s="24" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G182" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="H182" s="57">
+        <v>102</v>
+      </c>
+      <c r="H182" s="53">
         <v>0</v>
       </c>
       <c r="I182" s="45">
@@ -10979,7 +10979,7 @@
         <v>37</v>
       </c>
       <c r="N182" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O182" s="44"/>
       <c r="P182" s="44"/>
@@ -10990,27 +10990,27 @@
     </row>
     <row r="183" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A183" s="49">
-        <v>10400011</v>
+        <v>10310011</v>
       </c>
       <c r="B183" s="49">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C183" s="50" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D183" s="51">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E183" s="52">
         <v>12</v>
       </c>
       <c r="F183" s="24" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G183" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="H183" s="57">
+        <v>104</v>
+      </c>
+      <c r="H183" s="53">
         <v>0</v>
       </c>
       <c r="I183" s="45">
@@ -11029,7 +11029,7 @@
         <v>40</v>
       </c>
       <c r="N183" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O183" s="44"/>
       <c r="P183" s="44"/>
@@ -11040,25 +11040,25 @@
     </row>
     <row r="184" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A184" s="49">
-        <v>10400012</v>
+        <v>10310012</v>
       </c>
       <c r="B184" s="49">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C184" s="50" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D184" s="51">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E184" s="52">
         <v>13</v>
       </c>
       <c r="F184" s="24" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G184" s="25" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H184" s="57">
         <v>0</v>
@@ -11079,7 +11079,7 @@
         <v>43</v>
       </c>
       <c r="N184" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O184" s="44"/>
       <c r="P184" s="44"/>
@@ -11090,25 +11090,25 @@
     </row>
     <row r="185" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A185" s="49">
-        <v>10390010</v>
+        <v>10400010</v>
       </c>
       <c r="B185" s="49">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C185" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D185" s="51">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E185" s="52">
         <v>11</v>
       </c>
       <c r="F185" s="24" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G185" s="25" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="H185" s="57">
         <v>0</v>
@@ -11129,7 +11129,7 @@
         <v>37</v>
       </c>
       <c r="N185" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O185" s="44"/>
       <c r="P185" s="44"/>
@@ -11140,25 +11140,25 @@
     </row>
     <row r="186" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A186" s="49">
-        <v>10390011</v>
+        <v>10400011</v>
       </c>
       <c r="B186" s="49">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C186" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D186" s="51">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E186" s="52">
         <v>12</v>
       </c>
       <c r="F186" s="24" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G186" s="25" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="H186" s="57">
         <v>0</v>
@@ -11179,7 +11179,7 @@
         <v>40</v>
       </c>
       <c r="N186" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O186" s="44"/>
       <c r="P186" s="44"/>
@@ -11190,25 +11190,25 @@
     </row>
     <row r="187" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A187" s="49">
-        <v>10390012</v>
+        <v>10400012</v>
       </c>
       <c r="B187" s="49">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C187" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D187" s="51">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E187" s="52">
         <v>13</v>
       </c>
       <c r="F187" s="24" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G187" s="25" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="H187" s="57">
         <v>0</v>
@@ -11229,7 +11229,7 @@
         <v>43</v>
       </c>
       <c r="N187" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O187" s="44"/>
       <c r="P187" s="44"/>
@@ -11240,25 +11240,25 @@
     </row>
     <row r="188" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A188" s="49">
-        <v>10160010</v>
+        <v>10390010</v>
       </c>
       <c r="B188" s="49">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C188" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D188" s="51">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E188" s="52">
         <v>11</v>
       </c>
       <c r="F188" s="24" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="G188" s="25" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="H188" s="57">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>37</v>
       </c>
       <c r="N188" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O188" s="44"/>
       <c r="P188" s="44"/>
@@ -11290,25 +11290,25 @@
     </row>
     <row r="189" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A189" s="49">
-        <v>10160011</v>
+        <v>10390011</v>
       </c>
       <c r="B189" s="49">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C189" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D189" s="51">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E189" s="52">
         <v>12</v>
       </c>
       <c r="F189" s="24" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="G189" s="25" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="H189" s="57">
         <v>0</v>
@@ -11329,7 +11329,7 @@
         <v>40</v>
       </c>
       <c r="N189" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O189" s="44"/>
       <c r="P189" s="44"/>
@@ -11340,25 +11340,25 @@
     </row>
     <row r="190" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A190" s="49">
-        <v>10160012</v>
+        <v>10390012</v>
       </c>
       <c r="B190" s="49">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C190" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D190" s="51">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E190" s="52">
         <v>13</v>
       </c>
       <c r="F190" s="24" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="G190" s="25" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="H190" s="57">
         <v>0</v>
@@ -11379,7 +11379,7 @@
         <v>43</v>
       </c>
       <c r="N190" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O190" s="44"/>
       <c r="P190" s="44"/>
@@ -11390,16 +11390,16 @@
     </row>
     <row r="191" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A191" s="49">
-        <v>10150010</v>
+        <v>10160010</v>
       </c>
       <c r="B191" s="49">
-        <v>101500</v>
+        <v>101600</v>
       </c>
       <c r="C191" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D191" s="51">
-        <v>101500001</v>
+        <v>101600001</v>
       </c>
       <c r="E191" s="52">
         <v>11</v>
@@ -11429,7 +11429,7 @@
         <v>37</v>
       </c>
       <c r="N191" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O191" s="44"/>
       <c r="P191" s="44"/>
@@ -11440,16 +11440,16 @@
     </row>
     <row r="192" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A192" s="49">
-        <v>10150011</v>
+        <v>10160011</v>
       </c>
       <c r="B192" s="49">
-        <v>101500</v>
+        <v>101600</v>
       </c>
       <c r="C192" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D192" s="51">
-        <v>101500001</v>
+        <v>101600001</v>
       </c>
       <c r="E192" s="52">
         <v>12</v>
@@ -11479,7 +11479,7 @@
         <v>40</v>
       </c>
       <c r="N192" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O192" s="44"/>
       <c r="P192" s="44"/>
@@ -11490,16 +11490,16 @@
     </row>
     <row r="193" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A193" s="49">
-        <v>10150012</v>
+        <v>10160012</v>
       </c>
       <c r="B193" s="49">
-        <v>101500</v>
+        <v>101600</v>
       </c>
       <c r="C193" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D193" s="51">
-        <v>101500001</v>
+        <v>101600001</v>
       </c>
       <c r="E193" s="52">
         <v>13</v>
@@ -11529,7 +11529,7 @@
         <v>43</v>
       </c>
       <c r="N193" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O193" s="44"/>
       <c r="P193" s="44"/>
@@ -11540,16 +11540,16 @@
     </row>
     <row r="194" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A194" s="49">
-        <v>10260010</v>
+        <v>10150010</v>
       </c>
       <c r="B194" s="49">
-        <v>102600</v>
+        <v>101500</v>
       </c>
       <c r="C194" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D194" s="51">
-        <v>102600001</v>
+        <v>101500001</v>
       </c>
       <c r="E194" s="52">
         <v>11</v>
@@ -11579,7 +11579,7 @@
         <v>37</v>
       </c>
       <c r="N194" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O194" s="44"/>
       <c r="P194" s="44"/>
@@ -11590,16 +11590,16 @@
     </row>
     <row r="195" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A195" s="49">
-        <v>10260011</v>
+        <v>10150011</v>
       </c>
       <c r="B195" s="49">
-        <v>102600</v>
+        <v>101500</v>
       </c>
       <c r="C195" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D195" s="51">
-        <v>102600001</v>
+        <v>101500001</v>
       </c>
       <c r="E195" s="52">
         <v>12</v>
@@ -11629,7 +11629,7 @@
         <v>40</v>
       </c>
       <c r="N195" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O195" s="44"/>
       <c r="P195" s="44"/>
@@ -11640,16 +11640,16 @@
     </row>
     <row r="196" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A196" s="49">
-        <v>10260012</v>
+        <v>10150012</v>
       </c>
       <c r="B196" s="49">
-        <v>102600</v>
+        <v>101500</v>
       </c>
       <c r="C196" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D196" s="51">
-        <v>102600001</v>
+        <v>101500001</v>
       </c>
       <c r="E196" s="52">
         <v>13</v>
@@ -11679,7 +11679,7 @@
         <v>43</v>
       </c>
       <c r="N196" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O196" s="44"/>
       <c r="P196" s="44"/>
@@ -11690,16 +11690,16 @@
     </row>
     <row r="197" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A197" s="49">
-        <v>10500010</v>
+        <v>10260010</v>
       </c>
       <c r="B197" s="49">
-        <v>105000</v>
+        <v>102600</v>
       </c>
       <c r="C197" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D197" s="51">
-        <v>105000001</v>
+        <v>102600001</v>
       </c>
       <c r="E197" s="52">
         <v>11</v>
@@ -11729,7 +11729,7 @@
         <v>37</v>
       </c>
       <c r="N197" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O197" s="44"/>
       <c r="P197" s="44"/>
@@ -11740,16 +11740,16 @@
     </row>
     <row r="198" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A198" s="49">
-        <v>10500011</v>
+        <v>10260011</v>
       </c>
       <c r="B198" s="49">
-        <v>105000</v>
+        <v>102600</v>
       </c>
       <c r="C198" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D198" s="51">
-        <v>105000001</v>
+        <v>102600001</v>
       </c>
       <c r="E198" s="52">
         <v>12</v>
@@ -11779,7 +11779,7 @@
         <v>40</v>
       </c>
       <c r="N198" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O198" s="44"/>
       <c r="P198" s="44"/>
@@ -11790,16 +11790,16 @@
     </row>
     <row r="199" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A199" s="49">
-        <v>10500012</v>
+        <v>10260012</v>
       </c>
       <c r="B199" s="49">
-        <v>105000</v>
+        <v>102600</v>
       </c>
       <c r="C199" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D199" s="51">
-        <v>105000001</v>
+        <v>102600001</v>
       </c>
       <c r="E199" s="52">
         <v>13</v>
@@ -11829,7 +11829,7 @@
         <v>43</v>
       </c>
       <c r="N199" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O199" s="44"/>
       <c r="P199" s="44"/>
@@ -11840,27 +11840,27 @@
     </row>
     <row r="200" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A200" s="49">
-        <v>10510010</v>
+        <v>10500010</v>
       </c>
       <c r="B200" s="49">
-        <v>105100</v>
+        <v>105000</v>
       </c>
       <c r="C200" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D200" s="51">
-        <v>105100001</v>
+        <v>105000001</v>
       </c>
       <c r="E200" s="52">
         <v>11</v>
       </c>
       <c r="F200" s="24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G200" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="H200" s="53">
+        <v>51</v>
+      </c>
+      <c r="H200" s="57">
         <v>0</v>
       </c>
       <c r="I200" s="45">
@@ -11879,7 +11879,7 @@
         <v>37</v>
       </c>
       <c r="N200" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O200" s="44"/>
       <c r="P200" s="44"/>
@@ -11890,27 +11890,27 @@
     </row>
     <row r="201" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A201" s="49">
-        <v>10510011</v>
+        <v>10500011</v>
       </c>
       <c r="B201" s="49">
-        <v>105100</v>
+        <v>105000</v>
       </c>
       <c r="C201" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D201" s="51">
-        <v>105100001</v>
+        <v>105000001</v>
       </c>
       <c r="E201" s="52">
         <v>12</v>
       </c>
       <c r="F201" s="24" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G201" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="H201" s="53">
+        <v>53</v>
+      </c>
+      <c r="H201" s="57">
         <v>0</v>
       </c>
       <c r="I201" s="45">
@@ -11929,7 +11929,7 @@
         <v>40</v>
       </c>
       <c r="N201" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O201" s="44"/>
       <c r="P201" s="44"/>
@@ -11940,25 +11940,25 @@
     </row>
     <row r="202" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A202" s="49">
-        <v>10510012</v>
+        <v>10500012</v>
       </c>
       <c r="B202" s="49">
-        <v>105100</v>
+        <v>105000</v>
       </c>
       <c r="C202" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D202" s="51">
-        <v>105100001</v>
+        <v>105000001</v>
       </c>
       <c r="E202" s="52">
         <v>13</v>
       </c>
       <c r="F202" s="24" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G202" s="25" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H202" s="57">
         <v>0</v>
@@ -11979,7 +11979,7 @@
         <v>43</v>
       </c>
       <c r="N202" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O202" s="44"/>
       <c r="P202" s="44"/>
@@ -11990,31 +11990,31 @@
     </row>
     <row r="203" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A203" s="49">
-        <v>10540011</v>
+        <v>10510010</v>
       </c>
       <c r="B203" s="49">
-        <v>105400</v>
+        <v>105100</v>
       </c>
       <c r="C203" s="50" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="D203" s="51">
-        <v>105400001</v>
+        <v>105100001</v>
       </c>
       <c r="E203" s="52">
         <v>11</v>
       </c>
       <c r="F203" s="24" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="G203" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H203" s="57">
+        <v>39</v>
+      </c>
+      <c r="H203" s="53">
         <v>0</v>
       </c>
       <c r="I203" s="45">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J203" s="54">
         <v>0</v>
@@ -12026,10 +12026,10 @@
         <v>0</v>
       </c>
       <c r="M203" s="26" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="N203" s="56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O203" s="44"/>
       <c r="P203" s="44"/>
@@ -12040,31 +12040,31 @@
     </row>
     <row r="204" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A204" s="49">
-        <v>10540012</v>
+        <v>10510011</v>
       </c>
       <c r="B204" s="49">
-        <v>105400</v>
+        <v>105100</v>
       </c>
       <c r="C204" s="50" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="D204" s="51">
-        <v>105400001</v>
+        <v>105100001</v>
       </c>
       <c r="E204" s="52">
         <v>12</v>
       </c>
       <c r="F204" s="24" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="G204" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="H204" s="57">
+        <v>42</v>
+      </c>
+      <c r="H204" s="53">
         <v>0</v>
       </c>
       <c r="I204" s="45">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J204" s="54">
         <v>0</v>
@@ -12076,10 +12076,10 @@
         <v>0</v>
       </c>
       <c r="M204" s="26" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="N204" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O204" s="44"/>
       <c r="P204" s="44"/>
@@ -12090,31 +12090,31 @@
     </row>
     <row r="205" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A205" s="49">
-        <v>10540013</v>
+        <v>10510012</v>
       </c>
       <c r="B205" s="49">
-        <v>105400</v>
+        <v>105100</v>
       </c>
       <c r="C205" s="50" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="D205" s="51">
-        <v>105400001</v>
+        <v>105100001</v>
       </c>
       <c r="E205" s="52">
         <v>13</v>
       </c>
       <c r="F205" s="24" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="G205" s="25" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H205" s="57">
         <v>0</v>
       </c>
       <c r="I205" s="45">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J205" s="54">
         <v>0</v>
@@ -12126,10 +12126,10 @@
         <v>0</v>
       </c>
       <c r="M205" s="26" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="N205" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O205" s="44"/>
       <c r="P205" s="44"/>
@@ -12138,20 +12138,20 @@
       <c r="S205" s="45"/>
       <c r="T205" s="45"/>
     </row>
-    <row r="206" ht="16.5" spans="1:20">
-      <c r="A206" s="8">
-        <v>10080010</v>
-      </c>
-      <c r="B206" s="8">
-        <v>100800</v>
-      </c>
-      <c r="C206" s="13" t="s">
+    <row r="206" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A206" s="49">
+        <v>10540011</v>
+      </c>
+      <c r="B206" s="49">
+        <v>105400</v>
+      </c>
+      <c r="C206" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="D206" s="35">
-        <v>100800001</v>
-      </c>
-      <c r="E206" s="13">
+      <c r="D206" s="51">
+        <v>105400001</v>
+      </c>
+      <c r="E206" s="52">
         <v>11</v>
       </c>
       <c r="F206" s="24" t="s">
@@ -12160,42 +12160,48 @@
       <c r="G206" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="H206" s="31">
-        <v>0</v>
-      </c>
-      <c r="I206" s="26">
+      <c r="H206" s="57">
+        <v>0</v>
+      </c>
+      <c r="I206" s="45">
         <v>9600</v>
       </c>
-      <c r="J206" s="26">
-        <v>0</v>
-      </c>
-      <c r="K206" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L206" s="29">
+      <c r="J206" s="54">
+        <v>0</v>
+      </c>
+      <c r="K206" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L206" s="58">
         <v>0</v>
       </c>
       <c r="M206" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="N206" s="24" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="207" ht="16.5" spans="1:20">
-      <c r="A207" s="8">
-        <v>10080011</v>
-      </c>
-      <c r="B207" s="8">
-        <v>100800</v>
-      </c>
-      <c r="C207" s="13" t="s">
+      <c r="N206" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="O206" s="44"/>
+      <c r="P206" s="44"/>
+      <c r="Q206" s="44"/>
+      <c r="R206" s="44"/>
+      <c r="S206" s="45"/>
+      <c r="T206" s="45"/>
+    </row>
+    <row r="207" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A207" s="49">
+        <v>10540012</v>
+      </c>
+      <c r="B207" s="49">
+        <v>105400</v>
+      </c>
+      <c r="C207" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="D207" s="35">
-        <v>100800001</v>
-      </c>
-      <c r="E207" s="13">
+      <c r="D207" s="51">
+        <v>105400001</v>
+      </c>
+      <c r="E207" s="52">
         <v>12</v>
       </c>
       <c r="F207" s="24" t="s">
@@ -12204,42 +12210,48 @@
       <c r="G207" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="H207" s="31">
-        <v>0</v>
-      </c>
-      <c r="I207" s="26">
+      <c r="H207" s="57">
+        <v>0</v>
+      </c>
+      <c r="I207" s="45">
         <v>9600</v>
       </c>
-      <c r="J207" s="26">
-        <v>0</v>
-      </c>
-      <c r="K207" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L207" s="29">
+      <c r="J207" s="54">
+        <v>0</v>
+      </c>
+      <c r="K207" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L207" s="58">
         <v>0</v>
       </c>
       <c r="M207" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="N207" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="208" ht="16.5" spans="1:20">
-      <c r="A208" s="8">
-        <v>10080012</v>
-      </c>
-      <c r="B208" s="8">
-        <v>100800</v>
-      </c>
-      <c r="C208" s="13" t="s">
+      <c r="N207" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="O207" s="44"/>
+      <c r="P207" s="44"/>
+      <c r="Q207" s="44"/>
+      <c r="R207" s="44"/>
+      <c r="S207" s="45"/>
+      <c r="T207" s="45"/>
+    </row>
+    <row r="208" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A208" s="49">
+        <v>10540013</v>
+      </c>
+      <c r="B208" s="49">
+        <v>105400</v>
+      </c>
+      <c r="C208" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="D208" s="35">
-        <v>100800001</v>
-      </c>
-      <c r="E208" s="13">
+      <c r="D208" s="51">
+        <v>105400001</v>
+      </c>
+      <c r="E208" s="52">
         <v>13</v>
       </c>
       <c r="F208" s="24" t="s">
@@ -12248,40 +12260,46 @@
       <c r="G208" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="H208" s="31">
-        <v>0</v>
-      </c>
-      <c r="I208" s="26">
+      <c r="H208" s="57">
+        <v>0</v>
+      </c>
+      <c r="I208" s="45">
         <v>9600</v>
       </c>
-      <c r="J208" s="26">
-        <v>0</v>
-      </c>
-      <c r="K208" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L208" s="29">
+      <c r="J208" s="54">
+        <v>0</v>
+      </c>
+      <c r="K208" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L208" s="58">
         <v>0</v>
       </c>
       <c r="M208" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="N208" s="24" t="s">
-        <v>128</v>
-      </c>
+      <c r="N208" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="O208" s="44"/>
+      <c r="P208" s="44"/>
+      <c r="Q208" s="44"/>
+      <c r="R208" s="44"/>
+      <c r="S208" s="45"/>
+      <c r="T208" s="45"/>
     </row>
     <row r="209" ht="16.5" spans="1:14">
-      <c r="A209" s="22">
-        <v>10530010</v>
-      </c>
-      <c r="B209" s="22">
-        <v>105300</v>
-      </c>
-      <c r="C209" s="23" t="s">
-        <v>124</v>
+      <c r="A209" s="8">
+        <v>10080010</v>
+      </c>
+      <c r="B209" s="8">
+        <v>100800</v>
+      </c>
+      <c r="C209" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="D209" s="35">
-        <v>105300001</v>
+        <v>100800001</v>
       </c>
       <c r="E209" s="13">
         <v>11</v>
@@ -12311,21 +12329,21 @@
         <v>117</v>
       </c>
       <c r="N209" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:14">
-      <c r="A210" s="22">
-        <v>10530011</v>
-      </c>
-      <c r="B210" s="22">
-        <v>105300</v>
-      </c>
-      <c r="C210" s="23" t="s">
-        <v>124</v>
+      <c r="A210" s="8">
+        <v>10080011</v>
+      </c>
+      <c r="B210" s="8">
+        <v>100800</v>
+      </c>
+      <c r="C210" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="D210" s="35">
-        <v>105300001</v>
+        <v>100800001</v>
       </c>
       <c r="E210" s="13">
         <v>12</v>
@@ -12355,21 +12373,21 @@
         <v>119</v>
       </c>
       <c r="N210" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:14">
-      <c r="A211" s="22">
-        <v>10530012</v>
-      </c>
-      <c r="B211" s="22">
-        <v>105300</v>
-      </c>
-      <c r="C211" s="23" t="s">
-        <v>124</v>
+      <c r="A211" s="8">
+        <v>10080012</v>
+      </c>
+      <c r="B211" s="8">
+        <v>100800</v>
+      </c>
+      <c r="C211" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="D211" s="35">
-        <v>105300001</v>
+        <v>100800001</v>
       </c>
       <c r="E211" s="13">
         <v>13</v>
@@ -12399,21 +12417,21 @@
         <v>121</v>
       </c>
       <c r="N211" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="212" ht="16.5" spans="1:14">
-      <c r="A212" s="8">
-        <v>10570010</v>
-      </c>
-      <c r="B212" s="8">
-        <v>105700</v>
-      </c>
-      <c r="C212" t="s">
-        <v>131</v>
+      <c r="A212" s="22">
+        <v>10530010</v>
+      </c>
+      <c r="B212" s="22">
+        <v>105300</v>
+      </c>
+      <c r="C212" s="23" t="s">
+        <v>124</v>
       </c>
       <c r="D212" s="35">
-        <v>105700001</v>
+        <v>105300001</v>
       </c>
       <c r="E212" s="13">
         <v>11</v>
@@ -12443,21 +12461,21 @@
         <v>117</v>
       </c>
       <c r="N212" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="213" ht="16.5" spans="1:14">
-      <c r="A213" s="8">
-        <v>10570011</v>
-      </c>
-      <c r="B213" s="8">
-        <v>105700</v>
-      </c>
-      <c r="C213" t="s">
-        <v>131</v>
+      <c r="A213" s="22">
+        <v>10530011</v>
+      </c>
+      <c r="B213" s="22">
+        <v>105300</v>
+      </c>
+      <c r="C213" s="23" t="s">
+        <v>124</v>
       </c>
       <c r="D213" s="35">
-        <v>105700001</v>
+        <v>105300001</v>
       </c>
       <c r="E213" s="13">
         <v>12</v>
@@ -12487,21 +12505,21 @@
         <v>119</v>
       </c>
       <c r="N213" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="214" ht="16.5" spans="1:14">
-      <c r="A214" s="8">
-        <v>10570012</v>
-      </c>
-      <c r="B214" s="8">
-        <v>105700</v>
-      </c>
-      <c r="C214" t="s">
-        <v>131</v>
+      <c r="A214" s="22">
+        <v>10530012</v>
+      </c>
+      <c r="B214" s="22">
+        <v>105300</v>
+      </c>
+      <c r="C214" s="23" t="s">
+        <v>124</v>
       </c>
       <c r="D214" s="35">
-        <v>105700001</v>
+        <v>105300001</v>
       </c>
       <c r="E214" s="13">
         <v>13</v>
@@ -12531,21 +12549,21 @@
         <v>121</v>
       </c>
       <c r="N214" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="215" s="7" customFormat="1" ht="16.5" spans="1:14">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="215" ht="16.5" spans="1:14">
       <c r="A215" s="8">
-        <v>10580010</v>
+        <v>10570010</v>
       </c>
       <c r="B215" s="8">
-        <v>105800</v>
-      </c>
-      <c r="C215" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D215" s="61">
-        <v>105800001</v>
+        <v>105700</v>
+      </c>
+      <c r="C215" t="s">
+        <v>126</v>
+      </c>
+      <c r="D215" s="35">
+        <v>105700001</v>
       </c>
       <c r="E215" s="13">
         <v>11</v>
@@ -12575,21 +12593,21 @@
         <v>117</v>
       </c>
       <c r="N215" s="24" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="216" ht="16.5" spans="1:14">
+      <c r="A216" s="8">
+        <v>10570011</v>
+      </c>
+      <c r="B216" s="8">
+        <v>105700</v>
+      </c>
+      <c r="C216" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="216" s="7" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A216" s="8">
-        <v>10580011</v>
-      </c>
-      <c r="B216" s="8">
-        <v>105800</v>
-      </c>
-      <c r="C216" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D216" s="61">
-        <v>105800001</v>
+      <c r="D216" s="35">
+        <v>105700001</v>
       </c>
       <c r="E216" s="13">
         <v>12</v>
@@ -12619,21 +12637,21 @@
         <v>119</v>
       </c>
       <c r="N216" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="217" s="7" customFormat="1" ht="16.5" spans="1:14">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="217" ht="16.5" spans="1:14">
       <c r="A217" s="8">
-        <v>10580012</v>
+        <v>10570012</v>
       </c>
       <c r="B217" s="8">
-        <v>105800</v>
-      </c>
-      <c r="C217" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D217" s="61">
-        <v>105800001</v>
+        <v>105700</v>
+      </c>
+      <c r="C217" t="s">
+        <v>126</v>
+      </c>
+      <c r="D217" s="35">
+        <v>105700001</v>
       </c>
       <c r="E217" s="13">
         <v>13</v>
@@ -12663,30 +12681,30 @@
         <v>121</v>
       </c>
       <c r="N217" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="218" s="7" customFormat="1" ht="16.5" spans="1:14">
       <c r="A218" s="8">
-        <v>10550010</v>
+        <v>10580010</v>
       </c>
       <c r="B218" s="8">
-        <v>105500</v>
-      </c>
-      <c r="C218" s="8" t="s">
-        <v>114</v>
+        <v>105800</v>
+      </c>
+      <c r="C218" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="D218" s="61">
-        <v>105500001</v>
+        <v>105800001</v>
       </c>
       <c r="E218" s="13">
         <v>11</v>
       </c>
       <c r="F218" s="24" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="G218" s="25" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H218" s="31">
         <v>0</v>
@@ -12707,30 +12725,30 @@
         <v>117</v>
       </c>
       <c r="N218" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="219" s="7" customFormat="1" ht="16.5" spans="1:14">
       <c r="A219" s="8">
-        <v>10550011</v>
+        <v>10580011</v>
       </c>
       <c r="B219" s="8">
-        <v>105500</v>
-      </c>
-      <c r="C219" s="8" t="s">
-        <v>114</v>
+        <v>105800</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="D219" s="61">
-        <v>105500001</v>
+        <v>105800001</v>
       </c>
       <c r="E219" s="13">
         <v>12</v>
       </c>
       <c r="F219" s="24" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="G219" s="25" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H219" s="31">
         <v>0</v>
@@ -12751,30 +12769,30 @@
         <v>119</v>
       </c>
       <c r="N219" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="220" s="7" customFormat="1" ht="16.5" spans="1:14">
       <c r="A220" s="8">
-        <v>10550012</v>
+        <v>10580012</v>
       </c>
       <c r="B220" s="8">
-        <v>105500</v>
-      </c>
-      <c r="C220" s="8" t="s">
-        <v>114</v>
+        <v>105800</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="D220" s="61">
-        <v>105500001</v>
+        <v>105800001</v>
       </c>
       <c r="E220" s="13">
         <v>13</v>
       </c>
       <c r="F220" s="24" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="G220" s="25" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H220" s="31">
         <v>0</v>
@@ -12795,30 +12813,30 @@
         <v>121</v>
       </c>
       <c r="N220" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="221" ht="16.5" spans="1:14">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="221" s="7" customFormat="1" ht="16.5" spans="1:14">
       <c r="A221" s="8">
-        <v>10480010</v>
+        <v>10550010</v>
       </c>
       <c r="B221" s="8">
-        <v>104800</v>
-      </c>
-      <c r="C221" t="s">
-        <v>115</v>
-      </c>
-      <c r="D221" s="27">
-        <v>104800001</v>
+        <v>105500</v>
+      </c>
+      <c r="C221" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D221" s="61">
+        <v>105500001</v>
       </c>
       <c r="E221" s="13">
         <v>11</v>
       </c>
       <c r="F221" s="24" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="G221" s="25" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="H221" s="31">
         <v>0</v>
@@ -12839,30 +12857,30 @@
         <v>117</v>
       </c>
       <c r="N221" s="24" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="222" ht="16.5" spans="1:14">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="222" s="7" customFormat="1" ht="16.5" spans="1:14">
       <c r="A222" s="8">
-        <v>10480011</v>
+        <v>10550011</v>
       </c>
       <c r="B222" s="8">
-        <v>104800</v>
-      </c>
-      <c r="C222" t="s">
-        <v>115</v>
-      </c>
-      <c r="D222" s="27">
-        <v>104800001</v>
+        <v>105500</v>
+      </c>
+      <c r="C222" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D222" s="61">
+        <v>105500001</v>
       </c>
       <c r="E222" s="13">
         <v>12</v>
       </c>
       <c r="F222" s="24" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="G222" s="25" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="H222" s="31">
         <v>0</v>
@@ -12883,30 +12901,30 @@
         <v>119</v>
       </c>
       <c r="N222" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="223" ht="16.5" spans="1:14">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="223" s="7" customFormat="1" ht="16.5" spans="1:14">
       <c r="A223" s="8">
-        <v>10480012</v>
+        <v>10550012</v>
       </c>
       <c r="B223" s="8">
-        <v>104800</v>
-      </c>
-      <c r="C223" t="s">
-        <v>115</v>
-      </c>
-      <c r="D223" s="27">
-        <v>104800001</v>
+        <v>105500</v>
+      </c>
+      <c r="C223" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D223" s="61">
+        <v>105500001</v>
       </c>
       <c r="E223" s="13">
         <v>13</v>
       </c>
       <c r="F223" s="24" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="G223" s="25" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="H223" s="31">
         <v>0</v>
@@ -12927,30 +12945,30 @@
         <v>121</v>
       </c>
       <c r="N223" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="224" s="8" customFormat="1" ht="16.5" spans="1:14">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="224" ht="16.5" spans="1:14">
       <c r="A224" s="8">
-        <v>10550110</v>
+        <v>10480010</v>
       </c>
       <c r="B224" s="8">
-        <v>105501</v>
-      </c>
-      <c r="C224" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D224" s="61">
-        <v>105501001</v>
-      </c>
-      <c r="E224" s="62">
+        <v>104800</v>
+      </c>
+      <c r="C224" t="s">
+        <v>115</v>
+      </c>
+      <c r="D224" s="27">
+        <v>104800001</v>
+      </c>
+      <c r="E224" s="13">
         <v>11</v>
       </c>
       <c r="F224" s="24" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="G224" s="25" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H224" s="31">
         <v>0</v>
@@ -12971,30 +12989,30 @@
         <v>117</v>
       </c>
       <c r="N224" s="24" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="225" s="8" customFormat="1" ht="16.5" spans="1:20">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="225" ht="16.5" spans="1:20">
       <c r="A225" s="8">
-        <v>10550111</v>
+        <v>10480011</v>
       </c>
       <c r="B225" s="8">
-        <v>105501</v>
-      </c>
-      <c r="C225" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D225" s="61">
-        <v>105501001</v>
-      </c>
-      <c r="E225" s="62">
+        <v>104800</v>
+      </c>
+      <c r="C225" t="s">
+        <v>115</v>
+      </c>
+      <c r="D225" s="27">
+        <v>104800001</v>
+      </c>
+      <c r="E225" s="13">
         <v>12</v>
       </c>
       <c r="F225" s="24" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="G225" s="25" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H225" s="31">
         <v>0</v>
@@ -13015,30 +13033,30 @@
         <v>119</v>
       </c>
       <c r="N225" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="226" s="8" customFormat="1" ht="16.5" spans="1:20">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="226" ht="16.5" spans="1:20">
       <c r="A226" s="8">
-        <v>10550112</v>
+        <v>10480012</v>
       </c>
       <c r="B226" s="8">
-        <v>105501</v>
-      </c>
-      <c r="C226" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D226" s="61">
-        <v>105501001</v>
-      </c>
-      <c r="E226" s="62">
+        <v>104800</v>
+      </c>
+      <c r="C226" t="s">
+        <v>115</v>
+      </c>
+      <c r="D226" s="27">
+        <v>104800001</v>
+      </c>
+      <c r="E226" s="13">
         <v>13</v>
       </c>
       <c r="F226" s="24" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="G226" s="25" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H226" s="31">
         <v>0</v>
@@ -13059,21 +13077,21 @@
         <v>121</v>
       </c>
       <c r="N226" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="227" s="8" customFormat="1" ht="16.5" spans="1:20">
       <c r="A227" s="8">
-        <v>10550210</v>
+        <v>10550110</v>
       </c>
       <c r="B227" s="8">
-        <v>105502</v>
+        <v>105501</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D227" s="61">
-        <v>105502001</v>
+        <v>105501001</v>
       </c>
       <c r="E227" s="62">
         <v>11</v>
@@ -13103,21 +13121,21 @@
         <v>117</v>
       </c>
       <c r="N227" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="228" s="8" customFormat="1" ht="16.5" spans="1:20">
       <c r="A228" s="8">
-        <v>10550211</v>
+        <v>10550111</v>
       </c>
       <c r="B228" s="8">
-        <v>105502</v>
+        <v>105501</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D228" s="61">
-        <v>105502001</v>
+        <v>105501001</v>
       </c>
       <c r="E228" s="62">
         <v>12</v>
@@ -13147,21 +13165,21 @@
         <v>119</v>
       </c>
       <c r="N228" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="229" s="8" customFormat="1" ht="16.5" spans="1:20">
       <c r="A229" s="8">
-        <v>10550212</v>
+        <v>10550112</v>
       </c>
       <c r="B229" s="8">
-        <v>105502</v>
+        <v>105501</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D229" s="61">
-        <v>105502001</v>
+        <v>105501001</v>
       </c>
       <c r="E229" s="62">
         <v>13</v>
@@ -13191,153 +13209,153 @@
         <v>121</v>
       </c>
       <c r="N229" s="24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="230" s="8" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A230" s="8">
+        <v>10550210</v>
+      </c>
+      <c r="B230" s="8">
+        <v>105502</v>
+      </c>
+      <c r="C230" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D230" s="61">
+        <v>105502001</v>
+      </c>
+      <c r="E230" s="62">
+        <v>11</v>
+      </c>
+      <c r="F230" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="G230" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H230" s="31">
+        <v>0</v>
+      </c>
+      <c r="I230" s="26">
+        <v>9600</v>
+      </c>
+      <c r="J230" s="26">
+        <v>0</v>
+      </c>
+      <c r="K230" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L230" s="29">
+        <v>0</v>
+      </c>
+      <c r="M230" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="N230" s="24" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="231" s="8" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A231" s="8">
+        <v>10550211</v>
+      </c>
+      <c r="B231" s="8">
+        <v>105502</v>
+      </c>
+      <c r="C231" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D231" s="61">
+        <v>105502001</v>
+      </c>
+      <c r="E231" s="62">
+        <v>12</v>
+      </c>
+      <c r="F231" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="G231" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="H231" s="31">
+        <v>0</v>
+      </c>
+      <c r="I231" s="26">
+        <v>9600</v>
+      </c>
+      <c r="J231" s="26">
+        <v>0</v>
+      </c>
+      <c r="K231" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L231" s="29">
+        <v>0</v>
+      </c>
+      <c r="M231" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="N231" s="24" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="230" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A230" s="8">
-        <v>10410010</v>
-      </c>
-      <c r="B230" s="46">
-        <v>104100</v>
-      </c>
-      <c r="C230" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="D230" s="27">
-        <v>104100001</v>
-      </c>
-      <c r="E230" s="13">
-        <v>11</v>
-      </c>
-      <c r="F230" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="G230" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="H230" s="65">
-        <v>0</v>
-      </c>
-      <c r="I230" s="48">
+    <row r="232" s="8" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A232" s="8">
+        <v>10550212</v>
+      </c>
+      <c r="B232" s="8">
+        <v>105502</v>
+      </c>
+      <c r="C232" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D232" s="61">
+        <v>105502001</v>
+      </c>
+      <c r="E232" s="62">
+        <v>13</v>
+      </c>
+      <c r="F232" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="G232" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="H232" s="31">
+        <v>0</v>
+      </c>
+      <c r="I232" s="26">
         <v>9600</v>
       </c>
-      <c r="J230" s="48">
-        <v>0</v>
-      </c>
-      <c r="K230" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="L230" s="66">
-        <v>0</v>
-      </c>
-      <c r="M230" s="48" t="s">
-        <v>117</v>
-      </c>
-      <c r="N230" s="47" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="231" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A231" s="8">
-        <v>10410011</v>
-      </c>
-      <c r="B231" s="46">
-        <v>104100</v>
-      </c>
-      <c r="C231" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="D231" s="27">
-        <v>104100001</v>
-      </c>
-      <c r="E231" s="13">
-        <v>12</v>
-      </c>
-      <c r="F231" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="G231" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="H231" s="65">
-        <v>0</v>
-      </c>
-      <c r="I231" s="48">
-        <v>9600</v>
-      </c>
-      <c r="J231" s="48">
-        <v>0</v>
-      </c>
-      <c r="K231" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="L231" s="66">
-        <v>0</v>
-      </c>
-      <c r="M231" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="N231" s="47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="232" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A232" s="8">
-        <v>10410012</v>
-      </c>
-      <c r="B232" s="46">
-        <v>104100</v>
-      </c>
-      <c r="C232" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="D232" s="27">
-        <v>104100001</v>
-      </c>
-      <c r="E232" s="13">
-        <v>13</v>
-      </c>
-      <c r="F232" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="G232" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="H232" s="65">
-        <v>0</v>
-      </c>
-      <c r="I232" s="48">
-        <v>9600</v>
-      </c>
-      <c r="J232" s="48">
-        <v>0</v>
-      </c>
-      <c r="K232" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="L232" s="66">
-        <v>0</v>
-      </c>
-      <c r="M232" s="48" t="s">
+      <c r="J232" s="26">
+        <v>0</v>
+      </c>
+      <c r="K232" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L232" s="29">
+        <v>0</v>
+      </c>
+      <c r="M232" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="N232" s="47" t="s">
-        <v>128</v>
+      <c r="N232" s="24" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="233" customFormat="1" ht="16.5" spans="1:20">
       <c r="A233" s="8">
-        <v>10420010</v>
+        <v>10410010</v>
       </c>
       <c r="B233" s="46">
-        <v>104200</v>
+        <v>104100</v>
       </c>
       <c r="C233" s="63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D233" s="27">
-        <v>104200001</v>
+        <v>104100001</v>
       </c>
       <c r="E233" s="13">
         <v>11</v>
@@ -13367,21 +13385,21 @@
         <v>117</v>
       </c>
       <c r="N233" s="47" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="234" customFormat="1" ht="16.5" spans="1:20">
       <c r="A234" s="8">
-        <v>10420011</v>
+        <v>10410011</v>
       </c>
       <c r="B234" s="46">
-        <v>104200</v>
+        <v>104100</v>
       </c>
       <c r="C234" s="63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D234" s="27">
-        <v>104200001</v>
+        <v>104100001</v>
       </c>
       <c r="E234" s="13">
         <v>12</v>
@@ -13411,21 +13429,21 @@
         <v>119</v>
       </c>
       <c r="N234" s="47" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="235" customFormat="1" ht="16.5" spans="1:20">
       <c r="A235" s="8">
-        <v>10420012</v>
+        <v>10410012</v>
       </c>
       <c r="B235" s="46">
-        <v>104200</v>
+        <v>104100</v>
       </c>
       <c r="C235" s="63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D235" s="27">
-        <v>104200001</v>
+        <v>104100001</v>
       </c>
       <c r="E235" s="13">
         <v>13</v>
@@ -13455,180 +13473,162 @@
         <v>121</v>
       </c>
       <c r="N235" s="47" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="236" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A236" s="8">
+        <v>10420010</v>
+      </c>
+      <c r="B236" s="46">
+        <v>104200</v>
+      </c>
+      <c r="C236" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="D236" s="27">
+        <v>104200001</v>
+      </c>
+      <c r="E236" s="13">
+        <v>11</v>
+      </c>
+      <c r="F236" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="G236" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="H236" s="65">
+        <v>0</v>
+      </c>
+      <c r="I236" s="48">
+        <v>9600</v>
+      </c>
+      <c r="J236" s="48">
+        <v>0</v>
+      </c>
+      <c r="K236" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L236" s="66">
+        <v>0</v>
+      </c>
+      <c r="M236" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="N236" s="47" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="237" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A237" s="8">
+        <v>10420011</v>
+      </c>
+      <c r="B237" s="46">
+        <v>104200</v>
+      </c>
+      <c r="C237" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="D237" s="27">
+        <v>104200001</v>
+      </c>
+      <c r="E237" s="13">
+        <v>12</v>
+      </c>
+      <c r="F237" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="G237" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="H237" s="65">
+        <v>0</v>
+      </c>
+      <c r="I237" s="48">
+        <v>9600</v>
+      </c>
+      <c r="J237" s="48">
+        <v>0</v>
+      </c>
+      <c r="K237" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L237" s="66">
+        <v>0</v>
+      </c>
+      <c r="M237" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="N237" s="47" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="236" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A236" s="22">
-        <v>10010021</v>
-      </c>
-      <c r="B236" s="22">
-        <v>100100</v>
-      </c>
-      <c r="C236" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D236" s="27">
-        <v>100100026</v>
-      </c>
-      <c r="E236" s="67">
-        <v>21</v>
-      </c>
-      <c r="F236" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="G236" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="H236" s="17">
-        <v>10000000</v>
-      </c>
-      <c r="I236" s="28">
-        <v>9500</v>
-      </c>
-      <c r="J236" s="26">
-        <v>5000000</v>
-      </c>
-      <c r="K236" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L236" s="30">
-        <v>100</v>
-      </c>
-      <c r="M236" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="N236" s="24">
-        <v>0</v>
-      </c>
-      <c r="O236" s="24"/>
-      <c r="P236" s="24"/>
-      <c r="Q236" s="24"/>
-      <c r="R236" s="24"/>
-      <c r="S236" s="26"/>
-      <c r="T236" s="26"/>
-    </row>
-    <row r="237" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A237" s="22">
-        <v>10010022</v>
-      </c>
-      <c r="B237" s="22">
-        <v>100100</v>
-      </c>
-      <c r="C237" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D237" s="27">
-        <v>100100026</v>
-      </c>
-      <c r="E237" s="67">
-        <v>22</v>
-      </c>
-      <c r="F237" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G237" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="H237" s="17">
-        <v>100000000</v>
-      </c>
-      <c r="I237" s="28">
-        <v>9500</v>
-      </c>
-      <c r="J237" s="26">
-        <v>50000000</v>
-      </c>
-      <c r="K237" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L237" s="30">
-        <v>100</v>
-      </c>
-      <c r="M237" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="N237" s="24">
-        <v>0</v>
-      </c>
-      <c r="O237" s="24"/>
-      <c r="P237" s="24"/>
-      <c r="Q237" s="24"/>
-      <c r="R237" s="24"/>
-      <c r="S237" s="26"/>
-      <c r="T237" s="26"/>
-    </row>
-    <row r="238" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A238" s="22">
-        <v>10010023</v>
-      </c>
-      <c r="B238" s="22">
-        <v>100100</v>
-      </c>
-      <c r="C238" s="23" t="s">
-        <v>33</v>
+    <row r="238" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A238" s="8">
+        <v>10420012</v>
+      </c>
+      <c r="B238" s="46">
+        <v>104200</v>
+      </c>
+      <c r="C238" s="63" t="s">
+        <v>135</v>
       </c>
       <c r="D238" s="27">
-        <v>100100026</v>
-      </c>
-      <c r="E238" s="67">
-        <v>23</v>
-      </c>
-      <c r="F238" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="G238" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="H238" s="31">
-        <v>1000000000</v>
-      </c>
-      <c r="I238" s="28">
-        <v>9500</v>
-      </c>
-      <c r="J238" s="26">
-        <v>500000000</v>
-      </c>
-      <c r="K238" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L238" s="30">
-        <v>100</v>
-      </c>
-      <c r="M238" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="N238" s="24">
-        <v>0</v>
-      </c>
-      <c r="O238" s="24"/>
-      <c r="P238" s="24"/>
-      <c r="Q238" s="24"/>
-      <c r="R238" s="24"/>
-      <c r="S238" s="26"/>
-      <c r="T238" s="26"/>
+        <v>104200001</v>
+      </c>
+      <c r="E238" s="13">
+        <v>13</v>
+      </c>
+      <c r="F238" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="G238" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="H238" s="65">
+        <v>0</v>
+      </c>
+      <c r="I238" s="48">
+        <v>9600</v>
+      </c>
+      <c r="J238" s="48">
+        <v>0</v>
+      </c>
+      <c r="K238" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L238" s="66">
+        <v>0</v>
+      </c>
+      <c r="M238" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="N238" s="47" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="239" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A239" s="22">
-        <v>10030021</v>
+        <v>10010021</v>
       </c>
       <c r="B239" s="22">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C239" s="23" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D239" s="27">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E239" s="67">
         <v>21</v>
       </c>
       <c r="F239" s="24" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G239" s="25" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H239" s="17">
         <v>10000000</v>
@@ -13660,25 +13660,25 @@
     </row>
     <row r="240" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A240" s="22">
-        <v>10030022</v>
+        <v>10010022</v>
       </c>
       <c r="B240" s="22">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C240" s="23" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D240" s="27">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E240" s="67">
         <v>22</v>
       </c>
       <c r="F240" s="24" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G240" s="25" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H240" s="17">
         <v>100000000</v>
@@ -13710,25 +13710,25 @@
     </row>
     <row r="241" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A241" s="22">
-        <v>10030023</v>
+        <v>10010023</v>
       </c>
       <c r="B241" s="22">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C241" s="23" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D241" s="27">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E241" s="67">
         <v>23</v>
       </c>
       <c r="F241" s="24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G241" s="25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H241" s="31">
         <v>1000000000</v>
@@ -13760,25 +13760,25 @@
     </row>
     <row r="242" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A242" s="22">
-        <v>10070021</v>
+        <v>10030021</v>
       </c>
       <c r="B242" s="22">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D242" s="27">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E242" s="67">
         <v>21</v>
       </c>
       <c r="F242" s="24" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G242" s="25" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H242" s="17">
         <v>10000000</v>
@@ -13793,7 +13793,7 @@
         <v>36</v>
       </c>
       <c r="L242" s="30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M242" s="26" t="s">
         <v>37</v>
@@ -13810,25 +13810,25 @@
     </row>
     <row r="243" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A243" s="22">
-        <v>10070022</v>
+        <v>10030022</v>
       </c>
       <c r="B243" s="22">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C243" s="23" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D243" s="27">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E243" s="67">
         <v>22</v>
       </c>
       <c r="F243" s="24" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G243" s="25" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H243" s="17">
         <v>100000000</v>
@@ -13843,7 +13843,7 @@
         <v>36</v>
       </c>
       <c r="L243" s="30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M243" s="26" t="s">
         <v>40</v>
@@ -13860,25 +13860,25 @@
     </row>
     <row r="244" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A244" s="22">
-        <v>10070023</v>
+        <v>10030023</v>
       </c>
       <c r="B244" s="22">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C244" s="23" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D244" s="27">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E244" s="67">
         <v>23</v>
       </c>
       <c r="F244" s="24" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G244" s="25" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H244" s="31">
         <v>1000000000</v>
@@ -13893,7 +13893,7 @@
         <v>36</v>
       </c>
       <c r="L244" s="30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M244" s="26" t="s">
         <v>43</v>
@@ -13910,31 +13910,31 @@
     </row>
     <row r="245" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A245" s="22">
-        <v>10120021</v>
+        <v>10070021</v>
       </c>
       <c r="B245" s="22">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="C245" s="23" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D245" s="27">
-        <v>101200001</v>
+        <v>100700001</v>
       </c>
       <c r="E245" s="67">
         <v>21</v>
       </c>
-      <c r="F245" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="G245" s="33" t="s">
-        <v>58</v>
+      <c r="F245" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G245" s="25" t="s">
+        <v>51</v>
       </c>
       <c r="H245" s="17">
         <v>10000000</v>
       </c>
-      <c r="I245" s="34">
-        <v>9700</v>
+      <c r="I245" s="28">
+        <v>9500</v>
       </c>
       <c r="J245" s="26">
         <v>5000000</v>
@@ -13943,7 +13943,7 @@
         <v>36</v>
       </c>
       <c r="L245" s="30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M245" s="26" t="s">
         <v>37</v>
@@ -13960,25 +13960,25 @@
     </row>
     <row r="246" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A246" s="22">
-        <v>10120022</v>
+        <v>10070022</v>
       </c>
       <c r="B246" s="22">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="C246" s="23" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D246" s="27">
-        <v>101200001</v>
+        <v>100700001</v>
       </c>
       <c r="E246" s="67">
         <v>22</v>
       </c>
       <c r="F246" s="24" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G246" s="25" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H246" s="17">
         <v>100000000</v>
@@ -13993,7 +13993,7 @@
         <v>36</v>
       </c>
       <c r="L246" s="30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M246" s="26" t="s">
         <v>40</v>
@@ -14010,25 +14010,25 @@
     </row>
     <row r="247" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A247" s="22">
-        <v>10120023</v>
+        <v>10070023</v>
       </c>
       <c r="B247" s="22">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="C247" s="23" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D247" s="27">
-        <v>101200001</v>
+        <v>100700001</v>
       </c>
       <c r="E247" s="67">
         <v>23</v>
       </c>
       <c r="F247" s="24" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G247" s="25" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H247" s="31">
         <v>1000000000</v>
@@ -14043,7 +14043,7 @@
         <v>36</v>
       </c>
       <c r="L247" s="30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M247" s="26" t="s">
         <v>43</v>
@@ -14060,31 +14060,31 @@
     </row>
     <row r="248" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A248" s="22">
-        <v>10140021</v>
+        <v>10120021</v>
       </c>
       <c r="B248" s="22">
-        <v>101400</v>
+        <v>101200</v>
       </c>
       <c r="C248" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D248" s="27">
-        <v>101400001</v>
+        <v>101200001</v>
       </c>
       <c r="E248" s="67">
         <v>21</v>
       </c>
-      <c r="F248" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G248" s="25" t="s">
-        <v>39</v>
+      <c r="F248" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="G248" s="33" t="s">
+        <v>58</v>
       </c>
       <c r="H248" s="17">
         <v>10000000</v>
       </c>
-      <c r="I248" s="28">
-        <v>9500</v>
+      <c r="I248" s="34">
+        <v>9700</v>
       </c>
       <c r="J248" s="26">
         <v>5000000</v>
@@ -14110,16 +14110,16 @@
     </row>
     <row r="249" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A249" s="22">
-        <v>10140022</v>
+        <v>10120022</v>
       </c>
       <c r="B249" s="22">
-        <v>101400</v>
+        <v>101200</v>
       </c>
       <c r="C249" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D249" s="27">
-        <v>101400001</v>
+        <v>101200001</v>
       </c>
       <c r="E249" s="67">
         <v>22</v>
@@ -14160,16 +14160,16 @@
     </row>
     <row r="250" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A250" s="22">
-        <v>10140023</v>
+        <v>10120023</v>
       </c>
       <c r="B250" s="22">
-        <v>101400</v>
+        <v>101200</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D250" s="27">
-        <v>101400001</v>
+        <v>101200001</v>
       </c>
       <c r="E250" s="67">
         <v>23</v>
@@ -14210,25 +14210,25 @@
     </row>
     <row r="251" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A251" s="22">
-        <v>10170021</v>
+        <v>10140021</v>
       </c>
       <c r="B251" s="22">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D251" s="27">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E251" s="67">
         <v>21</v>
       </c>
       <c r="F251" s="24" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G251" s="25" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H251" s="17">
         <v>10000000</v>
@@ -14260,25 +14260,25 @@
     </row>
     <row r="252" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A252" s="22">
-        <v>10170022</v>
+        <v>10140022</v>
       </c>
       <c r="B252" s="22">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C252" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D252" s="27">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E252" s="67">
         <v>22</v>
       </c>
       <c r="F252" s="24" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G252" s="25" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H252" s="17">
         <v>100000000</v>
@@ -14310,25 +14310,25 @@
     </row>
     <row r="253" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A253" s="22">
-        <v>10170023</v>
+        <v>10140023</v>
       </c>
       <c r="B253" s="22">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C253" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D253" s="27">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E253" s="67">
         <v>23</v>
       </c>
       <c r="F253" s="24" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G253" s="25" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H253" s="31">
         <v>1000000000</v>
@@ -14360,16 +14360,16 @@
     </row>
     <row r="254" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A254" s="22">
-        <v>10210021</v>
+        <v>10170021</v>
       </c>
       <c r="B254" s="22">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D254" s="27">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E254" s="67">
         <v>21</v>
@@ -14410,16 +14410,16 @@
     </row>
     <row r="255" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A255" s="22">
-        <v>10210022</v>
+        <v>10170022</v>
       </c>
       <c r="B255" s="22">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C255" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D255" s="27">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E255" s="67">
         <v>22</v>
@@ -14460,16 +14460,16 @@
     </row>
     <row r="256" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A256" s="22">
-        <v>10210023</v>
+        <v>10170023</v>
       </c>
       <c r="B256" s="22">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C256" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D256" s="27">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E256" s="67">
         <v>23</v>
@@ -14510,16 +14510,16 @@
     </row>
     <row r="257" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A257" s="22">
-        <v>10220021</v>
+        <v>10210021</v>
       </c>
       <c r="B257" s="22">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C257" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D257" s="27">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E257" s="67">
         <v>21</v>
@@ -14560,16 +14560,16 @@
     </row>
     <row r="258" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A258" s="22">
-        <v>10220022</v>
+        <v>10210022</v>
       </c>
       <c r="B258" s="22">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C258" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D258" s="27">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E258" s="67">
         <v>22</v>
@@ -14610,16 +14610,16 @@
     </row>
     <row r="259" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A259" s="22">
-        <v>10220023</v>
+        <v>10210023</v>
       </c>
       <c r="B259" s="22">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D259" s="27">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E259" s="67">
         <v>23</v>
@@ -14660,31 +14660,31 @@
     </row>
     <row r="260" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A260" s="22">
-        <v>10240021</v>
+        <v>10220021</v>
       </c>
       <c r="B260" s="22">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C260" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D260" s="27">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E260" s="67">
         <v>21</v>
       </c>
-      <c r="F260" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="G260" s="33" t="s">
-        <v>65</v>
+      <c r="F260" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G260" s="25" t="s">
+        <v>51</v>
       </c>
       <c r="H260" s="17">
         <v>10000000</v>
       </c>
-      <c r="I260" s="34">
-        <v>9700</v>
+      <c r="I260" s="28">
+        <v>9500</v>
       </c>
       <c r="J260" s="26">
         <v>5000000</v>
@@ -14710,25 +14710,25 @@
     </row>
     <row r="261" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A261" s="22">
-        <v>10240022</v>
+        <v>10220022</v>
       </c>
       <c r="B261" s="22">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C261" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D261" s="27">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E261" s="67">
         <v>22</v>
       </c>
       <c r="F261" s="24" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G261" s="25" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H261" s="17">
         <v>100000000</v>
@@ -14760,25 +14760,25 @@
     </row>
     <row r="262" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A262" s="22">
-        <v>10240023</v>
+        <v>10220023</v>
       </c>
       <c r="B262" s="22">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C262" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D262" s="27">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E262" s="67">
         <v>23</v>
       </c>
       <c r="F262" s="24" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G262" s="25" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H262" s="31">
         <v>1000000000</v>
@@ -14810,31 +14810,31 @@
     </row>
     <row r="263" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A263" s="22">
-        <v>10180021</v>
+        <v>10240021</v>
       </c>
       <c r="B263" s="22">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C263" s="23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D263" s="27">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E263" s="67">
         <v>21</v>
       </c>
-      <c r="F263" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="G263" s="25" t="s">
-        <v>51</v>
+      <c r="F263" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="G263" s="33" t="s">
+        <v>65</v>
       </c>
       <c r="H263" s="17">
         <v>10000000</v>
       </c>
-      <c r="I263" s="28">
-        <v>9500</v>
+      <c r="I263" s="34">
+        <v>9700</v>
       </c>
       <c r="J263" s="26">
         <v>5000000</v>
@@ -14860,25 +14860,25 @@
     </row>
     <row r="264" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A264" s="22">
-        <v>10180022</v>
+        <v>10240022</v>
       </c>
       <c r="B264" s="22">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C264" s="23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D264" s="27">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E264" s="67">
         <v>22</v>
       </c>
       <c r="F264" s="24" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G264" s="25" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H264" s="17">
         <v>100000000</v>
@@ -14910,25 +14910,25 @@
     </row>
     <row r="265" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A265" s="22">
-        <v>10180023</v>
+        <v>10240023</v>
       </c>
       <c r="B265" s="22">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C265" s="23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D265" s="27">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E265" s="67">
         <v>23</v>
       </c>
       <c r="F265" s="24" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G265" s="25" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H265" s="31">
         <v>1000000000</v>
@@ -14960,25 +14960,25 @@
     </row>
     <row r="266" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A266" s="22">
-        <v>10250021</v>
+        <v>10180021</v>
       </c>
       <c r="B266" s="22">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C266" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D266" s="27">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E266" s="67">
         <v>21</v>
       </c>
       <c r="F266" s="24" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G266" s="25" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H266" s="17">
         <v>10000000</v>
@@ -15010,25 +15010,25 @@
     </row>
     <row r="267" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A267" s="22">
-        <v>10250022</v>
+        <v>10180022</v>
       </c>
       <c r="B267" s="22">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C267" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D267" s="27">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E267" s="67">
         <v>22</v>
       </c>
       <c r="F267" s="24" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G267" s="25" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="H267" s="17">
         <v>100000000</v>
@@ -15060,25 +15060,25 @@
     </row>
     <row r="268" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A268" s="22">
-        <v>10250023</v>
+        <v>10180023</v>
       </c>
       <c r="B268" s="22">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C268" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D268" s="27">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E268" s="67">
         <v>23</v>
       </c>
       <c r="F268" s="24" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G268" s="25" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H268" s="31">
         <v>1000000000</v>
@@ -15110,25 +15110,25 @@
     </row>
     <row r="269" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A269" s="22">
-        <v>10230021</v>
+        <v>10250021</v>
       </c>
       <c r="B269" s="22">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C269" s="23" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D269" s="27">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E269" s="67">
         <v>21</v>
       </c>
       <c r="F269" s="24" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G269" s="25" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H269" s="17">
         <v>10000000</v>
@@ -15160,25 +15160,25 @@
     </row>
     <row r="270" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A270" s="22">
-        <v>10230022</v>
+        <v>10250022</v>
       </c>
       <c r="B270" s="22">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C270" s="23" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D270" s="27">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E270" s="67">
         <v>22</v>
       </c>
       <c r="F270" s="24" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G270" s="25" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H270" s="17">
         <v>100000000</v>
@@ -15210,25 +15210,25 @@
     </row>
     <row r="271" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A271" s="22">
-        <v>10230023</v>
+        <v>10250023</v>
       </c>
       <c r="B271" s="22">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C271" s="23" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D271" s="27">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E271" s="67">
         <v>23</v>
       </c>
       <c r="F271" s="24" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G271" s="25" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="H271" s="31">
         <v>1000000000</v>
@@ -15260,31 +15260,31 @@
     </row>
     <row r="272" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A272" s="22">
-        <v>10340021</v>
+        <v>10230021</v>
       </c>
       <c r="B272" s="22">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C272" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D272" s="27">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E272" s="67">
         <v>21</v>
       </c>
-      <c r="F272" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="G272" s="33" t="s">
-        <v>69</v>
+      <c r="F272" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G272" s="25" t="s">
+        <v>51</v>
       </c>
       <c r="H272" s="17">
         <v>10000000</v>
       </c>
-      <c r="I272" s="34">
-        <v>9700</v>
+      <c r="I272" s="28">
+        <v>9500</v>
       </c>
       <c r="J272" s="26">
         <v>5000000</v>
@@ -15310,25 +15310,25 @@
     </row>
     <row r="273" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A273" s="22">
-        <v>10340022</v>
+        <v>10230022</v>
       </c>
       <c r="B273" s="22">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C273" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D273" s="27">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E273" s="67">
         <v>22</v>
       </c>
       <c r="F273" s="24" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G273" s="25" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H273" s="17">
         <v>100000000</v>
@@ -15360,25 +15360,25 @@
     </row>
     <row r="274" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A274" s="22">
-        <v>10340023</v>
+        <v>10230023</v>
       </c>
       <c r="B274" s="22">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C274" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D274" s="27">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E274" s="67">
         <v>23</v>
       </c>
       <c r="F274" s="24" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="G274" s="25" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H274" s="31">
         <v>1000000000</v>
@@ -15410,31 +15410,31 @@
     </row>
     <row r="275" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A275" s="22">
-        <v>10350021</v>
+        <v>10340021</v>
       </c>
       <c r="B275" s="22">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C275" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D275" s="35">
-        <v>102900001</v>
+        <v>75</v>
+      </c>
+      <c r="D275" s="27">
+        <v>103000001</v>
       </c>
       <c r="E275" s="67">
         <v>21</v>
       </c>
-      <c r="F275" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G275" s="25" t="s">
-        <v>39</v>
+      <c r="F275" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="G275" s="33" t="s">
+        <v>69</v>
       </c>
       <c r="H275" s="17">
         <v>10000000</v>
       </c>
-      <c r="I275" s="28">
-        <v>9500</v>
+      <c r="I275" s="34">
+        <v>9700</v>
       </c>
       <c r="J275" s="26">
         <v>5000000</v>
@@ -15442,7 +15442,7 @@
       <c r="K275" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="L275" s="29">
+      <c r="L275" s="30">
         <v>100</v>
       </c>
       <c r="M275" s="26" t="s">
@@ -15460,25 +15460,25 @@
     </row>
     <row r="276" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A276" s="22">
-        <v>10350022</v>
+        <v>10340022</v>
       </c>
       <c r="B276" s="22">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C276" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D276" s="35">
-        <v>102900001</v>
+        <v>75</v>
+      </c>
+      <c r="D276" s="27">
+        <v>103000001</v>
       </c>
       <c r="E276" s="67">
         <v>22</v>
       </c>
       <c r="F276" s="24" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G276" s="25" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H276" s="17">
         <v>100000000</v>
@@ -15492,7 +15492,7 @@
       <c r="K276" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="L276" s="29">
+      <c r="L276" s="30">
         <v>100</v>
       </c>
       <c r="M276" s="26" t="s">
@@ -15510,25 +15510,25 @@
     </row>
     <row r="277" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A277" s="22">
-        <v>10350023</v>
+        <v>10340023</v>
       </c>
       <c r="B277" s="22">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C277" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D277" s="35">
-        <v>102900001</v>
+        <v>75</v>
+      </c>
+      <c r="D277" s="27">
+        <v>103000001</v>
       </c>
       <c r="E277" s="67">
         <v>23</v>
       </c>
       <c r="F277" s="24" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G277" s="25" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="H277" s="31">
         <v>1000000000</v>
@@ -15542,7 +15542,7 @@
       <c r="K277" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="L277" s="29">
+      <c r="L277" s="30">
         <v>100</v>
       </c>
       <c r="M277" s="26" t="s">
@@ -15560,16 +15560,16 @@
     </row>
     <row r="278" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A278" s="22">
-        <v>10350121</v>
+        <v>10350021</v>
       </c>
       <c r="B278" s="22">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C278" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D278" s="35">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E278" s="67">
         <v>21</v>
@@ -15610,16 +15610,16 @@
     </row>
     <row r="279" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A279" s="22">
-        <v>10350122</v>
+        <v>10350022</v>
       </c>
       <c r="B279" s="22">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C279" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D279" s="35">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E279" s="67">
         <v>22</v>
@@ -15660,16 +15660,16 @@
     </row>
     <row r="280" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A280" s="22">
-        <v>10350123</v>
+        <v>10350023</v>
       </c>
       <c r="B280" s="22">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C280" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D280" s="35">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E280" s="67">
         <v>23</v>
@@ -15708,79 +15708,79 @@
       <c r="S280" s="26"/>
       <c r="T280" s="26"/>
     </row>
-    <row r="281" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A281" s="36">
-        <v>10360021</v>
-      </c>
-      <c r="B281" s="36">
-        <v>103600</v>
-      </c>
-      <c r="C281" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="D281" s="38">
-        <v>103600001</v>
+    <row r="281" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A281" s="22">
+        <v>10350121</v>
+      </c>
+      <c r="B281" s="22">
+        <v>103501</v>
+      </c>
+      <c r="C281" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D281" s="35">
+        <v>103501001</v>
       </c>
       <c r="E281" s="67">
         <v>21</v>
       </c>
-      <c r="F281" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="G281" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="H281" s="41">
+      <c r="F281" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G281" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="H281" s="17">
         <v>10000000</v>
       </c>
-      <c r="I281" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J281" s="42">
+      <c r="I281" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J281" s="26">
         <v>5000000</v>
       </c>
-      <c r="K281" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="L281" s="43">
+      <c r="K281" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L281" s="29">
         <v>100</v>
       </c>
       <c r="M281" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N281" s="39">
-        <v>0</v>
-      </c>
-      <c r="O281" s="39"/>
-      <c r="P281" s="39"/>
-      <c r="Q281" s="39"/>
-      <c r="R281" s="39"/>
-      <c r="S281" s="42"/>
-      <c r="T281" s="42"/>
+      <c r="N281" s="24">
+        <v>0</v>
+      </c>
+      <c r="O281" s="24"/>
+      <c r="P281" s="24"/>
+      <c r="Q281" s="24"/>
+      <c r="R281" s="24"/>
+      <c r="S281" s="26"/>
+      <c r="T281" s="26"/>
     </row>
     <row r="282" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A282" s="22">
-        <v>10360022</v>
+        <v>10350122</v>
       </c>
       <c r="B282" s="22">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C282" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D282" s="35">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E282" s="67">
         <v>22</v>
       </c>
       <c r="F282" s="24" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G282" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="H282" s="31">
+        <v>42</v>
+      </c>
+      <c r="H282" s="17">
         <v>100000000</v>
       </c>
       <c r="I282" s="28">
@@ -15810,25 +15810,25 @@
     </row>
     <row r="283" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A283" s="22">
-        <v>10360023</v>
+        <v>10350123</v>
       </c>
       <c r="B283" s="22">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C283" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D283" s="35">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E283" s="67">
         <v>23</v>
       </c>
       <c r="F283" s="24" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="G283" s="25" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H283" s="31">
         <v>1000000000</v>
@@ -15858,77 +15858,77 @@
       <c r="S283" s="26"/>
       <c r="T283" s="26"/>
     </row>
-    <row r="284" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A284" s="22">
-        <v>10200021</v>
-      </c>
-      <c r="B284" s="22">
-        <v>102000</v>
-      </c>
-      <c r="C284" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="D284" s="35">
-        <v>102000001</v>
+    <row r="284" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A284" s="36">
+        <v>10360021</v>
+      </c>
+      <c r="B284" s="36">
+        <v>103600</v>
+      </c>
+      <c r="C284" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D284" s="38">
+        <v>103600001</v>
       </c>
       <c r="E284" s="67">
         <v>21</v>
       </c>
-      <c r="F284" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="G284" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="H284" s="31">
+      <c r="F284" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="G284" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="H284" s="41">
         <v>10000000</v>
       </c>
-      <c r="I284" s="28">
-        <v>9500</v>
-      </c>
-      <c r="J284" s="26">
+      <c r="I284" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J284" s="42">
         <v>5000000</v>
       </c>
-      <c r="K284" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L284" s="29">
+      <c r="K284" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="L284" s="43">
         <v>100</v>
       </c>
       <c r="M284" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N284" s="24">
-        <v>0</v>
-      </c>
-      <c r="O284" s="24"/>
-      <c r="P284" s="24"/>
-      <c r="Q284" s="24"/>
-      <c r="R284" s="24"/>
-      <c r="S284" s="26"/>
-      <c r="T284" s="26"/>
+      <c r="N284" s="39">
+        <v>0</v>
+      </c>
+      <c r="O284" s="39"/>
+      <c r="P284" s="39"/>
+      <c r="Q284" s="39"/>
+      <c r="R284" s="39"/>
+      <c r="S284" s="42"/>
+      <c r="T284" s="42"/>
     </row>
     <row r="285" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A285" s="22">
-        <v>10200022</v>
+        <v>10360022</v>
       </c>
       <c r="B285" s="22">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C285" s="23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D285" s="35">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="E285" s="67">
         <v>22</v>
       </c>
       <c r="F285" s="24" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G285" s="25" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="H285" s="31">
         <v>100000000</v>
@@ -15960,25 +15960,25 @@
     </row>
     <row r="286" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A286" s="22">
-        <v>10200023</v>
+        <v>10360023</v>
       </c>
       <c r="B286" s="22">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C286" s="23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D286" s="35">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="E286" s="67">
         <v>23</v>
       </c>
       <c r="F286" s="24" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G286" s="25" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H286" s="31">
         <v>1000000000</v>
@@ -16010,25 +16010,25 @@
     </row>
     <row r="287" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A287" s="22">
-        <v>10340121</v>
+        <v>10200021</v>
       </c>
       <c r="B287" s="22">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C287" s="23" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D287" s="35">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E287" s="67">
         <v>21</v>
       </c>
       <c r="F287" s="24" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G287" s="25" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H287" s="31">
         <v>10000000</v>
@@ -16060,25 +16060,25 @@
     </row>
     <row r="288" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A288" s="22">
-        <v>10340122</v>
+        <v>10200022</v>
       </c>
       <c r="B288" s="22">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C288" s="23" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D288" s="35">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E288" s="67">
         <v>22</v>
       </c>
       <c r="F288" s="24" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G288" s="25" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="H288" s="31">
         <v>100000000</v>
@@ -16110,25 +16110,25 @@
     </row>
     <row r="289" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A289" s="22">
-        <v>10340123</v>
+        <v>10200023</v>
       </c>
       <c r="B289" s="22">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C289" s="23" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D289" s="35">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E289" s="67">
         <v>23</v>
       </c>
       <c r="F289" s="24" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G289" s="25" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H289" s="31">
         <v>1000000000</v>
@@ -16160,25 +16160,25 @@
     </row>
     <row r="290" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A290" s="22">
-        <v>10380021</v>
+        <v>10340121</v>
       </c>
       <c r="B290" s="22">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C290" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D290" s="35">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E290" s="67">
         <v>21</v>
       </c>
       <c r="F290" s="24" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G290" s="25" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="H290" s="31">
         <v>10000000</v>
@@ -16210,25 +16210,25 @@
     </row>
     <row r="291" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A291" s="22">
-        <v>10380022</v>
+        <v>10340122</v>
       </c>
       <c r="B291" s="22">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C291" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D291" s="35">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E291" s="67">
         <v>22</v>
       </c>
       <c r="F291" s="24" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="G291" s="25" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H291" s="31">
         <v>100000000</v>
@@ -16260,25 +16260,25 @@
     </row>
     <row r="292" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A292" s="22">
-        <v>10380023</v>
+        <v>10340123</v>
       </c>
       <c r="B292" s="22">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C292" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D292" s="35">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E292" s="67">
         <v>23</v>
       </c>
       <c r="F292" s="24" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G292" s="25" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="H292" s="31">
         <v>1000000000</v>
@@ -16310,16 +16310,16 @@
     </row>
     <row r="293" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A293" s="22">
-        <v>10400021</v>
+        <v>10380021</v>
       </c>
       <c r="B293" s="22">
-        <v>104000</v>
+        <v>103800</v>
       </c>
       <c r="C293" s="23" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D293" s="35">
-        <v>104000001</v>
+        <v>103800001</v>
       </c>
       <c r="E293" s="67">
         <v>21</v>
@@ -16360,16 +16360,16 @@
     </row>
     <row r="294" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A294" s="22">
-        <v>10400022</v>
+        <v>10380022</v>
       </c>
       <c r="B294" s="22">
-        <v>104000</v>
+        <v>103800</v>
       </c>
       <c r="C294" s="23" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D294" s="35">
-        <v>104000001</v>
+        <v>103800001</v>
       </c>
       <c r="E294" s="67">
         <v>22</v>
@@ -16410,16 +16410,16 @@
     </row>
     <row r="295" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A295" s="22">
-        <v>10400023</v>
+        <v>10380023</v>
       </c>
       <c r="B295" s="22">
-        <v>104000</v>
+        <v>103800</v>
       </c>
       <c r="C295" s="23" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D295" s="35">
-        <v>104000001</v>
+        <v>103800001</v>
       </c>
       <c r="E295" s="67">
         <v>23</v>
@@ -16457,6 +16457,156 @@
       <c r="R295" s="24"/>
       <c r="S295" s="26"/>
       <c r="T295" s="26"/>
+    </row>
+    <row r="296" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A296" s="22">
+        <v>10400021</v>
+      </c>
+      <c r="B296" s="22">
+        <v>104000</v>
+      </c>
+      <c r="C296" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D296" s="35">
+        <v>104000001</v>
+      </c>
+      <c r="E296" s="67">
+        <v>21</v>
+      </c>
+      <c r="F296" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="G296" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="H296" s="31">
+        <v>10000000</v>
+      </c>
+      <c r="I296" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J296" s="26">
+        <v>5000000</v>
+      </c>
+      <c r="K296" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L296" s="29">
+        <v>100</v>
+      </c>
+      <c r="M296" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N296" s="24">
+        <v>0</v>
+      </c>
+      <c r="O296" s="24"/>
+      <c r="P296" s="24"/>
+      <c r="Q296" s="24"/>
+      <c r="R296" s="24"/>
+      <c r="S296" s="26"/>
+      <c r="T296" s="26"/>
+    </row>
+    <row r="297" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A297" s="22">
+        <v>10400022</v>
+      </c>
+      <c r="B297" s="22">
+        <v>104000</v>
+      </c>
+      <c r="C297" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D297" s="35">
+        <v>104000001</v>
+      </c>
+      <c r="E297" s="67">
+        <v>22</v>
+      </c>
+      <c r="F297" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="G297" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="H297" s="31">
+        <v>100000000</v>
+      </c>
+      <c r="I297" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J297" s="26">
+        <v>50000000</v>
+      </c>
+      <c r="K297" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L297" s="29">
+        <v>100</v>
+      </c>
+      <c r="M297" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="N297" s="24">
+        <v>0</v>
+      </c>
+      <c r="O297" s="24"/>
+      <c r="P297" s="24"/>
+      <c r="Q297" s="24"/>
+      <c r="R297" s="24"/>
+      <c r="S297" s="26"/>
+      <c r="T297" s="26"/>
+    </row>
+    <row r="298" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A298" s="22">
+        <v>10400023</v>
+      </c>
+      <c r="B298" s="22">
+        <v>104000</v>
+      </c>
+      <c r="C298" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D298" s="35">
+        <v>104000001</v>
+      </c>
+      <c r="E298" s="67">
+        <v>23</v>
+      </c>
+      <c r="F298" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G298" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="H298" s="31">
+        <v>1000000000</v>
+      </c>
+      <c r="I298" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J298" s="26">
+        <v>500000000</v>
+      </c>
+      <c r="K298" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L298" s="29">
+        <v>100</v>
+      </c>
+      <c r="M298" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="N298" s="24">
+        <v>0</v>
+      </c>
+      <c r="O298" s="24"/>
+      <c r="P298" s="24"/>
+      <c r="Q298" s="24"/>
+      <c r="R298" s="24"/>
+      <c r="S298" s="26"/>
+      <c r="T298" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="137">
   <si>
     <t>id</t>
   </si>
@@ -569,6 +569,9 @@
     <t>赏金大对决</t>
   </si>
   <si>
+    <t>连环夺宝</t>
+  </si>
+  <si>
     <t>1980000_500000</t>
   </si>
   <si>
@@ -820,18 +823,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -844,7 +842,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1911,7 +1914,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T298"/>
+  <dimension ref="A1:T301"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -7638,177 +7641,177 @@
       <c r="S115" s="48"/>
       <c r="T115" s="48"/>
     </row>
-    <row r="116" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A116" s="49">
-        <v>10010010</v>
-      </c>
-      <c r="B116" s="49">
-        <v>100100</v>
-      </c>
-      <c r="C116" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D116" s="51">
-        <v>100100026</v>
-      </c>
-      <c r="E116" s="52">
-        <v>10</v>
+    <row r="116" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A116" s="22">
+        <v>1052001</v>
+      </c>
+      <c r="B116" s="22">
+        <v>105200</v>
+      </c>
+      <c r="C116" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D116" s="35">
+        <v>105100001</v>
+      </c>
+      <c r="E116" s="23">
+        <v>1</v>
       </c>
       <c r="F116" s="24" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G116" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="H116" s="53">
-        <v>0</v>
-      </c>
-      <c r="I116" s="45">
-        <v>9500</v>
-      </c>
-      <c r="J116" s="54">
-        <v>0</v>
-      </c>
-      <c r="K116" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L116" s="55">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="H116" s="31">
+        <v>10000000</v>
+      </c>
+      <c r="I116" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J116" s="26">
+        <v>5000000</v>
+      </c>
+      <c r="K116" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L116" s="29">
+        <v>100</v>
       </c>
       <c r="M116" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N116" s="56" t="s">
+      <c r="N116" s="24">
+        <v>0</v>
+      </c>
+      <c r="O116" s="24"/>
+      <c r="P116" s="24"/>
+      <c r="Q116" s="24"/>
+      <c r="R116" s="24"/>
+      <c r="S116" s="26"/>
+      <c r="T116" s="26"/>
+    </row>
+    <row r="117" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A117" s="22">
+        <v>1052002</v>
+      </c>
+      <c r="B117" s="22">
+        <v>105200</v>
+      </c>
+      <c r="C117" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="O116" s="44"/>
-      <c r="P116" s="44"/>
-      <c r="Q116" s="44"/>
-      <c r="R116" s="44"/>
-      <c r="S116" s="45"/>
-      <c r="T116" s="45"/>
-    </row>
-    <row r="117" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A117" s="49">
-        <v>10010011</v>
-      </c>
-      <c r="B117" s="49">
-        <v>100100</v>
-      </c>
-      <c r="C117" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D117" s="51">
-        <v>100100026</v>
-      </c>
-      <c r="E117" s="52">
-        <v>11</v>
+      <c r="D117" s="35">
+        <v>105100001</v>
+      </c>
+      <c r="E117" s="23">
+        <v>2</v>
       </c>
       <c r="F117" s="24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G117" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="H117" s="53">
-        <v>0</v>
-      </c>
-      <c r="I117" s="45">
-        <v>9500</v>
-      </c>
-      <c r="J117" s="54">
-        <v>0</v>
-      </c>
-      <c r="K117" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L117" s="55">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="H117" s="31">
+        <v>100000000</v>
+      </c>
+      <c r="I117" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J117" s="26">
+        <v>50000000</v>
+      </c>
+      <c r="K117" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L117" s="29">
+        <v>100</v>
       </c>
       <c r="M117" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="N117" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="O117" s="44"/>
-      <c r="P117" s="44"/>
-      <c r="Q117" s="44"/>
-      <c r="R117" s="44"/>
-      <c r="S117" s="45"/>
-      <c r="T117" s="45"/>
-    </row>
-    <row r="118" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A118" s="49">
-        <v>10010012</v>
-      </c>
-      <c r="B118" s="49">
-        <v>100100</v>
-      </c>
-      <c r="C118" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D118" s="51">
-        <v>100100026</v>
-      </c>
-      <c r="E118" s="52">
-        <v>12</v>
+      <c r="N117" s="24">
+        <v>0</v>
+      </c>
+      <c r="O117" s="24"/>
+      <c r="P117" s="24"/>
+      <c r="Q117" s="24"/>
+      <c r="R117" s="24"/>
+      <c r="S117" s="26"/>
+      <c r="T117" s="26"/>
+    </row>
+    <row r="118" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A118" s="22">
+        <v>1052003</v>
+      </c>
+      <c r="B118" s="22">
+        <v>105200</v>
+      </c>
+      <c r="C118" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D118" s="35">
+        <v>105100001</v>
+      </c>
+      <c r="E118" s="23">
+        <v>3</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G118" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="H118" s="57">
-        <v>0</v>
-      </c>
-      <c r="I118" s="45">
-        <v>9500</v>
-      </c>
-      <c r="J118" s="54">
-        <v>0</v>
-      </c>
-      <c r="K118" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L118" s="55">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="H118" s="31">
+        <v>1000000000</v>
+      </c>
+      <c r="I118" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J118" s="26">
+        <v>500000000</v>
+      </c>
+      <c r="K118" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L118" s="29">
+        <v>100</v>
       </c>
       <c r="M118" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="N118" s="56" t="s">
-        <v>129</v>
-      </c>
-      <c r="O118" s="44"/>
-      <c r="P118" s="44"/>
-      <c r="Q118" s="44"/>
-      <c r="R118" s="44"/>
-      <c r="S118" s="45"/>
-      <c r="T118" s="45"/>
+      <c r="N118" s="24">
+        <v>0</v>
+      </c>
+      <c r="O118" s="24"/>
+      <c r="P118" s="24"/>
+      <c r="Q118" s="24"/>
+      <c r="R118" s="24"/>
+      <c r="S118" s="26"/>
+      <c r="T118" s="26"/>
     </row>
     <row r="119" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A119" s="49">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B119" s="49">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C119" s="50" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D119" s="51">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E119" s="52">
         <v>10</v>
       </c>
       <c r="F119" s="24" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G119" s="25" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H119" s="53">
         <v>0</v>
@@ -7822,14 +7825,14 @@
       <c r="K119" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L119" s="58">
+      <c r="L119" s="55">
         <v>0</v>
       </c>
       <c r="M119" s="26" t="s">
         <v>37</v>
       </c>
       <c r="N119" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O119" s="44"/>
       <c r="P119" s="44"/>
@@ -7840,25 +7843,25 @@
     </row>
     <row r="120" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A120" s="49">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B120" s="49">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C120" s="50" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D120" s="51">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E120" s="52">
         <v>11</v>
       </c>
       <c r="F120" s="24" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G120" s="25" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H120" s="53">
         <v>0</v>
@@ -7872,14 +7875,14 @@
       <c r="K120" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L120" s="58">
+      <c r="L120" s="55">
         <v>0</v>
       </c>
       <c r="M120" s="26" t="s">
         <v>40</v>
       </c>
       <c r="N120" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O120" s="44"/>
       <c r="P120" s="44"/>
@@ -7890,25 +7893,25 @@
     </row>
     <row r="121" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A121" s="49">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B121" s="49">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C121" s="50" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D121" s="51">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E121" s="52">
         <v>12</v>
       </c>
       <c r="F121" s="24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G121" s="25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H121" s="57">
         <v>0</v>
@@ -7922,14 +7925,14 @@
       <c r="K121" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L121" s="58">
+      <c r="L121" s="55">
         <v>0</v>
       </c>
       <c r="M121" s="26" t="s">
         <v>43</v>
       </c>
       <c r="N121" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O121" s="44"/>
       <c r="P121" s="44"/>
@@ -7940,25 +7943,25 @@
     </row>
     <row r="122" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A122" s="49">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B122" s="49">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C122" s="50" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D122" s="51">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E122" s="52">
         <v>10</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G122" s="25" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H122" s="53">
         <v>0</v>
@@ -7972,14 +7975,14 @@
       <c r="K122" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L122" s="55">
+      <c r="L122" s="58">
         <v>0</v>
       </c>
       <c r="M122" s="26" t="s">
         <v>37</v>
       </c>
       <c r="N122" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O122" s="44"/>
       <c r="P122" s="44"/>
@@ -7990,25 +7993,25 @@
     </row>
     <row r="123" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A123" s="49">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B123" s="49">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C123" s="50" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D123" s="51">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E123" s="52">
         <v>11</v>
       </c>
       <c r="F123" s="24" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G123" s="25" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H123" s="53">
         <v>0</v>
@@ -8022,14 +8025,14 @@
       <c r="K123" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L123" s="55">
+      <c r="L123" s="58">
         <v>0</v>
       </c>
       <c r="M123" s="26" t="s">
         <v>40</v>
       </c>
       <c r="N123" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O123" s="44"/>
       <c r="P123" s="44"/>
@@ -8040,25 +8043,25 @@
     </row>
     <row r="124" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A124" s="49">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B124" s="49">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C124" s="50" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D124" s="51">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E124" s="52">
         <v>12</v>
       </c>
       <c r="F124" s="24" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G124" s="25" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H124" s="57">
         <v>0</v>
@@ -8072,14 +8075,14 @@
       <c r="K124" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L124" s="55">
+      <c r="L124" s="58">
         <v>0</v>
       </c>
       <c r="M124" s="26" t="s">
         <v>43</v>
       </c>
       <c r="N124" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O124" s="44"/>
       <c r="P124" s="44"/>
@@ -8088,168 +8091,168 @@
       <c r="S124" s="45"/>
       <c r="T124" s="45"/>
     </row>
-    <row r="125" s="6" customFormat="1" ht="16.5" spans="1:20">
+    <row r="125" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A125" s="49">
-        <v>10120010</v>
-      </c>
-      <c r="B125" s="59">
-        <v>101200</v>
-      </c>
-      <c r="C125" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="D125" s="60">
-        <v>101200001</v>
+        <v>10070010</v>
+      </c>
+      <c r="B125" s="49">
+        <v>100700</v>
+      </c>
+      <c r="C125" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D125" s="51">
+        <v>100700001</v>
       </c>
       <c r="E125" s="52">
         <v>10</v>
       </c>
       <c r="F125" s="24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G125" s="25" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H125" s="53">
         <v>0</v>
       </c>
-      <c r="I125" s="54">
+      <c r="I125" s="45">
         <v>9500</v>
       </c>
       <c r="J125" s="54">
         <v>0</v>
       </c>
-      <c r="K125" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L125" s="58">
+      <c r="K125" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L125" s="55">
         <v>0</v>
       </c>
       <c r="M125" s="26" t="s">
         <v>37</v>
       </c>
       <c r="N125" s="56" t="s">
-        <v>127</v>
-      </c>
-      <c r="O125" s="56"/>
-      <c r="P125" s="56"/>
-      <c r="Q125" s="56"/>
-      <c r="R125" s="56"/>
-      <c r="S125" s="54"/>
-      <c r="T125" s="54"/>
-    </row>
-    <row r="126" s="6" customFormat="1" ht="16.5" spans="1:20">
+        <v>128</v>
+      </c>
+      <c r="O125" s="44"/>
+      <c r="P125" s="44"/>
+      <c r="Q125" s="44"/>
+      <c r="R125" s="44"/>
+      <c r="S125" s="45"/>
+      <c r="T125" s="45"/>
+    </row>
+    <row r="126" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A126" s="49">
-        <v>10120011</v>
-      </c>
-      <c r="B126" s="59">
-        <v>101200</v>
-      </c>
-      <c r="C126" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="D126" s="60">
-        <v>101200001</v>
+        <v>10070011</v>
+      </c>
+      <c r="B126" s="49">
+        <v>100700</v>
+      </c>
+      <c r="C126" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D126" s="51">
+        <v>100700001</v>
       </c>
       <c r="E126" s="52">
         <v>11</v>
       </c>
       <c r="F126" s="24" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G126" s="25" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H126" s="53">
         <v>0</v>
       </c>
-      <c r="I126" s="54">
+      <c r="I126" s="45">
         <v>9500</v>
       </c>
       <c r="J126" s="54">
         <v>0</v>
       </c>
-      <c r="K126" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L126" s="58">
+      <c r="K126" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L126" s="55">
         <v>0</v>
       </c>
       <c r="M126" s="26" t="s">
         <v>40</v>
       </c>
       <c r="N126" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="O126" s="56"/>
-      <c r="P126" s="56"/>
-      <c r="Q126" s="56"/>
-      <c r="R126" s="56"/>
-      <c r="S126" s="54"/>
-      <c r="T126" s="54"/>
-    </row>
-    <row r="127" s="6" customFormat="1" ht="16.5" spans="1:20">
+        <v>129</v>
+      </c>
+      <c r="O126" s="44"/>
+      <c r="P126" s="44"/>
+      <c r="Q126" s="44"/>
+      <c r="R126" s="44"/>
+      <c r="S126" s="45"/>
+      <c r="T126" s="45"/>
+    </row>
+    <row r="127" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A127" s="49">
-        <v>10120012</v>
-      </c>
-      <c r="B127" s="59">
-        <v>101200</v>
-      </c>
-      <c r="C127" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="D127" s="60">
-        <v>101200001</v>
+        <v>10070012</v>
+      </c>
+      <c r="B127" s="49">
+        <v>100700</v>
+      </c>
+      <c r="C127" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D127" s="51">
+        <v>100700001</v>
       </c>
       <c r="E127" s="52">
         <v>12</v>
       </c>
       <c r="F127" s="24" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G127" s="25" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H127" s="57">
         <v>0</v>
       </c>
-      <c r="I127" s="54">
+      <c r="I127" s="45">
         <v>9500</v>
       </c>
       <c r="J127" s="54">
         <v>0</v>
       </c>
-      <c r="K127" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="L127" s="58">
+      <c r="K127" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L127" s="55">
         <v>0</v>
       </c>
       <c r="M127" s="26" t="s">
         <v>43</v>
       </c>
       <c r="N127" s="56" t="s">
-        <v>129</v>
-      </c>
-      <c r="O127" s="56"/>
-      <c r="P127" s="56"/>
-      <c r="Q127" s="56"/>
-      <c r="R127" s="56"/>
-      <c r="S127" s="54"/>
-      <c r="T127" s="54"/>
-    </row>
-    <row r="128" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>130</v>
+      </c>
+      <c r="O127" s="44"/>
+      <c r="P127" s="44"/>
+      <c r="Q127" s="44"/>
+      <c r="R127" s="44"/>
+      <c r="S127" s="45"/>
+      <c r="T127" s="45"/>
+    </row>
+    <row r="128" s="6" customFormat="1" ht="16.5" spans="1:20">
       <c r="A128" s="49">
-        <v>10140010</v>
-      </c>
-      <c r="B128" s="49">
-        <v>101400</v>
-      </c>
-      <c r="C128" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="D128" s="51">
-        <v>101400001</v>
+        <v>10120010</v>
+      </c>
+      <c r="B128" s="59">
+        <v>101200</v>
+      </c>
+      <c r="C128" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D128" s="60">
+        <v>101200001</v>
       </c>
       <c r="E128" s="52">
         <v>10</v>
@@ -8263,43 +8266,43 @@
       <c r="H128" s="53">
         <v>0</v>
       </c>
-      <c r="I128" s="45">
+      <c r="I128" s="54">
         <v>9500</v>
       </c>
       <c r="J128" s="54">
         <v>0</v>
       </c>
-      <c r="K128" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L128" s="55">
+      <c r="K128" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="L128" s="58">
         <v>0</v>
       </c>
       <c r="M128" s="26" t="s">
         <v>37</v>
       </c>
       <c r="N128" s="56" t="s">
-        <v>127</v>
-      </c>
-      <c r="O128" s="44"/>
-      <c r="P128" s="44"/>
-      <c r="Q128" s="44"/>
-      <c r="R128" s="44"/>
-      <c r="S128" s="45"/>
-      <c r="T128" s="45"/>
-    </row>
-    <row r="129" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>128</v>
+      </c>
+      <c r="O128" s="56"/>
+      <c r="P128" s="56"/>
+      <c r="Q128" s="56"/>
+      <c r="R128" s="56"/>
+      <c r="S128" s="54"/>
+      <c r="T128" s="54"/>
+    </row>
+    <row r="129" s="6" customFormat="1" ht="16.5" spans="1:20">
       <c r="A129" s="49">
-        <v>10140011</v>
-      </c>
-      <c r="B129" s="49">
-        <v>101400</v>
-      </c>
-      <c r="C129" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="D129" s="51">
-        <v>101400001</v>
+        <v>10120011</v>
+      </c>
+      <c r="B129" s="59">
+        <v>101200</v>
+      </c>
+      <c r="C129" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D129" s="60">
+        <v>101200001</v>
       </c>
       <c r="E129" s="52">
         <v>11</v>
@@ -8313,43 +8316,43 @@
       <c r="H129" s="53">
         <v>0</v>
       </c>
-      <c r="I129" s="45">
+      <c r="I129" s="54">
         <v>9500</v>
       </c>
       <c r="J129" s="54">
         <v>0</v>
       </c>
-      <c r="K129" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L129" s="55">
+      <c r="K129" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="L129" s="58">
         <v>0</v>
       </c>
       <c r="M129" s="26" t="s">
         <v>40</v>
       </c>
       <c r="N129" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="O129" s="44"/>
-      <c r="P129" s="44"/>
-      <c r="Q129" s="44"/>
-      <c r="R129" s="44"/>
-      <c r="S129" s="45"/>
-      <c r="T129" s="45"/>
-    </row>
-    <row r="130" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>129</v>
+      </c>
+      <c r="O129" s="56"/>
+      <c r="P129" s="56"/>
+      <c r="Q129" s="56"/>
+      <c r="R129" s="56"/>
+      <c r="S129" s="54"/>
+      <c r="T129" s="54"/>
+    </row>
+    <row r="130" s="6" customFormat="1" ht="16.5" spans="1:20">
       <c r="A130" s="49">
-        <v>10140012</v>
-      </c>
-      <c r="B130" s="49">
-        <v>101400</v>
-      </c>
-      <c r="C130" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="D130" s="51">
-        <v>101400001</v>
+        <v>10120012</v>
+      </c>
+      <c r="B130" s="59">
+        <v>101200</v>
+      </c>
+      <c r="C130" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D130" s="60">
+        <v>101200001</v>
       </c>
       <c r="E130" s="52">
         <v>12</v>
@@ -8363,52 +8366,52 @@
       <c r="H130" s="57">
         <v>0</v>
       </c>
-      <c r="I130" s="45">
+      <c r="I130" s="54">
         <v>9500</v>
       </c>
       <c r="J130" s="54">
         <v>0</v>
       </c>
-      <c r="K130" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="L130" s="55">
+      <c r="K130" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="L130" s="58">
         <v>0</v>
       </c>
       <c r="M130" s="26" t="s">
         <v>43</v>
       </c>
       <c r="N130" s="56" t="s">
-        <v>129</v>
-      </c>
-      <c r="O130" s="44"/>
-      <c r="P130" s="44"/>
-      <c r="Q130" s="44"/>
-      <c r="R130" s="44"/>
-      <c r="S130" s="45"/>
-      <c r="T130" s="45"/>
+        <v>130</v>
+      </c>
+      <c r="O130" s="56"/>
+      <c r="P130" s="56"/>
+      <c r="Q130" s="56"/>
+      <c r="R130" s="56"/>
+      <c r="S130" s="54"/>
+      <c r="T130" s="54"/>
     </row>
     <row r="131" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A131" s="49">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B131" s="49">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D131" s="51">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E131" s="52">
         <v>10</v>
       </c>
       <c r="F131" s="24" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G131" s="25" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H131" s="53">
         <v>0</v>
@@ -8429,7 +8432,7 @@
         <v>37</v>
       </c>
       <c r="N131" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O131" s="44"/>
       <c r="P131" s="44"/>
@@ -8440,25 +8443,25 @@
     </row>
     <row r="132" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A132" s="49">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B132" s="49">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D132" s="51">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E132" s="52">
         <v>11</v>
       </c>
       <c r="F132" s="24" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G132" s="25" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H132" s="53">
         <v>0</v>
@@ -8479,7 +8482,7 @@
         <v>40</v>
       </c>
       <c r="N132" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O132" s="44"/>
       <c r="P132" s="44"/>
@@ -8490,25 +8493,25 @@
     </row>
     <row r="133" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A133" s="49">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B133" s="49">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D133" s="51">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E133" s="52">
         <v>12</v>
       </c>
       <c r="F133" s="24" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G133" s="25" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H133" s="57">
         <v>0</v>
@@ -8529,7 +8532,7 @@
         <v>43</v>
       </c>
       <c r="N133" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O133" s="44"/>
       <c r="P133" s="44"/>
@@ -8540,16 +8543,16 @@
     </row>
     <row r="134" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A134" s="49">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B134" s="49">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D134" s="51">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E134" s="52">
         <v>10</v>
@@ -8572,14 +8575,14 @@
       <c r="K134" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L134" s="58">
+      <c r="L134" s="55">
         <v>0</v>
       </c>
       <c r="M134" s="26" t="s">
         <v>37</v>
       </c>
       <c r="N134" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O134" s="44"/>
       <c r="P134" s="44"/>
@@ -8590,16 +8593,16 @@
     </row>
     <row r="135" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A135" s="49">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B135" s="49">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D135" s="51">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E135" s="52">
         <v>11</v>
@@ -8622,14 +8625,14 @@
       <c r="K135" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L135" s="58">
+      <c r="L135" s="55">
         <v>0</v>
       </c>
       <c r="M135" s="26" t="s">
         <v>40</v>
       </c>
       <c r="N135" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O135" s="44"/>
       <c r="P135" s="44"/>
@@ -8640,16 +8643,16 @@
     </row>
     <row r="136" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A136" s="49">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B136" s="49">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D136" s="51">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E136" s="52">
         <v>12</v>
@@ -8672,14 +8675,14 @@
       <c r="K136" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="L136" s="58">
+      <c r="L136" s="55">
         <v>0</v>
       </c>
       <c r="M136" s="26" t="s">
         <v>43</v>
       </c>
       <c r="N136" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O136" s="44"/>
       <c r="P136" s="44"/>
@@ -8690,16 +8693,16 @@
     </row>
     <row r="137" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A137" s="49">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B137" s="49">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D137" s="51">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E137" s="52">
         <v>10</v>
@@ -8729,7 +8732,7 @@
         <v>37</v>
       </c>
       <c r="N137" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O137" s="44"/>
       <c r="P137" s="44"/>
@@ -8740,16 +8743,16 @@
     </row>
     <row r="138" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A138" s="49">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B138" s="49">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D138" s="51">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E138" s="52">
         <v>11</v>
@@ -8779,7 +8782,7 @@
         <v>40</v>
       </c>
       <c r="N138" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O138" s="44"/>
       <c r="P138" s="44"/>
@@ -8790,16 +8793,16 @@
     </row>
     <row r="139" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A139" s="49">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B139" s="49">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D139" s="51">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E139" s="52">
         <v>12</v>
@@ -8829,7 +8832,7 @@
         <v>43</v>
       </c>
       <c r="N139" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O139" s="44"/>
       <c r="P139" s="44"/>
@@ -8840,25 +8843,25 @@
     </row>
     <row r="140" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A140" s="49">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B140" s="49">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C140" s="50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D140" s="51">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E140" s="52">
         <v>10</v>
       </c>
       <c r="F140" s="24" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G140" s="25" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H140" s="53">
         <v>0</v>
@@ -8879,7 +8882,7 @@
         <v>37</v>
       </c>
       <c r="N140" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O140" s="44"/>
       <c r="P140" s="44"/>
@@ -8890,25 +8893,25 @@
     </row>
     <row r="141" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A141" s="49">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B141" s="49">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D141" s="51">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E141" s="52">
         <v>11</v>
       </c>
       <c r="F141" s="24" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G141" s="25" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H141" s="53">
         <v>0</v>
@@ -8929,7 +8932,7 @@
         <v>40</v>
       </c>
       <c r="N141" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O141" s="44"/>
       <c r="P141" s="44"/>
@@ -8940,25 +8943,25 @@
     </row>
     <row r="142" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A142" s="49">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B142" s="49">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D142" s="51">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E142" s="52">
         <v>12</v>
       </c>
       <c r="F142" s="24" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G142" s="25" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H142" s="57">
         <v>0</v>
@@ -8979,7 +8982,7 @@
         <v>43</v>
       </c>
       <c r="N142" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O142" s="44"/>
       <c r="P142" s="44"/>
@@ -8990,27 +8993,27 @@
     </row>
     <row r="143" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A143" s="49">
-        <v>10180010</v>
+        <v>10240010</v>
       </c>
       <c r="B143" s="49">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D143" s="51">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E143" s="52">
         <v>10</v>
       </c>
       <c r="F143" s="24" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G143" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H143" s="57">
+        <v>35</v>
+      </c>
+      <c r="H143" s="53">
         <v>0</v>
       </c>
       <c r="I143" s="45">
@@ -9029,7 +9032,7 @@
         <v>37</v>
       </c>
       <c r="N143" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O143" s="44"/>
       <c r="P143" s="44"/>
@@ -9040,27 +9043,27 @@
     </row>
     <row r="144" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A144" s="49">
-        <v>10180011</v>
+        <v>10240011</v>
       </c>
       <c r="B144" s="49">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D144" s="51">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E144" s="52">
         <v>11</v>
       </c>
       <c r="F144" s="24" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G144" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="H144" s="57">
+        <v>39</v>
+      </c>
+      <c r="H144" s="53">
         <v>0</v>
       </c>
       <c r="I144" s="45">
@@ -9079,7 +9082,7 @@
         <v>40</v>
       </c>
       <c r="N144" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O144" s="44"/>
       <c r="P144" s="44"/>
@@ -9090,25 +9093,25 @@
     </row>
     <row r="145" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A145" s="49">
-        <v>10180012</v>
+        <v>10240012</v>
       </c>
       <c r="B145" s="49">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D145" s="51">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E145" s="52">
         <v>12</v>
       </c>
       <c r="F145" s="24" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G145" s="25" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H145" s="57">
         <v>0</v>
@@ -9129,7 +9132,7 @@
         <v>43</v>
       </c>
       <c r="N145" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O145" s="44"/>
       <c r="P145" s="44"/>
@@ -9140,25 +9143,25 @@
     </row>
     <row r="146" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A146" s="49">
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B146" s="49">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D146" s="51">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E146" s="52">
         <v>10</v>
       </c>
       <c r="F146" s="24" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G146" s="25" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H146" s="57">
         <v>0</v>
@@ -9179,7 +9182,7 @@
         <v>37</v>
       </c>
       <c r="N146" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O146" s="44"/>
       <c r="P146" s="44"/>
@@ -9190,25 +9193,25 @@
     </row>
     <row r="147" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A147" s="49">
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B147" s="49">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D147" s="51">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E147" s="52">
         <v>11</v>
       </c>
       <c r="F147" s="24" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G147" s="25" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="H147" s="57">
         <v>0</v>
@@ -9229,7 +9232,7 @@
         <v>40</v>
       </c>
       <c r="N147" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O147" s="44"/>
       <c r="P147" s="44"/>
@@ -9240,25 +9243,25 @@
     </row>
     <row r="148" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A148" s="49">
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B148" s="49">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C148" s="50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D148" s="51">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E148" s="52">
         <v>12</v>
       </c>
       <c r="F148" s="24" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G148" s="25" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H148" s="57">
         <v>0</v>
@@ -9279,7 +9282,7 @@
         <v>43</v>
       </c>
       <c r="N148" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O148" s="44"/>
       <c r="P148" s="44"/>
@@ -9290,25 +9293,25 @@
     </row>
     <row r="149" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A149" s="49">
-        <v>10230010</v>
+        <v>10250010</v>
       </c>
       <c r="B149" s="49">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D149" s="51">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E149" s="52">
         <v>10</v>
       </c>
       <c r="F149" s="24" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G149" s="25" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H149" s="57">
         <v>0</v>
@@ -9329,7 +9332,7 @@
         <v>37</v>
       </c>
       <c r="N149" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O149" s="44"/>
       <c r="P149" s="44"/>
@@ -9340,25 +9343,25 @@
     </row>
     <row r="150" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A150" s="49">
-        <v>10230011</v>
+        <v>10250011</v>
       </c>
       <c r="B150" s="49">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D150" s="51">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E150" s="52">
         <v>11</v>
       </c>
       <c r="F150" s="24" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G150" s="25" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H150" s="57">
         <v>0</v>
@@ -9379,7 +9382,7 @@
         <v>40</v>
       </c>
       <c r="N150" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O150" s="44"/>
       <c r="P150" s="44"/>
@@ -9390,25 +9393,25 @@
     </row>
     <row r="151" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A151" s="49">
-        <v>10230012</v>
+        <v>10250012</v>
       </c>
       <c r="B151" s="49">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C151" s="50" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D151" s="51">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E151" s="52">
         <v>12</v>
       </c>
       <c r="F151" s="24" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G151" s="25" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="H151" s="57">
         <v>0</v>
@@ -9429,7 +9432,7 @@
         <v>43</v>
       </c>
       <c r="N151" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O151" s="44"/>
       <c r="P151" s="44"/>
@@ -9440,25 +9443,25 @@
     </row>
     <row r="152" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A152" s="49">
-        <v>10340010</v>
+        <v>10230010</v>
       </c>
       <c r="B152" s="49">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C152" s="50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D152" s="51">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E152" s="52">
         <v>10</v>
       </c>
       <c r="F152" s="24" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G152" s="25" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H152" s="57">
         <v>0</v>
@@ -9479,7 +9482,7 @@
         <v>37</v>
       </c>
       <c r="N152" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O152" s="44"/>
       <c r="P152" s="44"/>
@@ -9490,25 +9493,25 @@
     </row>
     <row r="153" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A153" s="49">
-        <v>10340011</v>
+        <v>10230011</v>
       </c>
       <c r="B153" s="49">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D153" s="51">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E153" s="52">
         <v>11</v>
       </c>
       <c r="F153" s="24" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G153" s="25" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H153" s="57">
         <v>0</v>
@@ -9529,7 +9532,7 @@
         <v>40</v>
       </c>
       <c r="N153" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O153" s="44"/>
       <c r="P153" s="44"/>
@@ -9540,25 +9543,25 @@
     </row>
     <row r="154" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A154" s="49">
-        <v>10340012</v>
+        <v>10230012</v>
       </c>
       <c r="B154" s="49">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D154" s="51">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E154" s="52">
         <v>12</v>
       </c>
       <c r="F154" s="24" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="G154" s="25" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H154" s="57">
         <v>0</v>
@@ -9579,7 +9582,7 @@
         <v>43</v>
       </c>
       <c r="N154" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O154" s="44"/>
       <c r="P154" s="44"/>
@@ -9590,25 +9593,25 @@
     </row>
     <row r="155" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A155" s="49">
-        <v>10350010</v>
+        <v>10340010</v>
       </c>
       <c r="B155" s="49">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D155" s="51">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E155" s="52">
         <v>10</v>
       </c>
       <c r="F155" s="24" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G155" s="25" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="H155" s="57">
         <v>0</v>
@@ -9629,7 +9632,7 @@
         <v>37</v>
       </c>
       <c r="N155" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O155" s="44"/>
       <c r="P155" s="44"/>
@@ -9640,25 +9643,25 @@
     </row>
     <row r="156" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A156" s="49">
-        <v>10350011</v>
+        <v>10340011</v>
       </c>
       <c r="B156" s="49">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D156" s="51">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E156" s="52">
         <v>11</v>
       </c>
       <c r="F156" s="24" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G156" s="25" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H156" s="57">
         <v>0</v>
@@ -9679,7 +9682,7 @@
         <v>40</v>
       </c>
       <c r="N156" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O156" s="44"/>
       <c r="P156" s="44"/>
@@ -9690,25 +9693,25 @@
     </row>
     <row r="157" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A157" s="49">
-        <v>10350012</v>
+        <v>10340012</v>
       </c>
       <c r="B157" s="49">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C157" s="50" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D157" s="51">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E157" s="52">
         <v>12</v>
       </c>
       <c r="F157" s="24" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G157" s="25" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="H157" s="57">
         <v>0</v>
@@ -9729,7 +9732,7 @@
         <v>43</v>
       </c>
       <c r="N157" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O157" s="44"/>
       <c r="P157" s="44"/>
@@ -9740,16 +9743,16 @@
     </row>
     <row r="158" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A158" s="49">
-        <v>10350110</v>
+        <v>10350010</v>
       </c>
       <c r="B158" s="49">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C158" s="50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D158" s="51">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E158" s="52">
         <v>10</v>
@@ -9779,7 +9782,7 @@
         <v>37</v>
       </c>
       <c r="N158" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O158" s="44"/>
       <c r="P158" s="44"/>
@@ -9790,16 +9793,16 @@
     </row>
     <row r="159" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A159" s="49">
-        <v>10350111</v>
+        <v>10350011</v>
       </c>
       <c r="B159" s="49">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C159" s="50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D159" s="51">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E159" s="52">
         <v>11</v>
@@ -9829,7 +9832,7 @@
         <v>40</v>
       </c>
       <c r="N159" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O159" s="44"/>
       <c r="P159" s="44"/>
@@ -9840,16 +9843,16 @@
     </row>
     <row r="160" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A160" s="49">
-        <v>10350112</v>
+        <v>10350012</v>
       </c>
       <c r="B160" s="49">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C160" s="50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D160" s="51">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E160" s="52">
         <v>12</v>
@@ -9879,7 +9882,7 @@
         <v>43</v>
       </c>
       <c r="N160" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O160" s="44"/>
       <c r="P160" s="44"/>
@@ -9890,27 +9893,27 @@
     </row>
     <row r="161" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A161" s="49">
-        <v>10360010</v>
+        <v>10350110</v>
       </c>
       <c r="B161" s="49">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C161" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D161" s="51">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E161" s="52">
         <v>10</v>
       </c>
       <c r="F161" s="24" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="G161" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H161" s="53">
+        <v>39</v>
+      </c>
+      <c r="H161" s="57">
         <v>0</v>
       </c>
       <c r="I161" s="45">
@@ -9929,7 +9932,7 @@
         <v>37</v>
       </c>
       <c r="N161" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O161" s="44"/>
       <c r="P161" s="44"/>
@@ -9940,27 +9943,27 @@
     </row>
     <row r="162" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A162" s="49">
-        <v>10360011</v>
+        <v>10350111</v>
       </c>
       <c r="B162" s="49">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C162" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D162" s="51">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E162" s="52">
         <v>11</v>
       </c>
       <c r="F162" s="24" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G162" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="H162" s="53">
+        <v>42</v>
+      </c>
+      <c r="H162" s="57">
         <v>0</v>
       </c>
       <c r="I162" s="45">
@@ -9979,7 +9982,7 @@
         <v>40</v>
       </c>
       <c r="N162" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O162" s="44"/>
       <c r="P162" s="44"/>
@@ -9990,25 +9993,25 @@
     </row>
     <row r="163" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A163" s="49">
-        <v>10360012</v>
+        <v>10350112</v>
       </c>
       <c r="B163" s="49">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C163" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D163" s="51">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E163" s="52">
         <v>12</v>
       </c>
       <c r="F163" s="24" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="G163" s="25" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H163" s="57">
         <v>0</v>
@@ -10029,7 +10032,7 @@
         <v>43</v>
       </c>
       <c r="N163" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O163" s="44"/>
       <c r="P163" s="44"/>
@@ -10040,27 +10043,27 @@
     </row>
     <row r="164" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A164" s="49">
-        <v>10280010</v>
+        <v>10360010</v>
       </c>
       <c r="B164" s="49">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C164" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D164" s="51">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E164" s="52">
         <v>10</v>
       </c>
       <c r="F164" s="24" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G164" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H164" s="57">
+        <v>71</v>
+      </c>
+      <c r="H164" s="53">
         <v>0</v>
       </c>
       <c r="I164" s="45">
@@ -10079,7 +10082,7 @@
         <v>37</v>
       </c>
       <c r="N164" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O164" s="44"/>
       <c r="P164" s="44"/>
@@ -10090,27 +10093,27 @@
     </row>
     <row r="165" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A165" s="49">
-        <v>10280011</v>
+        <v>10360011</v>
       </c>
       <c r="B165" s="49">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C165" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D165" s="51">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E165" s="52">
         <v>11</v>
       </c>
       <c r="F165" s="24" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G165" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="H165" s="57">
+        <v>73</v>
+      </c>
+      <c r="H165" s="53">
         <v>0</v>
       </c>
       <c r="I165" s="45">
@@ -10129,7 +10132,7 @@
         <v>40</v>
       </c>
       <c r="N165" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O165" s="44"/>
       <c r="P165" s="44"/>
@@ -10140,25 +10143,25 @@
     </row>
     <row r="166" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A166" s="49">
-        <v>10280012</v>
+        <v>10360012</v>
       </c>
       <c r="B166" s="49">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C166" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D166" s="51">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E166" s="52">
         <v>12</v>
       </c>
       <c r="F166" s="24" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="G166" s="25" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="H166" s="57">
         <v>0</v>
@@ -10179,7 +10182,7 @@
         <v>43</v>
       </c>
       <c r="N166" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O166" s="44"/>
       <c r="P166" s="44"/>
@@ -10190,25 +10193,25 @@
     </row>
     <row r="167" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A167" s="49">
-        <v>10200010</v>
+        <v>10280010</v>
       </c>
       <c r="B167" s="49">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C167" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D167" s="51">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E167" s="52">
         <v>10</v>
       </c>
       <c r="F167" s="24" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G167" s="25" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="H167" s="57">
         <v>0</v>
@@ -10229,7 +10232,7 @@
         <v>37</v>
       </c>
       <c r="N167" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O167" s="44"/>
       <c r="P167" s="44"/>
@@ -10240,25 +10243,25 @@
     </row>
     <row r="168" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A168" s="49">
-        <v>10200011</v>
+        <v>10280011</v>
       </c>
       <c r="B168" s="49">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C168" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D168" s="51">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E168" s="52">
         <v>11</v>
       </c>
       <c r="F168" s="24" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="G168" s="25" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="H168" s="57">
         <v>0</v>
@@ -10279,7 +10282,7 @@
         <v>40</v>
       </c>
       <c r="N168" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O168" s="44"/>
       <c r="P168" s="44"/>
@@ -10290,25 +10293,25 @@
     </row>
     <row r="169" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A169" s="49">
-        <v>10200012</v>
+        <v>10280012</v>
       </c>
       <c r="B169" s="49">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C169" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D169" s="51">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E169" s="52">
         <v>12</v>
       </c>
       <c r="F169" s="24" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="G169" s="25" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="H169" s="57">
         <v>0</v>
@@ -10329,7 +10332,7 @@
         <v>43</v>
       </c>
       <c r="N169" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O169" s="44"/>
       <c r="P169" s="44"/>
@@ -10340,25 +10343,25 @@
     </row>
     <row r="170" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A170" s="49">
-        <v>10340110</v>
+        <v>10200010</v>
       </c>
       <c r="B170" s="49">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C170" s="50" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D170" s="51">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E170" s="52">
         <v>10</v>
       </c>
       <c r="F170" s="24" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G170" s="25" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H170" s="57">
         <v>0</v>
@@ -10379,7 +10382,7 @@
         <v>37</v>
       </c>
       <c r="N170" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O170" s="44"/>
       <c r="P170" s="44"/>
@@ -10390,25 +10393,25 @@
     </row>
     <row r="171" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A171" s="49">
-        <v>10340111</v>
+        <v>10200011</v>
       </c>
       <c r="B171" s="49">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C171" s="50" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D171" s="51">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E171" s="52">
         <v>11</v>
       </c>
       <c r="F171" s="24" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G171" s="25" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="H171" s="57">
         <v>0</v>
@@ -10429,7 +10432,7 @@
         <v>40</v>
       </c>
       <c r="N171" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O171" s="44"/>
       <c r="P171" s="44"/>
@@ -10440,25 +10443,25 @@
     </row>
     <row r="172" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A172" s="49">
-        <v>10340112</v>
+        <v>10200012</v>
       </c>
       <c r="B172" s="49">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C172" s="50" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D172" s="51">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E172" s="52">
         <v>12</v>
       </c>
       <c r="F172" s="24" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G172" s="25" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H172" s="57">
         <v>0</v>
@@ -10479,7 +10482,7 @@
         <v>43</v>
       </c>
       <c r="N172" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O172" s="44"/>
       <c r="P172" s="44"/>
@@ -10490,25 +10493,25 @@
     </row>
     <row r="173" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A173" s="49">
-        <v>10380010</v>
+        <v>10340110</v>
       </c>
       <c r="B173" s="49">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C173" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D173" s="51">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E173" s="52">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F173" s="24" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G173" s="25" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="H173" s="57">
         <v>0</v>
@@ -10529,7 +10532,7 @@
         <v>37</v>
       </c>
       <c r="N173" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O173" s="44"/>
       <c r="P173" s="44"/>
@@ -10540,25 +10543,25 @@
     </row>
     <row r="174" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A174" s="49">
-        <v>10380011</v>
+        <v>10340111</v>
       </c>
       <c r="B174" s="49">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C174" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D174" s="51">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E174" s="52">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F174" s="24" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="G174" s="25" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H174" s="57">
         <v>0</v>
@@ -10579,7 +10582,7 @@
         <v>40</v>
       </c>
       <c r="N174" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O174" s="44"/>
       <c r="P174" s="44"/>
@@ -10590,25 +10593,25 @@
     </row>
     <row r="175" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A175" s="49">
-        <v>10380012</v>
+        <v>10340112</v>
       </c>
       <c r="B175" s="49">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C175" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D175" s="51">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E175" s="52">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F175" s="24" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G175" s="25" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="H175" s="57">
         <v>0</v>
@@ -10629,7 +10632,7 @@
         <v>43</v>
       </c>
       <c r="N175" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O175" s="44"/>
       <c r="P175" s="44"/>
@@ -10640,25 +10643,25 @@
     </row>
     <row r="176" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A176" s="49">
-        <v>10270010</v>
+        <v>10380010</v>
       </c>
       <c r="B176" s="49">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C176" s="50" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D176" s="51">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E176" s="52">
         <v>11</v>
       </c>
       <c r="F176" s="24" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G176" s="25" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="H176" s="57">
         <v>0</v>
@@ -10679,7 +10682,7 @@
         <v>37</v>
       </c>
       <c r="N176" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O176" s="44"/>
       <c r="P176" s="44"/>
@@ -10690,25 +10693,25 @@
     </row>
     <row r="177" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A177" s="49">
-        <v>10270011</v>
+        <v>10380011</v>
       </c>
       <c r="B177" s="49">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C177" s="50" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D177" s="51">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E177" s="52">
         <v>12</v>
       </c>
       <c r="F177" s="24" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="G177" s="25" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="H177" s="57">
         <v>0</v>
@@ -10729,7 +10732,7 @@
         <v>40</v>
       </c>
       <c r="N177" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O177" s="44"/>
       <c r="P177" s="44"/>
@@ -10740,25 +10743,25 @@
     </row>
     <row r="178" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A178" s="49">
-        <v>10270012</v>
+        <v>10380012</v>
       </c>
       <c r="B178" s="49">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C178" s="50" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D178" s="51">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E178" s="52">
         <v>13</v>
       </c>
       <c r="F178" s="24" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="G178" s="25" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="H178" s="57">
         <v>0</v>
@@ -10779,7 +10782,7 @@
         <v>43</v>
       </c>
       <c r="N178" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O178" s="44"/>
       <c r="P178" s="44"/>
@@ -10790,25 +10793,25 @@
     </row>
     <row r="179" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A179" s="49">
-        <v>10370010</v>
+        <v>10270010</v>
       </c>
       <c r="B179" s="49">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C179" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D179" s="51">
-        <v>103700001</v>
+        <v>102700001</v>
       </c>
       <c r="E179" s="52">
         <v>11</v>
       </c>
       <c r="F179" s="24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G179" s="25" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H179" s="57">
         <v>0</v>
@@ -10829,7 +10832,7 @@
         <v>37</v>
       </c>
       <c r="N179" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O179" s="44"/>
       <c r="P179" s="44"/>
@@ -10840,25 +10843,25 @@
     </row>
     <row r="180" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A180" s="49">
-        <v>10370011</v>
+        <v>10270011</v>
       </c>
       <c r="B180" s="49">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C180" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D180" s="51">
-        <v>103700001</v>
+        <v>102700001</v>
       </c>
       <c r="E180" s="52">
         <v>12</v>
       </c>
       <c r="F180" s="24" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G180" s="25" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H180" s="57">
         <v>0</v>
@@ -10879,7 +10882,7 @@
         <v>40</v>
       </c>
       <c r="N180" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O180" s="44"/>
       <c r="P180" s="44"/>
@@ -10890,25 +10893,25 @@
     </row>
     <row r="181" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A181" s="49">
-        <v>10370012</v>
+        <v>10270012</v>
       </c>
       <c r="B181" s="49">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C181" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D181" s="51">
-        <v>103100001</v>
+        <v>102700001</v>
       </c>
       <c r="E181" s="52">
         <v>13</v>
       </c>
       <c r="F181" s="24" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G181" s="25" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H181" s="57">
         <v>0</v>
@@ -10929,7 +10932,7 @@
         <v>43</v>
       </c>
       <c r="N181" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O181" s="44"/>
       <c r="P181" s="44"/>
@@ -10940,27 +10943,27 @@
     </row>
     <row r="182" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A182" s="49">
-        <v>10310010</v>
+        <v>10370010</v>
       </c>
       <c r="B182" s="49">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C182" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D182" s="51">
-        <v>103100001</v>
+        <v>103700001</v>
       </c>
       <c r="E182" s="52">
         <v>11</v>
       </c>
       <c r="F182" s="24" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="G182" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="H182" s="53">
+        <v>39</v>
+      </c>
+      <c r="H182" s="57">
         <v>0</v>
       </c>
       <c r="I182" s="45">
@@ -10979,7 +10982,7 @@
         <v>37</v>
       </c>
       <c r="N182" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O182" s="44"/>
       <c r="P182" s="44"/>
@@ -10990,27 +10993,27 @@
     </row>
     <row r="183" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A183" s="49">
-        <v>10310011</v>
+        <v>10370011</v>
       </c>
       <c r="B183" s="49">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C183" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D183" s="51">
-        <v>103100001</v>
+        <v>103700001</v>
       </c>
       <c r="E183" s="52">
         <v>12</v>
       </c>
       <c r="F183" s="24" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="G183" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="H183" s="53">
+        <v>42</v>
+      </c>
+      <c r="H183" s="57">
         <v>0</v>
       </c>
       <c r="I183" s="45">
@@ -11029,7 +11032,7 @@
         <v>40</v>
       </c>
       <c r="N183" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O183" s="44"/>
       <c r="P183" s="44"/>
@@ -11040,13 +11043,13 @@
     </row>
     <row r="184" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A184" s="49">
-        <v>10310012</v>
+        <v>10370012</v>
       </c>
       <c r="B184" s="49">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C184" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D184" s="51">
         <v>103100001</v>
@@ -11055,10 +11058,10 @@
         <v>13</v>
       </c>
       <c r="F184" s="24" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="G184" s="25" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="H184" s="57">
         <v>0</v>
@@ -11079,7 +11082,7 @@
         <v>43</v>
       </c>
       <c r="N184" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O184" s="44"/>
       <c r="P184" s="44"/>
@@ -11090,27 +11093,27 @@
     </row>
     <row r="185" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A185" s="49">
-        <v>10400010</v>
+        <v>10310010</v>
       </c>
       <c r="B185" s="49">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C185" s="50" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D185" s="51">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E185" s="52">
         <v>11</v>
       </c>
       <c r="F185" s="24" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G185" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="H185" s="57">
+        <v>102</v>
+      </c>
+      <c r="H185" s="53">
         <v>0</v>
       </c>
       <c r="I185" s="45">
@@ -11129,7 +11132,7 @@
         <v>37</v>
       </c>
       <c r="N185" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O185" s="44"/>
       <c r="P185" s="44"/>
@@ -11140,27 +11143,27 @@
     </row>
     <row r="186" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A186" s="49">
-        <v>10400011</v>
+        <v>10310011</v>
       </c>
       <c r="B186" s="49">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C186" s="50" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D186" s="51">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E186" s="52">
         <v>12</v>
       </c>
       <c r="F186" s="24" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G186" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="H186" s="57">
+        <v>104</v>
+      </c>
+      <c r="H186" s="53">
         <v>0</v>
       </c>
       <c r="I186" s="45">
@@ -11179,7 +11182,7 @@
         <v>40</v>
       </c>
       <c r="N186" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O186" s="44"/>
       <c r="P186" s="44"/>
@@ -11190,25 +11193,25 @@
     </row>
     <row r="187" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A187" s="49">
-        <v>10400012</v>
+        <v>10310012</v>
       </c>
       <c r="B187" s="49">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C187" s="50" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D187" s="51">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E187" s="52">
         <v>13</v>
       </c>
       <c r="F187" s="24" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G187" s="25" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H187" s="57">
         <v>0</v>
@@ -11229,7 +11232,7 @@
         <v>43</v>
       </c>
       <c r="N187" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O187" s="44"/>
       <c r="P187" s="44"/>
@@ -11240,25 +11243,25 @@
     </row>
     <row r="188" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A188" s="49">
-        <v>10390010</v>
+        <v>10400010</v>
       </c>
       <c r="B188" s="49">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C188" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D188" s="51">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E188" s="52">
         <v>11</v>
       </c>
       <c r="F188" s="24" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G188" s="25" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="H188" s="57">
         <v>0</v>
@@ -11279,7 +11282,7 @@
         <v>37</v>
       </c>
       <c r="N188" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O188" s="44"/>
       <c r="P188" s="44"/>
@@ -11290,25 +11293,25 @@
     </row>
     <row r="189" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A189" s="49">
-        <v>10390011</v>
+        <v>10400011</v>
       </c>
       <c r="B189" s="49">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C189" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D189" s="51">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E189" s="52">
         <v>12</v>
       </c>
       <c r="F189" s="24" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G189" s="25" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="H189" s="57">
         <v>0</v>
@@ -11329,7 +11332,7 @@
         <v>40</v>
       </c>
       <c r="N189" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O189" s="44"/>
       <c r="P189" s="44"/>
@@ -11340,25 +11343,25 @@
     </row>
     <row r="190" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A190" s="49">
-        <v>10390012</v>
+        <v>10400012</v>
       </c>
       <c r="B190" s="49">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C190" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D190" s="51">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E190" s="52">
         <v>13</v>
       </c>
       <c r="F190" s="24" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G190" s="25" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="H190" s="57">
         <v>0</v>
@@ -11379,7 +11382,7 @@
         <v>43</v>
       </c>
       <c r="N190" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O190" s="44"/>
       <c r="P190" s="44"/>
@@ -11390,25 +11393,25 @@
     </row>
     <row r="191" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A191" s="49">
-        <v>10160010</v>
+        <v>10390010</v>
       </c>
       <c r="B191" s="49">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C191" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D191" s="51">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E191" s="52">
         <v>11</v>
       </c>
       <c r="F191" s="24" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="G191" s="25" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="H191" s="57">
         <v>0</v>
@@ -11429,7 +11432,7 @@
         <v>37</v>
       </c>
       <c r="N191" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O191" s="44"/>
       <c r="P191" s="44"/>
@@ -11440,25 +11443,25 @@
     </row>
     <row r="192" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A192" s="49">
-        <v>10160011</v>
+        <v>10390011</v>
       </c>
       <c r="B192" s="49">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C192" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D192" s="51">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E192" s="52">
         <v>12</v>
       </c>
       <c r="F192" s="24" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="G192" s="25" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="H192" s="57">
         <v>0</v>
@@ -11479,7 +11482,7 @@
         <v>40</v>
       </c>
       <c r="N192" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O192" s="44"/>
       <c r="P192" s="44"/>
@@ -11490,25 +11493,25 @@
     </row>
     <row r="193" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A193" s="49">
-        <v>10160012</v>
+        <v>10390012</v>
       </c>
       <c r="B193" s="49">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C193" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D193" s="51">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E193" s="52">
         <v>13</v>
       </c>
       <c r="F193" s="24" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="G193" s="25" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="H193" s="57">
         <v>0</v>
@@ -11529,7 +11532,7 @@
         <v>43</v>
       </c>
       <c r="N193" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O193" s="44"/>
       <c r="P193" s="44"/>
@@ -11540,16 +11543,16 @@
     </row>
     <row r="194" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A194" s="49">
-        <v>10150010</v>
+        <v>10160010</v>
       </c>
       <c r="B194" s="49">
-        <v>101500</v>
+        <v>101600</v>
       </c>
       <c r="C194" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D194" s="51">
-        <v>101500001</v>
+        <v>101600001</v>
       </c>
       <c r="E194" s="52">
         <v>11</v>
@@ -11579,7 +11582,7 @@
         <v>37</v>
       </c>
       <c r="N194" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O194" s="44"/>
       <c r="P194" s="44"/>
@@ -11590,16 +11593,16 @@
     </row>
     <row r="195" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A195" s="49">
-        <v>10150011</v>
+        <v>10160011</v>
       </c>
       <c r="B195" s="49">
-        <v>101500</v>
+        <v>101600</v>
       </c>
       <c r="C195" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D195" s="51">
-        <v>101500001</v>
+        <v>101600001</v>
       </c>
       <c r="E195" s="52">
         <v>12</v>
@@ -11629,7 +11632,7 @@
         <v>40</v>
       </c>
       <c r="N195" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O195" s="44"/>
       <c r="P195" s="44"/>
@@ -11640,16 +11643,16 @@
     </row>
     <row r="196" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A196" s="49">
-        <v>10150012</v>
+        <v>10160012</v>
       </c>
       <c r="B196" s="49">
-        <v>101500</v>
+        <v>101600</v>
       </c>
       <c r="C196" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D196" s="51">
-        <v>101500001</v>
+        <v>101600001</v>
       </c>
       <c r="E196" s="52">
         <v>13</v>
@@ -11679,7 +11682,7 @@
         <v>43</v>
       </c>
       <c r="N196" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O196" s="44"/>
       <c r="P196" s="44"/>
@@ -11690,16 +11693,16 @@
     </row>
     <row r="197" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A197" s="49">
-        <v>10260010</v>
+        <v>10150010</v>
       </c>
       <c r="B197" s="49">
-        <v>102600</v>
+        <v>101500</v>
       </c>
       <c r="C197" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D197" s="51">
-        <v>102600001</v>
+        <v>101500001</v>
       </c>
       <c r="E197" s="52">
         <v>11</v>
@@ -11729,7 +11732,7 @@
         <v>37</v>
       </c>
       <c r="N197" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O197" s="44"/>
       <c r="P197" s="44"/>
@@ -11740,16 +11743,16 @@
     </row>
     <row r="198" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A198" s="49">
-        <v>10260011</v>
+        <v>10150011</v>
       </c>
       <c r="B198" s="49">
-        <v>102600</v>
+        <v>101500</v>
       </c>
       <c r="C198" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D198" s="51">
-        <v>102600001</v>
+        <v>101500001</v>
       </c>
       <c r="E198" s="52">
         <v>12</v>
@@ -11779,7 +11782,7 @@
         <v>40</v>
       </c>
       <c r="N198" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O198" s="44"/>
       <c r="P198" s="44"/>
@@ -11790,16 +11793,16 @@
     </row>
     <row r="199" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A199" s="49">
-        <v>10260012</v>
+        <v>10150012</v>
       </c>
       <c r="B199" s="49">
-        <v>102600</v>
+        <v>101500</v>
       </c>
       <c r="C199" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D199" s="51">
-        <v>102600001</v>
+        <v>101500001</v>
       </c>
       <c r="E199" s="52">
         <v>13</v>
@@ -11829,7 +11832,7 @@
         <v>43</v>
       </c>
       <c r="N199" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O199" s="44"/>
       <c r="P199" s="44"/>
@@ -11840,16 +11843,16 @@
     </row>
     <row r="200" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A200" s="49">
-        <v>10500010</v>
+        <v>10260010</v>
       </c>
       <c r="B200" s="49">
-        <v>105000</v>
+        <v>102600</v>
       </c>
       <c r="C200" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D200" s="51">
-        <v>105000001</v>
+        <v>102600001</v>
       </c>
       <c r="E200" s="52">
         <v>11</v>
@@ -11879,7 +11882,7 @@
         <v>37</v>
       </c>
       <c r="N200" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O200" s="44"/>
       <c r="P200" s="44"/>
@@ -11890,16 +11893,16 @@
     </row>
     <row r="201" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A201" s="49">
-        <v>10500011</v>
+        <v>10260011</v>
       </c>
       <c r="B201" s="49">
-        <v>105000</v>
+        <v>102600</v>
       </c>
       <c r="C201" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D201" s="51">
-        <v>105000001</v>
+        <v>102600001</v>
       </c>
       <c r="E201" s="52">
         <v>12</v>
@@ -11929,7 +11932,7 @@
         <v>40</v>
       </c>
       <c r="N201" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O201" s="44"/>
       <c r="P201" s="44"/>
@@ -11940,16 +11943,16 @@
     </row>
     <row r="202" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A202" s="49">
-        <v>10500012</v>
+        <v>10260012</v>
       </c>
       <c r="B202" s="49">
-        <v>105000</v>
+        <v>102600</v>
       </c>
       <c r="C202" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D202" s="51">
-        <v>105000001</v>
+        <v>102600001</v>
       </c>
       <c r="E202" s="52">
         <v>13</v>
@@ -11979,7 +11982,7 @@
         <v>43</v>
       </c>
       <c r="N202" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O202" s="44"/>
       <c r="P202" s="44"/>
@@ -11990,27 +11993,27 @@
     </row>
     <row r="203" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A203" s="49">
-        <v>10510010</v>
+        <v>10500010</v>
       </c>
       <c r="B203" s="49">
-        <v>105100</v>
+        <v>105000</v>
       </c>
       <c r="C203" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D203" s="51">
-        <v>105100001</v>
+        <v>105000001</v>
       </c>
       <c r="E203" s="52">
         <v>11</v>
       </c>
       <c r="F203" s="24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G203" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="H203" s="53">
+        <v>51</v>
+      </c>
+      <c r="H203" s="57">
         <v>0</v>
       </c>
       <c r="I203" s="45">
@@ -12029,7 +12032,7 @@
         <v>37</v>
       </c>
       <c r="N203" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O203" s="44"/>
       <c r="P203" s="44"/>
@@ -12040,27 +12043,27 @@
     </row>
     <row r="204" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A204" s="49">
-        <v>10510011</v>
+        <v>10500011</v>
       </c>
       <c r="B204" s="49">
-        <v>105100</v>
+        <v>105000</v>
       </c>
       <c r="C204" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D204" s="51">
-        <v>105100001</v>
+        <v>105000001</v>
       </c>
       <c r="E204" s="52">
         <v>12</v>
       </c>
       <c r="F204" s="24" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G204" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="H204" s="53">
+        <v>53</v>
+      </c>
+      <c r="H204" s="57">
         <v>0</v>
       </c>
       <c r="I204" s="45">
@@ -12079,7 +12082,7 @@
         <v>40</v>
       </c>
       <c r="N204" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O204" s="44"/>
       <c r="P204" s="44"/>
@@ -12090,25 +12093,25 @@
     </row>
     <row r="205" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A205" s="49">
-        <v>10510012</v>
+        <v>10500012</v>
       </c>
       <c r="B205" s="49">
-        <v>105100</v>
+        <v>105000</v>
       </c>
       <c r="C205" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D205" s="51">
-        <v>105100001</v>
+        <v>105000001</v>
       </c>
       <c r="E205" s="52">
         <v>13</v>
       </c>
       <c r="F205" s="24" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G205" s="25" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H205" s="57">
         <v>0</v>
@@ -12129,7 +12132,7 @@
         <v>43</v>
       </c>
       <c r="N205" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O205" s="44"/>
       <c r="P205" s="44"/>
@@ -12140,31 +12143,31 @@
     </row>
     <row r="206" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A206" s="49">
-        <v>10540011</v>
+        <v>10510010</v>
       </c>
       <c r="B206" s="49">
-        <v>105400</v>
+        <v>105100</v>
       </c>
       <c r="C206" s="50" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D206" s="51">
-        <v>105400001</v>
+        <v>105100001</v>
       </c>
       <c r="E206" s="52">
         <v>11</v>
       </c>
       <c r="F206" s="24" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="G206" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H206" s="57">
+        <v>39</v>
+      </c>
+      <c r="H206" s="53">
         <v>0</v>
       </c>
       <c r="I206" s="45">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J206" s="54">
         <v>0</v>
@@ -12176,10 +12179,10 @@
         <v>0</v>
       </c>
       <c r="M206" s="26" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="N206" s="56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O206" s="44"/>
       <c r="P206" s="44"/>
@@ -12190,31 +12193,31 @@
     </row>
     <row r="207" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A207" s="49">
-        <v>10540012</v>
+        <v>10510011</v>
       </c>
       <c r="B207" s="49">
-        <v>105400</v>
+        <v>105100</v>
       </c>
       <c r="C207" s="50" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D207" s="51">
-        <v>105400001</v>
+        <v>105100001</v>
       </c>
       <c r="E207" s="52">
         <v>12</v>
       </c>
       <c r="F207" s="24" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="G207" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="H207" s="57">
+        <v>42</v>
+      </c>
+      <c r="H207" s="53">
         <v>0</v>
       </c>
       <c r="I207" s="45">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J207" s="54">
         <v>0</v>
@@ -12226,10 +12229,10 @@
         <v>0</v>
       </c>
       <c r="M207" s="26" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="N207" s="56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O207" s="44"/>
       <c r="P207" s="44"/>
@@ -12240,31 +12243,31 @@
     </row>
     <row r="208" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A208" s="49">
-        <v>10540013</v>
+        <v>10510012</v>
       </c>
       <c r="B208" s="49">
-        <v>105400</v>
+        <v>105100</v>
       </c>
       <c r="C208" s="50" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D208" s="51">
-        <v>105400001</v>
+        <v>105100001</v>
       </c>
       <c r="E208" s="52">
         <v>13</v>
       </c>
       <c r="F208" s="24" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="G208" s="25" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H208" s="57">
         <v>0</v>
       </c>
       <c r="I208" s="45">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J208" s="54">
         <v>0</v>
@@ -12276,10 +12279,10 @@
         <v>0</v>
       </c>
       <c r="M208" s="26" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="N208" s="56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O208" s="44"/>
       <c r="P208" s="44"/>
@@ -12288,20 +12291,20 @@
       <c r="S208" s="45"/>
       <c r="T208" s="45"/>
     </row>
-    <row r="209" ht="16.5" spans="1:14">
-      <c r="A209" s="8">
-        <v>10080010</v>
-      </c>
-      <c r="B209" s="8">
-        <v>100800</v>
-      </c>
-      <c r="C209" s="13" t="s">
+    <row r="209" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A209" s="49">
+        <v>10540011</v>
+      </c>
+      <c r="B209" s="49">
+        <v>105400</v>
+      </c>
+      <c r="C209" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="D209" s="35">
-        <v>100800001</v>
-      </c>
-      <c r="E209" s="13">
+      <c r="D209" s="51">
+        <v>105400001</v>
+      </c>
+      <c r="E209" s="52">
         <v>11</v>
       </c>
       <c r="F209" s="24" t="s">
@@ -12310,42 +12313,48 @@
       <c r="G209" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="H209" s="31">
-        <v>0</v>
-      </c>
-      <c r="I209" s="26">
+      <c r="H209" s="57">
+        <v>0</v>
+      </c>
+      <c r="I209" s="45">
         <v>9600</v>
       </c>
-      <c r="J209" s="26">
-        <v>0</v>
-      </c>
-      <c r="K209" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L209" s="29">
+      <c r="J209" s="54">
+        <v>0</v>
+      </c>
+      <c r="K209" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L209" s="58">
         <v>0</v>
       </c>
       <c r="M209" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="N209" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="210" ht="16.5" spans="1:14">
-      <c r="A210" s="8">
-        <v>10080011</v>
-      </c>
-      <c r="B210" s="8">
-        <v>100800</v>
-      </c>
-      <c r="C210" s="13" t="s">
+      <c r="N209" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="O209" s="44"/>
+      <c r="P209" s="44"/>
+      <c r="Q209" s="44"/>
+      <c r="R209" s="44"/>
+      <c r="S209" s="45"/>
+      <c r="T209" s="45"/>
+    </row>
+    <row r="210" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A210" s="49">
+        <v>10540012</v>
+      </c>
+      <c r="B210" s="49">
+        <v>105400</v>
+      </c>
+      <c r="C210" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="D210" s="35">
-        <v>100800001</v>
-      </c>
-      <c r="E210" s="13">
+      <c r="D210" s="51">
+        <v>105400001</v>
+      </c>
+      <c r="E210" s="52">
         <v>12</v>
       </c>
       <c r="F210" s="24" t="s">
@@ -12354,42 +12363,48 @@
       <c r="G210" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="H210" s="31">
-        <v>0</v>
-      </c>
-      <c r="I210" s="26">
+      <c r="H210" s="57">
+        <v>0</v>
+      </c>
+      <c r="I210" s="45">
         <v>9600</v>
       </c>
-      <c r="J210" s="26">
-        <v>0</v>
-      </c>
-      <c r="K210" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L210" s="29">
+      <c r="J210" s="54">
+        <v>0</v>
+      </c>
+      <c r="K210" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L210" s="58">
         <v>0</v>
       </c>
       <c r="M210" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="N210" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="211" ht="16.5" spans="1:14">
-      <c r="A211" s="8">
-        <v>10080012</v>
-      </c>
-      <c r="B211" s="8">
-        <v>100800</v>
-      </c>
-      <c r="C211" s="13" t="s">
+      <c r="N210" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="O210" s="44"/>
+      <c r="P210" s="44"/>
+      <c r="Q210" s="44"/>
+      <c r="R210" s="44"/>
+      <c r="S210" s="45"/>
+      <c r="T210" s="45"/>
+    </row>
+    <row r="211" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A211" s="49">
+        <v>10540013</v>
+      </c>
+      <c r="B211" s="49">
+        <v>105400</v>
+      </c>
+      <c r="C211" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="D211" s="35">
-        <v>100800001</v>
-      </c>
-      <c r="E211" s="13">
+      <c r="D211" s="51">
+        <v>105400001</v>
+      </c>
+      <c r="E211" s="52">
         <v>13</v>
       </c>
       <c r="F211" s="24" t="s">
@@ -12398,40 +12413,46 @@
       <c r="G211" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="H211" s="31">
-        <v>0</v>
-      </c>
-      <c r="I211" s="26">
+      <c r="H211" s="57">
+        <v>0</v>
+      </c>
+      <c r="I211" s="45">
         <v>9600</v>
       </c>
-      <c r="J211" s="26">
-        <v>0</v>
-      </c>
-      <c r="K211" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L211" s="29">
+      <c r="J211" s="54">
+        <v>0</v>
+      </c>
+      <c r="K211" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="L211" s="58">
         <v>0</v>
       </c>
       <c r="M211" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="N211" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="212" ht="16.5" spans="1:14">
-      <c r="A212" s="22">
-        <v>10530010</v>
-      </c>
-      <c r="B212" s="22">
-        <v>105300</v>
-      </c>
-      <c r="C212" s="23" t="s">
-        <v>124</v>
+      <c r="N211" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="O211" s="44"/>
+      <c r="P211" s="44"/>
+      <c r="Q211" s="44"/>
+      <c r="R211" s="44"/>
+      <c r="S211" s="45"/>
+      <c r="T211" s="45"/>
+    </row>
+    <row r="212" ht="16.5" spans="1:20">
+      <c r="A212" s="8">
+        <v>10080010</v>
+      </c>
+      <c r="B212" s="8">
+        <v>100800</v>
+      </c>
+      <c r="C212" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="D212" s="35">
-        <v>105300001</v>
+        <v>100800001</v>
       </c>
       <c r="E212" s="13">
         <v>11</v>
@@ -12461,21 +12482,21 @@
         <v>117</v>
       </c>
       <c r="N212" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="213" ht="16.5" spans="1:14">
-      <c r="A213" s="22">
-        <v>10530011</v>
-      </c>
-      <c r="B213" s="22">
-        <v>105300</v>
-      </c>
-      <c r="C213" s="23" t="s">
-        <v>124</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="213" ht="16.5" spans="1:20">
+      <c r="A213" s="8">
+        <v>10080011</v>
+      </c>
+      <c r="B213" s="8">
+        <v>100800</v>
+      </c>
+      <c r="C213" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="D213" s="35">
-        <v>105300001</v>
+        <v>100800001</v>
       </c>
       <c r="E213" s="13">
         <v>12</v>
@@ -12505,21 +12526,21 @@
         <v>119</v>
       </c>
       <c r="N213" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="214" ht="16.5" spans="1:14">
-      <c r="A214" s="22">
-        <v>10530012</v>
-      </c>
-      <c r="B214" s="22">
-        <v>105300</v>
-      </c>
-      <c r="C214" s="23" t="s">
-        <v>124</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="214" ht="16.5" spans="1:20">
+      <c r="A214" s="8">
+        <v>10080012</v>
+      </c>
+      <c r="B214" s="8">
+        <v>100800</v>
+      </c>
+      <c r="C214" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="D214" s="35">
-        <v>105300001</v>
+        <v>100800001</v>
       </c>
       <c r="E214" s="13">
         <v>13</v>
@@ -12549,21 +12570,21 @@
         <v>121</v>
       </c>
       <c r="N214" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="215" ht="16.5" spans="1:14">
-      <c r="A215" s="8">
-        <v>10570010</v>
-      </c>
-      <c r="B215" s="8">
-        <v>105700</v>
-      </c>
-      <c r="C215" t="s">
-        <v>126</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="215" ht="16.5" spans="1:20">
+      <c r="A215" s="22">
+        <v>10530010</v>
+      </c>
+      <c r="B215" s="22">
+        <v>105300</v>
+      </c>
+      <c r="C215" s="23" t="s">
+        <v>124</v>
       </c>
       <c r="D215" s="35">
-        <v>105700001</v>
+        <v>105300001</v>
       </c>
       <c r="E215" s="13">
         <v>11</v>
@@ -12593,21 +12614,21 @@
         <v>117</v>
       </c>
       <c r="N215" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="216" ht="16.5" spans="1:14">
-      <c r="A216" s="8">
-        <v>10570011</v>
-      </c>
-      <c r="B216" s="8">
-        <v>105700</v>
-      </c>
-      <c r="C216" t="s">
-        <v>126</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="216" ht="16.5" spans="1:20">
+      <c r="A216" s="22">
+        <v>10530011</v>
+      </c>
+      <c r="B216" s="22">
+        <v>105300</v>
+      </c>
+      <c r="C216" s="23" t="s">
+        <v>124</v>
       </c>
       <c r="D216" s="35">
-        <v>105700001</v>
+        <v>105300001</v>
       </c>
       <c r="E216" s="13">
         <v>12</v>
@@ -12637,21 +12658,21 @@
         <v>119</v>
       </c>
       <c r="N216" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="217" ht="16.5" spans="1:14">
-      <c r="A217" s="8">
-        <v>10570012</v>
-      </c>
-      <c r="B217" s="8">
-        <v>105700</v>
-      </c>
-      <c r="C217" t="s">
-        <v>126</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="217" ht="16.5" spans="1:20">
+      <c r="A217" s="22">
+        <v>10530012</v>
+      </c>
+      <c r="B217" s="22">
+        <v>105300</v>
+      </c>
+      <c r="C217" s="23" t="s">
+        <v>124</v>
       </c>
       <c r="D217" s="35">
-        <v>105700001</v>
+        <v>105300001</v>
       </c>
       <c r="E217" s="13">
         <v>13</v>
@@ -12681,21 +12702,21 @@
         <v>121</v>
       </c>
       <c r="N217" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="218" s="7" customFormat="1" ht="16.5" spans="1:14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="218" ht="16.5" spans="1:20">
       <c r="A218" s="8">
-        <v>10580010</v>
+        <v>10570010</v>
       </c>
       <c r="B218" s="8">
-        <v>105800</v>
-      </c>
-      <c r="C218" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D218" s="61">
-        <v>105800001</v>
+        <v>105700</v>
+      </c>
+      <c r="C218" t="s">
+        <v>126</v>
+      </c>
+      <c r="D218" s="35">
+        <v>105700001</v>
       </c>
       <c r="E218" s="13">
         <v>11</v>
@@ -12725,21 +12746,21 @@
         <v>117</v>
       </c>
       <c r="N218" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="219" s="7" customFormat="1" ht="16.5" spans="1:14">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="219" ht="16.5" spans="1:20">
       <c r="A219" s="8">
-        <v>10580011</v>
+        <v>10570011</v>
       </c>
       <c r="B219" s="8">
-        <v>105800</v>
-      </c>
-      <c r="C219" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D219" s="61">
-        <v>105800001</v>
+        <v>105700</v>
+      </c>
+      <c r="C219" t="s">
+        <v>126</v>
+      </c>
+      <c r="D219" s="35">
+        <v>105700001</v>
       </c>
       <c r="E219" s="13">
         <v>12</v>
@@ -12769,21 +12790,21 @@
         <v>119</v>
       </c>
       <c r="N219" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="220" s="7" customFormat="1" ht="16.5" spans="1:14">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="220" ht="16.5" spans="1:20">
       <c r="A220" s="8">
-        <v>10580012</v>
+        <v>10570012</v>
       </c>
       <c r="B220" s="8">
-        <v>105800</v>
-      </c>
-      <c r="C220" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D220" s="61">
-        <v>105800001</v>
+        <v>105700</v>
+      </c>
+      <c r="C220" t="s">
+        <v>126</v>
+      </c>
+      <c r="D220" s="35">
+        <v>105700001</v>
       </c>
       <c r="E220" s="13">
         <v>13</v>
@@ -12813,30 +12834,30 @@
         <v>121</v>
       </c>
       <c r="N220" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="221" s="7" customFormat="1" ht="16.5" spans="1:14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="221" s="7" customFormat="1" ht="16.5" spans="1:20">
       <c r="A221" s="8">
-        <v>10550010</v>
+        <v>10580010</v>
       </c>
       <c r="B221" s="8">
-        <v>105500</v>
-      </c>
-      <c r="C221" s="8" t="s">
-        <v>114</v>
+        <v>105800</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="D221" s="61">
-        <v>105500001</v>
+        <v>105800001</v>
       </c>
       <c r="E221" s="13">
         <v>11</v>
       </c>
       <c r="F221" s="24" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="G221" s="25" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H221" s="31">
         <v>0</v>
@@ -12857,30 +12878,30 @@
         <v>117</v>
       </c>
       <c r="N221" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="222" s="7" customFormat="1" ht="16.5" spans="1:14">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="222" s="7" customFormat="1" ht="16.5" spans="1:20">
       <c r="A222" s="8">
-        <v>10550011</v>
+        <v>10580011</v>
       </c>
       <c r="B222" s="8">
-        <v>105500</v>
-      </c>
-      <c r="C222" s="8" t="s">
-        <v>114</v>
+        <v>105800</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="D222" s="61">
-        <v>105500001</v>
+        <v>105800001</v>
       </c>
       <c r="E222" s="13">
         <v>12</v>
       </c>
       <c r="F222" s="24" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="G222" s="25" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H222" s="31">
         <v>0</v>
@@ -12901,30 +12922,30 @@
         <v>119</v>
       </c>
       <c r="N222" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="223" s="7" customFormat="1" ht="16.5" spans="1:14">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="223" s="7" customFormat="1" ht="16.5" spans="1:20">
       <c r="A223" s="8">
-        <v>10550012</v>
+        <v>10580012</v>
       </c>
       <c r="B223" s="8">
-        <v>105500</v>
-      </c>
-      <c r="C223" s="8" t="s">
-        <v>114</v>
+        <v>105800</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="D223" s="61">
-        <v>105500001</v>
+        <v>105800001</v>
       </c>
       <c r="E223" s="13">
         <v>13</v>
       </c>
       <c r="F223" s="24" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="G223" s="25" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H223" s="31">
         <v>0</v>
@@ -12945,30 +12966,30 @@
         <v>121</v>
       </c>
       <c r="N223" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="224" ht="16.5" spans="1:14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="224" s="7" customFormat="1" ht="16.5" spans="1:20">
       <c r="A224" s="8">
-        <v>10480010</v>
+        <v>10550010</v>
       </c>
       <c r="B224" s="8">
-        <v>104800</v>
-      </c>
-      <c r="C224" t="s">
-        <v>115</v>
-      </c>
-      <c r="D224" s="27">
-        <v>104800001</v>
+        <v>105500</v>
+      </c>
+      <c r="C224" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D224" s="61">
+        <v>105500001</v>
       </c>
       <c r="E224" s="13">
         <v>11</v>
       </c>
       <c r="F224" s="24" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="G224" s="25" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="H224" s="31">
         <v>0</v>
@@ -12989,30 +13010,30 @@
         <v>117</v>
       </c>
       <c r="N224" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="225" ht="16.5" spans="1:20">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="225" s="7" customFormat="1" ht="16.5" spans="1:14">
       <c r="A225" s="8">
-        <v>10480011</v>
+        <v>10550011</v>
       </c>
       <c r="B225" s="8">
-        <v>104800</v>
-      </c>
-      <c r="C225" t="s">
-        <v>115</v>
-      </c>
-      <c r="D225" s="27">
-        <v>104800001</v>
+        <v>105500</v>
+      </c>
+      <c r="C225" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D225" s="61">
+        <v>105500001</v>
       </c>
       <c r="E225" s="13">
         <v>12</v>
       </c>
       <c r="F225" s="24" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="G225" s="25" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="H225" s="31">
         <v>0</v>
@@ -13033,30 +13054,30 @@
         <v>119</v>
       </c>
       <c r="N225" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="226" ht="16.5" spans="1:20">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="226" s="7" customFormat="1" ht="16.5" spans="1:14">
       <c r="A226" s="8">
-        <v>10480012</v>
+        <v>10550012</v>
       </c>
       <c r="B226" s="8">
-        <v>104800</v>
-      </c>
-      <c r="C226" t="s">
-        <v>115</v>
-      </c>
-      <c r="D226" s="27">
-        <v>104800001</v>
+        <v>105500</v>
+      </c>
+      <c r="C226" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D226" s="61">
+        <v>105500001</v>
       </c>
       <c r="E226" s="13">
         <v>13</v>
       </c>
       <c r="F226" s="24" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="G226" s="25" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="H226" s="31">
         <v>0</v>
@@ -13077,30 +13098,30 @@
         <v>121</v>
       </c>
       <c r="N226" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="227" s="8" customFormat="1" ht="16.5" spans="1:20">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="227" ht="16.5" spans="1:14">
       <c r="A227" s="8">
-        <v>10550110</v>
+        <v>10480010</v>
       </c>
       <c r="B227" s="8">
-        <v>105501</v>
-      </c>
-      <c r="C227" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D227" s="61">
-        <v>105501001</v>
-      </c>
-      <c r="E227" s="62">
+        <v>104800</v>
+      </c>
+      <c r="C227" t="s">
+        <v>115</v>
+      </c>
+      <c r="D227" s="27">
+        <v>104800001</v>
+      </c>
+      <c r="E227" s="13">
         <v>11</v>
       </c>
       <c r="F227" s="24" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="G227" s="25" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H227" s="31">
         <v>0</v>
@@ -13121,30 +13142,30 @@
         <v>117</v>
       </c>
       <c r="N227" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="228" s="8" customFormat="1" ht="16.5" spans="1:20">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="228" ht="16.5" spans="1:14">
       <c r="A228" s="8">
-        <v>10550111</v>
+        <v>10480011</v>
       </c>
       <c r="B228" s="8">
-        <v>105501</v>
-      </c>
-      <c r="C228" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D228" s="61">
-        <v>105501001</v>
-      </c>
-      <c r="E228" s="62">
+        <v>104800</v>
+      </c>
+      <c r="C228" t="s">
+        <v>115</v>
+      </c>
+      <c r="D228" s="27">
+        <v>104800001</v>
+      </c>
+      <c r="E228" s="13">
         <v>12</v>
       </c>
       <c r="F228" s="24" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="G228" s="25" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H228" s="31">
         <v>0</v>
@@ -13165,30 +13186,30 @@
         <v>119</v>
       </c>
       <c r="N228" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="229" s="8" customFormat="1" ht="16.5" spans="1:20">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="229" ht="16.5" spans="1:14">
       <c r="A229" s="8">
-        <v>10550112</v>
+        <v>10480012</v>
       </c>
       <c r="B229" s="8">
-        <v>105501</v>
-      </c>
-      <c r="C229" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D229" s="61">
-        <v>105501001</v>
-      </c>
-      <c r="E229" s="62">
+        <v>104800</v>
+      </c>
+      <c r="C229" t="s">
+        <v>115</v>
+      </c>
+      <c r="D229" s="27">
+        <v>104800001</v>
+      </c>
+      <c r="E229" s="13">
         <v>13</v>
       </c>
       <c r="F229" s="24" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="G229" s="25" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H229" s="31">
         <v>0</v>
@@ -13209,21 +13230,21 @@
         <v>121</v>
       </c>
       <c r="N229" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="230" s="8" customFormat="1" ht="16.5" spans="1:20">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="230" s="8" customFormat="1" ht="16.5" spans="1:14">
       <c r="A230" s="8">
-        <v>10550210</v>
+        <v>10550110</v>
       </c>
       <c r="B230" s="8">
-        <v>105502</v>
+        <v>105501</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D230" s="61">
-        <v>105502001</v>
+        <v>105501001</v>
       </c>
       <c r="E230" s="62">
         <v>11</v>
@@ -13253,21 +13274,21 @@
         <v>117</v>
       </c>
       <c r="N230" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="231" s="8" customFormat="1" ht="16.5" spans="1:20">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="231" s="8" customFormat="1" ht="16.5" spans="1:14">
       <c r="A231" s="8">
-        <v>10550211</v>
+        <v>10550111</v>
       </c>
       <c r="B231" s="8">
-        <v>105502</v>
+        <v>105501</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D231" s="61">
-        <v>105502001</v>
+        <v>105501001</v>
       </c>
       <c r="E231" s="62">
         <v>12</v>
@@ -13297,21 +13318,21 @@
         <v>119</v>
       </c>
       <c r="N231" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="232" s="8" customFormat="1" ht="16.5" spans="1:20">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="232" s="8" customFormat="1" ht="16.5" spans="1:14">
       <c r="A232" s="8">
-        <v>10550212</v>
+        <v>10550112</v>
       </c>
       <c r="B232" s="8">
-        <v>105502</v>
+        <v>105501</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D232" s="61">
-        <v>105502001</v>
+        <v>105501001</v>
       </c>
       <c r="E232" s="62">
         <v>13</v>
@@ -13341,153 +13362,153 @@
         <v>121</v>
       </c>
       <c r="N232" s="24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="233" s="8" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A233" s="8">
+        <v>10550210</v>
+      </c>
+      <c r="B233" s="8">
+        <v>105502</v>
+      </c>
+      <c r="C233" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D233" s="61">
+        <v>105502001</v>
+      </c>
+      <c r="E233" s="62">
+        <v>11</v>
+      </c>
+      <c r="F233" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="G233" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H233" s="31">
+        <v>0</v>
+      </c>
+      <c r="I233" s="26">
+        <v>9600</v>
+      </c>
+      <c r="J233" s="26">
+        <v>0</v>
+      </c>
+      <c r="K233" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L233" s="29">
+        <v>0</v>
+      </c>
+      <c r="M233" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="N233" s="24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="234" s="8" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A234" s="8">
+        <v>10550211</v>
+      </c>
+      <c r="B234" s="8">
+        <v>105502</v>
+      </c>
+      <c r="C234" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D234" s="61">
+        <v>105502001</v>
+      </c>
+      <c r="E234" s="62">
+        <v>12</v>
+      </c>
+      <c r="F234" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="G234" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="H234" s="31">
+        <v>0</v>
+      </c>
+      <c r="I234" s="26">
+        <v>9600</v>
+      </c>
+      <c r="J234" s="26">
+        <v>0</v>
+      </c>
+      <c r="K234" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L234" s="29">
+        <v>0</v>
+      </c>
+      <c r="M234" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="N234" s="24" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="233" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A233" s="8">
+    <row r="235" s="8" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A235" s="8">
+        <v>10550212</v>
+      </c>
+      <c r="B235" s="8">
+        <v>105502</v>
+      </c>
+      <c r="C235" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D235" s="61">
+        <v>105502001</v>
+      </c>
+      <c r="E235" s="62">
+        <v>13</v>
+      </c>
+      <c r="F235" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="G235" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="H235" s="31">
+        <v>0</v>
+      </c>
+      <c r="I235" s="26">
+        <v>9600</v>
+      </c>
+      <c r="J235" s="26">
+        <v>0</v>
+      </c>
+      <c r="K235" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L235" s="29">
+        <v>0</v>
+      </c>
+      <c r="M235" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="N235" s="24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="236" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A236" s="8">
         <v>10410010</v>
       </c>
-      <c r="B233" s="46">
+      <c r="B236" s="46">
         <v>104100</v>
-      </c>
-      <c r="C233" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="D233" s="27">
-        <v>104100001</v>
-      </c>
-      <c r="E233" s="13">
-        <v>11</v>
-      </c>
-      <c r="F233" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="G233" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="H233" s="65">
-        <v>0</v>
-      </c>
-      <c r="I233" s="48">
-        <v>9600</v>
-      </c>
-      <c r="J233" s="48">
-        <v>0</v>
-      </c>
-      <c r="K233" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="L233" s="66">
-        <v>0</v>
-      </c>
-      <c r="M233" s="48" t="s">
-        <v>117</v>
-      </c>
-      <c r="N233" s="47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="234" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A234" s="8">
-        <v>10410011</v>
-      </c>
-      <c r="B234" s="46">
-        <v>104100</v>
-      </c>
-      <c r="C234" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="D234" s="27">
-        <v>104100001</v>
-      </c>
-      <c r="E234" s="13">
-        <v>12</v>
-      </c>
-      <c r="F234" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="G234" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="H234" s="65">
-        <v>0</v>
-      </c>
-      <c r="I234" s="48">
-        <v>9600</v>
-      </c>
-      <c r="J234" s="48">
-        <v>0</v>
-      </c>
-      <c r="K234" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="L234" s="66">
-        <v>0</v>
-      </c>
-      <c r="M234" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="N234" s="47" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="235" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A235" s="8">
-        <v>10410012</v>
-      </c>
-      <c r="B235" s="46">
-        <v>104100</v>
-      </c>
-      <c r="C235" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="D235" s="27">
-        <v>104100001</v>
-      </c>
-      <c r="E235" s="13">
-        <v>13</v>
-      </c>
-      <c r="F235" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="G235" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="H235" s="65">
-        <v>0</v>
-      </c>
-      <c r="I235" s="48">
-        <v>9600</v>
-      </c>
-      <c r="J235" s="48">
-        <v>0</v>
-      </c>
-      <c r="K235" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="L235" s="66">
-        <v>0</v>
-      </c>
-      <c r="M235" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="N235" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="236" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A236" s="8">
-        <v>10420010</v>
-      </c>
-      <c r="B236" s="46">
-        <v>104200</v>
       </c>
       <c r="C236" s="63" t="s">
         <v>135</v>
       </c>
       <c r="D236" s="27">
-        <v>104200001</v>
+        <v>104100001</v>
       </c>
       <c r="E236" s="13">
         <v>11</v>
@@ -13517,21 +13538,21 @@
         <v>117</v>
       </c>
       <c r="N236" s="47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="237" customFormat="1" ht="16.5" spans="1:20">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="237" customFormat="1" ht="16.5" spans="1:14">
       <c r="A237" s="8">
-        <v>10420011</v>
+        <v>10410011</v>
       </c>
       <c r="B237" s="46">
-        <v>104200</v>
+        <v>104100</v>
       </c>
       <c r="C237" s="63" t="s">
         <v>135</v>
       </c>
       <c r="D237" s="27">
-        <v>104200001</v>
+        <v>104100001</v>
       </c>
       <c r="E237" s="13">
         <v>12</v>
@@ -13561,21 +13582,21 @@
         <v>119</v>
       </c>
       <c r="N237" s="47" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="238" customFormat="1" ht="16.5" spans="1:20">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="238" customFormat="1" ht="16.5" spans="1:14">
       <c r="A238" s="8">
-        <v>10420012</v>
+        <v>10410012</v>
       </c>
       <c r="B238" s="46">
-        <v>104200</v>
+        <v>104100</v>
       </c>
       <c r="C238" s="63" t="s">
         <v>135</v>
       </c>
       <c r="D238" s="27">
-        <v>104200001</v>
+        <v>104100001</v>
       </c>
       <c r="E238" s="13">
         <v>13</v>
@@ -13605,180 +13626,162 @@
         <v>121</v>
       </c>
       <c r="N238" s="47" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="239" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A239" s="8">
+        <v>10420010</v>
+      </c>
+      <c r="B239" s="46">
+        <v>104200</v>
+      </c>
+      <c r="C239" s="63" t="s">
+        <v>136</v>
+      </c>
+      <c r="D239" s="27">
+        <v>104200001</v>
+      </c>
+      <c r="E239" s="13">
+        <v>11</v>
+      </c>
+      <c r="F239" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="G239" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="H239" s="65">
+        <v>0</v>
+      </c>
+      <c r="I239" s="48">
+        <v>9600</v>
+      </c>
+      <c r="J239" s="48">
+        <v>0</v>
+      </c>
+      <c r="K239" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L239" s="66">
+        <v>0</v>
+      </c>
+      <c r="M239" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="N239" s="47" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="240" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A240" s="8">
+        <v>10420011</v>
+      </c>
+      <c r="B240" s="46">
+        <v>104200</v>
+      </c>
+      <c r="C240" s="63" t="s">
+        <v>136</v>
+      </c>
+      <c r="D240" s="27">
+        <v>104200001</v>
+      </c>
+      <c r="E240" s="13">
+        <v>12</v>
+      </c>
+      <c r="F240" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="G240" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="H240" s="65">
+        <v>0</v>
+      </c>
+      <c r="I240" s="48">
+        <v>9600</v>
+      </c>
+      <c r="J240" s="48">
+        <v>0</v>
+      </c>
+      <c r="K240" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L240" s="66">
+        <v>0</v>
+      </c>
+      <c r="M240" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="N240" s="47" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="239" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A239" s="22">
-        <v>10010021</v>
-      </c>
-      <c r="B239" s="22">
-        <v>100100</v>
-      </c>
-      <c r="C239" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D239" s="27">
-        <v>100100026</v>
-      </c>
-      <c r="E239" s="67">
-        <v>21</v>
-      </c>
-      <c r="F239" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="G239" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="H239" s="17">
-        <v>10000000</v>
-      </c>
-      <c r="I239" s="28">
-        <v>9500</v>
-      </c>
-      <c r="J239" s="26">
-        <v>5000000</v>
-      </c>
-      <c r="K239" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L239" s="30">
-        <v>100</v>
-      </c>
-      <c r="M239" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="N239" s="24">
-        <v>0</v>
-      </c>
-      <c r="O239" s="24"/>
-      <c r="P239" s="24"/>
-      <c r="Q239" s="24"/>
-      <c r="R239" s="24"/>
-      <c r="S239" s="26"/>
-      <c r="T239" s="26"/>
-    </row>
-    <row r="240" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A240" s="22">
-        <v>10010022</v>
-      </c>
-      <c r="B240" s="22">
-        <v>100100</v>
-      </c>
-      <c r="C240" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D240" s="27">
-        <v>100100026</v>
-      </c>
-      <c r="E240" s="67">
-        <v>22</v>
-      </c>
-      <c r="F240" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G240" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="H240" s="17">
-        <v>100000000</v>
-      </c>
-      <c r="I240" s="28">
-        <v>9500</v>
-      </c>
-      <c r="J240" s="26">
-        <v>50000000</v>
-      </c>
-      <c r="K240" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L240" s="30">
-        <v>100</v>
-      </c>
-      <c r="M240" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="N240" s="24">
-        <v>0</v>
-      </c>
-      <c r="O240" s="24"/>
-      <c r="P240" s="24"/>
-      <c r="Q240" s="24"/>
-      <c r="R240" s="24"/>
-      <c r="S240" s="26"/>
-      <c r="T240" s="26"/>
-    </row>
-    <row r="241" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A241" s="22">
-        <v>10010023</v>
-      </c>
-      <c r="B241" s="22">
-        <v>100100</v>
-      </c>
-      <c r="C241" s="23" t="s">
-        <v>33</v>
+    <row r="241" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A241" s="8">
+        <v>10420012</v>
+      </c>
+      <c r="B241" s="46">
+        <v>104200</v>
+      </c>
+      <c r="C241" s="63" t="s">
+        <v>136</v>
       </c>
       <c r="D241" s="27">
-        <v>100100026</v>
-      </c>
-      <c r="E241" s="67">
-        <v>23</v>
-      </c>
-      <c r="F241" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="G241" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="H241" s="31">
-        <v>1000000000</v>
-      </c>
-      <c r="I241" s="28">
-        <v>9500</v>
-      </c>
-      <c r="J241" s="26">
-        <v>500000000</v>
-      </c>
-      <c r="K241" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L241" s="30">
-        <v>100</v>
-      </c>
-      <c r="M241" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="N241" s="24">
-        <v>0</v>
-      </c>
-      <c r="O241" s="24"/>
-      <c r="P241" s="24"/>
-      <c r="Q241" s="24"/>
-      <c r="R241" s="24"/>
-      <c r="S241" s="26"/>
-      <c r="T241" s="26"/>
+        <v>104200001</v>
+      </c>
+      <c r="E241" s="13">
+        <v>13</v>
+      </c>
+      <c r="F241" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="G241" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="H241" s="65">
+        <v>0</v>
+      </c>
+      <c r="I241" s="48">
+        <v>9600</v>
+      </c>
+      <c r="J241" s="48">
+        <v>0</v>
+      </c>
+      <c r="K241" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L241" s="66">
+        <v>0</v>
+      </c>
+      <c r="M241" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="N241" s="47" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="242" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A242" s="22">
-        <v>10030021</v>
+        <v>10010021</v>
       </c>
       <c r="B242" s="22">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D242" s="27">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E242" s="67">
         <v>21</v>
       </c>
       <c r="F242" s="24" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G242" s="25" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H242" s="17">
         <v>10000000</v>
@@ -13810,25 +13813,25 @@
     </row>
     <row r="243" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A243" s="22">
-        <v>10030022</v>
+        <v>10010022</v>
       </c>
       <c r="B243" s="22">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C243" s="23" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D243" s="27">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E243" s="67">
         <v>22</v>
       </c>
       <c r="F243" s="24" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G243" s="25" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H243" s="17">
         <v>100000000</v>
@@ -13860,25 +13863,25 @@
     </row>
     <row r="244" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A244" s="22">
-        <v>10030023</v>
+        <v>10010023</v>
       </c>
       <c r="B244" s="22">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C244" s="23" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D244" s="27">
-        <v>100300001</v>
+        <v>100100026</v>
       </c>
       <c r="E244" s="67">
         <v>23</v>
       </c>
       <c r="F244" s="24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G244" s="25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H244" s="31">
         <v>1000000000</v>
@@ -13910,25 +13913,25 @@
     </row>
     <row r="245" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A245" s="22">
-        <v>10070021</v>
+        <v>10030021</v>
       </c>
       <c r="B245" s="22">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C245" s="23" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D245" s="27">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E245" s="67">
         <v>21</v>
       </c>
       <c r="F245" s="24" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G245" s="25" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H245" s="17">
         <v>10000000</v>
@@ -13943,7 +13946,7 @@
         <v>36</v>
       </c>
       <c r="L245" s="30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M245" s="26" t="s">
         <v>37</v>
@@ -13960,25 +13963,25 @@
     </row>
     <row r="246" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A246" s="22">
-        <v>10070022</v>
+        <v>10030022</v>
       </c>
       <c r="B246" s="22">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C246" s="23" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D246" s="27">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E246" s="67">
         <v>22</v>
       </c>
       <c r="F246" s="24" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G246" s="25" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H246" s="17">
         <v>100000000</v>
@@ -13993,7 +13996,7 @@
         <v>36</v>
       </c>
       <c r="L246" s="30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M246" s="26" t="s">
         <v>40</v>
@@ -14010,25 +14013,25 @@
     </row>
     <row r="247" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A247" s="22">
-        <v>10070023</v>
+        <v>10030023</v>
       </c>
       <c r="B247" s="22">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C247" s="23" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D247" s="27">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="E247" s="67">
         <v>23</v>
       </c>
       <c r="F247" s="24" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G247" s="25" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H247" s="31">
         <v>1000000000</v>
@@ -14043,7 +14046,7 @@
         <v>36</v>
       </c>
       <c r="L247" s="30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M247" s="26" t="s">
         <v>43</v>
@@ -14060,31 +14063,31 @@
     </row>
     <row r="248" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A248" s="22">
-        <v>10120021</v>
+        <v>10070021</v>
       </c>
       <c r="B248" s="22">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="C248" s="23" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D248" s="27">
-        <v>101200001</v>
+        <v>100700001</v>
       </c>
       <c r="E248" s="67">
         <v>21</v>
       </c>
-      <c r="F248" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="G248" s="33" t="s">
-        <v>58</v>
+      <c r="F248" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G248" s="25" t="s">
+        <v>51</v>
       </c>
       <c r="H248" s="17">
         <v>10000000</v>
       </c>
-      <c r="I248" s="34">
-        <v>9700</v>
+      <c r="I248" s="28">
+        <v>9500</v>
       </c>
       <c r="J248" s="26">
         <v>5000000</v>
@@ -14093,7 +14096,7 @@
         <v>36</v>
       </c>
       <c r="L248" s="30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M248" s="26" t="s">
         <v>37</v>
@@ -14110,25 +14113,25 @@
     </row>
     <row r="249" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A249" s="22">
-        <v>10120022</v>
+        <v>10070022</v>
       </c>
       <c r="B249" s="22">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="C249" s="23" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D249" s="27">
-        <v>101200001</v>
+        <v>100700001</v>
       </c>
       <c r="E249" s="67">
         <v>22</v>
       </c>
       <c r="F249" s="24" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G249" s="25" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H249" s="17">
         <v>100000000</v>
@@ -14143,7 +14146,7 @@
         <v>36</v>
       </c>
       <c r="L249" s="30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M249" s="26" t="s">
         <v>40</v>
@@ -14160,25 +14163,25 @@
     </row>
     <row r="250" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A250" s="22">
-        <v>10120023</v>
+        <v>10070023</v>
       </c>
       <c r="B250" s="22">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D250" s="27">
-        <v>101200001</v>
+        <v>100700001</v>
       </c>
       <c r="E250" s="67">
         <v>23</v>
       </c>
       <c r="F250" s="24" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G250" s="25" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H250" s="31">
         <v>1000000000</v>
@@ -14193,7 +14196,7 @@
         <v>36</v>
       </c>
       <c r="L250" s="30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M250" s="26" t="s">
         <v>43</v>
@@ -14210,31 +14213,31 @@
     </row>
     <row r="251" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A251" s="22">
-        <v>10140021</v>
+        <v>10120021</v>
       </c>
       <c r="B251" s="22">
-        <v>101400</v>
+        <v>101200</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D251" s="27">
-        <v>101400001</v>
+        <v>101200001</v>
       </c>
       <c r="E251" s="67">
         <v>21</v>
       </c>
-      <c r="F251" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G251" s="25" t="s">
-        <v>39</v>
+      <c r="F251" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="G251" s="33" t="s">
+        <v>58</v>
       </c>
       <c r="H251" s="17">
         <v>10000000</v>
       </c>
-      <c r="I251" s="28">
-        <v>9500</v>
+      <c r="I251" s="34">
+        <v>9700</v>
       </c>
       <c r="J251" s="26">
         <v>5000000</v>
@@ -14260,16 +14263,16 @@
     </row>
     <row r="252" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A252" s="22">
-        <v>10140022</v>
+        <v>10120022</v>
       </c>
       <c r="B252" s="22">
-        <v>101400</v>
+        <v>101200</v>
       </c>
       <c r="C252" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D252" s="27">
-        <v>101400001</v>
+        <v>101200001</v>
       </c>
       <c r="E252" s="67">
         <v>22</v>
@@ -14310,16 +14313,16 @@
     </row>
     <row r="253" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A253" s="22">
-        <v>10140023</v>
+        <v>10120023</v>
       </c>
       <c r="B253" s="22">
-        <v>101400</v>
+        <v>101200</v>
       </c>
       <c r="C253" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D253" s="27">
-        <v>101400001</v>
+        <v>101200001</v>
       </c>
       <c r="E253" s="67">
         <v>23</v>
@@ -14360,25 +14363,25 @@
     </row>
     <row r="254" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A254" s="22">
-        <v>10170021</v>
+        <v>10140021</v>
       </c>
       <c r="B254" s="22">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D254" s="27">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E254" s="67">
         <v>21</v>
       </c>
       <c r="F254" s="24" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G254" s="25" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H254" s="17">
         <v>10000000</v>
@@ -14410,25 +14413,25 @@
     </row>
     <row r="255" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A255" s="22">
-        <v>10170022</v>
+        <v>10140022</v>
       </c>
       <c r="B255" s="22">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C255" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D255" s="27">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E255" s="67">
         <v>22</v>
       </c>
       <c r="F255" s="24" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G255" s="25" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H255" s="17">
         <v>100000000</v>
@@ -14460,25 +14463,25 @@
     </row>
     <row r="256" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A256" s="22">
-        <v>10170023</v>
+        <v>10140023</v>
       </c>
       <c r="B256" s="22">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C256" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D256" s="27">
-        <v>101700001</v>
+        <v>101400001</v>
       </c>
       <c r="E256" s="67">
         <v>23</v>
       </c>
       <c r="F256" s="24" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G256" s="25" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H256" s="31">
         <v>1000000000</v>
@@ -14510,16 +14513,16 @@
     </row>
     <row r="257" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A257" s="22">
-        <v>10210021</v>
+        <v>10170021</v>
       </c>
       <c r="B257" s="22">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C257" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D257" s="27">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E257" s="67">
         <v>21</v>
@@ -14560,16 +14563,16 @@
     </row>
     <row r="258" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A258" s="22">
-        <v>10210022</v>
+        <v>10170022</v>
       </c>
       <c r="B258" s="22">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C258" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D258" s="27">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E258" s="67">
         <v>22</v>
@@ -14610,16 +14613,16 @@
     </row>
     <row r="259" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A259" s="22">
-        <v>10210023</v>
+        <v>10170023</v>
       </c>
       <c r="B259" s="22">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D259" s="27">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E259" s="67">
         <v>23</v>
@@ -14660,16 +14663,16 @@
     </row>
     <row r="260" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A260" s="22">
-        <v>10220021</v>
+        <v>10210021</v>
       </c>
       <c r="B260" s="22">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C260" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D260" s="27">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E260" s="67">
         <v>21</v>
@@ -14710,16 +14713,16 @@
     </row>
     <row r="261" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A261" s="22">
-        <v>10220022</v>
+        <v>10210022</v>
       </c>
       <c r="B261" s="22">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C261" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D261" s="27">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E261" s="67">
         <v>22</v>
@@ -14760,16 +14763,16 @@
     </row>
     <row r="262" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A262" s="22">
-        <v>10220023</v>
+        <v>10210023</v>
       </c>
       <c r="B262" s="22">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C262" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D262" s="27">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E262" s="67">
         <v>23</v>
@@ -14810,31 +14813,31 @@
     </row>
     <row r="263" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A263" s="22">
-        <v>10240021</v>
+        <v>10220021</v>
       </c>
       <c r="B263" s="22">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C263" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D263" s="27">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E263" s="67">
         <v>21</v>
       </c>
-      <c r="F263" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="G263" s="33" t="s">
-        <v>65</v>
+      <c r="F263" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G263" s="25" t="s">
+        <v>51</v>
       </c>
       <c r="H263" s="17">
         <v>10000000</v>
       </c>
-      <c r="I263" s="34">
-        <v>9700</v>
+      <c r="I263" s="28">
+        <v>9500</v>
       </c>
       <c r="J263" s="26">
         <v>5000000</v>
@@ -14860,25 +14863,25 @@
     </row>
     <row r="264" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A264" s="22">
-        <v>10240022</v>
+        <v>10220022</v>
       </c>
       <c r="B264" s="22">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C264" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D264" s="27">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E264" s="67">
         <v>22</v>
       </c>
       <c r="F264" s="24" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G264" s="25" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H264" s="17">
         <v>100000000</v>
@@ -14910,25 +14913,25 @@
     </row>
     <row r="265" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A265" s="22">
-        <v>10240023</v>
+        <v>10220023</v>
       </c>
       <c r="B265" s="22">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C265" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D265" s="27">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E265" s="67">
         <v>23</v>
       </c>
       <c r="F265" s="24" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G265" s="25" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H265" s="31">
         <v>1000000000</v>
@@ -14960,31 +14963,31 @@
     </row>
     <row r="266" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A266" s="22">
-        <v>10180021</v>
+        <v>10240021</v>
       </c>
       <c r="B266" s="22">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C266" s="23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D266" s="27">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E266" s="67">
         <v>21</v>
       </c>
-      <c r="F266" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="G266" s="25" t="s">
-        <v>51</v>
+      <c r="F266" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="G266" s="33" t="s">
+        <v>65</v>
       </c>
       <c r="H266" s="17">
         <v>10000000</v>
       </c>
-      <c r="I266" s="28">
-        <v>9500</v>
+      <c r="I266" s="34">
+        <v>9700</v>
       </c>
       <c r="J266" s="26">
         <v>5000000</v>
@@ -15010,25 +15013,25 @@
     </row>
     <row r="267" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A267" s="22">
-        <v>10180022</v>
+        <v>10240022</v>
       </c>
       <c r="B267" s="22">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C267" s="23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D267" s="27">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E267" s="67">
         <v>22</v>
       </c>
       <c r="F267" s="24" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G267" s="25" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H267" s="17">
         <v>100000000</v>
@@ -15060,25 +15063,25 @@
     </row>
     <row r="268" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A268" s="22">
-        <v>10180023</v>
+        <v>10240023</v>
       </c>
       <c r="B268" s="22">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C268" s="23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D268" s="27">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E268" s="67">
         <v>23</v>
       </c>
       <c r="F268" s="24" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G268" s="25" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H268" s="31">
         <v>1000000000</v>
@@ -15110,25 +15113,25 @@
     </row>
     <row r="269" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A269" s="22">
-        <v>10250021</v>
+        <v>10180021</v>
       </c>
       <c r="B269" s="22">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C269" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D269" s="27">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E269" s="67">
         <v>21</v>
       </c>
       <c r="F269" s="24" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G269" s="25" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H269" s="17">
         <v>10000000</v>
@@ -15160,25 +15163,25 @@
     </row>
     <row r="270" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A270" s="22">
-        <v>10250022</v>
+        <v>10180022</v>
       </c>
       <c r="B270" s="22">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C270" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D270" s="27">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E270" s="67">
         <v>22</v>
       </c>
       <c r="F270" s="24" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G270" s="25" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="H270" s="17">
         <v>100000000</v>
@@ -15210,25 +15213,25 @@
     </row>
     <row r="271" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A271" s="22">
-        <v>10250023</v>
+        <v>10180023</v>
       </c>
       <c r="B271" s="22">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C271" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D271" s="27">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E271" s="67">
         <v>23</v>
       </c>
       <c r="F271" s="24" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G271" s="25" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H271" s="31">
         <v>1000000000</v>
@@ -15260,25 +15263,25 @@
     </row>
     <row r="272" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A272" s="22">
-        <v>10230021</v>
+        <v>10250021</v>
       </c>
       <c r="B272" s="22">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C272" s="23" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D272" s="27">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E272" s="67">
         <v>21</v>
       </c>
       <c r="F272" s="24" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G272" s="25" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H272" s="17">
         <v>10000000</v>
@@ -15310,25 +15313,25 @@
     </row>
     <row r="273" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A273" s="22">
-        <v>10230022</v>
+        <v>10250022</v>
       </c>
       <c r="B273" s="22">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C273" s="23" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D273" s="27">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E273" s="67">
         <v>22</v>
       </c>
       <c r="F273" s="24" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G273" s="25" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H273" s="17">
         <v>100000000</v>
@@ -15360,25 +15363,25 @@
     </row>
     <row r="274" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A274" s="22">
-        <v>10230023</v>
+        <v>10250023</v>
       </c>
       <c r="B274" s="22">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C274" s="23" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D274" s="27">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E274" s="67">
         <v>23</v>
       </c>
       <c r="F274" s="24" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G274" s="25" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="H274" s="31">
         <v>1000000000</v>
@@ -15410,31 +15413,31 @@
     </row>
     <row r="275" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A275" s="22">
-        <v>10340021</v>
+        <v>10230021</v>
       </c>
       <c r="B275" s="22">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C275" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D275" s="27">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E275" s="67">
         <v>21</v>
       </c>
-      <c r="F275" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="G275" s="33" t="s">
-        <v>69</v>
+      <c r="F275" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G275" s="25" t="s">
+        <v>51</v>
       </c>
       <c r="H275" s="17">
         <v>10000000</v>
       </c>
-      <c r="I275" s="34">
-        <v>9700</v>
+      <c r="I275" s="28">
+        <v>9500</v>
       </c>
       <c r="J275" s="26">
         <v>5000000</v>
@@ -15460,25 +15463,25 @@
     </row>
     <row r="276" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A276" s="22">
-        <v>10340022</v>
+        <v>10230022</v>
       </c>
       <c r="B276" s="22">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C276" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D276" s="27">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E276" s="67">
         <v>22</v>
       </c>
       <c r="F276" s="24" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G276" s="25" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H276" s="17">
         <v>100000000</v>
@@ -15510,25 +15513,25 @@
     </row>
     <row r="277" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A277" s="22">
-        <v>10340023</v>
+        <v>10230023</v>
       </c>
       <c r="B277" s="22">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C277" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D277" s="27">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E277" s="67">
         <v>23</v>
       </c>
       <c r="F277" s="24" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="G277" s="25" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H277" s="31">
         <v>1000000000</v>
@@ -15560,31 +15563,31 @@
     </row>
     <row r="278" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A278" s="22">
-        <v>10350021</v>
+        <v>10340021</v>
       </c>
       <c r="B278" s="22">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C278" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D278" s="35">
-        <v>102900001</v>
+        <v>75</v>
+      </c>
+      <c r="D278" s="27">
+        <v>103000001</v>
       </c>
       <c r="E278" s="67">
         <v>21</v>
       </c>
-      <c r="F278" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G278" s="25" t="s">
-        <v>39</v>
+      <c r="F278" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="G278" s="33" t="s">
+        <v>69</v>
       </c>
       <c r="H278" s="17">
         <v>10000000</v>
       </c>
-      <c r="I278" s="28">
-        <v>9500</v>
+      <c r="I278" s="34">
+        <v>9700</v>
       </c>
       <c r="J278" s="26">
         <v>5000000</v>
@@ -15592,7 +15595,7 @@
       <c r="K278" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="L278" s="29">
+      <c r="L278" s="30">
         <v>100</v>
       </c>
       <c r="M278" s="26" t="s">
@@ -15610,25 +15613,25 @@
     </row>
     <row r="279" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A279" s="22">
-        <v>10350022</v>
+        <v>10340022</v>
       </c>
       <c r="B279" s="22">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C279" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D279" s="35">
-        <v>102900001</v>
+        <v>75</v>
+      </c>
+      <c r="D279" s="27">
+        <v>103000001</v>
       </c>
       <c r="E279" s="67">
         <v>22</v>
       </c>
       <c r="F279" s="24" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G279" s="25" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H279" s="17">
         <v>100000000</v>
@@ -15642,7 +15645,7 @@
       <c r="K279" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="L279" s="29">
+      <c r="L279" s="30">
         <v>100</v>
       </c>
       <c r="M279" s="26" t="s">
@@ -15660,25 +15663,25 @@
     </row>
     <row r="280" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A280" s="22">
-        <v>10350023</v>
+        <v>10340023</v>
       </c>
       <c r="B280" s="22">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C280" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D280" s="35">
-        <v>102900001</v>
+        <v>75</v>
+      </c>
+      <c r="D280" s="27">
+        <v>103000001</v>
       </c>
       <c r="E280" s="67">
         <v>23</v>
       </c>
       <c r="F280" s="24" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G280" s="25" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="H280" s="31">
         <v>1000000000</v>
@@ -15692,7 +15695,7 @@
       <c r="K280" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="L280" s="29">
+      <c r="L280" s="30">
         <v>100</v>
       </c>
       <c r="M280" s="26" t="s">
@@ -15710,16 +15713,16 @@
     </row>
     <row r="281" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A281" s="22">
-        <v>10350121</v>
+        <v>10350021</v>
       </c>
       <c r="B281" s="22">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C281" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D281" s="35">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E281" s="67">
         <v>21</v>
@@ -15760,16 +15763,16 @@
     </row>
     <row r="282" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A282" s="22">
-        <v>10350122</v>
+        <v>10350022</v>
       </c>
       <c r="B282" s="22">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C282" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D282" s="35">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E282" s="67">
         <v>22</v>
@@ -15810,16 +15813,16 @@
     </row>
     <row r="283" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A283" s="22">
-        <v>10350123</v>
+        <v>10350023</v>
       </c>
       <c r="B283" s="22">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C283" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D283" s="35">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E283" s="67">
         <v>23</v>
@@ -15858,79 +15861,79 @@
       <c r="S283" s="26"/>
       <c r="T283" s="26"/>
     </row>
-    <row r="284" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A284" s="36">
-        <v>10360021</v>
-      </c>
-      <c r="B284" s="36">
-        <v>103600</v>
-      </c>
-      <c r="C284" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="D284" s="38">
-        <v>103600001</v>
+    <row r="284" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A284" s="22">
+        <v>10350121</v>
+      </c>
+      <c r="B284" s="22">
+        <v>103501</v>
+      </c>
+      <c r="C284" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D284" s="35">
+        <v>103501001</v>
       </c>
       <c r="E284" s="67">
         <v>21</v>
       </c>
-      <c r="F284" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="G284" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="H284" s="41">
+      <c r="F284" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G284" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="H284" s="17">
         <v>10000000</v>
       </c>
-      <c r="I284" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J284" s="42">
+      <c r="I284" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J284" s="26">
         <v>5000000</v>
       </c>
-      <c r="K284" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="L284" s="43">
+      <c r="K284" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L284" s="29">
         <v>100</v>
       </c>
       <c r="M284" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N284" s="39">
-        <v>0</v>
-      </c>
-      <c r="O284" s="39"/>
-      <c r="P284" s="39"/>
-      <c r="Q284" s="39"/>
-      <c r="R284" s="39"/>
-      <c r="S284" s="42"/>
-      <c r="T284" s="42"/>
+      <c r="N284" s="24">
+        <v>0</v>
+      </c>
+      <c r="O284" s="24"/>
+      <c r="P284" s="24"/>
+      <c r="Q284" s="24"/>
+      <c r="R284" s="24"/>
+      <c r="S284" s="26"/>
+      <c r="T284" s="26"/>
     </row>
     <row r="285" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A285" s="22">
-        <v>10360022</v>
+        <v>10350122</v>
       </c>
       <c r="B285" s="22">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C285" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D285" s="35">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E285" s="67">
         <v>22</v>
       </c>
       <c r="F285" s="24" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G285" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="H285" s="31">
+        <v>42</v>
+      </c>
+      <c r="H285" s="17">
         <v>100000000</v>
       </c>
       <c r="I285" s="28">
@@ -15960,25 +15963,25 @@
     </row>
     <row r="286" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A286" s="22">
-        <v>10360023</v>
+        <v>10350123</v>
       </c>
       <c r="B286" s="22">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C286" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D286" s="35">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E286" s="67">
         <v>23</v>
       </c>
       <c r="F286" s="24" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="G286" s="25" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H286" s="31">
         <v>1000000000</v>
@@ -16008,77 +16011,77 @@
       <c r="S286" s="26"/>
       <c r="T286" s="26"/>
     </row>
-    <row r="287" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A287" s="22">
-        <v>10200021</v>
-      </c>
-      <c r="B287" s="22">
-        <v>102000</v>
-      </c>
-      <c r="C287" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="D287" s="35">
-        <v>102000001</v>
+    <row r="287" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A287" s="36">
+        <v>10360021</v>
+      </c>
+      <c r="B287" s="36">
+        <v>103600</v>
+      </c>
+      <c r="C287" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D287" s="38">
+        <v>103600001</v>
       </c>
       <c r="E287" s="67">
         <v>21</v>
       </c>
-      <c r="F287" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="G287" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="H287" s="31">
+      <c r="F287" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="G287" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="H287" s="41">
         <v>10000000</v>
       </c>
-      <c r="I287" s="28">
-        <v>9500</v>
-      </c>
-      <c r="J287" s="26">
+      <c r="I287" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J287" s="42">
         <v>5000000</v>
       </c>
-      <c r="K287" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L287" s="29">
+      <c r="K287" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="L287" s="43">
         <v>100</v>
       </c>
       <c r="M287" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N287" s="24">
-        <v>0</v>
-      </c>
-      <c r="O287" s="24"/>
-      <c r="P287" s="24"/>
-      <c r="Q287" s="24"/>
-      <c r="R287" s="24"/>
-      <c r="S287" s="26"/>
-      <c r="T287" s="26"/>
+      <c r="N287" s="39">
+        <v>0</v>
+      </c>
+      <c r="O287" s="39"/>
+      <c r="P287" s="39"/>
+      <c r="Q287" s="39"/>
+      <c r="R287" s="39"/>
+      <c r="S287" s="42"/>
+      <c r="T287" s="42"/>
     </row>
     <row r="288" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A288" s="22">
-        <v>10200022</v>
+        <v>10360022</v>
       </c>
       <c r="B288" s="22">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C288" s="23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D288" s="35">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="E288" s="67">
         <v>22</v>
       </c>
       <c r="F288" s="24" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G288" s="25" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="H288" s="31">
         <v>100000000</v>
@@ -16110,25 +16113,25 @@
     </row>
     <row r="289" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A289" s="22">
-        <v>10200023</v>
+        <v>10360023</v>
       </c>
       <c r="B289" s="22">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C289" s="23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D289" s="35">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="E289" s="67">
         <v>23</v>
       </c>
       <c r="F289" s="24" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G289" s="25" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H289" s="31">
         <v>1000000000</v>
@@ -16160,25 +16163,25 @@
     </row>
     <row r="290" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A290" s="22">
-        <v>10340121</v>
+        <v>10200021</v>
       </c>
       <c r="B290" s="22">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C290" s="23" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D290" s="35">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E290" s="67">
         <v>21</v>
       </c>
       <c r="F290" s="24" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G290" s="25" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H290" s="31">
         <v>10000000</v>
@@ -16210,25 +16213,25 @@
     </row>
     <row r="291" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A291" s="22">
-        <v>10340122</v>
+        <v>10200022</v>
       </c>
       <c r="B291" s="22">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C291" s="23" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D291" s="35">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E291" s="67">
         <v>22</v>
       </c>
       <c r="F291" s="24" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G291" s="25" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="H291" s="31">
         <v>100000000</v>
@@ -16260,25 +16263,25 @@
     </row>
     <row r="292" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A292" s="22">
-        <v>10340123</v>
+        <v>10200023</v>
       </c>
       <c r="B292" s="22">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C292" s="23" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D292" s="35">
-        <v>103400001</v>
+        <v>102000001</v>
       </c>
       <c r="E292" s="67">
         <v>23</v>
       </c>
       <c r="F292" s="24" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G292" s="25" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H292" s="31">
         <v>1000000000</v>
@@ -16310,25 +16313,25 @@
     </row>
     <row r="293" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A293" s="22">
-        <v>10380021</v>
+        <v>10340121</v>
       </c>
       <c r="B293" s="22">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C293" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D293" s="35">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E293" s="67">
         <v>21</v>
       </c>
       <c r="F293" s="24" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G293" s="25" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="H293" s="31">
         <v>10000000</v>
@@ -16360,25 +16363,25 @@
     </row>
     <row r="294" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A294" s="22">
-        <v>10380022</v>
+        <v>10340122</v>
       </c>
       <c r="B294" s="22">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C294" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D294" s="35">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E294" s="67">
         <v>22</v>
       </c>
       <c r="F294" s="24" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="G294" s="25" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H294" s="31">
         <v>100000000</v>
@@ -16410,25 +16413,25 @@
     </row>
     <row r="295" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A295" s="22">
-        <v>10380023</v>
+        <v>10340123</v>
       </c>
       <c r="B295" s="22">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C295" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D295" s="35">
-        <v>103800001</v>
+        <v>103400001</v>
       </c>
       <c r="E295" s="67">
         <v>23</v>
       </c>
       <c r="F295" s="24" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G295" s="25" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="H295" s="31">
         <v>1000000000</v>
@@ -16460,16 +16463,16 @@
     </row>
     <row r="296" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A296" s="22">
-        <v>10400021</v>
+        <v>10380021</v>
       </c>
       <c r="B296" s="22">
-        <v>104000</v>
+        <v>103800</v>
       </c>
       <c r="C296" s="23" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D296" s="35">
-        <v>104000001</v>
+        <v>103800001</v>
       </c>
       <c r="E296" s="67">
         <v>21</v>
@@ -16510,16 +16513,16 @@
     </row>
     <row r="297" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A297" s="22">
-        <v>10400022</v>
+        <v>10380022</v>
       </c>
       <c r="B297" s="22">
-        <v>104000</v>
+        <v>103800</v>
       </c>
       <c r="C297" s="23" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D297" s="35">
-        <v>104000001</v>
+        <v>103800001</v>
       </c>
       <c r="E297" s="67">
         <v>22</v>
@@ -16560,16 +16563,16 @@
     </row>
     <row r="298" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A298" s="22">
-        <v>10400023</v>
+        <v>10380023</v>
       </c>
       <c r="B298" s="22">
-        <v>104000</v>
+        <v>103800</v>
       </c>
       <c r="C298" s="23" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D298" s="35">
-        <v>104000001</v>
+        <v>103800001</v>
       </c>
       <c r="E298" s="67">
         <v>23</v>
@@ -16607,6 +16610,156 @@
       <c r="R298" s="24"/>
       <c r="S298" s="26"/>
       <c r="T298" s="26"/>
+    </row>
+    <row r="299" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A299" s="22">
+        <v>10400021</v>
+      </c>
+      <c r="B299" s="22">
+        <v>104000</v>
+      </c>
+      <c r="C299" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D299" s="35">
+        <v>104000001</v>
+      </c>
+      <c r="E299" s="67">
+        <v>21</v>
+      </c>
+      <c r="F299" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="G299" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="H299" s="31">
+        <v>10000000</v>
+      </c>
+      <c r="I299" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J299" s="26">
+        <v>5000000</v>
+      </c>
+      <c r="K299" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L299" s="29">
+        <v>100</v>
+      </c>
+      <c r="M299" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N299" s="24">
+        <v>0</v>
+      </c>
+      <c r="O299" s="24"/>
+      <c r="P299" s="24"/>
+      <c r="Q299" s="24"/>
+      <c r="R299" s="24"/>
+      <c r="S299" s="26"/>
+      <c r="T299" s="26"/>
+    </row>
+    <row r="300" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A300" s="22">
+        <v>10400022</v>
+      </c>
+      <c r="B300" s="22">
+        <v>104000</v>
+      </c>
+      <c r="C300" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D300" s="35">
+        <v>104000001</v>
+      </c>
+      <c r="E300" s="67">
+        <v>22</v>
+      </c>
+      <c r="F300" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="G300" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="H300" s="31">
+        <v>100000000</v>
+      </c>
+      <c r="I300" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J300" s="26">
+        <v>50000000</v>
+      </c>
+      <c r="K300" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L300" s="29">
+        <v>100</v>
+      </c>
+      <c r="M300" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="N300" s="24">
+        <v>0</v>
+      </c>
+      <c r="O300" s="24"/>
+      <c r="P300" s="24"/>
+      <c r="Q300" s="24"/>
+      <c r="R300" s="24"/>
+      <c r="S300" s="26"/>
+      <c r="T300" s="26"/>
+    </row>
+    <row r="301" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A301" s="22">
+        <v>10400023</v>
+      </c>
+      <c r="B301" s="22">
+        <v>104000</v>
+      </c>
+      <c r="C301" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D301" s="35">
+        <v>104000001</v>
+      </c>
+      <c r="E301" s="67">
+        <v>23</v>
+      </c>
+      <c r="F301" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G301" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="H301" s="31">
+        <v>1000000000</v>
+      </c>
+      <c r="I301" s="28">
+        <v>9500</v>
+      </c>
+      <c r="J301" s="26">
+        <v>500000000</v>
+      </c>
+      <c r="K301" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L301" s="29">
+        <v>100</v>
+      </c>
+      <c r="M301" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="N301" s="24">
+        <v>0</v>
+      </c>
+      <c r="O301" s="24"/>
+      <c r="P301" s="24"/>
+      <c r="Q301" s="24"/>
+      <c r="R301" s="24"/>
+      <c r="S301" s="26"/>
+      <c r="T301" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="135">
   <si>
     <t>id</t>
   </si>
@@ -338,9 +338,6 @@
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>50_100_250_400_600_800_1000</t>
-  </si>
-  <si>
     <t>50:1</t>
   </si>
   <si>
@@ -359,16 +356,13 @@
     <t>财神</t>
   </si>
   <si>
-    <t>8_16_40_80_160_400_800</t>
-  </si>
-  <si>
-    <t>8:1</t>
-  </si>
-  <si>
     <t>埃及艳后</t>
   </si>
   <si>
     <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>50_100_250_400_600_800_1000</t>
   </si>
   <si>
     <t>杰克船长</t>
@@ -390,9 +384,6 @@
   </si>
   <si>
     <t>寒冰王座</t>
-  </si>
-  <si>
-    <t>20_40_100_160_240_320_400</t>
   </si>
   <si>
     <t>20:1</t>
@@ -440,16 +431,10 @@
     <t>宙斯vs哈迪斯</t>
   </si>
   <si>
-    <t>75_150_375_600_900_1200_1500</t>
-  </si>
-  <si>
-    <t>75:1</t>
+    <t>750:1</t>
   </si>
   <si>
     <t>750_1500_3750_6000_9000_12000_15000</t>
-  </si>
-  <si>
-    <t>750:1</t>
   </si>
   <si>
     <t>7500_15000_37500_60000_90000_120000_150000</t>
@@ -489,9 +474,6 @@
   </si>
   <si>
     <t>绿巨人</t>
-  </si>
-  <si>
-    <t>40_80_200_320_480_640_800</t>
   </si>
   <si>
     <t>40:1</t>
@@ -572,6 +554,18 @@
     <t>1980000_50000000</t>
   </si>
   <si>
+    <t>20_40_100_160_240_320_400</t>
+  </si>
+  <si>
+    <t>75_150_375_600_900_1200_1500</t>
+  </si>
+  <si>
+    <t>75:1</t>
+  </si>
+  <si>
+    <t>40_80_200_320_480_640_800</t>
+  </si>
+  <si>
     <t>黄金帝国</t>
   </si>
   <si>
@@ -591,6 +585,12 @@
   </si>
   <si>
     <t>狂野沙滩</t>
+  </si>
+  <si>
+    <t>8_16_40_80_160_400_800</t>
+  </si>
+  <si>
+    <t>8:1</t>
   </si>
 </sst>
 </file>
@@ -805,6 +805,7 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -825,17 +826,16 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -2401,11 +2401,11 @@
       <c r="E11" s="23">
         <v>1</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="24">
         <v>50</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11" s="17">
         <v>10000000</v>
@@ -2452,10 +2452,10 @@
         <v>2</v>
       </c>
       <c r="F12" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G12" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H12" s="17">
         <v>100000000</v>
@@ -2502,10 +2502,10 @@
         <v>3</v>
       </c>
       <c r="F13" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H13" s="31">
         <v>1000000000</v>
@@ -2543,7 +2543,7 @@
         <v>101200</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" s="27">
         <v>101200001</v>
@@ -2551,11 +2551,11 @@
       <c r="E14" s="23">
         <v>1</v>
       </c>
-      <c r="F14" s="32" t="s">
-        <v>57</v>
+      <c r="F14" s="32">
+        <v>50</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H14" s="17">
         <v>10000000</v>
@@ -2593,7 +2593,7 @@
         <v>101200</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="27">
         <v>101200001</v>
@@ -2643,7 +2643,7 @@
         <v>101200</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="27">
         <v>101200001</v>
@@ -2693,7 +2693,7 @@
         <v>101400</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D17" s="27">
         <v>101400001</v>
@@ -2743,7 +2743,7 @@
         <v>101400</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D18" s="27">
         <v>101400001</v>
@@ -2793,7 +2793,7 @@
         <v>101400</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D19" s="27">
         <v>101400001</v>
@@ -2843,7 +2843,7 @@
         <v>101700</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D20" s="27">
         <v>101700001</v>
@@ -2852,10 +2852,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H20" s="17">
         <v>10000000</v>
@@ -2893,7 +2893,7 @@
         <v>101700</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D21" s="27">
         <v>101700001</v>
@@ -2902,10 +2902,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H21" s="17">
         <v>100000000</v>
@@ -2943,7 +2943,7 @@
         <v>101700</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D22" s="27">
         <v>101700001</v>
@@ -2952,10 +2952,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H22" s="31">
         <v>1000000000</v>
@@ -2993,7 +2993,7 @@
         <v>102100</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D23" s="27">
         <v>102100001</v>
@@ -3001,11 +3001,11 @@
       <c r="E23" s="23">
         <v>1</v>
       </c>
-      <c r="F23" s="24" t="s">
-        <v>50</v>
+      <c r="F23" s="24">
+        <v>100</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H23" s="17">
         <v>10000000</v>
@@ -3043,7 +3043,7 @@
         <v>102100</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D24" s="27">
         <v>102100001</v>
@@ -3052,10 +3052,10 @@
         <v>2</v>
       </c>
       <c r="F24" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H24" s="17">
         <v>100000000</v>
@@ -3093,7 +3093,7 @@
         <v>102100</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D25" s="27">
         <v>102100001</v>
@@ -3102,10 +3102,10 @@
         <v>3</v>
       </c>
       <c r="F25" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H25" s="31">
         <v>1000000000</v>
@@ -3143,7 +3143,7 @@
         <v>102200</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D26" s="27">
         <v>102200001</v>
@@ -3151,11 +3151,11 @@
       <c r="E26" s="23">
         <v>1</v>
       </c>
-      <c r="F26" s="24" t="s">
-        <v>50</v>
+      <c r="F26" s="24">
+        <v>100</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H26" s="17">
         <v>10000000</v>
@@ -3193,7 +3193,7 @@
         <v>102200</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D27" s="27">
         <v>102200001</v>
@@ -3202,10 +3202,10 @@
         <v>2</v>
       </c>
       <c r="F27" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G27" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H27" s="17">
         <v>100000000</v>
@@ -3243,7 +3243,7 @@
         <v>102200</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D28" s="27">
         <v>102200001</v>
@@ -3252,10 +3252,10 @@
         <v>3</v>
       </c>
       <c r="F28" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G28" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H28" s="31">
         <v>1000000000</v>
@@ -3293,7 +3293,7 @@
         <v>102400</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D29" s="27">
         <v>102400026</v>
@@ -3302,10 +3302,10 @@
         <v>1</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G29" s="33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H29" s="17">
         <v>10000000</v>
@@ -3343,7 +3343,7 @@
         <v>102400</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D30" s="27">
         <v>102400026</v>
@@ -3393,7 +3393,7 @@
         <v>102400</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D31" s="27">
         <v>102400026</v>
@@ -3443,7 +3443,7 @@
         <v>101800</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D32" s="27">
         <v>101800001</v>
@@ -3451,11 +3451,11 @@
       <c r="E32" s="23">
         <v>1</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="24">
         <v>50</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H32" s="17">
         <v>10000000</v>
@@ -3493,7 +3493,7 @@
         <v>101800</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D33" s="27">
         <v>101800001</v>
@@ -3502,10 +3502,10 @@
         <v>2</v>
       </c>
       <c r="F33" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G33" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H33" s="17">
         <v>100000000</v>
@@ -3543,7 +3543,7 @@
         <v>101800</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D34" s="27">
         <v>101800001</v>
@@ -3552,10 +3552,10 @@
         <v>3</v>
       </c>
       <c r="F34" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G34" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H34" s="31">
         <v>1000000000</v>
@@ -3593,7 +3593,7 @@
         <v>102500</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D35" s="27">
         <v>102500001</v>
@@ -3601,11 +3601,11 @@
       <c r="E35" s="23">
         <v>1</v>
       </c>
-      <c r="F35" s="24" t="s">
-        <v>68</v>
+      <c r="F35" s="24">
+        <v>20</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H35" s="17">
         <v>10000000</v>
@@ -3643,7 +3643,7 @@
         <v>102500</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D36" s="27">
         <v>102500001</v>
@@ -3652,10 +3652,10 @@
         <v>2</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H36" s="17">
         <v>100000000</v>
@@ -3693,7 +3693,7 @@
         <v>102500</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D37" s="27">
         <v>102500001</v>
@@ -3702,10 +3702,10 @@
         <v>3</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H37" s="31">
         <v>1000000000</v>
@@ -3743,7 +3743,7 @@
         <v>102300</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D38" s="27">
         <v>102300001</v>
@@ -3752,10 +3752,10 @@
         <v>1</v>
       </c>
       <c r="F38" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G38" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H38" s="17">
         <v>10000000</v>
@@ -3793,7 +3793,7 @@
         <v>102300</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D39" s="27">
         <v>102300001</v>
@@ -3802,10 +3802,10 @@
         <v>2</v>
       </c>
       <c r="F39" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G39" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G39" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H39" s="17">
         <v>100000000</v>
@@ -3843,7 +3843,7 @@
         <v>102300</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D40" s="27">
         <v>102300001</v>
@@ -3852,10 +3852,10 @@
         <v>3</v>
       </c>
       <c r="F40" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G40" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G40" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H40" s="31">
         <v>1000000000</v>
@@ -3893,7 +3893,7 @@
         <v>103400</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D41" s="27">
         <v>103000001</v>
@@ -3902,10 +3902,10 @@
         <v>1</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G41" s="33" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H41" s="17">
         <v>10000000</v>
@@ -3943,7 +3943,7 @@
         <v>103400</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D42" s="27">
         <v>103000001</v>
@@ -3952,10 +3952,10 @@
         <v>2</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G42" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H42" s="17">
         <v>100000000</v>
@@ -3993,7 +3993,7 @@
         <v>103400</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D43" s="27">
         <v>103000001</v>
@@ -4002,10 +4002,10 @@
         <v>3</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H43" s="31">
         <v>1000000000</v>
@@ -4043,7 +4043,7 @@
         <v>103500</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D44" s="35">
         <v>102900001</v>
@@ -4093,7 +4093,7 @@
         <v>103500</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D45" s="35">
         <v>102900001</v>
@@ -4143,7 +4143,7 @@
         <v>103500</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D46" s="35">
         <v>102900001</v>
@@ -4193,7 +4193,7 @@
         <v>103501</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D47" s="35">
         <v>103501001</v>
@@ -4243,7 +4243,7 @@
         <v>103501</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D48" s="35">
         <v>103501001</v>
@@ -4293,7 +4293,7 @@
         <v>103501</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D49" s="35">
         <v>103501001</v>
@@ -4343,7 +4343,7 @@
         <v>103600</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D50" s="38">
         <v>103600001</v>
@@ -4352,10 +4352,10 @@
         <v>1</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H50" s="41">
         <v>10000000</v>
@@ -4393,7 +4393,7 @@
         <v>103600</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D51" s="35">
         <v>103600001</v>
@@ -4402,10 +4402,10 @@
         <v>2</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H51" s="31">
         <v>100000000</v>
@@ -4443,7 +4443,7 @@
         <v>103600</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D52" s="35">
         <v>103600001</v>
@@ -4452,10 +4452,10 @@
         <v>3</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H52" s="31">
         <v>1000000000</v>
@@ -4493,7 +4493,7 @@
         <v>102800</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D53" s="35">
         <v>102800001</v>
@@ -4502,10 +4502,10 @@
         <v>1</v>
       </c>
       <c r="F53" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G53" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G53" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H53" s="31">
         <v>10000000</v>
@@ -4543,7 +4543,7 @@
         <v>102800</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D54" s="35">
         <v>102800001</v>
@@ -4552,10 +4552,10 @@
         <v>2</v>
       </c>
       <c r="F54" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G54" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G54" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H54" s="31">
         <v>100000000</v>
@@ -4593,7 +4593,7 @@
         <v>102800</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D55" s="35">
         <v>102800001</v>
@@ -4602,10 +4602,10 @@
         <v>3</v>
       </c>
       <c r="F55" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G55" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G55" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H55" s="31">
         <v>1000000000</v>
@@ -4643,7 +4643,7 @@
         <v>102000</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D56" s="35">
         <v>102000001</v>
@@ -4651,11 +4651,11 @@
       <c r="E56" s="23">
         <v>1</v>
       </c>
-      <c r="F56" s="24" t="s">
-        <v>84</v>
+      <c r="F56" s="24">
+        <v>750</v>
       </c>
       <c r="G56" s="25" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H56" s="31">
         <v>10000000</v>
@@ -4693,7 +4693,7 @@
         <v>102000</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D57" s="35">
         <v>102000001</v>
@@ -4702,10 +4702,10 @@
         <v>2</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G57" s="25" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H57" s="31">
         <v>100000000</v>
@@ -4743,7 +4743,7 @@
         <v>102000</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D58" s="35">
         <v>102000001</v>
@@ -4752,10 +4752,10 @@
         <v>3</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G58" s="25" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H58" s="31">
         <v>1000000000</v>
@@ -4793,7 +4793,7 @@
         <v>103401</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D59" s="35">
         <v>103400001</v>
@@ -4802,10 +4802,10 @@
         <v>1</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G59" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H59" s="31">
         <v>10000000</v>
@@ -4843,7 +4843,7 @@
         <v>103401</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D60" s="35">
         <v>103400001</v>
@@ -4852,10 +4852,10 @@
         <v>2</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G60" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H60" s="31">
         <v>100000000</v>
@@ -4893,7 +4893,7 @@
         <v>103401</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D61" s="35">
         <v>103400001</v>
@@ -4902,10 +4902,10 @@
         <v>3</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G61" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H61" s="31">
         <v>1000000000</v>
@@ -4943,7 +4943,7 @@
         <v>103800</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D62" s="35">
         <v>103800001</v>
@@ -4952,10 +4952,10 @@
         <v>1</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G62" s="25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H62" s="31">
         <v>10000000</v>
@@ -4993,7 +4993,7 @@
         <v>103800</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D63" s="35">
         <v>103800001</v>
@@ -5002,10 +5002,10 @@
         <v>2</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G63" s="25" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H63" s="31">
         <v>100000000</v>
@@ -5043,7 +5043,7 @@
         <v>103800</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D64" s="35">
         <v>103800001</v>
@@ -5052,10 +5052,10 @@
         <v>3</v>
       </c>
       <c r="F64" s="24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G64" s="25" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H64" s="31">
         <v>1000000000</v>
@@ -5093,7 +5093,7 @@
         <v>102700</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D65" s="35">
         <v>102700001</v>
@@ -5102,10 +5102,10 @@
         <v>1</v>
       </c>
       <c r="F65" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G65" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G65" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H65" s="31">
         <v>10000000</v>
@@ -5143,7 +5143,7 @@
         <v>102700</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D66" s="35">
         <v>102700001</v>
@@ -5152,10 +5152,10 @@
         <v>2</v>
       </c>
       <c r="F66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G66" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G66" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H66" s="31">
         <v>100000000</v>
@@ -5193,7 +5193,7 @@
         <v>102700</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D67" s="35">
         <v>102700001</v>
@@ -5202,10 +5202,10 @@
         <v>3</v>
       </c>
       <c r="F67" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G67" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G67" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H67" s="31">
         <v>1000000000</v>
@@ -5243,7 +5243,7 @@
         <v>103700</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D68" s="35">
         <v>103700001</v>
@@ -5293,7 +5293,7 @@
         <v>103700</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D69" s="35">
         <v>103700001</v>
@@ -5343,7 +5343,7 @@
         <v>103700</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D70" s="35">
         <v>103700001</v>
@@ -5393,7 +5393,7 @@
         <v>103100</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D71" s="35">
         <v>103100001</v>
@@ -5401,11 +5401,11 @@
       <c r="E71" s="23">
         <v>1</v>
       </c>
-      <c r="F71" s="24" t="s">
-        <v>101</v>
+      <c r="F71" s="24">
+        <v>40</v>
       </c>
       <c r="G71" s="25" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H71" s="31">
         <v>10000000</v>
@@ -5443,7 +5443,7 @@
         <v>103100</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D72" s="35">
         <v>103100001</v>
@@ -5452,10 +5452,10 @@
         <v>2</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G72" s="25" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H72" s="31">
         <v>100000000</v>
@@ -5493,7 +5493,7 @@
         <v>103100</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D73" s="35">
         <v>103100001</v>
@@ -5502,10 +5502,10 @@
         <v>3</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G73" s="25" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H73" s="31">
         <v>1000000000</v>
@@ -5543,7 +5543,7 @@
         <v>104000</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D74" s="35">
         <v>104000001</v>
@@ -5552,10 +5552,10 @@
         <v>1</v>
       </c>
       <c r="F74" s="24" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H74" s="31">
         <v>10000000</v>
@@ -5593,7 +5593,7 @@
         <v>104000</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D75" s="35">
         <v>104000001</v>
@@ -5602,10 +5602,10 @@
         <v>2</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G75" s="25" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H75" s="31">
         <v>100000000</v>
@@ -5643,7 +5643,7 @@
         <v>104000</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D76" s="35">
         <v>104000001</v>
@@ -5652,10 +5652,10 @@
         <v>3</v>
       </c>
       <c r="F76" s="24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G76" s="25" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H76" s="31">
         <v>1000000000</v>
@@ -5693,7 +5693,7 @@
         <v>103900</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D77" s="35">
         <v>103900001</v>
@@ -5701,11 +5701,11 @@
       <c r="E77" s="23">
         <v>1</v>
       </c>
-      <c r="F77" s="24" t="s">
-        <v>101</v>
+      <c r="F77" s="24">
+        <v>200</v>
       </c>
       <c r="G77" s="25" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="H77" s="31">
         <v>10000000</v>
@@ -5743,7 +5743,7 @@
         <v>103900</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D78" s="35">
         <v>103900001</v>
@@ -5752,10 +5752,10 @@
         <v>2</v>
       </c>
       <c r="F78" s="24" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G78" s="25" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H78" s="31">
         <v>100000000</v>
@@ -5793,7 +5793,7 @@
         <v>103900</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D79" s="35">
         <v>103900001</v>
@@ -5802,10 +5802,10 @@
         <v>3</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G79" s="25" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H79" s="31">
         <v>1000000000</v>
@@ -5843,7 +5843,7 @@
         <v>101600</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D80" s="35">
         <v>101600001</v>
@@ -5852,10 +5852,10 @@
         <v>1</v>
       </c>
       <c r="F80" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G80" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G80" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H80" s="31">
         <v>10000000</v>
@@ -5893,7 +5893,7 @@
         <v>101600</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D81" s="35">
         <v>101600001</v>
@@ -5902,10 +5902,10 @@
         <v>2</v>
       </c>
       <c r="F81" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G81" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G81" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H81" s="31">
         <v>100000000</v>
@@ -5943,7 +5943,7 @@
         <v>101600</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D82" s="35">
         <v>101600001</v>
@@ -5952,10 +5952,10 @@
         <v>3</v>
       </c>
       <c r="F82" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G82" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G82" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H82" s="31">
         <v>1000000000</v>
@@ -5993,7 +5993,7 @@
         <v>101500</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D83" s="35">
         <v>101500001</v>
@@ -6002,10 +6002,10 @@
         <v>1</v>
       </c>
       <c r="F83" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G83" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G83" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H83" s="31">
         <v>10000000</v>
@@ -6043,7 +6043,7 @@
         <v>101500</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D84" s="35">
         <v>101500001</v>
@@ -6052,10 +6052,10 @@
         <v>2</v>
       </c>
       <c r="F84" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G84" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G84" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H84" s="31">
         <v>100000000</v>
@@ -6093,7 +6093,7 @@
         <v>101500</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D85" s="35">
         <v>101500001</v>
@@ -6102,10 +6102,10 @@
         <v>3</v>
       </c>
       <c r="F85" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G85" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G85" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H85" s="31">
         <v>1000000000</v>
@@ -6143,7 +6143,7 @@
         <v>102600</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D86" s="35">
         <v>102600001</v>
@@ -6152,10 +6152,10 @@
         <v>1</v>
       </c>
       <c r="F86" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G86" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G86" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H86" s="31">
         <v>10000000</v>
@@ -6193,7 +6193,7 @@
         <v>102600</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D87" s="35">
         <v>102600001</v>
@@ -6202,10 +6202,10 @@
         <v>2</v>
       </c>
       <c r="F87" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G87" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G87" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H87" s="31">
         <v>100000000</v>
@@ -6243,7 +6243,7 @@
         <v>102600</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D88" s="35">
         <v>102600001</v>
@@ -6252,10 +6252,10 @@
         <v>3</v>
       </c>
       <c r="F88" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G88" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G88" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H88" s="31">
         <v>1000000000</v>
@@ -6293,7 +6293,7 @@
         <v>105000</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D89" s="35">
         <v>105000001</v>
@@ -6302,10 +6302,10 @@
         <v>1</v>
       </c>
       <c r="F89" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G89" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G89" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H89" s="31">
         <v>10000000</v>
@@ -6343,7 +6343,7 @@
         <v>105000</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D90" s="35">
         <v>105000001</v>
@@ -6352,10 +6352,10 @@
         <v>2</v>
       </c>
       <c r="F90" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G90" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G90" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H90" s="31">
         <v>100000000</v>
@@ -6393,7 +6393,7 @@
         <v>105000</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D91" s="35">
         <v>105000001</v>
@@ -6402,10 +6402,10 @@
         <v>3</v>
       </c>
       <c r="F91" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G91" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G91" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H91" s="31">
         <v>1000000000</v>
@@ -6443,7 +6443,7 @@
         <v>105100</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D92" s="35">
         <v>105100001</v>
@@ -6493,7 +6493,7 @@
         <v>105100</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D93" s="35">
         <v>105100001</v>
@@ -6543,7 +6543,7 @@
         <v>105100</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D94" s="35">
         <v>105100001</v>
@@ -6593,7 +6593,7 @@
         <v>105500</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D95" s="35">
         <v>105500001</v>
@@ -6602,10 +6602,10 @@
         <v>1</v>
       </c>
       <c r="F95" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H95" s="31">
         <v>10000000</v>
@@ -6643,7 +6643,7 @@
         <v>105500</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D96" s="35">
         <v>105500001</v>
@@ -6652,10 +6652,10 @@
         <v>2</v>
       </c>
       <c r="F96" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G96" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H96" s="31">
         <v>100000000</v>
@@ -6693,7 +6693,7 @@
         <v>105500</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D97" s="35">
         <v>105500001</v>
@@ -6702,10 +6702,10 @@
         <v>3</v>
       </c>
       <c r="F97" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G97" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H97" s="31">
         <v>1000000000</v>
@@ -6743,7 +6743,7 @@
         <v>104800</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D98" s="27">
         <v>104800001</v>
@@ -6752,10 +6752,10 @@
         <v>1</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G98" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H98" s="17">
         <v>10000000</v>
@@ -6773,7 +6773,7 @@
         <v>100</v>
       </c>
       <c r="M98" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N98" s="24">
         <v>0</v>
@@ -6793,7 +6793,7 @@
         <v>104800</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D99" s="27">
         <v>104800001</v>
@@ -6802,10 +6802,10 @@
         <v>2</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G99" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H99" s="17">
         <v>100000000</v>
@@ -6823,7 +6823,7 @@
         <v>100</v>
       </c>
       <c r="M99" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N99" s="24">
         <v>0</v>
@@ -6843,7 +6843,7 @@
         <v>104800</v>
       </c>
       <c r="C100" s="23" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D100" s="27">
         <v>104800001</v>
@@ -6852,10 +6852,10 @@
         <v>3</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G100" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H100" s="31">
         <v>1000000000</v>
@@ -6873,7 +6873,7 @@
         <v>100</v>
       </c>
       <c r="M100" s="26" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="N100" s="24">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>105501</v>
       </c>
       <c r="C101" s="23" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D101" s="35">
         <v>105501001</v>
@@ -6902,10 +6902,10 @@
         <v>1</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G101" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H101" s="31">
         <v>10000000</v>
@@ -6943,7 +6943,7 @@
         <v>105501</v>
       </c>
       <c r="C102" s="23" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D102" s="35">
         <v>105501001</v>
@@ -6952,10 +6952,10 @@
         <v>2</v>
       </c>
       <c r="F102" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G102" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H102" s="31">
         <v>100000000</v>
@@ -6993,7 +6993,7 @@
         <v>105501</v>
       </c>
       <c r="C103" s="23" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D103" s="35">
         <v>105501001</v>
@@ -7002,10 +7002,10 @@
         <v>3</v>
       </c>
       <c r="F103" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G103" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H103" s="31">
         <v>1000000000</v>
@@ -7043,7 +7043,7 @@
         <v>105502</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D104" s="35">
         <v>105502001</v>
@@ -7052,10 +7052,10 @@
         <v>1</v>
       </c>
       <c r="F104" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G104" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H104" s="31">
         <v>10000000</v>
@@ -7093,7 +7093,7 @@
         <v>105502</v>
       </c>
       <c r="C105" s="23" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D105" s="35">
         <v>105502001</v>
@@ -7102,10 +7102,10 @@
         <v>2</v>
       </c>
       <c r="F105" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G105" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H105" s="31">
         <v>100000000</v>
@@ -7143,7 +7143,7 @@
         <v>105502</v>
       </c>
       <c r="C106" s="23" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D106" s="35">
         <v>105502001</v>
@@ -7152,10 +7152,10 @@
         <v>3</v>
       </c>
       <c r="F106" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G106" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H106" s="31">
         <v>1000000000</v>
@@ -7193,7 +7193,7 @@
         <v>105300</v>
       </c>
       <c r="C107" s="23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D107" s="35">
         <v>105300001</v>
@@ -7202,10 +7202,10 @@
         <v>1</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G107" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H107" s="31">
         <v>10000000</v>
@@ -7243,7 +7243,7 @@
         <v>105300</v>
       </c>
       <c r="C108" s="23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D108" s="35">
         <v>105300001</v>
@@ -7252,10 +7252,10 @@
         <v>2</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G108" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H108" s="31">
         <v>100000000</v>
@@ -7293,7 +7293,7 @@
         <v>105300</v>
       </c>
       <c r="C109" s="23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D109" s="35">
         <v>105300001</v>
@@ -7302,10 +7302,10 @@
         <v>3</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G109" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H109" s="31">
         <v>1000000000</v>
@@ -7376,7 +7376,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O110" s="44"/>
       <c r="P110" s="44"/>
@@ -7426,7 +7426,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O111" s="44"/>
       <c r="P111" s="44"/>
@@ -7476,7 +7476,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O112" s="44"/>
       <c r="P112" s="44"/>
@@ -7526,7 +7526,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O113" s="44"/>
       <c r="P113" s="44"/>
@@ -7576,7 +7576,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O114" s="44"/>
       <c r="P114" s="44"/>
@@ -7626,7 +7626,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O115" s="44"/>
       <c r="P115" s="44"/>
@@ -7652,10 +7652,10 @@
         <v>10</v>
       </c>
       <c r="F116" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G116" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G116" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H116" s="53">
         <v>0</v>
@@ -7676,7 +7676,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O116" s="44"/>
       <c r="P116" s="44"/>
@@ -7702,10 +7702,10 @@
         <v>11</v>
       </c>
       <c r="F117" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G117" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G117" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H117" s="53">
         <v>0</v>
@@ -7726,7 +7726,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O117" s="44"/>
       <c r="P117" s="44"/>
@@ -7752,10 +7752,10 @@
         <v>12</v>
       </c>
       <c r="F118" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G118" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G118" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H118" s="57">
         <v>0</v>
@@ -7776,7 +7776,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O118" s="44"/>
       <c r="P118" s="44"/>
@@ -7793,7 +7793,7 @@
         <v>101200</v>
       </c>
       <c r="C119" s="52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D119" s="60">
         <v>101200001</v>
@@ -7826,7 +7826,7 @@
         <v>37</v>
       </c>
       <c r="N119" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O119" s="56"/>
       <c r="P119" s="56"/>
@@ -7843,7 +7843,7 @@
         <v>101200</v>
       </c>
       <c r="C120" s="52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D120" s="60">
         <v>101200001</v>
@@ -7876,7 +7876,7 @@
         <v>40</v>
       </c>
       <c r="N120" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O120" s="56"/>
       <c r="P120" s="56"/>
@@ -7893,7 +7893,7 @@
         <v>101200</v>
       </c>
       <c r="C121" s="52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D121" s="60">
         <v>101200001</v>
@@ -7926,7 +7926,7 @@
         <v>43</v>
       </c>
       <c r="N121" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O121" s="56"/>
       <c r="P121" s="56"/>
@@ -7943,7 +7943,7 @@
         <v>101400</v>
       </c>
       <c r="C122" s="50" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D122" s="51">
         <v>101400001</v>
@@ -7976,7 +7976,7 @@
         <v>37</v>
       </c>
       <c r="N122" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O122" s="44"/>
       <c r="P122" s="44"/>
@@ -7993,7 +7993,7 @@
         <v>101400</v>
       </c>
       <c r="C123" s="50" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D123" s="51">
         <v>101400001</v>
@@ -8026,7 +8026,7 @@
         <v>40</v>
       </c>
       <c r="N123" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O123" s="44"/>
       <c r="P123" s="44"/>
@@ -8043,7 +8043,7 @@
         <v>101400</v>
       </c>
       <c r="C124" s="50" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D124" s="51">
         <v>101400001</v>
@@ -8076,7 +8076,7 @@
         <v>43</v>
       </c>
       <c r="N124" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O124" s="44"/>
       <c r="P124" s="44"/>
@@ -8093,7 +8093,7 @@
         <v>101700</v>
       </c>
       <c r="C125" s="50" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D125" s="51">
         <v>101700001</v>
@@ -8102,10 +8102,10 @@
         <v>10</v>
       </c>
       <c r="F125" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G125" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G125" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H125" s="53">
         <v>0</v>
@@ -8126,7 +8126,7 @@
         <v>37</v>
       </c>
       <c r="N125" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O125" s="44"/>
       <c r="P125" s="44"/>
@@ -8143,7 +8143,7 @@
         <v>101700</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D126" s="51">
         <v>101700001</v>
@@ -8152,10 +8152,10 @@
         <v>11</v>
       </c>
       <c r="F126" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G126" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G126" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H126" s="53">
         <v>0</v>
@@ -8176,7 +8176,7 @@
         <v>40</v>
       </c>
       <c r="N126" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O126" s="44"/>
       <c r="P126" s="44"/>
@@ -8193,7 +8193,7 @@
         <v>101700</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D127" s="51">
         <v>101700001</v>
@@ -8202,10 +8202,10 @@
         <v>12</v>
       </c>
       <c r="F127" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G127" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G127" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H127" s="57">
         <v>0</v>
@@ -8226,7 +8226,7 @@
         <v>43</v>
       </c>
       <c r="N127" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O127" s="44"/>
       <c r="P127" s="44"/>
@@ -8243,7 +8243,7 @@
         <v>102100</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D128" s="51">
         <v>102100001</v>
@@ -8252,10 +8252,10 @@
         <v>10</v>
       </c>
       <c r="F128" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G128" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G128" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H128" s="53">
         <v>0</v>
@@ -8276,7 +8276,7 @@
         <v>37</v>
       </c>
       <c r="N128" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O128" s="44"/>
       <c r="P128" s="44"/>
@@ -8293,7 +8293,7 @@
         <v>102100</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D129" s="51">
         <v>102100001</v>
@@ -8302,10 +8302,10 @@
         <v>11</v>
       </c>
       <c r="F129" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G129" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G129" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H129" s="53">
         <v>0</v>
@@ -8326,7 +8326,7 @@
         <v>40</v>
       </c>
       <c r="N129" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O129" s="44"/>
       <c r="P129" s="44"/>
@@ -8343,7 +8343,7 @@
         <v>102100</v>
       </c>
       <c r="C130" s="50" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D130" s="51">
         <v>102100001</v>
@@ -8352,10 +8352,10 @@
         <v>12</v>
       </c>
       <c r="F130" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G130" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G130" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H130" s="57">
         <v>0</v>
@@ -8376,7 +8376,7 @@
         <v>43</v>
       </c>
       <c r="N130" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O130" s="44"/>
       <c r="P130" s="44"/>
@@ -8393,7 +8393,7 @@
         <v>102200</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D131" s="51">
         <v>102200001</v>
@@ -8402,10 +8402,10 @@
         <v>10</v>
       </c>
       <c r="F131" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G131" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G131" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H131" s="53">
         <v>0</v>
@@ -8426,7 +8426,7 @@
         <v>37</v>
       </c>
       <c r="N131" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O131" s="44"/>
       <c r="P131" s="44"/>
@@ -8443,7 +8443,7 @@
         <v>102200</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D132" s="51">
         <v>102200001</v>
@@ -8452,10 +8452,10 @@
         <v>11</v>
       </c>
       <c r="F132" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G132" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G132" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H132" s="53">
         <v>0</v>
@@ -8476,7 +8476,7 @@
         <v>40</v>
       </c>
       <c r="N132" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O132" s="44"/>
       <c r="P132" s="44"/>
@@ -8493,7 +8493,7 @@
         <v>102200</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D133" s="51">
         <v>102200001</v>
@@ -8502,10 +8502,10 @@
         <v>12</v>
       </c>
       <c r="F133" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G133" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G133" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H133" s="57">
         <v>0</v>
@@ -8526,7 +8526,7 @@
         <v>43</v>
       </c>
       <c r="N133" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O133" s="44"/>
       <c r="P133" s="44"/>
@@ -8543,7 +8543,7 @@
         <v>102400</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D134" s="51">
         <v>102400026</v>
@@ -8576,7 +8576,7 @@
         <v>37</v>
       </c>
       <c r="N134" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O134" s="44"/>
       <c r="P134" s="44"/>
@@ -8593,7 +8593,7 @@
         <v>102400</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D135" s="51">
         <v>102400026</v>
@@ -8626,7 +8626,7 @@
         <v>40</v>
       </c>
       <c r="N135" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O135" s="44"/>
       <c r="P135" s="44"/>
@@ -8643,7 +8643,7 @@
         <v>102400</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D136" s="51">
         <v>102400026</v>
@@ -8676,7 +8676,7 @@
         <v>43</v>
       </c>
       <c r="N136" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O136" s="44"/>
       <c r="P136" s="44"/>
@@ -8693,7 +8693,7 @@
         <v>101800</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D137" s="51">
         <v>101800001</v>
@@ -8702,10 +8702,10 @@
         <v>10</v>
       </c>
       <c r="F137" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G137" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G137" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H137" s="57">
         <v>0</v>
@@ -8726,7 +8726,7 @@
         <v>37</v>
       </c>
       <c r="N137" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O137" s="44"/>
       <c r="P137" s="44"/>
@@ -8743,7 +8743,7 @@
         <v>101800</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D138" s="51">
         <v>101800001</v>
@@ -8752,10 +8752,10 @@
         <v>11</v>
       </c>
       <c r="F138" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G138" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G138" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H138" s="57">
         <v>0</v>
@@ -8776,7 +8776,7 @@
         <v>40</v>
       </c>
       <c r="N138" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O138" s="44"/>
       <c r="P138" s="44"/>
@@ -8793,7 +8793,7 @@
         <v>101800</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D139" s="51">
         <v>101800001</v>
@@ -8802,10 +8802,10 @@
         <v>12</v>
       </c>
       <c r="F139" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G139" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G139" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H139" s="57">
         <v>0</v>
@@ -8826,7 +8826,7 @@
         <v>43</v>
       </c>
       <c r="N139" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O139" s="44"/>
       <c r="P139" s="44"/>
@@ -8843,7 +8843,7 @@
         <v>102500</v>
       </c>
       <c r="C140" s="50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D140" s="51">
         <v>102500001</v>
@@ -8852,10 +8852,10 @@
         <v>10</v>
       </c>
       <c r="F140" s="24" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="G140" s="25" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H140" s="57">
         <v>0</v>
@@ -8876,7 +8876,7 @@
         <v>37</v>
       </c>
       <c r="N140" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O140" s="44"/>
       <c r="P140" s="44"/>
@@ -8893,7 +8893,7 @@
         <v>102500</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D141" s="51">
         <v>102500001</v>
@@ -8902,10 +8902,10 @@
         <v>11</v>
       </c>
       <c r="F141" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G141" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H141" s="57">
         <v>0</v>
@@ -8926,7 +8926,7 @@
         <v>40</v>
       </c>
       <c r="N141" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O141" s="44"/>
       <c r="P141" s="44"/>
@@ -8943,7 +8943,7 @@
         <v>102500</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D142" s="51">
         <v>102500001</v>
@@ -8952,10 +8952,10 @@
         <v>12</v>
       </c>
       <c r="F142" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G142" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H142" s="57">
         <v>0</v>
@@ -8976,7 +8976,7 @@
         <v>43</v>
       </c>
       <c r="N142" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O142" s="44"/>
       <c r="P142" s="44"/>
@@ -8993,7 +8993,7 @@
         <v>102300</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D143" s="51">
         <v>102300001</v>
@@ -9002,10 +9002,10 @@
         <v>10</v>
       </c>
       <c r="F143" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G143" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G143" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H143" s="57">
         <v>0</v>
@@ -9026,7 +9026,7 @@
         <v>37</v>
       </c>
       <c r="N143" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O143" s="44"/>
       <c r="P143" s="44"/>
@@ -9043,7 +9043,7 @@
         <v>102300</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D144" s="51">
         <v>102300001</v>
@@ -9052,10 +9052,10 @@
         <v>11</v>
       </c>
       <c r="F144" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G144" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G144" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H144" s="57">
         <v>0</v>
@@ -9076,7 +9076,7 @@
         <v>40</v>
       </c>
       <c r="N144" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O144" s="44"/>
       <c r="P144" s="44"/>
@@ -9093,7 +9093,7 @@
         <v>102300</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D145" s="51">
         <v>102300001</v>
@@ -9102,10 +9102,10 @@
         <v>12</v>
       </c>
       <c r="F145" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G145" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G145" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H145" s="57">
         <v>0</v>
@@ -9126,7 +9126,7 @@
         <v>43</v>
       </c>
       <c r="N145" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O145" s="44"/>
       <c r="P145" s="44"/>
@@ -9143,7 +9143,7 @@
         <v>103400</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D146" s="51">
         <v>103000001</v>
@@ -9152,10 +9152,10 @@
         <v>10</v>
       </c>
       <c r="F146" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G146" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H146" s="57">
         <v>0</v>
@@ -9176,7 +9176,7 @@
         <v>37</v>
       </c>
       <c r="N146" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O146" s="44"/>
       <c r="P146" s="44"/>
@@ -9193,7 +9193,7 @@
         <v>103400</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D147" s="51">
         <v>103000001</v>
@@ -9202,10 +9202,10 @@
         <v>11</v>
       </c>
       <c r="F147" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G147" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H147" s="57">
         <v>0</v>
@@ -9226,7 +9226,7 @@
         <v>40</v>
       </c>
       <c r="N147" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O147" s="44"/>
       <c r="P147" s="44"/>
@@ -9243,7 +9243,7 @@
         <v>103400</v>
       </c>
       <c r="C148" s="50" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D148" s="51">
         <v>103000001</v>
@@ -9252,10 +9252,10 @@
         <v>12</v>
       </c>
       <c r="F148" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G148" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H148" s="57">
         <v>0</v>
@@ -9276,7 +9276,7 @@
         <v>43</v>
       </c>
       <c r="N148" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O148" s="44"/>
       <c r="P148" s="44"/>
@@ -9293,7 +9293,7 @@
         <v>103500</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D149" s="51">
         <v>102900001</v>
@@ -9326,7 +9326,7 @@
         <v>37</v>
       </c>
       <c r="N149" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O149" s="44"/>
       <c r="P149" s="44"/>
@@ -9343,7 +9343,7 @@
         <v>103500</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D150" s="51">
         <v>102900001</v>
@@ -9376,7 +9376,7 @@
         <v>40</v>
       </c>
       <c r="N150" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O150" s="44"/>
       <c r="P150" s="44"/>
@@ -9393,7 +9393,7 @@
         <v>103500</v>
       </c>
       <c r="C151" s="50" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D151" s="51">
         <v>102900001</v>
@@ -9426,7 +9426,7 @@
         <v>43</v>
       </c>
       <c r="N151" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O151" s="44"/>
       <c r="P151" s="44"/>
@@ -9443,7 +9443,7 @@
         <v>103501</v>
       </c>
       <c r="C152" s="50" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D152" s="51">
         <v>103501001</v>
@@ -9476,7 +9476,7 @@
         <v>37</v>
       </c>
       <c r="N152" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O152" s="44"/>
       <c r="P152" s="44"/>
@@ -9493,7 +9493,7 @@
         <v>103501</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D153" s="51">
         <v>103501001</v>
@@ -9526,7 +9526,7 @@
         <v>40</v>
       </c>
       <c r="N153" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O153" s="44"/>
       <c r="P153" s="44"/>
@@ -9543,7 +9543,7 @@
         <v>103501</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D154" s="51">
         <v>103501001</v>
@@ -9576,7 +9576,7 @@
         <v>43</v>
       </c>
       <c r="N154" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O154" s="44"/>
       <c r="P154" s="44"/>
@@ -9593,7 +9593,7 @@
         <v>103600</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D155" s="51">
         <v>103600001</v>
@@ -9602,10 +9602,10 @@
         <v>10</v>
       </c>
       <c r="F155" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G155" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H155" s="53">
         <v>0</v>
@@ -9626,7 +9626,7 @@
         <v>37</v>
       </c>
       <c r="N155" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O155" s="44"/>
       <c r="P155" s="44"/>
@@ -9643,7 +9643,7 @@
         <v>103600</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D156" s="51">
         <v>103600001</v>
@@ -9652,10 +9652,10 @@
         <v>11</v>
       </c>
       <c r="F156" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G156" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H156" s="53">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>40</v>
       </c>
       <c r="N156" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O156" s="44"/>
       <c r="P156" s="44"/>
@@ -9693,7 +9693,7 @@
         <v>103600</v>
       </c>
       <c r="C157" s="50" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D157" s="51">
         <v>103600001</v>
@@ -9702,10 +9702,10 @@
         <v>12</v>
       </c>
       <c r="F157" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G157" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H157" s="57">
         <v>0</v>
@@ -9726,7 +9726,7 @@
         <v>43</v>
       </c>
       <c r="N157" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O157" s="44"/>
       <c r="P157" s="44"/>
@@ -9743,7 +9743,7 @@
         <v>102800</v>
       </c>
       <c r="C158" s="50" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D158" s="51">
         <v>102800001</v>
@@ -9752,10 +9752,10 @@
         <v>10</v>
       </c>
       <c r="F158" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G158" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G158" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H158" s="57">
         <v>0</v>
@@ -9776,7 +9776,7 @@
         <v>37</v>
       </c>
       <c r="N158" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O158" s="44"/>
       <c r="P158" s="44"/>
@@ -9793,7 +9793,7 @@
         <v>102800</v>
       </c>
       <c r="C159" s="50" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D159" s="51">
         <v>102800001</v>
@@ -9802,10 +9802,10 @@
         <v>11</v>
       </c>
       <c r="F159" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G159" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G159" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H159" s="57">
         <v>0</v>
@@ -9826,7 +9826,7 @@
         <v>40</v>
       </c>
       <c r="N159" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O159" s="44"/>
       <c r="P159" s="44"/>
@@ -9843,7 +9843,7 @@
         <v>102800</v>
       </c>
       <c r="C160" s="50" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D160" s="51">
         <v>102800001</v>
@@ -9852,10 +9852,10 @@
         <v>12</v>
       </c>
       <c r="F160" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G160" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G160" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H160" s="57">
         <v>0</v>
@@ -9876,7 +9876,7 @@
         <v>43</v>
       </c>
       <c r="N160" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O160" s="44"/>
       <c r="P160" s="44"/>
@@ -9893,7 +9893,7 @@
         <v>102000</v>
       </c>
       <c r="C161" s="50" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D161" s="51">
         <v>102000001</v>
@@ -9902,10 +9902,10 @@
         <v>10</v>
       </c>
       <c r="F161" s="24" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="G161" s="25" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="H161" s="57">
         <v>0</v>
@@ -9926,7 +9926,7 @@
         <v>37</v>
       </c>
       <c r="N161" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O161" s="44"/>
       <c r="P161" s="44"/>
@@ -9943,7 +9943,7 @@
         <v>102000</v>
       </c>
       <c r="C162" s="50" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D162" s="51">
         <v>102000001</v>
@@ -9952,10 +9952,10 @@
         <v>11</v>
       </c>
       <c r="F162" s="24" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G162" s="25" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H162" s="57">
         <v>0</v>
@@ -9976,7 +9976,7 @@
         <v>40</v>
       </c>
       <c r="N162" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O162" s="44"/>
       <c r="P162" s="44"/>
@@ -9993,7 +9993,7 @@
         <v>102000</v>
       </c>
       <c r="C163" s="50" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D163" s="51">
         <v>102000001</v>
@@ -10002,10 +10002,10 @@
         <v>12</v>
       </c>
       <c r="F163" s="24" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G163" s="25" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H163" s="57">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>43</v>
       </c>
       <c r="N163" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O163" s="44"/>
       <c r="P163" s="44"/>
@@ -10043,7 +10043,7 @@
         <v>103401</v>
       </c>
       <c r="C164" s="50" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D164" s="51">
         <v>103400001</v>
@@ -10052,10 +10052,10 @@
         <v>10</v>
       </c>
       <c r="F164" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G164" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H164" s="57">
         <v>0</v>
@@ -10076,7 +10076,7 @@
         <v>37</v>
       </c>
       <c r="N164" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O164" s="44"/>
       <c r="P164" s="44"/>
@@ -10093,7 +10093,7 @@
         <v>103401</v>
       </c>
       <c r="C165" s="50" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D165" s="51">
         <v>103400001</v>
@@ -10102,10 +10102,10 @@
         <v>11</v>
       </c>
       <c r="F165" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G165" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H165" s="57">
         <v>0</v>
@@ -10126,7 +10126,7 @@
         <v>40</v>
       </c>
       <c r="N165" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O165" s="44"/>
       <c r="P165" s="44"/>
@@ -10143,7 +10143,7 @@
         <v>103401</v>
       </c>
       <c r="C166" s="50" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D166" s="51">
         <v>103400001</v>
@@ -10152,10 +10152,10 @@
         <v>12</v>
       </c>
       <c r="F166" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G166" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H166" s="57">
         <v>0</v>
@@ -10176,7 +10176,7 @@
         <v>43</v>
       </c>
       <c r="N166" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O166" s="44"/>
       <c r="P166" s="44"/>
@@ -10193,7 +10193,7 @@
         <v>103800</v>
       </c>
       <c r="C167" s="50" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D167" s="51">
         <v>103800001</v>
@@ -10202,10 +10202,10 @@
         <v>11</v>
       </c>
       <c r="F167" s="24" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G167" s="25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H167" s="57">
         <v>0</v>
@@ -10226,7 +10226,7 @@
         <v>37</v>
       </c>
       <c r="N167" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O167" s="44"/>
       <c r="P167" s="44"/>
@@ -10243,7 +10243,7 @@
         <v>103800</v>
       </c>
       <c r="C168" s="50" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D168" s="51">
         <v>103800001</v>
@@ -10252,10 +10252,10 @@
         <v>12</v>
       </c>
       <c r="F168" s="24" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G168" s="25" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H168" s="57">
         <v>0</v>
@@ -10276,7 +10276,7 @@
         <v>40</v>
       </c>
       <c r="N168" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O168" s="44"/>
       <c r="P168" s="44"/>
@@ -10293,7 +10293,7 @@
         <v>103800</v>
       </c>
       <c r="C169" s="50" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D169" s="51">
         <v>103800001</v>
@@ -10302,10 +10302,10 @@
         <v>13</v>
       </c>
       <c r="F169" s="24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G169" s="25" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H169" s="57">
         <v>0</v>
@@ -10326,7 +10326,7 @@
         <v>43</v>
       </c>
       <c r="N169" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O169" s="44"/>
       <c r="P169" s="44"/>
@@ -10343,7 +10343,7 @@
         <v>102700</v>
       </c>
       <c r="C170" s="50" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D170" s="51">
         <v>102700001</v>
@@ -10352,10 +10352,10 @@
         <v>11</v>
       </c>
       <c r="F170" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G170" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G170" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H170" s="57">
         <v>0</v>
@@ -10376,7 +10376,7 @@
         <v>37</v>
       </c>
       <c r="N170" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O170" s="44"/>
       <c r="P170" s="44"/>
@@ -10393,7 +10393,7 @@
         <v>102700</v>
       </c>
       <c r="C171" s="50" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D171" s="51">
         <v>102700001</v>
@@ -10402,10 +10402,10 @@
         <v>12</v>
       </c>
       <c r="F171" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G171" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G171" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H171" s="57">
         <v>0</v>
@@ -10426,7 +10426,7 @@
         <v>40</v>
       </c>
       <c r="N171" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O171" s="44"/>
       <c r="P171" s="44"/>
@@ -10443,7 +10443,7 @@
         <v>102700</v>
       </c>
       <c r="C172" s="50" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D172" s="51">
         <v>102700001</v>
@@ -10452,10 +10452,10 @@
         <v>13</v>
       </c>
       <c r="F172" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G172" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G172" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H172" s="57">
         <v>0</v>
@@ -10476,7 +10476,7 @@
         <v>43</v>
       </c>
       <c r="N172" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O172" s="44"/>
       <c r="P172" s="44"/>
@@ -10493,7 +10493,7 @@
         <v>103700</v>
       </c>
       <c r="C173" s="50" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D173" s="51">
         <v>103700001</v>
@@ -10526,7 +10526,7 @@
         <v>37</v>
       </c>
       <c r="N173" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O173" s="44"/>
       <c r="P173" s="44"/>
@@ -10543,7 +10543,7 @@
         <v>103700</v>
       </c>
       <c r="C174" s="50" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D174" s="51">
         <v>103700001</v>
@@ -10576,7 +10576,7 @@
         <v>40</v>
       </c>
       <c r="N174" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O174" s="44"/>
       <c r="P174" s="44"/>
@@ -10593,7 +10593,7 @@
         <v>103700</v>
       </c>
       <c r="C175" s="50" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D175" s="51">
         <v>103100001</v>
@@ -10626,7 +10626,7 @@
         <v>43</v>
       </c>
       <c r="N175" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O175" s="44"/>
       <c r="P175" s="44"/>
@@ -10643,7 +10643,7 @@
         <v>103100</v>
       </c>
       <c r="C176" s="50" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D176" s="51">
         <v>103100001</v>
@@ -10652,10 +10652,10 @@
         <v>11</v>
       </c>
       <c r="F176" s="24" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="G176" s="25" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H176" s="53">
         <v>0</v>
@@ -10676,7 +10676,7 @@
         <v>37</v>
       </c>
       <c r="N176" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O176" s="44"/>
       <c r="P176" s="44"/>
@@ -10693,7 +10693,7 @@
         <v>103100</v>
       </c>
       <c r="C177" s="50" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D177" s="51">
         <v>103100001</v>
@@ -10702,10 +10702,10 @@
         <v>12</v>
       </c>
       <c r="F177" s="24" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G177" s="25" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H177" s="53">
         <v>0</v>
@@ -10726,7 +10726,7 @@
         <v>40</v>
       </c>
       <c r="N177" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O177" s="44"/>
       <c r="P177" s="44"/>
@@ -10743,7 +10743,7 @@
         <v>103100</v>
       </c>
       <c r="C178" s="50" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D178" s="51">
         <v>103100001</v>
@@ -10752,10 +10752,10 @@
         <v>13</v>
       </c>
       <c r="F178" s="24" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G178" s="25" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H178" s="57">
         <v>0</v>
@@ -10776,7 +10776,7 @@
         <v>43</v>
       </c>
       <c r="N178" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O178" s="44"/>
       <c r="P178" s="44"/>
@@ -10793,7 +10793,7 @@
         <v>104000</v>
       </c>
       <c r="C179" s="50" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D179" s="51">
         <v>104000001</v>
@@ -10802,10 +10802,10 @@
         <v>11</v>
       </c>
       <c r="F179" s="24" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G179" s="25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H179" s="57">
         <v>0</v>
@@ -10826,7 +10826,7 @@
         <v>37</v>
       </c>
       <c r="N179" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O179" s="44"/>
       <c r="P179" s="44"/>
@@ -10843,7 +10843,7 @@
         <v>104000</v>
       </c>
       <c r="C180" s="50" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D180" s="51">
         <v>104000001</v>
@@ -10852,10 +10852,10 @@
         <v>12</v>
       </c>
       <c r="F180" s="24" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G180" s="25" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H180" s="57">
         <v>0</v>
@@ -10876,7 +10876,7 @@
         <v>40</v>
       </c>
       <c r="N180" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O180" s="44"/>
       <c r="P180" s="44"/>
@@ -10893,7 +10893,7 @@
         <v>104000</v>
       </c>
       <c r="C181" s="50" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D181" s="51">
         <v>104000001</v>
@@ -10902,10 +10902,10 @@
         <v>13</v>
       </c>
       <c r="F181" s="24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G181" s="25" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H181" s="57">
         <v>0</v>
@@ -10926,7 +10926,7 @@
         <v>43</v>
       </c>
       <c r="N181" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O181" s="44"/>
       <c r="P181" s="44"/>
@@ -10943,7 +10943,7 @@
         <v>103900</v>
       </c>
       <c r="C182" s="50" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D182" s="51">
         <v>103900001</v>
@@ -10952,10 +10952,10 @@
         <v>11</v>
       </c>
       <c r="F182" s="24" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="G182" s="25" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H182" s="57">
         <v>0</v>
@@ -10976,7 +10976,7 @@
         <v>37</v>
       </c>
       <c r="N182" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O182" s="44"/>
       <c r="P182" s="44"/>
@@ -10993,7 +10993,7 @@
         <v>103900</v>
       </c>
       <c r="C183" s="50" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D183" s="51">
         <v>103900001</v>
@@ -11002,10 +11002,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="24" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G183" s="25" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H183" s="57">
         <v>0</v>
@@ -11026,7 +11026,7 @@
         <v>40</v>
       </c>
       <c r="N183" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O183" s="44"/>
       <c r="P183" s="44"/>
@@ -11043,7 +11043,7 @@
         <v>103900</v>
       </c>
       <c r="C184" s="50" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D184" s="51">
         <v>103900001</v>
@@ -11052,10 +11052,10 @@
         <v>13</v>
       </c>
       <c r="F184" s="24" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G184" s="25" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H184" s="57">
         <v>0</v>
@@ -11076,7 +11076,7 @@
         <v>43</v>
       </c>
       <c r="N184" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O184" s="44"/>
       <c r="P184" s="44"/>
@@ -11093,7 +11093,7 @@
         <v>101600</v>
       </c>
       <c r="C185" s="50" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D185" s="51">
         <v>101600001</v>
@@ -11102,10 +11102,10 @@
         <v>11</v>
       </c>
       <c r="F185" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G185" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G185" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H185" s="57">
         <v>0</v>
@@ -11126,7 +11126,7 @@
         <v>37</v>
       </c>
       <c r="N185" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O185" s="44"/>
       <c r="P185" s="44"/>
@@ -11143,7 +11143,7 @@
         <v>101600</v>
       </c>
       <c r="C186" s="50" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D186" s="51">
         <v>101600001</v>
@@ -11152,10 +11152,10 @@
         <v>12</v>
       </c>
       <c r="F186" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G186" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G186" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H186" s="57">
         <v>0</v>
@@ -11176,7 +11176,7 @@
         <v>40</v>
       </c>
       <c r="N186" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O186" s="44"/>
       <c r="P186" s="44"/>
@@ -11193,7 +11193,7 @@
         <v>101600</v>
       </c>
       <c r="C187" s="50" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D187" s="51">
         <v>101600001</v>
@@ -11202,10 +11202,10 @@
         <v>13</v>
       </c>
       <c r="F187" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G187" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G187" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H187" s="57">
         <v>0</v>
@@ -11226,7 +11226,7 @@
         <v>43</v>
       </c>
       <c r="N187" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O187" s="44"/>
       <c r="P187" s="44"/>
@@ -11243,7 +11243,7 @@
         <v>101500</v>
       </c>
       <c r="C188" s="50" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D188" s="51">
         <v>101500001</v>
@@ -11252,10 +11252,10 @@
         <v>11</v>
       </c>
       <c r="F188" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G188" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G188" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H188" s="57">
         <v>0</v>
@@ -11276,7 +11276,7 @@
         <v>37</v>
       </c>
       <c r="N188" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O188" s="44"/>
       <c r="P188" s="44"/>
@@ -11293,7 +11293,7 @@
         <v>101500</v>
       </c>
       <c r="C189" s="50" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D189" s="51">
         <v>101500001</v>
@@ -11302,10 +11302,10 @@
         <v>12</v>
       </c>
       <c r="F189" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G189" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G189" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H189" s="57">
         <v>0</v>
@@ -11326,7 +11326,7 @@
         <v>40</v>
       </c>
       <c r="N189" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O189" s="44"/>
       <c r="P189" s="44"/>
@@ -11343,7 +11343,7 @@
         <v>101500</v>
       </c>
       <c r="C190" s="50" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D190" s="51">
         <v>101500001</v>
@@ -11352,10 +11352,10 @@
         <v>13</v>
       </c>
       <c r="F190" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G190" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G190" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H190" s="57">
         <v>0</v>
@@ -11376,7 +11376,7 @@
         <v>43</v>
       </c>
       <c r="N190" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O190" s="44"/>
       <c r="P190" s="44"/>
@@ -11393,7 +11393,7 @@
         <v>102600</v>
       </c>
       <c r="C191" s="50" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D191" s="51">
         <v>102600001</v>
@@ -11402,10 +11402,10 @@
         <v>11</v>
       </c>
       <c r="F191" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G191" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G191" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H191" s="57">
         <v>0</v>
@@ -11426,7 +11426,7 @@
         <v>37</v>
       </c>
       <c r="N191" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O191" s="44"/>
       <c r="P191" s="44"/>
@@ -11443,7 +11443,7 @@
         <v>102600</v>
       </c>
       <c r="C192" s="50" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D192" s="51">
         <v>102600001</v>
@@ -11452,10 +11452,10 @@
         <v>12</v>
       </c>
       <c r="F192" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G192" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G192" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H192" s="57">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>40</v>
       </c>
       <c r="N192" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O192" s="44"/>
       <c r="P192" s="44"/>
@@ -11493,7 +11493,7 @@
         <v>102600</v>
       </c>
       <c r="C193" s="50" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D193" s="51">
         <v>102600001</v>
@@ -11502,10 +11502,10 @@
         <v>13</v>
       </c>
       <c r="F193" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G193" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G193" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H193" s="57">
         <v>0</v>
@@ -11526,7 +11526,7 @@
         <v>43</v>
       </c>
       <c r="N193" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O193" s="44"/>
       <c r="P193" s="44"/>
@@ -11543,7 +11543,7 @@
         <v>105000</v>
       </c>
       <c r="C194" s="50" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D194" s="51">
         <v>105000001</v>
@@ -11552,10 +11552,10 @@
         <v>11</v>
       </c>
       <c r="F194" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G194" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G194" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H194" s="57">
         <v>0</v>
@@ -11576,7 +11576,7 @@
         <v>37</v>
       </c>
       <c r="N194" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O194" s="44"/>
       <c r="P194" s="44"/>
@@ -11593,7 +11593,7 @@
         <v>105000</v>
       </c>
       <c r="C195" s="50" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D195" s="51">
         <v>105000001</v>
@@ -11602,10 +11602,10 @@
         <v>12</v>
       </c>
       <c r="F195" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G195" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G195" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H195" s="57">
         <v>0</v>
@@ -11626,7 +11626,7 @@
         <v>40</v>
       </c>
       <c r="N195" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O195" s="44"/>
       <c r="P195" s="44"/>
@@ -11643,7 +11643,7 @@
         <v>105000</v>
       </c>
       <c r="C196" s="50" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D196" s="51">
         <v>105000001</v>
@@ -11652,10 +11652,10 @@
         <v>13</v>
       </c>
       <c r="F196" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G196" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G196" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H196" s="57">
         <v>0</v>
@@ -11676,7 +11676,7 @@
         <v>43</v>
       </c>
       <c r="N196" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O196" s="44"/>
       <c r="P196" s="44"/>
@@ -11693,7 +11693,7 @@
         <v>105100</v>
       </c>
       <c r="C197" s="50" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D197" s="51">
         <v>105100001</v>
@@ -11726,7 +11726,7 @@
         <v>37</v>
       </c>
       <c r="N197" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O197" s="44"/>
       <c r="P197" s="44"/>
@@ -11743,7 +11743,7 @@
         <v>105100</v>
       </c>
       <c r="C198" s="50" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D198" s="51">
         <v>105100001</v>
@@ -11776,7 +11776,7 @@
         <v>40</v>
       </c>
       <c r="N198" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O198" s="44"/>
       <c r="P198" s="44"/>
@@ -11793,7 +11793,7 @@
         <v>105100</v>
       </c>
       <c r="C199" s="50" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D199" s="51">
         <v>105100001</v>
@@ -11826,7 +11826,7 @@
         <v>43</v>
       </c>
       <c r="N199" s="56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O199" s="44"/>
       <c r="P199" s="44"/>
@@ -11843,7 +11843,7 @@
         <v>105400</v>
       </c>
       <c r="C200" s="50" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D200" s="51">
         <v>105400001</v>
@@ -11852,10 +11852,10 @@
         <v>11</v>
       </c>
       <c r="F200" s="24" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G200" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H200" s="57">
         <v>0</v>
@@ -11873,10 +11873,10 @@
         <v>0</v>
       </c>
       <c r="M200" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N200" s="56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O200" s="44"/>
       <c r="P200" s="44"/>
@@ -11893,7 +11893,7 @@
         <v>105400</v>
       </c>
       <c r="C201" s="50" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D201" s="51">
         <v>105400001</v>
@@ -11902,10 +11902,10 @@
         <v>12</v>
       </c>
       <c r="F201" s="24" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G201" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H201" s="57">
         <v>0</v>
@@ -11923,10 +11923,10 @@
         <v>0</v>
       </c>
       <c r="M201" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N201" s="56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O201" s="44"/>
       <c r="P201" s="44"/>
@@ -11943,7 +11943,7 @@
         <v>105400</v>
       </c>
       <c r="C202" s="50" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D202" s="51">
         <v>105400001</v>
@@ -11952,10 +11952,10 @@
         <v>13</v>
       </c>
       <c r="F202" s="24" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G202" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H202" s="57">
         <v>0</v>
@@ -11973,10 +11973,10 @@
         <v>0</v>
       </c>
       <c r="M202" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="N202" s="56" t="s">
         <v>121</v>
-      </c>
-      <c r="N202" s="56" t="s">
-        <v>127</v>
       </c>
       <c r="O202" s="44"/>
       <c r="P202" s="44"/>
@@ -11993,7 +11993,7 @@
         <v>100800</v>
       </c>
       <c r="C203" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D203" s="35">
         <v>100800001</v>
@@ -12002,10 +12002,10 @@
         <v>11</v>
       </c>
       <c r="F203" s="24" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G203" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H203" s="31">
         <v>0</v>
@@ -12023,10 +12023,10 @@
         <v>0</v>
       </c>
       <c r="M203" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N203" s="24" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:20">
@@ -12037,7 +12037,7 @@
         <v>100800</v>
       </c>
       <c r="C204" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D204" s="35">
         <v>100800001</v>
@@ -12046,10 +12046,10 @@
         <v>12</v>
       </c>
       <c r="F204" s="24" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G204" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H204" s="31">
         <v>0</v>
@@ -12067,10 +12067,10 @@
         <v>0</v>
       </c>
       <c r="M204" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N204" s="24" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:20">
@@ -12081,7 +12081,7 @@
         <v>100800</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D205" s="35">
         <v>100800001</v>
@@ -12090,10 +12090,10 @@
         <v>13</v>
       </c>
       <c r="F205" s="24" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G205" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H205" s="31">
         <v>0</v>
@@ -12111,10 +12111,10 @@
         <v>0</v>
       </c>
       <c r="M205" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="N205" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="N205" s="24" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:20">
@@ -12125,7 +12125,7 @@
         <v>105300</v>
       </c>
       <c r="C206" s="23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D206" s="35">
         <v>105300001</v>
@@ -12134,10 +12134,10 @@
         <v>11</v>
       </c>
       <c r="F206" s="24" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G206" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H206" s="31">
         <v>0</v>
@@ -12155,10 +12155,10 @@
         <v>0</v>
       </c>
       <c r="M206" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N206" s="24" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:20">
@@ -12169,7 +12169,7 @@
         <v>105300</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D207" s="35">
         <v>105300001</v>
@@ -12178,10 +12178,10 @@
         <v>12</v>
       </c>
       <c r="F207" s="24" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G207" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H207" s="31">
         <v>0</v>
@@ -12199,10 +12199,10 @@
         <v>0</v>
       </c>
       <c r="M207" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N207" s="24" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:20">
@@ -12213,7 +12213,7 @@
         <v>105300</v>
       </c>
       <c r="C208" s="23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D208" s="35">
         <v>105300001</v>
@@ -12222,10 +12222,10 @@
         <v>13</v>
       </c>
       <c r="F208" s="24" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G208" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H208" s="31">
         <v>0</v>
@@ -12243,10 +12243,10 @@
         <v>0</v>
       </c>
       <c r="M208" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="N208" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="N208" s="24" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:14">
@@ -12257,7 +12257,7 @@
         <v>105700</v>
       </c>
       <c r="C209" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D209" s="35">
         <v>105700001</v>
@@ -12266,10 +12266,10 @@
         <v>11</v>
       </c>
       <c r="F209" s="24" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G209" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H209" s="31">
         <v>0</v>
@@ -12287,10 +12287,10 @@
         <v>0</v>
       </c>
       <c r="M209" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N209" s="24" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:14">
@@ -12301,7 +12301,7 @@
         <v>105700</v>
       </c>
       <c r="C210" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D210" s="35">
         <v>105700001</v>
@@ -12310,10 +12310,10 @@
         <v>12</v>
       </c>
       <c r="F210" s="24" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G210" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H210" s="31">
         <v>0</v>
@@ -12331,10 +12331,10 @@
         <v>0</v>
       </c>
       <c r="M210" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N210" s="24" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:14">
@@ -12345,7 +12345,7 @@
         <v>105700</v>
       </c>
       <c r="C211" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D211" s="35">
         <v>105700001</v>
@@ -12354,10 +12354,10 @@
         <v>13</v>
       </c>
       <c r="F211" s="24" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G211" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H211" s="31">
         <v>0</v>
@@ -12375,10 +12375,10 @@
         <v>0</v>
       </c>
       <c r="M211" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="N211" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="N211" s="24" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="212" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12389,7 +12389,7 @@
         <v>105800</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D212" s="61">
         <v>105800001</v>
@@ -12398,10 +12398,10 @@
         <v>11</v>
       </c>
       <c r="F212" s="24" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G212" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H212" s="31">
         <v>0</v>
@@ -12419,10 +12419,10 @@
         <v>0</v>
       </c>
       <c r="M212" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N212" s="24" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="213" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12433,7 +12433,7 @@
         <v>105800</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D213" s="61">
         <v>105800001</v>
@@ -12442,10 +12442,10 @@
         <v>12</v>
       </c>
       <c r="F213" s="24" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G213" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H213" s="31">
         <v>0</v>
@@ -12463,10 +12463,10 @@
         <v>0</v>
       </c>
       <c r="M213" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N213" s="24" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="214" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12477,7 +12477,7 @@
         <v>105800</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D214" s="61">
         <v>105800001</v>
@@ -12486,10 +12486,10 @@
         <v>13</v>
       </c>
       <c r="F214" s="24" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G214" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H214" s="31">
         <v>0</v>
@@ -12507,10 +12507,10 @@
         <v>0</v>
       </c>
       <c r="M214" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="N214" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="N214" s="24" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="215" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12521,7 +12521,7 @@
         <v>105500</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D215" s="61">
         <v>105500001</v>
@@ -12530,10 +12530,10 @@
         <v>11</v>
       </c>
       <c r="F215" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G215" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H215" s="31">
         <v>0</v>
@@ -12551,10 +12551,10 @@
         <v>0</v>
       </c>
       <c r="M215" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N215" s="24" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="216" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12565,7 +12565,7 @@
         <v>105500</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D216" s="61">
         <v>105500001</v>
@@ -12574,10 +12574,10 @@
         <v>12</v>
       </c>
       <c r="F216" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G216" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H216" s="31">
         <v>0</v>
@@ -12595,10 +12595,10 @@
         <v>0</v>
       </c>
       <c r="M216" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N216" s="24" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="217" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12609,7 +12609,7 @@
         <v>105500</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D217" s="61">
         <v>105500001</v>
@@ -12618,10 +12618,10 @@
         <v>13</v>
       </c>
       <c r="F217" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G217" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H217" s="31">
         <v>0</v>
@@ -12639,10 +12639,10 @@
         <v>0</v>
       </c>
       <c r="M217" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="N217" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="N217" s="24" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:14">
@@ -12653,7 +12653,7 @@
         <v>104800</v>
       </c>
       <c r="C218" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D218" s="27">
         <v>104800001</v>
@@ -12662,10 +12662,10 @@
         <v>11</v>
       </c>
       <c r="F218" s="24" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G218" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H218" s="31">
         <v>0</v>
@@ -12683,10 +12683,10 @@
         <v>0</v>
       </c>
       <c r="M218" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N218" s="24" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:14">
@@ -12697,7 +12697,7 @@
         <v>104800</v>
       </c>
       <c r="C219" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D219" s="27">
         <v>104800001</v>
@@ -12706,10 +12706,10 @@
         <v>12</v>
       </c>
       <c r="F219" s="24" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G219" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H219" s="31">
         <v>0</v>
@@ -12727,10 +12727,10 @@
         <v>0</v>
       </c>
       <c r="M219" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N219" s="24" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:14">
@@ -12741,7 +12741,7 @@
         <v>104800</v>
       </c>
       <c r="C220" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D220" s="27">
         <v>104800001</v>
@@ -12750,10 +12750,10 @@
         <v>13</v>
       </c>
       <c r="F220" s="24" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G220" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H220" s="31">
         <v>0</v>
@@ -12771,10 +12771,10 @@
         <v>0</v>
       </c>
       <c r="M220" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="N220" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="N220" s="24" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="221" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12785,7 +12785,7 @@
         <v>105501</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D221" s="61">
         <v>105501001</v>
@@ -12794,10 +12794,10 @@
         <v>11</v>
       </c>
       <c r="F221" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G221" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H221" s="31">
         <v>0</v>
@@ -12815,10 +12815,10 @@
         <v>0</v>
       </c>
       <c r="M221" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N221" s="24" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="222" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12829,7 +12829,7 @@
         <v>105501</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D222" s="61">
         <v>105501001</v>
@@ -12838,10 +12838,10 @@
         <v>12</v>
       </c>
       <c r="F222" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G222" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H222" s="31">
         <v>0</v>
@@ -12859,10 +12859,10 @@
         <v>0</v>
       </c>
       <c r="M222" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N222" s="24" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="223" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12873,7 +12873,7 @@
         <v>105501</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D223" s="61">
         <v>105501001</v>
@@ -12882,10 +12882,10 @@
         <v>13</v>
       </c>
       <c r="F223" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G223" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H223" s="31">
         <v>0</v>
@@ -12903,10 +12903,10 @@
         <v>0</v>
       </c>
       <c r="M223" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="N223" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="N223" s="24" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="224" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12917,7 +12917,7 @@
         <v>105502</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D224" s="61">
         <v>105502001</v>
@@ -12926,10 +12926,10 @@
         <v>11</v>
       </c>
       <c r="F224" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G224" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H224" s="31">
         <v>0</v>
@@ -12947,10 +12947,10 @@
         <v>0</v>
       </c>
       <c r="M224" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N224" s="24" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="225" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -12961,7 +12961,7 @@
         <v>105502</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D225" s="61">
         <v>105502001</v>
@@ -12970,10 +12970,10 @@
         <v>12</v>
       </c>
       <c r="F225" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G225" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H225" s="31">
         <v>0</v>
@@ -12991,10 +12991,10 @@
         <v>0</v>
       </c>
       <c r="M225" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N225" s="24" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="226" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -13005,7 +13005,7 @@
         <v>105502</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D226" s="61">
         <v>105502001</v>
@@ -13014,10 +13014,10 @@
         <v>13</v>
       </c>
       <c r="F226" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G226" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H226" s="31">
         <v>0</v>
@@ -13035,10 +13035,10 @@
         <v>0</v>
       </c>
       <c r="M226" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="N226" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="N226" s="24" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="227" customFormat="1" ht="16.5" spans="1:20">
@@ -13049,7 +13049,7 @@
         <v>104100</v>
       </c>
       <c r="C227" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D227" s="27">
         <v>104100001</v>
@@ -13058,10 +13058,10 @@
         <v>11</v>
       </c>
       <c r="F227" s="47" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G227" s="64" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H227" s="65">
         <v>0</v>
@@ -13079,10 +13079,10 @@
         <v>0</v>
       </c>
       <c r="M227" s="48" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N227" s="47" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="228" customFormat="1" ht="16.5" spans="1:20">
@@ -13093,7 +13093,7 @@
         <v>104100</v>
       </c>
       <c r="C228" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D228" s="27">
         <v>104100001</v>
@@ -13102,10 +13102,10 @@
         <v>12</v>
       </c>
       <c r="F228" s="47" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G228" s="64" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H228" s="65">
         <v>0</v>
@@ -13123,10 +13123,10 @@
         <v>0</v>
       </c>
       <c r="M228" s="48" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N228" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="229" customFormat="1" ht="16.5" spans="1:20">
@@ -13137,7 +13137,7 @@
         <v>104100</v>
       </c>
       <c r="C229" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D229" s="27">
         <v>104100001</v>
@@ -13146,10 +13146,10 @@
         <v>13</v>
       </c>
       <c r="F229" s="47" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G229" s="64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H229" s="65">
         <v>0</v>
@@ -13167,10 +13167,10 @@
         <v>0</v>
       </c>
       <c r="M229" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="N229" s="47" t="s">
         <v>121</v>
-      </c>
-      <c r="N229" s="47" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="230" customFormat="1" ht="16.5" spans="1:20">
@@ -13181,7 +13181,7 @@
         <v>104200</v>
       </c>
       <c r="C230" s="63" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D230" s="27">
         <v>104200001</v>
@@ -13190,10 +13190,10 @@
         <v>11</v>
       </c>
       <c r="F230" s="47" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G230" s="64" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H230" s="65">
         <v>0</v>
@@ -13211,10 +13211,10 @@
         <v>0</v>
       </c>
       <c r="M230" s="48" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N230" s="47" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="231" customFormat="1" ht="16.5" spans="1:20">
@@ -13225,7 +13225,7 @@
         <v>104200</v>
       </c>
       <c r="C231" s="63" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D231" s="27">
         <v>104200001</v>
@@ -13234,10 +13234,10 @@
         <v>12</v>
       </c>
       <c r="F231" s="47" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G231" s="64" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H231" s="65">
         <v>0</v>
@@ -13255,10 +13255,10 @@
         <v>0</v>
       </c>
       <c r="M231" s="48" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N231" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="232" customFormat="1" ht="16.5" spans="1:20">
@@ -13269,7 +13269,7 @@
         <v>104200</v>
       </c>
       <c r="C232" s="63" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D232" s="27">
         <v>104200001</v>
@@ -13278,10 +13278,10 @@
         <v>13</v>
       </c>
       <c r="F232" s="47" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G232" s="64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H232" s="65">
         <v>0</v>
@@ -13299,10 +13299,10 @@
         <v>0</v>
       </c>
       <c r="M232" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="N232" s="47" t="s">
         <v>121</v>
-      </c>
-      <c r="N232" s="47" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="233" s="2" customFormat="1" ht="16.5" spans="1:20">
@@ -13622,10 +13622,10 @@
         <v>21</v>
       </c>
       <c r="F239" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G239" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G239" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H239" s="17">
         <v>10000000</v>
@@ -13672,10 +13672,10 @@
         <v>22</v>
       </c>
       <c r="F240" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G240" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G240" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H240" s="17">
         <v>100000000</v>
@@ -13722,10 +13722,10 @@
         <v>23</v>
       </c>
       <c r="F241" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G241" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G241" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H241" s="31">
         <v>1000000000</v>
@@ -13763,7 +13763,7 @@
         <v>101200</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D242" s="27">
         <v>101200001</v>
@@ -13772,10 +13772,10 @@
         <v>21</v>
       </c>
       <c r="F242" s="32" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="G242" s="33" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="H242" s="17">
         <v>10000000</v>
@@ -13813,7 +13813,7 @@
         <v>101200</v>
       </c>
       <c r="C243" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D243" s="27">
         <v>101200001</v>
@@ -13863,7 +13863,7 @@
         <v>101200</v>
       </c>
       <c r="C244" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D244" s="27">
         <v>101200001</v>
@@ -13913,7 +13913,7 @@
         <v>101400</v>
       </c>
       <c r="C245" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D245" s="27">
         <v>101400001</v>
@@ -13963,7 +13963,7 @@
         <v>101400</v>
       </c>
       <c r="C246" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D246" s="27">
         <v>101400001</v>
@@ -14013,7 +14013,7 @@
         <v>101400</v>
       </c>
       <c r="C247" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D247" s="27">
         <v>101400001</v>
@@ -14063,7 +14063,7 @@
         <v>101700</v>
       </c>
       <c r="C248" s="23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D248" s="27">
         <v>101700001</v>
@@ -14072,10 +14072,10 @@
         <v>21</v>
       </c>
       <c r="F248" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G248" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G248" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H248" s="17">
         <v>10000000</v>
@@ -14113,7 +14113,7 @@
         <v>101700</v>
       </c>
       <c r="C249" s="23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D249" s="27">
         <v>101700001</v>
@@ -14122,10 +14122,10 @@
         <v>22</v>
       </c>
       <c r="F249" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G249" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G249" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H249" s="17">
         <v>100000000</v>
@@ -14163,7 +14163,7 @@
         <v>101700</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D250" s="27">
         <v>101700001</v>
@@ -14172,10 +14172,10 @@
         <v>23</v>
       </c>
       <c r="F250" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G250" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G250" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H250" s="31">
         <v>1000000000</v>
@@ -14213,7 +14213,7 @@
         <v>102100</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D251" s="27">
         <v>102100001</v>
@@ -14222,10 +14222,10 @@
         <v>21</v>
       </c>
       <c r="F251" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G251" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G251" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H251" s="17">
         <v>10000000</v>
@@ -14263,7 +14263,7 @@
         <v>102100</v>
       </c>
       <c r="C252" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D252" s="27">
         <v>102100001</v>
@@ -14272,10 +14272,10 @@
         <v>22</v>
       </c>
       <c r="F252" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G252" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G252" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H252" s="17">
         <v>100000000</v>
@@ -14313,7 +14313,7 @@
         <v>102100</v>
       </c>
       <c r="C253" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D253" s="27">
         <v>102100001</v>
@@ -14322,10 +14322,10 @@
         <v>23</v>
       </c>
       <c r="F253" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G253" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G253" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H253" s="31">
         <v>1000000000</v>
@@ -14363,7 +14363,7 @@
         <v>102200</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D254" s="27">
         <v>102200001</v>
@@ -14372,10 +14372,10 @@
         <v>21</v>
       </c>
       <c r="F254" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G254" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G254" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H254" s="17">
         <v>10000000</v>
@@ -14413,7 +14413,7 @@
         <v>102200</v>
       </c>
       <c r="C255" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D255" s="27">
         <v>102200001</v>
@@ -14422,10 +14422,10 @@
         <v>22</v>
       </c>
       <c r="F255" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G255" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G255" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H255" s="17">
         <v>100000000</v>
@@ -14463,7 +14463,7 @@
         <v>102200</v>
       </c>
       <c r="C256" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D256" s="27">
         <v>102200001</v>
@@ -14472,10 +14472,10 @@
         <v>23</v>
       </c>
       <c r="F256" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G256" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G256" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H256" s="31">
         <v>1000000000</v>
@@ -14513,7 +14513,7 @@
         <v>102400</v>
       </c>
       <c r="C257" s="23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D257" s="27">
         <v>102400026</v>
@@ -14522,10 +14522,10 @@
         <v>21</v>
       </c>
       <c r="F257" s="32" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G257" s="33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H257" s="17">
         <v>10000000</v>
@@ -14563,7 +14563,7 @@
         <v>102400</v>
       </c>
       <c r="C258" s="23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D258" s="27">
         <v>102400026</v>
@@ -14613,7 +14613,7 @@
         <v>102400</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D259" s="27">
         <v>102400026</v>
@@ -14663,7 +14663,7 @@
         <v>101800</v>
       </c>
       <c r="C260" s="23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D260" s="27">
         <v>101800001</v>
@@ -14672,10 +14672,10 @@
         <v>21</v>
       </c>
       <c r="F260" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G260" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G260" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H260" s="17">
         <v>10000000</v>
@@ -14713,7 +14713,7 @@
         <v>101800</v>
       </c>
       <c r="C261" s="23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D261" s="27">
         <v>101800001</v>
@@ -14722,10 +14722,10 @@
         <v>22</v>
       </c>
       <c r="F261" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G261" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G261" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H261" s="17">
         <v>100000000</v>
@@ -14763,7 +14763,7 @@
         <v>101800</v>
       </c>
       <c r="C262" s="23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D262" s="27">
         <v>101800001</v>
@@ -14772,10 +14772,10 @@
         <v>23</v>
       </c>
       <c r="F262" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G262" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G262" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H262" s="31">
         <v>1000000000</v>
@@ -14813,7 +14813,7 @@
         <v>102500</v>
       </c>
       <c r="C263" s="23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D263" s="27">
         <v>102500001</v>
@@ -14822,10 +14822,10 @@
         <v>21</v>
       </c>
       <c r="F263" s="24" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="G263" s="25" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H263" s="17">
         <v>10000000</v>
@@ -14863,7 +14863,7 @@
         <v>102500</v>
       </c>
       <c r="C264" s="23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D264" s="27">
         <v>102500001</v>
@@ -14872,10 +14872,10 @@
         <v>22</v>
       </c>
       <c r="F264" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G264" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H264" s="17">
         <v>100000000</v>
@@ -14913,7 +14913,7 @@
         <v>102500</v>
       </c>
       <c r="C265" s="23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D265" s="27">
         <v>102500001</v>
@@ -14922,10 +14922,10 @@
         <v>23</v>
       </c>
       <c r="F265" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G265" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H265" s="31">
         <v>1000000000</v>
@@ -14963,7 +14963,7 @@
         <v>102300</v>
       </c>
       <c r="C266" s="23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D266" s="27">
         <v>102300001</v>
@@ -14972,10 +14972,10 @@
         <v>21</v>
       </c>
       <c r="F266" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G266" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="G266" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="H266" s="17">
         <v>10000000</v>
@@ -15013,7 +15013,7 @@
         <v>102300</v>
       </c>
       <c r="C267" s="23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D267" s="27">
         <v>102300001</v>
@@ -15022,10 +15022,10 @@
         <v>22</v>
       </c>
       <c r="F267" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G267" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="G267" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="H267" s="17">
         <v>100000000</v>
@@ -15063,7 +15063,7 @@
         <v>102300</v>
       </c>
       <c r="C268" s="23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D268" s="27">
         <v>102300001</v>
@@ -15072,10 +15072,10 @@
         <v>23</v>
       </c>
       <c r="F268" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G268" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="G268" s="25" t="s">
-        <v>55</v>
       </c>
       <c r="H268" s="31">
         <v>1000000000</v>
@@ -15113,7 +15113,7 @@
         <v>103400</v>
       </c>
       <c r="C269" s="23" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D269" s="27">
         <v>103000001</v>
@@ -15122,10 +15122,10 @@
         <v>21</v>
       </c>
       <c r="F269" s="32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G269" s="33" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H269" s="17">
         <v>10000000</v>
@@ -15163,7 +15163,7 @@
         <v>103400</v>
       </c>
       <c r="C270" s="23" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D270" s="27">
         <v>103000001</v>
@@ -15172,10 +15172,10 @@
         <v>22</v>
       </c>
       <c r="F270" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G270" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H270" s="17">
         <v>100000000</v>
@@ -15213,7 +15213,7 @@
         <v>103400</v>
       </c>
       <c r="C271" s="23" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D271" s="27">
         <v>103000001</v>
@@ -15222,10 +15222,10 @@
         <v>23</v>
       </c>
       <c r="F271" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G271" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H271" s="31">
         <v>1000000000</v>
@@ -15263,7 +15263,7 @@
         <v>103500</v>
       </c>
       <c r="C272" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D272" s="35">
         <v>102900001</v>
@@ -15313,7 +15313,7 @@
         <v>103500</v>
       </c>
       <c r="C273" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D273" s="35">
         <v>102900001</v>
@@ -15363,7 +15363,7 @@
         <v>103500</v>
       </c>
       <c r="C274" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D274" s="35">
         <v>102900001</v>
@@ -15413,7 +15413,7 @@
         <v>103501</v>
       </c>
       <c r="C275" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D275" s="35">
         <v>103501001</v>
@@ -15463,7 +15463,7 @@
         <v>103501</v>
       </c>
       <c r="C276" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D276" s="35">
         <v>103501001</v>
@@ -15513,7 +15513,7 @@
         <v>103501</v>
       </c>
       <c r="C277" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D277" s="35">
         <v>103501001</v>
@@ -15563,7 +15563,7 @@
         <v>103600</v>
       </c>
       <c r="C278" s="37" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D278" s="38">
         <v>103600001</v>
@@ -15572,10 +15572,10 @@
         <v>21</v>
       </c>
       <c r="F278" s="39" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G278" s="40" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H278" s="41">
         <v>10000000</v>
@@ -15613,7 +15613,7 @@
         <v>103600</v>
       </c>
       <c r="C279" s="23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D279" s="35">
         <v>103600001</v>
@@ -15622,10 +15622,10 @@
         <v>22</v>
       </c>
       <c r="F279" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G279" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H279" s="31">
         <v>100000000</v>
@@ -15663,7 +15663,7 @@
         <v>103600</v>
       </c>
       <c r="C280" s="23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D280" s="35">
         <v>103600001</v>
@@ -15672,10 +15672,10 @@
         <v>23</v>
       </c>
       <c r="F280" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G280" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H280" s="31">
         <v>1000000000</v>
@@ -15713,7 +15713,7 @@
         <v>102000</v>
       </c>
       <c r="C281" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D281" s="35">
         <v>102000001</v>
@@ -15722,10 +15722,10 @@
         <v>21</v>
       </c>
       <c r="F281" s="24" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="G281" s="25" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="H281" s="31">
         <v>10000000</v>
@@ -15763,7 +15763,7 @@
         <v>102000</v>
       </c>
       <c r="C282" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D282" s="35">
         <v>102000001</v>
@@ -15772,10 +15772,10 @@
         <v>22</v>
       </c>
       <c r="F282" s="24" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G282" s="25" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H282" s="31">
         <v>100000000</v>
@@ -15813,7 +15813,7 @@
         <v>102000</v>
       </c>
       <c r="C283" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D283" s="35">
         <v>102000001</v>
@@ -15822,10 +15822,10 @@
         <v>23</v>
       </c>
       <c r="F283" s="24" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G283" s="25" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H283" s="31">
         <v>1000000000</v>
@@ -15863,7 +15863,7 @@
         <v>103401</v>
       </c>
       <c r="C284" s="23" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D284" s="35">
         <v>103400001</v>
@@ -15872,10 +15872,10 @@
         <v>21</v>
       </c>
       <c r="F284" s="24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G284" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H284" s="31">
         <v>10000000</v>
@@ -15913,7 +15913,7 @@
         <v>103401</v>
       </c>
       <c r="C285" s="23" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D285" s="35">
         <v>103400001</v>
@@ -15922,10 +15922,10 @@
         <v>22</v>
       </c>
       <c r="F285" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G285" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H285" s="31">
         <v>100000000</v>
@@ -15963,7 +15963,7 @@
         <v>103401</v>
       </c>
       <c r="C286" s="23" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D286" s="35">
         <v>103400001</v>
@@ -15972,10 +15972,10 @@
         <v>23</v>
       </c>
       <c r="F286" s="24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G286" s="25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H286" s="31">
         <v>1000000000</v>
@@ -16013,7 +16013,7 @@
         <v>103800</v>
       </c>
       <c r="C287" s="23" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D287" s="35">
         <v>103800001</v>
@@ -16022,10 +16022,10 @@
         <v>21</v>
       </c>
       <c r="F287" s="24" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G287" s="25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H287" s="31">
         <v>10000000</v>
@@ -16063,7 +16063,7 @@
         <v>103800</v>
       </c>
       <c r="C288" s="23" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D288" s="35">
         <v>103800001</v>
@@ -16072,10 +16072,10 @@
         <v>22</v>
       </c>
       <c r="F288" s="24" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G288" s="25" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H288" s="31">
         <v>100000000</v>
@@ -16113,7 +16113,7 @@
         <v>103800</v>
       </c>
       <c r="C289" s="23" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D289" s="35">
         <v>103800001</v>
@@ -16122,10 +16122,10 @@
         <v>23</v>
       </c>
       <c r="F289" s="24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G289" s="25" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H289" s="31">
         <v>1000000000</v>
@@ -16163,7 +16163,7 @@
         <v>104000</v>
       </c>
       <c r="C290" s="23" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D290" s="35">
         <v>104000001</v>
@@ -16172,10 +16172,10 @@
         <v>21</v>
       </c>
       <c r="F290" s="24" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G290" s="25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H290" s="31">
         <v>10000000</v>
@@ -16213,7 +16213,7 @@
         <v>104000</v>
       </c>
       <c r="C291" s="23" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D291" s="35">
         <v>104000001</v>
@@ -16222,10 +16222,10 @@
         <v>22</v>
       </c>
       <c r="F291" s="24" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G291" s="25" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H291" s="31">
         <v>100000000</v>
@@ -16263,7 +16263,7 @@
         <v>104000</v>
       </c>
       <c r="C292" s="23" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D292" s="35">
         <v>104000001</v>
@@ -16272,10 +16272,10 @@
         <v>23</v>
       </c>
       <c r="F292" s="24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G292" s="25" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H292" s="31">
         <v>1000000000</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="135">
   <si>
     <t>id</t>
   </si>
@@ -338,6 +338,9 @@
     <t>麻将胡了</t>
   </si>
   <si>
+    <t>50_100_250_400_600_800_1000</t>
+  </si>
+  <si>
     <t>50:1</t>
   </si>
   <si>
@@ -356,13 +359,16 @@
     <t>财神</t>
   </si>
   <si>
+    <t>8_16_40_80_160_400_800</t>
+  </si>
+  <si>
+    <t>8:1</t>
+  </si>
+  <si>
     <t>埃及艳后</t>
   </si>
   <si>
     <t>圣诞狂欢夜</t>
-  </si>
-  <si>
-    <t>50_100_250_400_600_800_1000</t>
   </si>
   <si>
     <t>杰克船长</t>
@@ -384,6 +390,9 @@
   </si>
   <si>
     <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>20_40_100_160_240_320_400</t>
   </si>
   <si>
     <t>20:1</t>
@@ -431,10 +440,16 @@
     <t>宙斯vs哈迪斯</t>
   </si>
   <si>
-    <t>750:1</t>
+    <t>75_150_375_600_900_1200_1500</t>
+  </si>
+  <si>
+    <t>75:1</t>
   </si>
   <si>
     <t>750_1500_3750_6000_9000_12000_15000</t>
+  </si>
+  <si>
+    <t>750:1</t>
   </si>
   <si>
     <t>7500_15000_37500_60000_90000_120000_150000</t>
@@ -474,6 +489,9 @@
   </si>
   <si>
     <t>绿巨人</t>
+  </si>
+  <si>
+    <t>40_80_200_320_480_640_800</t>
   </si>
   <si>
     <t>40:1</t>
@@ -554,18 +572,6 @@
     <t>1980000_50000000</t>
   </si>
   <si>
-    <t>20_40_100_160_240_320_400</t>
-  </si>
-  <si>
-    <t>75_150_375_600_900_1200_1500</t>
-  </si>
-  <si>
-    <t>75:1</t>
-  </si>
-  <si>
-    <t>40_80_200_320_480_640_800</t>
-  </si>
-  <si>
     <t>黄金帝国</t>
   </si>
   <si>
@@ -585,12 +591,6 @@
   </si>
   <si>
     <t>狂野沙滩</t>
-  </si>
-  <si>
-    <t>8_16_40_80_160_400_800</t>
-  </si>
-  <si>
-    <t>8:1</t>
   </si>
 </sst>
 </file>
@@ -805,7 +805,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -826,16 +825,17 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -2401,11 +2401,11 @@
       <c r="E11" s="23">
         <v>1</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="24" t="s">
         <v>50</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" s="17">
         <v>10000000</v>
@@ -2452,10 +2452,10 @@
         <v>2</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H12" s="17">
         <v>100000000</v>
@@ -2502,10 +2502,10 @@
         <v>3</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" s="31">
         <v>1000000000</v>
@@ -2543,7 +2543,7 @@
         <v>101200</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" s="27">
         <v>101200001</v>
@@ -2551,11 +2551,11 @@
       <c r="E14" s="23">
         <v>1</v>
       </c>
-      <c r="F14" s="32">
-        <v>50</v>
+      <c r="F14" s="32" t="s">
+        <v>57</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H14" s="17">
         <v>10000000</v>
@@ -2593,7 +2593,7 @@
         <v>101200</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="27">
         <v>101200001</v>
@@ -2643,7 +2643,7 @@
         <v>101200</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="27">
         <v>101200001</v>
@@ -2693,7 +2693,7 @@
         <v>101400</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D17" s="27">
         <v>101400001</v>
@@ -2743,7 +2743,7 @@
         <v>101400</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D18" s="27">
         <v>101400001</v>
@@ -2793,7 +2793,7 @@
         <v>101400</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D19" s="27">
         <v>101400001</v>
@@ -2843,7 +2843,7 @@
         <v>101700</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D20" s="27">
         <v>101700001</v>
@@ -2852,10 +2852,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H20" s="17">
         <v>10000000</v>
@@ -2893,7 +2893,7 @@
         <v>101700</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D21" s="27">
         <v>101700001</v>
@@ -2902,10 +2902,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H21" s="17">
         <v>100000000</v>
@@ -2943,7 +2943,7 @@
         <v>101700</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D22" s="27">
         <v>101700001</v>
@@ -2952,10 +2952,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H22" s="31">
         <v>1000000000</v>
@@ -2993,7 +2993,7 @@
         <v>102100</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D23" s="27">
         <v>102100001</v>
@@ -3001,11 +3001,11 @@
       <c r="E23" s="23">
         <v>1</v>
       </c>
-      <c r="F23" s="24">
-        <v>100</v>
+      <c r="F23" s="24" t="s">
+        <v>50</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H23" s="17">
         <v>10000000</v>
@@ -3043,7 +3043,7 @@
         <v>102100</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D24" s="27">
         <v>102100001</v>
@@ -3052,10 +3052,10 @@
         <v>2</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H24" s="17">
         <v>100000000</v>
@@ -3093,7 +3093,7 @@
         <v>102100</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D25" s="27">
         <v>102100001</v>
@@ -3102,10 +3102,10 @@
         <v>3</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H25" s="31">
         <v>1000000000</v>
@@ -3143,7 +3143,7 @@
         <v>102200</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D26" s="27">
         <v>102200001</v>
@@ -3151,11 +3151,11 @@
       <c r="E26" s="23">
         <v>1</v>
       </c>
-      <c r="F26" s="24">
-        <v>100</v>
+      <c r="F26" s="24" t="s">
+        <v>50</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H26" s="17">
         <v>10000000</v>
@@ -3193,7 +3193,7 @@
         <v>102200</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D27" s="27">
         <v>102200001</v>
@@ -3202,10 +3202,10 @@
         <v>2</v>
       </c>
       <c r="F27" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H27" s="17">
         <v>100000000</v>
@@ -3243,7 +3243,7 @@
         <v>102200</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D28" s="27">
         <v>102200001</v>
@@ -3252,10 +3252,10 @@
         <v>3</v>
       </c>
       <c r="F28" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H28" s="31">
         <v>1000000000</v>
@@ -3293,7 +3293,7 @@
         <v>102400</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D29" s="27">
         <v>102400026</v>
@@ -3302,10 +3302,10 @@
         <v>1</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G29" s="33" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H29" s="17">
         <v>10000000</v>
@@ -3343,7 +3343,7 @@
         <v>102400</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D30" s="27">
         <v>102400026</v>
@@ -3393,7 +3393,7 @@
         <v>102400</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D31" s="27">
         <v>102400026</v>
@@ -3443,7 +3443,7 @@
         <v>101800</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D32" s="27">
         <v>101800001</v>
@@ -3451,11 +3451,11 @@
       <c r="E32" s="23">
         <v>1</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="24" t="s">
         <v>50</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H32" s="17">
         <v>10000000</v>
@@ -3493,7 +3493,7 @@
         <v>101800</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D33" s="27">
         <v>101800001</v>
@@ -3502,10 +3502,10 @@
         <v>2</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H33" s="17">
         <v>100000000</v>
@@ -3543,7 +3543,7 @@
         <v>101800</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D34" s="27">
         <v>101800001</v>
@@ -3552,10 +3552,10 @@
         <v>3</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H34" s="31">
         <v>1000000000</v>
@@ -3593,7 +3593,7 @@
         <v>102500</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D35" s="27">
         <v>102500001</v>
@@ -3601,11 +3601,11 @@
       <c r="E35" s="23">
         <v>1</v>
       </c>
-      <c r="F35" s="24">
-        <v>20</v>
+      <c r="F35" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H35" s="17">
         <v>10000000</v>
@@ -3643,7 +3643,7 @@
         <v>102500</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D36" s="27">
         <v>102500001</v>
@@ -3652,10 +3652,10 @@
         <v>2</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H36" s="17">
         <v>100000000</v>
@@ -3693,7 +3693,7 @@
         <v>102500</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D37" s="27">
         <v>102500001</v>
@@ -3702,10 +3702,10 @@
         <v>3</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H37" s="31">
         <v>1000000000</v>
@@ -3743,7 +3743,7 @@
         <v>102300</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D38" s="27">
         <v>102300001</v>
@@ -3752,10 +3752,10 @@
         <v>1</v>
       </c>
       <c r="F38" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H38" s="17">
         <v>10000000</v>
@@ -3793,7 +3793,7 @@
         <v>102300</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D39" s="27">
         <v>102300001</v>
@@ -3802,10 +3802,10 @@
         <v>2</v>
       </c>
       <c r="F39" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G39" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H39" s="17">
         <v>100000000</v>
@@ -3843,7 +3843,7 @@
         <v>102300</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D40" s="27">
         <v>102300001</v>
@@ -3852,10 +3852,10 @@
         <v>3</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G40" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H40" s="31">
         <v>1000000000</v>
@@ -3893,7 +3893,7 @@
         <v>103400</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D41" s="27">
         <v>103000001</v>
@@ -3902,10 +3902,10 @@
         <v>1</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G41" s="33" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H41" s="17">
         <v>10000000</v>
@@ -3943,7 +3943,7 @@
         <v>103400</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D42" s="27">
         <v>103000001</v>
@@ -3952,10 +3952,10 @@
         <v>2</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G42" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H42" s="17">
         <v>100000000</v>
@@ -3993,7 +3993,7 @@
         <v>103400</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D43" s="27">
         <v>103000001</v>
@@ -4002,10 +4002,10 @@
         <v>3</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H43" s="31">
         <v>1000000000</v>
@@ -4043,7 +4043,7 @@
         <v>103500</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D44" s="35">
         <v>102900001</v>
@@ -4093,7 +4093,7 @@
         <v>103500</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D45" s="35">
         <v>102900001</v>
@@ -4143,7 +4143,7 @@
         <v>103500</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D46" s="35">
         <v>102900001</v>
@@ -4193,7 +4193,7 @@
         <v>103501</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D47" s="35">
         <v>103501001</v>
@@ -4243,7 +4243,7 @@
         <v>103501</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D48" s="35">
         <v>103501001</v>
@@ -4293,7 +4293,7 @@
         <v>103501</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D49" s="35">
         <v>103501001</v>
@@ -4343,7 +4343,7 @@
         <v>103600</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D50" s="38">
         <v>103600001</v>
@@ -4352,10 +4352,10 @@
         <v>1</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H50" s="41">
         <v>10000000</v>
@@ -4393,7 +4393,7 @@
         <v>103600</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D51" s="35">
         <v>103600001</v>
@@ -4402,10 +4402,10 @@
         <v>2</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H51" s="31">
         <v>100000000</v>
@@ -4443,7 +4443,7 @@
         <v>103600</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D52" s="35">
         <v>103600001</v>
@@ -4452,10 +4452,10 @@
         <v>3</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H52" s="31">
         <v>1000000000</v>
@@ -4493,7 +4493,7 @@
         <v>102800</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D53" s="35">
         <v>102800001</v>
@@ -4502,10 +4502,10 @@
         <v>1</v>
       </c>
       <c r="F53" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H53" s="31">
         <v>10000000</v>
@@ -4543,7 +4543,7 @@
         <v>102800</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D54" s="35">
         <v>102800001</v>
@@ -4552,10 +4552,10 @@
         <v>2</v>
       </c>
       <c r="F54" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G54" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H54" s="31">
         <v>100000000</v>
@@ -4593,7 +4593,7 @@
         <v>102800</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D55" s="35">
         <v>102800001</v>
@@ -4602,10 +4602,10 @@
         <v>3</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G55" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H55" s="31">
         <v>1000000000</v>
@@ -4643,7 +4643,7 @@
         <v>102000</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D56" s="35">
         <v>102000001</v>
@@ -4651,11 +4651,11 @@
       <c r="E56" s="23">
         <v>1</v>
       </c>
-      <c r="F56" s="24">
-        <v>750</v>
+      <c r="F56" s="24" t="s">
+        <v>84</v>
       </c>
       <c r="G56" s="25" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H56" s="31">
         <v>10000000</v>
@@ -4693,7 +4693,7 @@
         <v>102000</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D57" s="35">
         <v>102000001</v>
@@ -4702,10 +4702,10 @@
         <v>2</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G57" s="25" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H57" s="31">
         <v>100000000</v>
@@ -4743,7 +4743,7 @@
         <v>102000</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D58" s="35">
         <v>102000001</v>
@@ -4752,10 +4752,10 @@
         <v>3</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G58" s="25" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H58" s="31">
         <v>1000000000</v>
@@ -4793,7 +4793,7 @@
         <v>103401</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D59" s="35">
         <v>103400001</v>
@@ -4802,10 +4802,10 @@
         <v>1</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G59" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H59" s="31">
         <v>10000000</v>
@@ -4843,7 +4843,7 @@
         <v>103401</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D60" s="35">
         <v>103400001</v>
@@ -4852,10 +4852,10 @@
         <v>2</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G60" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H60" s="31">
         <v>100000000</v>
@@ -4893,7 +4893,7 @@
         <v>103401</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D61" s="35">
         <v>103400001</v>
@@ -4902,10 +4902,10 @@
         <v>3</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G61" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H61" s="31">
         <v>1000000000</v>
@@ -4943,7 +4943,7 @@
         <v>103800</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D62" s="35">
         <v>103800001</v>
@@ -4952,10 +4952,10 @@
         <v>1</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G62" s="25" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H62" s="31">
         <v>10000000</v>
@@ -4993,7 +4993,7 @@
         <v>103800</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D63" s="35">
         <v>103800001</v>
@@ -5002,10 +5002,10 @@
         <v>2</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G63" s="25" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H63" s="31">
         <v>100000000</v>
@@ -5043,7 +5043,7 @@
         <v>103800</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D64" s="35">
         <v>103800001</v>
@@ -5052,10 +5052,10 @@
         <v>3</v>
       </c>
       <c r="F64" s="24" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G64" s="25" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H64" s="31">
         <v>1000000000</v>
@@ -5093,7 +5093,7 @@
         <v>102700</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D65" s="35">
         <v>102700001</v>
@@ -5102,10 +5102,10 @@
         <v>1</v>
       </c>
       <c r="F65" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G65" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H65" s="31">
         <v>10000000</v>
@@ -5143,7 +5143,7 @@
         <v>102700</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D66" s="35">
         <v>102700001</v>
@@ -5152,10 +5152,10 @@
         <v>2</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G66" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H66" s="31">
         <v>100000000</v>
@@ -5193,7 +5193,7 @@
         <v>102700</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D67" s="35">
         <v>102700001</v>
@@ -5202,10 +5202,10 @@
         <v>3</v>
       </c>
       <c r="F67" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H67" s="31">
         <v>1000000000</v>
@@ -5243,7 +5243,7 @@
         <v>103700</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D68" s="35">
         <v>103700001</v>
@@ -5293,7 +5293,7 @@
         <v>103700</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D69" s="35">
         <v>103700001</v>
@@ -5343,7 +5343,7 @@
         <v>103700</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D70" s="35">
         <v>103700001</v>
@@ -5393,7 +5393,7 @@
         <v>103100</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D71" s="35">
         <v>103100001</v>
@@ -5401,11 +5401,11 @@
       <c r="E71" s="23">
         <v>1</v>
       </c>
-      <c r="F71" s="24">
-        <v>40</v>
+      <c r="F71" s="24" t="s">
+        <v>101</v>
       </c>
       <c r="G71" s="25" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H71" s="31">
         <v>10000000</v>
@@ -5443,7 +5443,7 @@
         <v>103100</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D72" s="35">
         <v>103100001</v>
@@ -5452,10 +5452,10 @@
         <v>2</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G72" s="25" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H72" s="31">
         <v>100000000</v>
@@ -5493,7 +5493,7 @@
         <v>103100</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D73" s="35">
         <v>103100001</v>
@@ -5502,10 +5502,10 @@
         <v>3</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G73" s="25" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H73" s="31">
         <v>1000000000</v>
@@ -5543,7 +5543,7 @@
         <v>104000</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D74" s="35">
         <v>104000001</v>
@@ -5552,10 +5552,10 @@
         <v>1</v>
       </c>
       <c r="F74" s="24" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H74" s="31">
         <v>10000000</v>
@@ -5593,7 +5593,7 @@
         <v>104000</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D75" s="35">
         <v>104000001</v>
@@ -5602,10 +5602,10 @@
         <v>2</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G75" s="25" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H75" s="31">
         <v>100000000</v>
@@ -5643,7 +5643,7 @@
         <v>104000</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D76" s="35">
         <v>104000001</v>
@@ -5652,10 +5652,10 @@
         <v>3</v>
       </c>
       <c r="F76" s="24" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G76" s="25" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H76" s="31">
         <v>1000000000</v>
@@ -5693,7 +5693,7 @@
         <v>103900</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D77" s="35">
         <v>103900001</v>
@@ -5701,11 +5701,11 @@
       <c r="E77" s="23">
         <v>1</v>
       </c>
-      <c r="F77" s="24">
-        <v>200</v>
+      <c r="F77" s="24" t="s">
+        <v>101</v>
       </c>
       <c r="G77" s="25" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="H77" s="31">
         <v>10000000</v>
@@ -5743,7 +5743,7 @@
         <v>103900</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D78" s="35">
         <v>103900001</v>
@@ -5752,10 +5752,10 @@
         <v>2</v>
       </c>
       <c r="F78" s="24" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G78" s="25" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H78" s="31">
         <v>100000000</v>
@@ -5793,7 +5793,7 @@
         <v>103900</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D79" s="35">
         <v>103900001</v>
@@ -5802,10 +5802,10 @@
         <v>3</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G79" s="25" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H79" s="31">
         <v>1000000000</v>
@@ -5843,7 +5843,7 @@
         <v>101600</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D80" s="35">
         <v>101600001</v>
@@ -5852,10 +5852,10 @@
         <v>1</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G80" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H80" s="31">
         <v>10000000</v>
@@ -5893,7 +5893,7 @@
         <v>101600</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D81" s="35">
         <v>101600001</v>
@@ -5902,10 +5902,10 @@
         <v>2</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G81" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H81" s="31">
         <v>100000000</v>
@@ -5943,7 +5943,7 @@
         <v>101600</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D82" s="35">
         <v>101600001</v>
@@ -5952,10 +5952,10 @@
         <v>3</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G82" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H82" s="31">
         <v>1000000000</v>
@@ -5993,7 +5993,7 @@
         <v>101500</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D83" s="35">
         <v>101500001</v>
@@ -6002,10 +6002,10 @@
         <v>1</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G83" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H83" s="31">
         <v>10000000</v>
@@ -6043,7 +6043,7 @@
         <v>101500</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D84" s="35">
         <v>101500001</v>
@@ -6052,10 +6052,10 @@
         <v>2</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G84" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H84" s="31">
         <v>100000000</v>
@@ -6093,7 +6093,7 @@
         <v>101500</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D85" s="35">
         <v>101500001</v>
@@ -6102,10 +6102,10 @@
         <v>3</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G85" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H85" s="31">
         <v>1000000000</v>
@@ -6143,7 +6143,7 @@
         <v>102600</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D86" s="35">
         <v>102600001</v>
@@ -6152,10 +6152,10 @@
         <v>1</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G86" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H86" s="31">
         <v>10000000</v>
@@ -6193,7 +6193,7 @@
         <v>102600</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D87" s="35">
         <v>102600001</v>
@@ -6202,10 +6202,10 @@
         <v>2</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G87" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H87" s="31">
         <v>100000000</v>
@@ -6243,7 +6243,7 @@
         <v>102600</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D88" s="35">
         <v>102600001</v>
@@ -6252,10 +6252,10 @@
         <v>3</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G88" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H88" s="31">
         <v>1000000000</v>
@@ -6293,7 +6293,7 @@
         <v>105000</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D89" s="35">
         <v>105000001</v>
@@ -6302,10 +6302,10 @@
         <v>1</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G89" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H89" s="31">
         <v>10000000</v>
@@ -6343,7 +6343,7 @@
         <v>105000</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D90" s="35">
         <v>105000001</v>
@@ -6352,10 +6352,10 @@
         <v>2</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G90" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H90" s="31">
         <v>100000000</v>
@@ -6393,7 +6393,7 @@
         <v>105000</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D91" s="35">
         <v>105000001</v>
@@ -6402,10 +6402,10 @@
         <v>3</v>
       </c>
       <c r="F91" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G91" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H91" s="31">
         <v>1000000000</v>
@@ -6443,7 +6443,7 @@
         <v>105100</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D92" s="35">
         <v>105100001</v>
@@ -6493,7 +6493,7 @@
         <v>105100</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D93" s="35">
         <v>105100001</v>
@@ -6543,7 +6543,7 @@
         <v>105100</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D94" s="35">
         <v>105100001</v>
@@ -6593,7 +6593,7 @@
         <v>105500</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D95" s="35">
         <v>105500001</v>
@@ -6602,10 +6602,10 @@
         <v>1</v>
       </c>
       <c r="F95" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H95" s="31">
         <v>10000000</v>
@@ -6643,7 +6643,7 @@
         <v>105500</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D96" s="35">
         <v>105500001</v>
@@ -6652,10 +6652,10 @@
         <v>2</v>
       </c>
       <c r="F96" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G96" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H96" s="31">
         <v>100000000</v>
@@ -6693,7 +6693,7 @@
         <v>105500</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D97" s="35">
         <v>105500001</v>
@@ -6702,10 +6702,10 @@
         <v>3</v>
       </c>
       <c r="F97" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G97" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H97" s="31">
         <v>1000000000</v>
@@ -6743,7 +6743,7 @@
         <v>104800</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D98" s="27">
         <v>104800001</v>
@@ -6752,10 +6752,10 @@
         <v>1</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G98" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H98" s="17">
         <v>10000000</v>
@@ -6773,7 +6773,7 @@
         <v>100</v>
       </c>
       <c r="M98" s="26" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N98" s="24">
         <v>0</v>
@@ -6793,7 +6793,7 @@
         <v>104800</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D99" s="27">
         <v>104800001</v>
@@ -6802,10 +6802,10 @@
         <v>2</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G99" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H99" s="17">
         <v>100000000</v>
@@ -6823,7 +6823,7 @@
         <v>100</v>
       </c>
       <c r="M99" s="26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N99" s="24">
         <v>0</v>
@@ -6843,7 +6843,7 @@
         <v>104800</v>
       </c>
       <c r="C100" s="23" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D100" s="27">
         <v>104800001</v>
@@ -6852,10 +6852,10 @@
         <v>3</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G100" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H100" s="31">
         <v>1000000000</v>
@@ -6873,7 +6873,7 @@
         <v>100</v>
       </c>
       <c r="M100" s="26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N100" s="24">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>105501</v>
       </c>
       <c r="C101" s="23" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D101" s="35">
         <v>105501001</v>
@@ -6902,10 +6902,10 @@
         <v>1</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G101" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H101" s="31">
         <v>10000000</v>
@@ -6943,7 +6943,7 @@
         <v>105501</v>
       </c>
       <c r="C102" s="23" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D102" s="35">
         <v>105501001</v>
@@ -6952,10 +6952,10 @@
         <v>2</v>
       </c>
       <c r="F102" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G102" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H102" s="31">
         <v>100000000</v>
@@ -6993,7 +6993,7 @@
         <v>105501</v>
       </c>
       <c r="C103" s="23" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D103" s="35">
         <v>105501001</v>
@@ -7002,10 +7002,10 @@
         <v>3</v>
       </c>
       <c r="F103" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G103" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H103" s="31">
         <v>1000000000</v>
@@ -7043,7 +7043,7 @@
         <v>105502</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D104" s="35">
         <v>105502001</v>
@@ -7052,10 +7052,10 @@
         <v>1</v>
       </c>
       <c r="F104" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G104" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H104" s="31">
         <v>10000000</v>
@@ -7093,7 +7093,7 @@
         <v>105502</v>
       </c>
       <c r="C105" s="23" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D105" s="35">
         <v>105502001</v>
@@ -7102,10 +7102,10 @@
         <v>2</v>
       </c>
       <c r="F105" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G105" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H105" s="31">
         <v>100000000</v>
@@ -7143,7 +7143,7 @@
         <v>105502</v>
       </c>
       <c r="C106" s="23" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D106" s="35">
         <v>105502001</v>
@@ -7152,10 +7152,10 @@
         <v>3</v>
       </c>
       <c r="F106" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G106" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H106" s="31">
         <v>1000000000</v>
@@ -7193,7 +7193,7 @@
         <v>105300</v>
       </c>
       <c r="C107" s="23" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D107" s="35">
         <v>105300001</v>
@@ -7202,10 +7202,10 @@
         <v>1</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G107" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H107" s="31">
         <v>10000000</v>
@@ -7243,7 +7243,7 @@
         <v>105300</v>
       </c>
       <c r="C108" s="23" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D108" s="35">
         <v>105300001</v>
@@ -7252,10 +7252,10 @@
         <v>2</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G108" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H108" s="31">
         <v>100000000</v>
@@ -7293,7 +7293,7 @@
         <v>105300</v>
       </c>
       <c r="C109" s="23" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D109" s="35">
         <v>105300001</v>
@@ -7302,10 +7302,10 @@
         <v>3</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G109" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H109" s="31">
         <v>1000000000</v>
@@ -7376,7 +7376,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O110" s="44"/>
       <c r="P110" s="44"/>
@@ -7426,7 +7426,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O111" s="44"/>
       <c r="P111" s="44"/>
@@ -7476,7 +7476,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O112" s="44"/>
       <c r="P112" s="44"/>
@@ -7526,7 +7526,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O113" s="44"/>
       <c r="P113" s="44"/>
@@ -7576,7 +7576,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O114" s="44"/>
       <c r="P114" s="44"/>
@@ -7626,7 +7626,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O115" s="44"/>
       <c r="P115" s="44"/>
@@ -7652,10 +7652,10 @@
         <v>10</v>
       </c>
       <c r="F116" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G116" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H116" s="53">
         <v>0</v>
@@ -7676,7 +7676,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O116" s="44"/>
       <c r="P116" s="44"/>
@@ -7702,10 +7702,10 @@
         <v>11</v>
       </c>
       <c r="F117" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G117" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H117" s="53">
         <v>0</v>
@@ -7726,7 +7726,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O117" s="44"/>
       <c r="P117" s="44"/>
@@ -7752,10 +7752,10 @@
         <v>12</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G118" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H118" s="57">
         <v>0</v>
@@ -7776,7 +7776,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O118" s="44"/>
       <c r="P118" s="44"/>
@@ -7793,7 +7793,7 @@
         <v>101200</v>
       </c>
       <c r="C119" s="52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D119" s="60">
         <v>101200001</v>
@@ -7826,7 +7826,7 @@
         <v>37</v>
       </c>
       <c r="N119" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O119" s="56"/>
       <c r="P119" s="56"/>
@@ -7843,7 +7843,7 @@
         <v>101200</v>
       </c>
       <c r="C120" s="52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D120" s="60">
         <v>101200001</v>
@@ -7876,7 +7876,7 @@
         <v>40</v>
       </c>
       <c r="N120" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O120" s="56"/>
       <c r="P120" s="56"/>
@@ -7893,7 +7893,7 @@
         <v>101200</v>
       </c>
       <c r="C121" s="52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D121" s="60">
         <v>101200001</v>
@@ -7926,7 +7926,7 @@
         <v>43</v>
       </c>
       <c r="N121" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O121" s="56"/>
       <c r="P121" s="56"/>
@@ -7943,7 +7943,7 @@
         <v>101400</v>
       </c>
       <c r="C122" s="50" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D122" s="51">
         <v>101400001</v>
@@ -7976,7 +7976,7 @@
         <v>37</v>
       </c>
       <c r="N122" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O122" s="44"/>
       <c r="P122" s="44"/>
@@ -7993,7 +7993,7 @@
         <v>101400</v>
       </c>
       <c r="C123" s="50" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D123" s="51">
         <v>101400001</v>
@@ -8026,7 +8026,7 @@
         <v>40</v>
       </c>
       <c r="N123" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O123" s="44"/>
       <c r="P123" s="44"/>
@@ -8043,7 +8043,7 @@
         <v>101400</v>
       </c>
       <c r="C124" s="50" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D124" s="51">
         <v>101400001</v>
@@ -8076,7 +8076,7 @@
         <v>43</v>
       </c>
       <c r="N124" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O124" s="44"/>
       <c r="P124" s="44"/>
@@ -8093,7 +8093,7 @@
         <v>101700</v>
       </c>
       <c r="C125" s="50" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D125" s="51">
         <v>101700001</v>
@@ -8102,10 +8102,10 @@
         <v>10</v>
       </c>
       <c r="F125" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G125" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H125" s="53">
         <v>0</v>
@@ -8126,7 +8126,7 @@
         <v>37</v>
       </c>
       <c r="N125" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O125" s="44"/>
       <c r="P125" s="44"/>
@@ -8143,7 +8143,7 @@
         <v>101700</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D126" s="51">
         <v>101700001</v>
@@ -8152,10 +8152,10 @@
         <v>11</v>
       </c>
       <c r="F126" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G126" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H126" s="53">
         <v>0</v>
@@ -8176,7 +8176,7 @@
         <v>40</v>
       </c>
       <c r="N126" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O126" s="44"/>
       <c r="P126" s="44"/>
@@ -8193,7 +8193,7 @@
         <v>101700</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D127" s="51">
         <v>101700001</v>
@@ -8202,10 +8202,10 @@
         <v>12</v>
       </c>
       <c r="F127" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G127" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H127" s="57">
         <v>0</v>
@@ -8226,7 +8226,7 @@
         <v>43</v>
       </c>
       <c r="N127" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O127" s="44"/>
       <c r="P127" s="44"/>
@@ -8243,7 +8243,7 @@
         <v>102100</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D128" s="51">
         <v>102100001</v>
@@ -8252,10 +8252,10 @@
         <v>10</v>
       </c>
       <c r="F128" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G128" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H128" s="53">
         <v>0</v>
@@ -8276,7 +8276,7 @@
         <v>37</v>
       </c>
       <c r="N128" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O128" s="44"/>
       <c r="P128" s="44"/>
@@ -8293,7 +8293,7 @@
         <v>102100</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D129" s="51">
         <v>102100001</v>
@@ -8302,10 +8302,10 @@
         <v>11</v>
       </c>
       <c r="F129" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G129" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H129" s="53">
         <v>0</v>
@@ -8326,7 +8326,7 @@
         <v>40</v>
       </c>
       <c r="N129" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O129" s="44"/>
       <c r="P129" s="44"/>
@@ -8343,7 +8343,7 @@
         <v>102100</v>
       </c>
       <c r="C130" s="50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D130" s="51">
         <v>102100001</v>
@@ -8352,10 +8352,10 @@
         <v>12</v>
       </c>
       <c r="F130" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G130" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H130" s="57">
         <v>0</v>
@@ -8376,7 +8376,7 @@
         <v>43</v>
       </c>
       <c r="N130" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O130" s="44"/>
       <c r="P130" s="44"/>
@@ -8393,7 +8393,7 @@
         <v>102200</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D131" s="51">
         <v>102200001</v>
@@ -8402,10 +8402,10 @@
         <v>10</v>
       </c>
       <c r="F131" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G131" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H131" s="53">
         <v>0</v>
@@ -8426,7 +8426,7 @@
         <v>37</v>
       </c>
       <c r="N131" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O131" s="44"/>
       <c r="P131" s="44"/>
@@ -8443,7 +8443,7 @@
         <v>102200</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D132" s="51">
         <v>102200001</v>
@@ -8452,10 +8452,10 @@
         <v>11</v>
       </c>
       <c r="F132" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G132" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H132" s="53">
         <v>0</v>
@@ -8476,7 +8476,7 @@
         <v>40</v>
       </c>
       <c r="N132" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O132" s="44"/>
       <c r="P132" s="44"/>
@@ -8493,7 +8493,7 @@
         <v>102200</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D133" s="51">
         <v>102200001</v>
@@ -8502,10 +8502,10 @@
         <v>12</v>
       </c>
       <c r="F133" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G133" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H133" s="57">
         <v>0</v>
@@ -8526,7 +8526,7 @@
         <v>43</v>
       </c>
       <c r="N133" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O133" s="44"/>
       <c r="P133" s="44"/>
@@ -8543,7 +8543,7 @@
         <v>102400</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D134" s="51">
         <v>102400026</v>
@@ -8576,7 +8576,7 @@
         <v>37</v>
       </c>
       <c r="N134" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O134" s="44"/>
       <c r="P134" s="44"/>
@@ -8593,7 +8593,7 @@
         <v>102400</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D135" s="51">
         <v>102400026</v>
@@ -8626,7 +8626,7 @@
         <v>40</v>
       </c>
       <c r="N135" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O135" s="44"/>
       <c r="P135" s="44"/>
@@ -8643,7 +8643,7 @@
         <v>102400</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D136" s="51">
         <v>102400026</v>
@@ -8676,7 +8676,7 @@
         <v>43</v>
       </c>
       <c r="N136" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O136" s="44"/>
       <c r="P136" s="44"/>
@@ -8693,7 +8693,7 @@
         <v>101800</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D137" s="51">
         <v>101800001</v>
@@ -8702,10 +8702,10 @@
         <v>10</v>
       </c>
       <c r="F137" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G137" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H137" s="57">
         <v>0</v>
@@ -8726,7 +8726,7 @@
         <v>37</v>
       </c>
       <c r="N137" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O137" s="44"/>
       <c r="P137" s="44"/>
@@ -8743,7 +8743,7 @@
         <v>101800</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D138" s="51">
         <v>101800001</v>
@@ -8752,10 +8752,10 @@
         <v>11</v>
       </c>
       <c r="F138" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G138" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H138" s="57">
         <v>0</v>
@@ -8776,7 +8776,7 @@
         <v>40</v>
       </c>
       <c r="N138" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O138" s="44"/>
       <c r="P138" s="44"/>
@@ -8793,7 +8793,7 @@
         <v>101800</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D139" s="51">
         <v>101800001</v>
@@ -8802,10 +8802,10 @@
         <v>12</v>
       </c>
       <c r="F139" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G139" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H139" s="57">
         <v>0</v>
@@ -8826,7 +8826,7 @@
         <v>43</v>
       </c>
       <c r="N139" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O139" s="44"/>
       <c r="P139" s="44"/>
@@ -8843,7 +8843,7 @@
         <v>102500</v>
       </c>
       <c r="C140" s="50" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D140" s="51">
         <v>102500001</v>
@@ -8852,10 +8852,10 @@
         <v>10</v>
       </c>
       <c r="F140" s="24" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="G140" s="25" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H140" s="57">
         <v>0</v>
@@ -8876,7 +8876,7 @@
         <v>37</v>
       </c>
       <c r="N140" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O140" s="44"/>
       <c r="P140" s="44"/>
@@ -8893,7 +8893,7 @@
         <v>102500</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D141" s="51">
         <v>102500001</v>
@@ -8902,10 +8902,10 @@
         <v>11</v>
       </c>
       <c r="F141" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G141" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H141" s="57">
         <v>0</v>
@@ -8926,7 +8926,7 @@
         <v>40</v>
       </c>
       <c r="N141" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O141" s="44"/>
       <c r="P141" s="44"/>
@@ -8943,7 +8943,7 @@
         <v>102500</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D142" s="51">
         <v>102500001</v>
@@ -8952,10 +8952,10 @@
         <v>12</v>
       </c>
       <c r="F142" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G142" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H142" s="57">
         <v>0</v>
@@ -8976,7 +8976,7 @@
         <v>43</v>
       </c>
       <c r="N142" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O142" s="44"/>
       <c r="P142" s="44"/>
@@ -8993,7 +8993,7 @@
         <v>102300</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D143" s="51">
         <v>102300001</v>
@@ -9002,10 +9002,10 @@
         <v>10</v>
       </c>
       <c r="F143" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G143" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H143" s="57">
         <v>0</v>
@@ -9026,7 +9026,7 @@
         <v>37</v>
       </c>
       <c r="N143" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O143" s="44"/>
       <c r="P143" s="44"/>
@@ -9043,7 +9043,7 @@
         <v>102300</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D144" s="51">
         <v>102300001</v>
@@ -9052,10 +9052,10 @@
         <v>11</v>
       </c>
       <c r="F144" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G144" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H144" s="57">
         <v>0</v>
@@ -9076,7 +9076,7 @@
         <v>40</v>
       </c>
       <c r="N144" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O144" s="44"/>
       <c r="P144" s="44"/>
@@ -9093,7 +9093,7 @@
         <v>102300</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D145" s="51">
         <v>102300001</v>
@@ -9102,10 +9102,10 @@
         <v>12</v>
       </c>
       <c r="F145" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G145" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H145" s="57">
         <v>0</v>
@@ -9126,7 +9126,7 @@
         <v>43</v>
       </c>
       <c r="N145" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O145" s="44"/>
       <c r="P145" s="44"/>
@@ -9143,7 +9143,7 @@
         <v>103400</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D146" s="51">
         <v>103000001</v>
@@ -9152,10 +9152,10 @@
         <v>10</v>
       </c>
       <c r="F146" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G146" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H146" s="57">
         <v>0</v>
@@ -9176,7 +9176,7 @@
         <v>37</v>
       </c>
       <c r="N146" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O146" s="44"/>
       <c r="P146" s="44"/>
@@ -9193,7 +9193,7 @@
         <v>103400</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D147" s="51">
         <v>103000001</v>
@@ -9202,10 +9202,10 @@
         <v>11</v>
       </c>
       <c r="F147" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G147" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H147" s="57">
         <v>0</v>
@@ -9226,7 +9226,7 @@
         <v>40</v>
       </c>
       <c r="N147" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O147" s="44"/>
       <c r="P147" s="44"/>
@@ -9243,7 +9243,7 @@
         <v>103400</v>
       </c>
       <c r="C148" s="50" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D148" s="51">
         <v>103000001</v>
@@ -9252,10 +9252,10 @@
         <v>12</v>
       </c>
       <c r="F148" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G148" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H148" s="57">
         <v>0</v>
@@ -9276,7 +9276,7 @@
         <v>43</v>
       </c>
       <c r="N148" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O148" s="44"/>
       <c r="P148" s="44"/>
@@ -9293,7 +9293,7 @@
         <v>103500</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D149" s="51">
         <v>102900001</v>
@@ -9326,7 +9326,7 @@
         <v>37</v>
       </c>
       <c r="N149" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O149" s="44"/>
       <c r="P149" s="44"/>
@@ -9343,7 +9343,7 @@
         <v>103500</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D150" s="51">
         <v>102900001</v>
@@ -9376,7 +9376,7 @@
         <v>40</v>
       </c>
       <c r="N150" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O150" s="44"/>
       <c r="P150" s="44"/>
@@ -9393,7 +9393,7 @@
         <v>103500</v>
       </c>
       <c r="C151" s="50" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D151" s="51">
         <v>102900001</v>
@@ -9426,7 +9426,7 @@
         <v>43</v>
       </c>
       <c r="N151" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O151" s="44"/>
       <c r="P151" s="44"/>
@@ -9443,7 +9443,7 @@
         <v>103501</v>
       </c>
       <c r="C152" s="50" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D152" s="51">
         <v>103501001</v>
@@ -9476,7 +9476,7 @@
         <v>37</v>
       </c>
       <c r="N152" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O152" s="44"/>
       <c r="P152" s="44"/>
@@ -9493,7 +9493,7 @@
         <v>103501</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D153" s="51">
         <v>103501001</v>
@@ -9526,7 +9526,7 @@
         <v>40</v>
       </c>
       <c r="N153" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O153" s="44"/>
       <c r="P153" s="44"/>
@@ -9543,7 +9543,7 @@
         <v>103501</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D154" s="51">
         <v>103501001</v>
@@ -9576,7 +9576,7 @@
         <v>43</v>
       </c>
       <c r="N154" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O154" s="44"/>
       <c r="P154" s="44"/>
@@ -9593,7 +9593,7 @@
         <v>103600</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D155" s="51">
         <v>103600001</v>
@@ -9602,10 +9602,10 @@
         <v>10</v>
       </c>
       <c r="F155" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G155" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H155" s="53">
         <v>0</v>
@@ -9626,7 +9626,7 @@
         <v>37</v>
       </c>
       <c r="N155" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O155" s="44"/>
       <c r="P155" s="44"/>
@@ -9643,7 +9643,7 @@
         <v>103600</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D156" s="51">
         <v>103600001</v>
@@ -9652,10 +9652,10 @@
         <v>11</v>
       </c>
       <c r="F156" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G156" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H156" s="53">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>40</v>
       </c>
       <c r="N156" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O156" s="44"/>
       <c r="P156" s="44"/>
@@ -9693,7 +9693,7 @@
         <v>103600</v>
       </c>
       <c r="C157" s="50" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D157" s="51">
         <v>103600001</v>
@@ -9702,10 +9702,10 @@
         <v>12</v>
       </c>
       <c r="F157" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G157" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H157" s="57">
         <v>0</v>
@@ -9726,7 +9726,7 @@
         <v>43</v>
       </c>
       <c r="N157" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O157" s="44"/>
       <c r="P157" s="44"/>
@@ -9743,7 +9743,7 @@
         <v>102800</v>
       </c>
       <c r="C158" s="50" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D158" s="51">
         <v>102800001</v>
@@ -9752,10 +9752,10 @@
         <v>10</v>
       </c>
       <c r="F158" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G158" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H158" s="57">
         <v>0</v>
@@ -9776,7 +9776,7 @@
         <v>37</v>
       </c>
       <c r="N158" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O158" s="44"/>
       <c r="P158" s="44"/>
@@ -9793,7 +9793,7 @@
         <v>102800</v>
       </c>
       <c r="C159" s="50" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D159" s="51">
         <v>102800001</v>
@@ -9802,10 +9802,10 @@
         <v>11</v>
       </c>
       <c r="F159" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G159" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H159" s="57">
         <v>0</v>
@@ -9826,7 +9826,7 @@
         <v>40</v>
       </c>
       <c r="N159" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O159" s="44"/>
       <c r="P159" s="44"/>
@@ -9843,7 +9843,7 @@
         <v>102800</v>
       </c>
       <c r="C160" s="50" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D160" s="51">
         <v>102800001</v>
@@ -9852,10 +9852,10 @@
         <v>12</v>
       </c>
       <c r="F160" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G160" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H160" s="57">
         <v>0</v>
@@ -9876,7 +9876,7 @@
         <v>43</v>
       </c>
       <c r="N160" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O160" s="44"/>
       <c r="P160" s="44"/>
@@ -9893,7 +9893,7 @@
         <v>102000</v>
       </c>
       <c r="C161" s="50" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D161" s="51">
         <v>102000001</v>
@@ -9902,10 +9902,10 @@
         <v>10</v>
       </c>
       <c r="F161" s="24" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="G161" s="25" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="H161" s="57">
         <v>0</v>
@@ -9926,7 +9926,7 @@
         <v>37</v>
       </c>
       <c r="N161" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O161" s="44"/>
       <c r="P161" s="44"/>
@@ -9943,7 +9943,7 @@
         <v>102000</v>
       </c>
       <c r="C162" s="50" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D162" s="51">
         <v>102000001</v>
@@ -9952,10 +9952,10 @@
         <v>11</v>
       </c>
       <c r="F162" s="24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G162" s="25" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H162" s="57">
         <v>0</v>
@@ -9976,7 +9976,7 @@
         <v>40</v>
       </c>
       <c r="N162" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O162" s="44"/>
       <c r="P162" s="44"/>
@@ -9993,7 +9993,7 @@
         <v>102000</v>
       </c>
       <c r="C163" s="50" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D163" s="51">
         <v>102000001</v>
@@ -10002,10 +10002,10 @@
         <v>12</v>
       </c>
       <c r="F163" s="24" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G163" s="25" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H163" s="57">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>43</v>
       </c>
       <c r="N163" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O163" s="44"/>
       <c r="P163" s="44"/>
@@ -10043,7 +10043,7 @@
         <v>103401</v>
       </c>
       <c r="C164" s="50" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D164" s="51">
         <v>103400001</v>
@@ -10052,10 +10052,10 @@
         <v>10</v>
       </c>
       <c r="F164" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G164" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H164" s="57">
         <v>0</v>
@@ -10076,7 +10076,7 @@
         <v>37</v>
       </c>
       <c r="N164" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O164" s="44"/>
       <c r="P164" s="44"/>
@@ -10093,7 +10093,7 @@
         <v>103401</v>
       </c>
       <c r="C165" s="50" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D165" s="51">
         <v>103400001</v>
@@ -10102,10 +10102,10 @@
         <v>11</v>
       </c>
       <c r="F165" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G165" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H165" s="57">
         <v>0</v>
@@ -10126,7 +10126,7 @@
         <v>40</v>
       </c>
       <c r="N165" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O165" s="44"/>
       <c r="P165" s="44"/>
@@ -10143,7 +10143,7 @@
         <v>103401</v>
       </c>
       <c r="C166" s="50" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D166" s="51">
         <v>103400001</v>
@@ -10152,10 +10152,10 @@
         <v>12</v>
       </c>
       <c r="F166" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G166" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H166" s="57">
         <v>0</v>
@@ -10176,7 +10176,7 @@
         <v>43</v>
       </c>
       <c r="N166" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O166" s="44"/>
       <c r="P166" s="44"/>
@@ -10193,7 +10193,7 @@
         <v>103800</v>
       </c>
       <c r="C167" s="50" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D167" s="51">
         <v>103800001</v>
@@ -10202,10 +10202,10 @@
         <v>11</v>
       </c>
       <c r="F167" s="24" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G167" s="25" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H167" s="57">
         <v>0</v>
@@ -10226,7 +10226,7 @@
         <v>37</v>
       </c>
       <c r="N167" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O167" s="44"/>
       <c r="P167" s="44"/>
@@ -10243,7 +10243,7 @@
         <v>103800</v>
       </c>
       <c r="C168" s="50" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D168" s="51">
         <v>103800001</v>
@@ -10252,10 +10252,10 @@
         <v>12</v>
       </c>
       <c r="F168" s="24" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G168" s="25" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H168" s="57">
         <v>0</v>
@@ -10276,7 +10276,7 @@
         <v>40</v>
       </c>
       <c r="N168" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O168" s="44"/>
       <c r="P168" s="44"/>
@@ -10293,7 +10293,7 @@
         <v>103800</v>
       </c>
       <c r="C169" s="50" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D169" s="51">
         <v>103800001</v>
@@ -10302,10 +10302,10 @@
         <v>13</v>
       </c>
       <c r="F169" s="24" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G169" s="25" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H169" s="57">
         <v>0</v>
@@ -10326,7 +10326,7 @@
         <v>43</v>
       </c>
       <c r="N169" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O169" s="44"/>
       <c r="P169" s="44"/>
@@ -10343,7 +10343,7 @@
         <v>102700</v>
       </c>
       <c r="C170" s="50" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D170" s="51">
         <v>102700001</v>
@@ -10352,10 +10352,10 @@
         <v>11</v>
       </c>
       <c r="F170" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G170" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H170" s="57">
         <v>0</v>
@@ -10376,7 +10376,7 @@
         <v>37</v>
       </c>
       <c r="N170" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O170" s="44"/>
       <c r="P170" s="44"/>
@@ -10393,7 +10393,7 @@
         <v>102700</v>
       </c>
       <c r="C171" s="50" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D171" s="51">
         <v>102700001</v>
@@ -10402,10 +10402,10 @@
         <v>12</v>
       </c>
       <c r="F171" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G171" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H171" s="57">
         <v>0</v>
@@ -10426,7 +10426,7 @@
         <v>40</v>
       </c>
       <c r="N171" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O171" s="44"/>
       <c r="P171" s="44"/>
@@ -10443,7 +10443,7 @@
         <v>102700</v>
       </c>
       <c r="C172" s="50" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D172" s="51">
         <v>102700001</v>
@@ -10452,10 +10452,10 @@
         <v>13</v>
       </c>
       <c r="F172" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G172" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H172" s="57">
         <v>0</v>
@@ -10476,7 +10476,7 @@
         <v>43</v>
       </c>
       <c r="N172" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O172" s="44"/>
       <c r="P172" s="44"/>
@@ -10493,7 +10493,7 @@
         <v>103700</v>
       </c>
       <c r="C173" s="50" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D173" s="51">
         <v>103700001</v>
@@ -10526,7 +10526,7 @@
         <v>37</v>
       </c>
       <c r="N173" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O173" s="44"/>
       <c r="P173" s="44"/>
@@ -10543,7 +10543,7 @@
         <v>103700</v>
       </c>
       <c r="C174" s="50" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D174" s="51">
         <v>103700001</v>
@@ -10576,7 +10576,7 @@
         <v>40</v>
       </c>
       <c r="N174" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O174" s="44"/>
       <c r="P174" s="44"/>
@@ -10593,7 +10593,7 @@
         <v>103700</v>
       </c>
       <c r="C175" s="50" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D175" s="51">
         <v>103100001</v>
@@ -10626,7 +10626,7 @@
         <v>43</v>
       </c>
       <c r="N175" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O175" s="44"/>
       <c r="P175" s="44"/>
@@ -10643,7 +10643,7 @@
         <v>103100</v>
       </c>
       <c r="C176" s="50" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D176" s="51">
         <v>103100001</v>
@@ -10652,10 +10652,10 @@
         <v>11</v>
       </c>
       <c r="F176" s="24" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G176" s="25" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H176" s="53">
         <v>0</v>
@@ -10676,7 +10676,7 @@
         <v>37</v>
       </c>
       <c r="N176" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O176" s="44"/>
       <c r="P176" s="44"/>
@@ -10693,7 +10693,7 @@
         <v>103100</v>
       </c>
       <c r="C177" s="50" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D177" s="51">
         <v>103100001</v>
@@ -10702,10 +10702,10 @@
         <v>12</v>
       </c>
       <c r="F177" s="24" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G177" s="25" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H177" s="53">
         <v>0</v>
@@ -10726,7 +10726,7 @@
         <v>40</v>
       </c>
       <c r="N177" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O177" s="44"/>
       <c r="P177" s="44"/>
@@ -10743,7 +10743,7 @@
         <v>103100</v>
       </c>
       <c r="C178" s="50" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D178" s="51">
         <v>103100001</v>
@@ -10752,10 +10752,10 @@
         <v>13</v>
       </c>
       <c r="F178" s="24" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G178" s="25" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H178" s="57">
         <v>0</v>
@@ -10776,7 +10776,7 @@
         <v>43</v>
       </c>
       <c r="N178" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O178" s="44"/>
       <c r="P178" s="44"/>
@@ -10793,7 +10793,7 @@
         <v>104000</v>
       </c>
       <c r="C179" s="50" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D179" s="51">
         <v>104000001</v>
@@ -10802,10 +10802,10 @@
         <v>11</v>
       </c>
       <c r="F179" s="24" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G179" s="25" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H179" s="57">
         <v>0</v>
@@ -10826,7 +10826,7 @@
         <v>37</v>
       </c>
       <c r="N179" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O179" s="44"/>
       <c r="P179" s="44"/>
@@ -10843,7 +10843,7 @@
         <v>104000</v>
       </c>
       <c r="C180" s="50" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D180" s="51">
         <v>104000001</v>
@@ -10852,10 +10852,10 @@
         <v>12</v>
       </c>
       <c r="F180" s="24" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G180" s="25" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H180" s="57">
         <v>0</v>
@@ -10876,7 +10876,7 @@
         <v>40</v>
       </c>
       <c r="N180" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O180" s="44"/>
       <c r="P180" s="44"/>
@@ -10893,7 +10893,7 @@
         <v>104000</v>
       </c>
       <c r="C181" s="50" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D181" s="51">
         <v>104000001</v>
@@ -10902,10 +10902,10 @@
         <v>13</v>
       </c>
       <c r="F181" s="24" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G181" s="25" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H181" s="57">
         <v>0</v>
@@ -10926,7 +10926,7 @@
         <v>43</v>
       </c>
       <c r="N181" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O181" s="44"/>
       <c r="P181" s="44"/>
@@ -10943,7 +10943,7 @@
         <v>103900</v>
       </c>
       <c r="C182" s="50" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D182" s="51">
         <v>103900001</v>
@@ -10952,10 +10952,10 @@
         <v>11</v>
       </c>
       <c r="F182" s="24" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G182" s="25" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H182" s="57">
         <v>0</v>
@@ -10976,7 +10976,7 @@
         <v>37</v>
       </c>
       <c r="N182" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O182" s="44"/>
       <c r="P182" s="44"/>
@@ -10993,7 +10993,7 @@
         <v>103900</v>
       </c>
       <c r="C183" s="50" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D183" s="51">
         <v>103900001</v>
@@ -11002,10 +11002,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="24" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G183" s="25" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H183" s="57">
         <v>0</v>
@@ -11026,7 +11026,7 @@
         <v>40</v>
       </c>
       <c r="N183" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O183" s="44"/>
       <c r="P183" s="44"/>
@@ -11043,7 +11043,7 @@
         <v>103900</v>
       </c>
       <c r="C184" s="50" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D184" s="51">
         <v>103900001</v>
@@ -11052,10 +11052,10 @@
         <v>13</v>
       </c>
       <c r="F184" s="24" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G184" s="25" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H184" s="57">
         <v>0</v>
@@ -11076,7 +11076,7 @@
         <v>43</v>
       </c>
       <c r="N184" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O184" s="44"/>
       <c r="P184" s="44"/>
@@ -11093,7 +11093,7 @@
         <v>101600</v>
       </c>
       <c r="C185" s="50" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D185" s="51">
         <v>101600001</v>
@@ -11102,10 +11102,10 @@
         <v>11</v>
       </c>
       <c r="F185" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G185" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H185" s="57">
         <v>0</v>
@@ -11126,7 +11126,7 @@
         <v>37</v>
       </c>
       <c r="N185" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O185" s="44"/>
       <c r="P185" s="44"/>
@@ -11143,7 +11143,7 @@
         <v>101600</v>
       </c>
       <c r="C186" s="50" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D186" s="51">
         <v>101600001</v>
@@ -11152,10 +11152,10 @@
         <v>12</v>
       </c>
       <c r="F186" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G186" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H186" s="57">
         <v>0</v>
@@ -11176,7 +11176,7 @@
         <v>40</v>
       </c>
       <c r="N186" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O186" s="44"/>
       <c r="P186" s="44"/>
@@ -11193,7 +11193,7 @@
         <v>101600</v>
       </c>
       <c r="C187" s="50" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D187" s="51">
         <v>101600001</v>
@@ -11202,10 +11202,10 @@
         <v>13</v>
       </c>
       <c r="F187" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G187" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H187" s="57">
         <v>0</v>
@@ -11226,7 +11226,7 @@
         <v>43</v>
       </c>
       <c r="N187" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O187" s="44"/>
       <c r="P187" s="44"/>
@@ -11243,7 +11243,7 @@
         <v>101500</v>
       </c>
       <c r="C188" s="50" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D188" s="51">
         <v>101500001</v>
@@ -11252,10 +11252,10 @@
         <v>11</v>
       </c>
       <c r="F188" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G188" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H188" s="57">
         <v>0</v>
@@ -11276,7 +11276,7 @@
         <v>37</v>
       </c>
       <c r="N188" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O188" s="44"/>
       <c r="P188" s="44"/>
@@ -11293,7 +11293,7 @@
         <v>101500</v>
       </c>
       <c r="C189" s="50" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D189" s="51">
         <v>101500001</v>
@@ -11302,10 +11302,10 @@
         <v>12</v>
       </c>
       <c r="F189" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G189" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H189" s="57">
         <v>0</v>
@@ -11326,7 +11326,7 @@
         <v>40</v>
       </c>
       <c r="N189" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O189" s="44"/>
       <c r="P189" s="44"/>
@@ -11343,7 +11343,7 @@
         <v>101500</v>
       </c>
       <c r="C190" s="50" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D190" s="51">
         <v>101500001</v>
@@ -11352,10 +11352,10 @@
         <v>13</v>
       </c>
       <c r="F190" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G190" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H190" s="57">
         <v>0</v>
@@ -11376,7 +11376,7 @@
         <v>43</v>
       </c>
       <c r="N190" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O190" s="44"/>
       <c r="P190" s="44"/>
@@ -11393,7 +11393,7 @@
         <v>102600</v>
       </c>
       <c r="C191" s="50" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D191" s="51">
         <v>102600001</v>
@@ -11402,10 +11402,10 @@
         <v>11</v>
       </c>
       <c r="F191" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G191" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H191" s="57">
         <v>0</v>
@@ -11426,7 +11426,7 @@
         <v>37</v>
       </c>
       <c r="N191" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O191" s="44"/>
       <c r="P191" s="44"/>
@@ -11443,7 +11443,7 @@
         <v>102600</v>
       </c>
       <c r="C192" s="50" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D192" s="51">
         <v>102600001</v>
@@ -11452,10 +11452,10 @@
         <v>12</v>
       </c>
       <c r="F192" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G192" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H192" s="57">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>40</v>
       </c>
       <c r="N192" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O192" s="44"/>
       <c r="P192" s="44"/>
@@ -11493,7 +11493,7 @@
         <v>102600</v>
       </c>
       <c r="C193" s="50" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D193" s="51">
         <v>102600001</v>
@@ -11502,10 +11502,10 @@
         <v>13</v>
       </c>
       <c r="F193" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G193" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H193" s="57">
         <v>0</v>
@@ -11526,7 +11526,7 @@
         <v>43</v>
       </c>
       <c r="N193" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O193" s="44"/>
       <c r="P193" s="44"/>
@@ -11543,7 +11543,7 @@
         <v>105000</v>
       </c>
       <c r="C194" s="50" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D194" s="51">
         <v>105000001</v>
@@ -11552,10 +11552,10 @@
         <v>11</v>
       </c>
       <c r="F194" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G194" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H194" s="57">
         <v>0</v>
@@ -11576,7 +11576,7 @@
         <v>37</v>
       </c>
       <c r="N194" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O194" s="44"/>
       <c r="P194" s="44"/>
@@ -11593,7 +11593,7 @@
         <v>105000</v>
       </c>
       <c r="C195" s="50" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D195" s="51">
         <v>105000001</v>
@@ -11602,10 +11602,10 @@
         <v>12</v>
       </c>
       <c r="F195" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G195" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H195" s="57">
         <v>0</v>
@@ -11626,7 +11626,7 @@
         <v>40</v>
       </c>
       <c r="N195" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O195" s="44"/>
       <c r="P195" s="44"/>
@@ -11643,7 +11643,7 @@
         <v>105000</v>
       </c>
       <c r="C196" s="50" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D196" s="51">
         <v>105000001</v>
@@ -11652,10 +11652,10 @@
         <v>13</v>
       </c>
       <c r="F196" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G196" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H196" s="57">
         <v>0</v>
@@ -11676,7 +11676,7 @@
         <v>43</v>
       </c>
       <c r="N196" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O196" s="44"/>
       <c r="P196" s="44"/>
@@ -11693,7 +11693,7 @@
         <v>105100</v>
       </c>
       <c r="C197" s="50" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D197" s="51">
         <v>105100001</v>
@@ -11726,7 +11726,7 @@
         <v>37</v>
       </c>
       <c r="N197" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O197" s="44"/>
       <c r="P197" s="44"/>
@@ -11743,7 +11743,7 @@
         <v>105100</v>
       </c>
       <c r="C198" s="50" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D198" s="51">
         <v>105100001</v>
@@ -11776,7 +11776,7 @@
         <v>40</v>
       </c>
       <c r="N198" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O198" s="44"/>
       <c r="P198" s="44"/>
@@ -11793,7 +11793,7 @@
         <v>105100</v>
       </c>
       <c r="C199" s="50" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D199" s="51">
         <v>105100001</v>
@@ -11826,7 +11826,7 @@
         <v>43</v>
       </c>
       <c r="N199" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O199" s="44"/>
       <c r="P199" s="44"/>
@@ -11843,7 +11843,7 @@
         <v>105400</v>
       </c>
       <c r="C200" s="50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D200" s="51">
         <v>105400001</v>
@@ -11852,10 +11852,10 @@
         <v>11</v>
       </c>
       <c r="F200" s="24" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G200" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H200" s="57">
         <v>0</v>
@@ -11873,10 +11873,10 @@
         <v>0</v>
       </c>
       <c r="M200" s="26" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N200" s="56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O200" s="44"/>
       <c r="P200" s="44"/>
@@ -11893,7 +11893,7 @@
         <v>105400</v>
       </c>
       <c r="C201" s="50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D201" s="51">
         <v>105400001</v>
@@ -11902,10 +11902,10 @@
         <v>12</v>
       </c>
       <c r="F201" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G201" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H201" s="57">
         <v>0</v>
@@ -11923,10 +11923,10 @@
         <v>0</v>
       </c>
       <c r="M201" s="26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N201" s="56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O201" s="44"/>
       <c r="P201" s="44"/>
@@ -11943,7 +11943,7 @@
         <v>105400</v>
       </c>
       <c r="C202" s="50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D202" s="51">
         <v>105400001</v>
@@ -11952,10 +11952,10 @@
         <v>13</v>
       </c>
       <c r="F202" s="24" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G202" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H202" s="57">
         <v>0</v>
@@ -11973,10 +11973,10 @@
         <v>0</v>
       </c>
       <c r="M202" s="26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N202" s="56" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O202" s="44"/>
       <c r="P202" s="44"/>
@@ -11993,7 +11993,7 @@
         <v>100800</v>
       </c>
       <c r="C203" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D203" s="35">
         <v>100800001</v>
@@ -12002,10 +12002,10 @@
         <v>11</v>
       </c>
       <c r="F203" s="24" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G203" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H203" s="31">
         <v>0</v>
@@ -12023,10 +12023,10 @@
         <v>0</v>
       </c>
       <c r="M203" s="26" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N203" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:20">
@@ -12037,7 +12037,7 @@
         <v>100800</v>
       </c>
       <c r="C204" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D204" s="35">
         <v>100800001</v>
@@ -12046,10 +12046,10 @@
         <v>12</v>
       </c>
       <c r="F204" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G204" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H204" s="31">
         <v>0</v>
@@ -12067,10 +12067,10 @@
         <v>0</v>
       </c>
       <c r="M204" s="26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N204" s="24" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:20">
@@ -12081,7 +12081,7 @@
         <v>100800</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D205" s="35">
         <v>100800001</v>
@@ -12090,10 +12090,10 @@
         <v>13</v>
       </c>
       <c r="F205" s="24" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G205" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H205" s="31">
         <v>0</v>
@@ -12111,10 +12111,10 @@
         <v>0</v>
       </c>
       <c r="M205" s="26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N205" s="24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:20">
@@ -12125,7 +12125,7 @@
         <v>105300</v>
       </c>
       <c r="C206" s="23" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D206" s="35">
         <v>105300001</v>
@@ -12134,10 +12134,10 @@
         <v>11</v>
       </c>
       <c r="F206" s="24" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G206" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H206" s="31">
         <v>0</v>
@@ -12155,10 +12155,10 @@
         <v>0</v>
       </c>
       <c r="M206" s="26" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N206" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:20">
@@ -12169,7 +12169,7 @@
         <v>105300</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D207" s="35">
         <v>105300001</v>
@@ -12178,10 +12178,10 @@
         <v>12</v>
       </c>
       <c r="F207" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G207" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H207" s="31">
         <v>0</v>
@@ -12199,10 +12199,10 @@
         <v>0</v>
       </c>
       <c r="M207" s="26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N207" s="24" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:20">
@@ -12213,7 +12213,7 @@
         <v>105300</v>
       </c>
       <c r="C208" s="23" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D208" s="35">
         <v>105300001</v>
@@ -12222,10 +12222,10 @@
         <v>13</v>
       </c>
       <c r="F208" s="24" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G208" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H208" s="31">
         <v>0</v>
@@ -12243,10 +12243,10 @@
         <v>0</v>
       </c>
       <c r="M208" s="26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N208" s="24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:14">
@@ -12257,7 +12257,7 @@
         <v>105700</v>
       </c>
       <c r="C209" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D209" s="35">
         <v>105700001</v>
@@ -12266,10 +12266,10 @@
         <v>11</v>
       </c>
       <c r="F209" s="24" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G209" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H209" s="31">
         <v>0</v>
@@ -12287,10 +12287,10 @@
         <v>0</v>
       </c>
       <c r="M209" s="26" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N209" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:14">
@@ -12301,7 +12301,7 @@
         <v>105700</v>
       </c>
       <c r="C210" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D210" s="35">
         <v>105700001</v>
@@ -12310,10 +12310,10 @@
         <v>12</v>
       </c>
       <c r="F210" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G210" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H210" s="31">
         <v>0</v>
@@ -12331,10 +12331,10 @@
         <v>0</v>
       </c>
       <c r="M210" s="26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N210" s="24" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:14">
@@ -12345,7 +12345,7 @@
         <v>105700</v>
       </c>
       <c r="C211" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D211" s="35">
         <v>105700001</v>
@@ -12354,10 +12354,10 @@
         <v>13</v>
       </c>
       <c r="F211" s="24" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G211" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H211" s="31">
         <v>0</v>
@@ -12375,10 +12375,10 @@
         <v>0</v>
       </c>
       <c r="M211" s="26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N211" s="24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="212" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12389,7 +12389,7 @@
         <v>105800</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D212" s="61">
         <v>105800001</v>
@@ -12398,10 +12398,10 @@
         <v>11</v>
       </c>
       <c r="F212" s="24" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G212" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H212" s="31">
         <v>0</v>
@@ -12419,10 +12419,10 @@
         <v>0</v>
       </c>
       <c r="M212" s="26" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N212" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="213" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12433,7 +12433,7 @@
         <v>105800</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D213" s="61">
         <v>105800001</v>
@@ -12442,10 +12442,10 @@
         <v>12</v>
       </c>
       <c r="F213" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G213" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H213" s="31">
         <v>0</v>
@@ -12463,10 +12463,10 @@
         <v>0</v>
       </c>
       <c r="M213" s="26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N213" s="24" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="214" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12477,7 +12477,7 @@
         <v>105800</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D214" s="61">
         <v>105800001</v>
@@ -12486,10 +12486,10 @@
         <v>13</v>
       </c>
       <c r="F214" s="24" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G214" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H214" s="31">
         <v>0</v>
@@ -12507,10 +12507,10 @@
         <v>0</v>
       </c>
       <c r="M214" s="26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N214" s="24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="215" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12521,7 +12521,7 @@
         <v>105500</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D215" s="61">
         <v>105500001</v>
@@ -12530,10 +12530,10 @@
         <v>11</v>
       </c>
       <c r="F215" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G215" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H215" s="31">
         <v>0</v>
@@ -12551,10 +12551,10 @@
         <v>0</v>
       </c>
       <c r="M215" s="26" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N215" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="216" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12565,7 +12565,7 @@
         <v>105500</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D216" s="61">
         <v>105500001</v>
@@ -12574,10 +12574,10 @@
         <v>12</v>
       </c>
       <c r="F216" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G216" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H216" s="31">
         <v>0</v>
@@ -12595,10 +12595,10 @@
         <v>0</v>
       </c>
       <c r="M216" s="26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N216" s="24" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="217" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12609,7 +12609,7 @@
         <v>105500</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D217" s="61">
         <v>105500001</v>
@@ -12618,10 +12618,10 @@
         <v>13</v>
       </c>
       <c r="F217" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G217" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H217" s="31">
         <v>0</v>
@@ -12639,10 +12639,10 @@
         <v>0</v>
       </c>
       <c r="M217" s="26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N217" s="24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:14">
@@ -12653,7 +12653,7 @@
         <v>104800</v>
       </c>
       <c r="C218" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D218" s="27">
         <v>104800001</v>
@@ -12662,10 +12662,10 @@
         <v>11</v>
       </c>
       <c r="F218" s="24" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G218" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H218" s="31">
         <v>0</v>
@@ -12683,10 +12683,10 @@
         <v>0</v>
       </c>
       <c r="M218" s="26" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N218" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:14">
@@ -12697,7 +12697,7 @@
         <v>104800</v>
       </c>
       <c r="C219" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D219" s="27">
         <v>104800001</v>
@@ -12706,10 +12706,10 @@
         <v>12</v>
       </c>
       <c r="F219" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G219" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H219" s="31">
         <v>0</v>
@@ -12727,10 +12727,10 @@
         <v>0</v>
       </c>
       <c r="M219" s="26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N219" s="24" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:14">
@@ -12741,7 +12741,7 @@
         <v>104800</v>
       </c>
       <c r="C220" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D220" s="27">
         <v>104800001</v>
@@ -12750,10 +12750,10 @@
         <v>13</v>
       </c>
       <c r="F220" s="24" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G220" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H220" s="31">
         <v>0</v>
@@ -12771,10 +12771,10 @@
         <v>0</v>
       </c>
       <c r="M220" s="26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N220" s="24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="221" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12785,7 +12785,7 @@
         <v>105501</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D221" s="61">
         <v>105501001</v>
@@ -12794,10 +12794,10 @@
         <v>11</v>
       </c>
       <c r="F221" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G221" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H221" s="31">
         <v>0</v>
@@ -12815,10 +12815,10 @@
         <v>0</v>
       </c>
       <c r="M221" s="26" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N221" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="222" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12829,7 +12829,7 @@
         <v>105501</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D222" s="61">
         <v>105501001</v>
@@ -12838,10 +12838,10 @@
         <v>12</v>
       </c>
       <c r="F222" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G222" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H222" s="31">
         <v>0</v>
@@ -12859,10 +12859,10 @@
         <v>0</v>
       </c>
       <c r="M222" s="26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N222" s="24" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="223" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12873,7 +12873,7 @@
         <v>105501</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D223" s="61">
         <v>105501001</v>
@@ -12882,10 +12882,10 @@
         <v>13</v>
       </c>
       <c r="F223" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G223" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H223" s="31">
         <v>0</v>
@@ -12903,10 +12903,10 @@
         <v>0</v>
       </c>
       <c r="M223" s="26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N223" s="24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="224" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12917,7 +12917,7 @@
         <v>105502</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D224" s="61">
         <v>105502001</v>
@@ -12926,10 +12926,10 @@
         <v>11</v>
       </c>
       <c r="F224" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G224" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H224" s="31">
         <v>0</v>
@@ -12947,10 +12947,10 @@
         <v>0</v>
       </c>
       <c r="M224" s="26" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N224" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="225" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -12961,7 +12961,7 @@
         <v>105502</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D225" s="61">
         <v>105502001</v>
@@ -12970,10 +12970,10 @@
         <v>12</v>
       </c>
       <c r="F225" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G225" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H225" s="31">
         <v>0</v>
@@ -12991,10 +12991,10 @@
         <v>0</v>
       </c>
       <c r="M225" s="26" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N225" s="24" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="226" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -13005,7 +13005,7 @@
         <v>105502</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D226" s="61">
         <v>105502001</v>
@@ -13014,10 +13014,10 @@
         <v>13</v>
       </c>
       <c r="F226" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G226" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H226" s="31">
         <v>0</v>
@@ -13035,10 +13035,10 @@
         <v>0</v>
       </c>
       <c r="M226" s="26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N226" s="24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="227" customFormat="1" ht="16.5" spans="1:20">
@@ -13049,7 +13049,7 @@
         <v>104100</v>
       </c>
       <c r="C227" s="63" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D227" s="27">
         <v>104100001</v>
@@ -13058,10 +13058,10 @@
         <v>11</v>
       </c>
       <c r="F227" s="47" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G227" s="64" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H227" s="65">
         <v>0</v>
@@ -13079,10 +13079,10 @@
         <v>0</v>
       </c>
       <c r="M227" s="48" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N227" s="47" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="228" customFormat="1" ht="16.5" spans="1:20">
@@ -13093,7 +13093,7 @@
         <v>104100</v>
       </c>
       <c r="C228" s="63" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D228" s="27">
         <v>104100001</v>
@@ -13102,10 +13102,10 @@
         <v>12</v>
       </c>
       <c r="F228" s="47" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G228" s="64" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H228" s="65">
         <v>0</v>
@@ -13123,10 +13123,10 @@
         <v>0</v>
       </c>
       <c r="M228" s="48" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N228" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="229" customFormat="1" ht="16.5" spans="1:20">
@@ -13137,7 +13137,7 @@
         <v>104100</v>
       </c>
       <c r="C229" s="63" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D229" s="27">
         <v>104100001</v>
@@ -13146,10 +13146,10 @@
         <v>13</v>
       </c>
       <c r="F229" s="47" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G229" s="64" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H229" s="65">
         <v>0</v>
@@ -13167,10 +13167,10 @@
         <v>0</v>
       </c>
       <c r="M229" s="48" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N229" s="47" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="230" customFormat="1" ht="16.5" spans="1:20">
@@ -13181,7 +13181,7 @@
         <v>104200</v>
       </c>
       <c r="C230" s="63" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D230" s="27">
         <v>104200001</v>
@@ -13190,10 +13190,10 @@
         <v>11</v>
       </c>
       <c r="F230" s="47" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G230" s="64" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H230" s="65">
         <v>0</v>
@@ -13211,10 +13211,10 @@
         <v>0</v>
       </c>
       <c r="M230" s="48" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N230" s="47" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="231" customFormat="1" ht="16.5" spans="1:20">
@@ -13225,7 +13225,7 @@
         <v>104200</v>
       </c>
       <c r="C231" s="63" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D231" s="27">
         <v>104200001</v>
@@ -13234,10 +13234,10 @@
         <v>12</v>
       </c>
       <c r="F231" s="47" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G231" s="64" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H231" s="65">
         <v>0</v>
@@ -13255,10 +13255,10 @@
         <v>0</v>
       </c>
       <c r="M231" s="48" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N231" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="232" customFormat="1" ht="16.5" spans="1:20">
@@ -13269,7 +13269,7 @@
         <v>104200</v>
       </c>
       <c r="C232" s="63" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D232" s="27">
         <v>104200001</v>
@@ -13278,10 +13278,10 @@
         <v>13</v>
       </c>
       <c r="F232" s="47" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G232" s="64" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H232" s="65">
         <v>0</v>
@@ -13299,10 +13299,10 @@
         <v>0</v>
       </c>
       <c r="M232" s="48" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N232" s="47" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="233" s="2" customFormat="1" ht="16.5" spans="1:20">
@@ -13622,10 +13622,10 @@
         <v>21</v>
       </c>
       <c r="F239" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G239" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H239" s="17">
         <v>10000000</v>
@@ -13672,10 +13672,10 @@
         <v>22</v>
       </c>
       <c r="F240" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G240" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H240" s="17">
         <v>100000000</v>
@@ -13722,10 +13722,10 @@
         <v>23</v>
       </c>
       <c r="F241" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G241" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H241" s="31">
         <v>1000000000</v>
@@ -13763,7 +13763,7 @@
         <v>101200</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D242" s="27">
         <v>101200001</v>
@@ -13772,10 +13772,10 @@
         <v>21</v>
       </c>
       <c r="F242" s="32" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="G242" s="33" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="H242" s="17">
         <v>10000000</v>
@@ -13813,7 +13813,7 @@
         <v>101200</v>
       </c>
       <c r="C243" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D243" s="27">
         <v>101200001</v>
@@ -13863,7 +13863,7 @@
         <v>101200</v>
       </c>
       <c r="C244" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D244" s="27">
         <v>101200001</v>
@@ -13913,7 +13913,7 @@
         <v>101400</v>
       </c>
       <c r="C245" s="23" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D245" s="27">
         <v>101400001</v>
@@ -13963,7 +13963,7 @@
         <v>101400</v>
       </c>
       <c r="C246" s="23" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D246" s="27">
         <v>101400001</v>
@@ -14013,7 +14013,7 @@
         <v>101400</v>
       </c>
       <c r="C247" s="23" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D247" s="27">
         <v>101400001</v>
@@ -14063,7 +14063,7 @@
         <v>101700</v>
       </c>
       <c r="C248" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D248" s="27">
         <v>101700001</v>
@@ -14072,10 +14072,10 @@
         <v>21</v>
       </c>
       <c r="F248" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G248" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H248" s="17">
         <v>10000000</v>
@@ -14113,7 +14113,7 @@
         <v>101700</v>
       </c>
       <c r="C249" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D249" s="27">
         <v>101700001</v>
@@ -14122,10 +14122,10 @@
         <v>22</v>
       </c>
       <c r="F249" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G249" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H249" s="17">
         <v>100000000</v>
@@ -14163,7 +14163,7 @@
         <v>101700</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D250" s="27">
         <v>101700001</v>
@@ -14172,10 +14172,10 @@
         <v>23</v>
       </c>
       <c r="F250" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G250" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H250" s="31">
         <v>1000000000</v>
@@ -14213,7 +14213,7 @@
         <v>102100</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D251" s="27">
         <v>102100001</v>
@@ -14222,10 +14222,10 @@
         <v>21</v>
       </c>
       <c r="F251" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G251" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H251" s="17">
         <v>10000000</v>
@@ -14263,7 +14263,7 @@
         <v>102100</v>
       </c>
       <c r="C252" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D252" s="27">
         <v>102100001</v>
@@ -14272,10 +14272,10 @@
         <v>22</v>
       </c>
       <c r="F252" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G252" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H252" s="17">
         <v>100000000</v>
@@ -14313,7 +14313,7 @@
         <v>102100</v>
       </c>
       <c r="C253" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D253" s="27">
         <v>102100001</v>
@@ -14322,10 +14322,10 @@
         <v>23</v>
       </c>
       <c r="F253" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G253" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H253" s="31">
         <v>1000000000</v>
@@ -14363,7 +14363,7 @@
         <v>102200</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D254" s="27">
         <v>102200001</v>
@@ -14372,10 +14372,10 @@
         <v>21</v>
       </c>
       <c r="F254" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G254" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H254" s="17">
         <v>10000000</v>
@@ -14413,7 +14413,7 @@
         <v>102200</v>
       </c>
       <c r="C255" s="23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D255" s="27">
         <v>102200001</v>
@@ -14422,10 +14422,10 @@
         <v>22</v>
       </c>
       <c r="F255" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G255" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H255" s="17">
         <v>100000000</v>
@@ -14463,7 +14463,7 @@
         <v>102200</v>
       </c>
       <c r="C256" s="23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D256" s="27">
         <v>102200001</v>
@@ -14472,10 +14472,10 @@
         <v>23</v>
       </c>
       <c r="F256" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G256" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H256" s="31">
         <v>1000000000</v>
@@ -14513,7 +14513,7 @@
         <v>102400</v>
       </c>
       <c r="C257" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D257" s="27">
         <v>102400026</v>
@@ -14522,10 +14522,10 @@
         <v>21</v>
       </c>
       <c r="F257" s="32" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G257" s="33" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H257" s="17">
         <v>10000000</v>
@@ -14563,7 +14563,7 @@
         <v>102400</v>
       </c>
       <c r="C258" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D258" s="27">
         <v>102400026</v>
@@ -14613,7 +14613,7 @@
         <v>102400</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D259" s="27">
         <v>102400026</v>
@@ -14663,7 +14663,7 @@
         <v>101800</v>
       </c>
       <c r="C260" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D260" s="27">
         <v>101800001</v>
@@ -14672,10 +14672,10 @@
         <v>21</v>
       </c>
       <c r="F260" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G260" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H260" s="17">
         <v>10000000</v>
@@ -14713,7 +14713,7 @@
         <v>101800</v>
       </c>
       <c r="C261" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D261" s="27">
         <v>101800001</v>
@@ -14722,10 +14722,10 @@
         <v>22</v>
       </c>
       <c r="F261" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G261" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H261" s="17">
         <v>100000000</v>
@@ -14763,7 +14763,7 @@
         <v>101800</v>
       </c>
       <c r="C262" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D262" s="27">
         <v>101800001</v>
@@ -14772,10 +14772,10 @@
         <v>23</v>
       </c>
       <c r="F262" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G262" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H262" s="31">
         <v>1000000000</v>
@@ -14813,7 +14813,7 @@
         <v>102500</v>
       </c>
       <c r="C263" s="23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D263" s="27">
         <v>102500001</v>
@@ -14822,10 +14822,10 @@
         <v>21</v>
       </c>
       <c r="F263" s="24" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="G263" s="25" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H263" s="17">
         <v>10000000</v>
@@ -14863,7 +14863,7 @@
         <v>102500</v>
       </c>
       <c r="C264" s="23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D264" s="27">
         <v>102500001</v>
@@ -14872,10 +14872,10 @@
         <v>22</v>
       </c>
       <c r="F264" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G264" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H264" s="17">
         <v>100000000</v>
@@ -14913,7 +14913,7 @@
         <v>102500</v>
       </c>
       <c r="C265" s="23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D265" s="27">
         <v>102500001</v>
@@ -14922,10 +14922,10 @@
         <v>23</v>
       </c>
       <c r="F265" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G265" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H265" s="31">
         <v>1000000000</v>
@@ -14963,7 +14963,7 @@
         <v>102300</v>
       </c>
       <c r="C266" s="23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D266" s="27">
         <v>102300001</v>
@@ -14972,10 +14972,10 @@
         <v>21</v>
       </c>
       <c r="F266" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G266" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H266" s="17">
         <v>10000000</v>
@@ -15013,7 +15013,7 @@
         <v>102300</v>
       </c>
       <c r="C267" s="23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D267" s="27">
         <v>102300001</v>
@@ -15022,10 +15022,10 @@
         <v>22</v>
       </c>
       <c r="F267" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G267" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H267" s="17">
         <v>100000000</v>
@@ -15063,7 +15063,7 @@
         <v>102300</v>
       </c>
       <c r="C268" s="23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D268" s="27">
         <v>102300001</v>
@@ -15072,10 +15072,10 @@
         <v>23</v>
       </c>
       <c r="F268" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G268" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H268" s="31">
         <v>1000000000</v>
@@ -15113,7 +15113,7 @@
         <v>103400</v>
       </c>
       <c r="C269" s="23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D269" s="27">
         <v>103000001</v>
@@ -15122,10 +15122,10 @@
         <v>21</v>
       </c>
       <c r="F269" s="32" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G269" s="33" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H269" s="17">
         <v>10000000</v>
@@ -15163,7 +15163,7 @@
         <v>103400</v>
       </c>
       <c r="C270" s="23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D270" s="27">
         <v>103000001</v>
@@ -15172,10 +15172,10 @@
         <v>22</v>
       </c>
       <c r="F270" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G270" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H270" s="17">
         <v>100000000</v>
@@ -15213,7 +15213,7 @@
         <v>103400</v>
       </c>
       <c r="C271" s="23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D271" s="27">
         <v>103000001</v>
@@ -15222,10 +15222,10 @@
         <v>23</v>
       </c>
       <c r="F271" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G271" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H271" s="31">
         <v>1000000000</v>
@@ -15263,7 +15263,7 @@
         <v>103500</v>
       </c>
       <c r="C272" s="23" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D272" s="35">
         <v>102900001</v>
@@ -15313,7 +15313,7 @@
         <v>103500</v>
       </c>
       <c r="C273" s="23" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D273" s="35">
         <v>102900001</v>
@@ -15363,7 +15363,7 @@
         <v>103500</v>
       </c>
       <c r="C274" s="23" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D274" s="35">
         <v>102900001</v>
@@ -15413,7 +15413,7 @@
         <v>103501</v>
       </c>
       <c r="C275" s="23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D275" s="35">
         <v>103501001</v>
@@ -15463,7 +15463,7 @@
         <v>103501</v>
       </c>
       <c r="C276" s="23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D276" s="35">
         <v>103501001</v>
@@ -15513,7 +15513,7 @@
         <v>103501</v>
       </c>
       <c r="C277" s="23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D277" s="35">
         <v>103501001</v>
@@ -15563,7 +15563,7 @@
         <v>103600</v>
       </c>
       <c r="C278" s="37" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D278" s="38">
         <v>103600001</v>
@@ -15572,10 +15572,10 @@
         <v>21</v>
       </c>
       <c r="F278" s="39" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G278" s="40" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H278" s="41">
         <v>10000000</v>
@@ -15613,7 +15613,7 @@
         <v>103600</v>
       </c>
       <c r="C279" s="23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D279" s="35">
         <v>103600001</v>
@@ -15622,10 +15622,10 @@
         <v>22</v>
       </c>
       <c r="F279" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G279" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H279" s="31">
         <v>100000000</v>
@@ -15663,7 +15663,7 @@
         <v>103600</v>
       </c>
       <c r="C280" s="23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D280" s="35">
         <v>103600001</v>
@@ -15672,10 +15672,10 @@
         <v>23</v>
       </c>
       <c r="F280" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G280" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H280" s="31">
         <v>1000000000</v>
@@ -15713,7 +15713,7 @@
         <v>102000</v>
       </c>
       <c r="C281" s="23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D281" s="35">
         <v>102000001</v>
@@ -15722,10 +15722,10 @@
         <v>21</v>
       </c>
       <c r="F281" s="24" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="G281" s="25" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="H281" s="31">
         <v>10000000</v>
@@ -15763,7 +15763,7 @@
         <v>102000</v>
       </c>
       <c r="C282" s="23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D282" s="35">
         <v>102000001</v>
@@ -15772,10 +15772,10 @@
         <v>22</v>
       </c>
       <c r="F282" s="24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G282" s="25" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H282" s="31">
         <v>100000000</v>
@@ -15813,7 +15813,7 @@
         <v>102000</v>
       </c>
       <c r="C283" s="23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D283" s="35">
         <v>102000001</v>
@@ -15822,10 +15822,10 @@
         <v>23</v>
       </c>
       <c r="F283" s="24" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G283" s="25" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H283" s="31">
         <v>1000000000</v>
@@ -15863,7 +15863,7 @@
         <v>103401</v>
       </c>
       <c r="C284" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D284" s="35">
         <v>103400001</v>
@@ -15872,10 +15872,10 @@
         <v>21</v>
       </c>
       <c r="F284" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G284" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H284" s="31">
         <v>10000000</v>
@@ -15913,7 +15913,7 @@
         <v>103401</v>
       </c>
       <c r="C285" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D285" s="35">
         <v>103400001</v>
@@ -15922,10 +15922,10 @@
         <v>22</v>
       </c>
       <c r="F285" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G285" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H285" s="31">
         <v>100000000</v>
@@ -15963,7 +15963,7 @@
         <v>103401</v>
       </c>
       <c r="C286" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D286" s="35">
         <v>103400001</v>
@@ -15972,10 +15972,10 @@
         <v>23</v>
       </c>
       <c r="F286" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G286" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H286" s="31">
         <v>1000000000</v>
@@ -16013,7 +16013,7 @@
         <v>103800</v>
       </c>
       <c r="C287" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D287" s="35">
         <v>103800001</v>
@@ -16022,10 +16022,10 @@
         <v>21</v>
       </c>
       <c r="F287" s="24" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G287" s="25" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H287" s="31">
         <v>10000000</v>
@@ -16063,7 +16063,7 @@
         <v>103800</v>
       </c>
       <c r="C288" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D288" s="35">
         <v>103800001</v>
@@ -16072,10 +16072,10 @@
         <v>22</v>
       </c>
       <c r="F288" s="24" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G288" s="25" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H288" s="31">
         <v>100000000</v>
@@ -16113,7 +16113,7 @@
         <v>103800</v>
       </c>
       <c r="C289" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D289" s="35">
         <v>103800001</v>
@@ -16122,10 +16122,10 @@
         <v>23</v>
       </c>
       <c r="F289" s="24" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G289" s="25" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H289" s="31">
         <v>1000000000</v>
@@ -16163,7 +16163,7 @@
         <v>104000</v>
       </c>
       <c r="C290" s="23" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D290" s="35">
         <v>104000001</v>
@@ -16172,10 +16172,10 @@
         <v>21</v>
       </c>
       <c r="F290" s="24" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G290" s="25" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H290" s="31">
         <v>10000000</v>
@@ -16213,7 +16213,7 @@
         <v>104000</v>
       </c>
       <c r="C291" s="23" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D291" s="35">
         <v>104000001</v>
@@ -16222,10 +16222,10 @@
         <v>22</v>
       </c>
       <c r="F291" s="24" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G291" s="25" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H291" s="31">
         <v>100000000</v>
@@ -16263,7 +16263,7 @@
         <v>104000</v>
       </c>
       <c r="C292" s="23" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D292" s="35">
         <v>104000001</v>
@@ -16272,10 +16272,10 @@
         <v>23</v>
       </c>
       <c r="F292" s="24" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G292" s="25" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H292" s="31">
         <v>1000000000</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="136">
   <si>
     <t>id</t>
   </si>
@@ -449,10 +449,7 @@
     <t>恶魔之子</t>
   </si>
   <si>
-    <t>25_50_125_200_300_400_500</t>
-  </si>
-  <si>
-    <t>25:1</t>
+    <t>5:1</t>
   </si>
   <si>
     <t>250_500_1250_2000_3000_4000_5000</t>
@@ -492,6 +489,12 @@
   </si>
   <si>
     <t>潘金莲</t>
+  </si>
+  <si>
+    <t>25_50_125_200_300_400_500</t>
+  </si>
+  <si>
+    <t>25:1</t>
   </si>
   <si>
     <t>愤怒的小鸡</t>
@@ -805,13 +808,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -824,9 +820,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -836,6 +832,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -4951,11 +4954,11 @@
       <c r="E62" s="23">
         <v>1</v>
       </c>
-      <c r="F62" s="24" t="s">
+      <c r="F62" s="24">
+        <v>5</v>
+      </c>
+      <c r="G62" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="G62" s="25" t="s">
-        <v>88</v>
       </c>
       <c r="H62" s="31">
         <v>10000000</v>
@@ -5002,10 +5005,10 @@
         <v>2</v>
       </c>
       <c r="F63" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G63" s="25" t="s">
         <v>89</v>
-      </c>
-      <c r="G63" s="25" t="s">
-        <v>90</v>
       </c>
       <c r="H63" s="31">
         <v>100000000</v>
@@ -5052,10 +5055,10 @@
         <v>3</v>
       </c>
       <c r="F64" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G64" s="25" t="s">
         <v>91</v>
-      </c>
-      <c r="G64" s="25" t="s">
-        <v>92</v>
       </c>
       <c r="H64" s="31">
         <v>1000000000</v>
@@ -5093,7 +5096,7 @@
         <v>102700</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D65" s="35">
         <v>102700001</v>
@@ -5143,7 +5146,7 @@
         <v>102700</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D66" s="35">
         <v>102700001</v>
@@ -5193,7 +5196,7 @@
         <v>102700</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D67" s="35">
         <v>102700001</v>
@@ -5243,7 +5246,7 @@
         <v>103700</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D68" s="35">
         <v>103700001</v>
@@ -5293,7 +5296,7 @@
         <v>103700</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D69" s="35">
         <v>103700001</v>
@@ -5343,7 +5346,7 @@
         <v>103700</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D70" s="35">
         <v>103700001</v>
@@ -5393,7 +5396,7 @@
         <v>103100</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D71" s="35">
         <v>103100001</v>
@@ -5405,7 +5408,7 @@
         <v>40</v>
       </c>
       <c r="G71" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H71" s="31">
         <v>10000000</v>
@@ -5443,7 +5446,7 @@
         <v>103100</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D72" s="35">
         <v>103100001</v>
@@ -5452,10 +5455,10 @@
         <v>2</v>
       </c>
       <c r="F72" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G72" s="25" t="s">
         <v>97</v>
-      </c>
-      <c r="G72" s="25" t="s">
-        <v>98</v>
       </c>
       <c r="H72" s="31">
         <v>100000000</v>
@@ -5493,7 +5496,7 @@
         <v>103100</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D73" s="35">
         <v>103100001</v>
@@ -5502,10 +5505,10 @@
         <v>3</v>
       </c>
       <c r="F73" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="G73" s="25" t="s">
         <v>99</v>
-      </c>
-      <c r="G73" s="25" t="s">
-        <v>100</v>
       </c>
       <c r="H73" s="31">
         <v>1000000000</v>
@@ -5543,7 +5546,7 @@
         <v>104000</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D74" s="35">
         <v>104000001</v>
@@ -5552,10 +5555,10 @@
         <v>1</v>
       </c>
       <c r="F74" s="24" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H74" s="31">
         <v>10000000</v>
@@ -5593,7 +5596,7 @@
         <v>104000</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D75" s="35">
         <v>104000001</v>
@@ -5602,10 +5605,10 @@
         <v>2</v>
       </c>
       <c r="F75" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G75" s="25" t="s">
         <v>89</v>
-      </c>
-      <c r="G75" s="25" t="s">
-        <v>90</v>
       </c>
       <c r="H75" s="31">
         <v>100000000</v>
@@ -5643,7 +5646,7 @@
         <v>104000</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D76" s="35">
         <v>104000001</v>
@@ -5652,10 +5655,10 @@
         <v>3</v>
       </c>
       <c r="F76" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G76" s="25" t="s">
         <v>91</v>
-      </c>
-      <c r="G76" s="25" t="s">
-        <v>92</v>
       </c>
       <c r="H76" s="31">
         <v>1000000000</v>
@@ -5693,7 +5696,7 @@
         <v>103900</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D77" s="35">
         <v>103900001</v>
@@ -5743,7 +5746,7 @@
         <v>103900</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D78" s="35">
         <v>103900001</v>
@@ -5752,10 +5755,10 @@
         <v>2</v>
       </c>
       <c r="F78" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G78" s="25" t="s">
         <v>97</v>
-      </c>
-      <c r="G78" s="25" t="s">
-        <v>98</v>
       </c>
       <c r="H78" s="31">
         <v>100000000</v>
@@ -5793,7 +5796,7 @@
         <v>103900</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D79" s="35">
         <v>103900001</v>
@@ -5802,10 +5805,10 @@
         <v>3</v>
       </c>
       <c r="F79" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="G79" s="25" t="s">
         <v>99</v>
-      </c>
-      <c r="G79" s="25" t="s">
-        <v>100</v>
       </c>
       <c r="H79" s="31">
         <v>1000000000</v>
@@ -5843,7 +5846,7 @@
         <v>101600</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D80" s="35">
         <v>101600001</v>
@@ -5893,7 +5896,7 @@
         <v>101600</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D81" s="35">
         <v>101600001</v>
@@ -5943,7 +5946,7 @@
         <v>101600</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D82" s="35">
         <v>101600001</v>
@@ -5993,7 +5996,7 @@
         <v>101500</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D83" s="35">
         <v>101500001</v>
@@ -6043,7 +6046,7 @@
         <v>101500</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D84" s="35">
         <v>101500001</v>
@@ -6093,7 +6096,7 @@
         <v>101500</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D85" s="35">
         <v>101500001</v>
@@ -6143,7 +6146,7 @@
         <v>102600</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D86" s="35">
         <v>102600001</v>
@@ -6193,7 +6196,7 @@
         <v>102600</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D87" s="35">
         <v>102600001</v>
@@ -6243,7 +6246,7 @@
         <v>102600</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D88" s="35">
         <v>102600001</v>
@@ -6293,7 +6296,7 @@
         <v>105000</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D89" s="35">
         <v>105000001</v>
@@ -6343,7 +6346,7 @@
         <v>105000</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D90" s="35">
         <v>105000001</v>
@@ -6393,7 +6396,7 @@
         <v>105000</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D91" s="35">
         <v>105000001</v>
@@ -6443,7 +6446,7 @@
         <v>105100</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D92" s="35">
         <v>105100001</v>
@@ -6493,7 +6496,7 @@
         <v>105100</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D93" s="35">
         <v>105100001</v>
@@ -6543,7 +6546,7 @@
         <v>105100</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D94" s="35">
         <v>105100001</v>
@@ -6593,7 +6596,7 @@
         <v>105500</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D95" s="35">
         <v>105500001</v>
@@ -6643,7 +6646,7 @@
         <v>105500</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D96" s="35">
         <v>105500001</v>
@@ -6693,7 +6696,7 @@
         <v>105500</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D97" s="35">
         <v>105500001</v>
@@ -6743,7 +6746,7 @@
         <v>104800</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D98" s="27">
         <v>104800001</v>
@@ -6752,7 +6755,7 @@
         <v>1</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G98" s="25" t="s">
         <v>50</v>
@@ -6773,7 +6776,7 @@
         <v>100</v>
       </c>
       <c r="M98" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N98" s="24">
         <v>0</v>
@@ -6793,7 +6796,7 @@
         <v>104800</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D99" s="27">
         <v>104800001</v>
@@ -6802,7 +6805,7 @@
         <v>2</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G99" s="25" t="s">
         <v>52</v>
@@ -6823,7 +6826,7 @@
         <v>100</v>
       </c>
       <c r="M99" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N99" s="24">
         <v>0</v>
@@ -6843,7 +6846,7 @@
         <v>104800</v>
       </c>
       <c r="C100" s="23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D100" s="27">
         <v>104800001</v>
@@ -6852,7 +6855,7 @@
         <v>3</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G100" s="25" t="s">
         <v>54</v>
@@ -6873,7 +6876,7 @@
         <v>100</v>
       </c>
       <c r="M100" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N100" s="24">
         <v>0</v>
@@ -6893,7 +6896,7 @@
         <v>105501</v>
       </c>
       <c r="C101" s="23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D101" s="35">
         <v>105501001</v>
@@ -6943,7 +6946,7 @@
         <v>105501</v>
       </c>
       <c r="C102" s="23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D102" s="35">
         <v>105501001</v>
@@ -6993,7 +6996,7 @@
         <v>105501</v>
       </c>
       <c r="C103" s="23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D103" s="35">
         <v>105501001</v>
@@ -7043,7 +7046,7 @@
         <v>105502</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D104" s="35">
         <v>105502001</v>
@@ -7093,7 +7096,7 @@
         <v>105502</v>
       </c>
       <c r="C105" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D105" s="35">
         <v>105502001</v>
@@ -7143,7 +7146,7 @@
         <v>105502</v>
       </c>
       <c r="C106" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D106" s="35">
         <v>105502001</v>
@@ -7193,7 +7196,7 @@
         <v>105300</v>
       </c>
       <c r="C107" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D107" s="35">
         <v>105300001</v>
@@ -7202,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G107" s="25" t="s">
         <v>50</v>
@@ -7243,7 +7246,7 @@
         <v>105300</v>
       </c>
       <c r="C108" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D108" s="35">
         <v>105300001</v>
@@ -7252,7 +7255,7 @@
         <v>2</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G108" s="25" t="s">
         <v>52</v>
@@ -7293,7 +7296,7 @@
         <v>105300</v>
       </c>
       <c r="C109" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D109" s="35">
         <v>105300001</v>
@@ -7302,7 +7305,7 @@
         <v>3</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G109" s="25" t="s">
         <v>54</v>
@@ -7376,7 +7379,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O110" s="44"/>
       <c r="P110" s="44"/>
@@ -7426,7 +7429,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O111" s="44"/>
       <c r="P111" s="44"/>
@@ -7476,7 +7479,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O112" s="44"/>
       <c r="P112" s="44"/>
@@ -7526,7 +7529,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O113" s="44"/>
       <c r="P113" s="44"/>
@@ -7576,7 +7579,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O114" s="44"/>
       <c r="P114" s="44"/>
@@ -7626,7 +7629,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O115" s="44"/>
       <c r="P115" s="44"/>
@@ -7676,7 +7679,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O116" s="44"/>
       <c r="P116" s="44"/>
@@ -7726,7 +7729,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O117" s="44"/>
       <c r="P117" s="44"/>
@@ -7776,7 +7779,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O118" s="44"/>
       <c r="P118" s="44"/>
@@ -7826,7 +7829,7 @@
         <v>37</v>
       </c>
       <c r="N119" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O119" s="56"/>
       <c r="P119" s="56"/>
@@ -7876,7 +7879,7 @@
         <v>40</v>
       </c>
       <c r="N120" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O120" s="56"/>
       <c r="P120" s="56"/>
@@ -7926,7 +7929,7 @@
         <v>43</v>
       </c>
       <c r="N121" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O121" s="56"/>
       <c r="P121" s="56"/>
@@ -7976,7 +7979,7 @@
         <v>37</v>
       </c>
       <c r="N122" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O122" s="44"/>
       <c r="P122" s="44"/>
@@ -8026,7 +8029,7 @@
         <v>40</v>
       </c>
       <c r="N123" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O123" s="44"/>
       <c r="P123" s="44"/>
@@ -8076,7 +8079,7 @@
         <v>43</v>
       </c>
       <c r="N124" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O124" s="44"/>
       <c r="P124" s="44"/>
@@ -8126,7 +8129,7 @@
         <v>37</v>
       </c>
       <c r="N125" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O125" s="44"/>
       <c r="P125" s="44"/>
@@ -8176,7 +8179,7 @@
         <v>40</v>
       </c>
       <c r="N126" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O126" s="44"/>
       <c r="P126" s="44"/>
@@ -8226,7 +8229,7 @@
         <v>43</v>
       </c>
       <c r="N127" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O127" s="44"/>
       <c r="P127" s="44"/>
@@ -8276,7 +8279,7 @@
         <v>37</v>
       </c>
       <c r="N128" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O128" s="44"/>
       <c r="P128" s="44"/>
@@ -8326,7 +8329,7 @@
         <v>40</v>
       </c>
       <c r="N129" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O129" s="44"/>
       <c r="P129" s="44"/>
@@ -8376,7 +8379,7 @@
         <v>43</v>
       </c>
       <c r="N130" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O130" s="44"/>
       <c r="P130" s="44"/>
@@ -8426,7 +8429,7 @@
         <v>37</v>
       </c>
       <c r="N131" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O131" s="44"/>
       <c r="P131" s="44"/>
@@ -8476,7 +8479,7 @@
         <v>40</v>
       </c>
       <c r="N132" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O132" s="44"/>
       <c r="P132" s="44"/>
@@ -8526,7 +8529,7 @@
         <v>43</v>
       </c>
       <c r="N133" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O133" s="44"/>
       <c r="P133" s="44"/>
@@ -8576,7 +8579,7 @@
         <v>37</v>
       </c>
       <c r="N134" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O134" s="44"/>
       <c r="P134" s="44"/>
@@ -8626,7 +8629,7 @@
         <v>40</v>
       </c>
       <c r="N135" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O135" s="44"/>
       <c r="P135" s="44"/>
@@ -8676,7 +8679,7 @@
         <v>43</v>
       </c>
       <c r="N136" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O136" s="44"/>
       <c r="P136" s="44"/>
@@ -8726,7 +8729,7 @@
         <v>37</v>
       </c>
       <c r="N137" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O137" s="44"/>
       <c r="P137" s="44"/>
@@ -8776,7 +8779,7 @@
         <v>40</v>
       </c>
       <c r="N138" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O138" s="44"/>
       <c r="P138" s="44"/>
@@ -8826,7 +8829,7 @@
         <v>43</v>
       </c>
       <c r="N139" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O139" s="44"/>
       <c r="P139" s="44"/>
@@ -8852,7 +8855,7 @@
         <v>10</v>
       </c>
       <c r="F140" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G140" s="25" t="s">
         <v>66</v>
@@ -8876,7 +8879,7 @@
         <v>37</v>
       </c>
       <c r="N140" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O140" s="44"/>
       <c r="P140" s="44"/>
@@ -8926,7 +8929,7 @@
         <v>40</v>
       </c>
       <c r="N141" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O141" s="44"/>
       <c r="P141" s="44"/>
@@ -8976,7 +8979,7 @@
         <v>43</v>
       </c>
       <c r="N142" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O142" s="44"/>
       <c r="P142" s="44"/>
@@ -9026,7 +9029,7 @@
         <v>37</v>
       </c>
       <c r="N143" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O143" s="44"/>
       <c r="P143" s="44"/>
@@ -9076,7 +9079,7 @@
         <v>40</v>
       </c>
       <c r="N144" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O144" s="44"/>
       <c r="P144" s="44"/>
@@ -9126,7 +9129,7 @@
         <v>43</v>
       </c>
       <c r="N145" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O145" s="44"/>
       <c r="P145" s="44"/>
@@ -9176,7 +9179,7 @@
         <v>37</v>
       </c>
       <c r="N146" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O146" s="44"/>
       <c r="P146" s="44"/>
@@ -9226,7 +9229,7 @@
         <v>40</v>
       </c>
       <c r="N147" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O147" s="44"/>
       <c r="P147" s="44"/>
@@ -9276,7 +9279,7 @@
         <v>43</v>
       </c>
       <c r="N148" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O148" s="44"/>
       <c r="P148" s="44"/>
@@ -9326,7 +9329,7 @@
         <v>37</v>
       </c>
       <c r="N149" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O149" s="44"/>
       <c r="P149" s="44"/>
@@ -9376,7 +9379,7 @@
         <v>40</v>
       </c>
       <c r="N150" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O150" s="44"/>
       <c r="P150" s="44"/>
@@ -9426,7 +9429,7 @@
         <v>43</v>
       </c>
       <c r="N151" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O151" s="44"/>
       <c r="P151" s="44"/>
@@ -9476,7 +9479,7 @@
         <v>37</v>
       </c>
       <c r="N152" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O152" s="44"/>
       <c r="P152" s="44"/>
@@ -9526,7 +9529,7 @@
         <v>40</v>
       </c>
       <c r="N153" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O153" s="44"/>
       <c r="P153" s="44"/>
@@ -9576,7 +9579,7 @@
         <v>43</v>
       </c>
       <c r="N154" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O154" s="44"/>
       <c r="P154" s="44"/>
@@ -9626,7 +9629,7 @@
         <v>37</v>
       </c>
       <c r="N155" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O155" s="44"/>
       <c r="P155" s="44"/>
@@ -9676,7 +9679,7 @@
         <v>40</v>
       </c>
       <c r="N156" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O156" s="44"/>
       <c r="P156" s="44"/>
@@ -9726,7 +9729,7 @@
         <v>43</v>
       </c>
       <c r="N157" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O157" s="44"/>
       <c r="P157" s="44"/>
@@ -9776,7 +9779,7 @@
         <v>37</v>
       </c>
       <c r="N158" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O158" s="44"/>
       <c r="P158" s="44"/>
@@ -9826,7 +9829,7 @@
         <v>40</v>
       </c>
       <c r="N159" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O159" s="44"/>
       <c r="P159" s="44"/>
@@ -9876,7 +9879,7 @@
         <v>43</v>
       </c>
       <c r="N160" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O160" s="44"/>
       <c r="P160" s="44"/>
@@ -9902,10 +9905,10 @@
         <v>10</v>
       </c>
       <c r="F161" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G161" s="25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H161" s="57">
         <v>0</v>
@@ -9926,7 +9929,7 @@
         <v>37</v>
       </c>
       <c r="N161" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O161" s="44"/>
       <c r="P161" s="44"/>
@@ -9976,7 +9979,7 @@
         <v>40</v>
       </c>
       <c r="N162" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O162" s="44"/>
       <c r="P162" s="44"/>
@@ -10026,7 +10029,7 @@
         <v>43</v>
       </c>
       <c r="N163" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O163" s="44"/>
       <c r="P163" s="44"/>
@@ -10076,7 +10079,7 @@
         <v>37</v>
       </c>
       <c r="N164" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O164" s="44"/>
       <c r="P164" s="44"/>
@@ -10126,7 +10129,7 @@
         <v>40</v>
       </c>
       <c r="N165" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O165" s="44"/>
       <c r="P165" s="44"/>
@@ -10176,7 +10179,7 @@
         <v>43</v>
       </c>
       <c r="N166" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O166" s="44"/>
       <c r="P166" s="44"/>
@@ -10202,10 +10205,10 @@
         <v>11</v>
       </c>
       <c r="F167" s="24" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="G167" s="25" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H167" s="57">
         <v>0</v>
@@ -10226,7 +10229,7 @@
         <v>37</v>
       </c>
       <c r="N167" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O167" s="44"/>
       <c r="P167" s="44"/>
@@ -10252,10 +10255,10 @@
         <v>12</v>
       </c>
       <c r="F168" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G168" s="25" t="s">
         <v>89</v>
-      </c>
-      <c r="G168" s="25" t="s">
-        <v>90</v>
       </c>
       <c r="H168" s="57">
         <v>0</v>
@@ -10276,7 +10279,7 @@
         <v>40</v>
       </c>
       <c r="N168" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O168" s="44"/>
       <c r="P168" s="44"/>
@@ -10302,10 +10305,10 @@
         <v>13</v>
       </c>
       <c r="F169" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G169" s="25" t="s">
         <v>91</v>
-      </c>
-      <c r="G169" s="25" t="s">
-        <v>92</v>
       </c>
       <c r="H169" s="57">
         <v>0</v>
@@ -10326,7 +10329,7 @@
         <v>43</v>
       </c>
       <c r="N169" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O169" s="44"/>
       <c r="P169" s="44"/>
@@ -10343,7 +10346,7 @@
         <v>102700</v>
       </c>
       <c r="C170" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D170" s="51">
         <v>102700001</v>
@@ -10376,7 +10379,7 @@
         <v>37</v>
       </c>
       <c r="N170" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O170" s="44"/>
       <c r="P170" s="44"/>
@@ -10393,7 +10396,7 @@
         <v>102700</v>
       </c>
       <c r="C171" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D171" s="51">
         <v>102700001</v>
@@ -10426,7 +10429,7 @@
         <v>40</v>
       </c>
       <c r="N171" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O171" s="44"/>
       <c r="P171" s="44"/>
@@ -10443,7 +10446,7 @@
         <v>102700</v>
       </c>
       <c r="C172" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D172" s="51">
         <v>102700001</v>
@@ -10476,7 +10479,7 @@
         <v>43</v>
       </c>
       <c r="N172" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O172" s="44"/>
       <c r="P172" s="44"/>
@@ -10493,7 +10496,7 @@
         <v>103700</v>
       </c>
       <c r="C173" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D173" s="51">
         <v>103700001</v>
@@ -10526,7 +10529,7 @@
         <v>37</v>
       </c>
       <c r="N173" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O173" s="44"/>
       <c r="P173" s="44"/>
@@ -10543,7 +10546,7 @@
         <v>103700</v>
       </c>
       <c r="C174" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D174" s="51">
         <v>103700001</v>
@@ -10576,7 +10579,7 @@
         <v>40</v>
       </c>
       <c r="N174" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O174" s="44"/>
       <c r="P174" s="44"/>
@@ -10593,7 +10596,7 @@
         <v>103700</v>
       </c>
       <c r="C175" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D175" s="51">
         <v>103100001</v>
@@ -10626,7 +10629,7 @@
         <v>43</v>
       </c>
       <c r="N175" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O175" s="44"/>
       <c r="P175" s="44"/>
@@ -10643,7 +10646,7 @@
         <v>103100</v>
       </c>
       <c r="C176" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D176" s="51">
         <v>103100001</v>
@@ -10652,10 +10655,10 @@
         <v>11</v>
       </c>
       <c r="F176" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G176" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H176" s="53">
         <v>0</v>
@@ -10676,7 +10679,7 @@
         <v>37</v>
       </c>
       <c r="N176" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O176" s="44"/>
       <c r="P176" s="44"/>
@@ -10693,7 +10696,7 @@
         <v>103100</v>
       </c>
       <c r="C177" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D177" s="51">
         <v>103100001</v>
@@ -10702,10 +10705,10 @@
         <v>12</v>
       </c>
       <c r="F177" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G177" s="25" t="s">
         <v>97</v>
-      </c>
-      <c r="G177" s="25" t="s">
-        <v>98</v>
       </c>
       <c r="H177" s="53">
         <v>0</v>
@@ -10726,7 +10729,7 @@
         <v>40</v>
       </c>
       <c r="N177" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O177" s="44"/>
       <c r="P177" s="44"/>
@@ -10743,7 +10746,7 @@
         <v>103100</v>
       </c>
       <c r="C178" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D178" s="51">
         <v>103100001</v>
@@ -10752,10 +10755,10 @@
         <v>13</v>
       </c>
       <c r="F178" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="G178" s="25" t="s">
         <v>99</v>
-      </c>
-      <c r="G178" s="25" t="s">
-        <v>100</v>
       </c>
       <c r="H178" s="57">
         <v>0</v>
@@ -10776,7 +10779,7 @@
         <v>43</v>
       </c>
       <c r="N178" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O178" s="44"/>
       <c r="P178" s="44"/>
@@ -10793,7 +10796,7 @@
         <v>104000</v>
       </c>
       <c r="C179" s="50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D179" s="51">
         <v>104000001</v>
@@ -10802,10 +10805,10 @@
         <v>11</v>
       </c>
       <c r="F179" s="24" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="G179" s="25" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H179" s="57">
         <v>0</v>
@@ -10826,7 +10829,7 @@
         <v>37</v>
       </c>
       <c r="N179" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O179" s="44"/>
       <c r="P179" s="44"/>
@@ -10843,7 +10846,7 @@
         <v>104000</v>
       </c>
       <c r="C180" s="50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D180" s="51">
         <v>104000001</v>
@@ -10852,10 +10855,10 @@
         <v>12</v>
       </c>
       <c r="F180" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G180" s="25" t="s">
         <v>89</v>
-      </c>
-      <c r="G180" s="25" t="s">
-        <v>90</v>
       </c>
       <c r="H180" s="57">
         <v>0</v>
@@ -10876,7 +10879,7 @@
         <v>40</v>
       </c>
       <c r="N180" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O180" s="44"/>
       <c r="P180" s="44"/>
@@ -10893,7 +10896,7 @@
         <v>104000</v>
       </c>
       <c r="C181" s="50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D181" s="51">
         <v>104000001</v>
@@ -10902,10 +10905,10 @@
         <v>13</v>
       </c>
       <c r="F181" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G181" s="25" t="s">
         <v>91</v>
-      </c>
-      <c r="G181" s="25" t="s">
-        <v>92</v>
       </c>
       <c r="H181" s="57">
         <v>0</v>
@@ -10926,7 +10929,7 @@
         <v>43</v>
       </c>
       <c r="N181" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O181" s="44"/>
       <c r="P181" s="44"/>
@@ -10943,7 +10946,7 @@
         <v>103900</v>
       </c>
       <c r="C182" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D182" s="51">
         <v>103900001</v>
@@ -10952,10 +10955,10 @@
         <v>11</v>
       </c>
       <c r="F182" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G182" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H182" s="57">
         <v>0</v>
@@ -10976,7 +10979,7 @@
         <v>37</v>
       </c>
       <c r="N182" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O182" s="44"/>
       <c r="P182" s="44"/>
@@ -10993,7 +10996,7 @@
         <v>103900</v>
       </c>
       <c r="C183" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D183" s="51">
         <v>103900001</v>
@@ -11002,10 +11005,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G183" s="25" t="s">
         <v>97</v>
-      </c>
-      <c r="G183" s="25" t="s">
-        <v>98</v>
       </c>
       <c r="H183" s="57">
         <v>0</v>
@@ -11026,7 +11029,7 @@
         <v>40</v>
       </c>
       <c r="N183" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O183" s="44"/>
       <c r="P183" s="44"/>
@@ -11043,7 +11046,7 @@
         <v>103900</v>
       </c>
       <c r="C184" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D184" s="51">
         <v>103900001</v>
@@ -11052,10 +11055,10 @@
         <v>13</v>
       </c>
       <c r="F184" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="G184" s="25" t="s">
         <v>99</v>
-      </c>
-      <c r="G184" s="25" t="s">
-        <v>100</v>
       </c>
       <c r="H184" s="57">
         <v>0</v>
@@ -11076,7 +11079,7 @@
         <v>43</v>
       </c>
       <c r="N184" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O184" s="44"/>
       <c r="P184" s="44"/>
@@ -11093,7 +11096,7 @@
         <v>101600</v>
       </c>
       <c r="C185" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D185" s="51">
         <v>101600001</v>
@@ -11126,7 +11129,7 @@
         <v>37</v>
       </c>
       <c r="N185" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O185" s="44"/>
       <c r="P185" s="44"/>
@@ -11143,7 +11146,7 @@
         <v>101600</v>
       </c>
       <c r="C186" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D186" s="51">
         <v>101600001</v>
@@ -11176,7 +11179,7 @@
         <v>40</v>
       </c>
       <c r="N186" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O186" s="44"/>
       <c r="P186" s="44"/>
@@ -11193,7 +11196,7 @@
         <v>101600</v>
       </c>
       <c r="C187" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D187" s="51">
         <v>101600001</v>
@@ -11226,7 +11229,7 @@
         <v>43</v>
       </c>
       <c r="N187" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O187" s="44"/>
       <c r="P187" s="44"/>
@@ -11243,7 +11246,7 @@
         <v>101500</v>
       </c>
       <c r="C188" s="50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D188" s="51">
         <v>101500001</v>
@@ -11276,7 +11279,7 @@
         <v>37</v>
       </c>
       <c r="N188" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O188" s="44"/>
       <c r="P188" s="44"/>
@@ -11293,7 +11296,7 @@
         <v>101500</v>
       </c>
       <c r="C189" s="50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D189" s="51">
         <v>101500001</v>
@@ -11326,7 +11329,7 @@
         <v>40</v>
       </c>
       <c r="N189" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O189" s="44"/>
       <c r="P189" s="44"/>
@@ -11343,7 +11346,7 @@
         <v>101500</v>
       </c>
       <c r="C190" s="50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D190" s="51">
         <v>101500001</v>
@@ -11376,7 +11379,7 @@
         <v>43</v>
       </c>
       <c r="N190" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O190" s="44"/>
       <c r="P190" s="44"/>
@@ -11393,7 +11396,7 @@
         <v>102600</v>
       </c>
       <c r="C191" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D191" s="51">
         <v>102600001</v>
@@ -11426,7 +11429,7 @@
         <v>37</v>
       </c>
       <c r="N191" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O191" s="44"/>
       <c r="P191" s="44"/>
@@ -11443,7 +11446,7 @@
         <v>102600</v>
       </c>
       <c r="C192" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D192" s="51">
         <v>102600001</v>
@@ -11476,7 +11479,7 @@
         <v>40</v>
       </c>
       <c r="N192" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O192" s="44"/>
       <c r="P192" s="44"/>
@@ -11493,7 +11496,7 @@
         <v>102600</v>
       </c>
       <c r="C193" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D193" s="51">
         <v>102600001</v>
@@ -11526,7 +11529,7 @@
         <v>43</v>
       </c>
       <c r="N193" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O193" s="44"/>
       <c r="P193" s="44"/>
@@ -11543,7 +11546,7 @@
         <v>105000</v>
       </c>
       <c r="C194" s="50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D194" s="51">
         <v>105000001</v>
@@ -11576,7 +11579,7 @@
         <v>37</v>
       </c>
       <c r="N194" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O194" s="44"/>
       <c r="P194" s="44"/>
@@ -11593,7 +11596,7 @@
         <v>105000</v>
       </c>
       <c r="C195" s="50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D195" s="51">
         <v>105000001</v>
@@ -11626,7 +11629,7 @@
         <v>40</v>
       </c>
       <c r="N195" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O195" s="44"/>
       <c r="P195" s="44"/>
@@ -11643,7 +11646,7 @@
         <v>105000</v>
       </c>
       <c r="C196" s="50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D196" s="51">
         <v>105000001</v>
@@ -11676,7 +11679,7 @@
         <v>43</v>
       </c>
       <c r="N196" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O196" s="44"/>
       <c r="P196" s="44"/>
@@ -11693,7 +11696,7 @@
         <v>105100</v>
       </c>
       <c r="C197" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D197" s="51">
         <v>105100001</v>
@@ -11726,7 +11729,7 @@
         <v>37</v>
       </c>
       <c r="N197" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O197" s="44"/>
       <c r="P197" s="44"/>
@@ -11743,7 +11746,7 @@
         <v>105100</v>
       </c>
       <c r="C198" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D198" s="51">
         <v>105100001</v>
@@ -11776,7 +11779,7 @@
         <v>40</v>
       </c>
       <c r="N198" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O198" s="44"/>
       <c r="P198" s="44"/>
@@ -11793,7 +11796,7 @@
         <v>105100</v>
       </c>
       <c r="C199" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D199" s="51">
         <v>105100001</v>
@@ -11826,7 +11829,7 @@
         <v>43</v>
       </c>
       <c r="N199" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O199" s="44"/>
       <c r="P199" s="44"/>
@@ -11843,7 +11846,7 @@
         <v>105400</v>
       </c>
       <c r="C200" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D200" s="51">
         <v>105400001</v>
@@ -11852,7 +11855,7 @@
         <v>11</v>
       </c>
       <c r="F200" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G200" s="25" t="s">
         <v>50</v>
@@ -11873,10 +11876,10 @@
         <v>0</v>
       </c>
       <c r="M200" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N200" s="56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O200" s="44"/>
       <c r="P200" s="44"/>
@@ -11893,7 +11896,7 @@
         <v>105400</v>
       </c>
       <c r="C201" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D201" s="51">
         <v>105400001</v>
@@ -11902,7 +11905,7 @@
         <v>12</v>
       </c>
       <c r="F201" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G201" s="25" t="s">
         <v>52</v>
@@ -11923,10 +11926,10 @@
         <v>0</v>
       </c>
       <c r="M201" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N201" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O201" s="44"/>
       <c r="P201" s="44"/>
@@ -11943,7 +11946,7 @@
         <v>105400</v>
       </c>
       <c r="C202" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D202" s="51">
         <v>105400001</v>
@@ -11952,7 +11955,7 @@
         <v>13</v>
       </c>
       <c r="F202" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G202" s="25" t="s">
         <v>54</v>
@@ -11973,10 +11976,10 @@
         <v>0</v>
       </c>
       <c r="M202" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N202" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O202" s="44"/>
       <c r="P202" s="44"/>
@@ -11993,7 +11996,7 @@
         <v>100800</v>
       </c>
       <c r="C203" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D203" s="35">
         <v>100800001</v>
@@ -12002,7 +12005,7 @@
         <v>11</v>
       </c>
       <c r="F203" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G203" s="25" t="s">
         <v>50</v>
@@ -12023,10 +12026,10 @@
         <v>0</v>
       </c>
       <c r="M203" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N203" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:20">
@@ -12037,7 +12040,7 @@
         <v>100800</v>
       </c>
       <c r="C204" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D204" s="35">
         <v>100800001</v>
@@ -12046,7 +12049,7 @@
         <v>12</v>
       </c>
       <c r="F204" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G204" s="25" t="s">
         <v>52</v>
@@ -12067,10 +12070,10 @@
         <v>0</v>
       </c>
       <c r="M204" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N204" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:20">
@@ -12081,7 +12084,7 @@
         <v>100800</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D205" s="35">
         <v>100800001</v>
@@ -12090,7 +12093,7 @@
         <v>13</v>
       </c>
       <c r="F205" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G205" s="25" t="s">
         <v>54</v>
@@ -12111,10 +12114,10 @@
         <v>0</v>
       </c>
       <c r="M205" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N205" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:20">
@@ -12125,7 +12128,7 @@
         <v>105300</v>
       </c>
       <c r="C206" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D206" s="35">
         <v>105300001</v>
@@ -12134,7 +12137,7 @@
         <v>11</v>
       </c>
       <c r="F206" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G206" s="25" t="s">
         <v>50</v>
@@ -12155,10 +12158,10 @@
         <v>0</v>
       </c>
       <c r="M206" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N206" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:20">
@@ -12169,7 +12172,7 @@
         <v>105300</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D207" s="35">
         <v>105300001</v>
@@ -12178,7 +12181,7 @@
         <v>12</v>
       </c>
       <c r="F207" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G207" s="25" t="s">
         <v>52</v>
@@ -12199,10 +12202,10 @@
         <v>0</v>
       </c>
       <c r="M207" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N207" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:20">
@@ -12213,7 +12216,7 @@
         <v>105300</v>
       </c>
       <c r="C208" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D208" s="35">
         <v>105300001</v>
@@ -12222,7 +12225,7 @@
         <v>13</v>
       </c>
       <c r="F208" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G208" s="25" t="s">
         <v>54</v>
@@ -12243,10 +12246,10 @@
         <v>0</v>
       </c>
       <c r="M208" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N208" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:14">
@@ -12257,7 +12260,7 @@
         <v>105700</v>
       </c>
       <c r="C209" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D209" s="35">
         <v>105700001</v>
@@ -12266,7 +12269,7 @@
         <v>11</v>
       </c>
       <c r="F209" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G209" s="25" t="s">
         <v>50</v>
@@ -12287,10 +12290,10 @@
         <v>0</v>
       </c>
       <c r="M209" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N209" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:14">
@@ -12301,7 +12304,7 @@
         <v>105700</v>
       </c>
       <c r="C210" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D210" s="35">
         <v>105700001</v>
@@ -12310,7 +12313,7 @@
         <v>12</v>
       </c>
       <c r="F210" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G210" s="25" t="s">
         <v>52</v>
@@ -12331,10 +12334,10 @@
         <v>0</v>
       </c>
       <c r="M210" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N210" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:14">
@@ -12345,7 +12348,7 @@
         <v>105700</v>
       </c>
       <c r="C211" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D211" s="35">
         <v>105700001</v>
@@ -12354,7 +12357,7 @@
         <v>13</v>
       </c>
       <c r="F211" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G211" s="25" t="s">
         <v>54</v>
@@ -12375,10 +12378,10 @@
         <v>0</v>
       </c>
       <c r="M211" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N211" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="212" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12389,7 +12392,7 @@
         <v>105800</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D212" s="61">
         <v>105800001</v>
@@ -12398,7 +12401,7 @@
         <v>11</v>
       </c>
       <c r="F212" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G212" s="25" t="s">
         <v>50</v>
@@ -12419,10 +12422,10 @@
         <v>0</v>
       </c>
       <c r="M212" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N212" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="213" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12433,7 +12436,7 @@
         <v>105800</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D213" s="61">
         <v>105800001</v>
@@ -12442,7 +12445,7 @@
         <v>12</v>
       </c>
       <c r="F213" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G213" s="25" t="s">
         <v>52</v>
@@ -12463,10 +12466,10 @@
         <v>0</v>
       </c>
       <c r="M213" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N213" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="214" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12477,7 +12480,7 @@
         <v>105800</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D214" s="61">
         <v>105800001</v>
@@ -12486,7 +12489,7 @@
         <v>13</v>
       </c>
       <c r="F214" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G214" s="25" t="s">
         <v>54</v>
@@ -12507,10 +12510,10 @@
         <v>0</v>
       </c>
       <c r="M214" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N214" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="215" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12521,7 +12524,7 @@
         <v>105500</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D215" s="61">
         <v>105500001</v>
@@ -12551,10 +12554,10 @@
         <v>0</v>
       </c>
       <c r="M215" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N215" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="216" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12565,7 +12568,7 @@
         <v>105500</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D216" s="61">
         <v>105500001</v>
@@ -12595,10 +12598,10 @@
         <v>0</v>
       </c>
       <c r="M216" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N216" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="217" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12609,7 +12612,7 @@
         <v>105500</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D217" s="61">
         <v>105500001</v>
@@ -12639,10 +12642,10 @@
         <v>0</v>
       </c>
       <c r="M217" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N217" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:14">
@@ -12653,7 +12656,7 @@
         <v>104800</v>
       </c>
       <c r="C218" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D218" s="27">
         <v>104800001</v>
@@ -12662,7 +12665,7 @@
         <v>11</v>
       </c>
       <c r="F218" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G218" s="25" t="s">
         <v>50</v>
@@ -12683,10 +12686,10 @@
         <v>0</v>
       </c>
       <c r="M218" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N218" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:14">
@@ -12697,7 +12700,7 @@
         <v>104800</v>
       </c>
       <c r="C219" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D219" s="27">
         <v>104800001</v>
@@ -12706,7 +12709,7 @@
         <v>12</v>
       </c>
       <c r="F219" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G219" s="25" t="s">
         <v>52</v>
@@ -12727,10 +12730,10 @@
         <v>0</v>
       </c>
       <c r="M219" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N219" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:14">
@@ -12741,7 +12744,7 @@
         <v>104800</v>
       </c>
       <c r="C220" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D220" s="27">
         <v>104800001</v>
@@ -12750,7 +12753,7 @@
         <v>13</v>
       </c>
       <c r="F220" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G220" s="25" t="s">
         <v>54</v>
@@ -12771,10 +12774,10 @@
         <v>0</v>
       </c>
       <c r="M220" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N220" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="221" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12785,7 +12788,7 @@
         <v>105501</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D221" s="61">
         <v>105501001</v>
@@ -12815,10 +12818,10 @@
         <v>0</v>
       </c>
       <c r="M221" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N221" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="222" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12829,7 +12832,7 @@
         <v>105501</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D222" s="61">
         <v>105501001</v>
@@ -12859,10 +12862,10 @@
         <v>0</v>
       </c>
       <c r="M222" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N222" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="223" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12873,7 +12876,7 @@
         <v>105501</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D223" s="61">
         <v>105501001</v>
@@ -12903,10 +12906,10 @@
         <v>0</v>
       </c>
       <c r="M223" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N223" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="224" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12917,7 +12920,7 @@
         <v>105502</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D224" s="61">
         <v>105502001</v>
@@ -12947,10 +12950,10 @@
         <v>0</v>
       </c>
       <c r="M224" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N224" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="225" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -12961,7 +12964,7 @@
         <v>105502</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D225" s="61">
         <v>105502001</v>
@@ -12991,10 +12994,10 @@
         <v>0</v>
       </c>
       <c r="M225" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N225" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="226" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -13005,7 +13008,7 @@
         <v>105502</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D226" s="61">
         <v>105502001</v>
@@ -13035,10 +13038,10 @@
         <v>0</v>
       </c>
       <c r="M226" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N226" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="227" customFormat="1" ht="16.5" spans="1:20">
@@ -13049,7 +13052,7 @@
         <v>104100</v>
       </c>
       <c r="C227" s="63" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D227" s="27">
         <v>104100001</v>
@@ -13058,7 +13061,7 @@
         <v>11</v>
       </c>
       <c r="F227" s="47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G227" s="64" t="s">
         <v>50</v>
@@ -13079,10 +13082,10 @@
         <v>0</v>
       </c>
       <c r="M227" s="48" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N227" s="47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="228" customFormat="1" ht="16.5" spans="1:20">
@@ -13093,7 +13096,7 @@
         <v>104100</v>
       </c>
       <c r="C228" s="63" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D228" s="27">
         <v>104100001</v>
@@ -13102,7 +13105,7 @@
         <v>12</v>
       </c>
       <c r="F228" s="47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G228" s="64" t="s">
         <v>52</v>
@@ -13123,10 +13126,10 @@
         <v>0</v>
       </c>
       <c r="M228" s="48" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N228" s="47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="229" customFormat="1" ht="16.5" spans="1:20">
@@ -13137,7 +13140,7 @@
         <v>104100</v>
       </c>
       <c r="C229" s="63" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D229" s="27">
         <v>104100001</v>
@@ -13146,7 +13149,7 @@
         <v>13</v>
       </c>
       <c r="F229" s="47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G229" s="64" t="s">
         <v>54</v>
@@ -13167,10 +13170,10 @@
         <v>0</v>
       </c>
       <c r="M229" s="48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N229" s="47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="230" customFormat="1" ht="16.5" spans="1:20">
@@ -13181,7 +13184,7 @@
         <v>104200</v>
       </c>
       <c r="C230" s="63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D230" s="27">
         <v>104200001</v>
@@ -13190,7 +13193,7 @@
         <v>11</v>
       </c>
       <c r="F230" s="47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G230" s="64" t="s">
         <v>50</v>
@@ -13211,10 +13214,10 @@
         <v>0</v>
       </c>
       <c r="M230" s="48" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N230" s="47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="231" customFormat="1" ht="16.5" spans="1:20">
@@ -13225,7 +13228,7 @@
         <v>104200</v>
       </c>
       <c r="C231" s="63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D231" s="27">
         <v>104200001</v>
@@ -13234,7 +13237,7 @@
         <v>12</v>
       </c>
       <c r="F231" s="47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G231" s="64" t="s">
         <v>52</v>
@@ -13255,10 +13258,10 @@
         <v>0</v>
       </c>
       <c r="M231" s="48" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N231" s="47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="232" customFormat="1" ht="16.5" spans="1:20">
@@ -13269,7 +13272,7 @@
         <v>104200</v>
       </c>
       <c r="C232" s="63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D232" s="27">
         <v>104200001</v>
@@ -13278,7 +13281,7 @@
         <v>13</v>
       </c>
       <c r="F232" s="47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G232" s="64" t="s">
         <v>54</v>
@@ -13299,10 +13302,10 @@
         <v>0</v>
       </c>
       <c r="M232" s="48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N232" s="47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="233" s="2" customFormat="1" ht="16.5" spans="1:20">
@@ -13772,10 +13775,10 @@
         <v>21</v>
       </c>
       <c r="F242" s="32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G242" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H242" s="17">
         <v>10000000</v>
@@ -14822,7 +14825,7 @@
         <v>21</v>
       </c>
       <c r="F263" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G263" s="25" t="s">
         <v>66</v>
@@ -15722,10 +15725,10 @@
         <v>21</v>
       </c>
       <c r="F281" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G281" s="25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H281" s="31">
         <v>10000000</v>
@@ -16022,10 +16025,10 @@
         <v>21</v>
       </c>
       <c r="F287" s="24" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="G287" s="25" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H287" s="31">
         <v>10000000</v>
@@ -16072,10 +16075,10 @@
         <v>22</v>
       </c>
       <c r="F288" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G288" s="25" t="s">
         <v>89</v>
-      </c>
-      <c r="G288" s="25" t="s">
-        <v>90</v>
       </c>
       <c r="H288" s="31">
         <v>100000000</v>
@@ -16122,10 +16125,10 @@
         <v>23</v>
       </c>
       <c r="F289" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G289" s="25" t="s">
         <v>91</v>
-      </c>
-      <c r="G289" s="25" t="s">
-        <v>92</v>
       </c>
       <c r="H289" s="31">
         <v>1000000000</v>
@@ -16163,7 +16166,7 @@
         <v>104000</v>
       </c>
       <c r="C290" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D290" s="35">
         <v>104000001</v>
@@ -16172,10 +16175,10 @@
         <v>21</v>
       </c>
       <c r="F290" s="24" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="G290" s="25" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H290" s="31">
         <v>10000000</v>
@@ -16213,7 +16216,7 @@
         <v>104000</v>
       </c>
       <c r="C291" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D291" s="35">
         <v>104000001</v>
@@ -16222,10 +16225,10 @@
         <v>22</v>
       </c>
       <c r="F291" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G291" s="25" t="s">
         <v>89</v>
-      </c>
-      <c r="G291" s="25" t="s">
-        <v>90</v>
       </c>
       <c r="H291" s="31">
         <v>100000000</v>
@@ -16263,7 +16266,7 @@
         <v>104000</v>
       </c>
       <c r="C292" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D292" s="35">
         <v>104000001</v>
@@ -16272,10 +16275,10 @@
         <v>23</v>
       </c>
       <c r="F292" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G292" s="25" t="s">
         <v>91</v>
-      </c>
-      <c r="G292" s="25" t="s">
-        <v>92</v>
       </c>
       <c r="H292" s="31">
         <v>1000000000</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="136">
   <si>
     <t>id</t>
   </si>
@@ -368,6 +373,9 @@
     <t>杰克船长</t>
   </si>
   <si>
+    <t>200:1</t>
+  </si>
+  <si>
     <t>雷神</t>
   </si>
   <si>
@@ -390,9 +398,6 @@
   </si>
   <si>
     <t>200_400_1000_1600_2400_3200_4000</t>
-  </si>
-  <si>
-    <t>200:1</t>
   </si>
   <si>
     <t>2000_4000_10000_16000_24000_32000_40000</t>
@@ -808,8 +813,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -821,24 +833,17 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -3005,10 +3010,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="24">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H23" s="17">
         <v>10000000</v>
@@ -3146,7 +3151,7 @@
         <v>102200</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" s="27">
         <v>102200001</v>
@@ -3196,7 +3201,7 @@
         <v>102200</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D27" s="27">
         <v>102200001</v>
@@ -3246,7 +3251,7 @@
         <v>102200</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D28" s="27">
         <v>102200001</v>
@@ -3296,7 +3301,7 @@
         <v>102400</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D29" s="27">
         <v>102400026</v>
@@ -3305,10 +3310,10 @@
         <v>1</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G29" s="33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H29" s="17">
         <v>10000000</v>
@@ -3346,7 +3351,7 @@
         <v>102400</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D30" s="27">
         <v>102400026</v>
@@ -3396,7 +3401,7 @@
         <v>102400</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D31" s="27">
         <v>102400026</v>
@@ -3446,7 +3451,7 @@
         <v>101800</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D32" s="27">
         <v>101800001</v>
@@ -3496,7 +3501,7 @@
         <v>101800</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D33" s="27">
         <v>101800001</v>
@@ -3546,7 +3551,7 @@
         <v>101800</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D34" s="27">
         <v>101800001</v>
@@ -3596,7 +3601,7 @@
         <v>102500</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D35" s="27">
         <v>102500001</v>
@@ -3608,7 +3613,7 @@
         <v>20</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H35" s="17">
         <v>10000000</v>
@@ -3646,7 +3651,7 @@
         <v>102500</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D36" s="27">
         <v>102500001</v>
@@ -3655,10 +3660,10 @@
         <v>2</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H36" s="17">
         <v>100000000</v>
@@ -3696,7 +3701,7 @@
         <v>102500</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D37" s="27">
         <v>102500001</v>
@@ -3908,7 +3913,7 @@
         <v>73</v>
       </c>
       <c r="G41" s="33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H41" s="17">
         <v>10000000</v>
@@ -4355,10 +4360,10 @@
         <v>1</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H50" s="41">
         <v>10000000</v>
@@ -4805,10 +4810,10 @@
         <v>1</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G59" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H59" s="31">
         <v>10000000</v>
@@ -5104,8 +5109,8 @@
       <c r="E65" s="23">
         <v>1</v>
       </c>
-      <c r="F65" s="24" t="s">
-        <v>58</v>
+      <c r="F65" s="24">
+        <v>50</v>
       </c>
       <c r="G65" s="25" t="s">
         <v>50</v>
@@ -5705,10 +5710,10 @@
         <v>1</v>
       </c>
       <c r="F77" s="24">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="G77" s="25" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="H77" s="31">
         <v>10000000</v>
@@ -6605,10 +6610,10 @@
         <v>1</v>
       </c>
       <c r="F95" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H95" s="31">
         <v>10000000</v>
@@ -6905,10 +6910,10 @@
         <v>1</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G101" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H101" s="31">
         <v>10000000</v>
@@ -7055,10 +7060,10 @@
         <v>1</v>
       </c>
       <c r="F104" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G104" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H104" s="31">
         <v>10000000</v>
@@ -8396,7 +8401,7 @@
         <v>102200</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D131" s="51">
         <v>102200001</v>
@@ -8446,7 +8451,7 @@
         <v>102200</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D132" s="51">
         <v>102200001</v>
@@ -8496,7 +8501,7 @@
         <v>102200</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D133" s="51">
         <v>102200001</v>
@@ -8546,7 +8551,7 @@
         <v>102400</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D134" s="51">
         <v>102400026</v>
@@ -8596,7 +8601,7 @@
         <v>102400</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D135" s="51">
         <v>102400026</v>
@@ -8646,7 +8651,7 @@
         <v>102400</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D136" s="51">
         <v>102400026</v>
@@ -8696,7 +8701,7 @@
         <v>101800</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D137" s="51">
         <v>101800001</v>
@@ -8746,7 +8751,7 @@
         <v>101800</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D138" s="51">
         <v>101800001</v>
@@ -8796,7 +8801,7 @@
         <v>101800</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D139" s="51">
         <v>101800001</v>
@@ -8846,7 +8851,7 @@
         <v>102500</v>
       </c>
       <c r="C140" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D140" s="51">
         <v>102500001</v>
@@ -8858,7 +8863,7 @@
         <v>123</v>
       </c>
       <c r="G140" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H140" s="57">
         <v>0</v>
@@ -8896,7 +8901,7 @@
         <v>102500</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D141" s="51">
         <v>102500001</v>
@@ -8905,10 +8910,10 @@
         <v>11</v>
       </c>
       <c r="F141" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G141" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H141" s="57">
         <v>0</v>
@@ -8946,7 +8951,7 @@
         <v>102500</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D142" s="51">
         <v>102500001</v>
@@ -9155,10 +9160,10 @@
         <v>10</v>
       </c>
       <c r="F146" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G146" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H146" s="57">
         <v>0</v>
@@ -9605,10 +9610,10 @@
         <v>10</v>
       </c>
       <c r="F155" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G155" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H155" s="53">
         <v>0</v>
@@ -10055,10 +10060,10 @@
         <v>10</v>
       </c>
       <c r="F164" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G164" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H164" s="57">
         <v>0</v>
@@ -12533,10 +12538,10 @@
         <v>11</v>
       </c>
       <c r="F215" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G215" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H215" s="31">
         <v>0</v>
@@ -12797,10 +12802,10 @@
         <v>11</v>
       </c>
       <c r="F221" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G221" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H221" s="31">
         <v>0</v>
@@ -12929,10 +12934,10 @@
         <v>11</v>
       </c>
       <c r="F224" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G224" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H224" s="31">
         <v>0</v>
@@ -14366,7 +14371,7 @@
         <v>102200</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D254" s="27">
         <v>102200001</v>
@@ -14416,7 +14421,7 @@
         <v>102200</v>
       </c>
       <c r="C255" s="23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D255" s="27">
         <v>102200001</v>
@@ -14466,7 +14471,7 @@
         <v>102200</v>
       </c>
       <c r="C256" s="23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D256" s="27">
         <v>102200001</v>
@@ -14516,7 +14521,7 @@
         <v>102400</v>
       </c>
       <c r="C257" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D257" s="27">
         <v>102400026</v>
@@ -14525,10 +14530,10 @@
         <v>21</v>
       </c>
       <c r="F257" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G257" s="33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H257" s="17">
         <v>10000000</v>
@@ -14566,7 +14571,7 @@
         <v>102400</v>
       </c>
       <c r="C258" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D258" s="27">
         <v>102400026</v>
@@ -14616,7 +14621,7 @@
         <v>102400</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D259" s="27">
         <v>102400026</v>
@@ -14666,7 +14671,7 @@
         <v>101800</v>
       </c>
       <c r="C260" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D260" s="27">
         <v>101800001</v>
@@ -14716,7 +14721,7 @@
         <v>101800</v>
       </c>
       <c r="C261" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D261" s="27">
         <v>101800001</v>
@@ -14766,7 +14771,7 @@
         <v>101800</v>
       </c>
       <c r="C262" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D262" s="27">
         <v>101800001</v>
@@ -14816,7 +14821,7 @@
         <v>102500</v>
       </c>
       <c r="C263" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D263" s="27">
         <v>102500001</v>
@@ -14828,7 +14833,7 @@
         <v>123</v>
       </c>
       <c r="G263" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H263" s="17">
         <v>10000000</v>
@@ -14866,7 +14871,7 @@
         <v>102500</v>
       </c>
       <c r="C264" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D264" s="27">
         <v>102500001</v>
@@ -14875,10 +14880,10 @@
         <v>22</v>
       </c>
       <c r="F264" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G264" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H264" s="17">
         <v>100000000</v>
@@ -14916,7 +14921,7 @@
         <v>102500</v>
       </c>
       <c r="C265" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D265" s="27">
         <v>102500001</v>
@@ -15128,7 +15133,7 @@
         <v>73</v>
       </c>
       <c r="G269" s="33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H269" s="17">
         <v>10000000</v>
@@ -15575,10 +15580,10 @@
         <v>21</v>
       </c>
       <c r="F278" s="39" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G278" s="40" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H278" s="41">
         <v>10000000</v>
@@ -15875,10 +15880,10 @@
         <v>21</v>
       </c>
       <c r="F284" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G284" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H284" s="31">
         <v>10000000</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -191,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="137">
   <si>
     <t>id</t>
   </si>
@@ -511,6 +511,9 @@
     <t>狼月</t>
   </si>
   <si>
+    <t>800:1</t>
+  </si>
+  <si>
     <t>寻宝黄金城</t>
   </si>
   <si>
@@ -813,15 +816,20 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -832,8 +840,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -846,12 +855,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -6009,11 +6012,11 @@
       <c r="E83" s="23">
         <v>1</v>
       </c>
-      <c r="F83" s="24" t="s">
-        <v>58</v>
+      <c r="F83" s="24">
+        <v>800</v>
       </c>
       <c r="G83" s="25" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="H83" s="31">
         <v>10000000</v>
@@ -6151,7 +6154,7 @@
         <v>102600</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D86" s="35">
         <v>102600001</v>
@@ -6201,7 +6204,7 @@
         <v>102600</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D87" s="35">
         <v>102600001</v>
@@ -6251,7 +6254,7 @@
         <v>102600</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D88" s="35">
         <v>102600001</v>
@@ -6301,7 +6304,7 @@
         <v>105000</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D89" s="35">
         <v>105000001</v>
@@ -6351,7 +6354,7 @@
         <v>105000</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D90" s="35">
         <v>105000001</v>
@@ -6401,7 +6404,7 @@
         <v>105000</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D91" s="35">
         <v>105000001</v>
@@ -6451,7 +6454,7 @@
         <v>105100</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D92" s="35">
         <v>105100001</v>
@@ -6501,7 +6504,7 @@
         <v>105100</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D93" s="35">
         <v>105100001</v>
@@ -6551,7 +6554,7 @@
         <v>105100</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D94" s="35">
         <v>105100001</v>
@@ -6601,7 +6604,7 @@
         <v>105500</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D95" s="35">
         <v>105500001</v>
@@ -6651,7 +6654,7 @@
         <v>105500</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D96" s="35">
         <v>105500001</v>
@@ -6701,7 +6704,7 @@
         <v>105500</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D97" s="35">
         <v>105500001</v>
@@ -6751,7 +6754,7 @@
         <v>104800</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D98" s="27">
         <v>104800001</v>
@@ -6760,7 +6763,7 @@
         <v>1</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G98" s="25" t="s">
         <v>50</v>
@@ -6781,7 +6784,7 @@
         <v>100</v>
       </c>
       <c r="M98" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N98" s="24">
         <v>0</v>
@@ -6801,7 +6804,7 @@
         <v>104800</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D99" s="27">
         <v>104800001</v>
@@ -6810,7 +6813,7 @@
         <v>2</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G99" s="25" t="s">
         <v>52</v>
@@ -6831,7 +6834,7 @@
         <v>100</v>
       </c>
       <c r="M99" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N99" s="24">
         <v>0</v>
@@ -6851,7 +6854,7 @@
         <v>104800</v>
       </c>
       <c r="C100" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D100" s="27">
         <v>104800001</v>
@@ -6860,7 +6863,7 @@
         <v>3</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G100" s="25" t="s">
         <v>54</v>
@@ -6881,7 +6884,7 @@
         <v>100</v>
       </c>
       <c r="M100" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N100" s="24">
         <v>0</v>
@@ -6901,7 +6904,7 @@
         <v>105501</v>
       </c>
       <c r="C101" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D101" s="35">
         <v>105501001</v>
@@ -6951,7 +6954,7 @@
         <v>105501</v>
       </c>
       <c r="C102" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D102" s="35">
         <v>105501001</v>
@@ -7001,7 +7004,7 @@
         <v>105501</v>
       </c>
       <c r="C103" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D103" s="35">
         <v>105501001</v>
@@ -7051,7 +7054,7 @@
         <v>105502</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D104" s="35">
         <v>105502001</v>
@@ -7101,7 +7104,7 @@
         <v>105502</v>
       </c>
       <c r="C105" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D105" s="35">
         <v>105502001</v>
@@ -7151,7 +7154,7 @@
         <v>105502</v>
       </c>
       <c r="C106" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D106" s="35">
         <v>105502001</v>
@@ -7201,7 +7204,7 @@
         <v>105300</v>
       </c>
       <c r="C107" s="23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D107" s="35">
         <v>105300001</v>
@@ -7210,7 +7213,7 @@
         <v>1</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G107" s="25" t="s">
         <v>50</v>
@@ -7251,7 +7254,7 @@
         <v>105300</v>
       </c>
       <c r="C108" s="23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D108" s="35">
         <v>105300001</v>
@@ -7260,7 +7263,7 @@
         <v>2</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G108" s="25" t="s">
         <v>52</v>
@@ -7301,7 +7304,7 @@
         <v>105300</v>
       </c>
       <c r="C109" s="23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D109" s="35">
         <v>105300001</v>
@@ -7310,7 +7313,7 @@
         <v>3</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G109" s="25" t="s">
         <v>54</v>
@@ -7384,7 +7387,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O110" s="44"/>
       <c r="P110" s="44"/>
@@ -7434,7 +7437,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O111" s="44"/>
       <c r="P111" s="44"/>
@@ -7484,7 +7487,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O112" s="44"/>
       <c r="P112" s="44"/>
@@ -7534,7 +7537,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O113" s="44"/>
       <c r="P113" s="44"/>
@@ -7584,7 +7587,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O114" s="44"/>
       <c r="P114" s="44"/>
@@ -7634,7 +7637,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O115" s="44"/>
       <c r="P115" s="44"/>
@@ -7684,7 +7687,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O116" s="44"/>
       <c r="P116" s="44"/>
@@ -7734,7 +7737,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O117" s="44"/>
       <c r="P117" s="44"/>
@@ -7784,7 +7787,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O118" s="44"/>
       <c r="P118" s="44"/>
@@ -7834,7 +7837,7 @@
         <v>37</v>
       </c>
       <c r="N119" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O119" s="56"/>
       <c r="P119" s="56"/>
@@ -7884,7 +7887,7 @@
         <v>40</v>
       </c>
       <c r="N120" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O120" s="56"/>
       <c r="P120" s="56"/>
@@ -7934,7 +7937,7 @@
         <v>43</v>
       </c>
       <c r="N121" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O121" s="56"/>
       <c r="P121" s="56"/>
@@ -7984,7 +7987,7 @@
         <v>37</v>
       </c>
       <c r="N122" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O122" s="44"/>
       <c r="P122" s="44"/>
@@ -8034,7 +8037,7 @@
         <v>40</v>
       </c>
       <c r="N123" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O123" s="44"/>
       <c r="P123" s="44"/>
@@ -8084,7 +8087,7 @@
         <v>43</v>
       </c>
       <c r="N124" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O124" s="44"/>
       <c r="P124" s="44"/>
@@ -8134,7 +8137,7 @@
         <v>37</v>
       </c>
       <c r="N125" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O125" s="44"/>
       <c r="P125" s="44"/>
@@ -8184,7 +8187,7 @@
         <v>40</v>
       </c>
       <c r="N126" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O126" s="44"/>
       <c r="P126" s="44"/>
@@ -8234,7 +8237,7 @@
         <v>43</v>
       </c>
       <c r="N127" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O127" s="44"/>
       <c r="P127" s="44"/>
@@ -8284,7 +8287,7 @@
         <v>37</v>
       </c>
       <c r="N128" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O128" s="44"/>
       <c r="P128" s="44"/>
@@ -8334,7 +8337,7 @@
         <v>40</v>
       </c>
       <c r="N129" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O129" s="44"/>
       <c r="P129" s="44"/>
@@ -8384,7 +8387,7 @@
         <v>43</v>
       </c>
       <c r="N130" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O130" s="44"/>
       <c r="P130" s="44"/>
@@ -8434,7 +8437,7 @@
         <v>37</v>
       </c>
       <c r="N131" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O131" s="44"/>
       <c r="P131" s="44"/>
@@ -8484,7 +8487,7 @@
         <v>40</v>
       </c>
       <c r="N132" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O132" s="44"/>
       <c r="P132" s="44"/>
@@ -8534,7 +8537,7 @@
         <v>43</v>
       </c>
       <c r="N133" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O133" s="44"/>
       <c r="P133" s="44"/>
@@ -8584,7 +8587,7 @@
         <v>37</v>
       </c>
       <c r="N134" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O134" s="44"/>
       <c r="P134" s="44"/>
@@ -8634,7 +8637,7 @@
         <v>40</v>
       </c>
       <c r="N135" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O135" s="44"/>
       <c r="P135" s="44"/>
@@ -8684,7 +8687,7 @@
         <v>43</v>
       </c>
       <c r="N136" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O136" s="44"/>
       <c r="P136" s="44"/>
@@ -8734,7 +8737,7 @@
         <v>37</v>
       </c>
       <c r="N137" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O137" s="44"/>
       <c r="P137" s="44"/>
@@ -8784,7 +8787,7 @@
         <v>40</v>
       </c>
       <c r="N138" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O138" s="44"/>
       <c r="P138" s="44"/>
@@ -8834,7 +8837,7 @@
         <v>43</v>
       </c>
       <c r="N139" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O139" s="44"/>
       <c r="P139" s="44"/>
@@ -8860,7 +8863,7 @@
         <v>10</v>
       </c>
       <c r="F140" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G140" s="25" t="s">
         <v>67</v>
@@ -8884,7 +8887,7 @@
         <v>37</v>
       </c>
       <c r="N140" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O140" s="44"/>
       <c r="P140" s="44"/>
@@ -8934,7 +8937,7 @@
         <v>40</v>
       </c>
       <c r="N141" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O141" s="44"/>
       <c r="P141" s="44"/>
@@ -8984,7 +8987,7 @@
         <v>43</v>
       </c>
       <c r="N142" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O142" s="44"/>
       <c r="P142" s="44"/>
@@ -9034,7 +9037,7 @@
         <v>37</v>
       </c>
       <c r="N143" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O143" s="44"/>
       <c r="P143" s="44"/>
@@ -9084,7 +9087,7 @@
         <v>40</v>
       </c>
       <c r="N144" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O144" s="44"/>
       <c r="P144" s="44"/>
@@ -9134,7 +9137,7 @@
         <v>43</v>
       </c>
       <c r="N145" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O145" s="44"/>
       <c r="P145" s="44"/>
@@ -9184,7 +9187,7 @@
         <v>37</v>
       </c>
       <c r="N146" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O146" s="44"/>
       <c r="P146" s="44"/>
@@ -9234,7 +9237,7 @@
         <v>40</v>
       </c>
       <c r="N147" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O147" s="44"/>
       <c r="P147" s="44"/>
@@ -9284,7 +9287,7 @@
         <v>43</v>
       </c>
       <c r="N148" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O148" s="44"/>
       <c r="P148" s="44"/>
@@ -9334,7 +9337,7 @@
         <v>37</v>
       </c>
       <c r="N149" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O149" s="44"/>
       <c r="P149" s="44"/>
@@ -9384,7 +9387,7 @@
         <v>40</v>
       </c>
       <c r="N150" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O150" s="44"/>
       <c r="P150" s="44"/>
@@ -9434,7 +9437,7 @@
         <v>43</v>
       </c>
       <c r="N151" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O151" s="44"/>
       <c r="P151" s="44"/>
@@ -9484,7 +9487,7 @@
         <v>37</v>
       </c>
       <c r="N152" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O152" s="44"/>
       <c r="P152" s="44"/>
@@ -9534,7 +9537,7 @@
         <v>40</v>
       </c>
       <c r="N153" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O153" s="44"/>
       <c r="P153" s="44"/>
@@ -9584,7 +9587,7 @@
         <v>43</v>
       </c>
       <c r="N154" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O154" s="44"/>
       <c r="P154" s="44"/>
@@ -9634,7 +9637,7 @@
         <v>37</v>
       </c>
       <c r="N155" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O155" s="44"/>
       <c r="P155" s="44"/>
@@ -9684,7 +9687,7 @@
         <v>40</v>
       </c>
       <c r="N156" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O156" s="44"/>
       <c r="P156" s="44"/>
@@ -9734,7 +9737,7 @@
         <v>43</v>
       </c>
       <c r="N157" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O157" s="44"/>
       <c r="P157" s="44"/>
@@ -9784,7 +9787,7 @@
         <v>37</v>
       </c>
       <c r="N158" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O158" s="44"/>
       <c r="P158" s="44"/>
@@ -9834,7 +9837,7 @@
         <v>40</v>
       </c>
       <c r="N159" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O159" s="44"/>
       <c r="P159" s="44"/>
@@ -9884,7 +9887,7 @@
         <v>43</v>
       </c>
       <c r="N160" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O160" s="44"/>
       <c r="P160" s="44"/>
@@ -9910,10 +9913,10 @@
         <v>10</v>
       </c>
       <c r="F161" s="24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G161" s="25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H161" s="57">
         <v>0</v>
@@ -9934,7 +9937,7 @@
         <v>37</v>
       </c>
       <c r="N161" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O161" s="44"/>
       <c r="P161" s="44"/>
@@ -9984,7 +9987,7 @@
         <v>40</v>
       </c>
       <c r="N162" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O162" s="44"/>
       <c r="P162" s="44"/>
@@ -10034,7 +10037,7 @@
         <v>43</v>
       </c>
       <c r="N163" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O163" s="44"/>
       <c r="P163" s="44"/>
@@ -10084,7 +10087,7 @@
         <v>37</v>
       </c>
       <c r="N164" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O164" s="44"/>
       <c r="P164" s="44"/>
@@ -10134,7 +10137,7 @@
         <v>40</v>
       </c>
       <c r="N165" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O165" s="44"/>
       <c r="P165" s="44"/>
@@ -10184,7 +10187,7 @@
         <v>43</v>
       </c>
       <c r="N166" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O166" s="44"/>
       <c r="P166" s="44"/>
@@ -10234,7 +10237,7 @@
         <v>37</v>
       </c>
       <c r="N167" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O167" s="44"/>
       <c r="P167" s="44"/>
@@ -10284,7 +10287,7 @@
         <v>40</v>
       </c>
       <c r="N168" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O168" s="44"/>
       <c r="P168" s="44"/>
@@ -10334,7 +10337,7 @@
         <v>43</v>
       </c>
       <c r="N169" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O169" s="44"/>
       <c r="P169" s="44"/>
@@ -10384,7 +10387,7 @@
         <v>37</v>
       </c>
       <c r="N170" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O170" s="44"/>
       <c r="P170" s="44"/>
@@ -10434,7 +10437,7 @@
         <v>40</v>
       </c>
       <c r="N171" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O171" s="44"/>
       <c r="P171" s="44"/>
@@ -10484,7 +10487,7 @@
         <v>43</v>
       </c>
       <c r="N172" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O172" s="44"/>
       <c r="P172" s="44"/>
@@ -10534,7 +10537,7 @@
         <v>37</v>
       </c>
       <c r="N173" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O173" s="44"/>
       <c r="P173" s="44"/>
@@ -10584,7 +10587,7 @@
         <v>40</v>
       </c>
       <c r="N174" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O174" s="44"/>
       <c r="P174" s="44"/>
@@ -10634,7 +10637,7 @@
         <v>43</v>
       </c>
       <c r="N175" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O175" s="44"/>
       <c r="P175" s="44"/>
@@ -10660,7 +10663,7 @@
         <v>11</v>
       </c>
       <c r="F176" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G176" s="25" t="s">
         <v>95</v>
@@ -10684,7 +10687,7 @@
         <v>37</v>
       </c>
       <c r="N176" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O176" s="44"/>
       <c r="P176" s="44"/>
@@ -10734,7 +10737,7 @@
         <v>40</v>
       </c>
       <c r="N177" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O177" s="44"/>
       <c r="P177" s="44"/>
@@ -10784,7 +10787,7 @@
         <v>43</v>
       </c>
       <c r="N178" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O178" s="44"/>
       <c r="P178" s="44"/>
@@ -10834,7 +10837,7 @@
         <v>37</v>
       </c>
       <c r="N179" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O179" s="44"/>
       <c r="P179" s="44"/>
@@ -10884,7 +10887,7 @@
         <v>40</v>
       </c>
       <c r="N180" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O180" s="44"/>
       <c r="P180" s="44"/>
@@ -10934,7 +10937,7 @@
         <v>43</v>
       </c>
       <c r="N181" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O181" s="44"/>
       <c r="P181" s="44"/>
@@ -10960,7 +10963,7 @@
         <v>11</v>
       </c>
       <c r="F182" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G182" s="25" t="s">
         <v>95</v>
@@ -10984,7 +10987,7 @@
         <v>37</v>
       </c>
       <c r="N182" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O182" s="44"/>
       <c r="P182" s="44"/>
@@ -11034,7 +11037,7 @@
         <v>40</v>
       </c>
       <c r="N183" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O183" s="44"/>
       <c r="P183" s="44"/>
@@ -11084,7 +11087,7 @@
         <v>43</v>
       </c>
       <c r="N184" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O184" s="44"/>
       <c r="P184" s="44"/>
@@ -11134,7 +11137,7 @@
         <v>37</v>
       </c>
       <c r="N185" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O185" s="44"/>
       <c r="P185" s="44"/>
@@ -11184,7 +11187,7 @@
         <v>40</v>
       </c>
       <c r="N186" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O186" s="44"/>
       <c r="P186" s="44"/>
@@ -11234,7 +11237,7 @@
         <v>43</v>
       </c>
       <c r="N187" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O187" s="44"/>
       <c r="P187" s="44"/>
@@ -11284,7 +11287,7 @@
         <v>37</v>
       </c>
       <c r="N188" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O188" s="44"/>
       <c r="P188" s="44"/>
@@ -11334,7 +11337,7 @@
         <v>40</v>
       </c>
       <c r="N189" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O189" s="44"/>
       <c r="P189" s="44"/>
@@ -11384,7 +11387,7 @@
         <v>43</v>
       </c>
       <c r="N190" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O190" s="44"/>
       <c r="P190" s="44"/>
@@ -11401,7 +11404,7 @@
         <v>102600</v>
       </c>
       <c r="C191" s="50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D191" s="51">
         <v>102600001</v>
@@ -11434,7 +11437,7 @@
         <v>37</v>
       </c>
       <c r="N191" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O191" s="44"/>
       <c r="P191" s="44"/>
@@ -11451,7 +11454,7 @@
         <v>102600</v>
       </c>
       <c r="C192" s="50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D192" s="51">
         <v>102600001</v>
@@ -11484,7 +11487,7 @@
         <v>40</v>
       </c>
       <c r="N192" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O192" s="44"/>
       <c r="P192" s="44"/>
@@ -11501,7 +11504,7 @@
         <v>102600</v>
       </c>
       <c r="C193" s="50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D193" s="51">
         <v>102600001</v>
@@ -11534,7 +11537,7 @@
         <v>43</v>
       </c>
       <c r="N193" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O193" s="44"/>
       <c r="P193" s="44"/>
@@ -11551,7 +11554,7 @@
         <v>105000</v>
       </c>
       <c r="C194" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D194" s="51">
         <v>105000001</v>
@@ -11584,7 +11587,7 @@
         <v>37</v>
       </c>
       <c r="N194" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O194" s="44"/>
       <c r="P194" s="44"/>
@@ -11601,7 +11604,7 @@
         <v>105000</v>
       </c>
       <c r="C195" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D195" s="51">
         <v>105000001</v>
@@ -11634,7 +11637,7 @@
         <v>40</v>
       </c>
       <c r="N195" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O195" s="44"/>
       <c r="P195" s="44"/>
@@ -11651,7 +11654,7 @@
         <v>105000</v>
       </c>
       <c r="C196" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D196" s="51">
         <v>105000001</v>
@@ -11684,7 +11687,7 @@
         <v>43</v>
       </c>
       <c r="N196" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O196" s="44"/>
       <c r="P196" s="44"/>
@@ -11701,7 +11704,7 @@
         <v>105100</v>
       </c>
       <c r="C197" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D197" s="51">
         <v>105100001</v>
@@ -11734,7 +11737,7 @@
         <v>37</v>
       </c>
       <c r="N197" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O197" s="44"/>
       <c r="P197" s="44"/>
@@ -11751,7 +11754,7 @@
         <v>105100</v>
       </c>
       <c r="C198" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D198" s="51">
         <v>105100001</v>
@@ -11784,7 +11787,7 @@
         <v>40</v>
       </c>
       <c r="N198" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O198" s="44"/>
       <c r="P198" s="44"/>
@@ -11801,7 +11804,7 @@
         <v>105100</v>
       </c>
       <c r="C199" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D199" s="51">
         <v>105100001</v>
@@ -11834,7 +11837,7 @@
         <v>43</v>
       </c>
       <c r="N199" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O199" s="44"/>
       <c r="P199" s="44"/>
@@ -11851,7 +11854,7 @@
         <v>105400</v>
       </c>
       <c r="C200" s="50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D200" s="51">
         <v>105400001</v>
@@ -11860,7 +11863,7 @@
         <v>11</v>
       </c>
       <c r="F200" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G200" s="25" t="s">
         <v>50</v>
@@ -11881,10 +11884,10 @@
         <v>0</v>
       </c>
       <c r="M200" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N200" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O200" s="44"/>
       <c r="P200" s="44"/>
@@ -11901,7 +11904,7 @@
         <v>105400</v>
       </c>
       <c r="C201" s="50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D201" s="51">
         <v>105400001</v>
@@ -11910,7 +11913,7 @@
         <v>12</v>
       </c>
       <c r="F201" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G201" s="25" t="s">
         <v>52</v>
@@ -11931,10 +11934,10 @@
         <v>0</v>
       </c>
       <c r="M201" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N201" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O201" s="44"/>
       <c r="P201" s="44"/>
@@ -11951,7 +11954,7 @@
         <v>105400</v>
       </c>
       <c r="C202" s="50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D202" s="51">
         <v>105400001</v>
@@ -11960,7 +11963,7 @@
         <v>13</v>
       </c>
       <c r="F202" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G202" s="25" t="s">
         <v>54</v>
@@ -11981,10 +11984,10 @@
         <v>0</v>
       </c>
       <c r="M202" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N202" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O202" s="44"/>
       <c r="P202" s="44"/>
@@ -12001,7 +12004,7 @@
         <v>100800</v>
       </c>
       <c r="C203" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D203" s="35">
         <v>100800001</v>
@@ -12010,7 +12013,7 @@
         <v>11</v>
       </c>
       <c r="F203" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G203" s="25" t="s">
         <v>50</v>
@@ -12031,10 +12034,10 @@
         <v>0</v>
       </c>
       <c r="M203" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N203" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:20">
@@ -12045,7 +12048,7 @@
         <v>100800</v>
       </c>
       <c r="C204" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D204" s="35">
         <v>100800001</v>
@@ -12054,7 +12057,7 @@
         <v>12</v>
       </c>
       <c r="F204" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G204" s="25" t="s">
         <v>52</v>
@@ -12075,10 +12078,10 @@
         <v>0</v>
       </c>
       <c r="M204" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N204" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:20">
@@ -12089,7 +12092,7 @@
         <v>100800</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D205" s="35">
         <v>100800001</v>
@@ -12098,7 +12101,7 @@
         <v>13</v>
       </c>
       <c r="F205" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G205" s="25" t="s">
         <v>54</v>
@@ -12119,10 +12122,10 @@
         <v>0</v>
       </c>
       <c r="M205" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N205" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:20">
@@ -12133,7 +12136,7 @@
         <v>105300</v>
       </c>
       <c r="C206" s="23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D206" s="35">
         <v>105300001</v>
@@ -12142,7 +12145,7 @@
         <v>11</v>
       </c>
       <c r="F206" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G206" s="25" t="s">
         <v>50</v>
@@ -12163,10 +12166,10 @@
         <v>0</v>
       </c>
       <c r="M206" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N206" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:20">
@@ -12177,7 +12180,7 @@
         <v>105300</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D207" s="35">
         <v>105300001</v>
@@ -12186,7 +12189,7 @@
         <v>12</v>
       </c>
       <c r="F207" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G207" s="25" t="s">
         <v>52</v>
@@ -12207,10 +12210,10 @@
         <v>0</v>
       </c>
       <c r="M207" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N207" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:20">
@@ -12221,7 +12224,7 @@
         <v>105300</v>
       </c>
       <c r="C208" s="23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D208" s="35">
         <v>105300001</v>
@@ -12230,7 +12233,7 @@
         <v>13</v>
       </c>
       <c r="F208" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G208" s="25" t="s">
         <v>54</v>
@@ -12251,10 +12254,10 @@
         <v>0</v>
       </c>
       <c r="M208" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N208" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:14">
@@ -12265,7 +12268,7 @@
         <v>105700</v>
       </c>
       <c r="C209" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D209" s="35">
         <v>105700001</v>
@@ -12274,7 +12277,7 @@
         <v>11</v>
       </c>
       <c r="F209" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G209" s="25" t="s">
         <v>50</v>
@@ -12295,10 +12298,10 @@
         <v>0</v>
       </c>
       <c r="M209" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N209" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:14">
@@ -12309,7 +12312,7 @@
         <v>105700</v>
       </c>
       <c r="C210" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D210" s="35">
         <v>105700001</v>
@@ -12318,7 +12321,7 @@
         <v>12</v>
       </c>
       <c r="F210" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G210" s="25" t="s">
         <v>52</v>
@@ -12339,10 +12342,10 @@
         <v>0</v>
       </c>
       <c r="M210" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N210" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:14">
@@ -12353,7 +12356,7 @@
         <v>105700</v>
       </c>
       <c r="C211" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D211" s="35">
         <v>105700001</v>
@@ -12362,7 +12365,7 @@
         <v>13</v>
       </c>
       <c r="F211" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G211" s="25" t="s">
         <v>54</v>
@@ -12383,10 +12386,10 @@
         <v>0</v>
       </c>
       <c r="M211" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N211" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="212" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12397,7 +12400,7 @@
         <v>105800</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D212" s="61">
         <v>105800001</v>
@@ -12406,7 +12409,7 @@
         <v>11</v>
       </c>
       <c r="F212" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G212" s="25" t="s">
         <v>50</v>
@@ -12427,10 +12430,10 @@
         <v>0</v>
       </c>
       <c r="M212" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N212" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="213" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12441,7 +12444,7 @@
         <v>105800</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D213" s="61">
         <v>105800001</v>
@@ -12450,7 +12453,7 @@
         <v>12</v>
       </c>
       <c r="F213" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G213" s="25" t="s">
         <v>52</v>
@@ -12471,10 +12474,10 @@
         <v>0</v>
       </c>
       <c r="M213" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N213" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="214" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12485,7 +12488,7 @@
         <v>105800</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D214" s="61">
         <v>105800001</v>
@@ -12494,7 +12497,7 @@
         <v>13</v>
       </c>
       <c r="F214" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G214" s="25" t="s">
         <v>54</v>
@@ -12515,10 +12518,10 @@
         <v>0</v>
       </c>
       <c r="M214" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N214" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="215" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12529,7 +12532,7 @@
         <v>105500</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D215" s="61">
         <v>105500001</v>
@@ -12559,10 +12562,10 @@
         <v>0</v>
       </c>
       <c r="M215" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N215" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="216" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12573,7 +12576,7 @@
         <v>105500</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D216" s="61">
         <v>105500001</v>
@@ -12603,10 +12606,10 @@
         <v>0</v>
       </c>
       <c r="M216" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N216" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="217" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12617,7 +12620,7 @@
         <v>105500</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D217" s="61">
         <v>105500001</v>
@@ -12647,10 +12650,10 @@
         <v>0</v>
       </c>
       <c r="M217" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N217" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:14">
@@ -12661,7 +12664,7 @@
         <v>104800</v>
       </c>
       <c r="C218" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D218" s="27">
         <v>104800001</v>
@@ -12670,7 +12673,7 @@
         <v>11</v>
       </c>
       <c r="F218" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G218" s="25" t="s">
         <v>50</v>
@@ -12691,10 +12694,10 @@
         <v>0</v>
       </c>
       <c r="M218" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N218" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:14">
@@ -12705,7 +12708,7 @@
         <v>104800</v>
       </c>
       <c r="C219" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D219" s="27">
         <v>104800001</v>
@@ -12714,7 +12717,7 @@
         <v>12</v>
       </c>
       <c r="F219" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G219" s="25" t="s">
         <v>52</v>
@@ -12735,10 +12738,10 @@
         <v>0</v>
       </c>
       <c r="M219" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N219" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:14">
@@ -12749,7 +12752,7 @@
         <v>104800</v>
       </c>
       <c r="C220" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D220" s="27">
         <v>104800001</v>
@@ -12758,7 +12761,7 @@
         <v>13</v>
       </c>
       <c r="F220" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G220" s="25" t="s">
         <v>54</v>
@@ -12779,10 +12782,10 @@
         <v>0</v>
       </c>
       <c r="M220" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N220" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="221" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12793,7 +12796,7 @@
         <v>105501</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D221" s="61">
         <v>105501001</v>
@@ -12823,10 +12826,10 @@
         <v>0</v>
       </c>
       <c r="M221" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N221" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="222" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12837,7 +12840,7 @@
         <v>105501</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D222" s="61">
         <v>105501001</v>
@@ -12867,10 +12870,10 @@
         <v>0</v>
       </c>
       <c r="M222" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N222" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="223" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12881,7 +12884,7 @@
         <v>105501</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D223" s="61">
         <v>105501001</v>
@@ -12911,10 +12914,10 @@
         <v>0</v>
       </c>
       <c r="M223" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N223" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="224" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12925,7 +12928,7 @@
         <v>105502</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D224" s="61">
         <v>105502001</v>
@@ -12955,10 +12958,10 @@
         <v>0</v>
       </c>
       <c r="M224" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N224" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="225" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -12969,7 +12972,7 @@
         <v>105502</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D225" s="61">
         <v>105502001</v>
@@ -12999,10 +13002,10 @@
         <v>0</v>
       </c>
       <c r="M225" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N225" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="226" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -13013,7 +13016,7 @@
         <v>105502</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D226" s="61">
         <v>105502001</v>
@@ -13043,10 +13046,10 @@
         <v>0</v>
       </c>
       <c r="M226" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N226" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="227" customFormat="1" ht="16.5" spans="1:20">
@@ -13057,7 +13060,7 @@
         <v>104100</v>
       </c>
       <c r="C227" s="63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D227" s="27">
         <v>104100001</v>
@@ -13066,7 +13069,7 @@
         <v>11</v>
       </c>
       <c r="F227" s="47" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G227" s="64" t="s">
         <v>50</v>
@@ -13087,10 +13090,10 @@
         <v>0</v>
       </c>
       <c r="M227" s="48" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N227" s="47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="228" customFormat="1" ht="16.5" spans="1:20">
@@ -13101,7 +13104,7 @@
         <v>104100</v>
       </c>
       <c r="C228" s="63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D228" s="27">
         <v>104100001</v>
@@ -13110,7 +13113,7 @@
         <v>12</v>
       </c>
       <c r="F228" s="47" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G228" s="64" t="s">
         <v>52</v>
@@ -13131,10 +13134,10 @@
         <v>0</v>
       </c>
       <c r="M228" s="48" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N228" s="47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="229" customFormat="1" ht="16.5" spans="1:20">
@@ -13145,7 +13148,7 @@
         <v>104100</v>
       </c>
       <c r="C229" s="63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D229" s="27">
         <v>104100001</v>
@@ -13154,7 +13157,7 @@
         <v>13</v>
       </c>
       <c r="F229" s="47" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G229" s="64" t="s">
         <v>54</v>
@@ -13175,10 +13178,10 @@
         <v>0</v>
       </c>
       <c r="M229" s="48" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N229" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="230" customFormat="1" ht="16.5" spans="1:20">
@@ -13189,7 +13192,7 @@
         <v>104200</v>
       </c>
       <c r="C230" s="63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D230" s="27">
         <v>104200001</v>
@@ -13198,7 +13201,7 @@
         <v>11</v>
       </c>
       <c r="F230" s="47" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G230" s="64" t="s">
         <v>50</v>
@@ -13219,10 +13222,10 @@
         <v>0</v>
       </c>
       <c r="M230" s="48" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N230" s="47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="231" customFormat="1" ht="16.5" spans="1:20">
@@ -13233,7 +13236,7 @@
         <v>104200</v>
       </c>
       <c r="C231" s="63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D231" s="27">
         <v>104200001</v>
@@ -13242,7 +13245,7 @@
         <v>12</v>
       </c>
       <c r="F231" s="47" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G231" s="64" t="s">
         <v>52</v>
@@ -13263,10 +13266,10 @@
         <v>0</v>
       </c>
       <c r="M231" s="48" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N231" s="47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="232" customFormat="1" ht="16.5" spans="1:20">
@@ -13277,7 +13280,7 @@
         <v>104200</v>
       </c>
       <c r="C232" s="63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D232" s="27">
         <v>104200001</v>
@@ -13286,7 +13289,7 @@
         <v>13</v>
       </c>
       <c r="F232" s="47" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G232" s="64" t="s">
         <v>54</v>
@@ -13307,10 +13310,10 @@
         <v>0</v>
       </c>
       <c r="M232" s="48" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N232" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="233" s="2" customFormat="1" ht="16.5" spans="1:20">
@@ -13780,10 +13783,10 @@
         <v>21</v>
       </c>
       <c r="F242" s="32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G242" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H242" s="17">
         <v>10000000</v>
@@ -14830,7 +14833,7 @@
         <v>21</v>
       </c>
       <c r="F263" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G263" s="25" t="s">
         <v>67</v>
@@ -15730,10 +15733,10 @@
         <v>21</v>
       </c>
       <c r="F281" s="24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G281" s="25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H281" s="31">
         <v>10000000</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -191,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="140">
   <si>
     <t>id</t>
   </si>
@@ -328,6 +328,9 @@
     <t>超级明星</t>
   </si>
   <si>
+    <t>16000:1</t>
+  </si>
+  <si>
     <t>10000_20000_50000_80000_120000_160000_200000</t>
   </si>
   <si>
@@ -361,6 +364,9 @@
     <t>财神</t>
   </si>
   <si>
+    <t>400:1</t>
+  </si>
+  <si>
     <t>埃及艳后</t>
   </si>
   <si>
@@ -373,10 +379,13 @@
     <t>杰克船长</t>
   </si>
   <si>
-    <t>200:1</t>
+    <t>2500:1</t>
   </si>
   <si>
     <t>雷神</t>
+  </si>
+  <si>
+    <t>4000:1</t>
   </si>
   <si>
     <t>财富银行</t>
@@ -394,10 +403,13 @@
     <t>寒冰王座</t>
   </si>
   <si>
-    <t>20:1</t>
+    <t>80:1</t>
   </si>
   <si>
     <t>200_400_1000_1600_2400_3200_4000</t>
+  </si>
+  <si>
+    <t>200:1</t>
   </si>
   <si>
     <t>2000_4000_10000_16000_24000_32000_40000</t>
@@ -413,6 +425,9 @@
   </si>
   <si>
     <t>20_40_100_200_400_1000_2000</t>
+  </si>
+  <si>
+    <t>20:1</t>
   </si>
   <si>
     <t>20000_40000_100000_160000_240000_320000_400000</t>
@@ -436,10 +451,10 @@
     <t>宙斯vs哈迪斯</t>
   </si>
   <si>
-    <t>750:1</t>
+    <t>750_1500_3750_6000_9000_12000_15000</t>
   </si>
   <si>
-    <t>750_1500_3750_6000_9000_12000_15000</t>
+    <t>750:1</t>
   </si>
   <si>
     <t>7500_15000_37500_60000_90000_120000_150000</t>
@@ -466,9 +481,6 @@
     <t>2500_5000_12500_20000_30000_40000_50000</t>
   </si>
   <si>
-    <t>2500:1</t>
-  </si>
-  <si>
     <t>象财神</t>
   </si>
   <si>
@@ -478,19 +490,13 @@
     <t>绿巨人</t>
   </si>
   <si>
-    <t>40:1</t>
+    <t>160:1</t>
   </si>
   <si>
     <t>400_800_2000_3200_4800_6400_8000</t>
   </si>
   <si>
-    <t>400:1</t>
-  </si>
-  <si>
     <t>4000_8000_20000_32000_48000_64000_80000</t>
-  </si>
-  <si>
-    <t>4000:1</t>
   </si>
   <si>
     <t>潘金莲</t>
@@ -503,6 +509,9 @@
   </si>
   <si>
     <t>愤怒的小鸡</t>
+  </si>
+  <si>
+    <t>40:1</t>
   </si>
   <si>
     <t>热血足球</t>
@@ -816,9 +825,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -827,9 +836,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -840,16 +850,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2263,10 +2272,10 @@
         <v>1</v>
       </c>
       <c r="F8" s="24">
-        <v>1000</v>
+        <v>16000</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H8" s="17">
         <v>10000000</v>
@@ -2313,10 +2322,10 @@
         <v>2</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="17">
         <v>100000000</v>
@@ -2363,10 +2372,10 @@
         <v>3</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10" s="31">
         <v>1000000000</v>
@@ -2404,7 +2413,7 @@
         <v>100700</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="27">
         <v>100700001</v>
@@ -2416,7 +2425,7 @@
         <v>50</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" s="17">
         <v>10000000</v>
@@ -2454,7 +2463,7 @@
         <v>100700</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="27">
         <v>100700001</v>
@@ -2463,10 +2472,10 @@
         <v>2</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H12" s="17">
         <v>100000000</v>
@@ -2504,7 +2513,7 @@
         <v>100700</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="27">
         <v>100700001</v>
@@ -2513,10 +2522,10 @@
         <v>3</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" s="31">
         <v>1000000000</v>
@@ -2554,7 +2563,7 @@
         <v>101200</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" s="27">
         <v>101200001</v>
@@ -2563,10 +2572,10 @@
         <v>1</v>
       </c>
       <c r="F14" s="32">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H14" s="17">
         <v>10000000</v>
@@ -2604,7 +2613,7 @@
         <v>101200</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="27">
         <v>101200001</v>
@@ -2654,7 +2663,7 @@
         <v>101200</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="27">
         <v>101200001</v>
@@ -2663,10 +2672,10 @@
         <v>3</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H16" s="31">
         <v>1000000000</v>
@@ -2704,7 +2713,7 @@
         <v>101400</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D17" s="27">
         <v>101400001</v>
@@ -2754,7 +2763,7 @@
         <v>101400</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" s="27">
         <v>101400001</v>
@@ -2804,7 +2813,7 @@
         <v>101400</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D19" s="27">
         <v>101400001</v>
@@ -2813,10 +2822,10 @@
         <v>3</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H19" s="31">
         <v>1000000000</v>
@@ -2854,7 +2863,7 @@
         <v>101700</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="27">
         <v>101700001</v>
@@ -2863,10 +2872,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H20" s="17">
         <v>10000000</v>
@@ -2904,7 +2913,7 @@
         <v>101700</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D21" s="27">
         <v>101700001</v>
@@ -2913,10 +2922,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H21" s="17">
         <v>100000000</v>
@@ -2954,7 +2963,7 @@
         <v>101700</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D22" s="27">
         <v>101700001</v>
@@ -2963,10 +2972,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H22" s="31">
         <v>1000000000</v>
@@ -3004,7 +3013,7 @@
         <v>102100</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D23" s="27">
         <v>102100001</v>
@@ -3013,10 +3022,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="24">
-        <v>200</v>
+        <v>2500</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H23" s="17">
         <v>10000000</v>
@@ -3054,7 +3063,7 @@
         <v>102100</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D24" s="27">
         <v>102100001</v>
@@ -3063,10 +3072,10 @@
         <v>2</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H24" s="17">
         <v>100000000</v>
@@ -3104,7 +3113,7 @@
         <v>102100</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D25" s="27">
         <v>102100001</v>
@@ -3113,10 +3122,10 @@
         <v>3</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H25" s="31">
         <v>1000000000</v>
@@ -3154,7 +3163,7 @@
         <v>102200</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D26" s="27">
         <v>102200001</v>
@@ -3163,10 +3172,10 @@
         <v>1</v>
       </c>
       <c r="F26" s="24">
-        <v>100</v>
+        <v>4000</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="H26" s="17">
         <v>10000000</v>
@@ -3204,7 +3213,7 @@
         <v>102200</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D27" s="27">
         <v>102200001</v>
@@ -3213,10 +3222,10 @@
         <v>2</v>
       </c>
       <c r="F27" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H27" s="17">
         <v>100000000</v>
@@ -3254,7 +3263,7 @@
         <v>102200</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D28" s="27">
         <v>102200001</v>
@@ -3263,10 +3272,10 @@
         <v>3</v>
       </c>
       <c r="F28" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H28" s="31">
         <v>1000000000</v>
@@ -3304,7 +3313,7 @@
         <v>102400</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D29" s="27">
         <v>102400026</v>
@@ -3313,10 +3322,10 @@
         <v>1</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G29" s="33" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H29" s="17">
         <v>10000000</v>
@@ -3354,7 +3363,7 @@
         <v>102400</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D30" s="27">
         <v>102400026</v>
@@ -3404,7 +3413,7 @@
         <v>102400</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D31" s="27">
         <v>102400026</v>
@@ -3454,7 +3463,7 @@
         <v>101800</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D32" s="27">
         <v>101800001</v>
@@ -3466,7 +3475,7 @@
         <v>50</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H32" s="17">
         <v>10000000</v>
@@ -3504,7 +3513,7 @@
         <v>101800</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D33" s="27">
         <v>101800001</v>
@@ -3513,10 +3522,10 @@
         <v>2</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H33" s="17">
         <v>100000000</v>
@@ -3554,7 +3563,7 @@
         <v>101800</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D34" s="27">
         <v>101800001</v>
@@ -3563,10 +3572,10 @@
         <v>3</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H34" s="31">
         <v>1000000000</v>
@@ -3604,7 +3613,7 @@
         <v>102500</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D35" s="27">
         <v>102500001</v>
@@ -3613,10 +3622,10 @@
         <v>1</v>
       </c>
       <c r="F35" s="24">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H35" s="17">
         <v>10000000</v>
@@ -3654,7 +3663,7 @@
         <v>102500</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D36" s="27">
         <v>102500001</v>
@@ -3663,10 +3672,10 @@
         <v>2</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H36" s="17">
         <v>100000000</v>
@@ -3704,7 +3713,7 @@
         <v>102500</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D37" s="27">
         <v>102500001</v>
@@ -3713,10 +3722,10 @@
         <v>3</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H37" s="31">
         <v>1000000000</v>
@@ -3754,7 +3763,7 @@
         <v>102300</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D38" s="27">
         <v>102300001</v>
@@ -3763,10 +3772,10 @@
         <v>1</v>
       </c>
       <c r="F38" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H38" s="17">
         <v>10000000</v>
@@ -3804,7 +3813,7 @@
         <v>102300</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D39" s="27">
         <v>102300001</v>
@@ -3813,10 +3822,10 @@
         <v>2</v>
       </c>
       <c r="F39" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G39" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H39" s="17">
         <v>100000000</v>
@@ -3854,7 +3863,7 @@
         <v>102300</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D40" s="27">
         <v>102300001</v>
@@ -3863,10 +3872,10 @@
         <v>3</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G40" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H40" s="31">
         <v>1000000000</v>
@@ -3904,7 +3913,7 @@
         <v>103400</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D41" s="27">
         <v>103000001</v>
@@ -3913,10 +3922,10 @@
         <v>1</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G41" s="33" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="H41" s="17">
         <v>10000000</v>
@@ -3954,7 +3963,7 @@
         <v>103400</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D42" s="27">
         <v>103000001</v>
@@ -3963,10 +3972,10 @@
         <v>2</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G42" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H42" s="17">
         <v>100000000</v>
@@ -4004,7 +4013,7 @@
         <v>103400</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D43" s="27">
         <v>103000001</v>
@@ -4013,10 +4022,10 @@
         <v>3</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H43" s="31">
         <v>1000000000</v>
@@ -4054,7 +4063,7 @@
         <v>103500</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D44" s="35">
         <v>102900001</v>
@@ -4104,7 +4113,7 @@
         <v>103500</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D45" s="35">
         <v>102900001</v>
@@ -4154,7 +4163,7 @@
         <v>103500</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D46" s="35">
         <v>102900001</v>
@@ -4163,10 +4172,10 @@
         <v>3</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G46" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H46" s="31">
         <v>1000000000</v>
@@ -4204,7 +4213,7 @@
         <v>103501</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D47" s="35">
         <v>103501001</v>
@@ -4254,7 +4263,7 @@
         <v>103501</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D48" s="35">
         <v>103501001</v>
@@ -4304,7 +4313,7 @@
         <v>103501</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D49" s="35">
         <v>103501001</v>
@@ -4313,10 +4322,10 @@
         <v>3</v>
       </c>
       <c r="F49" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G49" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H49" s="31">
         <v>1000000000</v>
@@ -4354,7 +4363,7 @@
         <v>103600</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D50" s="38">
         <v>103600001</v>
@@ -4363,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H50" s="41">
         <v>10000000</v>
@@ -4404,7 +4413,7 @@
         <v>103600</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D51" s="35">
         <v>103600001</v>
@@ -4413,10 +4422,10 @@
         <v>2</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H51" s="31">
         <v>100000000</v>
@@ -4454,7 +4463,7 @@
         <v>103600</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D52" s="35">
         <v>103600001</v>
@@ -4463,10 +4472,10 @@
         <v>3</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H52" s="31">
         <v>1000000000</v>
@@ -4504,7 +4513,7 @@
         <v>102800</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D53" s="35">
         <v>102800001</v>
@@ -4513,10 +4522,10 @@
         <v>1</v>
       </c>
       <c r="F53" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H53" s="31">
         <v>10000000</v>
@@ -4554,7 +4563,7 @@
         <v>102800</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D54" s="35">
         <v>102800001</v>
@@ -4563,10 +4572,10 @@
         <v>2</v>
       </c>
       <c r="F54" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G54" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H54" s="31">
         <v>100000000</v>
@@ -4604,7 +4613,7 @@
         <v>102800</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D55" s="35">
         <v>102800001</v>
@@ -4613,10 +4622,10 @@
         <v>3</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G55" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H55" s="31">
         <v>1000000000</v>
@@ -4654,7 +4663,7 @@
         <v>102000</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D56" s="35">
         <v>102000001</v>
@@ -4663,10 +4672,10 @@
         <v>1</v>
       </c>
       <c r="F56" s="24">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G56" s="25" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H56" s="31">
         <v>10000000</v>
@@ -4704,7 +4713,7 @@
         <v>102000</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D57" s="35">
         <v>102000001</v>
@@ -4713,10 +4722,10 @@
         <v>2</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G57" s="25" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H57" s="31">
         <v>100000000</v>
@@ -4754,7 +4763,7 @@
         <v>102000</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D58" s="35">
         <v>102000001</v>
@@ -4763,10 +4772,10 @@
         <v>3</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G58" s="25" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H58" s="31">
         <v>1000000000</v>
@@ -4804,7 +4813,7 @@
         <v>103401</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D59" s="35">
         <v>103400001</v>
@@ -4813,10 +4822,10 @@
         <v>1</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G59" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H59" s="31">
         <v>10000000</v>
@@ -4854,7 +4863,7 @@
         <v>103401</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D60" s="35">
         <v>103400001</v>
@@ -4863,10 +4872,10 @@
         <v>2</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G60" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H60" s="31">
         <v>100000000</v>
@@ -4904,7 +4913,7 @@
         <v>103401</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D61" s="35">
         <v>103400001</v>
@@ -4913,10 +4922,10 @@
         <v>3</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G61" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H61" s="31">
         <v>1000000000</v>
@@ -4954,7 +4963,7 @@
         <v>103800</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D62" s="35">
         <v>103800001</v>
@@ -4966,7 +4975,7 @@
         <v>5</v>
       </c>
       <c r="G62" s="25" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H62" s="31">
         <v>10000000</v>
@@ -5004,7 +5013,7 @@
         <v>103800</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D63" s="35">
         <v>103800001</v>
@@ -5013,10 +5022,10 @@
         <v>2</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G63" s="25" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H63" s="31">
         <v>100000000</v>
@@ -5054,7 +5063,7 @@
         <v>103800</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D64" s="35">
         <v>103800001</v>
@@ -5063,10 +5072,10 @@
         <v>3</v>
       </c>
       <c r="F64" s="24" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G64" s="25" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="H64" s="31">
         <v>1000000000</v>
@@ -5104,7 +5113,7 @@
         <v>102700</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D65" s="35">
         <v>102700001</v>
@@ -5116,7 +5125,7 @@
         <v>50</v>
       </c>
       <c r="G65" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H65" s="31">
         <v>10000000</v>
@@ -5154,7 +5163,7 @@
         <v>102700</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D66" s="35">
         <v>102700001</v>
@@ -5163,10 +5172,10 @@
         <v>2</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G66" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H66" s="31">
         <v>100000000</v>
@@ -5204,7 +5213,7 @@
         <v>102700</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D67" s="35">
         <v>102700001</v>
@@ -5213,10 +5222,10 @@
         <v>3</v>
       </c>
       <c r="F67" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H67" s="31">
         <v>1000000000</v>
@@ -5254,7 +5263,7 @@
         <v>103700</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D68" s="35">
         <v>103700001</v>
@@ -5304,7 +5313,7 @@
         <v>103700</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D69" s="35">
         <v>103700001</v>
@@ -5354,7 +5363,7 @@
         <v>103700</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D70" s="35">
         <v>103700001</v>
@@ -5363,10 +5372,10 @@
         <v>3</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G70" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H70" s="31">
         <v>1000000000</v>
@@ -5404,7 +5413,7 @@
         <v>103100</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D71" s="35">
         <v>103100001</v>
@@ -5413,10 +5422,10 @@
         <v>1</v>
       </c>
       <c r="F71" s="24">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="G71" s="25" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H71" s="31">
         <v>10000000</v>
@@ -5454,7 +5463,7 @@
         <v>103100</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D72" s="35">
         <v>103100001</v>
@@ -5463,10 +5472,10 @@
         <v>2</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G72" s="25" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="H72" s="31">
         <v>100000000</v>
@@ -5504,7 +5513,7 @@
         <v>103100</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D73" s="35">
         <v>103100001</v>
@@ -5513,10 +5522,10 @@
         <v>3</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G73" s="25" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="H73" s="31">
         <v>1000000000</v>
@@ -5554,7 +5563,7 @@
         <v>104000</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D74" s="35">
         <v>104000001</v>
@@ -5563,10 +5572,10 @@
         <v>1</v>
       </c>
       <c r="F74" s="24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H74" s="31">
         <v>10000000</v>
@@ -5604,7 +5613,7 @@
         <v>104000</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D75" s="35">
         <v>104000001</v>
@@ -5613,10 +5622,10 @@
         <v>2</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G75" s="25" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H75" s="31">
         <v>100000000</v>
@@ -5654,7 +5663,7 @@
         <v>104000</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D76" s="35">
         <v>104000001</v>
@@ -5663,10 +5672,10 @@
         <v>3</v>
       </c>
       <c r="F76" s="24" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G76" s="25" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="H76" s="31">
         <v>1000000000</v>
@@ -5704,7 +5713,7 @@
         <v>103900</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D77" s="35">
         <v>103900001</v>
@@ -5716,7 +5725,7 @@
         <v>40</v>
       </c>
       <c r="G77" s="25" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H77" s="31">
         <v>10000000</v>
@@ -5754,7 +5763,7 @@
         <v>103900</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D78" s="35">
         <v>103900001</v>
@@ -5763,10 +5772,10 @@
         <v>2</v>
       </c>
       <c r="F78" s="24" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G78" s="25" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="H78" s="31">
         <v>100000000</v>
@@ -5804,7 +5813,7 @@
         <v>103900</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D79" s="35">
         <v>103900001</v>
@@ -5813,10 +5822,10 @@
         <v>3</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G79" s="25" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="H79" s="31">
         <v>1000000000</v>
@@ -5854,7 +5863,7 @@
         <v>101600</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D80" s="35">
         <v>101600001</v>
@@ -5863,10 +5872,10 @@
         <v>1</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G80" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H80" s="31">
         <v>10000000</v>
@@ -5904,7 +5913,7 @@
         <v>101600</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D81" s="35">
         <v>101600001</v>
@@ -5913,10 +5922,10 @@
         <v>2</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G81" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H81" s="31">
         <v>100000000</v>
@@ -5954,7 +5963,7 @@
         <v>101600</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D82" s="35">
         <v>101600001</v>
@@ -5963,10 +5972,10 @@
         <v>3</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G82" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H82" s="31">
         <v>1000000000</v>
@@ -6004,7 +6013,7 @@
         <v>101500</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D83" s="35">
         <v>101500001</v>
@@ -6016,7 +6025,7 @@
         <v>800</v>
       </c>
       <c r="G83" s="25" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H83" s="31">
         <v>10000000</v>
@@ -6054,7 +6063,7 @@
         <v>101500</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D84" s="35">
         <v>101500001</v>
@@ -6063,10 +6072,10 @@
         <v>2</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G84" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H84" s="31">
         <v>100000000</v>
@@ -6104,7 +6113,7 @@
         <v>101500</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D85" s="35">
         <v>101500001</v>
@@ -6113,10 +6122,10 @@
         <v>3</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G85" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H85" s="31">
         <v>1000000000</v>
@@ -6154,7 +6163,7 @@
         <v>102600</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D86" s="35">
         <v>102600001</v>
@@ -6163,10 +6172,10 @@
         <v>1</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G86" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H86" s="31">
         <v>10000000</v>
@@ -6204,7 +6213,7 @@
         <v>102600</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D87" s="35">
         <v>102600001</v>
@@ -6213,10 +6222,10 @@
         <v>2</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G87" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H87" s="31">
         <v>100000000</v>
@@ -6254,7 +6263,7 @@
         <v>102600</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D88" s="35">
         <v>102600001</v>
@@ -6263,10 +6272,10 @@
         <v>3</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G88" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H88" s="31">
         <v>1000000000</v>
@@ -6304,7 +6313,7 @@
         <v>105000</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D89" s="35">
         <v>105000001</v>
@@ -6313,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G89" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H89" s="31">
         <v>10000000</v>
@@ -6354,7 +6363,7 @@
         <v>105000</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D90" s="35">
         <v>105000001</v>
@@ -6363,10 +6372,10 @@
         <v>2</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G90" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H90" s="31">
         <v>100000000</v>
@@ -6404,7 +6413,7 @@
         <v>105000</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D91" s="35">
         <v>105000001</v>
@@ -6413,10 +6422,10 @@
         <v>3</v>
       </c>
       <c r="F91" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G91" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H91" s="31">
         <v>1000000000</v>
@@ -6454,7 +6463,7 @@
         <v>105100</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D92" s="35">
         <v>105100001</v>
@@ -6504,7 +6513,7 @@
         <v>105100</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D93" s="35">
         <v>105100001</v>
@@ -6554,7 +6563,7 @@
         <v>105100</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D94" s="35">
         <v>105100001</v>
@@ -6563,10 +6572,10 @@
         <v>3</v>
       </c>
       <c r="F94" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G94" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H94" s="31">
         <v>1000000000</v>
@@ -6604,7 +6613,7 @@
         <v>105500</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D95" s="35">
         <v>105500001</v>
@@ -6613,10 +6622,10 @@
         <v>1</v>
       </c>
       <c r="F95" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H95" s="31">
         <v>10000000</v>
@@ -6654,7 +6663,7 @@
         <v>105500</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D96" s="35">
         <v>105500001</v>
@@ -6663,10 +6672,10 @@
         <v>2</v>
       </c>
       <c r="F96" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G96" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H96" s="31">
         <v>100000000</v>
@@ -6704,7 +6713,7 @@
         <v>105500</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D97" s="35">
         <v>105500001</v>
@@ -6713,10 +6722,10 @@
         <v>3</v>
       </c>
       <c r="F97" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G97" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H97" s="31">
         <v>1000000000</v>
@@ -6754,7 +6763,7 @@
         <v>104800</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D98" s="27">
         <v>104800001</v>
@@ -6763,10 +6772,10 @@
         <v>1</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G98" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H98" s="17">
         <v>10000000</v>
@@ -6784,7 +6793,7 @@
         <v>100</v>
       </c>
       <c r="M98" s="26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N98" s="24">
         <v>0</v>
@@ -6804,7 +6813,7 @@
         <v>104800</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D99" s="27">
         <v>104800001</v>
@@ -6813,10 +6822,10 @@
         <v>2</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G99" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H99" s="17">
         <v>100000000</v>
@@ -6834,7 +6843,7 @@
         <v>100</v>
       </c>
       <c r="M99" s="26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N99" s="24">
         <v>0</v>
@@ -6854,7 +6863,7 @@
         <v>104800</v>
       </c>
       <c r="C100" s="23" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D100" s="27">
         <v>104800001</v>
@@ -6863,10 +6872,10 @@
         <v>3</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G100" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H100" s="31">
         <v>1000000000</v>
@@ -6884,7 +6893,7 @@
         <v>100</v>
       </c>
       <c r="M100" s="26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N100" s="24">
         <v>0</v>
@@ -6904,7 +6913,7 @@
         <v>105501</v>
       </c>
       <c r="C101" s="23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D101" s="35">
         <v>105501001</v>
@@ -6913,10 +6922,10 @@
         <v>1</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G101" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H101" s="31">
         <v>10000000</v>
@@ -6954,7 +6963,7 @@
         <v>105501</v>
       </c>
       <c r="C102" s="23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D102" s="35">
         <v>105501001</v>
@@ -6963,10 +6972,10 @@
         <v>2</v>
       </c>
       <c r="F102" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G102" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H102" s="31">
         <v>100000000</v>
@@ -7004,7 +7013,7 @@
         <v>105501</v>
       </c>
       <c r="C103" s="23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D103" s="35">
         <v>105501001</v>
@@ -7013,10 +7022,10 @@
         <v>3</v>
       </c>
       <c r="F103" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G103" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H103" s="31">
         <v>1000000000</v>
@@ -7054,7 +7063,7 @@
         <v>105502</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D104" s="35">
         <v>105502001</v>
@@ -7063,10 +7072,10 @@
         <v>1</v>
       </c>
       <c r="F104" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G104" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H104" s="31">
         <v>10000000</v>
@@ -7104,7 +7113,7 @@
         <v>105502</v>
       </c>
       <c r="C105" s="23" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D105" s="35">
         <v>105502001</v>
@@ -7113,10 +7122,10 @@
         <v>2</v>
       </c>
       <c r="F105" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G105" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H105" s="31">
         <v>100000000</v>
@@ -7154,7 +7163,7 @@
         <v>105502</v>
       </c>
       <c r="C106" s="23" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D106" s="35">
         <v>105502001</v>
@@ -7163,10 +7172,10 @@
         <v>3</v>
       </c>
       <c r="F106" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G106" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H106" s="31">
         <v>1000000000</v>
@@ -7204,7 +7213,7 @@
         <v>105300</v>
       </c>
       <c r="C107" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D107" s="35">
         <v>105300001</v>
@@ -7213,10 +7222,10 @@
         <v>1</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G107" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H107" s="31">
         <v>10000000</v>
@@ -7254,7 +7263,7 @@
         <v>105300</v>
       </c>
       <c r="C108" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D108" s="35">
         <v>105300001</v>
@@ -7263,10 +7272,10 @@
         <v>2</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G108" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H108" s="31">
         <v>100000000</v>
@@ -7304,7 +7313,7 @@
         <v>105300</v>
       </c>
       <c r="C109" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D109" s="35">
         <v>105300001</v>
@@ -7313,10 +7322,10 @@
         <v>3</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G109" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H109" s="31">
         <v>1000000000</v>
@@ -7387,7 +7396,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O110" s="44"/>
       <c r="P110" s="44"/>
@@ -7437,7 +7446,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O111" s="44"/>
       <c r="P111" s="44"/>
@@ -7487,7 +7496,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O112" s="44"/>
       <c r="P112" s="44"/>
@@ -7537,7 +7546,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O113" s="44"/>
       <c r="P113" s="44"/>
@@ -7563,10 +7572,10 @@
         <v>11</v>
       </c>
       <c r="F114" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G114" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H114" s="53">
         <v>0</v>
@@ -7587,7 +7596,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O114" s="44"/>
       <c r="P114" s="44"/>
@@ -7613,10 +7622,10 @@
         <v>12</v>
       </c>
       <c r="F115" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G115" s="25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H115" s="57">
         <v>0</v>
@@ -7637,7 +7646,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O115" s="44"/>
       <c r="P115" s="44"/>
@@ -7654,7 +7663,7 @@
         <v>100700</v>
       </c>
       <c r="C116" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D116" s="51">
         <v>100700001</v>
@@ -7663,10 +7672,10 @@
         <v>10</v>
       </c>
       <c r="F116" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G116" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H116" s="53">
         <v>0</v>
@@ -7687,7 +7696,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O116" s="44"/>
       <c r="P116" s="44"/>
@@ -7704,7 +7713,7 @@
         <v>100700</v>
       </c>
       <c r="C117" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D117" s="51">
         <v>100700001</v>
@@ -7713,10 +7722,10 @@
         <v>11</v>
       </c>
       <c r="F117" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G117" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H117" s="53">
         <v>0</v>
@@ -7737,7 +7746,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O117" s="44"/>
       <c r="P117" s="44"/>
@@ -7754,7 +7763,7 @@
         <v>100700</v>
       </c>
       <c r="C118" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D118" s="51">
         <v>100700001</v>
@@ -7763,10 +7772,10 @@
         <v>12</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G118" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H118" s="57">
         <v>0</v>
@@ -7787,7 +7796,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O118" s="44"/>
       <c r="P118" s="44"/>
@@ -7804,7 +7813,7 @@
         <v>101200</v>
       </c>
       <c r="C119" s="52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D119" s="60">
         <v>101200001</v>
@@ -7837,7 +7846,7 @@
         <v>37</v>
       </c>
       <c r="N119" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O119" s="56"/>
       <c r="P119" s="56"/>
@@ -7854,7 +7863,7 @@
         <v>101200</v>
       </c>
       <c r="C120" s="52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D120" s="60">
         <v>101200001</v>
@@ -7887,7 +7896,7 @@
         <v>40</v>
       </c>
       <c r="N120" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O120" s="56"/>
       <c r="P120" s="56"/>
@@ -7904,7 +7913,7 @@
         <v>101200</v>
       </c>
       <c r="C121" s="52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D121" s="60">
         <v>101200001</v>
@@ -7913,10 +7922,10 @@
         <v>12</v>
       </c>
       <c r="F121" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G121" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H121" s="57">
         <v>0</v>
@@ -7937,7 +7946,7 @@
         <v>43</v>
       </c>
       <c r="N121" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O121" s="56"/>
       <c r="P121" s="56"/>
@@ -7954,7 +7963,7 @@
         <v>101400</v>
       </c>
       <c r="C122" s="50" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D122" s="51">
         <v>101400001</v>
@@ -7987,7 +7996,7 @@
         <v>37</v>
       </c>
       <c r="N122" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O122" s="44"/>
       <c r="P122" s="44"/>
@@ -8004,7 +8013,7 @@
         <v>101400</v>
       </c>
       <c r="C123" s="50" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D123" s="51">
         <v>101400001</v>
@@ -8037,7 +8046,7 @@
         <v>40</v>
       </c>
       <c r="N123" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O123" s="44"/>
       <c r="P123" s="44"/>
@@ -8054,7 +8063,7 @@
         <v>101400</v>
       </c>
       <c r="C124" s="50" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D124" s="51">
         <v>101400001</v>
@@ -8063,10 +8072,10 @@
         <v>12</v>
       </c>
       <c r="F124" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G124" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H124" s="57">
         <v>0</v>
@@ -8087,7 +8096,7 @@
         <v>43</v>
       </c>
       <c r="N124" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O124" s="44"/>
       <c r="P124" s="44"/>
@@ -8104,7 +8113,7 @@
         <v>101700</v>
       </c>
       <c r="C125" s="50" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D125" s="51">
         <v>101700001</v>
@@ -8113,10 +8122,10 @@
         <v>10</v>
       </c>
       <c r="F125" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G125" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H125" s="53">
         <v>0</v>
@@ -8137,7 +8146,7 @@
         <v>37</v>
       </c>
       <c r="N125" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O125" s="44"/>
       <c r="P125" s="44"/>
@@ -8154,7 +8163,7 @@
         <v>101700</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D126" s="51">
         <v>101700001</v>
@@ -8163,10 +8172,10 @@
         <v>11</v>
       </c>
       <c r="F126" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G126" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H126" s="53">
         <v>0</v>
@@ -8187,7 +8196,7 @@
         <v>40</v>
       </c>
       <c r="N126" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O126" s="44"/>
       <c r="P126" s="44"/>
@@ -8204,7 +8213,7 @@
         <v>101700</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D127" s="51">
         <v>101700001</v>
@@ -8213,10 +8222,10 @@
         <v>12</v>
       </c>
       <c r="F127" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G127" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H127" s="57">
         <v>0</v>
@@ -8237,7 +8246,7 @@
         <v>43</v>
       </c>
       <c r="N127" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O127" s="44"/>
       <c r="P127" s="44"/>
@@ -8254,7 +8263,7 @@
         <v>102100</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D128" s="51">
         <v>102100001</v>
@@ -8263,10 +8272,10 @@
         <v>10</v>
       </c>
       <c r="F128" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G128" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H128" s="53">
         <v>0</v>
@@ -8287,7 +8296,7 @@
         <v>37</v>
       </c>
       <c r="N128" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O128" s="44"/>
       <c r="P128" s="44"/>
@@ -8304,7 +8313,7 @@
         <v>102100</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D129" s="51">
         <v>102100001</v>
@@ -8313,10 +8322,10 @@
         <v>11</v>
       </c>
       <c r="F129" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G129" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H129" s="53">
         <v>0</v>
@@ -8337,7 +8346,7 @@
         <v>40</v>
       </c>
       <c r="N129" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O129" s="44"/>
       <c r="P129" s="44"/>
@@ -8354,7 +8363,7 @@
         <v>102100</v>
       </c>
       <c r="C130" s="50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D130" s="51">
         <v>102100001</v>
@@ -8363,10 +8372,10 @@
         <v>12</v>
       </c>
       <c r="F130" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G130" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H130" s="57">
         <v>0</v>
@@ -8387,7 +8396,7 @@
         <v>43</v>
       </c>
       <c r="N130" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O130" s="44"/>
       <c r="P130" s="44"/>
@@ -8404,7 +8413,7 @@
         <v>102200</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D131" s="51">
         <v>102200001</v>
@@ -8413,10 +8422,10 @@
         <v>10</v>
       </c>
       <c r="F131" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G131" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H131" s="53">
         <v>0</v>
@@ -8437,7 +8446,7 @@
         <v>37</v>
       </c>
       <c r="N131" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O131" s="44"/>
       <c r="P131" s="44"/>
@@ -8454,7 +8463,7 @@
         <v>102200</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D132" s="51">
         <v>102200001</v>
@@ -8463,10 +8472,10 @@
         <v>11</v>
       </c>
       <c r="F132" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G132" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H132" s="53">
         <v>0</v>
@@ -8487,7 +8496,7 @@
         <v>40</v>
       </c>
       <c r="N132" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O132" s="44"/>
       <c r="P132" s="44"/>
@@ -8504,7 +8513,7 @@
         <v>102200</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D133" s="51">
         <v>102200001</v>
@@ -8513,10 +8522,10 @@
         <v>12</v>
       </c>
       <c r="F133" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G133" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H133" s="57">
         <v>0</v>
@@ -8537,7 +8546,7 @@
         <v>43</v>
       </c>
       <c r="N133" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O133" s="44"/>
       <c r="P133" s="44"/>
@@ -8554,7 +8563,7 @@
         <v>102400</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D134" s="51">
         <v>102400026</v>
@@ -8587,7 +8596,7 @@
         <v>37</v>
       </c>
       <c r="N134" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O134" s="44"/>
       <c r="P134" s="44"/>
@@ -8604,7 +8613,7 @@
         <v>102400</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D135" s="51">
         <v>102400026</v>
@@ -8637,7 +8646,7 @@
         <v>40</v>
       </c>
       <c r="N135" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O135" s="44"/>
       <c r="P135" s="44"/>
@@ -8654,7 +8663,7 @@
         <v>102400</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D136" s="51">
         <v>102400026</v>
@@ -8687,7 +8696,7 @@
         <v>43</v>
       </c>
       <c r="N136" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O136" s="44"/>
       <c r="P136" s="44"/>
@@ -8704,7 +8713,7 @@
         <v>101800</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D137" s="51">
         <v>101800001</v>
@@ -8713,10 +8722,10 @@
         <v>10</v>
       </c>
       <c r="F137" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G137" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H137" s="57">
         <v>0</v>
@@ -8737,7 +8746,7 @@
         <v>37</v>
       </c>
       <c r="N137" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O137" s="44"/>
       <c r="P137" s="44"/>
@@ -8754,7 +8763,7 @@
         <v>101800</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D138" s="51">
         <v>101800001</v>
@@ -8763,10 +8772,10 @@
         <v>11</v>
       </c>
       <c r="F138" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G138" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H138" s="57">
         <v>0</v>
@@ -8787,7 +8796,7 @@
         <v>40</v>
       </c>
       <c r="N138" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O138" s="44"/>
       <c r="P138" s="44"/>
@@ -8804,7 +8813,7 @@
         <v>101800</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D139" s="51">
         <v>101800001</v>
@@ -8813,10 +8822,10 @@
         <v>12</v>
       </c>
       <c r="F139" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G139" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H139" s="57">
         <v>0</v>
@@ -8837,7 +8846,7 @@
         <v>43</v>
       </c>
       <c r="N139" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O139" s="44"/>
       <c r="P139" s="44"/>
@@ -8854,7 +8863,7 @@
         <v>102500</v>
       </c>
       <c r="C140" s="50" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D140" s="51">
         <v>102500001</v>
@@ -8863,10 +8872,10 @@
         <v>10</v>
       </c>
       <c r="F140" s="24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G140" s="25" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="H140" s="57">
         <v>0</v>
@@ -8887,7 +8896,7 @@
         <v>37</v>
       </c>
       <c r="N140" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O140" s="44"/>
       <c r="P140" s="44"/>
@@ -8904,7 +8913,7 @@
         <v>102500</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D141" s="51">
         <v>102500001</v>
@@ -8913,10 +8922,10 @@
         <v>11</v>
       </c>
       <c r="F141" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G141" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H141" s="57">
         <v>0</v>
@@ -8937,7 +8946,7 @@
         <v>40</v>
       </c>
       <c r="N141" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O141" s="44"/>
       <c r="P141" s="44"/>
@@ -8954,7 +8963,7 @@
         <v>102500</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D142" s="51">
         <v>102500001</v>
@@ -8963,10 +8972,10 @@
         <v>12</v>
       </c>
       <c r="F142" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G142" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H142" s="57">
         <v>0</v>
@@ -8987,7 +8996,7 @@
         <v>43</v>
       </c>
       <c r="N142" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O142" s="44"/>
       <c r="P142" s="44"/>
@@ -9004,7 +9013,7 @@
         <v>102300</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D143" s="51">
         <v>102300001</v>
@@ -9013,10 +9022,10 @@
         <v>10</v>
       </c>
       <c r="F143" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G143" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H143" s="57">
         <v>0</v>
@@ -9037,7 +9046,7 @@
         <v>37</v>
       </c>
       <c r="N143" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O143" s="44"/>
       <c r="P143" s="44"/>
@@ -9054,7 +9063,7 @@
         <v>102300</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D144" s="51">
         <v>102300001</v>
@@ -9063,10 +9072,10 @@
         <v>11</v>
       </c>
       <c r="F144" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G144" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H144" s="57">
         <v>0</v>
@@ -9087,7 +9096,7 @@
         <v>40</v>
       </c>
       <c r="N144" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O144" s="44"/>
       <c r="P144" s="44"/>
@@ -9104,7 +9113,7 @@
         <v>102300</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D145" s="51">
         <v>102300001</v>
@@ -9113,10 +9122,10 @@
         <v>12</v>
       </c>
       <c r="F145" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G145" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H145" s="57">
         <v>0</v>
@@ -9137,7 +9146,7 @@
         <v>43</v>
       </c>
       <c r="N145" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O145" s="44"/>
       <c r="P145" s="44"/>
@@ -9154,7 +9163,7 @@
         <v>103400</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D146" s="51">
         <v>103000001</v>
@@ -9163,10 +9172,10 @@
         <v>10</v>
       </c>
       <c r="F146" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G146" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H146" s="57">
         <v>0</v>
@@ -9187,7 +9196,7 @@
         <v>37</v>
       </c>
       <c r="N146" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O146" s="44"/>
       <c r="P146" s="44"/>
@@ -9204,7 +9213,7 @@
         <v>103400</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D147" s="51">
         <v>103000001</v>
@@ -9213,10 +9222,10 @@
         <v>11</v>
       </c>
       <c r="F147" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G147" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H147" s="57">
         <v>0</v>
@@ -9237,7 +9246,7 @@
         <v>40</v>
       </c>
       <c r="N147" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O147" s="44"/>
       <c r="P147" s="44"/>
@@ -9254,7 +9263,7 @@
         <v>103400</v>
       </c>
       <c r="C148" s="50" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D148" s="51">
         <v>103000001</v>
@@ -9263,10 +9272,10 @@
         <v>12</v>
       </c>
       <c r="F148" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G148" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H148" s="57">
         <v>0</v>
@@ -9287,7 +9296,7 @@
         <v>43</v>
       </c>
       <c r="N148" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O148" s="44"/>
       <c r="P148" s="44"/>
@@ -9304,7 +9313,7 @@
         <v>103500</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D149" s="51">
         <v>102900001</v>
@@ -9337,7 +9346,7 @@
         <v>37</v>
       </c>
       <c r="N149" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O149" s="44"/>
       <c r="P149" s="44"/>
@@ -9354,7 +9363,7 @@
         <v>103500</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D150" s="51">
         <v>102900001</v>
@@ -9387,7 +9396,7 @@
         <v>40</v>
       </c>
       <c r="N150" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O150" s="44"/>
       <c r="P150" s="44"/>
@@ -9404,7 +9413,7 @@
         <v>103500</v>
       </c>
       <c r="C151" s="50" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D151" s="51">
         <v>102900001</v>
@@ -9413,10 +9422,10 @@
         <v>12</v>
       </c>
       <c r="F151" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G151" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H151" s="57">
         <v>0</v>
@@ -9437,7 +9446,7 @@
         <v>43</v>
       </c>
       <c r="N151" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O151" s="44"/>
       <c r="P151" s="44"/>
@@ -9454,7 +9463,7 @@
         <v>103501</v>
       </c>
       <c r="C152" s="50" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D152" s="51">
         <v>103501001</v>
@@ -9487,7 +9496,7 @@
         <v>37</v>
       </c>
       <c r="N152" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O152" s="44"/>
       <c r="P152" s="44"/>
@@ -9504,7 +9513,7 @@
         <v>103501</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D153" s="51">
         <v>103501001</v>
@@ -9537,7 +9546,7 @@
         <v>40</v>
       </c>
       <c r="N153" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O153" s="44"/>
       <c r="P153" s="44"/>
@@ -9554,7 +9563,7 @@
         <v>103501</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D154" s="51">
         <v>103501001</v>
@@ -9563,10 +9572,10 @@
         <v>12</v>
       </c>
       <c r="F154" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G154" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H154" s="57">
         <v>0</v>
@@ -9587,7 +9596,7 @@
         <v>43</v>
       </c>
       <c r="N154" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O154" s="44"/>
       <c r="P154" s="44"/>
@@ -9604,7 +9613,7 @@
         <v>103600</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D155" s="51">
         <v>103600001</v>
@@ -9613,10 +9622,10 @@
         <v>10</v>
       </c>
       <c r="F155" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G155" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H155" s="53">
         <v>0</v>
@@ -9637,7 +9646,7 @@
         <v>37</v>
       </c>
       <c r="N155" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O155" s="44"/>
       <c r="P155" s="44"/>
@@ -9654,7 +9663,7 @@
         <v>103600</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D156" s="51">
         <v>103600001</v>
@@ -9663,10 +9672,10 @@
         <v>11</v>
       </c>
       <c r="F156" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G156" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H156" s="53">
         <v>0</v>
@@ -9687,7 +9696,7 @@
         <v>40</v>
       </c>
       <c r="N156" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O156" s="44"/>
       <c r="P156" s="44"/>
@@ -9704,7 +9713,7 @@
         <v>103600</v>
       </c>
       <c r="C157" s="50" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D157" s="51">
         <v>103600001</v>
@@ -9713,10 +9722,10 @@
         <v>12</v>
       </c>
       <c r="F157" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G157" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H157" s="57">
         <v>0</v>
@@ -9737,7 +9746,7 @@
         <v>43</v>
       </c>
       <c r="N157" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O157" s="44"/>
       <c r="P157" s="44"/>
@@ -9754,7 +9763,7 @@
         <v>102800</v>
       </c>
       <c r="C158" s="50" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D158" s="51">
         <v>102800001</v>
@@ -9763,10 +9772,10 @@
         <v>10</v>
       </c>
       <c r="F158" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G158" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H158" s="57">
         <v>0</v>
@@ -9787,7 +9796,7 @@
         <v>37</v>
       </c>
       <c r="N158" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O158" s="44"/>
       <c r="P158" s="44"/>
@@ -9804,7 +9813,7 @@
         <v>102800</v>
       </c>
       <c r="C159" s="50" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D159" s="51">
         <v>102800001</v>
@@ -9813,10 +9822,10 @@
         <v>11</v>
       </c>
       <c r="F159" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G159" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H159" s="57">
         <v>0</v>
@@ -9837,7 +9846,7 @@
         <v>40</v>
       </c>
       <c r="N159" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O159" s="44"/>
       <c r="P159" s="44"/>
@@ -9854,7 +9863,7 @@
         <v>102800</v>
       </c>
       <c r="C160" s="50" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D160" s="51">
         <v>102800001</v>
@@ -9863,10 +9872,10 @@
         <v>12</v>
       </c>
       <c r="F160" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G160" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H160" s="57">
         <v>0</v>
@@ -9887,7 +9896,7 @@
         <v>43</v>
       </c>
       <c r="N160" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O160" s="44"/>
       <c r="P160" s="44"/>
@@ -9904,7 +9913,7 @@
         <v>102000</v>
       </c>
       <c r="C161" s="50" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D161" s="51">
         <v>102000001</v>
@@ -9913,10 +9922,10 @@
         <v>10</v>
       </c>
       <c r="F161" s="24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G161" s="25" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H161" s="57">
         <v>0</v>
@@ -9937,7 +9946,7 @@
         <v>37</v>
       </c>
       <c r="N161" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O161" s="44"/>
       <c r="P161" s="44"/>
@@ -9954,7 +9963,7 @@
         <v>102000</v>
       </c>
       <c r="C162" s="50" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D162" s="51">
         <v>102000001</v>
@@ -9963,10 +9972,10 @@
         <v>11</v>
       </c>
       <c r="F162" s="24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G162" s="25" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H162" s="57">
         <v>0</v>
@@ -9987,7 +9996,7 @@
         <v>40</v>
       </c>
       <c r="N162" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O162" s="44"/>
       <c r="P162" s="44"/>
@@ -10004,7 +10013,7 @@
         <v>102000</v>
       </c>
       <c r="C163" s="50" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D163" s="51">
         <v>102000001</v>
@@ -10013,10 +10022,10 @@
         <v>12</v>
       </c>
       <c r="F163" s="24" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G163" s="25" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H163" s="57">
         <v>0</v>
@@ -10037,7 +10046,7 @@
         <v>43</v>
       </c>
       <c r="N163" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O163" s="44"/>
       <c r="P163" s="44"/>
@@ -10054,7 +10063,7 @@
         <v>103401</v>
       </c>
       <c r="C164" s="50" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D164" s="51">
         <v>103400001</v>
@@ -10063,10 +10072,10 @@
         <v>10</v>
       </c>
       <c r="F164" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G164" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H164" s="57">
         <v>0</v>
@@ -10087,7 +10096,7 @@
         <v>37</v>
       </c>
       <c r="N164" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O164" s="44"/>
       <c r="P164" s="44"/>
@@ -10104,7 +10113,7 @@
         <v>103401</v>
       </c>
       <c r="C165" s="50" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D165" s="51">
         <v>103400001</v>
@@ -10113,10 +10122,10 @@
         <v>11</v>
       </c>
       <c r="F165" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G165" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H165" s="57">
         <v>0</v>
@@ -10137,7 +10146,7 @@
         <v>40</v>
       </c>
       <c r="N165" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O165" s="44"/>
       <c r="P165" s="44"/>
@@ -10154,7 +10163,7 @@
         <v>103401</v>
       </c>
       <c r="C166" s="50" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D166" s="51">
         <v>103400001</v>
@@ -10163,10 +10172,10 @@
         <v>12</v>
       </c>
       <c r="F166" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G166" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H166" s="57">
         <v>0</v>
@@ -10187,7 +10196,7 @@
         <v>43</v>
       </c>
       <c r="N166" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O166" s="44"/>
       <c r="P166" s="44"/>
@@ -10204,7 +10213,7 @@
         <v>103800</v>
       </c>
       <c r="C167" s="50" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D167" s="51">
         <v>103800001</v>
@@ -10213,10 +10222,10 @@
         <v>11</v>
       </c>
       <c r="F167" s="24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G167" s="25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H167" s="57">
         <v>0</v>
@@ -10237,7 +10246,7 @@
         <v>37</v>
       </c>
       <c r="N167" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O167" s="44"/>
       <c r="P167" s="44"/>
@@ -10254,7 +10263,7 @@
         <v>103800</v>
       </c>
       <c r="C168" s="50" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D168" s="51">
         <v>103800001</v>
@@ -10263,10 +10272,10 @@
         <v>12</v>
       </c>
       <c r="F168" s="24" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G168" s="25" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H168" s="57">
         <v>0</v>
@@ -10287,7 +10296,7 @@
         <v>40</v>
       </c>
       <c r="N168" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O168" s="44"/>
       <c r="P168" s="44"/>
@@ -10304,7 +10313,7 @@
         <v>103800</v>
       </c>
       <c r="C169" s="50" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D169" s="51">
         <v>103800001</v>
@@ -10313,10 +10322,10 @@
         <v>13</v>
       </c>
       <c r="F169" s="24" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G169" s="25" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="H169" s="57">
         <v>0</v>
@@ -10337,7 +10346,7 @@
         <v>43</v>
       </c>
       <c r="N169" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O169" s="44"/>
       <c r="P169" s="44"/>
@@ -10354,7 +10363,7 @@
         <v>102700</v>
       </c>
       <c r="C170" s="50" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D170" s="51">
         <v>102700001</v>
@@ -10363,10 +10372,10 @@
         <v>11</v>
       </c>
       <c r="F170" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G170" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H170" s="57">
         <v>0</v>
@@ -10387,7 +10396,7 @@
         <v>37</v>
       </c>
       <c r="N170" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O170" s="44"/>
       <c r="P170" s="44"/>
@@ -10404,7 +10413,7 @@
         <v>102700</v>
       </c>
       <c r="C171" s="50" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D171" s="51">
         <v>102700001</v>
@@ -10413,10 +10422,10 @@
         <v>12</v>
       </c>
       <c r="F171" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G171" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H171" s="57">
         <v>0</v>
@@ -10437,7 +10446,7 @@
         <v>40</v>
       </c>
       <c r="N171" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O171" s="44"/>
       <c r="P171" s="44"/>
@@ -10454,7 +10463,7 @@
         <v>102700</v>
       </c>
       <c r="C172" s="50" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D172" s="51">
         <v>102700001</v>
@@ -10463,10 +10472,10 @@
         <v>13</v>
       </c>
       <c r="F172" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G172" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H172" s="57">
         <v>0</v>
@@ -10487,7 +10496,7 @@
         <v>43</v>
       </c>
       <c r="N172" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O172" s="44"/>
       <c r="P172" s="44"/>
@@ -10504,7 +10513,7 @@
         <v>103700</v>
       </c>
       <c r="C173" s="50" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D173" s="51">
         <v>103700001</v>
@@ -10537,7 +10546,7 @@
         <v>37</v>
       </c>
       <c r="N173" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O173" s="44"/>
       <c r="P173" s="44"/>
@@ -10554,7 +10563,7 @@
         <v>103700</v>
       </c>
       <c r="C174" s="50" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D174" s="51">
         <v>103700001</v>
@@ -10587,7 +10596,7 @@
         <v>40</v>
       </c>
       <c r="N174" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O174" s="44"/>
       <c r="P174" s="44"/>
@@ -10604,7 +10613,7 @@
         <v>103700</v>
       </c>
       <c r="C175" s="50" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D175" s="51">
         <v>103100001</v>
@@ -10613,10 +10622,10 @@
         <v>13</v>
       </c>
       <c r="F175" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G175" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H175" s="57">
         <v>0</v>
@@ -10637,7 +10646,7 @@
         <v>43</v>
       </c>
       <c r="N175" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O175" s="44"/>
       <c r="P175" s="44"/>
@@ -10654,7 +10663,7 @@
         <v>103100</v>
       </c>
       <c r="C176" s="50" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D176" s="51">
         <v>103100001</v>
@@ -10663,10 +10672,10 @@
         <v>11</v>
       </c>
       <c r="F176" s="24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G176" s="25" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H176" s="53">
         <v>0</v>
@@ -10687,7 +10696,7 @@
         <v>37</v>
       </c>
       <c r="N176" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O176" s="44"/>
       <c r="P176" s="44"/>
@@ -10704,7 +10713,7 @@
         <v>103100</v>
       </c>
       <c r="C177" s="50" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D177" s="51">
         <v>103100001</v>
@@ -10713,10 +10722,10 @@
         <v>12</v>
       </c>
       <c r="F177" s="24" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G177" s="25" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="H177" s="53">
         <v>0</v>
@@ -10737,7 +10746,7 @@
         <v>40</v>
       </c>
       <c r="N177" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O177" s="44"/>
       <c r="P177" s="44"/>
@@ -10754,7 +10763,7 @@
         <v>103100</v>
       </c>
       <c r="C178" s="50" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D178" s="51">
         <v>103100001</v>
@@ -10763,10 +10772,10 @@
         <v>13</v>
       </c>
       <c r="F178" s="24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G178" s="25" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="H178" s="57">
         <v>0</v>
@@ -10787,7 +10796,7 @@
         <v>43</v>
       </c>
       <c r="N178" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O178" s="44"/>
       <c r="P178" s="44"/>
@@ -10804,7 +10813,7 @@
         <v>104000</v>
       </c>
       <c r="C179" s="50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D179" s="51">
         <v>104000001</v>
@@ -10813,10 +10822,10 @@
         <v>11</v>
       </c>
       <c r="F179" s="24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G179" s="25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H179" s="57">
         <v>0</v>
@@ -10837,7 +10846,7 @@
         <v>37</v>
       </c>
       <c r="N179" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O179" s="44"/>
       <c r="P179" s="44"/>
@@ -10854,7 +10863,7 @@
         <v>104000</v>
       </c>
       <c r="C180" s="50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D180" s="51">
         <v>104000001</v>
@@ -10863,10 +10872,10 @@
         <v>12</v>
       </c>
       <c r="F180" s="24" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G180" s="25" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H180" s="57">
         <v>0</v>
@@ -10887,7 +10896,7 @@
         <v>40</v>
       </c>
       <c r="N180" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O180" s="44"/>
       <c r="P180" s="44"/>
@@ -10904,7 +10913,7 @@
         <v>104000</v>
       </c>
       <c r="C181" s="50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D181" s="51">
         <v>104000001</v>
@@ -10913,10 +10922,10 @@
         <v>13</v>
       </c>
       <c r="F181" s="24" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G181" s="25" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="H181" s="57">
         <v>0</v>
@@ -10937,7 +10946,7 @@
         <v>43</v>
       </c>
       <c r="N181" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O181" s="44"/>
       <c r="P181" s="44"/>
@@ -10954,7 +10963,7 @@
         <v>103900</v>
       </c>
       <c r="C182" s="50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D182" s="51">
         <v>103900001</v>
@@ -10963,10 +10972,10 @@
         <v>11</v>
       </c>
       <c r="F182" s="24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G182" s="25" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H182" s="57">
         <v>0</v>
@@ -10987,7 +10996,7 @@
         <v>37</v>
       </c>
       <c r="N182" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O182" s="44"/>
       <c r="P182" s="44"/>
@@ -11004,7 +11013,7 @@
         <v>103900</v>
       </c>
       <c r="C183" s="50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D183" s="51">
         <v>103900001</v>
@@ -11013,10 +11022,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="24" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G183" s="25" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="H183" s="57">
         <v>0</v>
@@ -11037,7 +11046,7 @@
         <v>40</v>
       </c>
       <c r="N183" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O183" s="44"/>
       <c r="P183" s="44"/>
@@ -11054,7 +11063,7 @@
         <v>103900</v>
       </c>
       <c r="C184" s="50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D184" s="51">
         <v>103900001</v>
@@ -11063,10 +11072,10 @@
         <v>13</v>
       </c>
       <c r="F184" s="24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G184" s="25" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="H184" s="57">
         <v>0</v>
@@ -11087,7 +11096,7 @@
         <v>43</v>
       </c>
       <c r="N184" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O184" s="44"/>
       <c r="P184" s="44"/>
@@ -11104,7 +11113,7 @@
         <v>101600</v>
       </c>
       <c r="C185" s="50" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D185" s="51">
         <v>101600001</v>
@@ -11113,10 +11122,10 @@
         <v>11</v>
       </c>
       <c r="F185" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G185" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H185" s="57">
         <v>0</v>
@@ -11137,7 +11146,7 @@
         <v>37</v>
       </c>
       <c r="N185" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O185" s="44"/>
       <c r="P185" s="44"/>
@@ -11154,7 +11163,7 @@
         <v>101600</v>
       </c>
       <c r="C186" s="50" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D186" s="51">
         <v>101600001</v>
@@ -11163,10 +11172,10 @@
         <v>12</v>
       </c>
       <c r="F186" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G186" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H186" s="57">
         <v>0</v>
@@ -11187,7 +11196,7 @@
         <v>40</v>
       </c>
       <c r="N186" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O186" s="44"/>
       <c r="P186" s="44"/>
@@ -11204,7 +11213,7 @@
         <v>101600</v>
       </c>
       <c r="C187" s="50" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D187" s="51">
         <v>101600001</v>
@@ -11213,10 +11222,10 @@
         <v>13</v>
       </c>
       <c r="F187" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G187" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H187" s="57">
         <v>0</v>
@@ -11237,7 +11246,7 @@
         <v>43</v>
       </c>
       <c r="N187" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O187" s="44"/>
       <c r="P187" s="44"/>
@@ -11254,7 +11263,7 @@
         <v>101500</v>
       </c>
       <c r="C188" s="50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D188" s="51">
         <v>101500001</v>
@@ -11263,10 +11272,10 @@
         <v>11</v>
       </c>
       <c r="F188" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G188" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H188" s="57">
         <v>0</v>
@@ -11287,7 +11296,7 @@
         <v>37</v>
       </c>
       <c r="N188" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O188" s="44"/>
       <c r="P188" s="44"/>
@@ -11304,7 +11313,7 @@
         <v>101500</v>
       </c>
       <c r="C189" s="50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D189" s="51">
         <v>101500001</v>
@@ -11313,10 +11322,10 @@
         <v>12</v>
       </c>
       <c r="F189" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G189" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H189" s="57">
         <v>0</v>
@@ -11337,7 +11346,7 @@
         <v>40</v>
       </c>
       <c r="N189" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O189" s="44"/>
       <c r="P189" s="44"/>
@@ -11354,7 +11363,7 @@
         <v>101500</v>
       </c>
       <c r="C190" s="50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D190" s="51">
         <v>101500001</v>
@@ -11363,10 +11372,10 @@
         <v>13</v>
       </c>
       <c r="F190" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G190" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H190" s="57">
         <v>0</v>
@@ -11387,7 +11396,7 @@
         <v>43</v>
       </c>
       <c r="N190" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O190" s="44"/>
       <c r="P190" s="44"/>
@@ -11404,7 +11413,7 @@
         <v>102600</v>
       </c>
       <c r="C191" s="50" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D191" s="51">
         <v>102600001</v>
@@ -11413,10 +11422,10 @@
         <v>11</v>
       </c>
       <c r="F191" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G191" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H191" s="57">
         <v>0</v>
@@ -11437,7 +11446,7 @@
         <v>37</v>
       </c>
       <c r="N191" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O191" s="44"/>
       <c r="P191" s="44"/>
@@ -11454,7 +11463,7 @@
         <v>102600</v>
       </c>
       <c r="C192" s="50" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D192" s="51">
         <v>102600001</v>
@@ -11463,10 +11472,10 @@
         <v>12</v>
       </c>
       <c r="F192" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G192" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H192" s="57">
         <v>0</v>
@@ -11487,7 +11496,7 @@
         <v>40</v>
       </c>
       <c r="N192" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O192" s="44"/>
       <c r="P192" s="44"/>
@@ -11504,7 +11513,7 @@
         <v>102600</v>
       </c>
       <c r="C193" s="50" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D193" s="51">
         <v>102600001</v>
@@ -11513,10 +11522,10 @@
         <v>13</v>
       </c>
       <c r="F193" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G193" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H193" s="57">
         <v>0</v>
@@ -11537,7 +11546,7 @@
         <v>43</v>
       </c>
       <c r="N193" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O193" s="44"/>
       <c r="P193" s="44"/>
@@ -11554,7 +11563,7 @@
         <v>105000</v>
       </c>
       <c r="C194" s="50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D194" s="51">
         <v>105000001</v>
@@ -11563,10 +11572,10 @@
         <v>11</v>
       </c>
       <c r="F194" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G194" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H194" s="57">
         <v>0</v>
@@ -11587,7 +11596,7 @@
         <v>37</v>
       </c>
       <c r="N194" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O194" s="44"/>
       <c r="P194" s="44"/>
@@ -11604,7 +11613,7 @@
         <v>105000</v>
       </c>
       <c r="C195" s="50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D195" s="51">
         <v>105000001</v>
@@ -11613,10 +11622,10 @@
         <v>12</v>
       </c>
       <c r="F195" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G195" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H195" s="57">
         <v>0</v>
@@ -11637,7 +11646,7 @@
         <v>40</v>
       </c>
       <c r="N195" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O195" s="44"/>
       <c r="P195" s="44"/>
@@ -11654,7 +11663,7 @@
         <v>105000</v>
       </c>
       <c r="C196" s="50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D196" s="51">
         <v>105000001</v>
@@ -11663,10 +11672,10 @@
         <v>13</v>
       </c>
       <c r="F196" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G196" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H196" s="57">
         <v>0</v>
@@ -11687,7 +11696,7 @@
         <v>43</v>
       </c>
       <c r="N196" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O196" s="44"/>
       <c r="P196" s="44"/>
@@ -11704,7 +11713,7 @@
         <v>105100</v>
       </c>
       <c r="C197" s="50" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D197" s="51">
         <v>105100001</v>
@@ -11737,7 +11746,7 @@
         <v>37</v>
       </c>
       <c r="N197" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O197" s="44"/>
       <c r="P197" s="44"/>
@@ -11754,7 +11763,7 @@
         <v>105100</v>
       </c>
       <c r="C198" s="50" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D198" s="51">
         <v>105100001</v>
@@ -11787,7 +11796,7 @@
         <v>40</v>
       </c>
       <c r="N198" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O198" s="44"/>
       <c r="P198" s="44"/>
@@ -11804,7 +11813,7 @@
         <v>105100</v>
       </c>
       <c r="C199" s="50" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D199" s="51">
         <v>105100001</v>
@@ -11813,10 +11822,10 @@
         <v>13</v>
       </c>
       <c r="F199" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G199" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H199" s="57">
         <v>0</v>
@@ -11837,7 +11846,7 @@
         <v>43</v>
       </c>
       <c r="N199" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O199" s="44"/>
       <c r="P199" s="44"/>
@@ -11854,7 +11863,7 @@
         <v>105400</v>
       </c>
       <c r="C200" s="50" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D200" s="51">
         <v>105400001</v>
@@ -11863,10 +11872,10 @@
         <v>11</v>
       </c>
       <c r="F200" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G200" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H200" s="57">
         <v>0</v>
@@ -11884,10 +11893,10 @@
         <v>0</v>
       </c>
       <c r="M200" s="26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N200" s="56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O200" s="44"/>
       <c r="P200" s="44"/>
@@ -11904,7 +11913,7 @@
         <v>105400</v>
       </c>
       <c r="C201" s="50" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D201" s="51">
         <v>105400001</v>
@@ -11913,10 +11922,10 @@
         <v>12</v>
       </c>
       <c r="F201" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G201" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H201" s="57">
         <v>0</v>
@@ -11934,10 +11943,10 @@
         <v>0</v>
       </c>
       <c r="M201" s="26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N201" s="56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O201" s="44"/>
       <c r="P201" s="44"/>
@@ -11954,7 +11963,7 @@
         <v>105400</v>
       </c>
       <c r="C202" s="50" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D202" s="51">
         <v>105400001</v>
@@ -11963,10 +11972,10 @@
         <v>13</v>
       </c>
       <c r="F202" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G202" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H202" s="57">
         <v>0</v>
@@ -11984,10 +11993,10 @@
         <v>0</v>
       </c>
       <c r="M202" s="26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N202" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O202" s="44"/>
       <c r="P202" s="44"/>
@@ -12004,7 +12013,7 @@
         <v>100800</v>
       </c>
       <c r="C203" s="13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D203" s="35">
         <v>100800001</v>
@@ -12013,10 +12022,10 @@
         <v>11</v>
       </c>
       <c r="F203" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G203" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H203" s="31">
         <v>0</v>
@@ -12034,10 +12043,10 @@
         <v>0</v>
       </c>
       <c r="M203" s="26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N203" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:20">
@@ -12048,7 +12057,7 @@
         <v>100800</v>
       </c>
       <c r="C204" s="13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D204" s="35">
         <v>100800001</v>
@@ -12057,10 +12066,10 @@
         <v>12</v>
       </c>
       <c r="F204" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G204" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H204" s="31">
         <v>0</v>
@@ -12078,10 +12087,10 @@
         <v>0</v>
       </c>
       <c r="M204" s="26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N204" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:20">
@@ -12092,7 +12101,7 @@
         <v>100800</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D205" s="35">
         <v>100800001</v>
@@ -12101,10 +12110,10 @@
         <v>13</v>
       </c>
       <c r="F205" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G205" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H205" s="31">
         <v>0</v>
@@ -12122,10 +12131,10 @@
         <v>0</v>
       </c>
       <c r="M205" s="26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N205" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:20">
@@ -12136,7 +12145,7 @@
         <v>105300</v>
       </c>
       <c r="C206" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D206" s="35">
         <v>105300001</v>
@@ -12145,10 +12154,10 @@
         <v>11</v>
       </c>
       <c r="F206" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G206" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H206" s="31">
         <v>0</v>
@@ -12166,10 +12175,10 @@
         <v>0</v>
       </c>
       <c r="M206" s="26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N206" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:20">
@@ -12180,7 +12189,7 @@
         <v>105300</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D207" s="35">
         <v>105300001</v>
@@ -12189,10 +12198,10 @@
         <v>12</v>
       </c>
       <c r="F207" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G207" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H207" s="31">
         <v>0</v>
@@ -12210,10 +12219,10 @@
         <v>0</v>
       </c>
       <c r="M207" s="26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N207" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:20">
@@ -12224,7 +12233,7 @@
         <v>105300</v>
       </c>
       <c r="C208" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D208" s="35">
         <v>105300001</v>
@@ -12233,10 +12242,10 @@
         <v>13</v>
       </c>
       <c r="F208" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G208" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H208" s="31">
         <v>0</v>
@@ -12254,10 +12263,10 @@
         <v>0</v>
       </c>
       <c r="M208" s="26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N208" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:14">
@@ -12268,7 +12277,7 @@
         <v>105700</v>
       </c>
       <c r="C209" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D209" s="35">
         <v>105700001</v>
@@ -12277,10 +12286,10 @@
         <v>11</v>
       </c>
       <c r="F209" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G209" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H209" s="31">
         <v>0</v>
@@ -12298,10 +12307,10 @@
         <v>0</v>
       </c>
       <c r="M209" s="26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N209" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:14">
@@ -12312,7 +12321,7 @@
         <v>105700</v>
       </c>
       <c r="C210" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D210" s="35">
         <v>105700001</v>
@@ -12321,10 +12330,10 @@
         <v>12</v>
       </c>
       <c r="F210" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G210" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H210" s="31">
         <v>0</v>
@@ -12342,10 +12351,10 @@
         <v>0</v>
       </c>
       <c r="M210" s="26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N210" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:14">
@@ -12356,7 +12365,7 @@
         <v>105700</v>
       </c>
       <c r="C211" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D211" s="35">
         <v>105700001</v>
@@ -12365,10 +12374,10 @@
         <v>13</v>
       </c>
       <c r="F211" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G211" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H211" s="31">
         <v>0</v>
@@ -12386,10 +12395,10 @@
         <v>0</v>
       </c>
       <c r="M211" s="26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N211" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="212" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12400,7 +12409,7 @@
         <v>105800</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D212" s="61">
         <v>105800001</v>
@@ -12409,10 +12418,10 @@
         <v>11</v>
       </c>
       <c r="F212" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G212" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H212" s="31">
         <v>0</v>
@@ -12430,10 +12439,10 @@
         <v>0</v>
       </c>
       <c r="M212" s="26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N212" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="213" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12444,7 +12453,7 @@
         <v>105800</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D213" s="61">
         <v>105800001</v>
@@ -12453,10 +12462,10 @@
         <v>12</v>
       </c>
       <c r="F213" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G213" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H213" s="31">
         <v>0</v>
@@ -12474,10 +12483,10 @@
         <v>0</v>
       </c>
       <c r="M213" s="26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N213" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="214" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12488,7 +12497,7 @@
         <v>105800</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D214" s="61">
         <v>105800001</v>
@@ -12497,10 +12506,10 @@
         <v>13</v>
       </c>
       <c r="F214" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G214" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H214" s="31">
         <v>0</v>
@@ -12518,10 +12527,10 @@
         <v>0</v>
       </c>
       <c r="M214" s="26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N214" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="215" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12532,7 +12541,7 @@
         <v>105500</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D215" s="61">
         <v>105500001</v>
@@ -12541,10 +12550,10 @@
         <v>11</v>
       </c>
       <c r="F215" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G215" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H215" s="31">
         <v>0</v>
@@ -12562,10 +12571,10 @@
         <v>0</v>
       </c>
       <c r="M215" s="26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N215" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="216" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12576,7 +12585,7 @@
         <v>105500</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D216" s="61">
         <v>105500001</v>
@@ -12585,10 +12594,10 @@
         <v>12</v>
       </c>
       <c r="F216" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G216" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H216" s="31">
         <v>0</v>
@@ -12606,10 +12615,10 @@
         <v>0</v>
       </c>
       <c r="M216" s="26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N216" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="217" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12620,7 +12629,7 @@
         <v>105500</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D217" s="61">
         <v>105500001</v>
@@ -12629,10 +12638,10 @@
         <v>13</v>
       </c>
       <c r="F217" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G217" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H217" s="31">
         <v>0</v>
@@ -12650,10 +12659,10 @@
         <v>0</v>
       </c>
       <c r="M217" s="26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N217" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:14">
@@ -12664,7 +12673,7 @@
         <v>104800</v>
       </c>
       <c r="C218" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D218" s="27">
         <v>104800001</v>
@@ -12673,10 +12682,10 @@
         <v>11</v>
       </c>
       <c r="F218" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G218" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H218" s="31">
         <v>0</v>
@@ -12694,10 +12703,10 @@
         <v>0</v>
       </c>
       <c r="M218" s="26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N218" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:14">
@@ -12708,7 +12717,7 @@
         <v>104800</v>
       </c>
       <c r="C219" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D219" s="27">
         <v>104800001</v>
@@ -12717,10 +12726,10 @@
         <v>12</v>
       </c>
       <c r="F219" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G219" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H219" s="31">
         <v>0</v>
@@ -12738,10 +12747,10 @@
         <v>0</v>
       </c>
       <c r="M219" s="26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N219" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:14">
@@ -12752,7 +12761,7 @@
         <v>104800</v>
       </c>
       <c r="C220" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D220" s="27">
         <v>104800001</v>
@@ -12761,10 +12770,10 @@
         <v>13</v>
       </c>
       <c r="F220" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G220" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H220" s="31">
         <v>0</v>
@@ -12782,10 +12791,10 @@
         <v>0</v>
       </c>
       <c r="M220" s="26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N220" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="221" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12796,7 +12805,7 @@
         <v>105501</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D221" s="61">
         <v>105501001</v>
@@ -12805,10 +12814,10 @@
         <v>11</v>
       </c>
       <c r="F221" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G221" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H221" s="31">
         <v>0</v>
@@ -12826,10 +12835,10 @@
         <v>0</v>
       </c>
       <c r="M221" s="26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N221" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="222" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12840,7 +12849,7 @@
         <v>105501</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D222" s="61">
         <v>105501001</v>
@@ -12849,10 +12858,10 @@
         <v>12</v>
       </c>
       <c r="F222" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G222" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H222" s="31">
         <v>0</v>
@@ -12870,10 +12879,10 @@
         <v>0</v>
       </c>
       <c r="M222" s="26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N222" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="223" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12884,7 +12893,7 @@
         <v>105501</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D223" s="61">
         <v>105501001</v>
@@ -12893,10 +12902,10 @@
         <v>13</v>
       </c>
       <c r="F223" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G223" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H223" s="31">
         <v>0</v>
@@ -12914,10 +12923,10 @@
         <v>0</v>
       </c>
       <c r="M223" s="26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N223" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="224" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12928,7 +12937,7 @@
         <v>105502</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D224" s="61">
         <v>105502001</v>
@@ -12937,10 +12946,10 @@
         <v>11</v>
       </c>
       <c r="F224" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G224" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H224" s="31">
         <v>0</v>
@@ -12958,10 +12967,10 @@
         <v>0</v>
       </c>
       <c r="M224" s="26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N224" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="225" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -12972,7 +12981,7 @@
         <v>105502</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D225" s="61">
         <v>105502001</v>
@@ -12981,10 +12990,10 @@
         <v>12</v>
       </c>
       <c r="F225" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G225" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H225" s="31">
         <v>0</v>
@@ -13002,10 +13011,10 @@
         <v>0</v>
       </c>
       <c r="M225" s="26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N225" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="226" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -13016,7 +13025,7 @@
         <v>105502</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D226" s="61">
         <v>105502001</v>
@@ -13025,10 +13034,10 @@
         <v>13</v>
       </c>
       <c r="F226" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G226" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H226" s="31">
         <v>0</v>
@@ -13046,10 +13055,10 @@
         <v>0</v>
       </c>
       <c r="M226" s="26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N226" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="227" customFormat="1" ht="16.5" spans="1:20">
@@ -13060,7 +13069,7 @@
         <v>104100</v>
       </c>
       <c r="C227" s="63" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D227" s="27">
         <v>104100001</v>
@@ -13069,10 +13078,10 @@
         <v>11</v>
       </c>
       <c r="F227" s="47" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G227" s="64" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H227" s="65">
         <v>0</v>
@@ -13090,10 +13099,10 @@
         <v>0</v>
       </c>
       <c r="M227" s="48" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N227" s="47" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="228" customFormat="1" ht="16.5" spans="1:20">
@@ -13104,7 +13113,7 @@
         <v>104100</v>
       </c>
       <c r="C228" s="63" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D228" s="27">
         <v>104100001</v>
@@ -13113,10 +13122,10 @@
         <v>12</v>
       </c>
       <c r="F228" s="47" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G228" s="64" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H228" s="65">
         <v>0</v>
@@ -13134,10 +13143,10 @@
         <v>0</v>
       </c>
       <c r="M228" s="48" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N228" s="47" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="229" customFormat="1" ht="16.5" spans="1:20">
@@ -13148,7 +13157,7 @@
         <v>104100</v>
       </c>
       <c r="C229" s="63" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D229" s="27">
         <v>104100001</v>
@@ -13157,10 +13166,10 @@
         <v>13</v>
       </c>
       <c r="F229" s="47" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G229" s="64" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H229" s="65">
         <v>0</v>
@@ -13178,10 +13187,10 @@
         <v>0</v>
       </c>
       <c r="M229" s="48" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N229" s="47" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="230" customFormat="1" ht="16.5" spans="1:20">
@@ -13192,7 +13201,7 @@
         <v>104200</v>
       </c>
       <c r="C230" s="63" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D230" s="27">
         <v>104200001</v>
@@ -13201,10 +13210,10 @@
         <v>11</v>
       </c>
       <c r="F230" s="47" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G230" s="64" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H230" s="65">
         <v>0</v>
@@ -13222,10 +13231,10 @@
         <v>0</v>
       </c>
       <c r="M230" s="48" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N230" s="47" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="231" customFormat="1" ht="16.5" spans="1:20">
@@ -13236,7 +13245,7 @@
         <v>104200</v>
       </c>
       <c r="C231" s="63" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D231" s="27">
         <v>104200001</v>
@@ -13245,10 +13254,10 @@
         <v>12</v>
       </c>
       <c r="F231" s="47" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G231" s="64" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H231" s="65">
         <v>0</v>
@@ -13266,10 +13275,10 @@
         <v>0</v>
       </c>
       <c r="M231" s="48" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N231" s="47" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="232" customFormat="1" ht="16.5" spans="1:20">
@@ -13280,7 +13289,7 @@
         <v>104200</v>
       </c>
       <c r="C232" s="63" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D232" s="27">
         <v>104200001</v>
@@ -13289,10 +13298,10 @@
         <v>13</v>
       </c>
       <c r="F232" s="47" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G232" s="64" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H232" s="65">
         <v>0</v>
@@ -13310,10 +13319,10 @@
         <v>0</v>
       </c>
       <c r="M232" s="48" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N232" s="47" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="233" s="2" customFormat="1" ht="16.5" spans="1:20">
@@ -13533,10 +13542,10 @@
         <v>22</v>
       </c>
       <c r="F237" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G237" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H237" s="17">
         <v>100000000</v>
@@ -13583,10 +13592,10 @@
         <v>23</v>
       </c>
       <c r="F238" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G238" s="25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H238" s="31">
         <v>1000000000</v>
@@ -13624,7 +13633,7 @@
         <v>100700</v>
       </c>
       <c r="C239" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D239" s="27">
         <v>100700001</v>
@@ -13633,10 +13642,10 @@
         <v>21</v>
       </c>
       <c r="F239" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G239" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H239" s="17">
         <v>10000000</v>
@@ -13674,7 +13683,7 @@
         <v>100700</v>
       </c>
       <c r="C240" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D240" s="27">
         <v>100700001</v>
@@ -13683,10 +13692,10 @@
         <v>22</v>
       </c>
       <c r="F240" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G240" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H240" s="17">
         <v>100000000</v>
@@ -13724,7 +13733,7 @@
         <v>100700</v>
       </c>
       <c r="C241" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D241" s="27">
         <v>100700001</v>
@@ -13733,10 +13742,10 @@
         <v>23</v>
       </c>
       <c r="F241" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G241" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H241" s="31">
         <v>1000000000</v>
@@ -13774,7 +13783,7 @@
         <v>101200</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D242" s="27">
         <v>101200001</v>
@@ -13783,10 +13792,10 @@
         <v>21</v>
       </c>
       <c r="F242" s="32" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G242" s="33" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H242" s="17">
         <v>10000000</v>
@@ -13824,7 +13833,7 @@
         <v>101200</v>
       </c>
       <c r="C243" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D243" s="27">
         <v>101200001</v>
@@ -13874,7 +13883,7 @@
         <v>101200</v>
       </c>
       <c r="C244" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D244" s="27">
         <v>101200001</v>
@@ -13883,10 +13892,10 @@
         <v>23</v>
       </c>
       <c r="F244" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G244" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H244" s="31">
         <v>1000000000</v>
@@ -13924,7 +13933,7 @@
         <v>101400</v>
       </c>
       <c r="C245" s="23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D245" s="27">
         <v>101400001</v>
@@ -13974,7 +13983,7 @@
         <v>101400</v>
       </c>
       <c r="C246" s="23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D246" s="27">
         <v>101400001</v>
@@ -14024,7 +14033,7 @@
         <v>101400</v>
       </c>
       <c r="C247" s="23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D247" s="27">
         <v>101400001</v>
@@ -14033,10 +14042,10 @@
         <v>23</v>
       </c>
       <c r="F247" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G247" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H247" s="31">
         <v>1000000000</v>
@@ -14074,7 +14083,7 @@
         <v>101700</v>
       </c>
       <c r="C248" s="23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D248" s="27">
         <v>101700001</v>
@@ -14083,10 +14092,10 @@
         <v>21</v>
       </c>
       <c r="F248" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G248" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H248" s="17">
         <v>10000000</v>
@@ -14124,7 +14133,7 @@
         <v>101700</v>
       </c>
       <c r="C249" s="23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D249" s="27">
         <v>101700001</v>
@@ -14133,10 +14142,10 @@
         <v>22</v>
       </c>
       <c r="F249" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G249" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H249" s="17">
         <v>100000000</v>
@@ -14174,7 +14183,7 @@
         <v>101700</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D250" s="27">
         <v>101700001</v>
@@ -14183,10 +14192,10 @@
         <v>23</v>
       </c>
       <c r="F250" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G250" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H250" s="31">
         <v>1000000000</v>
@@ -14224,7 +14233,7 @@
         <v>102100</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D251" s="27">
         <v>102100001</v>
@@ -14233,10 +14242,10 @@
         <v>21</v>
       </c>
       <c r="F251" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G251" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H251" s="17">
         <v>10000000</v>
@@ -14274,7 +14283,7 @@
         <v>102100</v>
       </c>
       <c r="C252" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D252" s="27">
         <v>102100001</v>
@@ -14283,10 +14292,10 @@
         <v>22</v>
       </c>
       <c r="F252" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G252" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H252" s="17">
         <v>100000000</v>
@@ -14324,7 +14333,7 @@
         <v>102100</v>
       </c>
       <c r="C253" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D253" s="27">
         <v>102100001</v>
@@ -14333,10 +14342,10 @@
         <v>23</v>
       </c>
       <c r="F253" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G253" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H253" s="31">
         <v>1000000000</v>
@@ -14374,7 +14383,7 @@
         <v>102200</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D254" s="27">
         <v>102200001</v>
@@ -14383,10 +14392,10 @@
         <v>21</v>
       </c>
       <c r="F254" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G254" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H254" s="17">
         <v>10000000</v>
@@ -14424,7 +14433,7 @@
         <v>102200</v>
       </c>
       <c r="C255" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D255" s="27">
         <v>102200001</v>
@@ -14433,10 +14442,10 @@
         <v>22</v>
       </c>
       <c r="F255" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G255" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H255" s="17">
         <v>100000000</v>
@@ -14474,7 +14483,7 @@
         <v>102200</v>
       </c>
       <c r="C256" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D256" s="27">
         <v>102200001</v>
@@ -14483,10 +14492,10 @@
         <v>23</v>
       </c>
       <c r="F256" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G256" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H256" s="31">
         <v>1000000000</v>
@@ -14524,7 +14533,7 @@
         <v>102400</v>
       </c>
       <c r="C257" s="23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D257" s="27">
         <v>102400026</v>
@@ -14533,10 +14542,10 @@
         <v>21</v>
       </c>
       <c r="F257" s="32" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G257" s="33" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H257" s="17">
         <v>10000000</v>
@@ -14574,7 +14583,7 @@
         <v>102400</v>
       </c>
       <c r="C258" s="23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D258" s="27">
         <v>102400026</v>
@@ -14624,7 +14633,7 @@
         <v>102400</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D259" s="27">
         <v>102400026</v>
@@ -14674,7 +14683,7 @@
         <v>101800</v>
       </c>
       <c r="C260" s="23" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D260" s="27">
         <v>101800001</v>
@@ -14683,10 +14692,10 @@
         <v>21</v>
       </c>
       <c r="F260" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G260" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H260" s="17">
         <v>10000000</v>
@@ -14724,7 +14733,7 @@
         <v>101800</v>
       </c>
       <c r="C261" s="23" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D261" s="27">
         <v>101800001</v>
@@ -14733,10 +14742,10 @@
         <v>22</v>
       </c>
       <c r="F261" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G261" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H261" s="17">
         <v>100000000</v>
@@ -14774,7 +14783,7 @@
         <v>101800</v>
       </c>
       <c r="C262" s="23" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D262" s="27">
         <v>101800001</v>
@@ -14783,10 +14792,10 @@
         <v>23</v>
       </c>
       <c r="F262" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G262" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H262" s="31">
         <v>1000000000</v>
@@ -14824,7 +14833,7 @@
         <v>102500</v>
       </c>
       <c r="C263" s="23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D263" s="27">
         <v>102500001</v>
@@ -14833,10 +14842,10 @@
         <v>21</v>
       </c>
       <c r="F263" s="24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G263" s="25" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="H263" s="17">
         <v>10000000</v>
@@ -14874,7 +14883,7 @@
         <v>102500</v>
       </c>
       <c r="C264" s="23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D264" s="27">
         <v>102500001</v>
@@ -14883,10 +14892,10 @@
         <v>22</v>
       </c>
       <c r="F264" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G264" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H264" s="17">
         <v>100000000</v>
@@ -14924,7 +14933,7 @@
         <v>102500</v>
       </c>
       <c r="C265" s="23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D265" s="27">
         <v>102500001</v>
@@ -14933,10 +14942,10 @@
         <v>23</v>
       </c>
       <c r="F265" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G265" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H265" s="31">
         <v>1000000000</v>
@@ -14974,7 +14983,7 @@
         <v>102300</v>
       </c>
       <c r="C266" s="23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D266" s="27">
         <v>102300001</v>
@@ -14983,10 +14992,10 @@
         <v>21</v>
       </c>
       <c r="F266" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G266" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H266" s="17">
         <v>10000000</v>
@@ -15024,7 +15033,7 @@
         <v>102300</v>
       </c>
       <c r="C267" s="23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D267" s="27">
         <v>102300001</v>
@@ -15033,10 +15042,10 @@
         <v>22</v>
       </c>
       <c r="F267" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G267" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H267" s="17">
         <v>100000000</v>
@@ -15074,7 +15083,7 @@
         <v>102300</v>
       </c>
       <c r="C268" s="23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D268" s="27">
         <v>102300001</v>
@@ -15083,10 +15092,10 @@
         <v>23</v>
       </c>
       <c r="F268" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G268" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H268" s="31">
         <v>1000000000</v>
@@ -15124,7 +15133,7 @@
         <v>103400</v>
       </c>
       <c r="C269" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D269" s="27">
         <v>103000001</v>
@@ -15133,10 +15142,10 @@
         <v>21</v>
       </c>
       <c r="F269" s="32" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G269" s="33" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="H269" s="17">
         <v>10000000</v>
@@ -15174,7 +15183,7 @@
         <v>103400</v>
       </c>
       <c r="C270" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D270" s="27">
         <v>103000001</v>
@@ -15183,10 +15192,10 @@
         <v>22</v>
       </c>
       <c r="F270" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G270" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H270" s="17">
         <v>100000000</v>
@@ -15224,7 +15233,7 @@
         <v>103400</v>
       </c>
       <c r="C271" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D271" s="27">
         <v>103000001</v>
@@ -15233,10 +15242,10 @@
         <v>23</v>
       </c>
       <c r="F271" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G271" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H271" s="31">
         <v>1000000000</v>
@@ -15274,7 +15283,7 @@
         <v>103500</v>
       </c>
       <c r="C272" s="23" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D272" s="35">
         <v>102900001</v>
@@ -15324,7 +15333,7 @@
         <v>103500</v>
       </c>
       <c r="C273" s="23" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D273" s="35">
         <v>102900001</v>
@@ -15374,7 +15383,7 @@
         <v>103500</v>
       </c>
       <c r="C274" s="23" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D274" s="35">
         <v>102900001</v>
@@ -15383,10 +15392,10 @@
         <v>23</v>
       </c>
       <c r="F274" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G274" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H274" s="31">
         <v>1000000000</v>
@@ -15424,7 +15433,7 @@
         <v>103501</v>
       </c>
       <c r="C275" s="23" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D275" s="35">
         <v>103501001</v>
@@ -15474,7 +15483,7 @@
         <v>103501</v>
       </c>
       <c r="C276" s="23" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D276" s="35">
         <v>103501001</v>
@@ -15524,7 +15533,7 @@
         <v>103501</v>
       </c>
       <c r="C277" s="23" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D277" s="35">
         <v>103501001</v>
@@ -15533,10 +15542,10 @@
         <v>23</v>
       </c>
       <c r="F277" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G277" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H277" s="31">
         <v>1000000000</v>
@@ -15574,7 +15583,7 @@
         <v>103600</v>
       </c>
       <c r="C278" s="37" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D278" s="38">
         <v>103600001</v>
@@ -15583,10 +15592,10 @@
         <v>21</v>
       </c>
       <c r="F278" s="39" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G278" s="40" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H278" s="41">
         <v>10000000</v>
@@ -15624,7 +15633,7 @@
         <v>103600</v>
       </c>
       <c r="C279" s="23" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D279" s="35">
         <v>103600001</v>
@@ -15633,10 +15642,10 @@
         <v>22</v>
       </c>
       <c r="F279" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G279" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H279" s="31">
         <v>100000000</v>
@@ -15674,7 +15683,7 @@
         <v>103600</v>
       </c>
       <c r="C280" s="23" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D280" s="35">
         <v>103600001</v>
@@ -15683,10 +15692,10 @@
         <v>23</v>
       </c>
       <c r="F280" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G280" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H280" s="31">
         <v>1000000000</v>
@@ -15724,7 +15733,7 @@
         <v>102000</v>
       </c>
       <c r="C281" s="23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D281" s="35">
         <v>102000001</v>
@@ -15733,10 +15742,10 @@
         <v>21</v>
       </c>
       <c r="F281" s="24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G281" s="25" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H281" s="31">
         <v>10000000</v>
@@ -15774,7 +15783,7 @@
         <v>102000</v>
       </c>
       <c r="C282" s="23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D282" s="35">
         <v>102000001</v>
@@ -15783,10 +15792,10 @@
         <v>22</v>
       </c>
       <c r="F282" s="24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G282" s="25" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H282" s="31">
         <v>100000000</v>
@@ -15824,7 +15833,7 @@
         <v>102000</v>
       </c>
       <c r="C283" s="23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D283" s="35">
         <v>102000001</v>
@@ -15833,10 +15842,10 @@
         <v>23</v>
       </c>
       <c r="F283" s="24" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G283" s="25" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H283" s="31">
         <v>1000000000</v>
@@ -15874,7 +15883,7 @@
         <v>103401</v>
       </c>
       <c r="C284" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D284" s="35">
         <v>103400001</v>
@@ -15883,10 +15892,10 @@
         <v>21</v>
       </c>
       <c r="F284" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G284" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H284" s="31">
         <v>10000000</v>
@@ -15924,7 +15933,7 @@
         <v>103401</v>
       </c>
       <c r="C285" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D285" s="35">
         <v>103400001</v>
@@ -15933,10 +15942,10 @@
         <v>22</v>
       </c>
       <c r="F285" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G285" s="25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H285" s="31">
         <v>100000000</v>
@@ -15974,7 +15983,7 @@
         <v>103401</v>
       </c>
       <c r="C286" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D286" s="35">
         <v>103400001</v>
@@ -15983,10 +15992,10 @@
         <v>23</v>
       </c>
       <c r="F286" s="24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G286" s="25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H286" s="31">
         <v>1000000000</v>
@@ -16024,7 +16033,7 @@
         <v>103800</v>
       </c>
       <c r="C287" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D287" s="35">
         <v>103800001</v>
@@ -16033,10 +16042,10 @@
         <v>21</v>
       </c>
       <c r="F287" s="24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G287" s="25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H287" s="31">
         <v>10000000</v>
@@ -16074,7 +16083,7 @@
         <v>103800</v>
       </c>
       <c r="C288" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D288" s="35">
         <v>103800001</v>
@@ -16083,10 +16092,10 @@
         <v>22</v>
       </c>
       <c r="F288" s="24" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G288" s="25" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H288" s="31">
         <v>100000000</v>
@@ -16124,7 +16133,7 @@
         <v>103800</v>
       </c>
       <c r="C289" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D289" s="35">
         <v>103800001</v>
@@ -16133,10 +16142,10 @@
         <v>23</v>
       </c>
       <c r="F289" s="24" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G289" s="25" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="H289" s="31">
         <v>1000000000</v>
@@ -16174,7 +16183,7 @@
         <v>104000</v>
       </c>
       <c r="C290" s="23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D290" s="35">
         <v>104000001</v>
@@ -16183,10 +16192,10 @@
         <v>21</v>
       </c>
       <c r="F290" s="24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G290" s="25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H290" s="31">
         <v>10000000</v>
@@ -16224,7 +16233,7 @@
         <v>104000</v>
       </c>
       <c r="C291" s="23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D291" s="35">
         <v>104000001</v>
@@ -16233,10 +16242,10 @@
         <v>22</v>
       </c>
       <c r="F291" s="24" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G291" s="25" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H291" s="31">
         <v>100000000</v>
@@ -16274,7 +16283,7 @@
         <v>104000</v>
       </c>
       <c r="C292" s="23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D292" s="35">
         <v>104000001</v>
@@ -16283,10 +16292,10 @@
         <v>23</v>
       </c>
       <c r="F292" s="24" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G292" s="25" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="H292" s="31">
         <v>1000000000</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -191,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="144">
   <si>
     <t>id</t>
   </si>
@@ -328,7 +328,7 @@
     <t>超级明星</t>
   </si>
   <si>
-    <t>16000:1</t>
+    <t>80000:1</t>
   </si>
   <si>
     <t>10000_20000_50000_80000_120000_160000_200000</t>
@@ -346,7 +346,7 @@
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>50:1</t>
+    <t>400:1</t>
   </si>
   <si>
     <t>500_1000_2500_4000_6000_8000_10000</t>
@@ -364,7 +364,7 @@
     <t>财神</t>
   </si>
   <si>
-    <t>400:1</t>
+    <t>12000:1</t>
   </si>
   <si>
     <t>埃及艳后</t>
@@ -376,16 +376,19 @@
     <t>50_100_250_400_600_800_1000</t>
   </si>
   <si>
+    <t>50:1</t>
+  </si>
+  <si>
     <t>杰克船长</t>
   </si>
   <si>
-    <t>2500:1</t>
+    <t>14000:1</t>
   </si>
   <si>
     <t>雷神</t>
   </si>
   <si>
-    <t>4000:1</t>
+    <t>16000:1</t>
   </si>
   <si>
     <t>财富银行</t>
@@ -400,10 +403,13 @@
     <t>篮球巨星</t>
   </si>
   <si>
+    <t>900:1</t>
+  </si>
+  <si>
     <t>寒冰王座</t>
   </si>
   <si>
-    <t>80:1</t>
+    <t>840:1</t>
   </si>
   <si>
     <t>200_400_1000_1600_2400_3200_4000</t>
@@ -481,6 +487,9 @@
     <t>2500_5000_12500_20000_30000_40000_50000</t>
   </si>
   <si>
+    <t>2500:1</t>
+  </si>
+  <si>
     <t>象财神</t>
   </si>
   <si>
@@ -490,13 +499,16 @@
     <t>绿巨人</t>
   </si>
   <si>
-    <t>160:1</t>
+    <t>1200:1</t>
   </si>
   <si>
     <t>400_800_2000_3200_4800_6400_8000</t>
   </si>
   <si>
     <t>4000_8000_20000_32000_48000_64000_80000</t>
+  </si>
+  <si>
+    <t>4000:1</t>
   </si>
   <si>
     <t>潘金莲</t>
@@ -520,7 +532,7 @@
     <t>狼月</t>
   </si>
   <si>
-    <t>800:1</t>
+    <t>600:1</t>
   </si>
   <si>
     <t>寻宝黄金城</t>
@@ -825,20 +837,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -862,6 +867,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -2272,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="24">
-        <v>16000</v>
+        <v>80000</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>45</v>
@@ -2422,7 +2434,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="24">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>51</v>
@@ -2572,7 +2584,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="32">
-        <v>400</v>
+        <v>12000</v>
       </c>
       <c r="G14" s="33" t="s">
         <v>57</v>
@@ -2875,7 +2887,7 @@
         <v>60</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H20" s="17">
         <v>10000000</v>
@@ -3013,7 +3025,7 @@
         <v>102100</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D23" s="27">
         <v>102100001</v>
@@ -3022,10 +3034,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="24">
-        <v>2500</v>
+        <v>14000</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H23" s="17">
         <v>10000000</v>
@@ -3063,7 +3075,7 @@
         <v>102100</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" s="27">
         <v>102100001</v>
@@ -3113,7 +3125,7 @@
         <v>102100</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D25" s="27">
         <v>102100001</v>
@@ -3163,7 +3175,7 @@
         <v>102200</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" s="27">
         <v>102200001</v>
@@ -3172,10 +3184,10 @@
         <v>1</v>
       </c>
       <c r="F26" s="24">
-        <v>4000</v>
+        <v>16000</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H26" s="17">
         <v>10000000</v>
@@ -3213,7 +3225,7 @@
         <v>102200</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D27" s="27">
         <v>102200001</v>
@@ -3263,7 +3275,7 @@
         <v>102200</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D28" s="27">
         <v>102200001</v>
@@ -3313,7 +3325,7 @@
         <v>102400</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D29" s="27">
         <v>102400026</v>
@@ -3322,10 +3334,10 @@
         <v>1</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G29" s="33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H29" s="17">
         <v>10000000</v>
@@ -3363,7 +3375,7 @@
         <v>102400</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D30" s="27">
         <v>102400026</v>
@@ -3413,7 +3425,7 @@
         <v>102400</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D31" s="27">
         <v>102400026</v>
@@ -3463,7 +3475,7 @@
         <v>101800</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D32" s="27">
         <v>101800001</v>
@@ -3472,10 +3484,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="24">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H32" s="17">
         <v>10000000</v>
@@ -3513,7 +3525,7 @@
         <v>101800</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D33" s="27">
         <v>101800001</v>
@@ -3563,7 +3575,7 @@
         <v>101800</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D34" s="27">
         <v>101800001</v>
@@ -3613,7 +3625,7 @@
         <v>102500</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D35" s="27">
         <v>102500001</v>
@@ -3622,10 +3634,10 @@
         <v>1</v>
       </c>
       <c r="F35" s="24">
-        <v>80</v>
+        <v>840</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H35" s="17">
         <v>10000000</v>
@@ -3663,7 +3675,7 @@
         <v>102500</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D36" s="27">
         <v>102500001</v>
@@ -3672,10 +3684,10 @@
         <v>2</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H36" s="17">
         <v>100000000</v>
@@ -3713,7 +3725,7 @@
         <v>102500</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D37" s="27">
         <v>102500001</v>
@@ -3722,10 +3734,10 @@
         <v>3</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H37" s="31">
         <v>1000000000</v>
@@ -3763,7 +3775,7 @@
         <v>102300</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D38" s="27">
         <v>102300001</v>
@@ -3775,7 +3787,7 @@
         <v>60</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H38" s="17">
         <v>10000000</v>
@@ -3813,7 +3825,7 @@
         <v>102300</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D39" s="27">
         <v>102300001</v>
@@ -3863,7 +3875,7 @@
         <v>102300</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D40" s="27">
         <v>102300001</v>
@@ -3913,7 +3925,7 @@
         <v>103400</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D41" s="27">
         <v>103000001</v>
@@ -3922,10 +3934,10 @@
         <v>1</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G41" s="33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H41" s="17">
         <v>10000000</v>
@@ -3963,7 +3975,7 @@
         <v>103400</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D42" s="27">
         <v>103000001</v>
@@ -3972,10 +3984,10 @@
         <v>2</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G42" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H42" s="17">
         <v>100000000</v>
@@ -4013,7 +4025,7 @@
         <v>103400</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D43" s="27">
         <v>103000001</v>
@@ -4022,10 +4034,10 @@
         <v>3</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H43" s="31">
         <v>1000000000</v>
@@ -4063,7 +4075,7 @@
         <v>103500</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D44" s="35">
         <v>102900001</v>
@@ -4113,7 +4125,7 @@
         <v>103500</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D45" s="35">
         <v>102900001</v>
@@ -4163,7 +4175,7 @@
         <v>103500</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D46" s="35">
         <v>102900001</v>
@@ -4213,7 +4225,7 @@
         <v>103501</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D47" s="35">
         <v>103501001</v>
@@ -4263,7 +4275,7 @@
         <v>103501</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D48" s="35">
         <v>103501001</v>
@@ -4313,7 +4325,7 @@
         <v>103501</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D49" s="35">
         <v>103501001</v>
@@ -4363,7 +4375,7 @@
         <v>103600</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D50" s="38">
         <v>103600001</v>
@@ -4372,10 +4384,10 @@
         <v>1</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H50" s="41">
         <v>10000000</v>
@@ -4413,7 +4425,7 @@
         <v>103600</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D51" s="35">
         <v>103600001</v>
@@ -4422,10 +4434,10 @@
         <v>2</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H51" s="31">
         <v>100000000</v>
@@ -4463,7 +4475,7 @@
         <v>103600</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D52" s="35">
         <v>103600001</v>
@@ -4472,10 +4484,10 @@
         <v>3</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H52" s="31">
         <v>1000000000</v>
@@ -4513,7 +4525,7 @@
         <v>102800</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D53" s="35">
         <v>102800001</v>
@@ -4525,7 +4537,7 @@
         <v>60</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H53" s="31">
         <v>10000000</v>
@@ -4563,7 +4575,7 @@
         <v>102800</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D54" s="35">
         <v>102800001</v>
@@ -4613,7 +4625,7 @@
         <v>102800</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D55" s="35">
         <v>102800001</v>
@@ -4663,7 +4675,7 @@
         <v>102000</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D56" s="35">
         <v>102000001</v>
@@ -4675,7 +4687,7 @@
         <v>2000</v>
       </c>
       <c r="G56" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H56" s="31">
         <v>10000000</v>
@@ -4713,7 +4725,7 @@
         <v>102000</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D57" s="35">
         <v>102000001</v>
@@ -4722,10 +4734,10 @@
         <v>2</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G57" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H57" s="31">
         <v>100000000</v>
@@ -4763,7 +4775,7 @@
         <v>102000</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D58" s="35">
         <v>102000001</v>
@@ -4772,10 +4784,10 @@
         <v>3</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G58" s="25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H58" s="31">
         <v>1000000000</v>
@@ -4813,7 +4825,7 @@
         <v>103401</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D59" s="35">
         <v>103400001</v>
@@ -4822,10 +4834,10 @@
         <v>1</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G59" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H59" s="31">
         <v>10000000</v>
@@ -4863,7 +4875,7 @@
         <v>103401</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D60" s="35">
         <v>103400001</v>
@@ -4872,10 +4884,10 @@
         <v>2</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G60" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H60" s="31">
         <v>100000000</v>
@@ -4913,7 +4925,7 @@
         <v>103401</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D61" s="35">
         <v>103400001</v>
@@ -4922,10 +4934,10 @@
         <v>3</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G61" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H61" s="31">
         <v>1000000000</v>
@@ -4963,7 +4975,7 @@
         <v>103800</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D62" s="35">
         <v>103800001</v>
@@ -4975,7 +4987,7 @@
         <v>5</v>
       </c>
       <c r="G62" s="25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H62" s="31">
         <v>10000000</v>
@@ -5013,7 +5025,7 @@
         <v>103800</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D63" s="35">
         <v>103800001</v>
@@ -5022,10 +5034,10 @@
         <v>2</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G63" s="25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H63" s="31">
         <v>100000000</v>
@@ -5063,7 +5075,7 @@
         <v>103800</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D64" s="35">
         <v>103800001</v>
@@ -5072,10 +5084,10 @@
         <v>3</v>
       </c>
       <c r="F64" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G64" s="25" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="H64" s="31">
         <v>1000000000</v>
@@ -5113,7 +5125,7 @@
         <v>102700</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D65" s="35">
         <v>102700001</v>
@@ -5122,10 +5134,10 @@
         <v>1</v>
       </c>
       <c r="F65" s="24">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G65" s="25" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="H65" s="31">
         <v>10000000</v>
@@ -5163,7 +5175,7 @@
         <v>102700</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D66" s="35">
         <v>102700001</v>
@@ -5213,7 +5225,7 @@
         <v>102700</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D67" s="35">
         <v>102700001</v>
@@ -5263,7 +5275,7 @@
         <v>103700</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D68" s="35">
         <v>103700001</v>
@@ -5313,7 +5325,7 @@
         <v>103700</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D69" s="35">
         <v>103700001</v>
@@ -5363,7 +5375,7 @@
         <v>103700</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D70" s="35">
         <v>103700001</v>
@@ -5413,7 +5425,7 @@
         <v>103100</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D71" s="35">
         <v>103100001</v>
@@ -5422,10 +5434,10 @@
         <v>1</v>
       </c>
       <c r="F71" s="24">
-        <v>160</v>
+        <v>1200</v>
       </c>
       <c r="G71" s="25" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H71" s="31">
         <v>10000000</v>
@@ -5463,7 +5475,7 @@
         <v>103100</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D72" s="35">
         <v>103100001</v>
@@ -5472,10 +5484,10 @@
         <v>2</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G72" s="25" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H72" s="31">
         <v>100000000</v>
@@ -5513,7 +5525,7 @@
         <v>103100</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D73" s="35">
         <v>103100001</v>
@@ -5522,10 +5534,10 @@
         <v>3</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G73" s="25" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="H73" s="31">
         <v>1000000000</v>
@@ -5563,7 +5575,7 @@
         <v>104000</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D74" s="35">
         <v>104000001</v>
@@ -5572,10 +5584,10 @@
         <v>1</v>
       </c>
       <c r="F74" s="24" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H74" s="31">
         <v>10000000</v>
@@ -5613,7 +5625,7 @@
         <v>104000</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D75" s="35">
         <v>104000001</v>
@@ -5622,10 +5634,10 @@
         <v>2</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G75" s="25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H75" s="31">
         <v>100000000</v>
@@ -5663,7 +5675,7 @@
         <v>104000</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D76" s="35">
         <v>104000001</v>
@@ -5672,10 +5684,10 @@
         <v>3</v>
       </c>
       <c r="F76" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G76" s="25" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="H76" s="31">
         <v>1000000000</v>
@@ -5713,7 +5725,7 @@
         <v>103900</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D77" s="35">
         <v>103900001</v>
@@ -5725,7 +5737,7 @@
         <v>40</v>
       </c>
       <c r="G77" s="25" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H77" s="31">
         <v>10000000</v>
@@ -5763,7 +5775,7 @@
         <v>103900</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D78" s="35">
         <v>103900001</v>
@@ -5772,10 +5784,10 @@
         <v>2</v>
       </c>
       <c r="F78" s="24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G78" s="25" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H78" s="31">
         <v>100000000</v>
@@ -5813,7 +5825,7 @@
         <v>103900</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D79" s="35">
         <v>103900001</v>
@@ -5822,10 +5834,10 @@
         <v>3</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G79" s="25" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="H79" s="31">
         <v>1000000000</v>
@@ -5863,7 +5875,7 @@
         <v>101600</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D80" s="35">
         <v>101600001</v>
@@ -5875,7 +5887,7 @@
         <v>60</v>
       </c>
       <c r="G80" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H80" s="31">
         <v>10000000</v>
@@ -5913,7 +5925,7 @@
         <v>101600</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D81" s="35">
         <v>101600001</v>
@@ -5963,7 +5975,7 @@
         <v>101600</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D82" s="35">
         <v>101600001</v>
@@ -6013,7 +6025,7 @@
         <v>101500</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D83" s="35">
         <v>101500001</v>
@@ -6022,10 +6034,10 @@
         <v>1</v>
       </c>
       <c r="F83" s="24">
-        <v>800</v>
+        <v>6000</v>
       </c>
       <c r="G83" s="25" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H83" s="31">
         <v>10000000</v>
@@ -6063,7 +6075,7 @@
         <v>101500</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D84" s="35">
         <v>101500001</v>
@@ -6113,7 +6125,7 @@
         <v>101500</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D85" s="35">
         <v>101500001</v>
@@ -6163,7 +6175,7 @@
         <v>102600</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D86" s="35">
         <v>102600001</v>
@@ -6175,7 +6187,7 @@
         <v>60</v>
       </c>
       <c r="G86" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H86" s="31">
         <v>10000000</v>
@@ -6213,7 +6225,7 @@
         <v>102600</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D87" s="35">
         <v>102600001</v>
@@ -6263,7 +6275,7 @@
         <v>102600</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D88" s="35">
         <v>102600001</v>
@@ -6313,7 +6325,7 @@
         <v>105000</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D89" s="35">
         <v>105000001</v>
@@ -6325,7 +6337,7 @@
         <v>60</v>
       </c>
       <c r="G89" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H89" s="31">
         <v>10000000</v>
@@ -6363,7 +6375,7 @@
         <v>105000</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D90" s="35">
         <v>105000001</v>
@@ -6413,7 +6425,7 @@
         <v>105000</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D91" s="35">
         <v>105000001</v>
@@ -6463,7 +6475,7 @@
         <v>105100</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D92" s="35">
         <v>105100001</v>
@@ -6513,7 +6525,7 @@
         <v>105100</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D93" s="35">
         <v>105100001</v>
@@ -6563,7 +6575,7 @@
         <v>105100</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D94" s="35">
         <v>105100001</v>
@@ -6613,7 +6625,7 @@
         <v>105500</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D95" s="35">
         <v>105500001</v>
@@ -6622,10 +6634,10 @@
         <v>1</v>
       </c>
       <c r="F95" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H95" s="31">
         <v>10000000</v>
@@ -6663,7 +6675,7 @@
         <v>105500</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D96" s="35">
         <v>105500001</v>
@@ -6672,10 +6684,10 @@
         <v>2</v>
       </c>
       <c r="F96" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G96" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H96" s="31">
         <v>100000000</v>
@@ -6713,7 +6725,7 @@
         <v>105500</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D97" s="35">
         <v>105500001</v>
@@ -6722,10 +6734,10 @@
         <v>3</v>
       </c>
       <c r="F97" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G97" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H97" s="31">
         <v>1000000000</v>
@@ -6763,7 +6775,7 @@
         <v>104800</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D98" s="27">
         <v>104800001</v>
@@ -6772,10 +6784,10 @@
         <v>1</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G98" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H98" s="17">
         <v>10000000</v>
@@ -6793,7 +6805,7 @@
         <v>100</v>
       </c>
       <c r="M98" s="26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N98" s="24">
         <v>0</v>
@@ -6813,7 +6825,7 @@
         <v>104800</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D99" s="27">
         <v>104800001</v>
@@ -6822,7 +6834,7 @@
         <v>2</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G99" s="25" t="s">
         <v>53</v>
@@ -6843,7 +6855,7 @@
         <v>100</v>
       </c>
       <c r="M99" s="26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N99" s="24">
         <v>0</v>
@@ -6863,7 +6875,7 @@
         <v>104800</v>
       </c>
       <c r="C100" s="23" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D100" s="27">
         <v>104800001</v>
@@ -6872,7 +6884,7 @@
         <v>3</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G100" s="25" t="s">
         <v>55</v>
@@ -6893,7 +6905,7 @@
         <v>100</v>
       </c>
       <c r="M100" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N100" s="24">
         <v>0</v>
@@ -6913,7 +6925,7 @@
         <v>105501</v>
       </c>
       <c r="C101" s="23" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D101" s="35">
         <v>105501001</v>
@@ -6922,10 +6934,10 @@
         <v>1</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G101" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H101" s="31">
         <v>10000000</v>
@@ -6963,7 +6975,7 @@
         <v>105501</v>
       </c>
       <c r="C102" s="23" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D102" s="35">
         <v>105501001</v>
@@ -6972,10 +6984,10 @@
         <v>2</v>
       </c>
       <c r="F102" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G102" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H102" s="31">
         <v>100000000</v>
@@ -7013,7 +7025,7 @@
         <v>105501</v>
       </c>
       <c r="C103" s="23" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D103" s="35">
         <v>105501001</v>
@@ -7022,10 +7034,10 @@
         <v>3</v>
       </c>
       <c r="F103" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G103" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H103" s="31">
         <v>1000000000</v>
@@ -7063,7 +7075,7 @@
         <v>105502</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D104" s="35">
         <v>105502001</v>
@@ -7072,10 +7084,10 @@
         <v>1</v>
       </c>
       <c r="F104" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G104" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H104" s="31">
         <v>10000000</v>
@@ -7113,7 +7125,7 @@
         <v>105502</v>
       </c>
       <c r="C105" s="23" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D105" s="35">
         <v>105502001</v>
@@ -7122,10 +7134,10 @@
         <v>2</v>
       </c>
       <c r="F105" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G105" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H105" s="31">
         <v>100000000</v>
@@ -7163,7 +7175,7 @@
         <v>105502</v>
       </c>
       <c r="C106" s="23" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D106" s="35">
         <v>105502001</v>
@@ -7172,10 +7184,10 @@
         <v>3</v>
       </c>
       <c r="F106" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G106" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H106" s="31">
         <v>1000000000</v>
@@ -7213,7 +7225,7 @@
         <v>105300</v>
       </c>
       <c r="C107" s="23" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D107" s="35">
         <v>105300001</v>
@@ -7222,10 +7234,10 @@
         <v>1</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G107" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H107" s="31">
         <v>10000000</v>
@@ -7263,7 +7275,7 @@
         <v>105300</v>
       </c>
       <c r="C108" s="23" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D108" s="35">
         <v>105300001</v>
@@ -7272,7 +7284,7 @@
         <v>2</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G108" s="25" t="s">
         <v>53</v>
@@ -7313,7 +7325,7 @@
         <v>105300</v>
       </c>
       <c r="C109" s="23" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D109" s="35">
         <v>105300001</v>
@@ -7322,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G109" s="25" t="s">
         <v>55</v>
@@ -7396,7 +7408,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O110" s="44"/>
       <c r="P110" s="44"/>
@@ -7446,7 +7458,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O111" s="44"/>
       <c r="P111" s="44"/>
@@ -7496,7 +7508,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O112" s="44"/>
       <c r="P112" s="44"/>
@@ -7546,7 +7558,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O113" s="44"/>
       <c r="P113" s="44"/>
@@ -7596,7 +7608,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O114" s="44"/>
       <c r="P114" s="44"/>
@@ -7646,7 +7658,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O115" s="44"/>
       <c r="P115" s="44"/>
@@ -7675,7 +7687,7 @@
         <v>60</v>
       </c>
       <c r="G116" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H116" s="53">
         <v>0</v>
@@ -7696,7 +7708,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O116" s="44"/>
       <c r="P116" s="44"/>
@@ -7746,7 +7758,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O117" s="44"/>
       <c r="P117" s="44"/>
@@ -7796,7 +7808,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O118" s="44"/>
       <c r="P118" s="44"/>
@@ -7846,7 +7858,7 @@
         <v>37</v>
       </c>
       <c r="N119" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O119" s="56"/>
       <c r="P119" s="56"/>
@@ -7896,7 +7908,7 @@
         <v>40</v>
       </c>
       <c r="N120" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O120" s="56"/>
       <c r="P120" s="56"/>
@@ -7946,7 +7958,7 @@
         <v>43</v>
       </c>
       <c r="N121" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O121" s="56"/>
       <c r="P121" s="56"/>
@@ -7996,7 +8008,7 @@
         <v>37</v>
       </c>
       <c r="N122" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O122" s="44"/>
       <c r="P122" s="44"/>
@@ -8046,7 +8058,7 @@
         <v>40</v>
       </c>
       <c r="N123" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O123" s="44"/>
       <c r="P123" s="44"/>
@@ -8096,7 +8108,7 @@
         <v>43</v>
       </c>
       <c r="N124" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O124" s="44"/>
       <c r="P124" s="44"/>
@@ -8125,7 +8137,7 @@
         <v>60</v>
       </c>
       <c r="G125" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H125" s="53">
         <v>0</v>
@@ -8146,7 +8158,7 @@
         <v>37</v>
       </c>
       <c r="N125" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O125" s="44"/>
       <c r="P125" s="44"/>
@@ -8196,7 +8208,7 @@
         <v>40</v>
       </c>
       <c r="N126" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O126" s="44"/>
       <c r="P126" s="44"/>
@@ -8246,7 +8258,7 @@
         <v>43</v>
       </c>
       <c r="N127" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O127" s="44"/>
       <c r="P127" s="44"/>
@@ -8263,7 +8275,7 @@
         <v>102100</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D128" s="51">
         <v>102100001</v>
@@ -8275,7 +8287,7 @@
         <v>60</v>
       </c>
       <c r="G128" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H128" s="53">
         <v>0</v>
@@ -8296,7 +8308,7 @@
         <v>37</v>
       </c>
       <c r="N128" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O128" s="44"/>
       <c r="P128" s="44"/>
@@ -8313,7 +8325,7 @@
         <v>102100</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D129" s="51">
         <v>102100001</v>
@@ -8346,7 +8358,7 @@
         <v>40</v>
       </c>
       <c r="N129" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O129" s="44"/>
       <c r="P129" s="44"/>
@@ -8363,7 +8375,7 @@
         <v>102100</v>
       </c>
       <c r="C130" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D130" s="51">
         <v>102100001</v>
@@ -8396,7 +8408,7 @@
         <v>43</v>
       </c>
       <c r="N130" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O130" s="44"/>
       <c r="P130" s="44"/>
@@ -8413,7 +8425,7 @@
         <v>102200</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D131" s="51">
         <v>102200001</v>
@@ -8425,7 +8437,7 @@
         <v>60</v>
       </c>
       <c r="G131" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H131" s="53">
         <v>0</v>
@@ -8446,7 +8458,7 @@
         <v>37</v>
       </c>
       <c r="N131" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O131" s="44"/>
       <c r="P131" s="44"/>
@@ -8463,7 +8475,7 @@
         <v>102200</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D132" s="51">
         <v>102200001</v>
@@ -8496,7 +8508,7 @@
         <v>40</v>
       </c>
       <c r="N132" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O132" s="44"/>
       <c r="P132" s="44"/>
@@ -8513,7 +8525,7 @@
         <v>102200</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D133" s="51">
         <v>102200001</v>
@@ -8546,7 +8558,7 @@
         <v>43</v>
       </c>
       <c r="N133" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O133" s="44"/>
       <c r="P133" s="44"/>
@@ -8563,7 +8575,7 @@
         <v>102400</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D134" s="51">
         <v>102400026</v>
@@ -8596,7 +8608,7 @@
         <v>37</v>
       </c>
       <c r="N134" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O134" s="44"/>
       <c r="P134" s="44"/>
@@ -8613,7 +8625,7 @@
         <v>102400</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D135" s="51">
         <v>102400026</v>
@@ -8646,7 +8658,7 @@
         <v>40</v>
       </c>
       <c r="N135" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O135" s="44"/>
       <c r="P135" s="44"/>
@@ -8663,7 +8675,7 @@
         <v>102400</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D136" s="51">
         <v>102400026</v>
@@ -8696,7 +8708,7 @@
         <v>43</v>
       </c>
       <c r="N136" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O136" s="44"/>
       <c r="P136" s="44"/>
@@ -8713,7 +8725,7 @@
         <v>101800</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D137" s="51">
         <v>101800001</v>
@@ -8725,7 +8737,7 @@
         <v>60</v>
       </c>
       <c r="G137" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H137" s="57">
         <v>0</v>
@@ -8746,7 +8758,7 @@
         <v>37</v>
       </c>
       <c r="N137" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O137" s="44"/>
       <c r="P137" s="44"/>
@@ -8763,7 +8775,7 @@
         <v>101800</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D138" s="51">
         <v>101800001</v>
@@ -8796,7 +8808,7 @@
         <v>40</v>
       </c>
       <c r="N138" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O138" s="44"/>
       <c r="P138" s="44"/>
@@ -8813,7 +8825,7 @@
         <v>101800</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D139" s="51">
         <v>101800001</v>
@@ -8846,7 +8858,7 @@
         <v>43</v>
       </c>
       <c r="N139" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O139" s="44"/>
       <c r="P139" s="44"/>
@@ -8863,7 +8875,7 @@
         <v>102500</v>
       </c>
       <c r="C140" s="50" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D140" s="51">
         <v>102500001</v>
@@ -8872,10 +8884,10 @@
         <v>10</v>
       </c>
       <c r="F140" s="24" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G140" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H140" s="57">
         <v>0</v>
@@ -8896,7 +8908,7 @@
         <v>37</v>
       </c>
       <c r="N140" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O140" s="44"/>
       <c r="P140" s="44"/>
@@ -8913,7 +8925,7 @@
         <v>102500</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D141" s="51">
         <v>102500001</v>
@@ -8922,10 +8934,10 @@
         <v>11</v>
       </c>
       <c r="F141" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G141" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H141" s="57">
         <v>0</v>
@@ -8946,7 +8958,7 @@
         <v>40</v>
       </c>
       <c r="N141" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O141" s="44"/>
       <c r="P141" s="44"/>
@@ -8963,7 +8975,7 @@
         <v>102500</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D142" s="51">
         <v>102500001</v>
@@ -8972,10 +8984,10 @@
         <v>12</v>
       </c>
       <c r="F142" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G142" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H142" s="57">
         <v>0</v>
@@ -8996,7 +9008,7 @@
         <v>43</v>
       </c>
       <c r="N142" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O142" s="44"/>
       <c r="P142" s="44"/>
@@ -9013,7 +9025,7 @@
         <v>102300</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D143" s="51">
         <v>102300001</v>
@@ -9025,7 +9037,7 @@
         <v>60</v>
       </c>
       <c r="G143" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H143" s="57">
         <v>0</v>
@@ -9046,7 +9058,7 @@
         <v>37</v>
       </c>
       <c r="N143" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O143" s="44"/>
       <c r="P143" s="44"/>
@@ -9063,7 +9075,7 @@
         <v>102300</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D144" s="51">
         <v>102300001</v>
@@ -9096,7 +9108,7 @@
         <v>40</v>
       </c>
       <c r="N144" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O144" s="44"/>
       <c r="P144" s="44"/>
@@ -9113,7 +9125,7 @@
         <v>102300</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D145" s="51">
         <v>102300001</v>
@@ -9146,7 +9158,7 @@
         <v>43</v>
       </c>
       <c r="N145" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O145" s="44"/>
       <c r="P145" s="44"/>
@@ -9163,7 +9175,7 @@
         <v>103400</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D146" s="51">
         <v>103000001</v>
@@ -9172,10 +9184,10 @@
         <v>10</v>
       </c>
       <c r="F146" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G146" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H146" s="57">
         <v>0</v>
@@ -9196,7 +9208,7 @@
         <v>37</v>
       </c>
       <c r="N146" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O146" s="44"/>
       <c r="P146" s="44"/>
@@ -9213,7 +9225,7 @@
         <v>103400</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D147" s="51">
         <v>103000001</v>
@@ -9222,10 +9234,10 @@
         <v>11</v>
       </c>
       <c r="F147" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G147" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H147" s="57">
         <v>0</v>
@@ -9246,7 +9258,7 @@
         <v>40</v>
       </c>
       <c r="N147" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O147" s="44"/>
       <c r="P147" s="44"/>
@@ -9263,7 +9275,7 @@
         <v>103400</v>
       </c>
       <c r="C148" s="50" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D148" s="51">
         <v>103000001</v>
@@ -9272,10 +9284,10 @@
         <v>12</v>
       </c>
       <c r="F148" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G148" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H148" s="57">
         <v>0</v>
@@ -9296,7 +9308,7 @@
         <v>43</v>
       </c>
       <c r="N148" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O148" s="44"/>
       <c r="P148" s="44"/>
@@ -9313,7 +9325,7 @@
         <v>103500</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D149" s="51">
         <v>102900001</v>
@@ -9346,7 +9358,7 @@
         <v>37</v>
       </c>
       <c r="N149" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O149" s="44"/>
       <c r="P149" s="44"/>
@@ -9363,7 +9375,7 @@
         <v>103500</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D150" s="51">
         <v>102900001</v>
@@ -9396,7 +9408,7 @@
         <v>40</v>
       </c>
       <c r="N150" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O150" s="44"/>
       <c r="P150" s="44"/>
@@ -9413,7 +9425,7 @@
         <v>103500</v>
       </c>
       <c r="C151" s="50" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D151" s="51">
         <v>102900001</v>
@@ -9446,7 +9458,7 @@
         <v>43</v>
       </c>
       <c r="N151" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O151" s="44"/>
       <c r="P151" s="44"/>
@@ -9463,7 +9475,7 @@
         <v>103501</v>
       </c>
       <c r="C152" s="50" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D152" s="51">
         <v>103501001</v>
@@ -9496,7 +9508,7 @@
         <v>37</v>
       </c>
       <c r="N152" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O152" s="44"/>
       <c r="P152" s="44"/>
@@ -9513,7 +9525,7 @@
         <v>103501</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D153" s="51">
         <v>103501001</v>
@@ -9546,7 +9558,7 @@
         <v>40</v>
       </c>
       <c r="N153" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O153" s="44"/>
       <c r="P153" s="44"/>
@@ -9563,7 +9575,7 @@
         <v>103501</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D154" s="51">
         <v>103501001</v>
@@ -9596,7 +9608,7 @@
         <v>43</v>
       </c>
       <c r="N154" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O154" s="44"/>
       <c r="P154" s="44"/>
@@ -9613,7 +9625,7 @@
         <v>103600</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D155" s="51">
         <v>103600001</v>
@@ -9622,10 +9634,10 @@
         <v>10</v>
       </c>
       <c r="F155" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G155" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H155" s="53">
         <v>0</v>
@@ -9646,7 +9658,7 @@
         <v>37</v>
       </c>
       <c r="N155" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O155" s="44"/>
       <c r="P155" s="44"/>
@@ -9663,7 +9675,7 @@
         <v>103600</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D156" s="51">
         <v>103600001</v>
@@ -9672,10 +9684,10 @@
         <v>11</v>
       </c>
       <c r="F156" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G156" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H156" s="53">
         <v>0</v>
@@ -9696,7 +9708,7 @@
         <v>40</v>
       </c>
       <c r="N156" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O156" s="44"/>
       <c r="P156" s="44"/>
@@ -9713,7 +9725,7 @@
         <v>103600</v>
       </c>
       <c r="C157" s="50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D157" s="51">
         <v>103600001</v>
@@ -9722,10 +9734,10 @@
         <v>12</v>
       </c>
       <c r="F157" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G157" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H157" s="57">
         <v>0</v>
@@ -9746,7 +9758,7 @@
         <v>43</v>
       </c>
       <c r="N157" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O157" s="44"/>
       <c r="P157" s="44"/>
@@ -9763,7 +9775,7 @@
         <v>102800</v>
       </c>
       <c r="C158" s="50" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D158" s="51">
         <v>102800001</v>
@@ -9775,7 +9787,7 @@
         <v>60</v>
       </c>
       <c r="G158" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H158" s="57">
         <v>0</v>
@@ -9796,7 +9808,7 @@
         <v>37</v>
       </c>
       <c r="N158" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O158" s="44"/>
       <c r="P158" s="44"/>
@@ -9813,7 +9825,7 @@
         <v>102800</v>
       </c>
       <c r="C159" s="50" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D159" s="51">
         <v>102800001</v>
@@ -9846,7 +9858,7 @@
         <v>40</v>
       </c>
       <c r="N159" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O159" s="44"/>
       <c r="P159" s="44"/>
@@ -9863,7 +9875,7 @@
         <v>102800</v>
       </c>
       <c r="C160" s="50" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D160" s="51">
         <v>102800001</v>
@@ -9896,7 +9908,7 @@
         <v>43</v>
       </c>
       <c r="N160" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O160" s="44"/>
       <c r="P160" s="44"/>
@@ -9913,7 +9925,7 @@
         <v>102000</v>
       </c>
       <c r="C161" s="50" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D161" s="51">
         <v>102000001</v>
@@ -9922,10 +9934,10 @@
         <v>10</v>
       </c>
       <c r="F161" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G161" s="25" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H161" s="57">
         <v>0</v>
@@ -9946,7 +9958,7 @@
         <v>37</v>
       </c>
       <c r="N161" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O161" s="44"/>
       <c r="P161" s="44"/>
@@ -9963,7 +9975,7 @@
         <v>102000</v>
       </c>
       <c r="C162" s="50" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D162" s="51">
         <v>102000001</v>
@@ -9972,10 +9984,10 @@
         <v>11</v>
       </c>
       <c r="F162" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G162" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H162" s="57">
         <v>0</v>
@@ -9996,7 +10008,7 @@
         <v>40</v>
       </c>
       <c r="N162" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O162" s="44"/>
       <c r="P162" s="44"/>
@@ -10013,7 +10025,7 @@
         <v>102000</v>
       </c>
       <c r="C163" s="50" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D163" s="51">
         <v>102000001</v>
@@ -10022,10 +10034,10 @@
         <v>12</v>
       </c>
       <c r="F163" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G163" s="25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H163" s="57">
         <v>0</v>
@@ -10046,7 +10058,7 @@
         <v>43</v>
       </c>
       <c r="N163" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O163" s="44"/>
       <c r="P163" s="44"/>
@@ -10063,7 +10075,7 @@
         <v>103401</v>
       </c>
       <c r="C164" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D164" s="51">
         <v>103400001</v>
@@ -10072,10 +10084,10 @@
         <v>10</v>
       </c>
       <c r="F164" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G164" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H164" s="57">
         <v>0</v>
@@ -10096,7 +10108,7 @@
         <v>37</v>
       </c>
       <c r="N164" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O164" s="44"/>
       <c r="P164" s="44"/>
@@ -10113,7 +10125,7 @@
         <v>103401</v>
       </c>
       <c r="C165" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D165" s="51">
         <v>103400001</v>
@@ -10122,10 +10134,10 @@
         <v>11</v>
       </c>
       <c r="F165" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G165" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H165" s="57">
         <v>0</v>
@@ -10146,7 +10158,7 @@
         <v>40</v>
       </c>
       <c r="N165" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O165" s="44"/>
       <c r="P165" s="44"/>
@@ -10163,7 +10175,7 @@
         <v>103401</v>
       </c>
       <c r="C166" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D166" s="51">
         <v>103400001</v>
@@ -10172,10 +10184,10 @@
         <v>12</v>
       </c>
       <c r="F166" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G166" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H166" s="57">
         <v>0</v>
@@ -10196,7 +10208,7 @@
         <v>43</v>
       </c>
       <c r="N166" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O166" s="44"/>
       <c r="P166" s="44"/>
@@ -10213,7 +10225,7 @@
         <v>103800</v>
       </c>
       <c r="C167" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D167" s="51">
         <v>103800001</v>
@@ -10222,10 +10234,10 @@
         <v>11</v>
       </c>
       <c r="F167" s="24" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G167" s="25" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H167" s="57">
         <v>0</v>
@@ -10246,7 +10258,7 @@
         <v>37</v>
       </c>
       <c r="N167" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O167" s="44"/>
       <c r="P167" s="44"/>
@@ -10263,7 +10275,7 @@
         <v>103800</v>
       </c>
       <c r="C168" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D168" s="51">
         <v>103800001</v>
@@ -10272,10 +10284,10 @@
         <v>12</v>
       </c>
       <c r="F168" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G168" s="25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H168" s="57">
         <v>0</v>
@@ -10296,7 +10308,7 @@
         <v>40</v>
       </c>
       <c r="N168" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O168" s="44"/>
       <c r="P168" s="44"/>
@@ -10313,7 +10325,7 @@
         <v>103800</v>
       </c>
       <c r="C169" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D169" s="51">
         <v>103800001</v>
@@ -10322,10 +10334,10 @@
         <v>13</v>
       </c>
       <c r="F169" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G169" s="25" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="H169" s="57">
         <v>0</v>
@@ -10346,7 +10358,7 @@
         <v>43</v>
       </c>
       <c r="N169" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O169" s="44"/>
       <c r="P169" s="44"/>
@@ -10363,7 +10375,7 @@
         <v>102700</v>
       </c>
       <c r="C170" s="50" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D170" s="51">
         <v>102700001</v>
@@ -10375,7 +10387,7 @@
         <v>60</v>
       </c>
       <c r="G170" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H170" s="57">
         <v>0</v>
@@ -10396,7 +10408,7 @@
         <v>37</v>
       </c>
       <c r="N170" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O170" s="44"/>
       <c r="P170" s="44"/>
@@ -10413,7 +10425,7 @@
         <v>102700</v>
       </c>
       <c r="C171" s="50" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D171" s="51">
         <v>102700001</v>
@@ -10446,7 +10458,7 @@
         <v>40</v>
       </c>
       <c r="N171" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O171" s="44"/>
       <c r="P171" s="44"/>
@@ -10463,7 +10475,7 @@
         <v>102700</v>
       </c>
       <c r="C172" s="50" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D172" s="51">
         <v>102700001</v>
@@ -10496,7 +10508,7 @@
         <v>43</v>
       </c>
       <c r="N172" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O172" s="44"/>
       <c r="P172" s="44"/>
@@ -10513,7 +10525,7 @@
         <v>103700</v>
       </c>
       <c r="C173" s="50" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D173" s="51">
         <v>103700001</v>
@@ -10546,7 +10558,7 @@
         <v>37</v>
       </c>
       <c r="N173" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O173" s="44"/>
       <c r="P173" s="44"/>
@@ -10563,7 +10575,7 @@
         <v>103700</v>
       </c>
       <c r="C174" s="50" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D174" s="51">
         <v>103700001</v>
@@ -10596,7 +10608,7 @@
         <v>40</v>
       </c>
       <c r="N174" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O174" s="44"/>
       <c r="P174" s="44"/>
@@ -10613,7 +10625,7 @@
         <v>103700</v>
       </c>
       <c r="C175" s="50" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D175" s="51">
         <v>103100001</v>
@@ -10646,7 +10658,7 @@
         <v>43</v>
       </c>
       <c r="N175" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O175" s="44"/>
       <c r="P175" s="44"/>
@@ -10663,7 +10675,7 @@
         <v>103100</v>
       </c>
       <c r="C176" s="50" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D176" s="51">
         <v>103100001</v>
@@ -10672,10 +10684,10 @@
         <v>11</v>
       </c>
       <c r="F176" s="24" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G176" s="25" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H176" s="53">
         <v>0</v>
@@ -10696,7 +10708,7 @@
         <v>37</v>
       </c>
       <c r="N176" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O176" s="44"/>
       <c r="P176" s="44"/>
@@ -10713,7 +10725,7 @@
         <v>103100</v>
       </c>
       <c r="C177" s="50" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D177" s="51">
         <v>103100001</v>
@@ -10722,10 +10734,10 @@
         <v>12</v>
       </c>
       <c r="F177" s="24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G177" s="25" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H177" s="53">
         <v>0</v>
@@ -10746,7 +10758,7 @@
         <v>40</v>
       </c>
       <c r="N177" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O177" s="44"/>
       <c r="P177" s="44"/>
@@ -10763,7 +10775,7 @@
         <v>103100</v>
       </c>
       <c r="C178" s="50" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D178" s="51">
         <v>103100001</v>
@@ -10772,10 +10784,10 @@
         <v>13</v>
       </c>
       <c r="F178" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G178" s="25" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="H178" s="57">
         <v>0</v>
@@ -10796,7 +10808,7 @@
         <v>43</v>
       </c>
       <c r="N178" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O178" s="44"/>
       <c r="P178" s="44"/>
@@ -10813,7 +10825,7 @@
         <v>104000</v>
       </c>
       <c r="C179" s="50" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D179" s="51">
         <v>104000001</v>
@@ -10822,10 +10834,10 @@
         <v>11</v>
       </c>
       <c r="F179" s="24" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G179" s="25" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H179" s="57">
         <v>0</v>
@@ -10846,7 +10858,7 @@
         <v>37</v>
       </c>
       <c r="N179" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O179" s="44"/>
       <c r="P179" s="44"/>
@@ -10863,7 +10875,7 @@
         <v>104000</v>
       </c>
       <c r="C180" s="50" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D180" s="51">
         <v>104000001</v>
@@ -10872,10 +10884,10 @@
         <v>12</v>
       </c>
       <c r="F180" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G180" s="25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H180" s="57">
         <v>0</v>
@@ -10896,7 +10908,7 @@
         <v>40</v>
       </c>
       <c r="N180" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O180" s="44"/>
       <c r="P180" s="44"/>
@@ -10913,7 +10925,7 @@
         <v>104000</v>
       </c>
       <c r="C181" s="50" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D181" s="51">
         <v>104000001</v>
@@ -10922,10 +10934,10 @@
         <v>13</v>
       </c>
       <c r="F181" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G181" s="25" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="H181" s="57">
         <v>0</v>
@@ -10946,7 +10958,7 @@
         <v>43</v>
       </c>
       <c r="N181" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O181" s="44"/>
       <c r="P181" s="44"/>
@@ -10963,7 +10975,7 @@
         <v>103900</v>
       </c>
       <c r="C182" s="50" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D182" s="51">
         <v>103900001</v>
@@ -10972,10 +10984,10 @@
         <v>11</v>
       </c>
       <c r="F182" s="24" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G182" s="25" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H182" s="57">
         <v>0</v>
@@ -10996,7 +11008,7 @@
         <v>37</v>
       </c>
       <c r="N182" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O182" s="44"/>
       <c r="P182" s="44"/>
@@ -11013,7 +11025,7 @@
         <v>103900</v>
       </c>
       <c r="C183" s="50" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D183" s="51">
         <v>103900001</v>
@@ -11022,10 +11034,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G183" s="25" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H183" s="57">
         <v>0</v>
@@ -11046,7 +11058,7 @@
         <v>40</v>
       </c>
       <c r="N183" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O183" s="44"/>
       <c r="P183" s="44"/>
@@ -11063,7 +11075,7 @@
         <v>103900</v>
       </c>
       <c r="C184" s="50" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D184" s="51">
         <v>103900001</v>
@@ -11072,10 +11084,10 @@
         <v>13</v>
       </c>
       <c r="F184" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G184" s="25" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="H184" s="57">
         <v>0</v>
@@ -11096,7 +11108,7 @@
         <v>43</v>
       </c>
       <c r="N184" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O184" s="44"/>
       <c r="P184" s="44"/>
@@ -11113,7 +11125,7 @@
         <v>101600</v>
       </c>
       <c r="C185" s="50" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D185" s="51">
         <v>101600001</v>
@@ -11125,7 +11137,7 @@
         <v>60</v>
       </c>
       <c r="G185" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H185" s="57">
         <v>0</v>
@@ -11146,7 +11158,7 @@
         <v>37</v>
       </c>
       <c r="N185" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O185" s="44"/>
       <c r="P185" s="44"/>
@@ -11163,7 +11175,7 @@
         <v>101600</v>
       </c>
       <c r="C186" s="50" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D186" s="51">
         <v>101600001</v>
@@ -11196,7 +11208,7 @@
         <v>40</v>
       </c>
       <c r="N186" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O186" s="44"/>
       <c r="P186" s="44"/>
@@ -11213,7 +11225,7 @@
         <v>101600</v>
       </c>
       <c r="C187" s="50" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D187" s="51">
         <v>101600001</v>
@@ -11246,7 +11258,7 @@
         <v>43</v>
       </c>
       <c r="N187" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O187" s="44"/>
       <c r="P187" s="44"/>
@@ -11263,7 +11275,7 @@
         <v>101500</v>
       </c>
       <c r="C188" s="50" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D188" s="51">
         <v>101500001</v>
@@ -11275,7 +11287,7 @@
         <v>60</v>
       </c>
       <c r="G188" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H188" s="57">
         <v>0</v>
@@ -11296,7 +11308,7 @@
         <v>37</v>
       </c>
       <c r="N188" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O188" s="44"/>
       <c r="P188" s="44"/>
@@ -11313,7 +11325,7 @@
         <v>101500</v>
       </c>
       <c r="C189" s="50" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D189" s="51">
         <v>101500001</v>
@@ -11346,7 +11358,7 @@
         <v>40</v>
       </c>
       <c r="N189" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O189" s="44"/>
       <c r="P189" s="44"/>
@@ -11363,7 +11375,7 @@
         <v>101500</v>
       </c>
       <c r="C190" s="50" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D190" s="51">
         <v>101500001</v>
@@ -11396,7 +11408,7 @@
         <v>43</v>
       </c>
       <c r="N190" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O190" s="44"/>
       <c r="P190" s="44"/>
@@ -11413,7 +11425,7 @@
         <v>102600</v>
       </c>
       <c r="C191" s="50" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D191" s="51">
         <v>102600001</v>
@@ -11425,7 +11437,7 @@
         <v>60</v>
       </c>
       <c r="G191" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H191" s="57">
         <v>0</v>
@@ -11446,7 +11458,7 @@
         <v>37</v>
       </c>
       <c r="N191" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O191" s="44"/>
       <c r="P191" s="44"/>
@@ -11463,7 +11475,7 @@
         <v>102600</v>
       </c>
       <c r="C192" s="50" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D192" s="51">
         <v>102600001</v>
@@ -11496,7 +11508,7 @@
         <v>40</v>
       </c>
       <c r="N192" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O192" s="44"/>
       <c r="P192" s="44"/>
@@ -11513,7 +11525,7 @@
         <v>102600</v>
       </c>
       <c r="C193" s="50" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D193" s="51">
         <v>102600001</v>
@@ -11546,7 +11558,7 @@
         <v>43</v>
       </c>
       <c r="N193" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O193" s="44"/>
       <c r="P193" s="44"/>
@@ -11563,7 +11575,7 @@
         <v>105000</v>
       </c>
       <c r="C194" s="50" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D194" s="51">
         <v>105000001</v>
@@ -11575,7 +11587,7 @@
         <v>60</v>
       </c>
       <c r="G194" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H194" s="57">
         <v>0</v>
@@ -11596,7 +11608,7 @@
         <v>37</v>
       </c>
       <c r="N194" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O194" s="44"/>
       <c r="P194" s="44"/>
@@ -11613,7 +11625,7 @@
         <v>105000</v>
       </c>
       <c r="C195" s="50" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D195" s="51">
         <v>105000001</v>
@@ -11646,7 +11658,7 @@
         <v>40</v>
       </c>
       <c r="N195" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O195" s="44"/>
       <c r="P195" s="44"/>
@@ -11663,7 +11675,7 @@
         <v>105000</v>
       </c>
       <c r="C196" s="50" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D196" s="51">
         <v>105000001</v>
@@ -11696,7 +11708,7 @@
         <v>43</v>
       </c>
       <c r="N196" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O196" s="44"/>
       <c r="P196" s="44"/>
@@ -11713,7 +11725,7 @@
         <v>105100</v>
       </c>
       <c r="C197" s="50" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D197" s="51">
         <v>105100001</v>
@@ -11746,7 +11758,7 @@
         <v>37</v>
       </c>
       <c r="N197" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O197" s="44"/>
       <c r="P197" s="44"/>
@@ -11763,7 +11775,7 @@
         <v>105100</v>
       </c>
       <c r="C198" s="50" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D198" s="51">
         <v>105100001</v>
@@ -11796,7 +11808,7 @@
         <v>40</v>
       </c>
       <c r="N198" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O198" s="44"/>
       <c r="P198" s="44"/>
@@ -11813,7 +11825,7 @@
         <v>105100</v>
       </c>
       <c r="C199" s="50" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D199" s="51">
         <v>105100001</v>
@@ -11846,7 +11858,7 @@
         <v>43</v>
       </c>
       <c r="N199" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O199" s="44"/>
       <c r="P199" s="44"/>
@@ -11863,7 +11875,7 @@
         <v>105400</v>
       </c>
       <c r="C200" s="50" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D200" s="51">
         <v>105400001</v>
@@ -11872,10 +11884,10 @@
         <v>11</v>
       </c>
       <c r="F200" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G200" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H200" s="57">
         <v>0</v>
@@ -11893,10 +11905,10 @@
         <v>0</v>
       </c>
       <c r="M200" s="26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N200" s="56" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O200" s="44"/>
       <c r="P200" s="44"/>
@@ -11913,7 +11925,7 @@
         <v>105400</v>
       </c>
       <c r="C201" s="50" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D201" s="51">
         <v>105400001</v>
@@ -11922,7 +11934,7 @@
         <v>12</v>
       </c>
       <c r="F201" s="24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G201" s="25" t="s">
         <v>53</v>
@@ -11943,10 +11955,10 @@
         <v>0</v>
       </c>
       <c r="M201" s="26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N201" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O201" s="44"/>
       <c r="P201" s="44"/>
@@ -11963,7 +11975,7 @@
         <v>105400</v>
       </c>
       <c r="C202" s="50" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D202" s="51">
         <v>105400001</v>
@@ -11972,7 +11984,7 @@
         <v>13</v>
       </c>
       <c r="F202" s="24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G202" s="25" t="s">
         <v>55</v>
@@ -11993,10 +12005,10 @@
         <v>0</v>
       </c>
       <c r="M202" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N202" s="56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O202" s="44"/>
       <c r="P202" s="44"/>
@@ -12013,7 +12025,7 @@
         <v>100800</v>
       </c>
       <c r="C203" s="13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D203" s="35">
         <v>100800001</v>
@@ -12022,10 +12034,10 @@
         <v>11</v>
       </c>
       <c r="F203" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G203" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H203" s="31">
         <v>0</v>
@@ -12043,10 +12055,10 @@
         <v>0</v>
       </c>
       <c r="M203" s="26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N203" s="24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:20">
@@ -12057,7 +12069,7 @@
         <v>100800</v>
       </c>
       <c r="C204" s="13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D204" s="35">
         <v>100800001</v>
@@ -12066,7 +12078,7 @@
         <v>12</v>
       </c>
       <c r="F204" s="24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G204" s="25" t="s">
         <v>53</v>
@@ -12087,10 +12099,10 @@
         <v>0</v>
       </c>
       <c r="M204" s="26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N204" s="24" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:20">
@@ -12101,7 +12113,7 @@
         <v>100800</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D205" s="35">
         <v>100800001</v>
@@ -12110,7 +12122,7 @@
         <v>13</v>
       </c>
       <c r="F205" s="24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G205" s="25" t="s">
         <v>55</v>
@@ -12131,10 +12143,10 @@
         <v>0</v>
       </c>
       <c r="M205" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N205" s="24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:20">
@@ -12145,7 +12157,7 @@
         <v>105300</v>
       </c>
       <c r="C206" s="23" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D206" s="35">
         <v>105300001</v>
@@ -12154,10 +12166,10 @@
         <v>11</v>
       </c>
       <c r="F206" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G206" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H206" s="31">
         <v>0</v>
@@ -12175,10 +12187,10 @@
         <v>0</v>
       </c>
       <c r="M206" s="26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N206" s="24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:20">
@@ -12189,7 +12201,7 @@
         <v>105300</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D207" s="35">
         <v>105300001</v>
@@ -12198,7 +12210,7 @@
         <v>12</v>
       </c>
       <c r="F207" s="24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G207" s="25" t="s">
         <v>53</v>
@@ -12219,10 +12231,10 @@
         <v>0</v>
       </c>
       <c r="M207" s="26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N207" s="24" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:20">
@@ -12233,7 +12245,7 @@
         <v>105300</v>
       </c>
       <c r="C208" s="23" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D208" s="35">
         <v>105300001</v>
@@ -12242,7 +12254,7 @@
         <v>13</v>
       </c>
       <c r="F208" s="24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G208" s="25" t="s">
         <v>55</v>
@@ -12263,10 +12275,10 @@
         <v>0</v>
       </c>
       <c r="M208" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N208" s="24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:14">
@@ -12277,7 +12289,7 @@
         <v>105700</v>
       </c>
       <c r="C209" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D209" s="35">
         <v>105700001</v>
@@ -12286,10 +12298,10 @@
         <v>11</v>
       </c>
       <c r="F209" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G209" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H209" s="31">
         <v>0</v>
@@ -12307,10 +12319,10 @@
         <v>0</v>
       </c>
       <c r="M209" s="26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N209" s="24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:14">
@@ -12321,7 +12333,7 @@
         <v>105700</v>
       </c>
       <c r="C210" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D210" s="35">
         <v>105700001</v>
@@ -12330,7 +12342,7 @@
         <v>12</v>
       </c>
       <c r="F210" s="24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G210" s="25" t="s">
         <v>53</v>
@@ -12351,10 +12363,10 @@
         <v>0</v>
       </c>
       <c r="M210" s="26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N210" s="24" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:14">
@@ -12365,7 +12377,7 @@
         <v>105700</v>
       </c>
       <c r="C211" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D211" s="35">
         <v>105700001</v>
@@ -12374,7 +12386,7 @@
         <v>13</v>
       </c>
       <c r="F211" s="24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G211" s="25" t="s">
         <v>55</v>
@@ -12395,10 +12407,10 @@
         <v>0</v>
       </c>
       <c r="M211" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N211" s="24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="212" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12409,7 +12421,7 @@
         <v>105800</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D212" s="61">
         <v>105800001</v>
@@ -12418,10 +12430,10 @@
         <v>11</v>
       </c>
       <c r="F212" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G212" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H212" s="31">
         <v>0</v>
@@ -12439,10 +12451,10 @@
         <v>0</v>
       </c>
       <c r="M212" s="26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N212" s="24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="213" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12453,7 +12465,7 @@
         <v>105800</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D213" s="61">
         <v>105800001</v>
@@ -12462,7 +12474,7 @@
         <v>12</v>
       </c>
       <c r="F213" s="24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G213" s="25" t="s">
         <v>53</v>
@@ -12483,10 +12495,10 @@
         <v>0</v>
       </c>
       <c r="M213" s="26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N213" s="24" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="214" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12497,7 +12509,7 @@
         <v>105800</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D214" s="61">
         <v>105800001</v>
@@ -12506,7 +12518,7 @@
         <v>13</v>
       </c>
       <c r="F214" s="24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G214" s="25" t="s">
         <v>55</v>
@@ -12527,10 +12539,10 @@
         <v>0</v>
       </c>
       <c r="M214" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N214" s="24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="215" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12541,7 +12553,7 @@
         <v>105500</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D215" s="61">
         <v>105500001</v>
@@ -12550,10 +12562,10 @@
         <v>11</v>
       </c>
       <c r="F215" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G215" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H215" s="31">
         <v>0</v>
@@ -12571,10 +12583,10 @@
         <v>0</v>
       </c>
       <c r="M215" s="26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N215" s="24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="216" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12585,7 +12597,7 @@
         <v>105500</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D216" s="61">
         <v>105500001</v>
@@ -12594,10 +12606,10 @@
         <v>12</v>
       </c>
       <c r="F216" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G216" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H216" s="31">
         <v>0</v>
@@ -12615,10 +12627,10 @@
         <v>0</v>
       </c>
       <c r="M216" s="26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N216" s="24" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="217" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -12629,7 +12641,7 @@
         <v>105500</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D217" s="61">
         <v>105500001</v>
@@ -12638,10 +12650,10 @@
         <v>13</v>
       </c>
       <c r="F217" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G217" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H217" s="31">
         <v>0</v>
@@ -12659,10 +12671,10 @@
         <v>0</v>
       </c>
       <c r="M217" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N217" s="24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:14">
@@ -12673,7 +12685,7 @@
         <v>104800</v>
       </c>
       <c r="C218" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D218" s="27">
         <v>104800001</v>
@@ -12682,10 +12694,10 @@
         <v>11</v>
       </c>
       <c r="F218" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G218" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H218" s="31">
         <v>0</v>
@@ -12703,10 +12715,10 @@
         <v>0</v>
       </c>
       <c r="M218" s="26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N218" s="24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:14">
@@ -12717,7 +12729,7 @@
         <v>104800</v>
       </c>
       <c r="C219" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D219" s="27">
         <v>104800001</v>
@@ -12726,7 +12738,7 @@
         <v>12</v>
       </c>
       <c r="F219" s="24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G219" s="25" t="s">
         <v>53</v>
@@ -12747,10 +12759,10 @@
         <v>0</v>
       </c>
       <c r="M219" s="26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N219" s="24" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:14">
@@ -12761,7 +12773,7 @@
         <v>104800</v>
       </c>
       <c r="C220" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D220" s="27">
         <v>104800001</v>
@@ -12770,7 +12782,7 @@
         <v>13</v>
       </c>
       <c r="F220" s="24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G220" s="25" t="s">
         <v>55</v>
@@ -12791,10 +12803,10 @@
         <v>0</v>
       </c>
       <c r="M220" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N220" s="24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="221" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12805,7 +12817,7 @@
         <v>105501</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D221" s="61">
         <v>105501001</v>
@@ -12814,10 +12826,10 @@
         <v>11</v>
       </c>
       <c r="F221" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G221" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H221" s="31">
         <v>0</v>
@@ -12835,10 +12847,10 @@
         <v>0</v>
       </c>
       <c r="M221" s="26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N221" s="24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="222" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12849,7 +12861,7 @@
         <v>105501</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D222" s="61">
         <v>105501001</v>
@@ -12858,10 +12870,10 @@
         <v>12</v>
       </c>
       <c r="F222" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G222" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H222" s="31">
         <v>0</v>
@@ -12879,10 +12891,10 @@
         <v>0</v>
       </c>
       <c r="M222" s="26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N222" s="24" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="223" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12893,7 +12905,7 @@
         <v>105501</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D223" s="61">
         <v>105501001</v>
@@ -12902,10 +12914,10 @@
         <v>13</v>
       </c>
       <c r="F223" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G223" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H223" s="31">
         <v>0</v>
@@ -12923,10 +12935,10 @@
         <v>0</v>
       </c>
       <c r="M223" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N223" s="24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="224" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -12937,7 +12949,7 @@
         <v>105502</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D224" s="61">
         <v>105502001</v>
@@ -12946,10 +12958,10 @@
         <v>11</v>
       </c>
       <c r="F224" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G224" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H224" s="31">
         <v>0</v>
@@ -12967,10 +12979,10 @@
         <v>0</v>
       </c>
       <c r="M224" s="26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N224" s="24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="225" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -12981,7 +12993,7 @@
         <v>105502</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D225" s="61">
         <v>105502001</v>
@@ -12990,10 +13002,10 @@
         <v>12</v>
       </c>
       <c r="F225" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G225" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H225" s="31">
         <v>0</v>
@@ -13011,10 +13023,10 @@
         <v>0</v>
       </c>
       <c r="M225" s="26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N225" s="24" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="226" s="8" customFormat="1" ht="16.5" spans="1:20">
@@ -13025,7 +13037,7 @@
         <v>105502</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D226" s="61">
         <v>105502001</v>
@@ -13034,10 +13046,10 @@
         <v>13</v>
       </c>
       <c r="F226" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G226" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H226" s="31">
         <v>0</v>
@@ -13055,10 +13067,10 @@
         <v>0</v>
       </c>
       <c r="M226" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N226" s="24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="227" customFormat="1" ht="16.5" spans="1:20">
@@ -13069,7 +13081,7 @@
         <v>104100</v>
       </c>
       <c r="C227" s="63" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D227" s="27">
         <v>104100001</v>
@@ -13078,10 +13090,10 @@
         <v>11</v>
       </c>
       <c r="F227" s="47" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G227" s="64" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H227" s="65">
         <v>0</v>
@@ -13099,10 +13111,10 @@
         <v>0</v>
       </c>
       <c r="M227" s="48" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N227" s="47" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="228" customFormat="1" ht="16.5" spans="1:20">
@@ -13113,7 +13125,7 @@
         <v>104100</v>
       </c>
       <c r="C228" s="63" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D228" s="27">
         <v>104100001</v>
@@ -13122,7 +13134,7 @@
         <v>12</v>
       </c>
       <c r="F228" s="47" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G228" s="64" t="s">
         <v>53</v>
@@ -13143,10 +13155,10 @@
         <v>0</v>
       </c>
       <c r="M228" s="48" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N228" s="47" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="229" customFormat="1" ht="16.5" spans="1:20">
@@ -13157,7 +13169,7 @@
         <v>104100</v>
       </c>
       <c r="C229" s="63" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D229" s="27">
         <v>104100001</v>
@@ -13166,7 +13178,7 @@
         <v>13</v>
       </c>
       <c r="F229" s="47" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G229" s="64" t="s">
         <v>55</v>
@@ -13187,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="M229" s="48" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N229" s="47" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="230" customFormat="1" ht="16.5" spans="1:20">
@@ -13201,7 +13213,7 @@
         <v>104200</v>
       </c>
       <c r="C230" s="63" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D230" s="27">
         <v>104200001</v>
@@ -13210,10 +13222,10 @@
         <v>11</v>
       </c>
       <c r="F230" s="47" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G230" s="64" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H230" s="65">
         <v>0</v>
@@ -13231,10 +13243,10 @@
         <v>0</v>
       </c>
       <c r="M230" s="48" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N230" s="47" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="231" customFormat="1" ht="16.5" spans="1:20">
@@ -13245,7 +13257,7 @@
         <v>104200</v>
       </c>
       <c r="C231" s="63" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D231" s="27">
         <v>104200001</v>
@@ -13254,7 +13266,7 @@
         <v>12</v>
       </c>
       <c r="F231" s="47" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G231" s="64" t="s">
         <v>53</v>
@@ -13275,10 +13287,10 @@
         <v>0</v>
       </c>
       <c r="M231" s="48" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N231" s="47" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="232" customFormat="1" ht="16.5" spans="1:20">
@@ -13289,7 +13301,7 @@
         <v>104200</v>
       </c>
       <c r="C232" s="63" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D232" s="27">
         <v>104200001</v>
@@ -13298,7 +13310,7 @@
         <v>13</v>
       </c>
       <c r="F232" s="47" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G232" s="64" t="s">
         <v>55</v>
@@ -13319,10 +13331,10 @@
         <v>0</v>
       </c>
       <c r="M232" s="48" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N232" s="47" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="233" s="2" customFormat="1" ht="16.5" spans="1:20">
@@ -13645,7 +13657,7 @@
         <v>60</v>
       </c>
       <c r="G239" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H239" s="17">
         <v>10000000</v>
@@ -13792,10 +13804,10 @@
         <v>21</v>
       </c>
       <c r="F242" s="32" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G242" s="33" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H242" s="17">
         <v>10000000</v>
@@ -14095,7 +14107,7 @@
         <v>60</v>
       </c>
       <c r="G248" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H248" s="17">
         <v>10000000</v>
@@ -14233,7 +14245,7 @@
         <v>102100</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D251" s="27">
         <v>102100001</v>
@@ -14245,7 +14257,7 @@
         <v>60</v>
       </c>
       <c r="G251" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H251" s="17">
         <v>10000000</v>
@@ -14283,7 +14295,7 @@
         <v>102100</v>
       </c>
       <c r="C252" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D252" s="27">
         <v>102100001</v>
@@ -14333,7 +14345,7 @@
         <v>102100</v>
       </c>
       <c r="C253" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D253" s="27">
         <v>102100001</v>
@@ -14383,7 +14395,7 @@
         <v>102200</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D254" s="27">
         <v>102200001</v>
@@ -14395,7 +14407,7 @@
         <v>60</v>
       </c>
       <c r="G254" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H254" s="17">
         <v>10000000</v>
@@ -14433,7 +14445,7 @@
         <v>102200</v>
       </c>
       <c r="C255" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D255" s="27">
         <v>102200001</v>
@@ -14483,7 +14495,7 @@
         <v>102200</v>
       </c>
       <c r="C256" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D256" s="27">
         <v>102200001</v>
@@ -14533,7 +14545,7 @@
         <v>102400</v>
       </c>
       <c r="C257" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D257" s="27">
         <v>102400026</v>
@@ -14542,10 +14554,10 @@
         <v>21</v>
       </c>
       <c r="F257" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G257" s="33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H257" s="17">
         <v>10000000</v>
@@ -14583,7 +14595,7 @@
         <v>102400</v>
       </c>
       <c r="C258" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D258" s="27">
         <v>102400026</v>
@@ -14633,7 +14645,7 @@
         <v>102400</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D259" s="27">
         <v>102400026</v>
@@ -14683,7 +14695,7 @@
         <v>101800</v>
       </c>
       <c r="C260" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D260" s="27">
         <v>101800001</v>
@@ -14695,7 +14707,7 @@
         <v>60</v>
       </c>
       <c r="G260" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H260" s="17">
         <v>10000000</v>
@@ -14733,7 +14745,7 @@
         <v>101800</v>
       </c>
       <c r="C261" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D261" s="27">
         <v>101800001</v>
@@ -14783,7 +14795,7 @@
         <v>101800</v>
       </c>
       <c r="C262" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D262" s="27">
         <v>101800001</v>
@@ -14833,7 +14845,7 @@
         <v>102500</v>
       </c>
       <c r="C263" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D263" s="27">
         <v>102500001</v>
@@ -14842,10 +14854,10 @@
         <v>21</v>
       </c>
       <c r="F263" s="24" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G263" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H263" s="17">
         <v>10000000</v>
@@ -14883,7 +14895,7 @@
         <v>102500</v>
       </c>
       <c r="C264" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D264" s="27">
         <v>102500001</v>
@@ -14892,10 +14904,10 @@
         <v>22</v>
       </c>
       <c r="F264" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G264" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H264" s="17">
         <v>100000000</v>
@@ -14933,7 +14945,7 @@
         <v>102500</v>
       </c>
       <c r="C265" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D265" s="27">
         <v>102500001</v>
@@ -14942,10 +14954,10 @@
         <v>23</v>
       </c>
       <c r="F265" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G265" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H265" s="31">
         <v>1000000000</v>
@@ -14983,7 +14995,7 @@
         <v>102300</v>
       </c>
       <c r="C266" s="23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D266" s="27">
         <v>102300001</v>
@@ -14995,7 +15007,7 @@
         <v>60</v>
       </c>
       <c r="G266" s="25" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H266" s="17">
         <v>10000000</v>
@@ -15033,7 +15045,7 @@
         <v>102300</v>
       </c>
       <c r="C267" s="23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D267" s="27">
         <v>102300001</v>
@@ -15083,7 +15095,7 @@
         <v>102300</v>
       </c>
       <c r="C268" s="23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D268" s="27">
         <v>102300001</v>
@@ -15133,7 +15145,7 @@
         <v>103400</v>
       </c>
       <c r="C269" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D269" s="27">
         <v>103000001</v>
@@ -15142,10 +15154,10 @@
         <v>21</v>
       </c>
       <c r="F269" s="32" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G269" s="33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H269" s="17">
         <v>10000000</v>
@@ -15183,7 +15195,7 @@
         <v>103400</v>
       </c>
       <c r="C270" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D270" s="27">
         <v>103000001</v>
@@ -15192,10 +15204,10 @@
         <v>22</v>
       </c>
       <c r="F270" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G270" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H270" s="17">
         <v>100000000</v>
@@ -15233,7 +15245,7 @@
         <v>103400</v>
       </c>
       <c r="C271" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D271" s="27">
         <v>103000001</v>
@@ -15242,10 +15254,10 @@
         <v>23</v>
       </c>
       <c r="F271" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G271" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H271" s="31">
         <v>1000000000</v>
@@ -15283,7 +15295,7 @@
         <v>103500</v>
       </c>
       <c r="C272" s="23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D272" s="35">
         <v>102900001</v>
@@ -15333,7 +15345,7 @@
         <v>103500</v>
       </c>
       <c r="C273" s="23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D273" s="35">
         <v>102900001</v>
@@ -15383,7 +15395,7 @@
         <v>103500</v>
       </c>
       <c r="C274" s="23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D274" s="35">
         <v>102900001</v>
@@ -15433,7 +15445,7 @@
         <v>103501</v>
       </c>
       <c r="C275" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D275" s="35">
         <v>103501001</v>
@@ -15483,7 +15495,7 @@
         <v>103501</v>
       </c>
       <c r="C276" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D276" s="35">
         <v>103501001</v>
@@ -15533,7 +15545,7 @@
         <v>103501</v>
       </c>
       <c r="C277" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D277" s="35">
         <v>103501001</v>
@@ -15583,7 +15595,7 @@
         <v>103600</v>
       </c>
       <c r="C278" s="37" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D278" s="38">
         <v>103600001</v>
@@ -15592,10 +15604,10 @@
         <v>21</v>
       </c>
       <c r="F278" s="39" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G278" s="40" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H278" s="41">
         <v>10000000</v>
@@ -15633,7 +15645,7 @@
         <v>103600</v>
       </c>
       <c r="C279" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D279" s="35">
         <v>103600001</v>
@@ -15642,10 +15654,10 @@
         <v>22</v>
       </c>
       <c r="F279" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G279" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H279" s="31">
         <v>100000000</v>
@@ -15683,7 +15695,7 @@
         <v>103600</v>
       </c>
       <c r="C280" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D280" s="35">
         <v>103600001</v>
@@ -15692,10 +15704,10 @@
         <v>23</v>
       </c>
       <c r="F280" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G280" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H280" s="31">
         <v>1000000000</v>
@@ -15733,7 +15745,7 @@
         <v>102000</v>
       </c>
       <c r="C281" s="23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D281" s="35">
         <v>102000001</v>
@@ -15742,10 +15754,10 @@
         <v>21</v>
       </c>
       <c r="F281" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G281" s="25" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H281" s="31">
         <v>10000000</v>
@@ -15783,7 +15795,7 @@
         <v>102000</v>
       </c>
       <c r="C282" s="23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D282" s="35">
         <v>102000001</v>
@@ -15792,10 +15804,10 @@
         <v>22</v>
       </c>
       <c r="F282" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G282" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H282" s="31">
         <v>100000000</v>
@@ -15833,7 +15845,7 @@
         <v>102000</v>
       </c>
       <c r="C283" s="23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D283" s="35">
         <v>102000001</v>
@@ -15842,10 +15854,10 @@
         <v>23</v>
       </c>
       <c r="F283" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G283" s="25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H283" s="31">
         <v>1000000000</v>
@@ -15883,7 +15895,7 @@
         <v>103401</v>
       </c>
       <c r="C284" s="23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D284" s="35">
         <v>103400001</v>
@@ -15892,10 +15904,10 @@
         <v>21</v>
       </c>
       <c r="F284" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G284" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H284" s="31">
         <v>10000000</v>
@@ -15933,7 +15945,7 @@
         <v>103401</v>
       </c>
       <c r="C285" s="23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D285" s="35">
         <v>103400001</v>
@@ -15942,10 +15954,10 @@
         <v>22</v>
       </c>
       <c r="F285" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G285" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H285" s="31">
         <v>100000000</v>
@@ -15983,7 +15995,7 @@
         <v>103401</v>
       </c>
       <c r="C286" s="23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D286" s="35">
         <v>103400001</v>
@@ -15992,10 +16004,10 @@
         <v>23</v>
       </c>
       <c r="F286" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G286" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H286" s="31">
         <v>1000000000</v>
@@ -16033,7 +16045,7 @@
         <v>103800</v>
       </c>
       <c r="C287" s="23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D287" s="35">
         <v>103800001</v>
@@ -16042,10 +16054,10 @@
         <v>21</v>
       </c>
       <c r="F287" s="24" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G287" s="25" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H287" s="31">
         <v>10000000</v>
@@ -16083,7 +16095,7 @@
         <v>103800</v>
       </c>
       <c r="C288" s="23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D288" s="35">
         <v>103800001</v>
@@ -16092,10 +16104,10 @@
         <v>22</v>
       </c>
       <c r="F288" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G288" s="25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H288" s="31">
         <v>100000000</v>
@@ -16133,7 +16145,7 @@
         <v>103800</v>
       </c>
       <c r="C289" s="23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D289" s="35">
         <v>103800001</v>
@@ -16142,10 +16154,10 @@
         <v>23</v>
       </c>
       <c r="F289" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G289" s="25" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="H289" s="31">
         <v>1000000000</v>
@@ -16183,7 +16195,7 @@
         <v>104000</v>
       </c>
       <c r="C290" s="23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D290" s="35">
         <v>104000001</v>
@@ -16192,10 +16204,10 @@
         <v>21</v>
       </c>
       <c r="F290" s="24" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G290" s="25" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H290" s="31">
         <v>10000000</v>
@@ -16233,7 +16245,7 @@
         <v>104000</v>
       </c>
       <c r="C291" s="23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D291" s="35">
         <v>104000001</v>
@@ -16242,10 +16254,10 @@
         <v>22</v>
       </c>
       <c r="F291" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G291" s="25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H291" s="31">
         <v>100000000</v>
@@ -16283,7 +16295,7 @@
         <v>104000</v>
       </c>
       <c r="C292" s="23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D292" s="35">
         <v>104000001</v>
@@ -16292,10 +16304,10 @@
         <v>23</v>
       </c>
       <c r="F292" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G292" s="25" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="H292" s="31">
         <v>1000000000</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\slot\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -1050,9 +1050,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1069,21 +1076,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2744,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="35">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>71</v>
@@ -5636,7 +5636,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="35">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G65" s="25" t="s">
         <v>129</v>
@@ -6284,7 +6284,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77" s="25" t="s">
         <v>144</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\slot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="181">
   <si>
     <t>id</t>
   </si>
@@ -668,9 +668,6 @@
     <t>象财神</t>
   </si>
   <si>
-    <t>24:1</t>
-  </si>
-  <si>
     <t>240000_17001</t>
   </si>
   <si>
@@ -713,7 +710,7 @@
     <t>愤怒的小鸡</t>
   </si>
   <si>
-    <t>3:1</t>
+    <t>4:1</t>
   </si>
   <si>
     <t>120000_17001</t>
@@ -1051,19 +1048,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
@@ -1082,8 +1066,21 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -5639,7 +5636,7 @@
         <v>10</v>
       </c>
       <c r="G65" s="25" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="H65" s="34">
         <v>10000000</v>
@@ -5657,7 +5654,7 @@
         <v>100</v>
       </c>
       <c r="M65" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N65" s="24">
         <v>0</v>
@@ -5672,7 +5669,7 @@
         <v>56478</v>
       </c>
       <c r="R65" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S65" s="24" t="s">
         <v>73</v>
@@ -5795,7 +5792,7 @@
         <v>103700</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="41">
         <v>103700001</v>
@@ -5847,7 +5844,7 @@
         <v>103700</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D69" s="41">
         <v>103700001</v>
@@ -5899,7 +5896,7 @@
         <v>103700</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D70" s="41">
         <v>103700001</v>
@@ -5951,7 +5948,7 @@
         <v>103100</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D71" s="41">
         <v>103100001</v>
@@ -5963,7 +5960,7 @@
         <v>3500</v>
       </c>
       <c r="G71" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H71" s="34">
         <v>10000000</v>
@@ -5996,7 +5993,7 @@
         <v>487120</v>
       </c>
       <c r="R71" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S71" s="24" t="s">
         <v>73</v>
@@ -6015,7 +6012,7 @@
         <v>103100</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D72" s="41">
         <v>103100001</v>
@@ -6024,10 +6021,10 @@
         <v>2</v>
       </c>
       <c r="F72" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G72" s="25" t="s">
         <v>136</v>
-      </c>
-      <c r="G72" s="25" t="s">
-        <v>137</v>
       </c>
       <c r="H72" s="34">
         <v>100000000</v>
@@ -6067,7 +6064,7 @@
         <v>103100</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D73" s="41">
         <v>103100001</v>
@@ -6076,10 +6073,10 @@
         <v>3</v>
       </c>
       <c r="F73" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="G73" s="25" t="s">
         <v>138</v>
-      </c>
-      <c r="G73" s="25" t="s">
-        <v>139</v>
       </c>
       <c r="H73" s="34">
         <v>1000000000</v>
@@ -6119,7 +6116,7 @@
         <v>104000</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D74" s="41">
         <v>104000001</v>
@@ -6128,10 +6125,10 @@
         <v>1</v>
       </c>
       <c r="F74" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G74" s="25" t="s">
         <v>141</v>
-      </c>
-      <c r="G74" s="25" t="s">
-        <v>142</v>
       </c>
       <c r="H74" s="34">
         <v>10000000</v>
@@ -6171,7 +6168,7 @@
         <v>104000</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D75" s="41">
         <v>104000001</v>
@@ -6223,7 +6220,7 @@
         <v>104000</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D76" s="41">
         <v>104000001</v>
@@ -6275,7 +6272,7 @@
         <v>103900</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D77" s="41">
         <v>103900001</v>
@@ -6287,7 +6284,7 @@
         <v>4</v>
       </c>
       <c r="G77" s="25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H77" s="34">
         <v>10000000</v>
@@ -6305,7 +6302,7 @@
         <v>100</v>
       </c>
       <c r="M77" s="26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N77" s="24">
         <v>0</v>
@@ -6320,7 +6317,7 @@
         <v>24514</v>
       </c>
       <c r="R77" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S77" s="24" t="s">
         <v>73</v>
@@ -6339,7 +6336,7 @@
         <v>103900</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D78" s="41">
         <v>103900001</v>
@@ -6348,10 +6345,10 @@
         <v>2</v>
       </c>
       <c r="F78" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G78" s="25" t="s">
         <v>136</v>
-      </c>
-      <c r="G78" s="25" t="s">
-        <v>137</v>
       </c>
       <c r="H78" s="34">
         <v>100000000</v>
@@ -6391,7 +6388,7 @@
         <v>103900</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D79" s="41">
         <v>103900001</v>
@@ -6400,10 +6397,10 @@
         <v>3</v>
       </c>
       <c r="F79" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="G79" s="25" t="s">
         <v>138</v>
-      </c>
-      <c r="G79" s="25" t="s">
-        <v>139</v>
       </c>
       <c r="H79" s="34">
         <v>1000000000</v>
@@ -6443,7 +6440,7 @@
         <v>101600</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D80" s="41">
         <v>101600001</v>
@@ -6495,7 +6492,7 @@
         <v>101600</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D81" s="41">
         <v>101600001</v>
@@ -6547,7 +6544,7 @@
         <v>101600</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D82" s="41">
         <v>101600001</v>
@@ -6599,7 +6596,7 @@
         <v>101500</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D83" s="41">
         <v>101500001</v>
@@ -6611,7 +6608,7 @@
         <v>900000</v>
       </c>
       <c r="G83" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H83" s="34">
         <v>10000000</v>
@@ -6644,7 +6641,7 @@
         <v>1647124</v>
       </c>
       <c r="R83" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S83" s="24" t="s">
         <v>73</v>
@@ -6663,7 +6660,7 @@
         <v>101500</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D84" s="41">
         <v>101500001</v>
@@ -6715,7 +6712,7 @@
         <v>101500</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D85" s="41">
         <v>101500001</v>
@@ -6767,7 +6764,7 @@
         <v>102600</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D86" s="41">
         <v>102600001</v>
@@ -6819,7 +6816,7 @@
         <v>102600</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D87" s="41">
         <v>102600001</v>
@@ -6871,7 +6868,7 @@
         <v>102600</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D88" s="41">
         <v>102600001</v>
@@ -6923,7 +6920,7 @@
         <v>105000</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D89" s="41">
         <v>105000001</v>
@@ -6975,7 +6972,7 @@
         <v>105000</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D90" s="41">
         <v>105000001</v>
@@ -7027,7 +7024,7 @@
         <v>105000</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D91" s="41">
         <v>105000001</v>
@@ -7079,7 +7076,7 @@
         <v>105100</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D92" s="41">
         <v>105100001</v>
@@ -7131,7 +7128,7 @@
         <v>105100</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D93" s="41">
         <v>105100001</v>
@@ -7183,7 +7180,7 @@
         <v>105100</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D94" s="41">
         <v>105100001</v>
@@ -7235,7 +7232,7 @@
         <v>105500</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D95" s="41">
         <v>105500001</v>
@@ -7287,7 +7284,7 @@
         <v>105500</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D96" s="41">
         <v>105500001</v>
@@ -7339,7 +7336,7 @@
         <v>105500</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D97" s="41">
         <v>105500001</v>
@@ -7391,7 +7388,7 @@
         <v>104800</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D98" s="30">
         <v>104800001</v>
@@ -7400,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G98" s="25" t="s">
         <v>84</v>
@@ -7421,7 +7418,7 @@
         <v>100</v>
       </c>
       <c r="M98" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N98" s="24">
         <v>0</v>
@@ -7443,7 +7440,7 @@
         <v>104800</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D99" s="30">
         <v>104800001</v>
@@ -7452,7 +7449,7 @@
         <v>2</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G99" s="25" t="s">
         <v>75</v>
@@ -7473,7 +7470,7 @@
         <v>100</v>
       </c>
       <c r="M99" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N99" s="24">
         <v>0</v>
@@ -7495,7 +7492,7 @@
         <v>104800</v>
       </c>
       <c r="C100" s="23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D100" s="30">
         <v>104800001</v>
@@ -7504,7 +7501,7 @@
         <v>3</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G100" s="25" t="s">
         <v>77</v>
@@ -7525,7 +7522,7 @@
         <v>100</v>
       </c>
       <c r="M100" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N100" s="24">
         <v>0</v>
@@ -7547,7 +7544,7 @@
         <v>105501</v>
       </c>
       <c r="C101" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D101" s="41">
         <v>105501001</v>
@@ -7599,7 +7596,7 @@
         <v>105501</v>
       </c>
       <c r="C102" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D102" s="41">
         <v>105501001</v>
@@ -7651,7 +7648,7 @@
         <v>105501</v>
       </c>
       <c r="C103" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D103" s="41">
         <v>105501001</v>
@@ -7703,7 +7700,7 @@
         <v>105502</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D104" s="41">
         <v>105502001</v>
@@ -7755,7 +7752,7 @@
         <v>105502</v>
       </c>
       <c r="C105" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D105" s="41">
         <v>105502001</v>
@@ -7807,7 +7804,7 @@
         <v>105502</v>
       </c>
       <c r="C106" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D106" s="41">
         <v>105502001</v>
@@ -7859,7 +7856,7 @@
         <v>105300</v>
       </c>
       <c r="C107" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D107" s="41">
         <v>105300001</v>
@@ -7868,7 +7865,7 @@
         <v>1</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G107" s="25" t="s">
         <v>84</v>
@@ -7911,7 +7908,7 @@
         <v>105300</v>
       </c>
       <c r="C108" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D108" s="41">
         <v>105300001</v>
@@ -7920,7 +7917,7 @@
         <v>2</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G108" s="25" t="s">
         <v>75</v>
@@ -7963,7 +7960,7 @@
         <v>105300</v>
       </c>
       <c r="C109" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D109" s="41">
         <v>105300001</v>
@@ -7972,7 +7969,7 @@
         <v>3</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G109" s="25" t="s">
         <v>77</v>
@@ -8048,7 +8045,7 @@
         <v>52</v>
       </c>
       <c r="N110" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O110" s="50"/>
       <c r="P110" s="50"/>
@@ -8100,7 +8097,7 @@
         <v>55</v>
       </c>
       <c r="N111" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O111" s="50"/>
       <c r="P111" s="50"/>
@@ -8152,7 +8149,7 @@
         <v>58</v>
       </c>
       <c r="N112" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O112" s="50"/>
       <c r="P112" s="50"/>
@@ -8204,7 +8201,7 @@
         <v>52</v>
       </c>
       <c r="N113" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O113" s="50"/>
       <c r="P113" s="50"/>
@@ -8256,7 +8253,7 @@
         <v>55</v>
       </c>
       <c r="N114" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O114" s="50"/>
       <c r="P114" s="50"/>
@@ -8308,7 +8305,7 @@
         <v>58</v>
       </c>
       <c r="N115" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O115" s="50"/>
       <c r="P115" s="50"/>
@@ -8360,7 +8357,7 @@
         <v>52</v>
       </c>
       <c r="N116" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O116" s="50"/>
       <c r="P116" s="50"/>
@@ -8412,7 +8409,7 @@
         <v>55</v>
       </c>
       <c r="N117" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O117" s="50"/>
       <c r="P117" s="50"/>
@@ -8464,7 +8461,7 @@
         <v>58</v>
       </c>
       <c r="N118" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O118" s="50"/>
       <c r="P118" s="50"/>
@@ -8516,7 +8513,7 @@
         <v>52</v>
       </c>
       <c r="N119" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O119" s="62"/>
       <c r="P119" s="62"/>
@@ -8568,7 +8565,7 @@
         <v>55</v>
       </c>
       <c r="N120" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O120" s="62"/>
       <c r="P120" s="62"/>
@@ -8620,7 +8617,7 @@
         <v>58</v>
       </c>
       <c r="N121" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O121" s="62"/>
       <c r="P121" s="62"/>
@@ -8672,7 +8669,7 @@
         <v>52</v>
       </c>
       <c r="N122" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O122" s="50"/>
       <c r="P122" s="50"/>
@@ -8724,7 +8721,7 @@
         <v>55</v>
       </c>
       <c r="N123" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O123" s="50"/>
       <c r="P123" s="50"/>
@@ -8776,7 +8773,7 @@
         <v>58</v>
       </c>
       <c r="N124" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O124" s="50"/>
       <c r="P124" s="50"/>
@@ -8828,7 +8825,7 @@
         <v>52</v>
       </c>
       <c r="N125" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O125" s="50"/>
       <c r="P125" s="50"/>
@@ -8880,7 +8877,7 @@
         <v>55</v>
       </c>
       <c r="N126" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O126" s="50"/>
       <c r="P126" s="50"/>
@@ -8932,7 +8929,7 @@
         <v>58</v>
       </c>
       <c r="N127" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O127" s="50"/>
       <c r="P127" s="50"/>
@@ -8984,7 +8981,7 @@
         <v>52</v>
       </c>
       <c r="N128" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O128" s="50"/>
       <c r="P128" s="50"/>
@@ -9036,7 +9033,7 @@
         <v>55</v>
       </c>
       <c r="N129" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O129" s="50"/>
       <c r="P129" s="50"/>
@@ -9088,7 +9085,7 @@
         <v>58</v>
       </c>
       <c r="N130" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O130" s="50"/>
       <c r="P130" s="50"/>
@@ -9140,7 +9137,7 @@
         <v>52</v>
       </c>
       <c r="N131" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O131" s="50"/>
       <c r="P131" s="50"/>
@@ -9192,7 +9189,7 @@
         <v>55</v>
       </c>
       <c r="N132" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O132" s="50"/>
       <c r="P132" s="50"/>
@@ -9244,7 +9241,7 @@
         <v>58</v>
       </c>
       <c r="N133" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O133" s="50"/>
       <c r="P133" s="50"/>
@@ -9296,7 +9293,7 @@
         <v>52</v>
       </c>
       <c r="N134" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O134" s="50"/>
       <c r="P134" s="50"/>
@@ -9348,7 +9345,7 @@
         <v>55</v>
       </c>
       <c r="N135" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O135" s="50"/>
       <c r="P135" s="50"/>
@@ -9400,7 +9397,7 @@
         <v>58</v>
       </c>
       <c r="N136" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O136" s="50"/>
       <c r="P136" s="50"/>
@@ -9452,7 +9449,7 @@
         <v>52</v>
       </c>
       <c r="N137" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O137" s="50"/>
       <c r="P137" s="50"/>
@@ -9504,7 +9501,7 @@
         <v>55</v>
       </c>
       <c r="N138" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O138" s="50"/>
       <c r="P138" s="50"/>
@@ -9556,7 +9553,7 @@
         <v>58</v>
       </c>
       <c r="N139" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O139" s="50"/>
       <c r="P139" s="50"/>
@@ -9584,7 +9581,7 @@
         <v>10</v>
       </c>
       <c r="F140" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G140" s="25" t="s">
         <v>107</v>
@@ -9608,7 +9605,7 @@
         <v>52</v>
       </c>
       <c r="N140" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O140" s="50"/>
       <c r="P140" s="50"/>
@@ -9660,7 +9657,7 @@
         <v>55</v>
       </c>
       <c r="N141" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O141" s="50"/>
       <c r="P141" s="50"/>
@@ -9712,7 +9709,7 @@
         <v>58</v>
       </c>
       <c r="N142" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O142" s="50"/>
       <c r="P142" s="50"/>
@@ -9764,7 +9761,7 @@
         <v>52</v>
       </c>
       <c r="N143" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O143" s="50"/>
       <c r="P143" s="50"/>
@@ -9816,7 +9813,7 @@
         <v>55</v>
       </c>
       <c r="N144" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O144" s="50"/>
       <c r="P144" s="50"/>
@@ -9868,7 +9865,7 @@
         <v>58</v>
       </c>
       <c r="N145" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O145" s="50"/>
       <c r="P145" s="50"/>
@@ -9920,7 +9917,7 @@
         <v>52</v>
       </c>
       <c r="N146" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O146" s="50"/>
       <c r="P146" s="50"/>
@@ -9972,7 +9969,7 @@
         <v>55</v>
       </c>
       <c r="N147" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O147" s="50"/>
       <c r="P147" s="50"/>
@@ -10024,7 +10021,7 @@
         <v>58</v>
       </c>
       <c r="N148" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O148" s="50"/>
       <c r="P148" s="50"/>
@@ -10076,7 +10073,7 @@
         <v>52</v>
       </c>
       <c r="N149" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O149" s="50"/>
       <c r="P149" s="50"/>
@@ -10128,7 +10125,7 @@
         <v>55</v>
       </c>
       <c r="N150" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O150" s="50"/>
       <c r="P150" s="50"/>
@@ -10180,7 +10177,7 @@
         <v>58</v>
       </c>
       <c r="N151" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O151" s="50"/>
       <c r="P151" s="50"/>
@@ -10232,7 +10229,7 @@
         <v>52</v>
       </c>
       <c r="N152" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O152" s="50"/>
       <c r="P152" s="50"/>
@@ -10284,7 +10281,7 @@
         <v>55</v>
       </c>
       <c r="N153" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O153" s="50"/>
       <c r="P153" s="50"/>
@@ -10336,7 +10333,7 @@
         <v>58</v>
       </c>
       <c r="N154" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O154" s="50"/>
       <c r="P154" s="50"/>
@@ -10388,7 +10385,7 @@
         <v>52</v>
       </c>
       <c r="N155" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O155" s="50"/>
       <c r="P155" s="50"/>
@@ -10440,7 +10437,7 @@
         <v>55</v>
       </c>
       <c r="N156" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O156" s="50"/>
       <c r="P156" s="50"/>
@@ -10492,7 +10489,7 @@
         <v>58</v>
       </c>
       <c r="N157" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O157" s="50"/>
       <c r="P157" s="50"/>
@@ -10544,7 +10541,7 @@
         <v>52</v>
       </c>
       <c r="N158" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O158" s="50"/>
       <c r="P158" s="50"/>
@@ -10596,7 +10593,7 @@
         <v>55</v>
       </c>
       <c r="N159" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O159" s="50"/>
       <c r="P159" s="50"/>
@@ -10648,7 +10645,7 @@
         <v>58</v>
       </c>
       <c r="N160" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O160" s="50"/>
       <c r="P160" s="50"/>
@@ -10676,10 +10673,10 @@
         <v>10</v>
       </c>
       <c r="F161" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="G161" s="25" t="s">
         <v>169</v>
-      </c>
-      <c r="G161" s="25" t="s">
-        <v>170</v>
       </c>
       <c r="H161" s="63">
         <v>0</v>
@@ -10700,7 +10697,7 @@
         <v>52</v>
       </c>
       <c r="N161" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O161" s="50"/>
       <c r="P161" s="50"/>
@@ -10752,7 +10749,7 @@
         <v>55</v>
       </c>
       <c r="N162" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O162" s="50"/>
       <c r="P162" s="50"/>
@@ -10804,7 +10801,7 @@
         <v>58</v>
       </c>
       <c r="N163" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O163" s="50"/>
       <c r="P163" s="50"/>
@@ -10856,7 +10853,7 @@
         <v>52</v>
       </c>
       <c r="N164" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O164" s="50"/>
       <c r="P164" s="50"/>
@@ -10908,7 +10905,7 @@
         <v>55</v>
       </c>
       <c r="N165" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O165" s="50"/>
       <c r="P165" s="50"/>
@@ -10960,7 +10957,7 @@
         <v>58</v>
       </c>
       <c r="N166" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O166" s="50"/>
       <c r="P166" s="50"/>
@@ -10988,10 +10985,10 @@
         <v>11</v>
       </c>
       <c r="F167" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G167" s="25" t="s">
         <v>141</v>
-      </c>
-      <c r="G167" s="25" t="s">
-        <v>142</v>
       </c>
       <c r="H167" s="63">
         <v>0</v>
@@ -11012,7 +11009,7 @@
         <v>52</v>
       </c>
       <c r="N167" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O167" s="50"/>
       <c r="P167" s="50"/>
@@ -11064,7 +11061,7 @@
         <v>55</v>
       </c>
       <c r="N168" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O168" s="50"/>
       <c r="P168" s="50"/>
@@ -11116,7 +11113,7 @@
         <v>58</v>
       </c>
       <c r="N169" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O169" s="50"/>
       <c r="P169" s="50"/>
@@ -11168,7 +11165,7 @@
         <v>52</v>
       </c>
       <c r="N170" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O170" s="50"/>
       <c r="P170" s="50"/>
@@ -11220,7 +11217,7 @@
         <v>55</v>
       </c>
       <c r="N171" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O171" s="50"/>
       <c r="P171" s="50"/>
@@ -11272,7 +11269,7 @@
         <v>58</v>
       </c>
       <c r="N172" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O172" s="50"/>
       <c r="P172" s="50"/>
@@ -11291,7 +11288,7 @@
         <v>103700</v>
       </c>
       <c r="C173" s="56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D173" s="57">
         <v>103700001</v>
@@ -11324,7 +11321,7 @@
         <v>52</v>
       </c>
       <c r="N173" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O173" s="50"/>
       <c r="P173" s="50"/>
@@ -11343,7 +11340,7 @@
         <v>103700</v>
       </c>
       <c r="C174" s="56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D174" s="57">
         <v>103700001</v>
@@ -11376,7 +11373,7 @@
         <v>55</v>
       </c>
       <c r="N174" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O174" s="50"/>
       <c r="P174" s="50"/>
@@ -11395,7 +11392,7 @@
         <v>103700</v>
       </c>
       <c r="C175" s="56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D175" s="57">
         <v>103100001</v>
@@ -11428,7 +11425,7 @@
         <v>58</v>
       </c>
       <c r="N175" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O175" s="50"/>
       <c r="P175" s="50"/>
@@ -11447,7 +11444,7 @@
         <v>103100</v>
       </c>
       <c r="C176" s="56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D176" s="57">
         <v>103100001</v>
@@ -11456,10 +11453,10 @@
         <v>11</v>
       </c>
       <c r="F176" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="G176" s="25" t="s">
         <v>171</v>
-      </c>
-      <c r="G176" s="25" t="s">
-        <v>172</v>
       </c>
       <c r="H176" s="59">
         <v>0</v>
@@ -11480,7 +11477,7 @@
         <v>52</v>
       </c>
       <c r="N176" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O176" s="50"/>
       <c r="P176" s="50"/>
@@ -11499,7 +11496,7 @@
         <v>103100</v>
       </c>
       <c r="C177" s="56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D177" s="57">
         <v>103100001</v>
@@ -11508,10 +11505,10 @@
         <v>12</v>
       </c>
       <c r="F177" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G177" s="25" t="s">
         <v>136</v>
-      </c>
-      <c r="G177" s="25" t="s">
-        <v>137</v>
       </c>
       <c r="H177" s="59">
         <v>0</v>
@@ -11532,7 +11529,7 @@
         <v>55</v>
       </c>
       <c r="N177" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O177" s="50"/>
       <c r="P177" s="50"/>
@@ -11551,7 +11548,7 @@
         <v>103100</v>
       </c>
       <c r="C178" s="56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D178" s="57">
         <v>103100001</v>
@@ -11560,10 +11557,10 @@
         <v>13</v>
       </c>
       <c r="F178" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="G178" s="25" t="s">
         <v>138</v>
-      </c>
-      <c r="G178" s="25" t="s">
-        <v>139</v>
       </c>
       <c r="H178" s="63">
         <v>0</v>
@@ -11584,7 +11581,7 @@
         <v>58</v>
       </c>
       <c r="N178" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O178" s="50"/>
       <c r="P178" s="50"/>
@@ -11603,7 +11600,7 @@
         <v>104000</v>
       </c>
       <c r="C179" s="56" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D179" s="57">
         <v>104000001</v>
@@ -11612,10 +11609,10 @@
         <v>11</v>
       </c>
       <c r="F179" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G179" s="25" t="s">
         <v>141</v>
-      </c>
-      <c r="G179" s="25" t="s">
-        <v>142</v>
       </c>
       <c r="H179" s="63">
         <v>0</v>
@@ -11636,7 +11633,7 @@
         <v>52</v>
       </c>
       <c r="N179" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O179" s="50"/>
       <c r="P179" s="50"/>
@@ -11655,7 +11652,7 @@
         <v>104000</v>
       </c>
       <c r="C180" s="56" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D180" s="57">
         <v>104000001</v>
@@ -11688,7 +11685,7 @@
         <v>55</v>
       </c>
       <c r="N180" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O180" s="50"/>
       <c r="P180" s="50"/>
@@ -11707,7 +11704,7 @@
         <v>104000</v>
       </c>
       <c r="C181" s="56" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D181" s="57">
         <v>104000001</v>
@@ -11740,7 +11737,7 @@
         <v>58</v>
       </c>
       <c r="N181" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O181" s="50"/>
       <c r="P181" s="50"/>
@@ -11759,7 +11756,7 @@
         <v>103900</v>
       </c>
       <c r="C182" s="56" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D182" s="57">
         <v>103900001</v>
@@ -11768,10 +11765,10 @@
         <v>11</v>
       </c>
       <c r="F182" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="G182" s="25" t="s">
         <v>171</v>
-      </c>
-      <c r="G182" s="25" t="s">
-        <v>172</v>
       </c>
       <c r="H182" s="63">
         <v>0</v>
@@ -11792,7 +11789,7 @@
         <v>52</v>
       </c>
       <c r="N182" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O182" s="50"/>
       <c r="P182" s="50"/>
@@ -11811,7 +11808,7 @@
         <v>103900</v>
       </c>
       <c r="C183" s="56" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D183" s="57">
         <v>103900001</v>
@@ -11820,10 +11817,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G183" s="25" t="s">
         <v>136</v>
-      </c>
-      <c r="G183" s="25" t="s">
-        <v>137</v>
       </c>
       <c r="H183" s="63">
         <v>0</v>
@@ -11844,7 +11841,7 @@
         <v>55</v>
       </c>
       <c r="N183" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O183" s="50"/>
       <c r="P183" s="50"/>
@@ -11863,7 +11860,7 @@
         <v>103900</v>
       </c>
       <c r="C184" s="56" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D184" s="57">
         <v>103900001</v>
@@ -11872,10 +11869,10 @@
         <v>13</v>
       </c>
       <c r="F184" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="G184" s="25" t="s">
         <v>138</v>
-      </c>
-      <c r="G184" s="25" t="s">
-        <v>139</v>
       </c>
       <c r="H184" s="63">
         <v>0</v>
@@ -11896,7 +11893,7 @@
         <v>58</v>
       </c>
       <c r="N184" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O184" s="50"/>
       <c r="P184" s="50"/>
@@ -11915,7 +11912,7 @@
         <v>101600</v>
       </c>
       <c r="C185" s="56" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D185" s="57">
         <v>101600001</v>
@@ -11948,7 +11945,7 @@
         <v>52</v>
       </c>
       <c r="N185" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O185" s="50"/>
       <c r="P185" s="50"/>
@@ -11967,7 +11964,7 @@
         <v>101600</v>
       </c>
       <c r="C186" s="56" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D186" s="57">
         <v>101600001</v>
@@ -12000,7 +11997,7 @@
         <v>55</v>
       </c>
       <c r="N186" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O186" s="50"/>
       <c r="P186" s="50"/>
@@ -12019,7 +12016,7 @@
         <v>101600</v>
       </c>
       <c r="C187" s="56" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D187" s="57">
         <v>101600001</v>
@@ -12052,7 +12049,7 @@
         <v>58</v>
       </c>
       <c r="N187" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O187" s="50"/>
       <c r="P187" s="50"/>
@@ -12071,7 +12068,7 @@
         <v>101500</v>
       </c>
       <c r="C188" s="56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D188" s="57">
         <v>101500001</v>
@@ -12104,7 +12101,7 @@
         <v>52</v>
       </c>
       <c r="N188" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O188" s="50"/>
       <c r="P188" s="50"/>
@@ -12123,7 +12120,7 @@
         <v>101500</v>
       </c>
       <c r="C189" s="56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D189" s="57">
         <v>101500001</v>
@@ -12156,7 +12153,7 @@
         <v>55</v>
       </c>
       <c r="N189" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O189" s="50"/>
       <c r="P189" s="50"/>
@@ -12175,7 +12172,7 @@
         <v>101500</v>
       </c>
       <c r="C190" s="56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D190" s="57">
         <v>101500001</v>
@@ -12208,7 +12205,7 @@
         <v>58</v>
       </c>
       <c r="N190" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O190" s="50"/>
       <c r="P190" s="50"/>
@@ -12227,7 +12224,7 @@
         <v>102600</v>
       </c>
       <c r="C191" s="56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D191" s="57">
         <v>102600001</v>
@@ -12260,7 +12257,7 @@
         <v>52</v>
       </c>
       <c r="N191" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O191" s="50"/>
       <c r="P191" s="50"/>
@@ -12279,7 +12276,7 @@
         <v>102600</v>
       </c>
       <c r="C192" s="56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D192" s="57">
         <v>102600001</v>
@@ -12312,7 +12309,7 @@
         <v>55</v>
       </c>
       <c r="N192" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O192" s="50"/>
       <c r="P192" s="50"/>
@@ -12331,7 +12328,7 @@
         <v>102600</v>
       </c>
       <c r="C193" s="56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D193" s="57">
         <v>102600001</v>
@@ -12364,7 +12361,7 @@
         <v>58</v>
       </c>
       <c r="N193" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O193" s="50"/>
       <c r="P193" s="50"/>
@@ -12383,7 +12380,7 @@
         <v>105000</v>
       </c>
       <c r="C194" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D194" s="57">
         <v>105000001</v>
@@ -12416,7 +12413,7 @@
         <v>52</v>
       </c>
       <c r="N194" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O194" s="50"/>
       <c r="P194" s="50"/>
@@ -12435,7 +12432,7 @@
         <v>105000</v>
       </c>
       <c r="C195" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D195" s="57">
         <v>105000001</v>
@@ -12468,7 +12465,7 @@
         <v>55</v>
       </c>
       <c r="N195" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O195" s="50"/>
       <c r="P195" s="50"/>
@@ -12487,7 +12484,7 @@
         <v>105000</v>
       </c>
       <c r="C196" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D196" s="57">
         <v>105000001</v>
@@ -12520,7 +12517,7 @@
         <v>58</v>
       </c>
       <c r="N196" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O196" s="50"/>
       <c r="P196" s="50"/>
@@ -12539,7 +12536,7 @@
         <v>105100</v>
       </c>
       <c r="C197" s="56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D197" s="57">
         <v>105100001</v>
@@ -12572,7 +12569,7 @@
         <v>52</v>
       </c>
       <c r="N197" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O197" s="50"/>
       <c r="P197" s="50"/>
@@ -12591,7 +12588,7 @@
         <v>105100</v>
       </c>
       <c r="C198" s="56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D198" s="57">
         <v>105100001</v>
@@ -12624,7 +12621,7 @@
         <v>55</v>
       </c>
       <c r="N198" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O198" s="50"/>
       <c r="P198" s="50"/>
@@ -12643,7 +12640,7 @@
         <v>105100</v>
       </c>
       <c r="C199" s="56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D199" s="57">
         <v>105100001</v>
@@ -12676,7 +12673,7 @@
         <v>58</v>
       </c>
       <c r="N199" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O199" s="50"/>
       <c r="P199" s="50"/>
@@ -12695,7 +12692,7 @@
         <v>105400</v>
       </c>
       <c r="C200" s="56" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D200" s="57">
         <v>105400001</v>
@@ -12704,7 +12701,7 @@
         <v>11</v>
       </c>
       <c r="F200" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G200" s="25" t="s">
         <v>84</v>
@@ -12725,10 +12722,10 @@
         <v>0</v>
       </c>
       <c r="M200" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N200" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O200" s="50"/>
       <c r="P200" s="50"/>
@@ -12747,7 +12744,7 @@
         <v>105400</v>
       </c>
       <c r="C201" s="56" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D201" s="57">
         <v>105400001</v>
@@ -12756,7 +12753,7 @@
         <v>12</v>
       </c>
       <c r="F201" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G201" s="25" t="s">
         <v>75</v>
@@ -12777,10 +12774,10 @@
         <v>0</v>
       </c>
       <c r="M201" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N201" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O201" s="50"/>
       <c r="P201" s="50"/>
@@ -12799,7 +12796,7 @@
         <v>105400</v>
       </c>
       <c r="C202" s="56" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D202" s="57">
         <v>105400001</v>
@@ -12808,7 +12805,7 @@
         <v>13</v>
       </c>
       <c r="F202" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G202" s="25" t="s">
         <v>77</v>
@@ -12829,10 +12826,10 @@
         <v>0</v>
       </c>
       <c r="M202" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N202" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O202" s="50"/>
       <c r="P202" s="50"/>
@@ -12851,7 +12848,7 @@
         <v>100800</v>
       </c>
       <c r="C203" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D203" s="41">
         <v>100800001</v>
@@ -12860,7 +12857,7 @@
         <v>11</v>
       </c>
       <c r="F203" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G203" s="25" t="s">
         <v>84</v>
@@ -12881,10 +12878,10 @@
         <v>0</v>
       </c>
       <c r="M203" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N203" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:22">
@@ -12895,7 +12892,7 @@
         <v>100800</v>
       </c>
       <c r="C204" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D204" s="41">
         <v>100800001</v>
@@ -12904,7 +12901,7 @@
         <v>12</v>
       </c>
       <c r="F204" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G204" s="25" t="s">
         <v>75</v>
@@ -12925,10 +12922,10 @@
         <v>0</v>
       </c>
       <c r="M204" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N204" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:22">
@@ -12939,7 +12936,7 @@
         <v>100800</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D205" s="41">
         <v>100800001</v>
@@ -12948,7 +12945,7 @@
         <v>13</v>
       </c>
       <c r="F205" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G205" s="25" t="s">
         <v>77</v>
@@ -12969,10 +12966,10 @@
         <v>0</v>
       </c>
       <c r="M205" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N205" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:22">
@@ -12983,7 +12980,7 @@
         <v>105300</v>
       </c>
       <c r="C206" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D206" s="41">
         <v>105300001</v>
@@ -12992,7 +12989,7 @@
         <v>11</v>
       </c>
       <c r="F206" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G206" s="25" t="s">
         <v>84</v>
@@ -13013,10 +13010,10 @@
         <v>0</v>
       </c>
       <c r="M206" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N206" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:22">
@@ -13027,7 +13024,7 @@
         <v>105300</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D207" s="41">
         <v>105300001</v>
@@ -13036,7 +13033,7 @@
         <v>12</v>
       </c>
       <c r="F207" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G207" s="25" t="s">
         <v>75</v>
@@ -13057,10 +13054,10 @@
         <v>0</v>
       </c>
       <c r="M207" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N207" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:22">
@@ -13071,7 +13068,7 @@
         <v>105300</v>
       </c>
       <c r="C208" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D208" s="41">
         <v>105300001</v>
@@ -13080,7 +13077,7 @@
         <v>13</v>
       </c>
       <c r="F208" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G208" s="25" t="s">
         <v>77</v>
@@ -13101,10 +13098,10 @@
         <v>0</v>
       </c>
       <c r="M208" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N208" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:14">
@@ -13115,7 +13112,7 @@
         <v>105700</v>
       </c>
       <c r="C209" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D209" s="41">
         <v>105700001</v>
@@ -13124,7 +13121,7 @@
         <v>11</v>
       </c>
       <c r="F209" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G209" s="25" t="s">
         <v>84</v>
@@ -13145,10 +13142,10 @@
         <v>0</v>
       </c>
       <c r="M209" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N209" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:14">
@@ -13159,7 +13156,7 @@
         <v>105700</v>
       </c>
       <c r="C210" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D210" s="41">
         <v>105700001</v>
@@ -13168,7 +13165,7 @@
         <v>12</v>
       </c>
       <c r="F210" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G210" s="25" t="s">
         <v>75</v>
@@ -13189,10 +13186,10 @@
         <v>0</v>
       </c>
       <c r="M210" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N210" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:14">
@@ -13203,7 +13200,7 @@
         <v>105700</v>
       </c>
       <c r="C211" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D211" s="41">
         <v>105700001</v>
@@ -13212,7 +13209,7 @@
         <v>13</v>
       </c>
       <c r="F211" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G211" s="25" t="s">
         <v>77</v>
@@ -13233,10 +13230,10 @@
         <v>0</v>
       </c>
       <c r="M211" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N211" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="212" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -13247,7 +13244,7 @@
         <v>105800</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D212" s="67">
         <v>105800001</v>
@@ -13256,7 +13253,7 @@
         <v>11</v>
       </c>
       <c r="F212" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G212" s="25" t="s">
         <v>84</v>
@@ -13277,10 +13274,10 @@
         <v>0</v>
       </c>
       <c r="M212" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N212" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="213" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -13291,7 +13288,7 @@
         <v>105800</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D213" s="67">
         <v>105800001</v>
@@ -13300,7 +13297,7 @@
         <v>12</v>
       </c>
       <c r="F213" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G213" s="25" t="s">
         <v>75</v>
@@ -13321,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="M213" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N213" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="214" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -13335,7 +13332,7 @@
         <v>105800</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D214" s="67">
         <v>105800001</v>
@@ -13344,7 +13341,7 @@
         <v>13</v>
       </c>
       <c r="F214" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G214" s="25" t="s">
         <v>77</v>
@@ -13365,10 +13362,10 @@
         <v>0</v>
       </c>
       <c r="M214" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N214" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="215" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -13379,7 +13376,7 @@
         <v>105500</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D215" s="67">
         <v>105500001</v>
@@ -13409,10 +13406,10 @@
         <v>0</v>
       </c>
       <c r="M215" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N215" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="216" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -13423,7 +13420,7 @@
         <v>105500</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D216" s="67">
         <v>105500001</v>
@@ -13453,10 +13450,10 @@
         <v>0</v>
       </c>
       <c r="M216" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N216" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="217" s="7" customFormat="1" ht="16.5" spans="1:14">
@@ -13467,7 +13464,7 @@
         <v>105500</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D217" s="67">
         <v>105500001</v>
@@ -13497,10 +13494,10 @@
         <v>0</v>
       </c>
       <c r="M217" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N217" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:14">
@@ -13511,7 +13508,7 @@
         <v>104800</v>
       </c>
       <c r="C218" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D218" s="30">
         <v>104800001</v>
@@ -13520,7 +13517,7 @@
         <v>11</v>
       </c>
       <c r="F218" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G218" s="25" t="s">
         <v>84</v>
@@ -13541,10 +13538,10 @@
         <v>0</v>
       </c>
       <c r="M218" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N218" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:14">
@@ -13555,7 +13552,7 @@
         <v>104800</v>
       </c>
       <c r="C219" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D219" s="30">
         <v>104800001</v>
@@ -13564,7 +13561,7 @@
         <v>12</v>
       </c>
       <c r="F219" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G219" s="25" t="s">
         <v>75</v>
@@ -13585,10 +13582,10 @@
         <v>0</v>
       </c>
       <c r="M219" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N219" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:14">
@@ -13599,7 +13596,7 @@
         <v>104800</v>
       </c>
       <c r="C220" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D220" s="30">
         <v>104800001</v>
@@ -13608,7 +13605,7 @@
         <v>13</v>
       </c>
       <c r="F220" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G220" s="25" t="s">
         <v>77</v>
@@ -13629,10 +13626,10 @@
         <v>0</v>
       </c>
       <c r="M220" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N220" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="221" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -13643,7 +13640,7 @@
         <v>105501</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D221" s="67">
         <v>105501001</v>
@@ -13673,10 +13670,10 @@
         <v>0</v>
       </c>
       <c r="M221" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N221" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="222" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -13687,7 +13684,7 @@
         <v>105501</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D222" s="67">
         <v>105501001</v>
@@ -13717,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="M222" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N222" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="223" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -13731,7 +13728,7 @@
         <v>105501</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D223" s="67">
         <v>105501001</v>
@@ -13761,10 +13758,10 @@
         <v>0</v>
       </c>
       <c r="M223" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N223" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="224" s="8" customFormat="1" ht="16.5" spans="1:14">
@@ -13775,7 +13772,7 @@
         <v>105502</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D224" s="67">
         <v>105502001</v>
@@ -13805,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="M224" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N224" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="225" s="8" customFormat="1" ht="16.5" spans="1:22">
@@ -13819,7 +13816,7 @@
         <v>105502</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D225" s="67">
         <v>105502001</v>
@@ -13849,10 +13846,10 @@
         <v>0</v>
       </c>
       <c r="M225" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N225" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="226" s="8" customFormat="1" ht="16.5" spans="1:22">
@@ -13863,7 +13860,7 @@
         <v>105502</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D226" s="67">
         <v>105502001</v>
@@ -13893,10 +13890,10 @@
         <v>0</v>
       </c>
       <c r="M226" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N226" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="227" customFormat="1" ht="16.5" spans="1:22">
@@ -13907,7 +13904,7 @@
         <v>104100</v>
       </c>
       <c r="C227" s="69" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D227" s="30">
         <v>104100001</v>
@@ -13916,7 +13913,7 @@
         <v>11</v>
       </c>
       <c r="F227" s="53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G227" s="70" t="s">
         <v>84</v>
@@ -13937,10 +13934,10 @@
         <v>0</v>
       </c>
       <c r="M227" s="54" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N227" s="53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="228" customFormat="1" ht="16.5" spans="1:22">
@@ -13951,7 +13948,7 @@
         <v>104100</v>
       </c>
       <c r="C228" s="69" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D228" s="30">
         <v>104100001</v>
@@ -13960,7 +13957,7 @@
         <v>12</v>
       </c>
       <c r="F228" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G228" s="70" t="s">
         <v>75</v>
@@ -13981,10 +13978,10 @@
         <v>0</v>
       </c>
       <c r="M228" s="54" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N228" s="53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="229" customFormat="1" ht="16.5" spans="1:22">
@@ -13995,7 +13992,7 @@
         <v>104100</v>
       </c>
       <c r="C229" s="69" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D229" s="30">
         <v>104100001</v>
@@ -14004,7 +14001,7 @@
         <v>13</v>
       </c>
       <c r="F229" s="53" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G229" s="70" t="s">
         <v>77</v>
@@ -14025,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="M229" s="54" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N229" s="53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="230" customFormat="1" ht="16.5" spans="1:22">
@@ -14039,7 +14036,7 @@
         <v>104200</v>
       </c>
       <c r="C230" s="69" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D230" s="30">
         <v>104200001</v>
@@ -14048,7 +14045,7 @@
         <v>11</v>
       </c>
       <c r="F230" s="53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G230" s="70" t="s">
         <v>84</v>
@@ -14069,10 +14066,10 @@
         <v>0</v>
       </c>
       <c r="M230" s="54" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N230" s="53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="231" customFormat="1" ht="16.5" spans="1:22">
@@ -14083,7 +14080,7 @@
         <v>104200</v>
       </c>
       <c r="C231" s="69" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D231" s="30">
         <v>104200001</v>
@@ -14092,7 +14089,7 @@
         <v>12</v>
       </c>
       <c r="F231" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G231" s="70" t="s">
         <v>75</v>
@@ -14113,10 +14110,10 @@
         <v>0</v>
       </c>
       <c r="M231" s="54" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N231" s="53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="232" customFormat="1" ht="16.5" spans="1:22">
@@ -14127,7 +14124,7 @@
         <v>104200</v>
       </c>
       <c r="C232" s="69" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D232" s="30">
         <v>104200001</v>
@@ -14136,7 +14133,7 @@
         <v>13</v>
       </c>
       <c r="F232" s="53" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G232" s="70" t="s">
         <v>77</v>
@@ -14157,10 +14154,10 @@
         <v>0</v>
       </c>
       <c r="M232" s="54" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N232" s="53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="233" s="2" customFormat="1" ht="16.5" spans="1:22">
@@ -14648,10 +14645,10 @@
         <v>21</v>
       </c>
       <c r="F242" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="G242" s="37" t="s">
         <v>180</v>
-      </c>
-      <c r="G242" s="37" t="s">
-        <v>181</v>
       </c>
       <c r="H242" s="17">
         <v>10000000</v>
@@ -15740,7 +15737,7 @@
         <v>21</v>
       </c>
       <c r="F263" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G263" s="25" t="s">
         <v>107</v>
@@ -16676,10 +16673,10 @@
         <v>21</v>
       </c>
       <c r="F281" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="G281" s="25" t="s">
         <v>169</v>
-      </c>
-      <c r="G281" s="25" t="s">
-        <v>170</v>
       </c>
       <c r="H281" s="34">
         <v>10000000</v>
@@ -16988,10 +16985,10 @@
         <v>21</v>
       </c>
       <c r="F287" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G287" s="25" t="s">
         <v>141</v>
-      </c>
-      <c r="G287" s="25" t="s">
-        <v>142</v>
       </c>
       <c r="H287" s="34">
         <v>10000000</v>
@@ -17135,7 +17132,7 @@
         <v>104000</v>
       </c>
       <c r="C290" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D290" s="41">
         <v>104000001</v>
@@ -17144,10 +17141,10 @@
         <v>21</v>
       </c>
       <c r="F290" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G290" s="25" t="s">
         <v>141</v>
-      </c>
-      <c r="G290" s="25" t="s">
-        <v>142</v>
       </c>
       <c r="H290" s="34">
         <v>10000000</v>
@@ -17187,7 +17184,7 @@
         <v>104000</v>
       </c>
       <c r="C291" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D291" s="41">
         <v>104000001</v>
@@ -17239,7 +17236,7 @@
         <v>104000</v>
       </c>
       <c r="C292" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D292" s="41">
         <v>104000001</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -566,7 +566,7 @@
     <t>篮球巨星</t>
   </si>
   <si>
-    <t>700:1</t>
+    <t>30:1</t>
   </si>
   <si>
     <t>40_20000|30_22000|20_24000|20_26000|10_28000|5_30000</t>
@@ -680,7 +680,7 @@
     <t>绿巨人</t>
   </si>
   <si>
-    <t>3500:1</t>
+    <t>48:1</t>
   </si>
   <si>
     <t>40_32000|30_34000|20_36000|20_38000|10_40000|5_42000</t>
@@ -1054,14 +1054,21 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1072,13 +1079,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -3881,7 +3881,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="35">
-        <v>700</v>
+        <v>30</v>
       </c>
       <c r="G32" s="25" t="s">
         <v>95</v>
@@ -5957,7 +5957,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="35">
-        <v>3500</v>
+        <v>48</v>
       </c>
       <c r="G71" s="25" t="s">
         <v>133</v>
